--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA11A448-C331-49FF-8A96-ADC49E2F8F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C7267E-3A19-4F75-8D1F-1881E7CD7D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -823,7 +823,63 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -4417,6 +4473,16 @@
       <sortCondition ref="R1"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="J2:J1048576">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+      <formula>0.10001</formula>
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+      <formula>0.001%</formula>
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C7267E-3A19-4F75-8D1F-1881E7CD7D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A769B3-B4EE-472D-B5BB-EE79E1078628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -498,6 +498,156 @@
   </si>
   <si>
     <t>0992.HK</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>SHOUGANG RES</t>
+  </si>
+  <si>
+    <t>Coking Coal</t>
+  </si>
+  <si>
+    <t>CHINA FOODS</t>
+  </si>
+  <si>
+    <t>Beverages - Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>CHINA TELECOM</t>
+  </si>
+  <si>
+    <t>MIDEA REAL EST</t>
+  </si>
+  <si>
+    <t>Real Estate - Development</t>
+  </si>
+  <si>
+    <t>HYSAN DEV</t>
+  </si>
+  <si>
+    <t>Real Estate Services</t>
+  </si>
+  <si>
+    <t>FUYAO GLASS</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>CONCH CEMENT</t>
+  </si>
+  <si>
+    <t>CH OVS G OCEANS</t>
+  </si>
+  <si>
+    <t>ANTA SPORTS</t>
+  </si>
+  <si>
+    <t>POP MART</t>
+  </si>
+  <si>
+    <t>CHINA WATER</t>
+  </si>
+  <si>
+    <t>CHINA UNICOM</t>
+  </si>
+  <si>
+    <t>CK ASSET</t>
+  </si>
+  <si>
+    <t>COSCO SHIP ENGY</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>COSCO SHIP INTL</t>
+  </si>
+  <si>
+    <t>HENGAN INT'L</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>CHOW TAI FOOK</t>
+  </si>
+  <si>
+    <t>KB LAMINATES</t>
+  </si>
+  <si>
+    <t>KINGBOARD HLDG</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>HKT-SS</t>
+  </si>
+  <si>
+    <t>TENCENT</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>CHINA LIT</t>
+  </si>
+  <si>
+    <t>ZIJIN MINING</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>PCCW</t>
+  </si>
+  <si>
+    <t>CHINA MER PORT</t>
+  </si>
+  <si>
+    <t>LEGENDHOLDING</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>CTIHK</t>
+  </si>
+  <si>
+    <t>Tobacco</t>
+  </si>
+  <si>
+    <t>YUM CHINA</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
+  </si>
+  <si>
+    <t>AUSNUTRIA</t>
+  </si>
+  <si>
+    <t>TINGYI</t>
+  </si>
+  <si>
+    <t>LEE &amp; MAN PAPER</t>
+  </si>
+  <si>
+    <t>Paper &amp; Paper Products</t>
+  </si>
+  <si>
+    <t>BYD ELECTRONIC</t>
+  </si>
+  <si>
+    <t>PRADA</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>LENOVO GROUP</t>
   </si>
   <si>
     <t>Company Evaluation Framework (MECE Scorecard)
@@ -532,6 +682,18 @@
 0 = CapEx &lt;5% revenue (5y avg)
 1 = CapEx 5-15% revenue
 2 = CapEx &gt;15% revenue
+Operating Margin (0-2):
+0 = &gt;20% margin (vs. industry avg)
+1 = 10-20%
+2 = &lt;10%
+Debt Level (0-2):
+0 = Debt/EBITDA &lt;2x
+1 = 2-4x
+2 = &gt;4x
+ROE (0-2):
+0 = &gt;15% (5y avg)
+1 = 10-15%
+2 = &lt;10%
 3. MOAT Components
 Switching Costs (0-2):
 0 = High (contractual/technical/data barriers)
@@ -553,158 +715,8 @@
 0 = Natural monopoly/duopoly
 1 = Regional dominance
 2 = No scale protection
-Total Score (0-28) = Sum of all categories
-Ideal Profile: Low Five Forces risk (0-5), Stable finances (0-2), Strong moat (0-5) → Total ≤12</t>
-  </si>
-  <si>
-    <t> </t>
-  </si>
-  <si>
-    <t>SHOUGANG RES</t>
-  </si>
-  <si>
-    <t>Coking Coal</t>
-  </si>
-  <si>
-    <t>CHINA FOODS</t>
-  </si>
-  <si>
-    <t>Beverages - Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>CHINA TELECOM</t>
-  </si>
-  <si>
-    <t>MIDEA REAL EST</t>
-  </si>
-  <si>
-    <t>Real Estate - Development</t>
-  </si>
-  <si>
-    <t>HYSAN DEV</t>
-  </si>
-  <si>
-    <t>Real Estate Services</t>
-  </si>
-  <si>
-    <t>FUYAO GLASS</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>CONCH CEMENT</t>
-  </si>
-  <si>
-    <t>CH OVS G OCEANS</t>
-  </si>
-  <si>
-    <t>ANTA SPORTS</t>
-  </si>
-  <si>
-    <t>POP MART</t>
-  </si>
-  <si>
-    <t>CHINA WATER</t>
-  </si>
-  <si>
-    <t>CHINA UNICOM</t>
-  </si>
-  <si>
-    <t>CK ASSET</t>
-  </si>
-  <si>
-    <t>COSCO SHIP ENGY</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>COSCO SHIP INTL</t>
-  </si>
-  <si>
-    <t>HENGAN INT'L</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>CHOW TAI FOOK</t>
-  </si>
-  <si>
-    <t>KB LAMINATES</t>
-  </si>
-  <si>
-    <t>KINGBOARD HLDG</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
-  </si>
-  <si>
-    <t>HKT-SS</t>
-  </si>
-  <si>
-    <t>TENCENT</t>
-  </si>
-  <si>
-    <t>Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>CHINA LIT</t>
-  </si>
-  <si>
-    <t>ZIJIN MINING</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>PCCW</t>
-  </si>
-  <si>
-    <t>CHINA MER PORT</t>
-  </si>
-  <si>
-    <t>LEGENDHOLDING</t>
-  </si>
-  <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>CTIHK</t>
-  </si>
-  <si>
-    <t>Tobacco</t>
-  </si>
-  <si>
-    <t>YUM CHINA</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>AUSNUTRIA</t>
-  </si>
-  <si>
-    <t>TINGYI</t>
-  </si>
-  <si>
-    <t>LEE &amp; MAN PAPER</t>
-  </si>
-  <si>
-    <t>Paper &amp; Paper Products</t>
-  </si>
-  <si>
-    <t>BYD ELECTRONIC</t>
-  </si>
-  <si>
-    <t>PRADA</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>LENOVO GROUP</t>
+Total Score (0-30): Sum of all 15 categories
+Ideal Profile: Low Five Forces risk (0-5), Stable finances (0-5), Strong moat (0-5) → Total ≤15</t>
   </si>
 </sst>
 </file>
@@ -823,14 +835,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -842,40 +847,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2591,10 +2562,10 @@
         <v>120</v>
       </c>
       <c r="C26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" t="s">
         <v>157</v>
-      </c>
-      <c r="D26" t="s">
-        <v>158</v>
       </c>
       <c r="E26">
         <v>2.63</v>
@@ -2645,10 +2616,10 @@
         <v>121</v>
       </c>
       <c r="C27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" t="s">
         <v>159</v>
-      </c>
-      <c r="D27" t="s">
-        <v>160</v>
       </c>
       <c r="E27">
         <v>3.12</v>
@@ -2699,7 +2670,7 @@
         <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
         <v>108</v>
@@ -2753,10 +2724,10 @@
         <v>123</v>
       </c>
       <c r="C29" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" t="s">
         <v>162</v>
-      </c>
-      <c r="D29" t="s">
-        <v>163</v>
       </c>
       <c r="E29">
         <v>3.86</v>
@@ -2861,10 +2832,10 @@
         <v>124</v>
       </c>
       <c r="C31" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" t="s">
         <v>164</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
       </c>
       <c r="E31">
         <v>12.78</v>
@@ -2915,10 +2886,10 @@
         <v>125</v>
       </c>
       <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" t="s">
         <v>166</v>
-      </c>
-      <c r="D32" t="s">
-        <v>167</v>
       </c>
       <c r="E32">
         <v>58.65</v>
@@ -2969,7 +2940,7 @@
         <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D33" t="s">
         <v>103</v>
@@ -3023,10 +2994,10 @@
         <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34">
         <v>1.71</v>
@@ -3077,7 +3048,7 @@
         <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -3131,7 +3102,7 @@
         <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" t="s">
         <v>94</v>
@@ -3185,7 +3156,7 @@
         <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
         <v>76</v>
@@ -3239,7 +3210,7 @@
         <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -3293,10 +3264,10 @@
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>32.5</v>
@@ -3347,10 +3318,10 @@
         <v>133</v>
       </c>
       <c r="C40" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" t="s">
         <v>175</v>
-      </c>
-      <c r="D40" t="s">
-        <v>176</v>
       </c>
       <c r="E40">
         <v>6.1</v>
@@ -3401,7 +3372,7 @@
         <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D41" t="s">
         <v>85</v>
@@ -3455,10 +3426,10 @@
         <v>135</v>
       </c>
       <c r="C42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" t="s">
         <v>178</v>
-      </c>
-      <c r="D42" t="s">
-        <v>179</v>
       </c>
       <c r="E42">
         <v>21.7</v>
@@ -3509,7 +3480,7 @@
         <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D43" t="s">
         <v>119</v>
@@ -3563,7 +3534,7 @@
         <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
         <v>114</v>
@@ -3617,10 +3588,10 @@
         <v>138</v>
       </c>
       <c r="C45" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" t="s">
         <v>182</v>
-      </c>
-      <c r="D45" t="s">
-        <v>183</v>
       </c>
       <c r="E45">
         <v>22</v>
@@ -3671,7 +3642,7 @@
         <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D46" t="s">
         <v>108</v>
@@ -3725,10 +3696,10 @@
         <v>140</v>
       </c>
       <c r="C47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" t="s">
         <v>185</v>
-      </c>
-      <c r="D47" t="s">
-        <v>186</v>
       </c>
       <c r="E47">
         <v>510</v>
@@ -3779,10 +3750,10 @@
         <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48">
         <v>27.55</v>
@@ -3833,10 +3804,10 @@
         <v>143</v>
       </c>
       <c r="C49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" t="s">
         <v>188</v>
-      </c>
-      <c r="D49" t="s">
-        <v>189</v>
       </c>
       <c r="E49">
         <v>18.440000000000001</v>
@@ -3887,7 +3858,7 @@
         <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
         <v>108</v>
@@ -3941,7 +3912,7 @@
         <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D51" t="s">
         <v>85</v>
@@ -3995,10 +3966,10 @@
         <v>146</v>
       </c>
       <c r="C52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D52" t="s">
         <v>192</v>
-      </c>
-      <c r="D52" t="s">
-        <v>193</v>
       </c>
       <c r="E52">
         <v>7.97</v>
@@ -4049,10 +4020,10 @@
         <v>147</v>
       </c>
       <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" t="s">
         <v>194</v>
-      </c>
-      <c r="D53" t="s">
-        <v>195</v>
       </c>
       <c r="E53">
         <v>33.75</v>
@@ -4103,10 +4074,10 @@
         <v>148</v>
       </c>
       <c r="C54" t="s">
+        <v>195</v>
+      </c>
+      <c r="D54" t="s">
         <v>196</v>
-      </c>
-      <c r="D54" t="s">
-        <v>197</v>
       </c>
       <c r="E54">
         <v>334</v>
@@ -4157,7 +4128,7 @@
         <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
         <v>97</v>
@@ -4211,7 +4182,7 @@
         <v>150</v>
       </c>
       <c r="C56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D56" t="s">
         <v>97</v>
@@ -4265,10 +4236,10 @@
         <v>151</v>
       </c>
       <c r="C57" t="s">
+        <v>199</v>
+      </c>
+      <c r="D57" t="s">
         <v>200</v>
-      </c>
-      <c r="D57" t="s">
-        <v>201</v>
       </c>
       <c r="E57">
         <v>2.1</v>
@@ -4319,7 +4290,7 @@
         <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
         <v>114</v>
@@ -4373,7 +4344,7 @@
         <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D59" t="s">
         <v>119</v>
@@ -4407,7 +4378,7 @@
         <v>4811702000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q59" s="12">
         <v>0.26583067696212276</v>
@@ -4418,10 +4389,10 @@
         <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E60">
         <v>9.2899999999999991</v>
@@ -4474,13 +4445,13 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J2:J1048576">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+      <formula>0.001%</formula>
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
       <formula>0.10001</formula>
       <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
-      <formula>0.001%</formula>
-      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5381,12 +5352,12 @@
     </row>
     <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
       <c r="B3" s="15" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A769B3-B4EE-472D-B5BB-EE79E1078628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B2357A-8BF3-A94E-B871-ACB641911FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cn_screener!$B$1:$R$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">hk_screener!$B$1:$R$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">hk_screener!$B$1:$R$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">us_screener!$B$1:$R$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -28,12 +28,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="201">
   <si>
     <t>Ticker</t>
   </si>
@@ -95,18 +106,12 @@
     <t>1193.HK</t>
   </si>
   <si>
-    <t>1857.HK</t>
-  </si>
-  <si>
     <t>2232.HK</t>
   </si>
   <si>
     <t>2111.HK</t>
   </si>
   <si>
-    <t>0709.HK</t>
-  </si>
-  <si>
     <t>1919.HK</t>
   </si>
   <si>
@@ -122,9 +127,6 @@
     <t>2155.HK</t>
   </si>
   <si>
-    <t>6858.HK</t>
-  </si>
-  <si>
     <t>1475.HK</t>
   </si>
   <si>
@@ -260,9 +262,6 @@
     <t>Utilities - Regulated Gas</t>
   </si>
   <si>
-    <t>CEB WATER</t>
-  </si>
-  <si>
     <t>Utilities - Regulated Water</t>
   </si>
   <si>
@@ -281,9 +280,6 @@
     <t>Textile Manufacturing</t>
   </si>
   <si>
-    <t>GIORDANO INT'L</t>
-  </si>
-  <si>
     <t>Apparel Retail</t>
   </si>
   <si>
@@ -314,13 +310,7 @@
     <t>MORIMATSU INTL</t>
   </si>
   <si>
-    <t>HONMAGOLF</t>
-  </si>
-  <si>
     <t>Leisure</t>
-  </si>
-  <si>
-    <t>JPY</t>
   </si>
   <si>
     <t>NISSIN FOODS</t>
@@ -717,6 +707,12 @@
 2 = No scale protection
 Total Score (0-30): Sum of all 15 categories
 Ideal Profile: Low Five Forces risk (0-5), Stable finances (0-5), Strong moat (0-5) → Total ≤15</t>
+  </si>
+  <si>
+    <t>0981.HK</t>
+  </si>
+  <si>
+    <t>0341.HK</t>
   </si>
 </sst>
 </file>
@@ -833,7 +829,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1185,26 +1181,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V60"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="B1:V58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
-    <col min="12" max="13" width="18.5625" style="13" customWidth="1"/>
+    <col min="12" max="13" width="18.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1218,34 +1214,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -1261,21 +1257,21 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E2">
         <v>14.76</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G2" s="7">
         <v>266968530944</v>
@@ -1287,7 +1283,7 @@
         <v>9.52</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
+        <f t="shared" ref="J2:J29" si="0">E2/I2-1</f>
         <v>0.55042016806722693</v>
       </c>
       <c r="K2" s="11">
@@ -1300,7 +1296,7 @@
         <v>269343749000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O2" s="6">
         <v>1.0683760683760684</v>
@@ -1315,21 +1311,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>2.8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3" s="7">
         <v>17363415040</v>
@@ -1354,7 +1350,7 @@
         <v>10569000000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O3" s="6">
         <v>1.0683760683760684</v>
@@ -1369,21 +1365,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4">
         <v>2.5099999999999998</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G4" s="7">
         <v>2609923072</v>
@@ -1408,7 +1404,7 @@
         <v>5008319000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O4" s="6">
         <v>1</v>
@@ -1423,279 +1419,279 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="E5">
-        <v>1.45</v>
+        <v>6.24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G5" s="7">
-        <v>2343446528</v>
+        <v>7609742336</v>
       </c>
       <c r="H5" s="6">
-        <v>2.2000000000000002</v>
+        <v>8.6</v>
       </c>
       <c r="I5" s="6">
-        <v>1.27</v>
+        <v>3.46</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.1417322834645669</v>
+        <v>0.80346820809248554</v>
       </c>
       <c r="K5" s="11">
-        <v>9.6551724137931047E-2</v>
+        <v>2.2596153846153842E-2</v>
       </c>
       <c r="L5" s="13">
-        <v>397000000</v>
+        <v>921702000</v>
       </c>
       <c r="M5" s="13">
-        <v>2024000000</v>
+        <v>5262544000</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O5" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P5" s="12">
-        <v>0.17633108095738884</v>
+        <v>0.19110296733656484</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.19614624505928854</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R5" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>6.24</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7">
-        <v>7609742336</v>
+        <v>144632446976</v>
       </c>
       <c r="H6" s="6">
-        <v>8.6</v>
+        <v>10.76</v>
       </c>
       <c r="I6" s="6">
-        <v>3.46</v>
+        <v>7.16</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.80346820809248554</v>
+        <v>0.238826815642458</v>
       </c>
       <c r="K6" s="11">
-        <v>2.2596153846153842E-2</v>
+        <v>5.4002254791431795E-2</v>
       </c>
       <c r="L6" s="13">
-        <v>921702000</v>
+        <v>32866046000</v>
       </c>
       <c r="M6" s="13">
-        <v>5262544000</v>
+        <v>215280386000</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O6" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P6" s="12">
-        <v>0.19110296733656484</v>
+        <v>0.19339190520925856</v>
       </c>
       <c r="Q6" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R6" s="14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7">
-        <v>8.8699999999999992</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G7" s="7">
-        <v>144632446976</v>
+        <v>72562425856</v>
       </c>
       <c r="H7" s="6">
-        <v>10.76</v>
+        <v>9.23</v>
       </c>
       <c r="I7" s="6">
-        <v>7.16</v>
+        <v>6.81</v>
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>0.238826815642458</v>
+        <v>0.23054331864904576</v>
       </c>
       <c r="K7" s="11">
-        <v>5.4002254791431795E-2</v>
+        <v>3.7708830548926014E-2</v>
       </c>
       <c r="L7" s="13">
-        <v>32866046000</v>
+        <v>13438000000</v>
       </c>
       <c r="M7" s="13">
-        <v>215280386000</v>
+        <v>88611000000</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O7" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.19339190520925856</v>
+        <v>0.20876044908337377</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R7" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>8.3800000000000008</v>
+        <v>15.08</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G8" s="7">
-        <v>72562425856</v>
+        <v>31470602240</v>
       </c>
       <c r="H8" s="6">
-        <v>9.23</v>
+        <v>15.48</v>
       </c>
       <c r="I8" s="6">
-        <v>6.81</v>
+        <v>7.96</v>
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.23054331864904576</v>
+        <v>0.89447236180904532</v>
       </c>
       <c r="K8" s="11">
-        <v>3.7708830548926014E-2</v>
+        <v>7.4270557029177731E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>13438000000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M8" s="13">
-        <v>88611000000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O8" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.20876044908337377</v>
+        <v>0.1667239217205066</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R8" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E9">
-        <v>15.08</v>
+        <v>4.76</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G9" s="7">
-        <v>31470602240</v>
+        <v>5043601408</v>
       </c>
       <c r="H9" s="6">
-        <v>15.48</v>
+        <v>6.4</v>
       </c>
       <c r="I9" s="6">
-        <v>7.96</v>
+        <v>3.97</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.89447236180904532</v>
+        <v>0.19899244332493682</v>
       </c>
       <c r="K9" s="11">
-        <v>7.4270557029177731E-2</v>
+        <v>0.10294117647058824</v>
       </c>
       <c r="L9" s="13">
-        <v>5451928473.2399998</v>
+        <v>866801000</v>
       </c>
       <c r="M9" s="13">
-        <v>25994816572.18</v>
+        <v>7530053000</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O9" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>0.1667239217205066</v>
+        <v>0.42327814020636439</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R9" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
@@ -1704,2743 +1700,2537 @@
         <v>99</v>
       </c>
       <c r="E10">
-        <v>4.76</v>
+        <v>14.54</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G10" s="7">
-        <v>5043601408</v>
+        <v>12101467136</v>
       </c>
       <c r="H10" s="6">
-        <v>6.4</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I10" s="6">
-        <v>3.97</v>
+        <v>12.12</v>
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>0.19899244332493682</v>
+        <v>0.1996699669966997</v>
       </c>
       <c r="K10" s="11">
-        <v>0.10294117647058824</v>
+        <v>1.0178817056396148E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>866801000</v>
+        <v>199557000</v>
       </c>
       <c r="M10" s="13">
-        <v>7530053000</v>
+        <v>1108087000</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="O10" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P10" s="12">
-        <v>0.42327814020636439</v>
+        <v>0.17178876691916867</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R10" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="E11">
-        <v>14.54</v>
+        <v>4.8</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G11" s="7">
-        <v>12101467136</v>
+        <v>13693536256</v>
       </c>
       <c r="H11" s="6">
-        <v>19.440000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="I11" s="6">
-        <v>12.12</v>
+        <v>3.22</v>
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.1996699669966997</v>
+        <v>0.49068322981366452</v>
       </c>
       <c r="K11" s="11">
-        <v>1.0178817056396148E-2</v>
+        <v>8.7500000000000008E-3</v>
       </c>
       <c r="L11" s="13">
-        <v>199557000</v>
+        <v>259348000</v>
       </c>
       <c r="M11" s="13">
-        <v>1108087000</v>
+        <v>1677627000</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O11" s="6">
         <v>7.6923076923076916</v>
       </c>
       <c r="P11" s="12">
-        <v>0.17178876691916867</v>
+        <v>0.16971440431040136</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R11" s="14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E12">
-        <v>4.8</v>
+        <v>4.43</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G12" s="7">
-        <v>13693536256</v>
+        <v>51084984320</v>
       </c>
       <c r="H12" s="6">
-        <v>6.21</v>
+        <v>5.14</v>
       </c>
       <c r="I12" s="6">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.49068322981366452</v>
+        <v>0.28034682080924855</v>
       </c>
       <c r="K12" s="11">
-        <v>8.7500000000000008E-3</v>
+        <v>5.3273137697516931E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>259348000</v>
+        <v>4734613000</v>
       </c>
       <c r="M12" s="13">
-        <v>1677627000</v>
+        <v>16213395000</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="O12" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.16971440431040136</v>
+        <v>0.1056668547805296</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R12" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E13">
-        <v>4.43</v>
+        <v>6.05</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G13" s="7">
-        <v>51084984320</v>
+        <v>54856863744</v>
       </c>
       <c r="H13" s="6">
-        <v>5.14</v>
+        <v>7.38</v>
       </c>
       <c r="I13" s="6">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.28034682080924855</v>
+        <v>0.78466076696165188</v>
       </c>
       <c r="K13" s="11">
-        <v>5.3273137697516931E-2</v>
+        <v>5.0743801652892565E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>4734613000</v>
+        <v>5594372000</v>
       </c>
       <c r="M13" s="13">
-        <v>16213395000</v>
+        <v>26933044000</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O13" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.1056668547805296</v>
+        <v>0.12978201086967631</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E14">
-        <v>6.05</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G14" s="7">
-        <v>54856863744</v>
+        <v>60313841664</v>
       </c>
       <c r="H14" s="6">
-        <v>7.38</v>
+        <v>5.77</v>
       </c>
       <c r="I14" s="6">
-        <v>3.39</v>
+        <v>4.12</v>
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.78466076696165188</v>
+        <v>0.24029126213592233</v>
       </c>
       <c r="K14" s="11">
-        <v>5.0743801652892565E-2</v>
+        <v>4.6575342465753421E-2</v>
       </c>
       <c r="L14" s="13">
-        <v>5594372000</v>
+        <v>5687261000</v>
       </c>
       <c r="M14" s="13">
-        <v>26933044000</v>
+        <v>21716551000</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O14" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.12978201086967631</v>
+        <v>0.10616681847056487</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.26188601495697911</v>
       </c>
       <c r="R14" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E15">
-        <v>5.1100000000000003</v>
+        <v>387.2</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G15" s="7">
-        <v>60313841664</v>
+        <v>489358852096</v>
       </c>
       <c r="H15" s="6">
-        <v>5.77</v>
+        <v>398.6</v>
       </c>
       <c r="I15" s="6">
-        <v>4.12</v>
+        <v>218.4</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.24029126213592233</v>
+        <v>0.77289377289377281</v>
       </c>
       <c r="K15" s="11">
-        <v>4.6575342465753421E-2</v>
+        <v>2.3915289256198347E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>5687261000</v>
+        <v>20744000000</v>
       </c>
       <c r="M15" s="13">
-        <v>21716551000</v>
+        <v>53852000000</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O15" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P15" s="12">
-        <v>0.10616681847056487</v>
+        <v>5.8222585692903818E-2</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.26188601495697911</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R15" s="14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E16">
-        <v>3.33</v>
+        <v>5.76</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G16" s="7">
-        <v>2016787712</v>
+        <v>4488203776</v>
       </c>
       <c r="H16" s="6">
-        <v>3.68</v>
+        <v>8.09</v>
       </c>
       <c r="I16" s="6">
-        <v>3.14</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>6.0509554140127264E-2</v>
+        <v>0.43283582089552253</v>
       </c>
       <c r="K16" s="11">
-        <v>0.45045045045045046</v>
+        <v>2.9513888888888892E-2</v>
       </c>
       <c r="L16" s="13">
-        <v>5342751000</v>
+        <v>437453000</v>
       </c>
       <c r="M16" s="13">
-        <v>35707835000</v>
+        <v>4911072000</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="O16" s="6">
-        <v>5.3931905576019713E-2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.17491165408885032</v>
+        <v>0.19895488336167233</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.14962405309647028</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R16" s="14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="E17">
-        <v>387.2</v>
+        <v>12.16</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G17" s="7">
-        <v>489358852096</v>
+        <v>57380364288</v>
       </c>
       <c r="H17" s="6">
-        <v>398.6</v>
+        <v>13.56</v>
       </c>
       <c r="I17" s="6">
-        <v>218.4</v>
+        <v>7.51</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.77289377289377281</v>
+        <v>0.61917443408788286</v>
       </c>
       <c r="K17" s="11">
-        <v>2.3915289256198347E-2</v>
+        <v>3.6019736842105264E-2</v>
       </c>
       <c r="L17" s="13">
-        <v>20744000000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M17" s="13">
-        <v>53852000000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O17" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>5.8222585692903818E-2</v>
+        <v>0.13294201683080747</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.38520389214885242</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R17" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="E18">
-        <v>5.76</v>
+        <v>49.45</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G18" s="7">
-        <v>4488203776</v>
+        <v>134003572736</v>
       </c>
       <c r="H18" s="6">
-        <v>8.09</v>
+        <v>82.25</v>
       </c>
       <c r="I18" s="6">
-        <v>4.0199999999999996</v>
+        <v>37.85</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.43283582089552253</v>
+        <v>0.30647291941875832</v>
       </c>
       <c r="K18" s="11">
-        <v>2.9513888888888892E-2</v>
+        <v>2.1233569261880688E-2</v>
       </c>
       <c r="L18" s="13">
-        <v>437453000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M18" s="13">
-        <v>4911072000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O18" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P18" s="12">
-        <v>0.19895488336167233</v>
+        <v>6.6311605293517414E-2</v>
       </c>
       <c r="Q18" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R18" s="14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E19">
-        <v>21.85</v>
+        <v>1.42</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G19" s="7">
-        <v>49604308992</v>
+        <v>7756792320</v>
       </c>
       <c r="H19" s="6">
-        <v>35.200000000000003</v>
+        <v>1.82</v>
       </c>
       <c r="I19" s="6">
-        <v>19.940000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>9.578736208625882E-2</v>
+        <v>0.75308641975308621</v>
       </c>
       <c r="K19" s="11">
-        <v>4.3478260869565209E-2</v>
+        <v>2.3943661971830989E-2</v>
       </c>
       <c r="L19" s="13">
-        <v>8486605000</v>
+        <v>1384865000</v>
       </c>
       <c r="M19" s="13">
-        <v>64172826000</v>
+        <v>23827484000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O19" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P19" s="12">
-        <v>0.12937271786140314</v>
+        <v>7.8406950129255665E-2</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.13224608497060733</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R19" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="E20">
-        <v>12.16</v>
+        <v>6.8</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G20" s="7">
-        <v>57380364288</v>
+        <v>7096072192</v>
       </c>
       <c r="H20" s="6">
-        <v>13.56</v>
+        <v>6.93</v>
       </c>
       <c r="I20" s="6">
-        <v>7.51</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="0"/>
-        <v>0.61917443408788286</v>
+        <v>0.691542288557214</v>
       </c>
       <c r="K20" s="11">
-        <v>3.6019736842105264E-2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="13">
-        <v>3967214824.1399999</v>
+        <v>303335000</v>
       </c>
       <c r="M20" s="13">
-        <v>41038539262.660004</v>
+        <v>3620162000</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O20" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P20" s="12">
-        <v>0.13294201683080747</v>
+        <v>5.0538017065101339E-2</v>
       </c>
       <c r="Q20" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R20" s="14">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="E21">
-        <v>49.45</v>
+        <v>11.58</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G21" s="7">
-        <v>134003572736</v>
+        <v>203817271296</v>
       </c>
       <c r="H21" s="6">
-        <v>82.25</v>
+        <v>12.46</v>
       </c>
       <c r="I21" s="6">
-        <v>37.85</v>
+        <v>9.1</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.30647291941875832</v>
+        <v>0.27252747252747267</v>
       </c>
       <c r="K21" s="11">
-        <v>2.1233569261880688E-2</v>
+        <v>3.6010362694300517E-2</v>
       </c>
       <c r="L21" s="13">
-        <v>6350637223.7200003</v>
+        <v>16758000000</v>
       </c>
       <c r="M21" s="13">
-        <v>57896384836.860001</v>
+        <v>269590000000</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O21" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>6.6311605293517414E-2</v>
+        <v>5.9696501972347493E-2</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.10968970241604512</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R21" s="14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="E22">
-        <v>1.37</v>
+        <v>2.63</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22" s="7">
-        <v>3919405312</v>
+        <v>13389514752</v>
       </c>
       <c r="H22" s="6">
-        <v>1.73</v>
+        <v>3.64</v>
       </c>
       <c r="I22" s="6">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="J22" s="12">
         <f t="shared" si="0"/>
-        <v>3.7878787878787845E-2</v>
+        <v>0.17937219730941689</v>
       </c>
       <c r="K22" s="11">
-        <v>8.6861313868613121E-2</v>
+        <v>0.11406844106463879</v>
       </c>
       <c r="L22" s="13">
-        <v>1987136000</v>
+        <v>2527643000</v>
       </c>
       <c r="M22" s="13">
-        <v>29031712000</v>
+        <v>16480074000</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O22" s="6">
         <v>1</v>
       </c>
       <c r="P22" s="12">
-        <v>0.10749808518062026</v>
+        <v>0.43903173388000094</v>
       </c>
       <c r="Q22" s="12">
-        <v>6.8447082969133891E-2</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R22" s="14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="E23">
-        <v>1.42</v>
+        <v>3.12</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G23" s="7">
-        <v>7756792320</v>
+        <v>8727326720</v>
       </c>
       <c r="H23" s="6">
-        <v>1.82</v>
+        <v>3.35</v>
       </c>
       <c r="I23" s="6">
-        <v>0.81</v>
+        <v>2.36</v>
       </c>
       <c r="J23" s="12">
         <f t="shared" si="0"/>
-        <v>0.75308641975308621</v>
+        <v>0.32203389830508478</v>
       </c>
       <c r="K23" s="11">
-        <v>2.3943661971830989E-2</v>
+        <v>4.9038461538461538E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>1384865000</v>
+        <v>1871151000</v>
       </c>
       <c r="M23" s="13">
-        <v>23827484000</v>
+        <v>6461978000</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O23" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>7.8406950129255665E-2</v>
+        <v>0.44131348531551057</v>
       </c>
       <c r="Q23" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>0.28956319566547578</v>
       </c>
       <c r="R23" s="14">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24">
-        <v>6.8</v>
+        <v>5.86</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G24" s="7">
-        <v>7096072192</v>
+        <v>755119620096</v>
       </c>
       <c r="H24" s="6">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="I24" s="6">
-        <v>4.0199999999999996</v>
+        <v>4.08</v>
       </c>
       <c r="J24" s="12">
         <f t="shared" si="0"/>
-        <v>0.691542288557214</v>
+        <v>0.43627450980392157</v>
       </c>
       <c r="K24" s="11">
-        <v>0</v>
+        <v>4.4368600682593858E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>303335000</v>
+        <v>44563000000</v>
       </c>
       <c r="M24" s="13">
-        <v>3620162000</v>
+        <v>463922000000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O24" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>5.0538017065101339E-2</v>
+        <v>6.5024342087621825E-2</v>
       </c>
       <c r="Q24" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R24" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E25">
-        <v>11.58</v>
+        <v>3.86</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G25" s="7">
-        <v>203817271296</v>
+        <v>5540682752</v>
       </c>
       <c r="H25" s="6">
-        <v>12.46</v>
+        <v>7.92</v>
       </c>
       <c r="I25" s="6">
-        <v>9.1</v>
+        <v>2.36</v>
       </c>
       <c r="J25" s="12">
         <f t="shared" si="0"/>
-        <v>0.27252747252747267</v>
+        <v>0.63559322033898313</v>
       </c>
       <c r="K25" s="11">
-        <v>3.6010362694300517E-2</v>
+        <v>6.5803108808290156E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>16758000000</v>
+        <v>811880000</v>
       </c>
       <c r="M25" s="13">
-        <v>269590000000</v>
+        <v>5532140000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O25" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P25" s="12">
-        <v>5.9696501972347493E-2</v>
+        <v>0.16283852472600896</v>
       </c>
       <c r="Q25" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R25" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>71</v>
       </c>
       <c r="E26">
-        <v>2.63</v>
+        <v>21.85</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G26" s="7">
-        <v>13389514752</v>
+        <v>49604308992</v>
       </c>
       <c r="H26" s="6">
-        <v>3.64</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="I26" s="6">
-        <v>2.23</v>
+        <v>19.940000000000001</v>
       </c>
       <c r="J26" s="12">
         <f t="shared" si="0"/>
-        <v>0.17937219730941689</v>
+        <v>9.578736208625882E-2</v>
       </c>
       <c r="K26" s="11">
-        <v>0.11406844106463879</v>
+        <v>4.3478260869565209E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>2527643000</v>
+        <v>8486605000</v>
       </c>
       <c r="M26" s="13">
-        <v>16480074000</v>
+        <v>64172826000</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O26" s="6">
         <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>0.43903173388000094</v>
+        <v>0.12937271786140314</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.13224608497060733</v>
       </c>
       <c r="R26" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E27">
-        <v>3.12</v>
+        <v>12.78</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G27" s="7">
-        <v>8727326720</v>
+        <v>13125187584</v>
       </c>
       <c r="H27" s="6">
-        <v>3.35</v>
+        <v>14.5</v>
       </c>
       <c r="I27" s="6">
-        <v>2.36</v>
+        <v>10.36</v>
       </c>
       <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>0.32203389830508478</v>
+        <v>0.23359073359073368</v>
       </c>
       <c r="K27" s="11">
-        <v>4.9038461538461538E-2</v>
+        <v>8.4507042253521139E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>1871151000</v>
+        <v>984000000</v>
       </c>
       <c r="M27" s="13">
-        <v>6461978000</v>
+        <v>101944000000</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O27" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P27" s="12">
-        <v>0.44131348531551057</v>
+        <v>2.5843602157681757E-2</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.28956319566547578</v>
+        <v>9.6523581574197593E-3</v>
       </c>
       <c r="R27" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="E28">
-        <v>5.86</v>
+        <v>58.65</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G28" s="7">
-        <v>755119620096</v>
+        <v>164297998336</v>
       </c>
       <c r="H28" s="6">
-        <v>6.98</v>
+        <v>60</v>
       </c>
       <c r="I28" s="6">
-        <v>4.08</v>
+        <v>38.4</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="0"/>
-        <v>0.43627450980392157</v>
+        <v>0.52734375</v>
       </c>
       <c r="K28" s="11">
-        <v>4.4368600682593858E-2</v>
+        <v>3.0690537084398978E-2</v>
       </c>
       <c r="L28" s="13">
-        <v>44563000000</v>
+        <v>8955723006</v>
       </c>
       <c r="M28" s="13">
-        <v>463922000000</v>
+        <v>47495870210</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O28" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>6.5024342087621825E-2</v>
+        <v>5.9707343267352463E-2</v>
       </c>
       <c r="Q28" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R28" s="14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="E29">
-        <v>3.86</v>
+        <v>20.65</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G29" s="7">
-        <v>5540682752</v>
+        <v>128460144640</v>
       </c>
       <c r="H29" s="6">
-        <v>7.92</v>
+        <v>26.6</v>
       </c>
       <c r="I29" s="6">
-        <v>2.36</v>
+        <v>16.02</v>
       </c>
       <c r="J29" s="12">
         <f t="shared" si="0"/>
-        <v>0.63559322033898313</v>
+        <v>0.28901373283395748</v>
       </c>
       <c r="K29" s="11">
-        <v>6.5803108808290156E-2</v>
+        <v>3.4382566585956419E-2</v>
       </c>
       <c r="L29" s="13">
-        <v>811880000</v>
+        <v>10795274825</v>
       </c>
       <c r="M29" s="13">
-        <v>5532140000</v>
+        <v>215275428010</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O29" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P29" s="12">
-        <v>0.16283852472600896</v>
+        <v>0.13569108016282685</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.14675695119790894</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R29" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="E30">
-        <v>21.85</v>
+        <v>1.71</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G30" s="7">
-        <v>49604308992</v>
+        <v>6086522880</v>
       </c>
       <c r="H30" s="6">
-        <v>35.200000000000003</v>
+        <v>2.95</v>
       </c>
       <c r="I30" s="6">
-        <v>19.940000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
-        <v>9.578736208625882E-2</v>
+        <f t="shared" ref="J30:J56" si="1">E30/I30-1</f>
+        <v>0.24817518248175174</v>
       </c>
       <c r="K30" s="11">
-        <v>4.3478260869565209E-2</v>
+        <v>5.4970760233918128E-2</v>
       </c>
       <c r="L30" s="13">
-        <v>8486605000</v>
+        <v>2220197000</v>
       </c>
       <c r="M30" s="13">
-        <v>64172826000</v>
+        <v>71097505000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O30" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.12937271786140314</v>
+        <v>0.12244255356679254</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.13224608497060733</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R30" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31">
+        <v>92.25</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="7">
+        <v>257193918464</v>
+      </c>
+      <c r="H31" s="6">
+        <v>107.5</v>
+      </c>
+      <c r="I31" s="6">
+        <v>65.55</v>
+      </c>
+      <c r="J31" s="12">
+        <f t="shared" si="1"/>
+        <v>0.40732265446224258</v>
+      </c>
+      <c r="K31" s="11">
+        <v>2.4043360433604336E-2</v>
+      </c>
+      <c r="L31" s="13">
+        <v>22510000000</v>
+      </c>
+      <c r="M31" s="13">
+        <v>82545000000</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O31" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P31" s="12">
+        <v>8.7429866091066066E-2</v>
+      </c>
+      <c r="Q31" s="12">
+        <v>0.27269973953601068</v>
+      </c>
+      <c r="R31" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" t="s">
         <v>163</v>
       </c>
-      <c r="D31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31">
-        <v>12.78</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="7">
-        <v>13125187584</v>
-      </c>
-      <c r="H31" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="I31" s="6">
-        <v>10.36</v>
-      </c>
-      <c r="J31" s="12">
-        <f t="shared" si="0"/>
-        <v>0.23359073359073368</v>
-      </c>
-      <c r="K31" s="11">
-        <v>8.4507042253521139E-2</v>
-      </c>
-      <c r="L31" s="13">
-        <v>984000000</v>
-      </c>
-      <c r="M31" s="13">
-        <v>101944000000</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O31" s="6">
-        <v>1</v>
-      </c>
-      <c r="P31" s="12">
-        <v>2.5843602157681757E-2</v>
-      </c>
-      <c r="Q31" s="12">
-        <v>9.6523581574197593E-3</v>
-      </c>
-      <c r="R31" s="14">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="B32" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" t="s">
-        <v>165</v>
-      </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="E32">
-        <v>58.65</v>
+        <v>221.2</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G32" s="7">
-        <v>164297998336</v>
+        <v>293788975104</v>
       </c>
       <c r="H32" s="6">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="I32" s="6">
-        <v>38.4</v>
+        <v>34.4</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
-        <v>0.52734375</v>
+        <f t="shared" si="1"/>
+        <v>5.4302325581395348</v>
       </c>
       <c r="K32" s="11">
-        <v>3.0690537084398978E-2</v>
+        <v>3.6844484629294755E-3</v>
       </c>
       <c r="L32" s="13">
-        <v>8955723006</v>
+        <v>4414795000</v>
       </c>
       <c r="M32" s="13">
-        <v>47495870210</v>
+        <v>10683505000</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O32" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P32" s="12">
-        <v>5.9707343267352463E-2</v>
+        <v>1.6360665114900662E-2</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.41323470153287706</v>
       </c>
       <c r="R32" s="14">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E33">
-        <v>20.65</v>
+        <v>5.86</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G33" s="7">
-        <v>128460144640</v>
+        <v>9532520448</v>
       </c>
       <c r="H33" s="6">
-        <v>26.6</v>
+        <v>7.05</v>
       </c>
       <c r="I33" s="6">
-        <v>16.02</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
-        <v>0.28901373283395748</v>
+        <f t="shared" si="1"/>
+        <v>0.37236533957845452</v>
       </c>
       <c r="K33" s="11">
-        <v>3.4382566585956419E-2</v>
+        <v>4.778156996587031E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>10795274825</v>
+        <v>4094312000</v>
       </c>
       <c r="M33" s="13">
-        <v>215275428010</v>
+        <v>37637054000</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O33" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P33" s="12">
-        <v>0.13569108016282685</v>
+        <v>0.13670988611818785</v>
       </c>
       <c r="Q33" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R33" s="14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="E34">
-        <v>1.71</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G34" s="7">
-        <v>6086522880</v>
+        <v>292210900992</v>
       </c>
       <c r="H34" s="6">
-        <v>2.95</v>
+        <v>11.56</v>
       </c>
       <c r="I34" s="6">
-        <v>1.37</v>
+        <v>5.88</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J60" si="1">E34/I34-1</f>
-        <v>0.24817518248175174</v>
+        <f t="shared" si="1"/>
+        <v>0.62414965986394577</v>
       </c>
       <c r="K34" s="11">
-        <v>5.4970760233918128E-2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="13">
-        <v>2220197000</v>
+        <v>26994000000</v>
       </c>
       <c r="M34" s="13">
-        <v>71097505000</v>
+        <v>363169000000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O34" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>0.12244255356679254</v>
+        <v>9.478416599662691E-2</v>
       </c>
       <c r="Q34" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R34" s="14">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="E35">
-        <v>92.25</v>
+        <v>32.5</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G35" s="7">
-        <v>257193918464</v>
+        <v>113742856192</v>
       </c>
       <c r="H35" s="6">
-        <v>107.5</v>
+        <v>37.25</v>
       </c>
       <c r="I35" s="6">
-        <v>65.55</v>
+        <v>28.1</v>
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
-        <v>0.40732265446224258</v>
+        <v>0.15658362989323837</v>
       </c>
       <c r="K35" s="11">
-        <v>2.4043360433604336E-2</v>
+        <v>5.3538461538461535E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>22510000000</v>
+        <v>16863000000</v>
       </c>
       <c r="M35" s="13">
-        <v>82545000000</v>
+        <v>448320000000</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O35" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P35" s="12">
-        <v>8.7429866091066066E-2</v>
+        <v>0.12462875203325478</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.27269973953601068</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="E36">
-        <v>221.2</v>
+        <v>6.1</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G36" s="7">
-        <v>293788975104</v>
+        <v>46354022400</v>
       </c>
       <c r="H36" s="6">
-        <v>229</v>
+        <v>11.72</v>
       </c>
       <c r="I36" s="6">
-        <v>34.4</v>
+        <v>5</v>
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
-        <v>5.4302325581395348</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="K36" s="11">
-        <v>3.6844484629294755E-3</v>
+        <v>7.0491803278688522E-2</v>
       </c>
       <c r="L36" s="13">
-        <v>4414795000</v>
+        <v>6749146000</v>
       </c>
       <c r="M36" s="13">
-        <v>10683505000</v>
+        <v>70848374000</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O36" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>1.6360665114900662E-2</v>
+        <v>9.1338900700346573E-2</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.41323470153287706</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R36" s="14">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E37">
-        <v>5.86</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G37" s="7">
-        <v>9532520448</v>
+        <v>7168593408</v>
       </c>
       <c r="H37" s="6">
-        <v>7.05</v>
+        <v>5.04</v>
       </c>
       <c r="I37" s="6">
-        <v>4.2699999999999996</v>
+        <v>3.45</v>
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
-        <v>0.37236533957845452</v>
+        <v>0.4173913043478259</v>
       </c>
       <c r="K37" s="11">
-        <v>4.778156996587031E-2</v>
+        <v>9.815950920245399E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>4094312000</v>
+        <v>784607000</v>
       </c>
       <c r="M37" s="13">
-        <v>37637054000</v>
+        <v>7872586000</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O37" s="6">
         <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.13670988611818785</v>
+        <v>0.54182145938124371</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.10878407220713927</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R37" s="14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E38">
-        <v>9.5500000000000007</v>
+        <v>21.7</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G38" s="7">
-        <v>292210900992</v>
+        <v>24714563584</v>
       </c>
       <c r="H38" s="6">
-        <v>11.56</v>
+        <v>28.75</v>
       </c>
       <c r="I38" s="6">
-        <v>5.88</v>
+        <v>19.52</v>
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
-        <v>0.62414965986394577</v>
+        <v>0.11168032786885251</v>
       </c>
       <c r="K38" s="11">
-        <v>0</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>26994000000</v>
+        <v>3446618000</v>
       </c>
       <c r="M38" s="13">
-        <v>363169000000</v>
+        <v>34010798000</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O38" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>9.478416599662691E-2</v>
+        <v>0.15677822911473666</v>
       </c>
       <c r="Q38" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R38" s="14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="E39">
-        <v>32.5</v>
+        <v>10.96</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G39" s="7">
-        <v>113742856192</v>
+        <v>109460914176</v>
       </c>
       <c r="H39" s="6">
-        <v>37.25</v>
+        <v>11.56</v>
       </c>
       <c r="I39" s="6">
-        <v>28.1</v>
+        <v>5.83</v>
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
-        <v>0.15658362989323837</v>
+        <v>0.87993138936535176</v>
       </c>
       <c r="K39" s="11">
-        <v>5.3538461538461535E-2</v>
+        <v>4.5620437956204379E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>16863000000</v>
+        <v>9432900000</v>
       </c>
       <c r="M39" s="13">
-        <v>448320000000</v>
+        <v>54338700000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O39" s="6">
         <v>1</v>
       </c>
       <c r="P39" s="12">
-        <v>0.12462875203325478</v>
+        <v>7.1647857486001235E-2</v>
       </c>
       <c r="Q39" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>0.17359450999011755</v>
       </c>
       <c r="R39" s="14">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="E40">
-        <v>6.1</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G40" s="7">
-        <v>46354022400</v>
+        <v>26426400768</v>
       </c>
       <c r="H40" s="6">
-        <v>11.72</v>
+        <v>10.1</v>
       </c>
       <c r="I40" s="6">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J40" s="12">
         <f t="shared" si="1"/>
-        <v>0.21999999999999997</v>
+        <v>0.51250000000000018</v>
       </c>
       <c r="K40" s="11">
-        <v>7.0491803278688522E-2</v>
+        <v>3.7780401416765051E-2</v>
       </c>
       <c r="L40" s="13">
-        <v>6749146000</v>
+        <v>1990539000</v>
       </c>
       <c r="M40" s="13">
-        <v>70848374000</v>
+        <v>18620709000</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O40" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P40" s="12">
-        <v>9.1338900700346573E-2</v>
+        <v>6.8216437993046053E-2</v>
       </c>
       <c r="Q40" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R40" s="14">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="E41">
-        <v>4.8899999999999997</v>
+        <v>22</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G41" s="7">
-        <v>7168593408</v>
+        <v>24382820352</v>
       </c>
       <c r="H41" s="6">
-        <v>5.04</v>
+        <v>24.55</v>
       </c>
       <c r="I41" s="6">
-        <v>3.45</v>
+        <v>14.52</v>
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
-        <v>0.4173913043478259</v>
+        <v>0.51515151515151514</v>
       </c>
       <c r="K41" s="11">
-        <v>9.815950920245399E-2</v>
+        <v>4.2727272727272725E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>784607000</v>
+        <v>3838344000</v>
       </c>
       <c r="M41" s="13">
-        <v>7872586000</v>
+        <v>81520873000</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O41" s="6">
         <v>1</v>
       </c>
       <c r="P41" s="12">
-        <v>0.54182145938124371</v>
+        <v>9.0954347828542711E-2</v>
       </c>
       <c r="Q41" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="E42">
-        <v>21.7</v>
+        <v>11.26</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G42" s="7">
-        <v>24714563584</v>
+        <v>85298552832</v>
       </c>
       <c r="H42" s="6">
-        <v>28.75</v>
+        <v>11.5</v>
       </c>
       <c r="I42" s="6">
-        <v>19.52</v>
+        <v>8.48</v>
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
-        <v>0.11168032786885251</v>
+        <v>0.32783018867924518</v>
       </c>
       <c r="K42" s="11">
-        <v>6.4516129032258063E-2</v>
+        <v>6.99822380106572E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>3446618000</v>
+        <v>8154000000</v>
       </c>
       <c r="M42" s="13">
-        <v>34010798000</v>
+        <v>79588000000</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O42" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P42" s="12">
-        <v>0.15677822911473666</v>
+        <v>6.4403740674301074E-2</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R42" s="14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="E43">
-        <v>10.96</v>
+        <v>510</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G43" s="7">
-        <v>109460914176</v>
+        <v>4642591211520</v>
       </c>
       <c r="H43" s="6">
-        <v>11.56</v>
+        <v>547</v>
       </c>
       <c r="I43" s="6">
-        <v>5.83</v>
+        <v>349</v>
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
-        <v>0.87993138936535176</v>
+        <v>0.4613180515759312</v>
       </c>
       <c r="K43" s="11">
-        <v>4.5620437956204379E-2</v>
+        <v>8.2921568627450978E-3</v>
       </c>
       <c r="L43" s="13">
-        <v>9432900000</v>
+        <v>253932000000</v>
       </c>
       <c r="M43" s="13">
-        <v>54338700000</v>
+        <v>1312163000000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O43" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>7.1647857486001235E-2</v>
+        <v>5.5552123649375187E-2</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.17359450999011755</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R43" s="14">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="E44">
-        <v>8.4700000000000006</v>
+        <v>27.55</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G44" s="7">
-        <v>26426400768</v>
+        <v>28136538112</v>
       </c>
       <c r="H44" s="6">
-        <v>10.1</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6">
-        <v>5.6</v>
+        <v>22.4</v>
       </c>
       <c r="J44" s="12">
         <f t="shared" si="1"/>
-        <v>0.51250000000000018</v>
+        <v>0.22991071428571441</v>
       </c>
       <c r="K44" s="11">
-        <v>3.7780401416765051E-2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="13">
-        <v>1990539000</v>
+        <v>-90314000</v>
       </c>
       <c r="M44" s="13">
-        <v>18620709000</v>
+        <v>18374441000</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O44" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>6.8216437993046053E-2</v>
+        <v>-3.8865083660601265E-3</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.10689920561026972</v>
+        <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R44" s="14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C45" t="s">
+        <v>180</v>
+      </c>
+      <c r="D45" t="s">
         <v>181</v>
       </c>
-      <c r="D45" t="s">
-        <v>182</v>
-      </c>
       <c r="E45">
-        <v>22</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G45" s="7">
-        <v>24382820352</v>
+        <v>520091009024</v>
       </c>
       <c r="H45" s="6">
-        <v>24.55</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="I45" s="6">
-        <v>14.52</v>
+        <v>13.52</v>
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
-        <v>0.51515151515151514</v>
+        <v>0.36390532544378718</v>
       </c>
       <c r="K45" s="11">
-        <v>4.2727272727272725E-2</v>
+        <v>2.0607375271149673E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>3838344000</v>
+        <v>52374992116</v>
       </c>
       <c r="M45" s="13">
-        <v>81520873000</v>
+        <v>269573093476</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O45" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>9.0954347828542711E-2</v>
+        <v>8.6837688985510905E-2</v>
       </c>
       <c r="Q45" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>0.19428864891763736</v>
       </c>
       <c r="R45" s="14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E46">
-        <v>11.26</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G46" s="7">
-        <v>85298552832</v>
+        <v>39479406592</v>
       </c>
       <c r="H46" s="6">
-        <v>11.5</v>
+        <v>5.49</v>
       </c>
       <c r="I46" s="6">
-        <v>8.48</v>
+        <v>3.8</v>
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
-        <v>0.32783018867924518</v>
+        <v>0.34210526315789469</v>
       </c>
       <c r="K46" s="11">
-        <v>6.99822380106572E-2</v>
+        <v>7.509803921568628E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>8154000000</v>
+        <v>5474000000</v>
       </c>
       <c r="M46" s="13">
-        <v>79588000000</v>
+        <v>59407000000</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O46" s="6">
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>6.4403740674301074E-2</v>
+        <v>6.0066448420561427E-2</v>
       </c>
       <c r="Q46" s="12">
-        <v>0.10245263104990703</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="E47">
-        <v>510</v>
+        <v>14.5</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G47" s="7">
-        <v>4642591211520</v>
+        <v>60871147520</v>
       </c>
       <c r="H47" s="6">
-        <v>547</v>
+        <v>14.56</v>
       </c>
       <c r="I47" s="6">
-        <v>349</v>
+        <v>10.98</v>
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
-        <v>0.4613180515759312</v>
+        <v>0.32058287795992713</v>
       </c>
       <c r="K47" s="11">
-        <v>8.2921568627450978E-3</v>
+        <v>6.1103448275862067E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>253932000000</v>
+        <v>11996000000</v>
       </c>
       <c r="M47" s="13">
-        <v>1312163000000</v>
+        <v>138296000000</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O47" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>5.5552123649375187E-2</v>
+        <v>0.14279397368178412</v>
       </c>
       <c r="Q47" s="12">
-        <v>0.19352168899747973</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R47" s="14">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D48" t="s">
         <v>185</v>
       </c>
       <c r="E48">
-        <v>27.55</v>
+        <v>7.97</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G48" s="7">
-        <v>28136538112</v>
+        <v>18779152384</v>
       </c>
       <c r="H48" s="6">
-        <v>36</v>
+        <v>11.68</v>
       </c>
       <c r="I48" s="6">
-        <v>22.4</v>
+        <v>5.19</v>
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
-        <v>0.22991071428571441</v>
+        <v>0.5356454720616568</v>
       </c>
       <c r="K48" s="11">
         <v>0</v>
       </c>
       <c r="L48" s="13">
-        <v>-90314000</v>
+        <v>13493113000</v>
       </c>
       <c r="M48" s="13">
-        <v>18374441000</v>
+        <v>208027754000</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O48" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>-3.8865083660601265E-3</v>
+        <v>0.12223007169246884</v>
       </c>
       <c r="Q48" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R48" s="14">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" t="s">
         <v>187</v>
       </c>
-      <c r="D49" t="s">
-        <v>188</v>
-      </c>
       <c r="E49">
-        <v>18.440000000000001</v>
+        <v>33.75</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G49" s="7">
-        <v>520091009024</v>
+        <v>23344199680</v>
       </c>
       <c r="H49" s="6">
-        <v>19.260000000000002</v>
+        <v>35.75</v>
       </c>
       <c r="I49" s="6">
-        <v>13.52</v>
+        <v>12.38</v>
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
-        <v>0.36390532544378718</v>
+        <v>1.7261712439418413</v>
       </c>
       <c r="K49" s="11">
-        <v>2.0607375271149673E-2</v>
+        <v>1.362962962962963E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>52374992116</v>
+        <v>1323087000</v>
       </c>
       <c r="M49" s="13">
-        <v>269573093476</v>
+        <v>5952918000</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O49" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P49" s="12">
-        <v>8.6837688985510905E-2</v>
+        <v>5.1268427139119555E-2</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.19428864891763736</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R49" s="14">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
+        <v>188</v>
+      </c>
+      <c r="D50" t="s">
         <v>189</v>
       </c>
-      <c r="D50" t="s">
-        <v>108</v>
-      </c>
       <c r="E50">
-        <v>5.0999999999999996</v>
+        <v>334</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G50" s="7">
-        <v>39479406592</v>
+        <v>124495159296</v>
       </c>
       <c r="H50" s="6">
-        <v>5.49</v>
+        <v>421.4</v>
       </c>
       <c r="I50" s="6">
-        <v>3.8</v>
+        <v>225.2</v>
       </c>
       <c r="J50" s="12">
         <f t="shared" si="1"/>
-        <v>0.34210526315789469</v>
+        <v>0.48312611012433404</v>
       </c>
       <c r="K50" s="11">
-        <v>7.509803921568628E-2</v>
+        <v>2.155688622754491E-3</v>
       </c>
       <c r="L50" s="13">
-        <v>5474000000</v>
+        <v>1200000000</v>
       </c>
       <c r="M50" s="13">
-        <v>59407000000</v>
+        <v>5855000000</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="O50" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P50" s="12">
-        <v>6.0066448420561427E-2</v>
+        <v>6.7150257796866272E-2</v>
       </c>
       <c r="Q50" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R50" s="14">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
         <v>190</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E51">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G51" s="7">
-        <v>60871147520</v>
+        <v>3379130880</v>
       </c>
       <c r="H51" s="6">
-        <v>14.56</v>
+        <v>2.73</v>
       </c>
       <c r="I51" s="6">
-        <v>10.98</v>
+        <v>1.79</v>
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
-        <v>0.32058287795992713</v>
+        <v>6.1452513966480327E-2</v>
       </c>
       <c r="K51" s="11">
-        <v>6.1103448275862067E-2</v>
+        <v>2.9473684210526319E-2</v>
       </c>
       <c r="L51" s="13">
-        <v>11996000000</v>
+        <v>364157000</v>
       </c>
       <c r="M51" s="13">
-        <v>138296000000</v>
+        <v>7859317000</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="O51" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P51" s="12">
-        <v>0.14279397368178412</v>
+        <v>8.6692498863775544E-2</v>
       </c>
       <c r="Q51" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>4.6334433386514377E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
         <v>191</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="E52">
-        <v>7.97</v>
+        <v>13.4</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G52" s="7">
-        <v>18779152384</v>
+        <v>75501494272</v>
       </c>
       <c r="H52" s="6">
-        <v>11.68</v>
+        <v>14.24</v>
       </c>
       <c r="I52" s="6">
-        <v>5.19</v>
+        <v>8.81</v>
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
-        <v>0.5356454720616568</v>
+        <v>0.52099886492622005</v>
       </c>
       <c r="K52" s="11">
-        <v>0</v>
+        <v>2.4701492537313432E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>13493113000</v>
+        <v>6482967000</v>
       </c>
       <c r="M52" s="13">
-        <v>208027754000</v>
+        <v>27483863000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O52" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.12223007169246884</v>
+        <v>8.4558135136038812E-2</v>
       </c>
       <c r="Q52" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R52" s="14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" t="s">
         <v>193</v>
       </c>
-      <c r="D53" t="s">
-        <v>194</v>
-      </c>
       <c r="E53">
-        <v>33.75</v>
+        <v>2.1</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G53" s="7">
-        <v>23344199680</v>
+        <v>9019499520</v>
       </c>
       <c r="H53" s="6">
-        <v>35.75</v>
+        <v>3.04</v>
       </c>
       <c r="I53" s="6">
-        <v>12.38</v>
+        <v>1.93</v>
       </c>
       <c r="J53" s="12">
         <f t="shared" si="1"/>
-        <v>1.7261712439418413</v>
+        <v>8.8082901554404236E-2</v>
       </c>
       <c r="K53" s="11">
-        <v>1.362962962962963E-2</v>
+        <v>5.095238095238095E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>1323087000</v>
+        <v>1938532000</v>
       </c>
       <c r="M53" s="13">
-        <v>5952918000</v>
+        <v>49986396000</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O53" s="6">
         <v>1</v>
       </c>
       <c r="P53" s="12">
-        <v>5.1268427139119555E-2</v>
+        <v>6.560613897790224E-2</v>
       </c>
       <c r="Q53" s="12">
-        <v>0.222258562943417</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R53" s="14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="E54">
-        <v>334</v>
+        <v>32.5</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G54" s="7">
-        <v>124495159296</v>
+        <v>73228992512</v>
       </c>
       <c r="H54" s="6">
-        <v>421.4</v>
+        <v>61.55</v>
       </c>
       <c r="I54" s="6">
-        <v>225.2</v>
+        <v>24.85</v>
       </c>
       <c r="J54" s="12">
         <f t="shared" si="1"/>
-        <v>0.48312611012433404</v>
+        <v>0.30784708249496973</v>
       </c>
       <c r="K54" s="11">
-        <v>2.155688622754491E-3</v>
+        <v>1.7476923076923074E-2</v>
       </c>
       <c r="L54" s="13">
-        <v>1200000000</v>
+        <v>5261270000</v>
       </c>
       <c r="M54" s="13">
-        <v>5855000000</v>
+        <v>43208997000</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="O54" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>6.7150257796866272E-2</v>
+        <v>7.1146490186410088E-2</v>
       </c>
       <c r="Q54" s="12">
-        <v>0.20495303159692571</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R54" s="14">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E55">
-        <v>1.9</v>
+        <v>51</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G55" s="7">
-        <v>3379130880</v>
+        <v>130499821568</v>
       </c>
       <c r="H55" s="6">
-        <v>2.73</v>
+        <v>71.7</v>
       </c>
       <c r="I55" s="6">
-        <v>1.79</v>
+        <v>43.55</v>
       </c>
       <c r="J55" s="12">
         <f t="shared" si="1"/>
-        <v>6.1452513966480327E-2</v>
+        <v>0.17106773823191745</v>
       </c>
       <c r="K55" s="11">
-        <v>2.9473684210526319E-2</v>
+        <v>3.2156862745098039E-3</v>
       </c>
       <c r="L55" s="13">
-        <v>364157000</v>
+        <v>1279098000</v>
       </c>
       <c r="M55" s="13">
-        <v>7859317000</v>
+        <v>4811702000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="O55" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-      <c r="P55" s="12">
-        <v>8.6692498863775544E-2</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="12">
-        <v>4.6334433386514377E-2</v>
-      </c>
-      <c r="R55" s="14">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.5">
+        <v>0.26583067696212276</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="E56">
-        <v>13.4</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G56" s="7">
-        <v>75501494272</v>
+        <v>115239665664</v>
       </c>
       <c r="H56" s="6">
-        <v>14.24</v>
+        <v>13.6</v>
       </c>
       <c r="I56" s="6">
-        <v>8.81</v>
+        <v>6.57</v>
       </c>
       <c r="J56" s="12">
         <f t="shared" si="1"/>
-        <v>0.52099886492622005</v>
+        <v>0.4140030441400302</v>
       </c>
       <c r="K56" s="11">
-        <v>2.4701492537313432E-2</v>
+        <v>5.3821313240043061E-3</v>
       </c>
       <c r="L56" s="13">
-        <v>6482967000</v>
+        <v>2125459000</v>
       </c>
       <c r="M56" s="13">
-        <v>27483863000</v>
+        <v>9202253000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="O56" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P56" s="12">
-        <v>8.4558135136038812E-2</v>
+        <v>0.13816921221661033</v>
       </c>
       <c r="Q56" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.23097158924015673</v>
       </c>
       <c r="R56" s="14">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" t="s">
         <v>199</v>
       </c>
-      <c r="D57" t="s">
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E57">
-        <v>2.1</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G57" s="7">
-        <v>9019499520</v>
-      </c>
-      <c r="H57" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="I57" s="6">
-        <v>1.93</v>
-      </c>
-      <c r="J57" s="12">
-        <f t="shared" si="1"/>
-        <v>8.8082901554404236E-2</v>
-      </c>
-      <c r="K57" s="11">
-        <v>5.095238095238095E-2</v>
-      </c>
-      <c r="L57" s="13">
-        <v>1938532000</v>
-      </c>
-      <c r="M57" s="13">
-        <v>49986396000</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O57" s="6">
-        <v>1</v>
-      </c>
-      <c r="P57" s="12">
-        <v>6.560613897790224E-2</v>
-      </c>
-      <c r="Q57" s="12">
-        <v>3.8781191586606881E-2</v>
-      </c>
-      <c r="R57" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="B58" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D58" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58">
-        <v>32.5</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G58" s="7">
-        <v>73228992512</v>
-      </c>
-      <c r="H58" s="6">
-        <v>61.55</v>
-      </c>
-      <c r="I58" s="6">
-        <v>24.85</v>
-      </c>
-      <c r="J58" s="12">
-        <f t="shared" si="1"/>
-        <v>0.30784708249496973</v>
-      </c>
-      <c r="K58" s="11">
-        <v>1.7476923076923074E-2</v>
-      </c>
-      <c r="L58" s="13">
-        <v>5261270000</v>
-      </c>
-      <c r="M58" s="13">
-        <v>43208997000</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="O58" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-      <c r="P58" s="12">
-        <v>7.1146490186410088E-2</v>
-      </c>
-      <c r="Q58" s="12">
-        <v>0.12176329850933591</v>
-      </c>
-      <c r="R58" s="14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="B59" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C59" t="s">
-        <v>202</v>
-      </c>
-      <c r="D59" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59">
-        <v>51</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59" s="7">
-        <v>130499821568</v>
-      </c>
-      <c r="H59" s="6">
-        <v>71.7</v>
-      </c>
-      <c r="I59" s="6">
-        <v>43.55</v>
-      </c>
-      <c r="J59" s="12">
-        <f t="shared" si="1"/>
-        <v>0.17106773823191745</v>
-      </c>
-      <c r="K59" s="11">
-        <v>3.2156862745098039E-3</v>
-      </c>
-      <c r="L59" s="13">
-        <v>1279098000</v>
-      </c>
-      <c r="M59" s="13">
-        <v>4811702000</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q59" s="12">
-        <v>0.26583067696212276</v>
-      </c>
-    </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="B60" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" t="s">
-        <v>204</v>
-      </c>
-      <c r="D60" t="s">
-        <v>192</v>
-      </c>
-      <c r="E60">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G60" s="7">
-        <v>115239665664</v>
-      </c>
-      <c r="H60" s="6">
-        <v>13.6</v>
-      </c>
-      <c r="I60" s="6">
-        <v>6.57</v>
-      </c>
-      <c r="J60" s="12">
-        <f t="shared" si="1"/>
-        <v>0.4140030441400302</v>
-      </c>
-      <c r="K60" s="11">
-        <v>5.3821313240043061E-3</v>
-      </c>
-      <c r="L60" s="13">
-        <v>2125459000</v>
-      </c>
-      <c r="M60" s="13">
-        <v>9202253000</v>
-      </c>
-      <c r="N60" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O60" s="6">
-        <v>7.6923076923076916</v>
-      </c>
-      <c r="P60" s="12">
-        <v>0.13816921221661033</v>
-      </c>
-      <c r="Q60" s="12">
-        <v>0.23097158924015673</v>
-      </c>
-      <c r="R60" s="14">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R25" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R25">
+  <autoFilter ref="B1:R21" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R21">
       <sortCondition ref="R1"/>
     </sortState>
   </autoFilter>
@@ -4461,25 +4251,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B46D05-099C-4A4C-836A-6062A20AA7D3}">
   <dimension ref="B1:V11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4493,34 +4283,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -4536,21 +4326,21 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>128.15</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G2" s="7">
         <v>497428299776</v>
@@ -4575,7 +4365,7 @@
         <v>133285282015.97</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O2" s="6">
         <v>1</v>
@@ -4590,21 +4380,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>8.5</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G3" s="7">
         <v>14667599872</v>
@@ -4629,7 +4419,7 @@
         <v>11970268017.99</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O3" s="6">
         <v>1</v>
@@ -4644,21 +4434,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4">
         <v>12.28</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G4" s="7">
         <v>12564895744</v>
@@ -4683,7 +4473,7 @@
         <v>11491269147.950001</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O4" s="6">
         <v>1</v>
@@ -4698,21 +4488,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5">
         <v>13.89</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G5" s="7">
         <v>24946440192</v>
@@ -4737,7 +4527,7 @@
         <v>15580673812.24</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O5" s="6">
         <v>1</v>
@@ -4752,21 +4542,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>104.24</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G6" s="7">
         <v>55394283520</v>
@@ -4791,7 +4581,7 @@
         <v>10336332783.18</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O6" s="6">
         <v>1</v>
@@ -4806,21 +4596,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>243.01</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G7" s="7">
         <v>44889538560</v>
@@ -4845,7 +4635,7 @@
         <v>12869225664</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O7" s="6">
         <v>1</v>
@@ -4860,21 +4650,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>9.3800000000000008</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7">
         <v>11384037376</v>
@@ -4899,7 +4689,7 @@
         <v>9527311896.5100002</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O8" s="6">
         <v>1</v>
@@ -4914,21 +4704,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9">
         <v>12.53</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G9" s="7">
         <v>4429643264</v>
@@ -4953,7 +4743,7 @@
         <v>2751572515.0799999</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O9" s="6">
         <v>1</v>
@@ -4968,21 +4758,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E10">
         <v>8.0299999999999994</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G10" s="7">
         <v>17844426752</v>
@@ -5007,7 +4797,7 @@
         <v>13696300546.360001</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O10" s="6">
         <v>1</v>
@@ -5022,21 +4812,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E11">
         <v>57.36</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11" s="7">
         <v>32998920192</v>
@@ -5061,7 +4851,7 @@
         <v>9067794807.8099995</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O11" s="6">
         <v>1</v>
@@ -5089,25 +4879,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FA5E83-3B3C-124C-A85B-B3DA799E441B}">
   <dimension ref="B1:V4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5121,34 +4911,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -5164,21 +4954,21 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>63.07</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G2" s="7">
         <v>2609899776</v>
@@ -5203,7 +4993,7 @@
         <v>1851800000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O2" s="6">
         <v>1</v>
@@ -5218,21 +5008,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E3">
         <v>206.61</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G3" s="7">
         <v>87313793024</v>
@@ -5257,7 +5047,7 @@
         <v>4294000000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O3" s="6">
         <v>1</v>
@@ -5272,21 +5062,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>164</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G4" s="7">
         <v>4521332224</v>
@@ -5311,7 +5101,7 @@
         <v>925772000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O4" s="6">
         <v>1</v>
@@ -5339,25 +5129,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54703291-9A5D-4E46-9F96-9938DF840B6E}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.6875" customWidth="1"/>
-    <col min="2" max="2" width="210.1875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="210.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="409.6" x14ac:dyDescent="0.2">
       <c r="B3" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.5">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B2357A-8BF3-A94E-B871-ACB641911FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC05381-2F39-4318-8844-467DBFE2264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -28,23 +28,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
   <si>
     <t>Ticker</t>
   </si>
@@ -713,6 +702,15 @@
   </si>
   <si>
     <t>0341.HK</t>
+  </si>
+  <si>
+    <t>SMIC</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>CAFE DE CORAL H</t>
   </si>
 </sst>
 </file>
@@ -829,7 +827,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1182,25 +1180,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
   <dimension ref="B1:V58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="18.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1255,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1268,13 +1266,13 @@
         <v>80</v>
       </c>
       <c r="E2">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="7">
-        <v>266968530944</v>
+        <v>266401906688</v>
       </c>
       <c r="H2" s="6">
         <v>15.14</v>
@@ -1283,11 +1281,11 @@
         <v>9.52</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J29" si="0">E2/I2-1</f>
-        <v>0.55042016806722693</v>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
+        <v>0.54831932773109249</v>
       </c>
       <c r="K2" s="11">
-        <v>0.10501355013550136</v>
+        <v>0.10515603799185889</v>
       </c>
       <c r="L2" s="13">
         <v>70144988000</v>
@@ -1302,7 +1300,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.49427208713102277</v>
+        <v>0.49612618476500991</v>
       </c>
       <c r="Q2" s="12">
         <v>0.26042924055386191</v>
@@ -1311,7 +1309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
@@ -1322,26 +1320,26 @@
         <v>78</v>
       </c>
       <c r="E3">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G3" s="7">
-        <v>17363415040</v>
+        <v>17859514368</v>
       </c>
       <c r="H3" s="6">
-        <v>5.46</v>
+        <v>5.33</v>
       </c>
       <c r="I3" s="6">
         <v>2.11</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.32701421800947861</v>
+        <v>0.36492890995260674</v>
       </c>
       <c r="K3" s="11">
-        <v>5.7142857142857148E-2</v>
+        <v>5.5555555555555559E-2</v>
       </c>
       <c r="L3" s="13">
         <v>2906500000</v>
@@ -1356,7 +1354,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.17092678595959268</v>
+        <v>0.16638325081256819</v>
       </c>
       <c r="Q3" s="12">
         <v>0.27500236540826944</v>
@@ -1365,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1376,13 +1374,13 @@
         <v>77</v>
       </c>
       <c r="E4">
-        <v>2.5099999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="7">
-        <v>2609923072</v>
+        <v>2599524864</v>
       </c>
       <c r="H4" s="6">
         <v>3.34</v>
@@ -1392,10 +1390,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.30729166666666652</v>
+        <v>0.30208333333333348</v>
       </c>
       <c r="K4" s="11">
-        <v>0.11633466135458168</v>
+        <v>0.11679999999999999</v>
       </c>
       <c r="L4" s="13">
         <v>762183000</v>
@@ -1410,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>0.22718080969113263</v>
+        <v>0.2278871120399093</v>
       </c>
       <c r="Q4" s="12">
         <v>0.15218339726363278</v>
@@ -1419,7 +1417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
@@ -1430,13 +1428,13 @@
         <v>51</v>
       </c>
       <c r="E5">
-        <v>6.24</v>
+        <v>6.28</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="7">
-        <v>7609742336</v>
+        <v>7658523136</v>
       </c>
       <c r="H5" s="6">
         <v>8.6</v>
@@ -1446,10 +1444,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.80346820809248554</v>
+        <v>0.81502890173410414</v>
       </c>
       <c r="K5" s="11">
-        <v>2.2596153846153842E-2</v>
+        <v>2.2452229299363056E-2</v>
       </c>
       <c r="L5" s="13">
         <v>921702000</v>
@@ -1464,7 +1462,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P5" s="12">
-        <v>0.19110296733656484</v>
+        <v>0.18931080612829809</v>
       </c>
       <c r="Q5" s="12">
         <v>0.17514380877385538</v>
@@ -1473,7 +1471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1484,13 +1482,13 @@
         <v>82</v>
       </c>
       <c r="E6">
-        <v>8.8699999999999992</v>
+        <v>8.85</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="7">
-        <v>144632446976</v>
+        <v>142903607296</v>
       </c>
       <c r="H6" s="6">
         <v>10.76</v>
@@ -1500,10 +1498,10 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.238826815642458</v>
+        <v>0.2360335195530725</v>
       </c>
       <c r="K6" s="11">
-        <v>5.4002254791431795E-2</v>
+        <v>5.4124293785310737E-2</v>
       </c>
       <c r="L6" s="13">
         <v>32866046000</v>
@@ -1518,16 +1516,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P6" s="12">
-        <v>0.19339190520925856</v>
+        <v>0.19525105677556878</v>
       </c>
       <c r="Q6" s="12">
         <v>0.15266623500015464</v>
       </c>
       <c r="R6" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,13 +1536,13 @@
         <v>84</v>
       </c>
       <c r="E7">
-        <v>8.3800000000000008</v>
+        <v>8.27</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="7">
-        <v>72562425856</v>
+        <v>71609933824</v>
       </c>
       <c r="H7" s="6">
         <v>9.23</v>
@@ -1554,10 +1552,10 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>0.23054331864904576</v>
+        <v>0.21439060205580041</v>
       </c>
       <c r="K7" s="11">
-        <v>3.7708830548926014E-2</v>
+        <v>3.8210399032648126E-2</v>
       </c>
       <c r="L7" s="13">
         <v>13438000000</v>
@@ -1572,7 +1570,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.20876044908337377</v>
+        <v>0.21169239559663214</v>
       </c>
       <c r="Q7" s="12">
         <v>0.15165160081705431</v>
@@ -1581,7 +1579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,13 +1590,13 @@
         <v>86</v>
       </c>
       <c r="E8">
-        <v>15.08</v>
+        <v>15.1</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="7">
-        <v>31470602240</v>
+        <v>31377195008</v>
       </c>
       <c r="H8" s="6">
         <v>15.48</v>
@@ -1608,10 +1606,10 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.89447236180904532</v>
+        <v>0.89698492462311563</v>
       </c>
       <c r="K8" s="11">
-        <v>7.4270557029177731E-2</v>
+        <v>7.4172185430463583E-2</v>
       </c>
       <c r="L8" s="13">
         <v>5451928473.2399998</v>
@@ -1626,16 +1624,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.1667239217205066</v>
+        <v>0.16717087768969968</v>
       </c>
       <c r="Q8" s="12">
         <v>0.20973136925592797</v>
       </c>
       <c r="R8" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
@@ -1646,26 +1644,26 @@
         <v>92</v>
       </c>
       <c r="E9">
-        <v>4.76</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="7">
-        <v>5043601408</v>
+        <v>5054196736</v>
       </c>
       <c r="H9" s="6">
-        <v>6.4</v>
+        <v>6.26</v>
       </c>
       <c r="I9" s="6">
         <v>3.97</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.19899244332493682</v>
+        <v>0.20151133501259433</v>
       </c>
       <c r="K9" s="11">
-        <v>0.10294117647058824</v>
+        <v>0.10272536687631029</v>
       </c>
       <c r="L9" s="13">
         <v>866801000</v>
@@ -1680,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>0.42327814020636439</v>
+        <v>0.42109939991480938</v>
       </c>
       <c r="Q9" s="12">
         <v>0.11511220438953086</v>
@@ -1689,7 +1687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,13 +1698,13 @@
         <v>99</v>
       </c>
       <c r="E10">
-        <v>14.54</v>
+        <v>14.4</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="7">
-        <v>12101467136</v>
+        <v>11984947200</v>
       </c>
       <c r="H10" s="6">
         <v>19.440000000000001</v>
@@ -1716,10 +1714,10 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>0.1996699669966997</v>
+        <v>0.18811881188118829</v>
       </c>
       <c r="K10" s="11">
-        <v>1.0178817056396148E-2</v>
+        <v>1.0277777777777776E-2</v>
       </c>
       <c r="L10" s="13">
         <v>199557000</v>
@@ -1734,16 +1732,16 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P10" s="12">
-        <v>0.17178876691916867</v>
+        <v>0.17405845676300949</v>
       </c>
       <c r="Q10" s="12">
         <v>0.18009145491283626</v>
       </c>
       <c r="R10" s="14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,13 +1752,13 @@
         <v>74</v>
       </c>
       <c r="E11">
-        <v>4.8</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="7">
-        <v>13693536256</v>
+        <v>14321156096</v>
       </c>
       <c r="H11" s="6">
         <v>6.21</v>
@@ -1770,10 +1768,10 @@
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.49068322981366452</v>
+        <v>0.55900621118012395</v>
       </c>
       <c r="K11" s="11">
-        <v>8.7500000000000008E-3</v>
+        <v>8.3665338645418346E-3</v>
       </c>
       <c r="L11" s="13">
         <v>259348000</v>
@@ -1788,16 +1786,16 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P11" s="12">
-        <v>0.16971440431040136</v>
+        <v>0.16111230357181586</v>
       </c>
       <c r="Q11" s="12">
         <v>0.15459217096529801</v>
       </c>
       <c r="R11" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1808,13 +1806,13 @@
         <v>74</v>
       </c>
       <c r="E12">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="7">
-        <v>51084984320</v>
+        <v>52238151680</v>
       </c>
       <c r="H12" s="6">
         <v>5.14</v>
@@ -1824,10 +1822,10 @@
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.28034682080924855</v>
+        <v>0.30924855491329484</v>
       </c>
       <c r="K12" s="11">
-        <v>5.3273137697516931E-2</v>
+        <v>5.2097130242825598E-2</v>
       </c>
       <c r="L12" s="13">
         <v>4734613000</v>
@@ -1842,16 +1840,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.1056668547805296</v>
+        <v>0.10318129921430115</v>
       </c>
       <c r="Q12" s="12">
         <v>0.29201860560357656</v>
       </c>
       <c r="R12" s="14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1862,13 +1860,13 @@
         <v>90</v>
       </c>
       <c r="E13">
-        <v>6.05</v>
+        <v>6.24</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="7">
-        <v>54856863744</v>
+        <v>56579637248</v>
       </c>
       <c r="H13" s="6">
         <v>7.38</v>
@@ -1878,10 +1876,10 @@
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.78466076696165188</v>
+        <v>0.84070796460176989</v>
       </c>
       <c r="K13" s="11">
-        <v>5.0743801652892565E-2</v>
+        <v>4.9198717948717947E-2</v>
       </c>
       <c r="L13" s="13">
         <v>5594372000</v>
@@ -1896,16 +1894,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.12978201086967631</v>
+        <v>0.12510216016396158</v>
       </c>
       <c r="Q13" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
@@ -1916,13 +1914,13 @@
         <v>90</v>
       </c>
       <c r="E14">
-        <v>5.1100000000000003</v>
+        <v>5.24</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="7">
-        <v>60313841664</v>
+        <v>61848240128</v>
       </c>
       <c r="H14" s="6">
         <v>5.77</v>
@@ -1932,10 +1930,10 @@
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.24029126213592233</v>
+        <v>0.27184466019417486</v>
       </c>
       <c r="K14" s="11">
-        <v>4.6575342465753421E-2</v>
+        <v>4.5419847328244271E-2</v>
       </c>
       <c r="L14" s="13">
         <v>5687261000</v>
@@ -1950,16 +1948,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.10616681847056487</v>
+        <v>0.10339478616831782</v>
       </c>
       <c r="Q14" s="12">
         <v>0.26188601495697911</v>
       </c>
       <c r="R14" s="14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
@@ -1970,26 +1968,26 @@
         <v>104</v>
       </c>
       <c r="E15">
-        <v>387.2</v>
+        <v>391</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="7">
-        <v>489358852096</v>
+        <v>494161428480</v>
       </c>
       <c r="H15" s="6">
-        <v>398.6</v>
+        <v>399.6</v>
       </c>
       <c r="I15" s="6">
         <v>218.4</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.77289377289377281</v>
+        <v>0.79029304029304015</v>
       </c>
       <c r="K15" s="11">
-        <v>2.3915289256198347E-2</v>
+        <v>2.3682864450127877E-2</v>
       </c>
       <c r="L15" s="13">
         <v>20744000000</v>
@@ -2004,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="12">
-        <v>5.8222585692903818E-2</v>
+        <v>5.7448213422109484E-2</v>
       </c>
       <c r="Q15" s="12">
         <v>0.38520389214885242</v>
@@ -2013,7 +2011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
@@ -2024,13 +2022,13 @@
         <v>107</v>
       </c>
       <c r="E16">
-        <v>5.76</v>
+        <v>5.86</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="7">
-        <v>4488203776</v>
+        <v>4566123520</v>
       </c>
       <c r="H16" s="6">
         <v>8.09</v>
@@ -2040,10 +2038,10 @@
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>0.43283582089552253</v>
+        <v>0.45771144278606979</v>
       </c>
       <c r="K16" s="11">
-        <v>2.9513888888888892E-2</v>
+        <v>2.9010238907849831E-2</v>
       </c>
       <c r="L16" s="13">
         <v>437453000</v>
@@ -2058,16 +2056,16 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.19895488336167233</v>
+        <v>0.19214560366758091</v>
       </c>
       <c r="Q16" s="12">
         <v>8.9074849645861431E-2</v>
       </c>
       <c r="R16" s="14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
@@ -2078,13 +2076,13 @@
         <v>51</v>
       </c>
       <c r="E17">
-        <v>12.16</v>
+        <v>12.34</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="7">
-        <v>57380364288</v>
+        <v>57997750272</v>
       </c>
       <c r="H17" s="6">
         <v>13.56</v>
@@ -2094,10 +2092,10 @@
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.61917443408788286</v>
+        <v>0.64314247669773628</v>
       </c>
       <c r="K17" s="11">
-        <v>3.6019736842105264E-2</v>
+        <v>3.5494327390599677E-2</v>
       </c>
       <c r="L17" s="13">
         <v>3967214824.1399999</v>
@@ -2112,7 +2110,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.13294201683080747</v>
+        <v>0.13041654887075355</v>
       </c>
       <c r="Q17" s="12">
         <v>9.6670468672106824E-2</v>
@@ -2121,7 +2119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
@@ -2132,13 +2130,13 @@
         <v>67</v>
       </c>
       <c r="E18">
-        <v>49.45</v>
+        <v>50.45</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="7">
-        <v>134003572736</v>
+        <v>137104433152</v>
       </c>
       <c r="H18" s="6">
         <v>82.25</v>
@@ -2148,10 +2146,10 @@
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.30647291941875832</v>
+        <v>0.33289299867899613</v>
       </c>
       <c r="K18" s="11">
-        <v>2.1233569261880688E-2</v>
+        <v>2.0812685827552031E-2</v>
       </c>
       <c r="L18" s="13">
         <v>6350637223.7200003</v>
@@ -2166,16 +2164,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P18" s="12">
-        <v>6.6311605293517414E-2</v>
+        <v>6.4361071109758666E-2</v>
       </c>
       <c r="Q18" s="12">
         <v>0.10968970241604512</v>
       </c>
       <c r="R18" s="14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>31</v>
       </c>
@@ -2186,13 +2184,13 @@
         <v>96</v>
       </c>
       <c r="E19">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="7">
-        <v>7756792320</v>
+        <v>7975293952</v>
       </c>
       <c r="H19" s="6">
         <v>1.82</v>
@@ -2202,10 +2200,10 @@
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>0.75308641975308621</v>
+        <v>0.80246913580246892</v>
       </c>
       <c r="K19" s="11">
-        <v>2.3943661971830989E-2</v>
+        <v>2.3287671232876714E-2</v>
       </c>
       <c r="L19" s="13">
         <v>1384865000</v>
@@ -2220,7 +2218,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P19" s="12">
-        <v>7.8406950129255665E-2</v>
+        <v>7.7509454513107826E-2</v>
       </c>
       <c r="Q19" s="12">
         <v>5.8120488088461209E-2</v>
@@ -2229,7 +2227,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2240,13 +2238,13 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="7">
-        <v>7096072192</v>
+        <v>7148248576</v>
       </c>
       <c r="H20" s="6">
         <v>6.93</v>
@@ -2256,7 +2254,7 @@
       </c>
       <c r="J20" s="12">
         <f t="shared" si="0"/>
-        <v>0.691542288557214</v>
+        <v>0.70398009950248763</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -2274,16 +2272,16 @@
         <v>1</v>
       </c>
       <c r="P20" s="12">
-        <v>5.0538017065101339E-2</v>
+        <v>5.0102476266993719E-2</v>
       </c>
       <c r="Q20" s="12">
         <v>8.3790449156695201E-2</v>
       </c>
       <c r="R20" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
@@ -2294,13 +2292,13 @@
         <v>101</v>
       </c>
       <c r="E21">
-        <v>11.58</v>
+        <v>11.72</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="7">
-        <v>203817271296</v>
+        <v>206281392128</v>
       </c>
       <c r="H21" s="6">
         <v>12.46</v>
@@ -2310,10 +2308,10 @@
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.27252747252747267</v>
+        <v>0.287912087912088</v>
       </c>
       <c r="K21" s="11">
-        <v>3.6010362694300517E-2</v>
+        <v>3.5580204778156994E-2</v>
       </c>
       <c r="L21" s="13">
         <v>16758000000</v>
@@ -2328,16 +2326,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>5.9696501972347493E-2</v>
+        <v>5.9210027773688667E-2</v>
       </c>
       <c r="Q21" s="12">
         <v>6.2161059386475759E-2</v>
       </c>
       <c r="R21" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>113</v>
       </c>
@@ -2391,7 +2389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>114</v>
       </c>
@@ -2402,13 +2400,13 @@
         <v>152</v>
       </c>
       <c r="E23">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="7">
-        <v>8727326720</v>
+        <v>8699354112</v>
       </c>
       <c r="H23" s="6">
         <v>3.35</v>
@@ -2418,10 +2416,10 @@
       </c>
       <c r="J23" s="12">
         <f t="shared" si="0"/>
-        <v>0.32203389830508478</v>
+        <v>0.31779661016949157</v>
       </c>
       <c r="K23" s="11">
-        <v>4.9038461538461538E-2</v>
+        <v>4.9196141479099682E-2</v>
       </c>
       <c r="L23" s="13">
         <v>1871151000</v>
@@ -2436,7 +2434,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.44131348531551057</v>
+        <v>0.44405559305801723</v>
       </c>
       <c r="Q23" s="12">
         <v>0.28956319566547578</v>
@@ -2445,7 +2443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>115</v>
       </c>
@@ -2456,13 +2454,13 @@
         <v>101</v>
       </c>
       <c r="E24">
-        <v>5.86</v>
+        <v>5.96</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="7">
-        <v>755119620096</v>
+        <v>754577702912</v>
       </c>
       <c r="H24" s="6">
         <v>6.98</v>
@@ -2472,10 +2470,10 @@
       </c>
       <c r="J24" s="12">
         <f t="shared" si="0"/>
-        <v>0.43627450980392157</v>
+        <v>0.46078431372549011</v>
       </c>
       <c r="K24" s="11">
-        <v>4.4368600682593858E-2</v>
+        <v>4.3624161073825503E-2</v>
       </c>
       <c r="L24" s="13">
         <v>44563000000</v>
@@ -2490,7 +2488,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>6.5024342087621825E-2</v>
+        <v>6.5072504456515662E-2</v>
       </c>
       <c r="Q24" s="12">
         <v>9.605709580489824E-2</v>
@@ -2499,7 +2497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>116</v>
       </c>
@@ -2510,13 +2508,13 @@
         <v>155</v>
       </c>
       <c r="E25">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="7">
-        <v>5540682752</v>
+        <v>5497620480</v>
       </c>
       <c r="H25" s="6">
         <v>7.92</v>
@@ -2526,10 +2524,10 @@
       </c>
       <c r="J25" s="12">
         <f t="shared" si="0"/>
-        <v>0.63559322033898313</v>
+        <v>0.62288135593220351</v>
       </c>
       <c r="K25" s="11">
-        <v>6.5803108808290156E-2</v>
+        <v>6.6318537859007834E-2</v>
       </c>
       <c r="L25" s="13">
         <v>811880000</v>
@@ -2544,7 +2542,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P25" s="12">
-        <v>0.16283852472600896</v>
+        <v>0.16416567610994109</v>
       </c>
       <c r="Q25" s="12">
         <v>0.14675695119790894</v>
@@ -2553,7 +2551,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2564,13 +2562,13 @@
         <v>71</v>
       </c>
       <c r="E26">
-        <v>21.85</v>
+        <v>22</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="7">
-        <v>49604308992</v>
+        <v>49944842240</v>
       </c>
       <c r="H26" s="6">
         <v>35.200000000000003</v>
@@ -2580,10 +2578,10 @@
       </c>
       <c r="J26" s="12">
         <f t="shared" si="0"/>
-        <v>9.578736208625882E-2</v>
+        <v>0.10330992978936804</v>
       </c>
       <c r="K26" s="11">
-        <v>4.3478260869565209E-2</v>
+        <v>4.3181818181818182E-2</v>
       </c>
       <c r="L26" s="13">
         <v>8486605000</v>
@@ -2598,16 +2596,16 @@
         <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>0.12937271786140314</v>
+        <v>0.1287045858881023</v>
       </c>
       <c r="Q26" s="12">
         <v>0.13224608497060733</v>
       </c>
       <c r="R26" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>117</v>
       </c>
@@ -2618,13 +2616,13 @@
         <v>157</v>
       </c>
       <c r="E27">
-        <v>12.78</v>
+        <v>12.68</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="7">
-        <v>13125187584</v>
+        <v>13022486528</v>
       </c>
       <c r="H27" s="6">
         <v>14.5</v>
@@ -2634,10 +2632,10 @@
       </c>
       <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>0.23359073359073368</v>
+        <v>0.22393822393822393</v>
       </c>
       <c r="K27" s="11">
-        <v>8.4507042253521139E-2</v>
+        <v>8.5173501577287078E-2</v>
       </c>
       <c r="L27" s="13">
         <v>984000000</v>
@@ -2652,16 +2650,16 @@
         <v>1</v>
       </c>
       <c r="P27" s="12">
-        <v>2.5843602157681757E-2</v>
+        <v>2.59134992193472E-2</v>
       </c>
       <c r="Q27" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R27" s="14">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
@@ -2672,13 +2670,13 @@
         <v>159</v>
       </c>
       <c r="E28">
-        <v>58.65</v>
+        <v>58.05</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="7">
-        <v>164297998336</v>
+        <v>162675261440</v>
       </c>
       <c r="H28" s="6">
         <v>60</v>
@@ -2688,10 +2686,10 @@
       </c>
       <c r="J28" s="12">
         <f t="shared" si="0"/>
-        <v>0.52734375</v>
+        <v>0.51171875</v>
       </c>
       <c r="K28" s="11">
-        <v>3.0690537084398978E-2</v>
+        <v>3.1007751937984499E-2</v>
       </c>
       <c r="L28" s="13">
         <v>8955723006</v>
@@ -2706,7 +2704,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>5.9707343267352463E-2</v>
+        <v>6.0318143253415502E-2</v>
       </c>
       <c r="Q28" s="12">
         <v>0.18855793075067021</v>
@@ -2715,7 +2713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>119</v>
       </c>
@@ -2732,7 +2730,7 @@
         <v>69</v>
       </c>
       <c r="G29" s="7">
-        <v>128460144640</v>
+        <v>128567304192</v>
       </c>
       <c r="H29" s="6">
         <v>26.6</v>
@@ -2760,7 +2758,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P29" s="12">
-        <v>0.13569108016282685</v>
+        <v>0.13552022486560977</v>
       </c>
       <c r="Q29" s="12">
         <v>5.0146340085309396E-2</v>
@@ -2769,7 +2767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>120</v>
       </c>
@@ -2795,7 +2793,7 @@
         <v>1.37</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" ref="J30:J56" si="1">E30/I30-1</f>
+        <f t="shared" si="0"/>
         <v>0.24817518248175174</v>
       </c>
       <c r="K30" s="11">
@@ -2820,10 +2818,10 @@
         <v>3.1227495254580313E-2</v>
       </c>
       <c r="R30" s="14">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>121</v>
       </c>
@@ -2834,13 +2832,13 @@
         <v>88</v>
       </c>
       <c r="E31">
-        <v>92.25</v>
+        <v>95.6</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="7">
-        <v>257193918464</v>
+        <v>266533748736</v>
       </c>
       <c r="H31" s="6">
         <v>107.5</v>
@@ -2849,11 +2847,11 @@
         <v>65.55</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="1"/>
-        <v>0.40732265446224258</v>
+        <f t="shared" si="0"/>
+        <v>0.45842868039664375</v>
       </c>
       <c r="K31" s="11">
-        <v>2.4043360433604336E-2</v>
+        <v>2.3200836820083684E-2</v>
       </c>
       <c r="L31" s="13">
         <v>22510000000</v>
@@ -2868,7 +2866,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P31" s="12">
-        <v>8.7429866091066066E-2</v>
+        <v>8.4558705548000476E-2</v>
       </c>
       <c r="Q31" s="12">
         <v>0.27269973953601068</v>
@@ -2877,7 +2875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>122</v>
       </c>
@@ -2888,26 +2886,26 @@
         <v>88</v>
       </c>
       <c r="E32">
-        <v>221.2</v>
+        <v>216.6</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G32" s="7">
-        <v>293788975104</v>
+        <v>287679479808</v>
       </c>
       <c r="H32" s="6">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I32" s="6">
         <v>34.4</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="1"/>
-        <v>5.4302325581395348</v>
+        <f t="shared" si="0"/>
+        <v>5.2965116279069768</v>
       </c>
       <c r="K32" s="11">
-        <v>3.6844484629294755E-3</v>
+        <v>3.7626962142197598E-3</v>
       </c>
       <c r="L32" s="13">
         <v>4414795000</v>
@@ -2922,16 +2920,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P32" s="12">
-        <v>1.6360665114900662E-2</v>
+        <v>1.6714886709713026E-2</v>
       </c>
       <c r="Q32" s="12">
         <v>0.41323470153287706</v>
       </c>
       <c r="R32" s="14">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>123</v>
       </c>
@@ -2942,13 +2940,13 @@
         <v>72</v>
       </c>
       <c r="E33">
-        <v>5.86</v>
+        <v>5.99</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G33" s="7">
-        <v>9532520448</v>
+        <v>9743992832</v>
       </c>
       <c r="H33" s="6">
         <v>7.05</v>
@@ -2957,11 +2955,11 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="1"/>
-        <v>0.37236533957845452</v>
+        <f t="shared" si="0"/>
+        <v>0.40281030444964894</v>
       </c>
       <c r="K33" s="11">
-        <v>4.778156996587031E-2</v>
+        <v>4.6744574290484141E-2</v>
       </c>
       <c r="L33" s="13">
         <v>4094312000</v>
@@ -2976,16 +2974,16 @@
         <v>1</v>
       </c>
       <c r="P33" s="12">
-        <v>0.13670988611818785</v>
+        <v>0.1357513317572113</v>
       </c>
       <c r="Q33" s="12">
         <v>0.10878407220713927</v>
       </c>
       <c r="R33" s="14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>124</v>
       </c>
@@ -2996,13 +2994,13 @@
         <v>101</v>
       </c>
       <c r="E34">
-        <v>9.5500000000000007</v>
+        <v>9.67</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G34" s="7">
-        <v>292210900992</v>
+        <v>295882653696</v>
       </c>
       <c r="H34" s="6">
         <v>11.56</v>
@@ -3011,8 +3009,8 @@
         <v>5.88</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="1"/>
-        <v>0.62414965986394577</v>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
+        <v>0.64455782312925169</v>
       </c>
       <c r="K34" s="11">
         <v>0</v>
@@ -3030,16 +3028,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>9.478416599662691E-2</v>
+        <v>9.3653995073074411E-2</v>
       </c>
       <c r="Q34" s="12">
         <v>7.4329031387590908E-2</v>
       </c>
       <c r="R34" s="14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>125</v>
       </c>
@@ -3050,13 +3048,13 @@
         <v>155</v>
       </c>
       <c r="E35">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G35" s="7">
-        <v>113742856192</v>
+        <v>111642984448</v>
       </c>
       <c r="H35" s="6">
         <v>37.25</v>
@@ -3066,10 +3064,10 @@
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
-        <v>0.15658362989323837</v>
+        <v>0.13523131672597843</v>
       </c>
       <c r="K35" s="11">
-        <v>5.3538461538461535E-2</v>
+        <v>5.454545454545455E-2</v>
       </c>
       <c r="L35" s="13">
         <v>16863000000</v>
@@ -3084,16 +3082,16 @@
         <v>1</v>
       </c>
       <c r="P35" s="12">
-        <v>0.12462875203325478</v>
+        <v>0.12659341147381301</v>
       </c>
       <c r="Q35" s="12">
         <v>3.7613758029978586E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>126</v>
       </c>
@@ -3104,13 +3102,13 @@
         <v>168</v>
       </c>
       <c r="E36">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G36" s="7">
-        <v>46354022400</v>
+        <v>47413411840</v>
       </c>
       <c r="H36" s="6">
         <v>11.72</v>
@@ -3120,10 +3118,10 @@
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
-        <v>0.21999999999999997</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="K36" s="11">
-        <v>7.0491803278688522E-2</v>
+        <v>6.9243156199677941E-2</v>
       </c>
       <c r="L36" s="13">
         <v>6749146000</v>
@@ -3138,7 +3136,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>9.1338900700346573E-2</v>
+        <v>9.0129403293835897E-2</v>
       </c>
       <c r="Q36" s="12">
         <v>9.5261833390841127E-2</v>
@@ -3147,7 +3145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>127</v>
       </c>
@@ -3158,13 +3156,13 @@
         <v>80</v>
       </c>
       <c r="E37">
-        <v>4.8899999999999997</v>
+        <v>4.93</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G37" s="7">
-        <v>7168593408</v>
+        <v>7227232256</v>
       </c>
       <c r="H37" s="6">
         <v>5.04</v>
@@ -3174,10 +3172,10 @@
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
-        <v>0.4173913043478259</v>
+        <v>0.42898550724637663</v>
       </c>
       <c r="K37" s="11">
-        <v>9.815950920245399E-2</v>
+        <v>9.7363083164300201E-2</v>
       </c>
       <c r="L37" s="13">
         <v>784607000</v>
@@ -3192,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.54182145938124371</v>
+        <v>0.52073488063015305</v>
       </c>
       <c r="Q37" s="12">
         <v>9.9663185641922489E-2</v>
@@ -3201,7 +3199,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
@@ -3212,13 +3210,13 @@
         <v>171</v>
       </c>
       <c r="E38">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G38" s="7">
-        <v>24714563584</v>
+        <v>24828452864</v>
       </c>
       <c r="H38" s="6">
         <v>28.75</v>
@@ -3228,10 +3226,10 @@
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
-        <v>0.11168032786885251</v>
+        <v>0.11680327868852469</v>
       </c>
       <c r="K38" s="11">
-        <v>6.4516129032258063E-2</v>
+        <v>6.4220183486238522E-2</v>
       </c>
       <c r="L38" s="13">
         <v>3446618000</v>
@@ -3246,16 +3244,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>0.15677822911473666</v>
+        <v>0.15602168152308715</v>
       </c>
       <c r="Q38" s="12">
         <v>0.10133893359397213</v>
       </c>
       <c r="R38" s="14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
         <v>129</v>
       </c>
@@ -3266,13 +3264,13 @@
         <v>112</v>
       </c>
       <c r="E39">
-        <v>10.96</v>
+        <v>11.22</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G39" s="7">
-        <v>109460914176</v>
+        <v>112057614336</v>
       </c>
       <c r="H39" s="6">
         <v>11.56</v>
@@ -3282,10 +3280,10 @@
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
-        <v>0.87993138936535176</v>
+        <v>0.92452830188679247</v>
       </c>
       <c r="K39" s="11">
-        <v>4.5620437956204379E-2</v>
+        <v>4.4563279857397504E-2</v>
       </c>
       <c r="L39" s="13">
         <v>9432900000</v>
@@ -3300,16 +3298,16 @@
         <v>1</v>
       </c>
       <c r="P39" s="12">
-        <v>7.1647857486001235E-2</v>
+        <v>7.0262057209279694E-2</v>
       </c>
       <c r="Q39" s="12">
         <v>0.17359450999011755</v>
       </c>
       <c r="R39" s="14">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
         <v>130</v>
       </c>
@@ -3360,10 +3358,10 @@
         <v>0.10689920561026972</v>
       </c>
       <c r="R40" s="14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
         <v>131</v>
       </c>
@@ -3374,13 +3372,13 @@
         <v>175</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>22.05</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G41" s="7">
-        <v>24382820352</v>
+        <v>24438235136</v>
       </c>
       <c r="H41" s="6">
         <v>24.55</v>
@@ -3390,10 +3388,10 @@
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
-        <v>0.51515151515151514</v>
+        <v>0.51859504132231415</v>
       </c>
       <c r="K41" s="11">
-        <v>4.2727272727272725E-2</v>
+        <v>4.2630385487528344E-2</v>
       </c>
       <c r="L41" s="13">
         <v>3838344000</v>
@@ -3408,16 +3406,16 @@
         <v>1</v>
       </c>
       <c r="P41" s="12">
-        <v>9.0954347828542711E-2</v>
+        <v>9.0835070261810882E-2</v>
       </c>
       <c r="Q41" s="12">
         <v>4.7084186647510511E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
         <v>132</v>
       </c>
@@ -3428,13 +3426,13 @@
         <v>101</v>
       </c>
       <c r="E42">
-        <v>11.26</v>
+        <v>11.36</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G42" s="7">
-        <v>85298552832</v>
+        <v>86056083456</v>
       </c>
       <c r="H42" s="6">
         <v>11.5</v>
@@ -3444,10 +3442,10 @@
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
-        <v>0.32783018867924518</v>
+        <v>0.33962264150943389</v>
       </c>
       <c r="K42" s="11">
-        <v>6.99822380106572E-2</v>
+        <v>6.9366197183098596E-2</v>
       </c>
       <c r="L42" s="13">
         <v>8154000000</v>
@@ -3462,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="12">
-        <v>6.4403740674301074E-2</v>
+        <v>6.4020685879869976E-2</v>
       </c>
       <c r="Q42" s="12">
         <v>0.10245263104990703</v>
@@ -3471,7 +3469,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
         <v>133</v>
       </c>
@@ -3482,13 +3480,13 @@
         <v>178</v>
       </c>
       <c r="E43">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="7">
-        <v>4642591211520</v>
+        <v>4605217341440</v>
       </c>
       <c r="H43" s="6">
         <v>547</v>
@@ -3498,10 +3496,10 @@
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
-        <v>0.4613180515759312</v>
+        <v>0.44985673352435529</v>
       </c>
       <c r="K43" s="11">
-        <v>8.2921568627450978E-3</v>
+        <v>8.3577075098814225E-3</v>
       </c>
       <c r="L43" s="13">
         <v>253932000000</v>
@@ -3516,7 +3514,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>5.5552123649375187E-2</v>
+        <v>5.5980538209562711E-2</v>
       </c>
       <c r="Q43" s="12">
         <v>0.19352168899747973</v>
@@ -3525,7 +3523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
         <v>134</v>
       </c>
@@ -3536,13 +3534,13 @@
         <v>178</v>
       </c>
       <c r="E44">
-        <v>27.55</v>
+        <v>27.1</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G44" s="7">
-        <v>28136538112</v>
+        <v>27676958720</v>
       </c>
       <c r="H44" s="6">
         <v>36</v>
@@ -3552,7 +3550,7 @@
       </c>
       <c r="J44" s="12">
         <f t="shared" si="1"/>
-        <v>0.22991071428571441</v>
+        <v>0.2098214285714286</v>
       </c>
       <c r="K44" s="11">
         <v>0</v>
@@ -3570,16 +3568,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>-3.8865083660601265E-3</v>
+        <v>-3.9598102780594776E-3</v>
       </c>
       <c r="Q44" s="12">
         <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R44" s="14">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
         <v>136</v>
       </c>
@@ -3590,13 +3588,13 @@
         <v>181</v>
       </c>
       <c r="E45">
-        <v>18.440000000000001</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G45" s="7">
-        <v>520091009024</v>
+        <v>508519284736</v>
       </c>
       <c r="H45" s="6">
         <v>19.260000000000002</v>
@@ -3606,10 +3604,10 @@
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
-        <v>0.36390532544378718</v>
+        <v>0.32396449704142016</v>
       </c>
       <c r="K45" s="11">
-        <v>2.0607375271149673E-2</v>
+        <v>2.1229050279329611E-2</v>
       </c>
       <c r="L45" s="13">
         <v>52374992116</v>
@@ -3624,16 +3622,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>8.6837688985510905E-2</v>
+        <v>8.8425637480669741E-2</v>
       </c>
       <c r="Q45" s="12">
         <v>0.19428864891763736</v>
       </c>
       <c r="R45" s="14">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
         <v>137</v>
       </c>
@@ -3644,13 +3642,13 @@
         <v>101</v>
       </c>
       <c r="E46">
-        <v>5.0999999999999996</v>
+        <v>5.14</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G46" s="7">
-        <v>39479406592</v>
+        <v>39789047808</v>
       </c>
       <c r="H46" s="6">
         <v>5.49</v>
@@ -3660,10 +3658,10 @@
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
-        <v>0.34210526315789469</v>
+        <v>0.35263157894736841</v>
       </c>
       <c r="K46" s="11">
-        <v>7.509803921568628E-2</v>
+        <v>7.4513618677042814E-2</v>
       </c>
       <c r="L46" s="13">
         <v>5474000000</v>
@@ -3678,16 +3676,16 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>6.0066448420561427E-2</v>
+        <v>5.986305131194903E-2</v>
       </c>
       <c r="Q46" s="12">
         <v>9.2144023431582137E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
         <v>138</v>
       </c>
@@ -3698,26 +3696,26 @@
         <v>80</v>
       </c>
       <c r="E47">
-        <v>14.5</v>
+        <v>15.02</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G47" s="7">
-        <v>60871147520</v>
+        <v>63054114816</v>
       </c>
       <c r="H47" s="6">
-        <v>14.56</v>
+        <v>15.08</v>
       </c>
       <c r="I47" s="6">
         <v>10.98</v>
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
-        <v>0.32058287795992713</v>
+        <v>0.36794171220400718</v>
       </c>
       <c r="K47" s="11">
-        <v>6.1103448275862067E-2</v>
+        <v>5.8988015978695074E-2</v>
       </c>
       <c r="L47" s="13">
         <v>11996000000</v>
@@ -3732,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>0.14279397368178412</v>
+        <v>0.13917746450018836</v>
       </c>
       <c r="Q47" s="12">
         <v>8.6741482038526066E-2</v>
@@ -3741,7 +3739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
         <v>139</v>
       </c>
@@ -3752,13 +3750,13 @@
         <v>185</v>
       </c>
       <c r="E48">
-        <v>7.97</v>
+        <v>8.01</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G48" s="7">
-        <v>18779152384</v>
+        <v>18873401344</v>
       </c>
       <c r="H48" s="6">
         <v>11.68</v>
@@ -3768,7 +3766,7 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
-        <v>0.5356454720616568</v>
+        <v>0.5433526011560692</v>
       </c>
       <c r="K48" s="11">
         <v>0</v>
@@ -3786,16 +3784,16 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>0.12223007169246884</v>
+        <v>0.122132471770363</v>
       </c>
       <c r="Q48" s="12">
         <v>6.4862080854845933E-2</v>
       </c>
       <c r="R48" s="14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
         <v>140</v>
       </c>
@@ -3806,26 +3804,26 @@
         <v>187</v>
       </c>
       <c r="E49">
-        <v>33.75</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G49" s="7">
-        <v>23344199680</v>
+        <v>23032942592</v>
       </c>
       <c r="H49" s="6">
         <v>35.75</v>
       </c>
       <c r="I49" s="6">
-        <v>12.38</v>
+        <v>13.2</v>
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
-        <v>1.7261712439418413</v>
+        <v>1.5227272727272725</v>
       </c>
       <c r="K49" s="11">
-        <v>1.362962962962963E-2</v>
+        <v>1.3813813813813816E-2</v>
       </c>
       <c r="L49" s="13">
         <v>1323087000</v>
@@ -3840,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="P49" s="12">
-        <v>5.1268427139119555E-2</v>
+        <v>5.1894320976402654E-2</v>
       </c>
       <c r="Q49" s="12">
         <v>0.222258562943417</v>
@@ -3849,7 +3847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
         <v>141</v>
       </c>
@@ -3860,13 +3858,13 @@
         <v>189</v>
       </c>
       <c r="E50">
-        <v>334</v>
+        <v>341.8</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G50" s="7">
-        <v>124495159296</v>
+        <v>127261024256</v>
       </c>
       <c r="H50" s="6">
         <v>421.4</v>
@@ -3876,10 +3874,10 @@
       </c>
       <c r="J50" s="12">
         <f t="shared" si="1"/>
-        <v>0.48312611012433404</v>
+        <v>0.51776198934280648</v>
       </c>
       <c r="K50" s="11">
-        <v>2.155688622754491E-3</v>
+        <v>2.1064950263311876E-3</v>
       </c>
       <c r="L50" s="13">
         <v>1200000000</v>
@@ -3894,7 +3892,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P50" s="12">
-        <v>6.7150257796866272E-2</v>
+        <v>6.5825803633519697E-2</v>
       </c>
       <c r="Q50" s="12">
         <v>0.20495303159692571</v>
@@ -3903,7 +3901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
         <v>142</v>
       </c>
@@ -3914,13 +3912,13 @@
         <v>90</v>
       </c>
       <c r="E51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G51" s="7">
-        <v>3379130880</v>
+        <v>3556699904</v>
       </c>
       <c r="H51" s="6">
         <v>2.73</v>
@@ -3930,10 +3928,10 @@
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
-        <v>6.1452513966480327E-2</v>
+        <v>0.11731843575418988</v>
       </c>
       <c r="K51" s="11">
-        <v>2.9473684210526319E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="L51" s="13">
         <v>364157000</v>
@@ -3948,7 +3946,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P51" s="12">
-        <v>8.6692498863775544E-2</v>
+        <v>8.3392871887460709E-2</v>
       </c>
       <c r="Q51" s="12">
         <v>4.6334433386514377E-2</v>
@@ -3957,7 +3955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
         <v>143</v>
       </c>
@@ -3968,13 +3966,13 @@
         <v>90</v>
       </c>
       <c r="E52">
-        <v>13.4</v>
+        <v>13.54</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G52" s="7">
-        <v>75501494272</v>
+        <v>76290318336</v>
       </c>
       <c r="H52" s="6">
         <v>14.24</v>
@@ -3984,10 +3982,10 @@
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
-        <v>0.52099886492622005</v>
+        <v>0.53688989784335961</v>
       </c>
       <c r="K52" s="11">
-        <v>2.4701492537313432E-2</v>
+        <v>2.4446085672082722E-2</v>
       </c>
       <c r="L52" s="13">
         <v>6482967000</v>
@@ -4002,7 +4000,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>8.4558135136038812E-2</v>
+        <v>8.3751586377721829E-2</v>
       </c>
       <c r="Q52" s="12">
         <v>0.23588267049650188</v>
@@ -4011,7 +4009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
         <v>144</v>
       </c>
@@ -4022,13 +4020,13 @@
         <v>193</v>
       </c>
       <c r="E53">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G53" s="7">
-        <v>9019499520</v>
+        <v>9105399808</v>
       </c>
       <c r="H53" s="6">
         <v>3.04</v>
@@ -4038,10 +4036,10 @@
       </c>
       <c r="J53" s="12">
         <f t="shared" si="1"/>
-        <v>8.8082901554404236E-2</v>
+        <v>9.8445595854922407E-2</v>
       </c>
       <c r="K53" s="11">
-        <v>5.095238095238095E-2</v>
+        <v>5.0471698113207543E-2</v>
       </c>
       <c r="L53" s="13">
         <v>1938532000</v>
@@ -4056,16 +4054,16 @@
         <v>1</v>
       </c>
       <c r="P53" s="12">
-        <v>6.560613897790224E-2</v>
+        <v>6.5415965529776049E-2</v>
       </c>
       <c r="Q53" s="12">
         <v>3.8781191586606881E-2</v>
       </c>
       <c r="R53" s="14">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
         <v>145</v>
       </c>
@@ -4076,13 +4074,13 @@
         <v>107</v>
       </c>
       <c r="E54">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G54" s="7">
-        <v>73228992512</v>
+        <v>72102395904</v>
       </c>
       <c r="H54" s="6">
         <v>61.55</v>
@@ -4092,10 +4090,10 @@
       </c>
       <c r="J54" s="12">
         <f t="shared" si="1"/>
-        <v>0.30784708249496973</v>
+        <v>0.28772635814889336</v>
       </c>
       <c r="K54" s="11">
-        <v>1.7476923076923074E-2</v>
+        <v>1.7749999999999998E-2</v>
       </c>
       <c r="L54" s="13">
         <v>5261270000</v>
@@ -4110,7 +4108,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>7.1146490186410088E-2</v>
+        <v>7.2175686211558024E-2</v>
       </c>
       <c r="Q54" s="12">
         <v>0.12176329850933591</v>
@@ -4119,7 +4117,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
         <v>146</v>
       </c>
@@ -4130,13 +4128,13 @@
         <v>112</v>
       </c>
       <c r="E55">
-        <v>51</v>
+        <v>51.25</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G55" s="7">
-        <v>130499821568</v>
+        <v>131139526656</v>
       </c>
       <c r="H55" s="6">
         <v>71.7</v>
@@ -4146,10 +4144,10 @@
       </c>
       <c r="J55" s="12">
         <f t="shared" si="1"/>
-        <v>0.17106773823191745</v>
+        <v>0.17680826636050528</v>
       </c>
       <c r="K55" s="11">
-        <v>3.2156862745098039E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L55" s="13">
         <v>1279098000</v>
@@ -4160,11 +4158,20 @@
       <c r="N55" s="9" t="s">
         <v>196</v>
       </c>
+      <c r="O55" s="6">
+        <v>8.7546153846153842</v>
+      </c>
+      <c r="P55" s="12">
+        <v>7.6339630042846232E-2</v>
+      </c>
       <c r="Q55" s="12">
         <v>0.26583067696212276</v>
       </c>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R55" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
         <v>147</v>
       </c>
@@ -4175,13 +4182,13 @@
         <v>185</v>
       </c>
       <c r="E56">
-        <v>9.2899999999999991</v>
+        <v>9.16</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G56" s="7">
-        <v>115239665664</v>
+        <v>113627054080</v>
       </c>
       <c r="H56" s="6">
         <v>13.6</v>
@@ -4191,10 +4198,10 @@
       </c>
       <c r="J56" s="12">
         <f t="shared" si="1"/>
-        <v>0.4140030441400302</v>
+        <v>0.39421613394216126</v>
       </c>
       <c r="K56" s="11">
-        <v>5.3821313240043061E-3</v>
+        <v>5.4585152838427953E-3</v>
       </c>
       <c r="L56" s="13">
         <v>2125459000</v>
@@ -4209,23 +4216,121 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P56" s="12">
-        <v>0.13816921221661033</v>
+        <v>0.14007819590180975</v>
       </c>
       <c r="Q56" s="12">
         <v>0.23097158924015673</v>
       </c>
       <c r="R56" s="14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G57" s="7">
+        <v>419697328128</v>
+      </c>
+      <c r="H57" s="6">
+        <v>59.7</v>
+      </c>
+      <c r="I57" s="6">
+        <v>15.24</v>
+      </c>
+      <c r="J57" s="12">
+        <f t="shared" si="1"/>
+        <v>1.6771653543307083</v>
+      </c>
+      <c r="K57" s="11">
+        <v>0</v>
+      </c>
+      <c r="L57" s="13">
+        <v>984027000</v>
+      </c>
+      <c r="M57" s="13">
+        <v>32183526000</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="O57" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P57" s="12">
+        <v>1.6457375883070016E-2</v>
+      </c>
+      <c r="Q57" s="12">
+        <v>3.0575487595734537E-2</v>
+      </c>
+      <c r="R57" s="14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
         <v>200</v>
+      </c>
+      <c r="C58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58">
+        <v>6.94</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G58" s="7">
+        <v>3981505792</v>
+      </c>
+      <c r="H58" s="6">
+        <v>9.24</v>
+      </c>
+      <c r="I58" s="6">
+        <v>6.85</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="1"/>
+        <v>1.3138686131386912E-2</v>
+      </c>
+      <c r="K58" s="11">
+        <v>8.2132564841498543E-2</v>
+      </c>
+      <c r="L58" s="13">
+        <v>498120000</v>
+      </c>
+      <c r="M58" s="13">
+        <v>3284848000</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O58" s="6">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12">
+        <v>9.6372678939714296E-2</v>
+      </c>
+      <c r="Q58" s="12">
+        <v>0.15164171979951585</v>
+      </c>
+      <c r="R58" s="14">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4251,25 +4356,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B46D05-099C-4A4C-836A-6062A20AA7D3}">
   <dimension ref="B1:V11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4326,7 +4431,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
@@ -4380,7 +4485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -4434,7 +4539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -4488,7 +4593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4542,7 +4647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -4596,7 +4701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
@@ -4650,7 +4755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
@@ -4704,7 +4809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4758,7 +4863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4812,7 +4917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4879,25 +4984,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FA5E83-3B3C-124C-A85B-B3DA799E441B}">
   <dimension ref="B1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4954,7 +5059,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>41</v>
       </c>
@@ -5008,7 +5113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
@@ -5062,7 +5167,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
@@ -5129,23 +5234,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54703291-9A5D-4E46-9F96-9938DF840B6E}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="210.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.6875" customWidth="1"/>
+    <col min="2" max="2" width="210.1875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
       <c r="B3" s="15" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
         <v>148</v>
       </c>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC05381-2F39-4318-8844-467DBFE2264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163C4586-0D4D-479C-8575-090390B12A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -1257,41 +1257,41 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E2">
-        <v>14.74</v>
+        <v>3.11</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="7">
-        <v>266401906688</v>
+        <v>8699354112</v>
       </c>
       <c r="H2" s="6">
-        <v>15.14</v>
+        <v>3.35</v>
       </c>
       <c r="I2" s="6">
-        <v>9.52</v>
+        <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.54831932773109249</v>
+        <f>E2/I2-1</f>
+        <v>0.31779661016949157</v>
       </c>
       <c r="K2" s="11">
-        <v>0.10515603799185889</v>
+        <v>4.9196141479099682E-2</v>
       </c>
       <c r="L2" s="13">
-        <v>70144988000</v>
+        <v>1871151000</v>
       </c>
       <c r="M2" s="13">
-        <v>269343749000</v>
+        <v>6461978000</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>52</v>
@@ -1300,52 +1300,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.49612618476500991</v>
+        <v>0.44405559305801723</v>
       </c>
       <c r="Q2" s="12">
-        <v>0.26042924055386191</v>
+        <v>0.28956319566547578</v>
       </c>
       <c r="R2" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3">
-        <v>2.88</v>
+        <v>14.74</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G3" s="7">
-        <v>17859514368</v>
+        <v>266401906688</v>
       </c>
       <c r="H3" s="6">
-        <v>5.33</v>
+        <v>15.14</v>
       </c>
       <c r="I3" s="6">
-        <v>2.11</v>
+        <v>9.52</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>0.36492890995260674</v>
+        <f>E3/I3-1</f>
+        <v>0.54831932773109249</v>
       </c>
       <c r="K3" s="11">
-        <v>5.5555555555555559E-2</v>
+        <v>0.10515603799185889</v>
       </c>
       <c r="L3" s="13">
-        <v>2906500000</v>
+        <v>70144988000</v>
       </c>
       <c r="M3" s="13">
-        <v>10569000000</v>
+        <v>269343749000</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>52</v>
@@ -1354,106 +1354,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.16638325081256819</v>
+        <v>0.49612618476500991</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.27500236540826944</v>
+        <v>0.26042924055386191</v>
       </c>
       <c r="R3" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="7">
-        <v>2599524864</v>
+        <v>17859514368</v>
       </c>
       <c r="H4" s="6">
-        <v>3.34</v>
+        <v>5.33</v>
       </c>
       <c r="I4" s="6">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.30208333333333348</v>
+        <f>E4/I4-1</f>
+        <v>0.36492890995260674</v>
       </c>
       <c r="K4" s="11">
-        <v>0.11679999999999999</v>
+        <v>5.5555555555555559E-2</v>
       </c>
       <c r="L4" s="13">
-        <v>762183000</v>
+        <v>2906500000</v>
       </c>
       <c r="M4" s="13">
-        <v>5008319000</v>
+        <v>10569000000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O4" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.2278871120399093</v>
+        <v>0.16638325081256819</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.15218339726363278</v>
+        <v>0.27500236540826944</v>
       </c>
       <c r="R4" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <v>6.28</v>
+        <v>15.1</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="7">
-        <v>7658523136</v>
+        <v>31377195008</v>
       </c>
       <c r="H5" s="6">
-        <v>8.6</v>
+        <v>15.48</v>
       </c>
       <c r="I5" s="6">
-        <v>3.46</v>
+        <v>7.96</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.81502890173410414</v>
+        <f>E5/I5-1</f>
+        <v>0.89698492462311563</v>
       </c>
       <c r="K5" s="11">
-        <v>2.2452229299363056E-2</v>
+        <v>7.4172185430463583E-2</v>
       </c>
       <c r="L5" s="13">
-        <v>921702000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M5" s="13">
-        <v>5262544000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>52</v>
@@ -1462,160 +1462,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P5" s="12">
-        <v>0.18931080612829809</v>
+        <v>0.16717087768969968</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R5" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>8.85</v>
+        <v>2.63</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="7">
-        <v>142903607296</v>
+        <v>13389514752</v>
       </c>
       <c r="H6" s="6">
-        <v>10.76</v>
+        <v>3.64</v>
       </c>
       <c r="I6" s="6">
-        <v>7.16</v>
+        <v>2.23</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.2360335195530725</v>
+        <f>E6/I6-1</f>
+        <v>0.17937219730941689</v>
       </c>
       <c r="K6" s="11">
-        <v>5.4124293785310737E-2</v>
+        <v>0.11406844106463879</v>
       </c>
       <c r="L6" s="13">
-        <v>32866046000</v>
+        <v>2527643000</v>
       </c>
       <c r="M6" s="13">
-        <v>215280386000</v>
+        <v>16480074000</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O6" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>0.19525105677556878</v>
+        <v>0.43903173388000094</v>
       </c>
       <c r="Q6" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R6" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="E7">
-        <v>8.27</v>
+        <v>9.16</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="7">
-        <v>71609933824</v>
+        <v>113627054080</v>
       </c>
       <c r="H7" s="6">
-        <v>9.23</v>
+        <v>13.6</v>
       </c>
       <c r="I7" s="6">
-        <v>6.81</v>
+        <v>6.57</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0.21439060205580041</v>
+        <f>E7/I7-1</f>
+        <v>0.39421613394216126</v>
       </c>
       <c r="K7" s="11">
-        <v>3.8210399032648126E-2</v>
+        <v>5.4585152838427953E-3</v>
       </c>
       <c r="L7" s="13">
-        <v>13438000000</v>
+        <v>2125459000</v>
       </c>
       <c r="M7" s="13">
-        <v>88611000000</v>
+        <v>9202253000</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="O7" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P7" s="12">
-        <v>0.21169239559663214</v>
+        <v>0.14007819590180975</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.23097158924015673</v>
       </c>
       <c r="R7" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>15.1</v>
+        <v>6.28</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="7">
-        <v>31377195008</v>
+        <v>7658523136</v>
       </c>
       <c r="H8" s="6">
-        <v>15.48</v>
+        <v>8.6</v>
       </c>
       <c r="I8" s="6">
-        <v>7.96</v>
+        <v>3.46</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.89698492462311563</v>
+        <f>E8/I8-1</f>
+        <v>0.81502890173410414</v>
       </c>
       <c r="K8" s="11">
-        <v>7.4172185430463583E-2</v>
+        <v>2.2452229299363056E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>5451928473.2399998</v>
+        <v>921702000</v>
       </c>
       <c r="M8" s="13">
-        <v>25994816572.18</v>
+        <v>5262544000</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>52</v>
@@ -1624,214 +1624,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.16717087768969968</v>
+        <v>0.18931080612829809</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R8" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E9">
-        <v>4.7699999999999996</v>
+        <v>14.4</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="7">
-        <v>5054196736</v>
+        <v>11984947200</v>
       </c>
       <c r="H9" s="6">
-        <v>6.26</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I9" s="6">
-        <v>3.97</v>
+        <v>12.12</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20151133501259433</v>
+        <f>E9/I9-1</f>
+        <v>0.18811881188118829</v>
       </c>
       <c r="K9" s="11">
-        <v>0.10272536687631029</v>
+        <v>1.0277777777777776E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>866801000</v>
+        <v>199557000</v>
       </c>
       <c r="M9" s="13">
-        <v>7530053000</v>
+        <v>1108087000</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O9" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P9" s="12">
-        <v>0.42109939991480938</v>
+        <v>0.17405845676300949</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R9" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="E10">
-        <v>14.4</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="7">
-        <v>11984947200</v>
+        <v>2599524864</v>
       </c>
       <c r="H10" s="6">
-        <v>19.440000000000001</v>
+        <v>3.34</v>
       </c>
       <c r="I10" s="6">
-        <v>12.12</v>
+        <v>1.92</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.18811881188118829</v>
+        <f>E10/I10-1</f>
+        <v>0.30208333333333348</v>
       </c>
       <c r="K10" s="11">
-        <v>1.0277777777777776E-2</v>
+        <v>0.11679999999999999</v>
       </c>
       <c r="L10" s="13">
-        <v>199557000</v>
+        <v>762183000</v>
       </c>
       <c r="M10" s="13">
-        <v>1108087000</v>
+        <v>5008319000</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O10" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.17405845676300949</v>
+        <v>0.2278871120399093</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.15218339726363278</v>
       </c>
       <c r="R10" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>74</v>
       </c>
       <c r="E11">
-        <v>5.0199999999999996</v>
+        <v>4.53</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="7">
-        <v>14321156096</v>
+        <v>52238151680</v>
       </c>
       <c r="H11" s="6">
-        <v>6.21</v>
+        <v>5.14</v>
       </c>
       <c r="I11" s="6">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>0.55900621118012395</v>
+        <f>E11/I11-1</f>
+        <v>0.30924855491329484</v>
       </c>
       <c r="K11" s="11">
-        <v>8.3665338645418346E-3</v>
+        <v>5.2097130242825598E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>259348000</v>
+        <v>4734613000</v>
       </c>
       <c r="M11" s="13">
-        <v>1677627000</v>
+        <v>16213395000</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="O11" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P11" s="12">
-        <v>0.16111230357181586</v>
+        <v>0.10318129921430115</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R11" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E12">
-        <v>4.53</v>
+        <v>8.85</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="7">
-        <v>52238151680</v>
+        <v>142903607296</v>
       </c>
       <c r="H12" s="6">
-        <v>5.14</v>
+        <v>10.76</v>
       </c>
       <c r="I12" s="6">
-        <v>3.46</v>
+        <v>7.16</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.30924855491329484</v>
+        <f>E12/I12-1</f>
+        <v>0.2360335195530725</v>
       </c>
       <c r="K12" s="11">
-        <v>5.2097130242825598E-2</v>
+        <v>5.4124293785310737E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>4734613000</v>
+        <v>32866046000</v>
       </c>
       <c r="M12" s="13">
-        <v>16213395000</v>
+        <v>215280386000</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>52</v>
@@ -1840,52 +1840,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.10318129921430115</v>
+        <v>0.19525105677556878</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R12" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E13">
-        <v>6.24</v>
+        <v>8.27</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="7">
-        <v>56579637248</v>
+        <v>71609933824</v>
       </c>
       <c r="H13" s="6">
-        <v>7.38</v>
+        <v>9.23</v>
       </c>
       <c r="I13" s="6">
-        <v>3.39</v>
+        <v>6.81</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
-        <v>0.84070796460176989</v>
+        <f>E13/I13-1</f>
+        <v>0.21439060205580041</v>
       </c>
       <c r="K13" s="11">
-        <v>4.9198717948717947E-2</v>
+        <v>3.8210399032648126E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>5594372000</v>
+        <v>13438000000</v>
       </c>
       <c r="M13" s="13">
-        <v>26933044000</v>
+        <v>88611000000</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>52</v>
@@ -1894,13 +1894,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.12510216016396158</v>
+        <v>0.21169239559663214</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R13" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -1929,7 +1929,7 @@
         <v>4.12</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
+        <f>E14/I14-1</f>
         <v>0.27184466019417486</v>
       </c>
       <c r="K14" s="11">
@@ -1959,41 +1959,41 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E15">
-        <v>391</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="7">
-        <v>494161428480</v>
+        <v>5054196736</v>
       </c>
       <c r="H15" s="6">
-        <v>399.6</v>
+        <v>6.26</v>
       </c>
       <c r="I15" s="6">
-        <v>218.4</v>
+        <v>3.97</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
-        <v>0.79029304029304015</v>
+        <f>E15/I15-1</f>
+        <v>0.20151133501259433</v>
       </c>
       <c r="K15" s="11">
-        <v>2.3682864450127877E-2</v>
+        <v>0.10272536687631029</v>
       </c>
       <c r="L15" s="13">
-        <v>20744000000</v>
+        <v>866801000</v>
       </c>
       <c r="M15" s="13">
-        <v>53852000000</v>
+        <v>7530053000</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>69</v>
@@ -2002,106 +2002,106 @@
         <v>1</v>
       </c>
       <c r="P15" s="12">
-        <v>5.7448213422109484E-2</v>
+        <v>0.42109939991480938</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R15" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="E16">
-        <v>5.86</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="7">
-        <v>4566123520</v>
+        <v>14321156096</v>
       </c>
       <c r="H16" s="6">
-        <v>8.09</v>
+        <v>6.21</v>
       </c>
       <c r="I16" s="6">
-        <v>4.0199999999999996</v>
+        <v>3.22</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="0"/>
-        <v>0.45771144278606979</v>
+        <f>E16/I16-1</f>
+        <v>0.55900621118012395</v>
       </c>
       <c r="K16" s="11">
-        <v>2.9010238907849831E-2</v>
+        <v>8.3665338645418346E-3</v>
       </c>
       <c r="L16" s="13">
-        <v>437453000</v>
+        <v>259348000</v>
       </c>
       <c r="M16" s="13">
-        <v>4911072000</v>
+        <v>1677627000</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O16" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P16" s="12">
-        <v>0.19214560366758091</v>
+        <v>0.16111230357181586</v>
       </c>
       <c r="Q16" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R16" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E17">
-        <v>12.34</v>
+        <v>6.24</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="7">
-        <v>57997750272</v>
+        <v>56579637248</v>
       </c>
       <c r="H17" s="6">
-        <v>13.56</v>
+        <v>7.38</v>
       </c>
       <c r="I17" s="6">
-        <v>7.51</v>
+        <v>3.39</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="0"/>
-        <v>0.64314247669773628</v>
+        <f>E17/I17-1</f>
+        <v>0.84070796460176989</v>
       </c>
       <c r="K17" s="11">
-        <v>3.5494327390599677E-2</v>
+        <v>4.9198717948717947E-2</v>
       </c>
       <c r="L17" s="13">
-        <v>3967214824.1399999</v>
+        <v>5594372000</v>
       </c>
       <c r="M17" s="13">
-        <v>41038539262.660004</v>
+        <v>26933044000</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>52</v>
@@ -2110,106 +2110,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.13041654887075355</v>
+        <v>0.12510216016396158</v>
       </c>
       <c r="Q17" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R17" s="14">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E18">
-        <v>50.45</v>
+        <v>4.93</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="7">
-        <v>137104433152</v>
+        <v>7227232256</v>
       </c>
       <c r="H18" s="6">
-        <v>82.25</v>
+        <v>5.04</v>
       </c>
       <c r="I18" s="6">
-        <v>37.85</v>
+        <v>3.45</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="0"/>
-        <v>0.33289299867899613</v>
+        <f>E18/I18-1</f>
+        <v>0.42898550724637663</v>
       </c>
       <c r="K18" s="11">
-        <v>2.0812685827552031E-2</v>
+        <v>9.7363083164300201E-2</v>
       </c>
       <c r="L18" s="13">
-        <v>6350637223.7200003</v>
+        <v>784607000</v>
       </c>
       <c r="M18" s="13">
-        <v>57896384836.860001</v>
+        <v>7872586000</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O18" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P18" s="12">
-        <v>6.4361071109758666E-2</v>
+        <v>0.52073488063015305</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.10968970241604512</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R18" s="14">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E19">
-        <v>1.46</v>
+        <v>95.6</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="7">
-        <v>7975293952</v>
+        <v>266533748736</v>
       </c>
       <c r="H19" s="6">
-        <v>1.82</v>
+        <v>107.5</v>
       </c>
       <c r="I19" s="6">
-        <v>0.81</v>
+        <v>65.55</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" si="0"/>
-        <v>0.80246913580246892</v>
+        <f>E19/I19-1</f>
+        <v>0.45842868039664375</v>
       </c>
       <c r="K19" s="11">
-        <v>2.3287671232876714E-2</v>
+        <v>2.3200836820083684E-2</v>
       </c>
       <c r="L19" s="13">
-        <v>1384865000</v>
+        <v>22510000000</v>
       </c>
       <c r="M19" s="13">
-        <v>23827484000</v>
+        <v>82545000000</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>52</v>
@@ -2218,106 +2218,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P19" s="12">
-        <v>7.7509454513107826E-2</v>
+        <v>8.4558705548000476E-2</v>
       </c>
       <c r="Q19" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>0.27269973953601068</v>
       </c>
       <c r="R19" s="14">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="E20">
-        <v>6.85</v>
+        <v>3.83</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="7">
-        <v>7148248576</v>
+        <v>5497620480</v>
       </c>
       <c r="H20" s="6">
-        <v>6.93</v>
+        <v>7.92</v>
       </c>
       <c r="I20" s="6">
-        <v>4.0199999999999996</v>
+        <v>2.36</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="0"/>
-        <v>0.70398009950248763</v>
+        <f>E20/I20-1</f>
+        <v>0.62288135593220351</v>
       </c>
       <c r="K20" s="11">
-        <v>0</v>
+        <v>6.6318537859007834E-2</v>
       </c>
       <c r="L20" s="13">
-        <v>303335000</v>
+        <v>811880000</v>
       </c>
       <c r="M20" s="13">
-        <v>3620162000</v>
+        <v>5532140000</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O20" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>5.0102476266993719E-2</v>
+        <v>0.16416567610994109</v>
       </c>
       <c r="Q20" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R20" s="14">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>11.72</v>
+        <v>13.54</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="7">
-        <v>206281392128</v>
+        <v>76290318336</v>
       </c>
       <c r="H21" s="6">
-        <v>12.46</v>
+        <v>14.24</v>
       </c>
       <c r="I21" s="6">
-        <v>9.1</v>
+        <v>8.81</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="0"/>
-        <v>0.287912087912088</v>
+        <f>E21/I21-1</f>
+        <v>0.53688989784335961</v>
       </c>
       <c r="K21" s="11">
-        <v>3.5580204778156994E-2</v>
+        <v>2.4446085672082722E-2</v>
       </c>
       <c r="L21" s="13">
-        <v>16758000000</v>
+        <v>6482967000</v>
       </c>
       <c r="M21" s="13">
-        <v>269590000000</v>
+        <v>27483863000</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>52</v>
@@ -2326,106 +2326,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>5.9210027773688667E-2</v>
+        <v>8.3751586377721829E-2</v>
       </c>
       <c r="Q21" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R21" s="14">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E22">
-        <v>2.63</v>
+        <v>51.25</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="7">
-        <v>13389514752</v>
+        <v>131139526656</v>
       </c>
       <c r="H22" s="6">
-        <v>3.64</v>
+        <v>71.7</v>
       </c>
       <c r="I22" s="6">
-        <v>2.23</v>
+        <v>43.55</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="0"/>
-        <v>0.17937219730941689</v>
+        <f>E22/I22-1</f>
+        <v>0.17680826636050528</v>
       </c>
       <c r="K22" s="11">
-        <v>0.11406844106463879</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L22" s="13">
-        <v>2527643000</v>
+        <v>1279098000</v>
       </c>
       <c r="M22" s="13">
-        <v>16480074000</v>
+        <v>4811702000</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="O22" s="6">
-        <v>1</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P22" s="12">
-        <v>0.43903173388000094</v>
+        <v>7.6339630042846232E-2</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R22" s="14">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="E23">
-        <v>3.11</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="7">
-        <v>8699354112</v>
+        <v>508519284736</v>
       </c>
       <c r="H23" s="6">
-        <v>3.35</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="I23" s="6">
-        <v>2.36</v>
+        <v>13.52</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="0"/>
-        <v>0.31779661016949157</v>
+        <f>E23/I23-1</f>
+        <v>0.32396449704142016</v>
       </c>
       <c r="K23" s="11">
-        <v>4.9196141479099682E-2</v>
+        <v>2.1229050279329611E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>1871151000</v>
+        <v>52374992116</v>
       </c>
       <c r="M23" s="13">
-        <v>6461978000</v>
+        <v>269573093476</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>52</v>
@@ -2434,160 +2434,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.44405559305801723</v>
+        <v>8.8425637480669741E-2</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.28956319566547578</v>
+        <v>0.19428864891763736</v>
       </c>
       <c r="R23" s="14">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E24">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="7">
-        <v>754577702912</v>
+        <v>4566123520</v>
       </c>
       <c r="H24" s="6">
-        <v>6.98</v>
+        <v>8.09</v>
       </c>
       <c r="I24" s="6">
-        <v>4.08</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46078431372549011</v>
+        <f>E24/I24-1</f>
+        <v>0.45771144278606979</v>
       </c>
       <c r="K24" s="11">
-        <v>4.3624161073825503E-2</v>
+        <v>2.9010238907849831E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>44563000000</v>
+        <v>437453000</v>
       </c>
       <c r="M24" s="13">
-        <v>463922000000</v>
+        <v>4911072000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O24" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P24" s="12">
-        <v>6.5072504456515662E-2</v>
+        <v>0.19214560366758091</v>
       </c>
       <c r="Q24" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R24" s="14">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="E25">
-        <v>3.83</v>
+        <v>22</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="7">
-        <v>5497620480</v>
+        <v>49944842240</v>
       </c>
       <c r="H25" s="6">
-        <v>7.92</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="I25" s="6">
-        <v>2.36</v>
+        <v>19.940000000000001</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="0"/>
-        <v>0.62288135593220351</v>
+        <f>E25/I25-1</f>
+        <v>0.10330992978936804</v>
       </c>
       <c r="K25" s="11">
-        <v>6.6318537859007834E-2</v>
+        <v>4.3181818181818182E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>811880000</v>
+        <v>8486605000</v>
       </c>
       <c r="M25" s="13">
-        <v>5532140000</v>
+        <v>64172826000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O25" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>0.16416567610994109</v>
+        <v>0.1287045858881023</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.14675695119790894</v>
+        <v>0.13224608497060733</v>
       </c>
       <c r="R25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>391</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="7">
-        <v>49944842240</v>
+        <v>494161428480</v>
       </c>
       <c r="H26" s="6">
-        <v>35.200000000000003</v>
+        <v>399.6</v>
       </c>
       <c r="I26" s="6">
-        <v>19.940000000000001</v>
+        <v>218.4</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="0"/>
-        <v>0.10330992978936804</v>
+        <f>E26/I26-1</f>
+        <v>0.79029304029304015</v>
       </c>
       <c r="K26" s="11">
-        <v>4.3181818181818182E-2</v>
+        <v>2.3682864450127877E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>8486605000</v>
+        <v>20744000000</v>
       </c>
       <c r="M26" s="13">
-        <v>64172826000</v>
+        <v>53852000000</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>69</v>
@@ -2596,52 +2596,52 @@
         <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>0.1287045858881023</v>
+        <v>5.7448213422109484E-2</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.13224608497060733</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R26" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="E27">
-        <v>12.68</v>
+        <v>5.99</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="7">
-        <v>13022486528</v>
+        <v>9743992832</v>
       </c>
       <c r="H27" s="6">
-        <v>14.5</v>
+        <v>7.05</v>
       </c>
       <c r="I27" s="6">
-        <v>10.36</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="0"/>
-        <v>0.22393822393822393</v>
+        <f>E27/I27-1</f>
+        <v>0.40281030444964894</v>
       </c>
       <c r="K27" s="11">
-        <v>8.5173501577287078E-2</v>
+        <v>4.6744574290484141E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>984000000</v>
+        <v>4094312000</v>
       </c>
       <c r="M27" s="13">
-        <v>101944000000</v>
+        <v>37637054000</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>69</v>
@@ -2650,52 +2650,52 @@
         <v>1</v>
       </c>
       <c r="P27" s="12">
-        <v>2.59134992193472E-2</v>
+        <v>0.1357513317572113</v>
       </c>
       <c r="Q27" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R27" s="14">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E28">
-        <v>58.05</v>
+        <v>21.8</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="7">
-        <v>162675261440</v>
+        <v>24828452864</v>
       </c>
       <c r="H28" s="6">
-        <v>60</v>
+        <v>28.75</v>
       </c>
       <c r="I28" s="6">
-        <v>38.4</v>
+        <v>19.52</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
-        <v>0.51171875</v>
+        <f>E28/I28-1</f>
+        <v>0.11680327868852469</v>
       </c>
       <c r="K28" s="11">
-        <v>3.1007751937984499E-2</v>
+        <v>6.4220183486238522E-2</v>
       </c>
       <c r="L28" s="13">
-        <v>8955723006</v>
+        <v>3446618000</v>
       </c>
       <c r="M28" s="13">
-        <v>47495870210</v>
+        <v>34010798000</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>52</v>
@@ -2704,52 +2704,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>6.0318143253415502E-2</v>
+        <v>0.15602168152308715</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R28" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E29">
-        <v>20.65</v>
+        <v>216.6</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="7">
-        <v>128567304192</v>
+        <v>287679479808</v>
       </c>
       <c r="H29" s="6">
-        <v>26.6</v>
+        <v>235</v>
       </c>
       <c r="I29" s="6">
-        <v>16.02</v>
+        <v>34.4</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="0"/>
-        <v>0.28901373283395748</v>
+        <f>E29/I29-1</f>
+        <v>5.2965116279069768</v>
       </c>
       <c r="K29" s="11">
-        <v>3.4382566585956419E-2</v>
+        <v>3.7626962142197598E-3</v>
       </c>
       <c r="L29" s="13">
-        <v>10795274825</v>
+        <v>4414795000</v>
       </c>
       <c r="M29" s="13">
-        <v>215275428010</v>
+        <v>10683505000</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>52</v>
@@ -2758,160 +2758,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P29" s="12">
-        <v>0.13552022486560977</v>
+        <v>1.6714886709713026E-2</v>
       </c>
       <c r="Q29" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.41323470153287706</v>
       </c>
       <c r="R29" s="14">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="E30">
-        <v>1.71</v>
+        <v>6.94</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="7">
-        <v>6086522880</v>
+        <v>3981505792</v>
       </c>
       <c r="H30" s="6">
-        <v>2.95</v>
+        <v>9.24</v>
       </c>
       <c r="I30" s="6">
-        <v>1.37</v>
+        <v>6.85</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
-        <v>0.24817518248175174</v>
+        <f>E30/I30-1</f>
+        <v>1.3138686131386912E-2</v>
       </c>
       <c r="K30" s="11">
-        <v>5.4970760233918128E-2</v>
+        <v>8.2132564841498543E-2</v>
       </c>
       <c r="L30" s="13">
-        <v>2220197000</v>
+        <v>498120000</v>
       </c>
       <c r="M30" s="13">
-        <v>71097505000</v>
+        <v>3284848000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O30" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P30" s="12">
-        <v>0.12244255356679254</v>
+        <v>9.6372678939714296E-2</v>
       </c>
       <c r="Q30" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>0.15164171979951585</v>
       </c>
       <c r="R30" s="14">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="E31">
-        <v>95.6</v>
+        <v>341.8</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="7">
-        <v>266533748736</v>
+        <v>127261024256</v>
       </c>
       <c r="H31" s="6">
-        <v>107.5</v>
+        <v>421.4</v>
       </c>
       <c r="I31" s="6">
-        <v>65.55</v>
+        <v>225.2</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="0"/>
-        <v>0.45842868039664375</v>
+        <f>E31/I31-1</f>
+        <v>0.51776198934280648</v>
       </c>
       <c r="K31" s="11">
-        <v>2.3200836820083684E-2</v>
+        <v>2.1064950263311876E-3</v>
       </c>
       <c r="L31" s="13">
-        <v>22510000000</v>
+        <v>1200000000</v>
       </c>
       <c r="M31" s="13">
-        <v>82545000000</v>
+        <v>5855000000</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="O31" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P31" s="12">
-        <v>8.4558705548000476E-2</v>
+        <v>6.5825803633519697E-2</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.27269973953601068</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R31" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E32">
-        <v>216.6</v>
+        <v>12.34</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G32" s="7">
-        <v>287679479808</v>
+        <v>57997750272</v>
       </c>
       <c r="H32" s="6">
-        <v>235</v>
+        <v>13.56</v>
       </c>
       <c r="I32" s="6">
-        <v>34.4</v>
+        <v>7.51</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
-        <v>5.2965116279069768</v>
+        <f>E32/I32-1</f>
+        <v>0.64314247669773628</v>
       </c>
       <c r="K32" s="11">
-        <v>3.7626962142197598E-3</v>
+        <v>3.5494327390599677E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>4414795000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M32" s="13">
-        <v>10683505000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>52</v>
@@ -2920,52 +2920,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P32" s="12">
-        <v>1.6714886709713026E-2</v>
+        <v>0.13041654887075355</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.41323470153287706</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R32" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="E33">
-        <v>5.99</v>
+        <v>11.22</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G33" s="7">
-        <v>9743992832</v>
+        <v>112057614336</v>
       </c>
       <c r="H33" s="6">
-        <v>7.05</v>
+        <v>11.56</v>
       </c>
       <c r="I33" s="6">
-        <v>4.2699999999999996</v>
+        <v>5.83</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
-        <v>0.40281030444964894</v>
+        <f>E33/I33-1</f>
+        <v>0.92452830188679247</v>
       </c>
       <c r="K33" s="11">
-        <v>4.6744574290484141E-2</v>
+        <v>4.4563279857397504E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>4094312000</v>
+        <v>9432900000</v>
       </c>
       <c r="M33" s="13">
-        <v>37637054000</v>
+        <v>54338700000</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>69</v>
@@ -2974,106 +2974,106 @@
         <v>1</v>
       </c>
       <c r="P33" s="12">
-        <v>0.1357513317572113</v>
+        <v>7.0262057209279694E-2</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.17359450999011755</v>
       </c>
       <c r="R33" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E34">
-        <v>9.67</v>
+        <v>15.02</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G34" s="7">
-        <v>295882653696</v>
+        <v>63054114816</v>
       </c>
       <c r="H34" s="6">
-        <v>11.56</v>
+        <v>15.08</v>
       </c>
       <c r="I34" s="6">
-        <v>5.88</v>
+        <v>10.98</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>0.64455782312925169</v>
+        <f>E34/I34-1</f>
+        <v>0.36794171220400718</v>
       </c>
       <c r="K34" s="11">
-        <v>0</v>
+        <v>5.8988015978695074E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>26994000000</v>
+        <v>11996000000</v>
       </c>
       <c r="M34" s="13">
-        <v>363169000000</v>
+        <v>138296000000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O34" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P34" s="12">
-        <v>9.3653995073074411E-2</v>
+        <v>0.13917746450018836</v>
       </c>
       <c r="Q34" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R34" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="E35">
-        <v>31.9</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G35" s="7">
-        <v>111642984448</v>
+        <v>23032942592</v>
       </c>
       <c r="H35" s="6">
-        <v>37.25</v>
+        <v>35.75</v>
       </c>
       <c r="I35" s="6">
-        <v>28.1</v>
+        <v>13.2</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="1"/>
-        <v>0.13523131672597843</v>
+        <f>E35/I35-1</f>
+        <v>1.5227272727272725</v>
       </c>
       <c r="K35" s="11">
-        <v>5.454545454545455E-2</v>
+        <v>1.3813813813813816E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>16863000000</v>
+        <v>1323087000</v>
       </c>
       <c r="M35" s="13">
-        <v>448320000000</v>
+        <v>5952918000</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>69</v>
@@ -3082,52 +3082,52 @@
         <v>1</v>
       </c>
       <c r="P35" s="12">
-        <v>0.12659341147381301</v>
+        <v>5.1894320976402654E-2</v>
       </c>
       <c r="Q35" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R35" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E36">
-        <v>6.21</v>
+        <v>58.05</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G36" s="7">
-        <v>47413411840</v>
+        <v>162675261440</v>
       </c>
       <c r="H36" s="6">
-        <v>11.72</v>
+        <v>60</v>
       </c>
       <c r="I36" s="6">
-        <v>5</v>
+        <v>38.4</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="1"/>
-        <v>0.24199999999999999</v>
+        <f>E36/I36-1</f>
+        <v>0.51171875</v>
       </c>
       <c r="K36" s="11">
-        <v>6.9243156199677941E-2</v>
+        <v>3.1007751937984499E-2</v>
       </c>
       <c r="L36" s="13">
-        <v>6749146000</v>
+        <v>8955723006</v>
       </c>
       <c r="M36" s="13">
-        <v>70848374000</v>
+        <v>47495870210</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>52</v>
@@ -3136,106 +3136,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>9.0129403293835897E-2</v>
+        <v>6.0318143253415502E-2</v>
       </c>
       <c r="Q36" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R36" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="E37">
-        <v>4.93</v>
+        <v>506</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G37" s="7">
-        <v>7227232256</v>
+        <v>4605217341440</v>
       </c>
       <c r="H37" s="6">
-        <v>5.04</v>
+        <v>547</v>
       </c>
       <c r="I37" s="6">
-        <v>3.45</v>
+        <v>349</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="1"/>
-        <v>0.42898550724637663</v>
+        <f>E37/I37-1</f>
+        <v>0.44985673352435529</v>
       </c>
       <c r="K37" s="11">
-        <v>9.7363083164300201E-2</v>
+        <v>8.3577075098814225E-3</v>
       </c>
       <c r="L37" s="13">
-        <v>784607000</v>
+        <v>253932000000</v>
       </c>
       <c r="M37" s="13">
-        <v>7872586000</v>
+        <v>1312163000000</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O37" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P37" s="12">
-        <v>0.52073488063015305</v>
+        <v>5.5980538209562711E-2</v>
       </c>
       <c r="Q37" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R37" s="14">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="E38">
-        <v>21.8</v>
+        <v>20.65</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G38" s="7">
-        <v>24828452864</v>
+        <v>128567304192</v>
       </c>
       <c r="H38" s="6">
-        <v>28.75</v>
+        <v>26.6</v>
       </c>
       <c r="I38" s="6">
-        <v>19.52</v>
+        <v>16.02</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="1"/>
-        <v>0.11680327868852469</v>
+        <f>E38/I38-1</f>
+        <v>0.28901373283395748</v>
       </c>
       <c r="K38" s="11">
-        <v>6.4220183486238522E-2</v>
+        <v>3.4382566585956419E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>3446618000</v>
+        <v>10795274825</v>
       </c>
       <c r="M38" s="13">
-        <v>34010798000</v>
+        <v>215275428010</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>52</v>
@@ -3244,376 +3244,376 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>0.15602168152308715</v>
+        <v>0.13552022486560977</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.10133893359397213</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R38" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E39">
-        <v>11.22</v>
+        <v>32</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G39" s="7">
-        <v>112057614336</v>
+        <v>72102395904</v>
       </c>
       <c r="H39" s="6">
-        <v>11.56</v>
+        <v>61.55</v>
       </c>
       <c r="I39" s="6">
-        <v>5.83</v>
+        <v>24.85</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="1"/>
-        <v>0.92452830188679247</v>
+        <f>E39/I39-1</f>
+        <v>0.28772635814889336</v>
       </c>
       <c r="K39" s="11">
-        <v>4.4563279857397504E-2</v>
+        <v>1.7749999999999998E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>9432900000</v>
+        <v>5261270000</v>
       </c>
       <c r="M39" s="13">
-        <v>54338700000</v>
+        <v>43208997000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O39" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P39" s="12">
-        <v>7.0262057209279694E-2</v>
+        <v>7.2175686211558024E-2</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.17359450999011755</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R39" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="E40">
-        <v>8.4700000000000006</v>
+        <v>6.21</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G40" s="7">
-        <v>26426400768</v>
+        <v>47413411840</v>
       </c>
       <c r="H40" s="6">
-        <v>10.1</v>
+        <v>11.72</v>
       </c>
       <c r="I40" s="6">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="1"/>
-        <v>0.51250000000000018</v>
+        <f>E40/I40-1</f>
+        <v>0.24199999999999999</v>
       </c>
       <c r="K40" s="11">
-        <v>3.7780401416765051E-2</v>
+        <v>6.9243156199677941E-2</v>
       </c>
       <c r="L40" s="13">
-        <v>1990539000</v>
+        <v>6749146000</v>
       </c>
       <c r="M40" s="13">
-        <v>18620709000</v>
+        <v>70848374000</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O40" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>6.8216437993046053E-2</v>
+        <v>9.0129403293835897E-2</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.10689920561026972</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R40" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E41">
-        <v>22.05</v>
+        <v>8.01</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G41" s="7">
-        <v>24438235136</v>
+        <v>18873401344</v>
       </c>
       <c r="H41" s="6">
-        <v>24.55</v>
+        <v>11.68</v>
       </c>
       <c r="I41" s="6">
-        <v>14.52</v>
+        <v>5.19</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="1"/>
-        <v>0.51859504132231415</v>
+        <f>E41/I41-1</f>
+        <v>0.5433526011560692</v>
       </c>
       <c r="K41" s="11">
-        <v>4.2630385487528344E-2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="13">
-        <v>3838344000</v>
+        <v>13493113000</v>
       </c>
       <c r="M41" s="13">
-        <v>81520873000</v>
+        <v>208027754000</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O41" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>9.0835070261810882E-2</v>
+        <v>0.122132471770363</v>
       </c>
       <c r="Q41" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
         <v>101</v>
       </c>
       <c r="E42">
-        <v>11.36</v>
+        <v>9.67</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G42" s="7">
-        <v>86056083456</v>
+        <v>295882653696</v>
       </c>
       <c r="H42" s="6">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="I42" s="6">
-        <v>8.48</v>
+        <v>5.88</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="1"/>
-        <v>0.33962264150943389</v>
+        <f>E42/I42-1</f>
+        <v>0.64455782312925169</v>
       </c>
       <c r="K42" s="11">
-        <v>6.9366197183098596E-2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="13">
-        <v>8154000000</v>
+        <v>26994000000</v>
       </c>
       <c r="M42" s="13">
-        <v>79588000000</v>
+        <v>363169000000</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O42" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>6.4020685879869976E-2</v>
+        <v>9.3653995073074411E-2</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.10245263104990703</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R42" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="E43">
-        <v>506</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="7">
-        <v>4605217341440</v>
+        <v>26426400768</v>
       </c>
       <c r="H43" s="6">
-        <v>547</v>
+        <v>10.1</v>
       </c>
       <c r="I43" s="6">
-        <v>349</v>
+        <v>5.6</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="1"/>
-        <v>0.44985673352435529</v>
+        <f>E43/I43-1</f>
+        <v>0.51250000000000018</v>
       </c>
       <c r="K43" s="11">
-        <v>8.3577075098814225E-3</v>
+        <v>3.7780401416765051E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>253932000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M43" s="13">
-        <v>1312163000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O43" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P43" s="12">
-        <v>5.5980538209562711E-2</v>
+        <v>6.8216437993046053E-2</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R43" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E44">
-        <v>27.1</v>
+        <v>31.9</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G44" s="7">
-        <v>27676958720</v>
+        <v>111642984448</v>
       </c>
       <c r="H44" s="6">
-        <v>36</v>
+        <v>37.25</v>
       </c>
       <c r="I44" s="6">
-        <v>22.4</v>
+        <v>28.1</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="1"/>
-        <v>0.2098214285714286</v>
+        <f>E44/I44-1</f>
+        <v>0.13523131672597843</v>
       </c>
       <c r="K44" s="11">
-        <v>0</v>
+        <v>5.454545454545455E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>-90314000</v>
+        <v>16863000000</v>
       </c>
       <c r="M44" s="13">
-        <v>18374441000</v>
+        <v>448320000000</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O44" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P44" s="12">
-        <v>-3.9598102780594776E-3</v>
+        <v>0.12659341147381301</v>
       </c>
       <c r="Q44" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R44" s="14">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="E45">
-        <v>17.899999999999999</v>
+        <v>50.45</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G45" s="7">
-        <v>508519284736</v>
+        <v>137104433152</v>
       </c>
       <c r="H45" s="6">
-        <v>19.260000000000002</v>
+        <v>82.25</v>
       </c>
       <c r="I45" s="6">
-        <v>13.52</v>
+        <v>37.85</v>
       </c>
       <c r="J45" s="12">
-        <f t="shared" si="1"/>
-        <v>0.32396449704142016</v>
+        <f>E45/I45-1</f>
+        <v>0.33289299867899613</v>
       </c>
       <c r="K45" s="11">
-        <v>2.1229050279329611E-2</v>
+        <v>2.0812685827552031E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>52374992116</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M45" s="13">
-        <v>269573093476</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>52</v>
@@ -3622,106 +3622,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>8.8425637480669741E-2</v>
+        <v>6.4361071109758666E-2</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.19428864891763736</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R45" s="14">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="E46">
-        <v>5.14</v>
+        <v>1.71</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G46" s="7">
-        <v>39789047808</v>
+        <v>6086522880</v>
       </c>
       <c r="H46" s="6">
-        <v>5.49</v>
+        <v>2.95</v>
       </c>
       <c r="I46" s="6">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="J46" s="12">
-        <f t="shared" si="1"/>
-        <v>0.35263157894736841</v>
+        <f>E46/I46-1</f>
+        <v>0.24817518248175174</v>
       </c>
       <c r="K46" s="11">
-        <v>7.4513618677042814E-2</v>
+        <v>5.4970760233918128E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>5474000000</v>
+        <v>2220197000</v>
       </c>
       <c r="M46" s="13">
-        <v>59407000000</v>
+        <v>71097505000</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O46" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P46" s="12">
-        <v>5.986305131194903E-2</v>
+        <v>0.12244255356679254</v>
       </c>
       <c r="Q46" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D47" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="E47">
-        <v>15.02</v>
+        <v>22.05</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G47" s="7">
-        <v>63054114816</v>
+        <v>24438235136</v>
       </c>
       <c r="H47" s="6">
-        <v>15.08</v>
+        <v>24.55</v>
       </c>
       <c r="I47" s="6">
-        <v>10.98</v>
+        <v>14.52</v>
       </c>
       <c r="J47" s="12">
-        <f t="shared" si="1"/>
-        <v>0.36794171220400718</v>
+        <f>E47/I47-1</f>
+        <v>0.51859504132231415</v>
       </c>
       <c r="K47" s="11">
-        <v>5.8988015978695074E-2</v>
+        <v>4.2630385487528344E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>11996000000</v>
+        <v>3838344000</v>
       </c>
       <c r="M47" s="13">
-        <v>138296000000</v>
+        <v>81520873000</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>69</v>
@@ -3730,175 +3730,175 @@
         <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>0.13917746450018836</v>
+        <v>9.0835070261810882E-2</v>
       </c>
       <c r="Q47" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R47" s="14">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="E48">
-        <v>8.01</v>
+        <v>11.36</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G48" s="7">
-        <v>18873401344</v>
+        <v>86056083456</v>
       </c>
       <c r="H48" s="6">
-        <v>11.68</v>
+        <v>11.5</v>
       </c>
       <c r="I48" s="6">
-        <v>5.19</v>
+        <v>8.48</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="1"/>
-        <v>0.5433526011560692</v>
+        <f>E48/I48-1</f>
+        <v>0.33962264150943389</v>
       </c>
       <c r="K48" s="11">
-        <v>0</v>
+        <v>6.9366197183098596E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>13493113000</v>
+        <v>8154000000</v>
       </c>
       <c r="M48" s="13">
-        <v>208027754000</v>
+        <v>79588000000</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O48" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P48" s="12">
-        <v>0.122132471770363</v>
+        <v>6.4020685879869976E-2</v>
       </c>
       <c r="Q48" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R48" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="E49">
-        <v>33.299999999999997</v>
+        <v>5.96</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G49" s="7">
-        <v>23032942592</v>
+        <v>754577702912</v>
       </c>
       <c r="H49" s="6">
-        <v>35.75</v>
+        <v>6.98</v>
       </c>
       <c r="I49" s="6">
-        <v>13.2</v>
+        <v>4.08</v>
       </c>
       <c r="J49" s="12">
-        <f t="shared" si="1"/>
-        <v>1.5227272727272725</v>
+        <f>E49/I49-1</f>
+        <v>0.46078431372549011</v>
       </c>
       <c r="K49" s="11">
-        <v>1.3813813813813816E-2</v>
+        <v>4.3624161073825503E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>1323087000</v>
+        <v>44563000000</v>
       </c>
       <c r="M49" s="13">
-        <v>5952918000</v>
+        <v>463922000000</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O49" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>5.1894320976402654E-2</v>
+        <v>6.5072504456515662E-2</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.222258562943417</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="E50">
-        <v>341.8</v>
+        <v>1.46</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G50" s="7">
-        <v>127261024256</v>
+        <v>7975293952</v>
       </c>
       <c r="H50" s="6">
-        <v>421.4</v>
+        <v>1.82</v>
       </c>
       <c r="I50" s="6">
-        <v>225.2</v>
+        <v>0.81</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="1"/>
-        <v>0.51776198934280648</v>
+        <f>E50/I50-1</f>
+        <v>0.80246913580246892</v>
       </c>
       <c r="K50" s="11">
-        <v>2.1064950263311876E-3</v>
+        <v>2.3287671232876714E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>1200000000</v>
+        <v>1384865000</v>
       </c>
       <c r="M50" s="13">
-        <v>5855000000</v>
+        <v>23827484000</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="O50" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>6.5825803633519697E-2</v>
+        <v>7.7509454513107826E-2</v>
       </c>
       <c r="Q50" s="12">
-        <v>0.20495303159692571</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R50" s="14">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -3927,7 +3927,7 @@
         <v>1.79</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="1"/>
+        <f>E51/I51-1</f>
         <v>0.11731843575418988</v>
       </c>
       <c r="K51" s="11">
@@ -3957,56 +3957,56 @@
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E52">
-        <v>13.54</v>
+        <v>5.14</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G52" s="7">
-        <v>76290318336</v>
+        <v>39789047808</v>
       </c>
       <c r="H52" s="6">
-        <v>14.24</v>
+        <v>5.49</v>
       </c>
       <c r="I52" s="6">
-        <v>8.81</v>
+        <v>3.8</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="1"/>
-        <v>0.53688989784335961</v>
+        <f>E52/I52-1</f>
+        <v>0.35263157894736841</v>
       </c>
       <c r="K52" s="11">
-        <v>2.4446085672082722E-2</v>
+        <v>7.4513618677042814E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>6482967000</v>
+        <v>5474000000</v>
       </c>
       <c r="M52" s="13">
-        <v>27483863000</v>
+        <v>59407000000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O52" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P52" s="12">
-        <v>8.3751586377721829E-2</v>
+        <v>5.986305131194903E-2</v>
       </c>
       <c r="Q52" s="12">
-        <v>0.23588267049650188</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R52" s="14">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
@@ -4035,7 +4035,7 @@
         <v>1.93</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="1"/>
+        <f>E53/I53-1</f>
         <v>9.8445595854922407E-2</v>
       </c>
       <c r="K53" s="11">
@@ -4065,41 +4065,41 @@
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E54">
-        <v>32</v>
+        <v>11.72</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G54" s="7">
-        <v>72102395904</v>
+        <v>206281392128</v>
       </c>
       <c r="H54" s="6">
-        <v>61.55</v>
+        <v>12.46</v>
       </c>
       <c r="I54" s="6">
-        <v>24.85</v>
+        <v>9.1</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="1"/>
-        <v>0.28772635814889336</v>
+        <f>E54/I54-1</f>
+        <v>0.287912087912088</v>
       </c>
       <c r="K54" s="11">
-        <v>1.7749999999999998E-2</v>
+        <v>3.5580204778156994E-2</v>
       </c>
       <c r="L54" s="13">
-        <v>5261270000</v>
+        <v>16758000000</v>
       </c>
       <c r="M54" s="13">
-        <v>43208997000</v>
+        <v>269590000000</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>52</v>
@@ -4108,121 +4108,121 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>7.2175686211558024E-2</v>
+        <v>5.9210027773688667E-2</v>
       </c>
       <c r="Q54" s="12">
-        <v>0.12176329850933591</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E55">
-        <v>51.25</v>
+        <v>6.85</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G55" s="7">
-        <v>131139526656</v>
+        <v>7148248576</v>
       </c>
       <c r="H55" s="6">
-        <v>71.7</v>
+        <v>6.93</v>
       </c>
       <c r="I55" s="6">
-        <v>43.55</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="1"/>
-        <v>0.17680826636050528</v>
+        <f>E55/I55-1</f>
+        <v>0.70398009950248763</v>
       </c>
       <c r="K55" s="11">
-        <v>3.2000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="13">
-        <v>1279098000</v>
+        <v>303335000</v>
       </c>
       <c r="M55" s="13">
-        <v>4811702000</v>
+        <v>3620162000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>69</v>
       </c>
       <c r="O55" s="6">
-        <v>8.7546153846153842</v>
+        <v>1</v>
       </c>
       <c r="P55" s="12">
-        <v>7.6339630042846232E-2</v>
+        <v>5.0102476266993719E-2</v>
       </c>
       <c r="Q55" s="12">
-        <v>0.26583067696212276</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R55" s="14">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E56">
-        <v>9.16</v>
+        <v>12.68</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G56" s="7">
-        <v>113627054080</v>
+        <v>13022486528</v>
       </c>
       <c r="H56" s="6">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="I56" s="6">
-        <v>6.57</v>
+        <v>10.36</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="1"/>
-        <v>0.39421613394216126</v>
+        <f>E56/I56-1</f>
+        <v>0.22393822393822393</v>
       </c>
       <c r="K56" s="11">
-        <v>5.4585152838427953E-3</v>
+        <v>8.5173501577287078E-2</v>
       </c>
       <c r="L56" s="13">
-        <v>2125459000</v>
+        <v>984000000</v>
       </c>
       <c r="M56" s="13">
-        <v>9202253000</v>
+        <v>101944000000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O56" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P56" s="12">
-        <v>0.14007819590180975</v>
+        <v>2.59134992193472E-2</v>
       </c>
       <c r="Q56" s="12">
-        <v>0.23097158924015673</v>
+        <v>9.6523581574197593E-3</v>
       </c>
       <c r="R56" s="14">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
@@ -4251,7 +4251,7 @@
         <v>15.24</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="1"/>
+        <f>E57/I57-1</f>
         <v>1.6771653543307083</v>
       </c>
       <c r="K57" s="11">
@@ -4281,62 +4281,62 @@
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="D58" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E58">
-        <v>6.94</v>
+        <v>27.1</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G58" s="7">
-        <v>3981505792</v>
+        <v>27676958720</v>
       </c>
       <c r="H58" s="6">
-        <v>9.24</v>
+        <v>36</v>
       </c>
       <c r="I58" s="6">
-        <v>6.85</v>
+        <v>22.4</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="1"/>
-        <v>1.3138686131386912E-2</v>
+        <f>E58/I58-1</f>
+        <v>0.2098214285714286</v>
       </c>
       <c r="K58" s="11">
-        <v>8.2132564841498543E-2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="13">
-        <v>498120000</v>
+        <v>-90314000</v>
       </c>
       <c r="M58" s="13">
-        <v>3284848000</v>
+        <v>18374441000</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="O58" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>9.6372678939714296E-2</v>
+        <v>-3.9598102780594776E-3</v>
       </c>
       <c r="Q58" s="12">
-        <v>0.15164171979951585</v>
+        <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R58" s="14">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:R21" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R21">
-      <sortCondition ref="R1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R58">
+      <sortCondition ref="R1:R21"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J2:J1048576">

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163C4586-0D4D-479C-8575-090390B12A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781AE16E-DBD6-4E9E-B088-713642BD9465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="201">
   <si>
     <t>Ticker</t>
   </si>
@@ -92,9 +92,6 @@
     <t>1880.HK</t>
   </si>
   <si>
-    <t>1193.HK</t>
-  </si>
-  <si>
     <t>2232.HK</t>
   </si>
   <si>
@@ -243,12 +240,6 @@
   </si>
   <si>
     <t>HKD</t>
-  </si>
-  <si>
-    <t>CHINA RES GAS</t>
-  </si>
-  <si>
-    <t>Utilities - Regulated Gas</t>
   </si>
   <si>
     <t>Utilities - Regulated Water</t>
@@ -1179,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V58"/>
+  <dimension ref="B1:V57"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1212,34 +1203,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="O1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -1257,19 +1248,19 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E2">
         <v>3.11</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="7">
         <v>8699354112</v>
@@ -1281,7 +1272,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J32" si="0">E2/I2-1</f>
         <v>0.31779661016949157</v>
       </c>
       <c r="K2" s="11">
@@ -1294,7 +1285,7 @@
         <v>6461978000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O2" s="6">
         <v>1.0683760683760684</v>
@@ -1311,19 +1302,19 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E3">
         <v>14.74</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="7">
         <v>266401906688</v>
@@ -1335,7 +1326,7 @@
         <v>9.52</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.54831932773109249</v>
       </c>
       <c r="K3" s="11">
@@ -1348,7 +1339,7 @@
         <v>269343749000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O3" s="6">
         <v>1.0683760683760684</v>
@@ -1365,19 +1356,19 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>2.88</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="7">
         <v>17859514368</v>
@@ -1389,7 +1380,7 @@
         <v>2.11</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.36492890995260674</v>
       </c>
       <c r="K4" s="11">
@@ -1402,7 +1393,7 @@
         <v>10569000000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O4" s="6">
         <v>1.0683760683760684</v>
@@ -1419,19 +1410,19 @@
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>15.1</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="7">
         <v>31377195008</v>
@@ -1443,7 +1434,7 @@
         <v>7.96</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>0.89698492462311563</v>
       </c>
       <c r="K5" s="11">
@@ -1456,7 +1447,7 @@
         <v>25994816572.18</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O5" s="6">
         <v>1.0683760683760684</v>
@@ -1473,19 +1464,19 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>2.63</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="7">
         <v>13389514752</v>
@@ -1497,7 +1488,7 @@
         <v>2.23</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.17937219730941689</v>
       </c>
       <c r="K6" s="11">
@@ -1510,7 +1501,7 @@
         <v>16480074000</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O6" s="6">
         <v>1</v>
@@ -1527,19 +1518,19 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E7">
         <v>9.16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="7">
         <v>113627054080</v>
@@ -1551,7 +1542,7 @@
         <v>6.57</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>0.39421613394216126</v>
       </c>
       <c r="K7" s="11">
@@ -1564,7 +1555,7 @@
         <v>9202253000</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O7" s="6">
         <v>7.6923076923076916</v>
@@ -1581,19 +1572,19 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>6.28</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="7">
         <v>7658523136</v>
@@ -1605,7 +1596,7 @@
         <v>3.46</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>0.81502890173410414</v>
       </c>
       <c r="K8" s="11">
@@ -1618,7 +1609,7 @@
         <v>5262544000</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O8" s="6">
         <v>1.0683760683760684</v>
@@ -1635,19 +1626,19 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>14.4</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="7">
         <v>11984947200</v>
@@ -1659,7 +1650,7 @@
         <v>12.12</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>0.18811881188118829</v>
       </c>
       <c r="K9" s="11">
@@ -1672,7 +1663,7 @@
         <v>1108087000</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O9" s="6">
         <v>7.6923076923076916</v>
@@ -1689,19 +1680,19 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E10">
         <v>2.5</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="7">
         <v>2599524864</v>
@@ -1713,7 +1704,7 @@
         <v>1.92</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>0.30208333333333348</v>
       </c>
       <c r="K10" s="11">
@@ -1726,7 +1717,7 @@
         <v>5008319000</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O10" s="6">
         <v>1</v>
@@ -1743,19 +1734,19 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11">
         <v>4.53</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="7">
         <v>52238151680</v>
@@ -1767,7 +1758,7 @@
         <v>3.46</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>0.30924855491329484</v>
       </c>
       <c r="K11" s="11">
@@ -1780,7 +1771,7 @@
         <v>16213395000</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11" s="6">
         <v>1.0683760683760684</v>
@@ -1797,19 +1788,19 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E12">
         <v>8.85</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="7">
         <v>142903607296</v>
@@ -1821,7 +1812,7 @@
         <v>7.16</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>0.2360335195530725</v>
       </c>
       <c r="K12" s="11">
@@ -1834,7 +1825,7 @@
         <v>215280386000</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O12" s="6">
         <v>1.0683760683760684</v>
@@ -1851,19 +1842,19 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E13">
         <v>8.27</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="7">
         <v>71609933824</v>
@@ -1875,7 +1866,7 @@
         <v>6.81</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>0.21439060205580041</v>
       </c>
       <c r="K13" s="11">
@@ -1888,7 +1879,7 @@
         <v>88611000000</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O13" s="6">
         <v>1.0683760683760684</v>
@@ -1905,19 +1896,19 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E14">
         <v>5.24</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="7">
         <v>61848240128</v>
@@ -1929,7 +1920,7 @@
         <v>4.12</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>0.27184466019417486</v>
       </c>
       <c r="K14" s="11">
@@ -1942,7 +1933,7 @@
         <v>21716551000</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O14" s="6">
         <v>1.0683760683760684</v>
@@ -1959,19 +1950,19 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>4.7699999999999996</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="7">
         <v>5054196736</v>
@@ -1983,7 +1974,7 @@
         <v>3.97</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.20151133501259433</v>
       </c>
       <c r="K15" s="11">
@@ -1996,7 +1987,7 @@
         <v>7530053000</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O15" s="6">
         <v>1</v>
@@ -2013,19 +2004,19 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>5.0199999999999996</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="7">
         <v>14321156096</v>
@@ -2037,7 +2028,7 @@
         <v>3.22</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>0.55900621118012395</v>
       </c>
       <c r="K16" s="11">
@@ -2050,7 +2041,7 @@
         <v>1677627000</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O16" s="6">
         <v>7.6923076923076916</v>
@@ -2067,19 +2058,19 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E17">
         <v>6.24</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="7">
         <v>56579637248</v>
@@ -2091,7 +2082,7 @@
         <v>3.39</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.84070796460176989</v>
       </c>
       <c r="K17" s="11">
@@ -2104,7 +2095,7 @@
         <v>26933044000</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O17" s="6">
         <v>1.0683760683760684</v>
@@ -2121,19 +2112,19 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E18">
         <v>4.93</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="7">
         <v>7227232256</v>
@@ -2145,7 +2136,7 @@
         <v>3.45</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
+        <f t="shared" si="0"/>
         <v>0.42898550724637663</v>
       </c>
       <c r="K18" s="11">
@@ -2158,7 +2149,7 @@
         <v>7872586000</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O18" s="6">
         <v>1</v>
@@ -2175,19 +2166,19 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E19">
         <v>95.6</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="7">
         <v>266533748736</v>
@@ -2199,7 +2190,7 @@
         <v>65.55</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
+        <f t="shared" si="0"/>
         <v>0.45842868039664375</v>
       </c>
       <c r="K19" s="11">
@@ -2212,7 +2203,7 @@
         <v>82545000000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O19" s="6">
         <v>1.0683760683760684</v>
@@ -2229,19 +2220,19 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E20">
         <v>3.83</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="7">
         <v>5497620480</v>
@@ -2253,7 +2244,7 @@
         <v>2.36</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
+        <f t="shared" si="0"/>
         <v>0.62288135593220351</v>
       </c>
       <c r="K20" s="11">
@@ -2266,7 +2257,7 @@
         <v>5532140000</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O20" s="6">
         <v>1.0683760683760684</v>
@@ -2283,19 +2274,19 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21">
         <v>13.54</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="7">
         <v>76290318336</v>
@@ -2307,7 +2298,7 @@
         <v>8.81</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
+        <f t="shared" si="0"/>
         <v>0.53688989784335961</v>
       </c>
       <c r="K21" s="11">
@@ -2320,7 +2311,7 @@
         <v>27483863000</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O21" s="6">
         <v>1.0683760683760684</v>
@@ -2337,19 +2328,19 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E22">
         <v>51.25</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="7">
         <v>131139526656</v>
@@ -2361,7 +2352,7 @@
         <v>43.55</v>
       </c>
       <c r="J22" s="12">
-        <f>E22/I22-1</f>
+        <f t="shared" si="0"/>
         <v>0.17680826636050528</v>
       </c>
       <c r="K22" s="11">
@@ -2374,7 +2365,7 @@
         <v>4811702000</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O22" s="6">
         <v>8.7546153846153842</v>
@@ -2391,19 +2382,19 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E23">
         <v>17.899999999999999</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="7">
         <v>508519284736</v>
@@ -2415,7 +2406,7 @@
         <v>13.52</v>
       </c>
       <c r="J23" s="12">
-        <f>E23/I23-1</f>
+        <f t="shared" si="0"/>
         <v>0.32396449704142016</v>
       </c>
       <c r="K23" s="11">
@@ -2428,7 +2419,7 @@
         <v>269573093476</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O23" s="6">
         <v>1.0683760683760684</v>
@@ -2445,19 +2436,19 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E24">
         <v>5.86</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="7">
         <v>4566123520</v>
@@ -2469,7 +2460,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J24" s="12">
-        <f>E24/I24-1</f>
+        <f t="shared" si="0"/>
         <v>0.45771144278606979</v>
       </c>
       <c r="K24" s="11">
@@ -2482,7 +2473,7 @@
         <v>4911072000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O24" s="6">
         <v>1</v>
@@ -2499,107 +2490,107 @@
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="E25">
-        <v>22</v>
+        <v>391</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>49944842240</v>
+        <v>494161428480</v>
       </c>
       <c r="H25" s="6">
-        <v>35.200000000000003</v>
+        <v>399.6</v>
       </c>
       <c r="I25" s="6">
-        <v>19.940000000000001</v>
+        <v>218.4</v>
       </c>
       <c r="J25" s="12">
-        <f>E25/I25-1</f>
-        <v>0.10330992978936804</v>
+        <f t="shared" si="0"/>
+        <v>0.79029304029304015</v>
       </c>
       <c r="K25" s="11">
-        <v>4.3181818181818182E-2</v>
+        <v>2.3682864450127877E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>8486605000</v>
+        <v>20744000000</v>
       </c>
       <c r="M25" s="13">
-        <v>64172826000</v>
+        <v>53852000000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O25" s="6">
         <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>0.1287045858881023</v>
+        <v>5.7448213422109484E-2</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.13224608497060733</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="E26">
-        <v>391</v>
+        <v>5.99</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>494161428480</v>
+        <v>9743992832</v>
       </c>
       <c r="H26" s="6">
-        <v>399.6</v>
+        <v>7.05</v>
       </c>
       <c r="I26" s="6">
-        <v>218.4</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J26" s="12">
-        <f>E26/I26-1</f>
-        <v>0.79029304029304015</v>
+        <f t="shared" si="0"/>
+        <v>0.40281030444964894</v>
       </c>
       <c r="K26" s="11">
-        <v>2.3682864450127877E-2</v>
+        <v>4.6744574290484141E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>20744000000</v>
+        <v>4094312000</v>
       </c>
       <c r="M26" s="13">
-        <v>53852000000</v>
+        <v>37637054000</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O26" s="6">
         <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>5.7448213422109484E-2</v>
+        <v>0.1357513317572113</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R26" s="14">
         <v>20</v>
@@ -2607,53 +2598,53 @@
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="E27">
-        <v>5.99</v>
+        <v>21.8</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>9743992832</v>
+        <v>24828452864</v>
       </c>
       <c r="H27" s="6">
-        <v>7.05</v>
+        <v>28.75</v>
       </c>
       <c r="I27" s="6">
-        <v>4.2699999999999996</v>
+        <v>19.52</v>
       </c>
       <c r="J27" s="12">
-        <f>E27/I27-1</f>
-        <v>0.40281030444964894</v>
+        <f t="shared" si="0"/>
+        <v>0.11680327868852469</v>
       </c>
       <c r="K27" s="11">
-        <v>4.6744574290484141E-2</v>
+        <v>6.4220183486238522E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>4094312000</v>
+        <v>3446618000</v>
       </c>
       <c r="M27" s="13">
-        <v>37637054000</v>
+        <v>34010798000</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="O27" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.1357513317572113</v>
+        <v>0.15602168152308715</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R27" s="14">
         <v>20</v>
@@ -2661,107 +2652,107 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="E28">
-        <v>21.8</v>
+        <v>216.6</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>24828452864</v>
+        <v>287679479808</v>
       </c>
       <c r="H28" s="6">
-        <v>28.75</v>
+        <v>235</v>
       </c>
       <c r="I28" s="6">
-        <v>19.52</v>
+        <v>34.4</v>
       </c>
       <c r="J28" s="12">
-        <f>E28/I28-1</f>
-        <v>0.11680327868852469</v>
+        <f t="shared" si="0"/>
+        <v>5.2965116279069768</v>
       </c>
       <c r="K28" s="11">
-        <v>6.4220183486238522E-2</v>
+        <v>3.7626962142197598E-3</v>
       </c>
       <c r="L28" s="13">
-        <v>3446618000</v>
+        <v>4414795000</v>
       </c>
       <c r="M28" s="13">
-        <v>34010798000</v>
+        <v>10683505000</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O28" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>0.15602168152308715</v>
+        <v>1.6714886709713026E-2</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.41323470153287706</v>
       </c>
       <c r="R28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="E29">
-        <v>216.6</v>
+        <v>6.94</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>287679479808</v>
+        <v>3981505792</v>
       </c>
       <c r="H29" s="6">
-        <v>235</v>
+        <v>9.24</v>
       </c>
       <c r="I29" s="6">
-        <v>34.4</v>
+        <v>6.85</v>
       </c>
       <c r="J29" s="12">
-        <f>E29/I29-1</f>
-        <v>5.2965116279069768</v>
+        <f t="shared" si="0"/>
+        <v>1.3138686131386912E-2</v>
       </c>
       <c r="K29" s="11">
-        <v>3.7626962142197598E-3</v>
+        <v>8.2132564841498543E-2</v>
       </c>
       <c r="L29" s="13">
-        <v>4414795000</v>
+        <v>498120000</v>
       </c>
       <c r="M29" s="13">
-        <v>10683505000</v>
+        <v>3284848000</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O29" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>1.6714886709713026E-2</v>
+        <v>9.6372678939714296E-2</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.41323470153287706</v>
+        <v>0.15164171979951585</v>
       </c>
       <c r="R29" s="14">
         <v>21</v>
@@ -2769,215 +2760,215 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E30">
-        <v>6.94</v>
+        <v>341.8</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>3981505792</v>
+        <v>127261024256</v>
       </c>
       <c r="H30" s="6">
-        <v>9.24</v>
+        <v>421.4</v>
       </c>
       <c r="I30" s="6">
-        <v>6.85</v>
+        <v>225.2</v>
       </c>
       <c r="J30" s="12">
-        <f>E30/I30-1</f>
-        <v>1.3138686131386912E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.51776198934280648</v>
       </c>
       <c r="K30" s="11">
-        <v>8.2132564841498543E-2</v>
+        <v>2.1064950263311876E-3</v>
       </c>
       <c r="L30" s="13">
-        <v>498120000</v>
+        <v>1200000000</v>
       </c>
       <c r="M30" s="13">
-        <v>3284848000</v>
+        <v>5855000000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O30" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P30" s="12">
-        <v>9.6372678939714296E-2</v>
+        <v>6.5825803633519697E-2</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.15164171979951585</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R30" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="E31">
-        <v>341.8</v>
+        <v>12.34</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>127261024256</v>
+        <v>57997750272</v>
       </c>
       <c r="H31" s="6">
-        <v>421.4</v>
+        <v>13.56</v>
       </c>
       <c r="I31" s="6">
-        <v>225.2</v>
+        <v>7.51</v>
       </c>
       <c r="J31" s="12">
-        <f>E31/I31-1</f>
-        <v>0.51776198934280648</v>
+        <f t="shared" si="0"/>
+        <v>0.64314247669773628</v>
       </c>
       <c r="K31" s="11">
-        <v>2.1064950263311876E-3</v>
+        <v>3.5494327390599677E-2</v>
       </c>
       <c r="L31" s="13">
-        <v>1200000000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M31" s="13">
-        <v>5855000000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="O31" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P31" s="12">
-        <v>6.5825803633519697E-2</v>
+        <v>0.13041654887075355</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.20495303159692571</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R31" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="E32">
-        <v>12.34</v>
+        <v>11.22</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>57997750272</v>
+        <v>112057614336</v>
       </c>
       <c r="H32" s="6">
-        <v>13.56</v>
+        <v>11.56</v>
       </c>
       <c r="I32" s="6">
-        <v>7.51</v>
+        <v>5.83</v>
       </c>
       <c r="J32" s="12">
-        <f>E32/I32-1</f>
-        <v>0.64314247669773628</v>
+        <f t="shared" si="0"/>
+        <v>0.92452830188679247</v>
       </c>
       <c r="K32" s="11">
-        <v>3.5494327390599677E-2</v>
+        <v>4.4563279857397504E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>3967214824.1399999</v>
+        <v>9432900000</v>
       </c>
       <c r="M32" s="13">
-        <v>41038539262.660004</v>
+        <v>54338700000</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O32" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.13041654887075355</v>
+        <v>7.0262057209279694E-2</v>
       </c>
       <c r="Q32" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>0.17359450999011755</v>
       </c>
       <c r="R32" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="E33">
-        <v>11.22</v>
+        <v>15.02</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>112057614336</v>
+        <v>63054114816</v>
       </c>
       <c r="H33" s="6">
-        <v>11.56</v>
+        <v>15.08</v>
       </c>
       <c r="I33" s="6">
-        <v>5.83</v>
+        <v>10.98</v>
       </c>
       <c r="J33" s="12">
-        <f>E33/I33-1</f>
-        <v>0.92452830188679247</v>
+        <f t="shared" ref="J33:J64" si="1">E33/I33-1</f>
+        <v>0.36794171220400718</v>
       </c>
       <c r="K33" s="11">
-        <v>4.4563279857397504E-2</v>
+        <v>5.8988015978695074E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>9432900000</v>
+        <v>11996000000</v>
       </c>
       <c r="M33" s="13">
-        <v>54338700000</v>
+        <v>138296000000</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O33" s="6">
         <v>1</v>
       </c>
       <c r="P33" s="12">
-        <v>7.0262057209279694E-2</v>
+        <v>0.13917746450018836</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.17359450999011755</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R33" s="14">
         <v>24</v>
@@ -2985,269 +2976,269 @@
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
         <v>183</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="E34">
-        <v>15.02</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>63054114816</v>
+        <v>23032942592</v>
       </c>
       <c r="H34" s="6">
-        <v>15.08</v>
+        <v>35.75</v>
       </c>
       <c r="I34" s="6">
-        <v>10.98</v>
+        <v>13.2</v>
       </c>
       <c r="J34" s="12">
-        <f>E34/I34-1</f>
-        <v>0.36794171220400718</v>
+        <f t="shared" si="1"/>
+        <v>1.5227272727272725</v>
       </c>
       <c r="K34" s="11">
-        <v>5.8988015978695074E-2</v>
+        <v>1.3813813813813816E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>11996000000</v>
+        <v>1323087000</v>
       </c>
       <c r="M34" s="13">
-        <v>138296000000</v>
+        <v>5952918000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O34" s="6">
         <v>1</v>
       </c>
       <c r="P34" s="12">
-        <v>0.13917746450018836</v>
+        <v>5.1894320976402654E-2</v>
       </c>
       <c r="Q34" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R34" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="E35">
-        <v>33.299999999999997</v>
+        <v>58.05</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>23032942592</v>
+        <v>162675261440</v>
       </c>
       <c r="H35" s="6">
-        <v>35.75</v>
+        <v>60</v>
       </c>
       <c r="I35" s="6">
-        <v>13.2</v>
+        <v>38.4</v>
       </c>
       <c r="J35" s="12">
-        <f>E35/I35-1</f>
-        <v>1.5227272727272725</v>
+        <f t="shared" si="1"/>
+        <v>0.51171875</v>
       </c>
       <c r="K35" s="11">
-        <v>1.3813813813813816E-2</v>
+        <v>3.1007751937984499E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>1323087000</v>
+        <v>8955723006</v>
       </c>
       <c r="M35" s="13">
-        <v>5952918000</v>
+        <v>47495870210</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="O35" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>5.1894320976402654E-2</v>
+        <v>6.0318143253415502E-2</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.222258562943417</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R35" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E36">
-        <v>58.05</v>
+        <v>506</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>162675261440</v>
+        <v>4605217341440</v>
       </c>
       <c r="H36" s="6">
-        <v>60</v>
+        <v>547</v>
       </c>
       <c r="I36" s="6">
-        <v>38.4</v>
+        <v>349</v>
       </c>
       <c r="J36" s="12">
-        <f>E36/I36-1</f>
-        <v>0.51171875</v>
+        <f t="shared" si="1"/>
+        <v>0.44985673352435529</v>
       </c>
       <c r="K36" s="11">
-        <v>3.1007751937984499E-2</v>
+        <v>8.3577075098814225E-3</v>
       </c>
       <c r="L36" s="13">
-        <v>8955723006</v>
+        <v>253932000000</v>
       </c>
       <c r="M36" s="13">
-        <v>47495870210</v>
+        <v>1312163000000</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O36" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>6.0318143253415502E-2</v>
+        <v>5.5980538209562711E-2</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R36" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="E37">
-        <v>506</v>
+        <v>20.65</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>4605217341440</v>
+        <v>128567304192</v>
       </c>
       <c r="H37" s="6">
-        <v>547</v>
+        <v>26.6</v>
       </c>
       <c r="I37" s="6">
-        <v>349</v>
+        <v>16.02</v>
       </c>
       <c r="J37" s="12">
-        <f>E37/I37-1</f>
-        <v>0.44985673352435529</v>
+        <f t="shared" si="1"/>
+        <v>0.28901373283395748</v>
       </c>
       <c r="K37" s="11">
-        <v>8.3577075098814225E-3</v>
+        <v>3.4382566585956419E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>253932000000</v>
+        <v>10795274825</v>
       </c>
       <c r="M37" s="13">
-        <v>1312163000000</v>
+        <v>215275428010</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O37" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P37" s="12">
-        <v>5.5980538209562711E-2</v>
+        <v>0.13552022486560977</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.19352168899747973</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R37" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E38">
-        <v>20.65</v>
+        <v>32</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>128567304192</v>
+        <v>72102395904</v>
       </c>
       <c r="H38" s="6">
-        <v>26.6</v>
+        <v>61.55</v>
       </c>
       <c r="I38" s="6">
-        <v>16.02</v>
+        <v>24.85</v>
       </c>
       <c r="J38" s="12">
-        <f>E38/I38-1</f>
-        <v>0.28901373283395748</v>
+        <f t="shared" si="1"/>
+        <v>0.28772635814889336</v>
       </c>
       <c r="K38" s="11">
-        <v>3.4382566585956419E-2</v>
+        <v>1.7749999999999998E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>10795274825</v>
+        <v>5261270000</v>
       </c>
       <c r="M38" s="13">
-        <v>215275428010</v>
+        <v>43208997000</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O38" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>0.13552022486560977</v>
+        <v>7.2175686211558024E-2</v>
       </c>
       <c r="Q38" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R38" s="14">
         <v>28</v>
@@ -3255,107 +3246,107 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="E39">
-        <v>32</v>
+        <v>6.21</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>72102395904</v>
+        <v>47413411840</v>
       </c>
       <c r="H39" s="6">
-        <v>61.55</v>
+        <v>11.72</v>
       </c>
       <c r="I39" s="6">
-        <v>24.85</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12">
-        <f>E39/I39-1</f>
-        <v>0.28772635814889336</v>
+        <f t="shared" si="1"/>
+        <v>0.24199999999999999</v>
       </c>
       <c r="K39" s="11">
-        <v>1.7749999999999998E-2</v>
+        <v>6.9243156199677941E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>5261270000</v>
+        <v>6749146000</v>
       </c>
       <c r="M39" s="13">
-        <v>43208997000</v>
+        <v>70848374000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O39" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P39" s="12">
-        <v>7.2175686211558024E-2</v>
+        <v>9.0129403293835897E-2</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.12176329850933591</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R39" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E40">
-        <v>6.21</v>
+        <v>8.01</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>47413411840</v>
+        <v>18873401344</v>
       </c>
       <c r="H40" s="6">
-        <v>11.72</v>
+        <v>11.68</v>
       </c>
       <c r="I40" s="6">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="J40" s="12">
-        <f>E40/I40-1</f>
-        <v>0.24199999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.5433526011560692</v>
       </c>
       <c r="K40" s="11">
-        <v>6.9243156199677941E-2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="13">
-        <v>6749146000</v>
+        <v>13493113000</v>
       </c>
       <c r="M40" s="13">
-        <v>70848374000</v>
+        <v>208027754000</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O40" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>9.0129403293835897E-2</v>
+        <v>0.122132471770363</v>
       </c>
       <c r="Q40" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R40" s="14">
         <v>29</v>
@@ -3363,107 +3354,107 @@
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="E41">
-        <v>8.01</v>
+        <v>9.67</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>18873401344</v>
+        <v>295882653696</v>
       </c>
       <c r="H41" s="6">
-        <v>11.68</v>
+        <v>11.56</v>
       </c>
       <c r="I41" s="6">
-        <v>5.19</v>
+        <v>5.88</v>
       </c>
       <c r="J41" s="12">
-        <f>E41/I41-1</f>
-        <v>0.5433526011560692</v>
+        <f t="shared" si="1"/>
+        <v>0.64455782312925169</v>
       </c>
       <c r="K41" s="11">
         <v>0</v>
       </c>
       <c r="L41" s="13">
-        <v>13493113000</v>
+        <v>26994000000</v>
       </c>
       <c r="M41" s="13">
-        <v>208027754000</v>
+        <v>363169000000</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O41" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>0.122132471770363</v>
+        <v>9.3653995073074411E-2</v>
       </c>
       <c r="Q41" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E42">
-        <v>9.67</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>295882653696</v>
+        <v>26426400768</v>
       </c>
       <c r="H42" s="6">
-        <v>11.56</v>
+        <v>10.1</v>
       </c>
       <c r="I42" s="6">
-        <v>5.88</v>
+        <v>5.6</v>
       </c>
       <c r="J42" s="12">
-        <f>E42/I42-1</f>
-        <v>0.64455782312925169</v>
+        <f t="shared" si="1"/>
+        <v>0.51250000000000018</v>
       </c>
       <c r="K42" s="11">
-        <v>0</v>
+        <v>3.7780401416765051E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>26994000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M42" s="13">
-        <v>363169000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O42" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P42" s="12">
-        <v>9.3653995073074411E-2</v>
+        <v>6.8216437993046053E-2</v>
       </c>
       <c r="Q42" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R42" s="14">
         <v>30</v>
@@ -3471,269 +3462,269 @@
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="E43">
-        <v>8.4700000000000006</v>
+        <v>31.9</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>26426400768</v>
+        <v>111642984448</v>
       </c>
       <c r="H43" s="6">
-        <v>10.1</v>
+        <v>37.25</v>
       </c>
       <c r="I43" s="6">
-        <v>5.6</v>
+        <v>28.1</v>
       </c>
       <c r="J43" s="12">
-        <f>E43/I43-1</f>
-        <v>0.51250000000000018</v>
+        <f t="shared" si="1"/>
+        <v>0.13523131672597843</v>
       </c>
       <c r="K43" s="11">
-        <v>3.7780401416765051E-2</v>
+        <v>5.454545454545455E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>1990539000</v>
+        <v>16863000000</v>
       </c>
       <c r="M43" s="13">
-        <v>18620709000</v>
+        <v>448320000000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O43" s="6">
         <v>1</v>
       </c>
       <c r="P43" s="12">
-        <v>6.8216437993046053E-2</v>
+        <v>0.12659341147381301</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.10689920561026972</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R43" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="E44">
-        <v>31.9</v>
+        <v>50.45</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>111642984448</v>
+        <v>137104433152</v>
       </c>
       <c r="H44" s="6">
-        <v>37.25</v>
+        <v>82.25</v>
       </c>
       <c r="I44" s="6">
-        <v>28.1</v>
+        <v>37.85</v>
       </c>
       <c r="J44" s="12">
-        <f>E44/I44-1</f>
-        <v>0.13523131672597843</v>
+        <f t="shared" si="1"/>
+        <v>0.33289299867899613</v>
       </c>
       <c r="K44" s="11">
-        <v>5.454545454545455E-2</v>
+        <v>2.0812685827552031E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>16863000000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M44" s="13">
-        <v>448320000000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="O44" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>0.12659341147381301</v>
+        <v>6.4361071109758666E-2</v>
       </c>
       <c r="Q44" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R44" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="E45">
-        <v>50.45</v>
+        <v>1.71</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>137104433152</v>
+        <v>6086522880</v>
       </c>
       <c r="H45" s="6">
-        <v>82.25</v>
+        <v>2.95</v>
       </c>
       <c r="I45" s="6">
-        <v>37.85</v>
+        <v>1.37</v>
       </c>
       <c r="J45" s="12">
-        <f>E45/I45-1</f>
-        <v>0.33289299867899613</v>
+        <f t="shared" si="1"/>
+        <v>0.24817518248175174</v>
       </c>
       <c r="K45" s="11">
-        <v>2.0812685827552031E-2</v>
+        <v>5.4970760233918128E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>6350637223.7200003</v>
+        <v>2220197000</v>
       </c>
       <c r="M45" s="13">
-        <v>57896384836.860001</v>
+        <v>71097505000</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O45" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>6.4361071109758666E-2</v>
+        <v>0.12244255356679254</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.10968970241604512</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R45" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D46" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="E46">
-        <v>1.71</v>
+        <v>22.05</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>6086522880</v>
+        <v>24438235136</v>
       </c>
       <c r="H46" s="6">
-        <v>2.95</v>
+        <v>24.55</v>
       </c>
       <c r="I46" s="6">
-        <v>1.37</v>
+        <v>14.52</v>
       </c>
       <c r="J46" s="12">
-        <f>E46/I46-1</f>
-        <v>0.24817518248175174</v>
+        <f t="shared" si="1"/>
+        <v>0.51859504132231415</v>
       </c>
       <c r="K46" s="11">
-        <v>5.4970760233918128E-2</v>
+        <v>4.2630385487528344E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>2220197000</v>
+        <v>3838344000</v>
       </c>
       <c r="M46" s="13">
-        <v>71097505000</v>
+        <v>81520873000</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O46" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>0.12244255356679254</v>
+        <v>9.0835070261810882E-2</v>
       </c>
       <c r="Q46" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="E47">
-        <v>22.05</v>
+        <v>11.36</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>24438235136</v>
+        <v>86056083456</v>
       </c>
       <c r="H47" s="6">
-        <v>24.55</v>
+        <v>11.5</v>
       </c>
       <c r="I47" s="6">
-        <v>14.52</v>
+        <v>8.48</v>
       </c>
       <c r="J47" s="12">
-        <f>E47/I47-1</f>
-        <v>0.51859504132231415</v>
+        <f t="shared" si="1"/>
+        <v>0.33962264150943389</v>
       </c>
       <c r="K47" s="11">
-        <v>4.2630385487528344E-2</v>
+        <v>6.9366197183098596E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>3838344000</v>
+        <v>8154000000</v>
       </c>
       <c r="M47" s="13">
-        <v>81520873000</v>
+        <v>79588000000</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O47" s="6">
         <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>9.0835070261810882E-2</v>
+        <v>6.4020685879869976E-2</v>
       </c>
       <c r="Q47" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R47" s="14">
         <v>34</v>
@@ -3741,595 +3732,541 @@
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E48">
-        <v>11.36</v>
+        <v>5.96</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>86056083456</v>
+        <v>754577702912</v>
       </c>
       <c r="H48" s="6">
-        <v>11.5</v>
+        <v>6.98</v>
       </c>
       <c r="I48" s="6">
-        <v>8.48</v>
+        <v>4.08</v>
       </c>
       <c r="J48" s="12">
-        <f>E48/I48-1</f>
-        <v>0.33962264150943389</v>
+        <f t="shared" si="1"/>
+        <v>0.46078431372549011</v>
       </c>
       <c r="K48" s="11">
-        <v>6.9366197183098596E-2</v>
+        <v>4.3624161073825503E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>8154000000</v>
+        <v>44563000000</v>
       </c>
       <c r="M48" s="13">
-        <v>79588000000</v>
+        <v>463922000000</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="O48" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>6.4020685879869976E-2</v>
+        <v>6.5072504456515662E-2</v>
       </c>
       <c r="Q48" s="12">
-        <v>0.10245263104990703</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R48" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E49">
-        <v>5.96</v>
+        <v>1.46</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>754577702912</v>
+        <v>7975293952</v>
       </c>
       <c r="H49" s="6">
-        <v>6.98</v>
+        <v>1.82</v>
       </c>
       <c r="I49" s="6">
-        <v>4.08</v>
+        <v>0.81</v>
       </c>
       <c r="J49" s="12">
-        <f>E49/I49-1</f>
-        <v>0.46078431372549011</v>
+        <f t="shared" si="1"/>
+        <v>0.80246913580246892</v>
       </c>
       <c r="K49" s="11">
-        <v>4.3624161073825503E-2</v>
+        <v>2.3287671232876714E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>44563000000</v>
+        <v>1384865000</v>
       </c>
       <c r="M49" s="13">
-        <v>463922000000</v>
+        <v>23827484000</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O49" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>6.5072504456515662E-2</v>
+        <v>7.7509454513107826E-2</v>
       </c>
       <c r="Q49" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E50">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>7975293952</v>
+        <v>3556699904</v>
       </c>
       <c r="H50" s="6">
-        <v>1.82</v>
+        <v>2.73</v>
       </c>
       <c r="I50" s="6">
-        <v>0.81</v>
+        <v>1.79</v>
       </c>
       <c r="J50" s="12">
-        <f>E50/I50-1</f>
-        <v>0.80246913580246892</v>
+        <f t="shared" si="1"/>
+        <v>0.11731843575418988</v>
       </c>
       <c r="K50" s="11">
-        <v>2.3287671232876714E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>1384865000</v>
+        <v>364157000</v>
       </c>
       <c r="M50" s="13">
-        <v>23827484000</v>
+        <v>7859317000</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O50" s="6">
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>7.7509454513107826E-2</v>
+        <v>8.3392871887460709E-2</v>
       </c>
       <c r="Q50" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>4.6334433386514377E-2</v>
       </c>
       <c r="R50" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>5.14</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>3556699904</v>
+        <v>39789047808</v>
       </c>
       <c r="H51" s="6">
-        <v>2.73</v>
+        <v>5.49</v>
       </c>
       <c r="I51" s="6">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="J51" s="12">
-        <f>E51/I51-1</f>
-        <v>0.11731843575418988</v>
+        <f t="shared" si="1"/>
+        <v>0.35263157894736841</v>
       </c>
       <c r="K51" s="11">
-        <v>2.8000000000000001E-2</v>
+        <v>7.4513618677042814E-2</v>
       </c>
       <c r="L51" s="13">
-        <v>364157000</v>
+        <v>5474000000</v>
       </c>
       <c r="M51" s="13">
-        <v>7859317000</v>
+        <v>59407000000</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O51" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P51" s="12">
-        <v>8.3392871887460709E-2</v>
+        <v>5.986305131194903E-2</v>
       </c>
       <c r="Q51" s="12">
-        <v>4.6334433386514377E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="E52">
-        <v>5.14</v>
+        <v>2.12</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>39789047808</v>
+        <v>9105399808</v>
       </c>
       <c r="H52" s="6">
-        <v>5.49</v>
+        <v>3.04</v>
       </c>
       <c r="I52" s="6">
-        <v>3.8</v>
+        <v>1.93</v>
       </c>
       <c r="J52" s="12">
-        <f>E52/I52-1</f>
-        <v>0.35263157894736841</v>
+        <f t="shared" si="1"/>
+        <v>9.8445595854922407E-2</v>
       </c>
       <c r="K52" s="11">
-        <v>7.4513618677042814E-2</v>
+        <v>5.0471698113207543E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>5474000000</v>
+        <v>1938532000</v>
       </c>
       <c r="M52" s="13">
-        <v>59407000000</v>
+        <v>49986396000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O52" s="6">
         <v>1</v>
       </c>
       <c r="P52" s="12">
-        <v>5.986305131194903E-2</v>
+        <v>6.5415965529776049E-2</v>
       </c>
       <c r="Q52" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R52" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
+        <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="E53">
-        <v>2.12</v>
+        <v>11.72</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>9105399808</v>
+        <v>206281392128</v>
       </c>
       <c r="H53" s="6">
-        <v>3.04</v>
+        <v>12.46</v>
       </c>
       <c r="I53" s="6">
-        <v>1.93</v>
+        <v>9.1</v>
       </c>
       <c r="J53" s="12">
-        <f>E53/I53-1</f>
-        <v>9.8445595854922407E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.287912087912088</v>
       </c>
       <c r="K53" s="11">
-        <v>5.0471698113207543E-2</v>
+        <v>3.5580204778156994E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>1938532000</v>
+        <v>16758000000</v>
       </c>
       <c r="M53" s="13">
-        <v>49986396000</v>
+        <v>269590000000</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="O53" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>6.5415965529776049E-2</v>
+        <v>5.9210027773688667E-2</v>
       </c>
       <c r="Q53" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R53" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E54">
-        <v>11.72</v>
+        <v>6.85</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>206281392128</v>
+        <v>7148248576</v>
       </c>
       <c r="H54" s="6">
-        <v>12.46</v>
+        <v>6.93</v>
       </c>
       <c r="I54" s="6">
-        <v>9.1</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J54" s="12">
-        <f>E54/I54-1</f>
-        <v>0.287912087912088</v>
+        <f t="shared" si="1"/>
+        <v>0.70398009950248763</v>
       </c>
       <c r="K54" s="11">
-        <v>3.5580204778156994E-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="13">
-        <v>16758000000</v>
+        <v>303335000</v>
       </c>
       <c r="M54" s="13">
-        <v>269590000000</v>
+        <v>3620162000</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O54" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P54" s="12">
-        <v>5.9210027773688667E-2</v>
+        <v>5.0102476266993719E-2</v>
       </c>
       <c r="Q54" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="E55">
-        <v>6.85</v>
+        <v>12.68</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>7148248576</v>
+        <v>13022486528</v>
       </c>
       <c r="H55" s="6">
-        <v>6.93</v>
+        <v>14.5</v>
       </c>
       <c r="I55" s="6">
-        <v>4.0199999999999996</v>
+        <v>10.36</v>
       </c>
       <c r="J55" s="12">
-        <f>E55/I55-1</f>
-        <v>0.70398009950248763</v>
+        <f t="shared" si="1"/>
+        <v>0.22393822393822393</v>
       </c>
       <c r="K55" s="11">
-        <v>0</v>
+        <v>8.5173501577287078E-2</v>
       </c>
       <c r="L55" s="13">
-        <v>303335000</v>
+        <v>984000000</v>
       </c>
       <c r="M55" s="13">
-        <v>3620162000</v>
+        <v>101944000000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O55" s="6">
         <v>1</v>
       </c>
       <c r="P55" s="12">
-        <v>5.0102476266993719E-2</v>
+        <v>2.59134992193472E-2</v>
       </c>
       <c r="Q55" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>9.6523581574197593E-3</v>
       </c>
       <c r="R55" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="E56">
-        <v>12.68</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>13022486528</v>
+        <v>419697328128</v>
       </c>
       <c r="H56" s="6">
-        <v>14.5</v>
+        <v>59.7</v>
       </c>
       <c r="I56" s="6">
-        <v>10.36</v>
+        <v>15.24</v>
       </c>
       <c r="J56" s="12">
-        <f>E56/I56-1</f>
-        <v>0.22393822393822393</v>
+        <f t="shared" si="1"/>
+        <v>1.6771653543307083</v>
       </c>
       <c r="K56" s="11">
-        <v>8.5173501577287078E-2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="13">
-        <v>984000000</v>
+        <v>984027000</v>
       </c>
       <c r="M56" s="13">
-        <v>101944000000</v>
+        <v>32183526000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O56" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P56" s="12">
-        <v>2.59134992193472E-2</v>
+        <v>1.6457375883070016E-2</v>
       </c>
       <c r="Q56" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>3.0575487595734537E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="E57">
-        <v>40.799999999999997</v>
+        <v>27.1</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>419697328128</v>
+        <v>27676958720</v>
       </c>
       <c r="H57" s="6">
-        <v>59.7</v>
+        <v>36</v>
       </c>
       <c r="I57" s="6">
-        <v>15.24</v>
+        <v>22.4</v>
       </c>
       <c r="J57" s="12">
-        <f>E57/I57-1</f>
-        <v>1.6771653543307083</v>
+        <f t="shared" si="1"/>
+        <v>0.2098214285714286</v>
       </c>
       <c r="K57" s="11">
         <v>0</v>
       </c>
       <c r="L57" s="13">
-        <v>984027000</v>
+        <v>-90314000</v>
       </c>
       <c r="M57" s="13">
-        <v>32183526000</v>
+        <v>18374441000</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="O57" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>1.6457375883070016E-2</v>
+        <v>-3.9598102780594776E-3</v>
       </c>
       <c r="Q57" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R57" s="14">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="B58" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" t="s">
-        <v>179</v>
-      </c>
-      <c r="D58" t="s">
-        <v>178</v>
-      </c>
-      <c r="E58">
-        <v>27.1</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G58" s="7">
-        <v>27676958720</v>
-      </c>
-      <c r="H58" s="6">
-        <v>36</v>
-      </c>
-      <c r="I58" s="6">
-        <v>22.4</v>
-      </c>
-      <c r="J58" s="12">
-        <f>E58/I58-1</f>
-        <v>0.2098214285714286</v>
-      </c>
-      <c r="K58" s="11">
-        <v>0</v>
-      </c>
-      <c r="L58" s="13">
-        <v>-90314000</v>
-      </c>
-      <c r="M58" s="13">
-        <v>18374441000</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="O58" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-      <c r="P58" s="12">
-        <v>-3.9598102780594776E-3</v>
-      </c>
-      <c r="Q58" s="12">
-        <v>-4.9151971480384084E-3</v>
-      </c>
-      <c r="R58" s="14">
         <v>44</v>
       </c>
     </row>
@@ -4388,34 +4325,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="O1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -4436,16 +4373,16 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2">
         <v>128.15</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" s="7">
         <v>497428299776</v>
@@ -4470,7 +4407,7 @@
         <v>133285282015.97</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O2" s="6">
         <v>1</v>
@@ -4490,16 +4427,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>8.5</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" s="7">
         <v>14667599872</v>
@@ -4524,7 +4461,7 @@
         <v>11970268017.99</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O3" s="6">
         <v>1</v>
@@ -4544,16 +4481,16 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4">
         <v>12.28</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" s="7">
         <v>12564895744</v>
@@ -4578,7 +4515,7 @@
         <v>11491269147.950001</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O4" s="6">
         <v>1</v>
@@ -4598,16 +4535,16 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>62</v>
       </c>
       <c r="E5">
         <v>13.89</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" s="7">
         <v>24946440192</v>
@@ -4632,7 +4569,7 @@
         <v>15580673812.24</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O5" s="6">
         <v>1</v>
@@ -4652,16 +4589,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
         <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
       </c>
       <c r="E6">
         <v>104.24</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="7">
         <v>55394283520</v>
@@ -4686,7 +4623,7 @@
         <v>10336332783.18</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O6" s="6">
         <v>1</v>
@@ -4706,16 +4643,16 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
         <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
       </c>
       <c r="E7">
         <v>243.01</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="7">
         <v>44889538560</v>
@@ -4740,7 +4677,7 @@
         <v>12869225664</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6">
         <v>1</v>
@@ -4760,16 +4697,16 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8">
         <v>9.3800000000000008</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="7">
         <v>11384037376</v>
@@ -4794,7 +4731,7 @@
         <v>9527311896.5100002</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O8" s="6">
         <v>1</v>
@@ -4814,16 +4751,16 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
         <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>67</v>
       </c>
       <c r="E9">
         <v>12.53</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="7">
         <v>4429643264</v>
@@ -4848,7 +4785,7 @@
         <v>2751572515.0799999</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O9" s="6">
         <v>1</v>
@@ -4868,16 +4805,16 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10">
         <v>8.0299999999999994</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="7">
         <v>17844426752</v>
@@ -4902,7 +4839,7 @@
         <v>13696300546.360001</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O10" s="6">
         <v>1</v>
@@ -4922,16 +4859,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
         <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
       </c>
       <c r="E11">
         <v>57.36</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" s="7">
         <v>32998920192</v>
@@ -4956,7 +4893,7 @@
         <v>9067794807.8099995</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11" s="6">
         <v>1</v>
@@ -5016,34 +4953,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="O1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>6</v>
@@ -5061,19 +4998,19 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E2">
         <v>63.07</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G2" s="7">
         <v>2609899776</v>
@@ -5098,7 +5035,7 @@
         <v>1851800000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O2" s="6">
         <v>1</v>
@@ -5115,19 +5052,19 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3">
         <v>206.61</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G3" s="7">
         <v>87313793024</v>
@@ -5152,7 +5089,7 @@
         <v>4294000000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O3" s="6">
         <v>1</v>
@@ -5169,19 +5106,19 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4">
         <v>164</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G4" s="7">
         <v>4521332224</v>
@@ -5206,7 +5143,7 @@
         <v>925772000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O4" s="6">
         <v>1</v>
@@ -5242,17 +5179,17 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
       <c r="B3" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781AE16E-DBD6-4E9E-B088-713642BD9465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A92E1D4-9B99-4746-85F8-C41A51093BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="212">
   <si>
     <t>Ticker</t>
   </si>
@@ -702,6 +713,39 @@
   </si>
   <si>
     <t>CAFE DE CORAL H</t>
+  </si>
+  <si>
+    <t>1258.HK</t>
+  </si>
+  <si>
+    <t>0316.HK</t>
+  </si>
+  <si>
+    <t>2360.HK</t>
+  </si>
+  <si>
+    <t>2338.HK</t>
+  </si>
+  <si>
+    <t>0716.HK</t>
+  </si>
+  <si>
+    <t>2388.HK</t>
+  </si>
+  <si>
+    <t>3328.HK</t>
+  </si>
+  <si>
+    <t>1398.HK</t>
+  </si>
+  <si>
+    <t>1658.HK</t>
+  </si>
+  <si>
+    <t>0939.HK</t>
+  </si>
+  <si>
+    <t>0998.HK</t>
   </si>
 </sst>
 </file>
@@ -818,7 +862,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1170,26 +1214,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V57"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="B1:V68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="18.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1290,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -1300,7 +1344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1354,7 +1398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1408,7 +1452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1462,7 +1506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
@@ -1516,7 +1560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1570,7 +1614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1624,7 +1668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1678,7 +1722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1732,7 +1776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1786,7 +1830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1840,7 +1884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1894,7 +1938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
@@ -1948,7 +1992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2002,7 +2046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2056,7 +2100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
@@ -2110,7 +2154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>124</v>
       </c>
@@ -2164,7 +2208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>118</v>
       </c>
@@ -2218,7 +2262,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>113</v>
       </c>
@@ -2272,7 +2316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>140</v>
       </c>
@@ -2326,7 +2370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>143</v>
       </c>
@@ -2380,7 +2424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -2434,7 +2478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2488,7 +2532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
@@ -2542,7 +2586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>120</v>
       </c>
@@ -2596,7 +2640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>125</v>
       </c>
@@ -2650,7 +2694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>119</v>
       </c>
@@ -2704,7 +2748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
         <v>197</v>
       </c>
@@ -2758,7 +2802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>138</v>
       </c>
@@ -2812,7 +2856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
@@ -2866,7 +2910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>126</v>
       </c>
@@ -2920,7 +2964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>135</v>
       </c>
@@ -2946,7 +2990,7 @@
         <v>10.98</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" ref="J33:J64" si="1">E33/I33-1</f>
+        <f t="shared" ref="J33:J57" si="1">E33/I33-1</f>
         <v>0.36794171220400718</v>
       </c>
       <c r="K33" s="11">
@@ -2974,7 +3018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>137</v>
       </c>
@@ -3028,7 +3072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>115</v>
       </c>
@@ -3082,7 +3126,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
         <v>130</v>
       </c>
@@ -3136,7 +3180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>116</v>
       </c>
@@ -3190,7 +3234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>142</v>
       </c>
@@ -3244,7 +3288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>123</v>
       </c>
@@ -3298,7 +3342,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>136</v>
       </c>
@@ -3352,7 +3396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>121</v>
       </c>
@@ -3406,7 +3450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>127</v>
       </c>
@@ -3460,7 +3504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>122</v>
       </c>
@@ -3514,7 +3558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
@@ -3568,7 +3612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>117</v>
       </c>
@@ -3622,7 +3666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
         <v>128</v>
       </c>
@@ -3676,7 +3720,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
         <v>129</v>
       </c>
@@ -3730,7 +3774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>112</v>
       </c>
@@ -3784,7 +3828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
@@ -3838,7 +3882,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>139</v>
       </c>
@@ -3892,7 +3936,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>134</v>
       </c>
@@ -3946,7 +3990,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>141</v>
       </c>
@@ -4000,7 +4044,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
@@ -4054,7 +4098,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>26</v>
       </c>
@@ -4108,7 +4152,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="55" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
         <v>114</v>
       </c>
@@ -4162,7 +4206,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="56" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
         <v>196</v>
       </c>
@@ -4216,7 +4260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.5">
+    <row r="57" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
         <v>131</v>
       </c>
@@ -4268,6 +4312,61 @@
       </c>
       <c r="R57" s="14">
         <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B60" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -4293,25 +4392,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B46D05-099C-4A4C-836A-6062A20AA7D3}">
   <dimension ref="B1:V11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4368,7 +4467,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
@@ -4422,7 +4521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -4476,7 +4575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -4530,7 +4629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4584,7 +4683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -4638,7 +4737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
@@ -4692,7 +4791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
@@ -4746,7 +4845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4800,7 +4899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4854,7 +4953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4921,25 +5020,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FA5E83-3B3C-124C-A85B-B3DA799E441B}">
   <dimension ref="B1:V4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.8125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4996,7 +5095,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
@@ -5050,7 +5149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
@@ -5104,7 +5203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
@@ -5171,23 +5270,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54703291-9A5D-4E46-9F96-9938DF840B6E}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.6875" customWidth="1"/>
-    <col min="2" max="2" width="210.1875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="210.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:2" ht="409.6" x14ac:dyDescent="0.2">
       <c r="B3" s="15" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>145</v>
       </c>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A92E1D4-9B99-4746-85F8-C41A51093BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9A44D9-7E79-43C6-AAC8-5C65C8B56DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -28,23 +28,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="223">
   <si>
     <t>Ticker</t>
   </si>
@@ -747,6 +736,39 @@
   <si>
     <t>0998.HK</t>
   </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>EBF</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>TAP</t>
+  </si>
+  <si>
+    <t>WU</t>
+  </si>
+  <si>
+    <t>JBSS</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>NOMD</t>
+  </si>
+  <si>
+    <t>MOV</t>
+  </si>
+  <si>
+    <t>WLKP</t>
+  </si>
 </sst>
 </file>
 
@@ -772,6 +794,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -862,7 +885,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1215,25 +1238,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
   <dimension ref="B1:V68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="18.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1290,7 +1313,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -1344,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1398,7 +1421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1452,7 +1475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1506,7 +1529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
@@ -1560,7 +1583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1614,7 +1637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1668,7 +1691,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1722,7 +1745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1776,7 +1799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1830,7 +1853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1884,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1938,7 +1961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,7 +2015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2046,7 +2069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2100,7 +2123,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
@@ -2154,7 +2177,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>124</v>
       </c>
@@ -2208,7 +2231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>118</v>
       </c>
@@ -2262,7 +2285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>113</v>
       </c>
@@ -2316,7 +2339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>140</v>
       </c>
@@ -2370,7 +2393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>143</v>
       </c>
@@ -2424,7 +2447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -2478,7 +2501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2532,7 +2555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
@@ -2586,7 +2609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>120</v>
       </c>
@@ -2640,7 +2663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>125</v>
       </c>
@@ -2694,7 +2717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>119</v>
       </c>
@@ -2748,7 +2771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>197</v>
       </c>
@@ -2802,7 +2825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>138</v>
       </c>
@@ -2856,7 +2879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
@@ -2910,7 +2933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>126</v>
       </c>
@@ -2964,7 +2987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>135</v>
       </c>
@@ -3018,7 +3041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>137</v>
       </c>
@@ -3072,7 +3095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>115</v>
       </c>
@@ -3126,7 +3149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>130</v>
       </c>
@@ -3180,7 +3203,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>116</v>
       </c>
@@ -3234,7 +3257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>142</v>
       </c>
@@ -3288,7 +3311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
         <v>123</v>
       </c>
@@ -3342,7 +3365,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
         <v>136</v>
       </c>
@@ -3396,7 +3419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
         <v>121</v>
       </c>
@@ -3450,7 +3473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
         <v>127</v>
       </c>
@@ -3504,7 +3527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
         <v>122</v>
       </c>
@@ -3558,7 +3581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
@@ -3612,7 +3635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
         <v>117</v>
       </c>
@@ -3666,7 +3689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
         <v>128</v>
       </c>
@@ -3720,7 +3743,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
         <v>129</v>
       </c>
@@ -3774,7 +3797,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
         <v>112</v>
       </c>
@@ -3828,7 +3851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
@@ -3882,7 +3905,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
         <v>139</v>
       </c>
@@ -3936,7 +3959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
         <v>134</v>
       </c>
@@ -3990,7 +4013,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
         <v>141</v>
       </c>
@@ -4044,7 +4067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
@@ -4098,7 +4121,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
         <v>26</v>
       </c>
@@ -4152,7 +4175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
         <v>114</v>
       </c>
@@ -4206,7 +4229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
         <v>196</v>
       </c>
@@ -4260,7 +4283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
         <v>131</v>
       </c>
@@ -4314,57 +4337,57 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
         <v>211</v>
       </c>
@@ -4392,25 +4415,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B46D05-099C-4A4C-836A-6062A20AA7D3}">
   <dimension ref="B1:V11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4467,7 +4490,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
@@ -4521,7 +4544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -4575,7 +4598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -4629,7 +4652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4683,7 +4706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -4737,7 +4760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
@@ -4791,7 +4814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
@@ -4845,7 +4868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4899,7 +4922,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4953,7 +4976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -5019,26 +5042,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FA5E83-3B3C-124C-A85B-B3DA799E441B}">
-  <dimension ref="B1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:V15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.8125" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1875" style="7" customWidth="1"/>
     <col min="8" max="9" width="11" style="6"/>
     <col min="10" max="10" width="11" style="12"/>
     <col min="11" max="11" width="11" style="11"/>
     <col min="12" max="13" width="15.5" style="13" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="5.1875" style="6" customWidth="1"/>
     <col min="16" max="17" width="11" style="12"/>
     <col min="18" max="18" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:22" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5095,7 +5118,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
@@ -5149,7 +5172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
@@ -5203,7 +5226,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
@@ -5255,6 +5278,61 @@
       </c>
       <c r="R4" s="14">
         <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B5" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B6" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B7" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B8" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B9" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B10" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B11" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B12" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B13" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B14" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B15" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -5270,23 +5348,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54703291-9A5D-4E46-9F96-9938DF840B6E}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="210.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.6875" customWidth="1"/>
+    <col min="2" max="2" width="210.1875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
       <c r="B3" s="15" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
         <v>145</v>
       </c>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9A44D9-7E79-43C6-AAC8-5C65C8B56DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5773E-0C24-4006-9AFD-0CC0A5C9DF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="256">
   <si>
     <t>Ticker</t>
   </si>
@@ -768,6 +768,105 @@
   </si>
   <si>
     <t>WLKP</t>
+  </si>
+  <si>
+    <t>CHINFMINING</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>OOIL</t>
+  </si>
+  <si>
+    <t>BEST MART 360</t>
+  </si>
+  <si>
+    <t>Grocery Stores</t>
+  </si>
+  <si>
+    <t>WEICHAI POWER</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>SINGAMAS CONT</t>
+  </si>
+  <si>
+    <t>Packaging &amp; Containers</t>
+  </si>
+  <si>
+    <t>BOC HONG KONG</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
+  </si>
+  <si>
+    <t>BANKCOMM</t>
+  </si>
+  <si>
+    <t>Banks - Diversified</t>
+  </si>
+  <si>
+    <t>ICBC</t>
+  </si>
+  <si>
+    <t>PSBC</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>CITIC BANK</t>
+  </si>
+  <si>
+    <t>Equinor ASA</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Integrated</t>
+  </si>
+  <si>
+    <t>Global Ship Lease Inc New</t>
+  </si>
+  <si>
+    <t>Ennis, Inc.</t>
+  </si>
+  <si>
+    <t>Atkore Inc.</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Molson Coors Beverage Company</t>
+  </si>
+  <si>
+    <t>Beverages - Brewers</t>
+  </si>
+  <si>
+    <t>Western Union Company (The)</t>
+  </si>
+  <si>
+    <t>Credit Services</t>
+  </si>
+  <si>
+    <t>John B. Sanfilippo &amp; Son, Inc.</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>Nomad Foods Limited</t>
+  </si>
+  <si>
+    <t>Movado Group Inc.</t>
+  </si>
+  <si>
+    <t>Westlake Chemical Partners LP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
   </si>
 </sst>
 </file>
@@ -1324,13 +1423,13 @@
         <v>149</v>
       </c>
       <c r="E2">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>8699354112</v>
+        <v>8755299328</v>
       </c>
       <c r="H2" s="6">
         <v>3.35</v>
@@ -1339,11 +1438,11 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J32" si="0">E2/I2-1</f>
-        <v>0.31779661016949157</v>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
+        <v>0.32627118644067798</v>
       </c>
       <c r="K2" s="11">
-        <v>4.9196141479099682E-2</v>
+        <v>4.8881789137380192E-2</v>
       </c>
       <c r="L2" s="13">
         <v>1871151000</v>
@@ -1358,7 +1457,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.44405559305801723</v>
+        <v>0.43860503555673142</v>
       </c>
       <c r="Q2" s="12">
         <v>0.28956319566547578</v>
@@ -1378,13 +1477,13 @@
         <v>77</v>
       </c>
       <c r="E3">
-        <v>14.74</v>
+        <v>13.16</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>266401906688</v>
+        <v>257500397568</v>
       </c>
       <c r="H3" s="6">
         <v>15.14</v>
@@ -1394,10 +1493,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.54831932773109249</v>
+        <v>0.38235294117647056</v>
       </c>
       <c r="K3" s="11">
-        <v>0.10515603799185889</v>
+        <v>0.11778115501519756</v>
       </c>
       <c r="L3" s="13">
         <v>70144988000</v>
@@ -1412,7 +1511,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.49612618476500991</v>
+        <v>0.52719360007237348</v>
       </c>
       <c r="Q3" s="12">
         <v>0.26042924055386191</v>
@@ -1441,7 +1540,7 @@
         <v>17859514368</v>
       </c>
       <c r="H4" s="6">
-        <v>5.33</v>
+        <v>5.19</v>
       </c>
       <c r="I4" s="6">
         <v>2.11</v>
@@ -1472,7 +1571,7 @@
         <v>0.27500236540826944</v>
       </c>
       <c r="R4" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
@@ -1486,13 +1585,13 @@
         <v>83</v>
       </c>
       <c r="E5">
-        <v>15.1</v>
+        <v>15.26</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>31377195008</v>
+        <v>31766437888</v>
       </c>
       <c r="H5" s="6">
         <v>15.48</v>
@@ -1502,10 +1601,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.89698492462311563</v>
+        <v>0.91708542713567831</v>
       </c>
       <c r="K5" s="11">
-        <v>7.4172185430463583E-2</v>
+        <v>7.3394495412844041E-2</v>
       </c>
       <c r="L5" s="13">
         <v>5451928473.2399998</v>
@@ -1520,13 +1619,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P5" s="12">
-        <v>0.16717087768969968</v>
+        <v>0.16532397994525591</v>
       </c>
       <c r="Q5" s="12">
         <v>0.20973136925592797</v>
       </c>
       <c r="R5" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -1540,26 +1639,26 @@
         <v>147</v>
       </c>
       <c r="E6">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>13389514752</v>
+        <v>13644067840</v>
       </c>
       <c r="H6" s="6">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="I6" s="6">
         <v>2.23</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.17937219730941689</v>
+        <v>0.20179372197309431</v>
       </c>
       <c r="K6" s="11">
-        <v>0.11406844106463879</v>
+        <v>0.11194029850746268</v>
       </c>
       <c r="L6" s="13">
         <v>2527643000</v>
@@ -1574,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>0.43903173388000094</v>
+        <v>0.42044234972482353</v>
       </c>
       <c r="Q6" s="12">
         <v>0.15337570692947131</v>
       </c>
       <c r="R6" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
@@ -1594,13 +1693,13 @@
         <v>182</v>
       </c>
       <c r="E7">
-        <v>9.16</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>113627054080</v>
+        <v>113254916096</v>
       </c>
       <c r="H7" s="6">
         <v>13.6</v>
@@ -1610,10 +1709,10 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>0.39421613394216126</v>
+        <v>0.38964992389649922</v>
       </c>
       <c r="K7" s="11">
-        <v>5.4585152838427953E-3</v>
+        <v>5.4764512595837896E-3</v>
       </c>
       <c r="L7" s="13">
         <v>2125459000</v>
@@ -1628,13 +1727,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P7" s="12">
-        <v>0.14007819590180975</v>
+        <v>0.14052624188977578</v>
       </c>
       <c r="Q7" s="12">
         <v>0.23097158924015673</v>
       </c>
       <c r="R7" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
@@ -1648,13 +1747,13 @@
         <v>50</v>
       </c>
       <c r="E8">
-        <v>6.28</v>
+        <v>6.36</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>7658523136</v>
+        <v>7920871424</v>
       </c>
       <c r="H8" s="6">
         <v>8.6</v>
@@ -1664,10 +1763,10 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.81502890173410414</v>
+        <v>0.83815028901734112</v>
       </c>
       <c r="K8" s="11">
-        <v>2.2452229299363056E-2</v>
+        <v>2.2169811320754712E-2</v>
       </c>
       <c r="L8" s="13">
         <v>921702000</v>
@@ -1682,13 +1781,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.18931080612829809</v>
+        <v>0.18022120457207247</v>
       </c>
       <c r="Q8" s="12">
         <v>0.17514380877385538</v>
       </c>
       <c r="R8" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
@@ -1702,13 +1801,13 @@
         <v>96</v>
       </c>
       <c r="E9">
-        <v>14.4</v>
+        <v>14.18</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>11984947200</v>
+        <v>11801843712</v>
       </c>
       <c r="H9" s="6">
         <v>19.440000000000001</v>
@@ -1718,10 +1817,10 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.18811881188118829</v>
+        <v>0.16996699669966997</v>
       </c>
       <c r="K9" s="11">
-        <v>1.0277777777777776E-2</v>
+        <v>1.0437235543018335E-2</v>
       </c>
       <c r="L9" s="13">
         <v>199557000</v>
@@ -1736,13 +1835,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P9" s="12">
-        <v>0.17405845676300949</v>
+        <v>0.1777488698356014</v>
       </c>
       <c r="Q9" s="12">
         <v>0.18009145491283626</v>
       </c>
       <c r="R9" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -1756,13 +1855,13 @@
         <v>74</v>
       </c>
       <c r="E10">
-        <v>2.5</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>2599524864</v>
+        <v>2412359168</v>
       </c>
       <c r="H10" s="6">
         <v>3.34</v>
@@ -1772,10 +1871,10 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>0.30208333333333348</v>
+        <v>0.20833333333333326</v>
       </c>
       <c r="K10" s="11">
-        <v>0.11679999999999999</v>
+        <v>0.12586206896551724</v>
       </c>
       <c r="L10" s="13">
         <v>762183000</v>
@@ -1790,13 +1889,13 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.2278871120399093</v>
+        <v>0.24139590873418154</v>
       </c>
       <c r="Q10" s="12">
         <v>0.15218339726363278</v>
       </c>
       <c r="R10" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -1810,13 +1909,13 @@
         <v>71</v>
       </c>
       <c r="E11">
-        <v>4.53</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>52238151680</v>
+        <v>50623721472</v>
       </c>
       <c r="H11" s="6">
         <v>5.14</v>
@@ -1826,10 +1925,10 @@
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.30924855491329484</v>
+        <v>0.26878612716762995</v>
       </c>
       <c r="K11" s="11">
-        <v>5.2097130242825598E-2</v>
+        <v>5.3758542141230069E-2</v>
       </c>
       <c r="L11" s="13">
         <v>4734613000</v>
@@ -1844,7 +1943,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P11" s="12">
-        <v>0.10318129921430115</v>
+        <v>0.10669492405071343</v>
       </c>
       <c r="Q11" s="12">
         <v>0.29201860560357656</v>
@@ -1864,13 +1963,13 @@
         <v>79</v>
       </c>
       <c r="E12">
-        <v>8.85</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>142903607296</v>
+        <v>140669730816</v>
       </c>
       <c r="H12" s="6">
         <v>10.76</v>
@@ -1880,10 +1979,10 @@
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.2360335195530725</v>
+        <v>0.19413407821229067</v>
       </c>
       <c r="K12" s="11">
-        <v>5.4124293785310737E-2</v>
+        <v>5.6023391812865489E-2</v>
       </c>
       <c r="L12" s="13">
         <v>32866046000</v>
@@ -1898,13 +1997,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.19525105677556878</v>
+        <v>0.19770691217459413</v>
       </c>
       <c r="Q12" s="12">
         <v>0.15266623500015464</v>
       </c>
       <c r="R12" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -1918,26 +2017,26 @@
         <v>81</v>
       </c>
       <c r="E13">
-        <v>8.27</v>
+        <v>7.9</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>71609933824</v>
+        <v>68406104064</v>
       </c>
       <c r="H13" s="6">
         <v>9.23</v>
       </c>
       <c r="I13" s="6">
-        <v>6.81</v>
+        <v>7.08</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.21439060205580041</v>
+        <v>0.11581920903954801</v>
       </c>
       <c r="K13" s="11">
-        <v>3.8210399032648126E-2</v>
+        <v>0.04</v>
       </c>
       <c r="L13" s="13">
         <v>13438000000</v>
@@ -1952,13 +2051,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.21169239559663214</v>
+        <v>0.22218873682092952</v>
       </c>
       <c r="Q13" s="12">
         <v>0.15165160081705431</v>
       </c>
       <c r="R13" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -1972,13 +2071,13 @@
         <v>87</v>
       </c>
       <c r="E14">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>61848240128</v>
+        <v>61494153216</v>
       </c>
       <c r="H14" s="6">
         <v>5.77</v>
@@ -1988,10 +2087,10 @@
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.27184466019417486</v>
+        <v>0.2645631067961165</v>
       </c>
       <c r="K14" s="11">
-        <v>4.5419847328244271E-2</v>
+        <v>4.5681381957773513E-2</v>
       </c>
       <c r="L14" s="13">
         <v>5687261000</v>
@@ -2006,13 +2105,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.10339478616831782</v>
+        <v>0.10402155086679897</v>
       </c>
       <c r="Q14" s="12">
         <v>0.26188601495697911</v>
       </c>
       <c r="R14" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
@@ -2026,26 +2125,26 @@
         <v>89</v>
       </c>
       <c r="E15">
-        <v>4.7699999999999996</v>
+        <v>5.36</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>5054196736</v>
+        <v>5679349248</v>
       </c>
       <c r="H15" s="6">
-        <v>6.26</v>
+        <v>5.99</v>
       </c>
       <c r="I15" s="6">
         <v>3.97</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.20151133501259433</v>
+        <v>0.35012594458438295</v>
       </c>
       <c r="K15" s="11">
-        <v>0.10272536687631029</v>
+        <v>9.141791044776118E-2</v>
       </c>
       <c r="L15" s="13">
         <v>866801000</v>
@@ -2060,13 +2159,13 @@
         <v>1</v>
       </c>
       <c r="P15" s="12">
-        <v>0.42109939991480938</v>
+        <v>0.32300218808614228</v>
       </c>
       <c r="Q15" s="12">
         <v>0.11511220438953086</v>
       </c>
       <c r="R15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2080,13 +2179,13 @@
         <v>71</v>
       </c>
       <c r="E16">
-        <v>5.0199999999999996</v>
+        <v>4.99</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>14321156096</v>
+        <v>14235571200</v>
       </c>
       <c r="H16" s="6">
         <v>6.21</v>
@@ -2096,10 +2195,10 @@
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>0.55900621118012395</v>
+        <v>0.54968944099378869</v>
       </c>
       <c r="K16" s="11">
-        <v>8.3665338645418346E-3</v>
+        <v>8.4168336673346687E-3</v>
       </c>
       <c r="L16" s="13">
         <v>259348000</v>
@@ -2114,13 +2213,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P16" s="12">
-        <v>0.16111230357181586</v>
+        <v>0.16223361728966321</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15459217096529801</v>
       </c>
       <c r="R16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
@@ -2134,13 +2233,13 @@
         <v>87</v>
       </c>
       <c r="E17">
-        <v>6.24</v>
+        <v>5.75</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>56579637248</v>
+        <v>52136685568</v>
       </c>
       <c r="H17" s="6">
         <v>7.38</v>
@@ -2150,10 +2249,10 @@
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.84070796460176989</v>
+        <v>0.69616519174041303</v>
       </c>
       <c r="K17" s="11">
-        <v>4.9198717948717947E-2</v>
+        <v>5.3391304347826088E-2</v>
       </c>
       <c r="L17" s="13">
         <v>5594372000</v>
@@ -2168,13 +2267,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.12510216016396158</v>
+        <v>0.13792889650292511</v>
       </c>
       <c r="Q17" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
@@ -2188,13 +2287,13 @@
         <v>77</v>
       </c>
       <c r="E18">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>7227232256</v>
+        <v>7095295488</v>
       </c>
       <c r="H18" s="6">
         <v>5.04</v>
@@ -2204,10 +2303,10 @@
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.42898550724637663</v>
+        <v>0.40289855072463765</v>
       </c>
       <c r="K18" s="11">
-        <v>9.7363083164300201E-2</v>
+        <v>9.9173553719008267E-2</v>
       </c>
       <c r="L18" s="13">
         <v>784607000</v>
@@ -2222,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="12">
-        <v>0.52073488063015305</v>
+        <v>0.57070898782144941</v>
       </c>
       <c r="Q18" s="12">
         <v>9.9663185641922489E-2</v>
@@ -2242,13 +2341,13 @@
         <v>85</v>
       </c>
       <c r="E19">
-        <v>95.6</v>
+        <v>96.85</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>266533748736</v>
+        <v>270018756608</v>
       </c>
       <c r="H19" s="6">
         <v>107.5</v>
@@ -2258,10 +2357,10 @@
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>0.45842868039664375</v>
+        <v>0.47749809305873381</v>
       </c>
       <c r="K19" s="11">
-        <v>2.3200836820083684E-2</v>
+        <v>2.2901393908105319E-2</v>
       </c>
       <c r="L19" s="13">
         <v>22510000000</v>
@@ -2276,13 +2375,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P19" s="12">
-        <v>8.4558705548000476E-2</v>
+        <v>8.3535102773332204E-2</v>
       </c>
       <c r="Q19" s="12">
         <v>0.27269973953601068</v>
       </c>
       <c r="R19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
@@ -2296,13 +2395,13 @@
         <v>152</v>
       </c>
       <c r="E20">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>5497620480</v>
+        <v>6028722176</v>
       </c>
       <c r="H20" s="6">
         <v>7.92</v>
@@ -2312,10 +2411,10 @@
       </c>
       <c r="J20" s="12">
         <f t="shared" si="0"/>
-        <v>0.62288135593220351</v>
+        <v>0.77966101694915269</v>
       </c>
       <c r="K20" s="11">
-        <v>6.6318537859007834E-2</v>
+        <v>6.0476190476190475E-2</v>
       </c>
       <c r="L20" s="13">
         <v>811880000</v>
@@ -2330,13 +2429,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>0.16416567610994109</v>
+        <v>0.14917127088890111</v>
       </c>
       <c r="Q20" s="12">
         <v>0.14675695119790894</v>
       </c>
       <c r="R20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
@@ -2350,13 +2449,13 @@
         <v>87</v>
       </c>
       <c r="E21">
-        <v>13.54</v>
+        <v>13.12</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>76290318336</v>
+        <v>73923854336</v>
       </c>
       <c r="H21" s="6">
         <v>14.24</v>
@@ -2366,10 +2465,10 @@
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.53688989784335961</v>
+        <v>0.48921679909194071</v>
       </c>
       <c r="K21" s="11">
-        <v>2.4446085672082722E-2</v>
+        <v>2.5228658536585367E-2</v>
       </c>
       <c r="L21" s="13">
         <v>6482967000</v>
@@ -2384,7 +2483,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>8.3751586377721829E-2</v>
+        <v>8.6218742696708636E-2</v>
       </c>
       <c r="Q21" s="12">
         <v>0.23588267049650188</v>
@@ -2404,13 +2503,13 @@
         <v>109</v>
       </c>
       <c r="E22">
-        <v>51.25</v>
+        <v>49.9</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>131139526656</v>
+        <v>127685124096</v>
       </c>
       <c r="H22" s="6">
         <v>71.7</v>
@@ -2420,10 +2519,10 @@
       </c>
       <c r="J22" s="12">
         <f t="shared" si="0"/>
-        <v>0.17680826636050528</v>
+        <v>0.14580941446613083</v>
       </c>
       <c r="K22" s="11">
-        <v>3.2000000000000002E-3</v>
+        <v>3.2865731462925853E-3</v>
       </c>
       <c r="L22" s="13">
         <v>1279098000</v>
@@ -2438,13 +2537,13 @@
         <v>8.7546153846153842</v>
       </c>
       <c r="P22" s="12">
-        <v>7.6339630042846232E-2</v>
+        <v>7.8180749364385127E-2</v>
       </c>
       <c r="Q22" s="12">
         <v>0.26583067696212276</v>
       </c>
       <c r="R22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
@@ -2458,13 +2557,13 @@
         <v>178</v>
       </c>
       <c r="E23">
-        <v>17.899999999999999</v>
+        <v>18.34</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>508519284736</v>
+        <v>518143541248</v>
       </c>
       <c r="H23" s="6">
         <v>19.260000000000002</v>
@@ -2474,10 +2573,10 @@
       </c>
       <c r="J23" s="12">
         <f t="shared" si="0"/>
-        <v>0.32396449704142016</v>
+        <v>0.35650887573964507</v>
       </c>
       <c r="K23" s="11">
-        <v>2.1229050279329611E-2</v>
+        <v>2.0719738276990186E-2</v>
       </c>
       <c r="L23" s="13">
         <v>52374992116</v>
@@ -2492,13 +2591,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>8.8425637480669741E-2</v>
+        <v>8.7100929788278658E-2</v>
       </c>
       <c r="Q23" s="12">
         <v>0.19428864891763736</v>
       </c>
       <c r="R23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
@@ -2512,13 +2611,13 @@
         <v>104</v>
       </c>
       <c r="E24">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>4566123520</v>
+        <v>4870012416</v>
       </c>
       <c r="H24" s="6">
         <v>8.09</v>
@@ -2528,10 +2627,10 @@
       </c>
       <c r="J24" s="12">
         <f t="shared" si="0"/>
-        <v>0.45771144278606979</v>
+        <v>0.55472636815920406</v>
       </c>
       <c r="K24" s="11">
-        <v>2.9010238907849831E-2</v>
+        <v>2.7200000000000002E-2</v>
       </c>
       <c r="L24" s="13">
         <v>437453000</v>
@@ -2546,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="P24" s="12">
-        <v>0.19214560366758091</v>
+        <v>0.16951840721592248</v>
       </c>
       <c r="Q24" s="12">
         <v>8.9074849645861431E-2</v>
       </c>
       <c r="R24" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
@@ -2566,26 +2665,26 @@
         <v>101</v>
       </c>
       <c r="E25">
-        <v>391</v>
+        <v>402.4</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>494161428480</v>
+        <v>508569223168</v>
       </c>
       <c r="H25" s="6">
-        <v>399.6</v>
+        <v>409.2</v>
       </c>
       <c r="I25" s="6">
         <v>218.4</v>
       </c>
       <c r="J25" s="12">
         <f t="shared" si="0"/>
-        <v>0.79029304029304015</v>
+        <v>0.84249084249084238</v>
       </c>
       <c r="K25" s="11">
-        <v>2.3682864450127877E-2</v>
+        <v>2.301192842942346E-2</v>
       </c>
       <c r="L25" s="13">
         <v>20744000000</v>
@@ -2600,13 +2699,13 @@
         <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>5.7448213422109484E-2</v>
+        <v>5.5243936509172288E-2</v>
       </c>
       <c r="Q25" s="12">
         <v>0.38520389214885242</v>
       </c>
       <c r="R25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
@@ -2620,13 +2719,13 @@
         <v>69</v>
       </c>
       <c r="E26">
-        <v>5.99</v>
+        <v>6.19</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>9743992832</v>
+        <v>10069335040</v>
       </c>
       <c r="H26" s="6">
         <v>7.05</v>
@@ -2636,10 +2735,10 @@
       </c>
       <c r="J26" s="12">
         <f t="shared" si="0"/>
-        <v>0.40281030444964894</v>
+        <v>0.44964871194379419</v>
       </c>
       <c r="K26" s="11">
-        <v>4.6744574290484141E-2</v>
+        <v>4.5234248788368341E-2</v>
       </c>
       <c r="L26" s="13">
         <v>4094312000</v>
@@ -2654,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>0.1357513317572113</v>
+        <v>0.13430259995228902</v>
       </c>
       <c r="Q26" s="12">
         <v>0.10878407220713927</v>
       </c>
       <c r="R26" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
@@ -2674,13 +2773,13 @@
         <v>168</v>
       </c>
       <c r="E27">
-        <v>21.8</v>
+        <v>21.95</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>24828452864</v>
+        <v>24970758144</v>
       </c>
       <c r="H27" s="6">
         <v>28.75</v>
@@ -2690,10 +2789,10 @@
       </c>
       <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>0.11680327868852469</v>
+        <v>0.12448770491803285</v>
       </c>
       <c r="K27" s="11">
-        <v>6.4220183486238522E-2</v>
+        <v>6.3781321184510242E-2</v>
       </c>
       <c r="L27" s="13">
         <v>3446618000</v>
@@ -2708,13 +2807,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.15602168152308715</v>
+        <v>0.15508657118243896</v>
       </c>
       <c r="Q27" s="12">
         <v>0.10133893359397213</v>
       </c>
       <c r="R27" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
@@ -2728,26 +2827,26 @@
         <v>85</v>
       </c>
       <c r="E28">
-        <v>216.6</v>
+        <v>244.8</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>287679479808</v>
+        <v>325133565952</v>
       </c>
       <c r="H28" s="6">
-        <v>235</v>
+        <v>252.6</v>
       </c>
       <c r="I28" s="6">
         <v>34.4</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="0"/>
-        <v>5.2965116279069768</v>
+        <v>6.1162790697674421</v>
       </c>
       <c r="K28" s="11">
-        <v>3.7626962142197598E-3</v>
+        <v>3.3292483660130713E-3</v>
       </c>
       <c r="L28" s="13">
         <v>4414795000</v>
@@ -2762,13 +2861,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>1.6714886709713026E-2</v>
+        <v>1.4756289561246224E-2</v>
       </c>
       <c r="Q28" s="12">
         <v>0.41323470153287706</v>
       </c>
       <c r="R28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
@@ -2782,13 +2881,13 @@
         <v>186</v>
       </c>
       <c r="E29">
-        <v>6.94</v>
+        <v>6.96</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>3981505792</v>
+        <v>3992979968</v>
       </c>
       <c r="H29" s="6">
         <v>9.24</v>
@@ -2798,10 +2897,10 @@
       </c>
       <c r="J29" s="12">
         <f t="shared" si="0"/>
-        <v>1.3138686131386912E-2</v>
+        <v>1.6058394160584077E-2</v>
       </c>
       <c r="K29" s="11">
-        <v>8.2132564841498543E-2</v>
+        <v>8.1896551724137928E-2</v>
       </c>
       <c r="L29" s="13">
         <v>498120000</v>
@@ -2816,13 +2915,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>9.6372678939714296E-2</v>
+        <v>9.6159211151065974E-2</v>
       </c>
       <c r="Q29" s="12">
         <v>0.15164171979951585</v>
       </c>
       <c r="R29" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
@@ -2836,13 +2935,13 @@
         <v>186</v>
       </c>
       <c r="E30">
-        <v>341.8</v>
+        <v>339.4</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>127261024256</v>
+        <v>126199775232</v>
       </c>
       <c r="H30" s="6">
         <v>421.4</v>
@@ -2852,10 +2951,10 @@
       </c>
       <c r="J30" s="12">
         <f t="shared" si="0"/>
-        <v>0.51776198934280648</v>
+        <v>0.50710479573712264</v>
       </c>
       <c r="K30" s="11">
-        <v>2.1064950263311876E-3</v>
+        <v>2.1213906894519742E-3</v>
       </c>
       <c r="L30" s="13">
         <v>1200000000</v>
@@ -2870,13 +2969,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P30" s="12">
-        <v>6.5825803633519697E-2</v>
+        <v>6.6327765757611262E-2</v>
       </c>
       <c r="Q30" s="12">
         <v>0.20495303159692571</v>
       </c>
       <c r="R30" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
@@ -2890,26 +2989,26 @@
         <v>50</v>
       </c>
       <c r="E31">
-        <v>12.34</v>
+        <v>12.54</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>57997750272</v>
+        <v>58221084672</v>
       </c>
       <c r="H31" s="6">
-        <v>13.56</v>
+        <v>13.44</v>
       </c>
       <c r="I31" s="6">
         <v>7.51</v>
       </c>
       <c r="J31" s="12">
         <f t="shared" si="0"/>
-        <v>0.64314247669773628</v>
+        <v>0.66977363515312915</v>
       </c>
       <c r="K31" s="11">
-        <v>3.5494327390599677E-2</v>
+        <v>3.4928229665071774E-2</v>
       </c>
       <c r="L31" s="13">
         <v>3967214824.1399999</v>
@@ -2924,13 +3023,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P31" s="12">
-        <v>0.13041654887075355</v>
+        <v>0.12952645270905808</v>
       </c>
       <c r="Q31" s="12">
         <v>9.6670468672106824E-2</v>
       </c>
       <c r="R31" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
@@ -2944,26 +3043,26 @@
         <v>109</v>
       </c>
       <c r="E32">
-        <v>11.22</v>
+        <v>11.88</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>112057614336</v>
+        <v>118649241600</v>
       </c>
       <c r="H32" s="6">
-        <v>11.56</v>
+        <v>12.16</v>
       </c>
       <c r="I32" s="6">
         <v>5.83</v>
       </c>
       <c r="J32" s="12">
         <f t="shared" si="0"/>
-        <v>0.92452830188679247</v>
+        <v>1.0377358490566038</v>
       </c>
       <c r="K32" s="11">
-        <v>4.4563279857397504E-2</v>
+        <v>4.2087542087542083E-2</v>
       </c>
       <c r="L32" s="13">
         <v>9432900000</v>
@@ -2978,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>7.0262057209279694E-2</v>
+        <v>6.6973746359587194E-2</v>
       </c>
       <c r="Q32" s="12">
         <v>0.17359450999011755</v>
       </c>
       <c r="R32" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
@@ -2998,26 +3097,26 @@
         <v>77</v>
       </c>
       <c r="E33">
-        <v>15.02</v>
+        <v>14.48</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>63054114816</v>
+        <v>60787183616</v>
       </c>
       <c r="H33" s="6">
-        <v>15.08</v>
+        <v>15.38</v>
       </c>
       <c r="I33" s="6">
         <v>10.98</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" ref="J33:J57" si="1">E33/I33-1</f>
-        <v>0.36794171220400718</v>
+        <f t="shared" si="0"/>
+        <v>0.31876138433515488</v>
       </c>
       <c r="K33" s="11">
-        <v>5.8988015978695074E-2</v>
+        <v>6.1187845303867401E-2</v>
       </c>
       <c r="L33" s="13">
         <v>11996000000</v>
@@ -3032,13 +3131,13 @@
         <v>1</v>
       </c>
       <c r="P33" s="12">
-        <v>0.13917746450018836</v>
+        <v>0.14293683353601874</v>
       </c>
       <c r="Q33" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R33" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
@@ -3052,26 +3151,26 @@
         <v>184</v>
       </c>
       <c r="E34">
-        <v>33.299999999999997</v>
+        <v>35</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>23032942592</v>
+        <v>24208799744</v>
       </c>
       <c r="H34" s="6">
-        <v>35.75</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="I34" s="6">
-        <v>13.2</v>
+        <v>13.48</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="1"/>
-        <v>1.5227272727272725</v>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
+        <v>1.5964391691394657</v>
       </c>
       <c r="K34" s="11">
-        <v>1.3813813813813816E-2</v>
+        <v>1.3142857142857144E-2</v>
       </c>
       <c r="L34" s="13">
         <v>1323087000</v>
@@ -3086,13 +3185,13 @@
         <v>1</v>
       </c>
       <c r="P34" s="12">
-        <v>5.1894320976402654E-2</v>
+        <v>4.9606487183200106E-2</v>
       </c>
       <c r="Q34" s="12">
         <v>0.222258562943417</v>
       </c>
       <c r="R34" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
@@ -3106,13 +3205,13 @@
         <v>156</v>
       </c>
       <c r="E35">
-        <v>58.05</v>
+        <v>57.05</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>162675261440</v>
+        <v>161359642624</v>
       </c>
       <c r="H35" s="6">
         <v>60</v>
@@ -3122,10 +3221,10 @@
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
-        <v>0.51171875</v>
+        <v>0.48567708333333326</v>
       </c>
       <c r="K35" s="11">
-        <v>3.1007751937984499E-2</v>
+        <v>3.15512708150745E-2</v>
       </c>
       <c r="L35" s="13">
         <v>8955723006</v>
@@ -3140,13 +3239,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>6.0318143253415502E-2</v>
+        <v>6.0822593303914124E-2</v>
       </c>
       <c r="Q35" s="12">
         <v>0.18855793075067021</v>
       </c>
       <c r="R35" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
@@ -3160,13 +3259,13 @@
         <v>175</v>
       </c>
       <c r="E36">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>4605217341440</v>
+        <v>4683229822976</v>
       </c>
       <c r="H36" s="6">
         <v>547</v>
@@ -3176,10 +3275,10 @@
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
-        <v>0.44985673352435529</v>
+        <v>0.47564469914040108</v>
       </c>
       <c r="K36" s="11">
-        <v>8.3577075098814225E-3</v>
+        <v>8.211650485436893E-3</v>
       </c>
       <c r="L36" s="13">
         <v>253932000000</v>
@@ -3194,13 +3293,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>5.5980538209562711E-2</v>
+        <v>5.5093665591363035E-2</v>
       </c>
       <c r="Q36" s="12">
         <v>0.19352168899747973</v>
       </c>
       <c r="R36" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
@@ -3214,13 +3313,13 @@
         <v>93</v>
       </c>
       <c r="E37">
-        <v>20.65</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>128567304192</v>
+        <v>125902422016</v>
       </c>
       <c r="H37" s="6">
         <v>26.6</v>
@@ -3230,10 +3329,10 @@
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
-        <v>0.28901373283395748</v>
+        <v>0.23345817727840212</v>
       </c>
       <c r="K37" s="11">
-        <v>3.4382566585956419E-2</v>
+        <v>3.5931174089068818E-2</v>
       </c>
       <c r="L37" s="13">
         <v>10795274825</v>
@@ -3248,13 +3347,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P37" s="12">
-        <v>0.13552022486560977</v>
+        <v>0.13990093886262106</v>
       </c>
       <c r="Q37" s="12">
         <v>5.0146340085309396E-2</v>
       </c>
       <c r="R37" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
@@ -3268,13 +3367,13 @@
         <v>104</v>
       </c>
       <c r="E38">
-        <v>32</v>
+        <v>32.049999999999997</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>72102395904</v>
+        <v>72215052288</v>
       </c>
       <c r="H38" s="6">
         <v>61.55</v>
@@ -3284,10 +3383,10 @@
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
-        <v>0.28772635814889336</v>
+        <v>0.28973843058350091</v>
       </c>
       <c r="K38" s="11">
-        <v>1.7749999999999998E-2</v>
+        <v>1.7722308892355695E-2</v>
       </c>
       <c r="L38" s="13">
         <v>5261270000</v>
@@ -3302,13 +3401,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>7.2175686211558024E-2</v>
+        <v>7.2071431632998909E-2</v>
       </c>
       <c r="Q38" s="12">
         <v>0.12176329850933591</v>
       </c>
       <c r="R38" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
@@ -3322,13 +3421,13 @@
         <v>165</v>
       </c>
       <c r="E39">
-        <v>6.21</v>
+        <v>5.88</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>47413411840</v>
+        <v>45912571904</v>
       </c>
       <c r="H39" s="6">
         <v>11.72</v>
@@ -3338,10 +3437,10 @@
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
-        <v>0.24199999999999999</v>
+        <v>0.17599999999999993</v>
       </c>
       <c r="K39" s="11">
-        <v>6.9243156199677941E-2</v>
+        <v>7.312925170068027E-2</v>
       </c>
       <c r="L39" s="13">
         <v>6749146000</v>
@@ -3356,13 +3455,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P39" s="12">
-        <v>9.0129403293835897E-2</v>
+        <v>9.1852537312565388E-2</v>
       </c>
       <c r="Q39" s="12">
         <v>9.5261833390841127E-2</v>
       </c>
       <c r="R39" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
@@ -3376,13 +3475,13 @@
         <v>182</v>
       </c>
       <c r="E40">
-        <v>8.01</v>
+        <v>8.18</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>18873401344</v>
+        <v>19273961472</v>
       </c>
       <c r="H40" s="6">
         <v>11.68</v>
@@ -3392,7 +3491,7 @@
       </c>
       <c r="J40" s="12">
         <f t="shared" si="1"/>
-        <v>0.5433526011560692</v>
+        <v>0.57610789980732169</v>
       </c>
       <c r="K40" s="11">
         <v>0</v>
@@ -3410,13 +3509,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.122132471770363</v>
+        <v>0.12171940299349211</v>
       </c>
       <c r="Q40" s="12">
         <v>6.4862080854845933E-2</v>
       </c>
       <c r="R40" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
@@ -3430,13 +3529,13 @@
         <v>98</v>
       </c>
       <c r="E41">
-        <v>9.67</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>295882653696</v>
+        <v>284255420416</v>
       </c>
       <c r="H41" s="6">
         <v>11.56</v>
@@ -3446,7 +3545,7 @@
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
-        <v>0.64455782312925169</v>
+        <v>0.57993197278911546</v>
       </c>
       <c r="K41" s="11">
         <v>0</v>
@@ -3464,13 +3563,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>9.3653995073074411E-2</v>
+        <v>9.7328961612878989E-2</v>
       </c>
       <c r="Q41" s="12">
         <v>7.4329031387590908E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
@@ -3484,13 +3583,13 @@
         <v>104</v>
       </c>
       <c r="E42">
-        <v>8.4700000000000006</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>26426400768</v>
+        <v>30576001024</v>
       </c>
       <c r="H42" s="6">
         <v>10.1</v>
@@ -3500,10 +3599,10 @@
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
-        <v>0.51250000000000018</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="K42" s="11">
-        <v>3.7780401416765051E-2</v>
+        <v>3.2653061224489792E-2</v>
       </c>
       <c r="L42" s="13">
         <v>1990539000</v>
@@ -3518,13 +3617,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="12">
-        <v>6.8216437993046053E-2</v>
+        <v>5.9723296140694736E-2</v>
       </c>
       <c r="Q42" s="12">
         <v>0.10689920561026972</v>
       </c>
       <c r="R42" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
@@ -3538,13 +3637,13 @@
         <v>152</v>
       </c>
       <c r="E43">
-        <v>31.9</v>
+        <v>32.950000000000003</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>111642984448</v>
+        <v>115317760000</v>
       </c>
       <c r="H43" s="6">
         <v>37.25</v>
@@ -3554,10 +3653,10 @@
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
-        <v>0.13523131672597843</v>
+        <v>0.17259786476868322</v>
       </c>
       <c r="K43" s="11">
-        <v>5.454545454545455E-2</v>
+        <v>5.2807283763277688E-2</v>
       </c>
       <c r="L43" s="13">
         <v>16863000000</v>
@@ -3572,13 +3671,13 @@
         <v>1</v>
       </c>
       <c r="P43" s="12">
-        <v>0.12659341147381301</v>
+        <v>0.12319481569213964</v>
       </c>
       <c r="Q43" s="12">
         <v>3.7613758029978586E-2</v>
       </c>
       <c r="R43" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
@@ -3598,7 +3697,7 @@
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>137104433152</v>
+        <v>137381412864</v>
       </c>
       <c r="H44" s="6">
         <v>82.25</v>
@@ -3626,13 +3725,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>6.4361071109758666E-2</v>
+        <v>6.4192410583388496E-2</v>
       </c>
       <c r="Q44" s="12">
         <v>0.10968970241604512</v>
       </c>
       <c r="R44" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
@@ -3646,13 +3745,13 @@
         <v>152</v>
       </c>
       <c r="E45">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>6086522880</v>
+        <v>6015335424</v>
       </c>
       <c r="H45" s="6">
         <v>2.95</v>
@@ -3662,10 +3761,10 @@
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
-        <v>0.24817518248175174</v>
+        <v>0.23357664233576636</v>
       </c>
       <c r="K45" s="11">
-        <v>5.4970760233918128E-2</v>
+        <v>5.562130177514793E-2</v>
       </c>
       <c r="L45" s="13">
         <v>2220197000</v>
@@ -3680,13 +3779,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>0.12244255356679254</v>
+        <v>0.12289415093467723</v>
       </c>
       <c r="Q45" s="12">
         <v>3.1227495254580313E-2</v>
       </c>
       <c r="R45" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
@@ -3700,13 +3799,13 @@
         <v>172</v>
       </c>
       <c r="E46">
-        <v>22.05</v>
+        <v>24</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>24438235136</v>
+        <v>26599440384</v>
       </c>
       <c r="H46" s="6">
         <v>24.55</v>
@@ -3716,10 +3815,10 @@
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
-        <v>0.51859504132231415</v>
+        <v>0.65289256198347112</v>
       </c>
       <c r="K46" s="11">
-        <v>4.2630385487528344E-2</v>
+        <v>3.9166666666666662E-2</v>
       </c>
       <c r="L46" s="13">
         <v>3838344000</v>
@@ -3734,13 +3833,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>9.0835070261810882E-2</v>
+        <v>8.6415332705047476E-2</v>
       </c>
       <c r="Q46" s="12">
         <v>4.7084186647510511E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
@@ -3754,26 +3853,26 @@
         <v>98</v>
       </c>
       <c r="E47">
-        <v>11.36</v>
+        <v>11.5</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>86056083456</v>
+        <v>87116636160</v>
       </c>
       <c r="H47" s="6">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="I47" s="6">
-        <v>8.48</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
-        <v>0.33962264150943389</v>
+        <v>0.34660421545667464</v>
       </c>
       <c r="K47" s="11">
-        <v>6.9366197183098596E-2</v>
+        <v>6.8521739130434786E-2</v>
       </c>
       <c r="L47" s="13">
         <v>8154000000</v>
@@ -3788,13 +3887,13 @@
         <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>6.4020685879869976E-2</v>
+        <v>6.3491996176225127E-2</v>
       </c>
       <c r="Q47" s="12">
         <v>0.10245263104990703</v>
       </c>
       <c r="R47" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
@@ -3808,13 +3907,13 @@
         <v>98</v>
       </c>
       <c r="E48">
-        <v>5.96</v>
+        <v>5.76</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>754577702912</v>
+        <v>760584994816</v>
       </c>
       <c r="H48" s="6">
         <v>6.98</v>
@@ -3824,10 +3923,10 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
-        <v>0.46078431372549011</v>
+        <v>0.41176470588235281</v>
       </c>
       <c r="K48" s="11">
-        <v>4.3624161073825503E-2</v>
+        <v>4.5138888888888895E-2</v>
       </c>
       <c r="L48" s="13">
         <v>44563000000</v>
@@ -3842,13 +3941,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>6.5072504456515662E-2</v>
+        <v>6.4542567843163007E-2</v>
       </c>
       <c r="Q48" s="12">
         <v>9.605709580489824E-2</v>
       </c>
       <c r="R48" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
@@ -3862,13 +3961,13 @@
         <v>93</v>
       </c>
       <c r="E49">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>7975293952</v>
+        <v>7483666432</v>
       </c>
       <c r="H49" s="6">
         <v>1.82</v>
@@ -3878,10 +3977,10 @@
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
-        <v>0.80246913580246892</v>
+        <v>0.69135802469135799</v>
       </c>
       <c r="K49" s="11">
-        <v>2.3287671232876714E-2</v>
+        <v>2.4817518248175182E-2</v>
       </c>
       <c r="L49" s="13">
         <v>1384865000</v>
@@ -3896,13 +3995,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>7.7509454513107826E-2</v>
+        <v>7.9558472213253753E-2</v>
       </c>
       <c r="Q49" s="12">
         <v>5.8120488088461209E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
@@ -3916,13 +4015,13 @@
         <v>87</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>3556699904</v>
+        <v>3485154560</v>
       </c>
       <c r="H50" s="6">
         <v>2.73</v>
@@ -3932,10 +4031,10 @@
       </c>
       <c r="J50" s="12">
         <f t="shared" si="1"/>
-        <v>0.11731843575418988</v>
+        <v>9.4972067039106101E-2</v>
       </c>
       <c r="K50" s="11">
-        <v>2.8000000000000001E-2</v>
+        <v>2.8571428571428574E-2</v>
       </c>
       <c r="L50" s="13">
         <v>364157000</v>
@@ -3950,13 +4049,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>8.3392871887460709E-2</v>
+        <v>8.469165949285995E-2</v>
       </c>
       <c r="Q50" s="12">
         <v>4.6334433386514377E-2</v>
       </c>
       <c r="R50" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -3970,13 +4069,13 @@
         <v>98</v>
       </c>
       <c r="E51">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>39789047808</v>
+        <v>40253509632</v>
       </c>
       <c r="H51" s="6">
         <v>5.49</v>
@@ -3986,10 +4085,10 @@
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
-        <v>0.35263157894736841</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K51" s="11">
-        <v>7.4513618677042814E-2</v>
+        <v>7.3653846153846153E-2</v>
       </c>
       <c r="L51" s="13">
         <v>5474000000</v>
@@ -4004,13 +4103,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="12">
-        <v>5.986305131194903E-2</v>
+        <v>5.9560525385179718E-2</v>
       </c>
       <c r="Q51" s="12">
         <v>9.2144023431582137E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
@@ -4024,13 +4123,13 @@
         <v>190</v>
       </c>
       <c r="E52">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>9105399808</v>
+        <v>9577849856</v>
       </c>
       <c r="H52" s="6">
         <v>3.04</v>
@@ -4040,10 +4139,10 @@
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
-        <v>9.8445595854922407E-2</v>
+        <v>0.15544041450777213</v>
       </c>
       <c r="K52" s="11">
-        <v>5.0471698113207543E-2</v>
+        <v>4.7982062780269057E-2</v>
       </c>
       <c r="L52" s="13">
         <v>1938532000</v>
@@ -4058,13 +4157,13 @@
         <v>1</v>
       </c>
       <c r="P52" s="12">
-        <v>6.5415965529776049E-2</v>
+        <v>6.4389413076261628E-2</v>
       </c>
       <c r="Q52" s="12">
         <v>3.8781191586606881E-2</v>
       </c>
       <c r="R52" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
@@ -4078,26 +4177,26 @@
         <v>98</v>
       </c>
       <c r="E53">
-        <v>11.72</v>
+        <v>11.42</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>206281392128</v>
+        <v>201001140224</v>
       </c>
       <c r="H53" s="6">
         <v>12.46</v>
       </c>
       <c r="I53" s="6">
-        <v>9.1</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J53" s="12">
         <f t="shared" si="1"/>
-        <v>0.287912087912088</v>
+        <v>0.24130434782608701</v>
       </c>
       <c r="K53" s="11">
-        <v>3.5580204778156994E-2</v>
+        <v>3.6514886164623464E-2</v>
       </c>
       <c r="L53" s="13">
         <v>16758000000</v>
@@ -4112,13 +4211,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>5.9210027773688667E-2</v>
+        <v>6.0262352193499312E-2</v>
       </c>
       <c r="Q53" s="12">
         <v>6.2161059386475759E-2</v>
       </c>
       <c r="R53" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
@@ -4132,23 +4231,23 @@
         <v>87</v>
       </c>
       <c r="E54">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>7148248576</v>
+        <v>7304779776</v>
       </c>
       <c r="H54" s="6">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="I54" s="6">
         <v>4.0199999999999996</v>
       </c>
       <c r="J54" s="12">
         <f t="shared" si="1"/>
-        <v>0.70398009950248763</v>
+        <v>0.74129353233830875</v>
       </c>
       <c r="K54" s="11">
         <v>0</v>
@@ -4166,13 +4265,13 @@
         <v>1</v>
       </c>
       <c r="P54" s="12">
-        <v>5.0102476266993719E-2</v>
+        <v>4.8839744900169083E-2</v>
       </c>
       <c r="Q54" s="12">
         <v>8.3790449156695201E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
@@ -4186,13 +4285,13 @@
         <v>154</v>
       </c>
       <c r="E55">
-        <v>12.68</v>
+        <v>14.04</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>13022486528</v>
+        <v>14419220480</v>
       </c>
       <c r="H55" s="6">
         <v>14.5</v>
@@ -4202,10 +4301,10 @@
       </c>
       <c r="J55" s="12">
         <f t="shared" si="1"/>
-        <v>0.22393822393822393</v>
+        <v>0.35521235521235517</v>
       </c>
       <c r="K55" s="11">
-        <v>8.5173501577287078E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="L55" s="13">
         <v>984000000</v>
@@ -4220,13 +4319,13 @@
         <v>1</v>
       </c>
       <c r="P55" s="12">
-        <v>2.59134992193472E-2</v>
+        <v>2.4994144867559236E-2</v>
       </c>
       <c r="Q55" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R55" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
@@ -4240,13 +4339,13 @@
         <v>199</v>
       </c>
       <c r="E56">
-        <v>40.799999999999997</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>419697328128</v>
+        <v>424905965568</v>
       </c>
       <c r="H56" s="6">
         <v>59.7</v>
@@ -4256,7 +4355,7 @@
       </c>
       <c r="J56" s="12">
         <f t="shared" si="1"/>
-        <v>1.6771653543307083</v>
+        <v>1.6377952755905514</v>
       </c>
       <c r="K56" s="11">
         <v>0</v>
@@ -4274,13 +4373,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P56" s="12">
-        <v>1.6457375883070016E-2</v>
+        <v>1.6273090414324575E-2</v>
       </c>
       <c r="Q56" s="12">
         <v>3.0575487595734537E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
@@ -4294,13 +4393,13 @@
         <v>175</v>
       </c>
       <c r="E57">
-        <v>27.1</v>
+        <v>29.1</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>27676958720</v>
+        <v>29713719296</v>
       </c>
       <c r="H57" s="6">
         <v>36</v>
@@ -4310,7 +4409,7 @@
       </c>
       <c r="J57" s="12">
         <f t="shared" si="1"/>
-        <v>0.2098214285714286</v>
+        <v>0.29910714285714302</v>
       </c>
       <c r="K57" s="11">
         <v>0</v>
@@ -4328,68 +4427,535 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>-3.9598102780594776E-3</v>
+        <v>-3.6543561486810142E-3</v>
       </c>
       <c r="Q57" s="12">
         <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R57" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="C58" t="s">
+        <v>223</v>
+      </c>
+      <c r="D58" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58">
+        <v>6.35</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G58" s="7">
+        <v>24777953280</v>
+      </c>
+      <c r="H58" s="6">
+        <v>7.28</v>
+      </c>
+      <c r="I58" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="1"/>
+        <v>0.50473933649289093</v>
+      </c>
+      <c r="K58" s="11">
+        <v>6.7716535433070867E-3</v>
+      </c>
+      <c r="L58" s="13">
+        <v>786762000</v>
+      </c>
+      <c r="M58" s="13">
+        <v>2279244000</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O58" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P58" s="12">
+        <v>0.34963394018564992</v>
+      </c>
+      <c r="Q58" s="12">
+        <v>0.34518550887925997</v>
+      </c>
+      <c r="R58" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="C59" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59">
+        <v>127.7</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" s="7">
+        <v>84329627648</v>
+      </c>
+      <c r="H59" s="6">
+        <v>149.5</v>
+      </c>
+      <c r="I59" s="6">
+        <v>91</v>
+      </c>
+      <c r="J59" s="12">
+        <f t="shared" si="1"/>
+        <v>0.40329670329670342</v>
+      </c>
+      <c r="K59" s="11">
+        <v>1.5270164447924823E-2</v>
+      </c>
+      <c r="L59" s="13">
+        <v>2635100000</v>
+      </c>
+      <c r="M59" s="13">
+        <v>13245550000</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O59" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P59" s="12">
+        <v>0.59448158016822761</v>
+      </c>
+      <c r="Q59" s="12">
+        <v>0.19894228627727803</v>
+      </c>
+      <c r="R59" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="C60" t="s">
+        <v>226</v>
+      </c>
+      <c r="D60" t="s">
+        <v>227</v>
+      </c>
+      <c r="E60">
+        <v>1.64</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60" s="7">
+        <v>1640000000</v>
+      </c>
+      <c r="H60" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="I60" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="J60" s="12">
+        <f t="shared" si="1"/>
+        <v>0.21481481481481457</v>
+      </c>
+      <c r="K60" s="11">
+        <v>0.12804878048780488</v>
+      </c>
+      <c r="L60" s="13">
+        <v>315190000</v>
+      </c>
+      <c r="M60" s="13">
+        <v>607806000</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O60" s="6">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12">
+        <v>0.1742687749876565</v>
+      </c>
+      <c r="Q60" s="12">
+        <v>0.51857007005524791</v>
+      </c>
+      <c r="R60" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="C61" t="s">
+        <v>228</v>
+      </c>
+      <c r="D61" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61">
+        <v>15.8</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="7">
+        <v>143318171648</v>
+      </c>
+      <c r="H61" s="6">
+        <v>17.88</v>
+      </c>
+      <c r="I61" s="6">
+        <v>10.6</v>
+      </c>
+      <c r="J61" s="12">
+        <f t="shared" si="1"/>
+        <v>0.49056603773584917</v>
+      </c>
+      <c r="K61" s="11">
+        <v>4.5506329113924049E-2</v>
+      </c>
+      <c r="L61" s="13">
+        <v>21175963859.630001</v>
+      </c>
+      <c r="M61" s="13">
+        <v>104071284594.97</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O61" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P61" s="12">
+        <v>0.20107063130825906</v>
+      </c>
+      <c r="Q61" s="12">
+        <v>0.20347556909712136</v>
+      </c>
+      <c r="R61" s="14">
+        <v>6</v>
+      </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
         <v>205</v>
       </c>
+      <c r="C62" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62" t="s">
+        <v>231</v>
+      </c>
+      <c r="E62">
+        <v>0.69</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1643724928</v>
+      </c>
+      <c r="H62" s="6">
+        <v>1.03</v>
+      </c>
+      <c r="I62" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J62" s="12">
+        <f t="shared" si="1"/>
+        <v>0.25454545454545441</v>
+      </c>
+      <c r="K62" s="11">
+        <v>1.4492753623188408E-2</v>
+      </c>
+      <c r="L62" s="13">
+        <v>54195000</v>
+      </c>
+      <c r="M62" s="13">
+        <v>586711000</v>
+      </c>
+      <c r="N62" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O62" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P62" s="12">
+        <v>1.2095413323209785</v>
+      </c>
+      <c r="Q62" s="12">
+        <v>9.2370860611101543E-2</v>
+      </c>
+      <c r="R62" s="14">
+        <v>15</v>
+      </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
         <v>206</v>
       </c>
+      <c r="C63" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" t="s">
+        <v>233</v>
+      </c>
+      <c r="E63">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63" s="7">
+        <v>361589768192</v>
+      </c>
+      <c r="H63" s="6">
+        <v>34.6</v>
+      </c>
+      <c r="I63" s="6">
+        <v>21.5</v>
+      </c>
+      <c r="J63" s="12">
+        <f t="shared" si="1"/>
+        <v>0.59069767441860477</v>
+      </c>
+      <c r="K63" s="11">
+        <v>5.8157894736842103E-2</v>
+      </c>
+      <c r="M63" s="13">
+        <v>415994000000</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O63" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64">
+        <v>7.07</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G64" s="7">
+        <v>577521451008</v>
+      </c>
+      <c r="H64" s="6">
+        <v>7.27</v>
+      </c>
+      <c r="I64" s="6">
+        <v>5.08</v>
+      </c>
+      <c r="J64" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3917322834645669</v>
+      </c>
+      <c r="K64" s="11">
+        <v>5.3606789250353608E-2</v>
+      </c>
+      <c r="M64" s="13">
+        <v>2314289000000</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O64" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="C65" t="s">
+        <v>236</v>
+      </c>
+      <c r="D65" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65">
+        <v>5.88</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="7">
+        <v>2603111415808</v>
+      </c>
+      <c r="H65" s="6">
+        <v>5.97</v>
+      </c>
+      <c r="I65" s="6">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="J65" s="12">
+        <f t="shared" si="1"/>
+        <v>0.44827586206896552</v>
+      </c>
+      <c r="K65" s="11">
+        <v>5.2380952380952382E-2</v>
+      </c>
+      <c r="M65" s="13">
+        <v>6434377000000</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O65" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="C66" t="s">
+        <v>237</v>
+      </c>
+      <c r="D66" t="s">
+        <v>233</v>
+      </c>
+      <c r="E66">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="7">
+        <v>566177759232</v>
+      </c>
+      <c r="H66" s="6">
+        <v>5.39</v>
+      </c>
+      <c r="I66" s="6">
+        <v>3.89</v>
+      </c>
+      <c r="J66" s="12">
+        <f t="shared" ref="J66:J68" si="2">E66/I66-1</f>
+        <v>0.31362467866323906</v>
+      </c>
+      <c r="K66" s="11">
+        <v>0</v>
+      </c>
+      <c r="M66" s="13">
+        <v>1271649000000</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="C67" t="s">
+        <v>238</v>
+      </c>
+      <c r="D67" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67">
+        <v>7.28</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G67" s="7">
+        <v>1844635631616</v>
+      </c>
+      <c r="H67" s="6">
+        <v>7.32</v>
+      </c>
+      <c r="I67" s="6">
+        <v>5.23</v>
+      </c>
+      <c r="J67" s="12">
+        <f t="shared" si="2"/>
+        <v>0.39196940726577423</v>
+      </c>
+      <c r="K67" s="11">
+        <v>5.5357142857142862E-2</v>
+      </c>
+      <c r="M67" s="13">
+        <v>6128626000000</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O67" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
         <v>211</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" t="s">
+        <v>233</v>
+      </c>
+      <c r="E68">
+        <v>7.21</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G68" s="7">
+        <v>482087305216</v>
+      </c>
+      <c r="H68" s="6">
+        <v>7.3</v>
+      </c>
+      <c r="I68" s="6">
+        <v>4.26</v>
+      </c>
+      <c r="J68" s="12">
+        <f t="shared" si="2"/>
+        <v>0.69248826291079824</v>
+      </c>
+      <c r="K68" s="11">
+        <v>4.9237170596393896E-2</v>
+      </c>
+      <c r="M68" s="13">
+        <v>2066897000000</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O68" s="6">
+        <v>1.0683760683760684</v>
       </c>
     </row>
   </sheetData>
@@ -4501,13 +5067,13 @@
         <v>59</v>
       </c>
       <c r="E2">
-        <v>128.15</v>
+        <v>125.09</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="7">
-        <v>497428299776</v>
+        <v>485550587904</v>
       </c>
       <c r="H2" s="6">
         <v>178.76</v>
@@ -4517,10 +5083,10 @@
       </c>
       <c r="J2" s="12">
         <f t="shared" ref="J2:J11" si="0">E2/I2-1</f>
-        <v>0.20521019467694912</v>
+        <v>0.17643186306780789</v>
       </c>
       <c r="K2" s="11">
-        <v>4.4830277019118223E-2</v>
+        <v>4.5926932608521862E-2</v>
       </c>
       <c r="L2" s="13">
         <v>44203762134.690002</v>
@@ -4535,13 +5101,13 @@
         <v>1</v>
       </c>
       <c r="P2" s="12">
-        <v>0.11920159066804709</v>
+        <v>0.12314594309994076</v>
       </c>
       <c r="Q2" s="12">
         <v>0.33164773684009302</v>
       </c>
       <c r="R2" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
@@ -4555,13 +5121,13 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="7">
-        <v>14667599872</v>
+        <v>14978208768</v>
       </c>
       <c r="H3" s="6">
         <v>9.76</v>
@@ -4571,7 +5137,7 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.20396600566572243</v>
+        <v>0.22946175637393762</v>
       </c>
       <c r="K3" s="11">
         <v>0</v>
@@ -4589,13 +5155,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12">
-        <v>0.19930343721694993</v>
+        <v>0.19160856410336488</v>
       </c>
       <c r="Q3" s="12">
         <v>0.1287769864044232</v>
       </c>
       <c r="R3" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
@@ -4609,13 +5175,13 @@
         <v>61</v>
       </c>
       <c r="E4">
-        <v>12.28</v>
+        <v>13.16</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G4" s="7">
-        <v>12564895744</v>
+        <v>13465312256</v>
       </c>
       <c r="H4" s="6">
         <v>13.58</v>
@@ -4625,10 +5191,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.33769063180827885</v>
+        <v>0.43355119825708077</v>
       </c>
       <c r="K4" s="11">
-        <v>4.8859934853420196E-2</v>
+        <v>4.5592705167173252E-2</v>
       </c>
       <c r="L4" s="13">
         <v>1324661161.8800001</v>
@@ -4643,13 +5209,13 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>0.17844935968956624</v>
+        <v>0.15914534730349833</v>
       </c>
       <c r="Q4" s="12">
         <v>0.11527544475940803</v>
       </c>
       <c r="R4" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
@@ -4663,13 +5229,13 @@
         <v>61</v>
       </c>
       <c r="E5">
-        <v>13.89</v>
+        <v>13.84</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G5" s="7">
-        <v>24946440192</v>
+        <v>24856639488</v>
       </c>
       <c r="H5" s="6">
         <v>15.58</v>
@@ -4679,10 +5245,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.2109851787271142</v>
+        <v>0.20662598081952921</v>
       </c>
       <c r="K5" s="11">
-        <v>3.9596832253419728E-2</v>
+        <v>3.9739884393063585E-2</v>
       </c>
       <c r="L5" s="13">
         <v>1789808265.4000001</v>
@@ -4697,13 +5263,13 @@
         <v>1</v>
       </c>
       <c r="P5" s="12">
-        <v>0.14270391389248785</v>
+        <v>0.14373303315463123</v>
       </c>
       <c r="Q5" s="12">
         <v>0.11487361117809598</v>
       </c>
       <c r="R5" s="14">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -4717,13 +5283,13 @@
         <v>56</v>
       </c>
       <c r="E6">
-        <v>104.24</v>
+        <v>105.42</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G6" s="7">
-        <v>55394283520</v>
+        <v>56034734080</v>
       </c>
       <c r="H6" s="6">
         <v>121.53</v>
@@ -4733,10 +5299,10 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>1.0760804620593505</v>
+        <v>1.0995817566221868</v>
       </c>
       <c r="K6" s="11">
-        <v>2.0145817344589412E-2</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2351242906.4000001</v>
@@ -4751,13 +5317,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>4.3143262796750632E-2</v>
+        <v>4.264214464208986E-2</v>
       </c>
       <c r="Q6" s="12">
         <v>0.22747360748931247</v>
       </c>
       <c r="R6" s="14">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
@@ -4771,13 +5337,13 @@
         <v>50</v>
       </c>
       <c r="E7">
-        <v>243.01</v>
+        <v>222.7</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G7" s="7">
-        <v>44889538560</v>
+        <v>41166761984</v>
       </c>
       <c r="H7" s="6">
         <v>333.5</v>
@@ -4787,10 +5353,10 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>0.40468208092485547</v>
+        <v>0.28728323699421954</v>
       </c>
       <c r="K7" s="11">
-        <v>4.4031109830871161E-3</v>
+        <v>4.8046699595868884E-3</v>
       </c>
       <c r="L7" s="13">
         <v>2107869808</v>
@@ -4805,13 +5371,13 @@
         <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>4.8320112585649305E-2</v>
+        <v>5.2828479318259083E-2</v>
       </c>
       <c r="Q7" s="12">
         <v>0.16379150253744434</v>
       </c>
       <c r="R7" s="14">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
@@ -4825,13 +5391,13 @@
         <v>61</v>
       </c>
       <c r="E8">
-        <v>9.3800000000000008</v>
+        <v>9.74</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G8" s="7">
-        <v>11384037376</v>
+        <v>11820951552</v>
       </c>
       <c r="H8" s="6">
         <v>10.27</v>
@@ -4841,10 +5407,10 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.24403183023872699</v>
+        <v>0.29177718832891242</v>
       </c>
       <c r="K8" s="11">
-        <v>4.2643923240938165E-2</v>
+        <v>4.1067761806981518E-2</v>
       </c>
       <c r="L8" s="13">
         <v>1074859531.29</v>
@@ -4859,13 +5425,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.11054322414135855</v>
+        <v>0.10578965566101749</v>
       </c>
       <c r="Q8" s="12">
         <v>0.1128187617835559</v>
       </c>
       <c r="R8" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
@@ -4879,13 +5445,13 @@
         <v>66</v>
       </c>
       <c r="E9">
-        <v>12.53</v>
+        <v>13.02</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="7">
-        <v>4429643264</v>
+        <v>4602869760</v>
       </c>
       <c r="H9" s="6">
         <v>14.68</v>
@@ -4895,10 +5461,10 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.28776978417266186</v>
+        <v>0.33812949640287759</v>
       </c>
       <c r="K9" s="11">
-        <v>3.830806065442937E-2</v>
+        <v>3.6866359447004608E-2</v>
       </c>
       <c r="L9" s="13">
         <v>339663210.94999999</v>
@@ -4913,13 +5479,13 @@
         <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>9.6853042007053705E-2</v>
+        <v>9.2294210563736004E-2</v>
       </c>
       <c r="Q9" s="12">
         <v>0.12344330708657501</v>
       </c>
       <c r="R9" s="14">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -4933,13 +5499,13 @@
         <v>61</v>
       </c>
       <c r="E10">
-        <v>8.0299999999999994</v>
+        <v>8.26</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="7">
-        <v>17844426752</v>
+        <v>18355537920</v>
       </c>
       <c r="H10" s="6">
         <v>10.53</v>
@@ -4949,10 +5515,10 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>0.12307692307692286</v>
+        <v>0.15524475524475512</v>
       </c>
       <c r="K10" s="11">
-        <v>3.7359900373599007E-2</v>
+        <v>3.6319612590799029E-2</v>
       </c>
       <c r="L10" s="13">
         <v>1357643494.6700001</v>
@@ -4967,13 +5533,13 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.11452436086299177</v>
+        <v>0.10979074265151259</v>
       </c>
       <c r="Q10" s="12">
         <v>9.9124832291360196E-2</v>
       </c>
       <c r="R10" s="14">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -4987,13 +5553,13 @@
         <v>54</v>
       </c>
       <c r="E11">
-        <v>57.36</v>
+        <v>53.03</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="7">
-        <v>32998920192</v>
+        <v>30507945984</v>
       </c>
       <c r="H11" s="6">
         <v>68.39</v>
@@ -5003,10 +5569,10 @@
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.58234482758620687</v>
+        <v>0.46289655172413791</v>
       </c>
       <c r="K11" s="11">
-        <v>7.8451882845188281E-3</v>
+        <v>8.4857627757872894E-3</v>
       </c>
       <c r="L11" s="13">
         <v>939613185.05999994</v>
@@ -5021,13 +5587,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>3.1437021734972918E-2</v>
+        <v>3.4295239856469741E-2</v>
       </c>
       <c r="Q11" s="12">
         <v>0.10362091390188061</v>
       </c>
       <c r="R11" s="14">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5129,26 +5695,26 @@
         <v>109</v>
       </c>
       <c r="E2">
-        <v>63.07</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G2" s="7">
-        <v>2609899776</v>
+        <v>3196547584</v>
       </c>
       <c r="H2" s="6">
-        <v>112.06</v>
+        <v>109.52</v>
       </c>
       <c r="I2" s="6">
         <v>45.55</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J4" si="0">E2/I2-1</f>
-        <v>0.38463227222832064</v>
+        <f t="shared" ref="J2:J15" si="0">E2/I2-1</f>
+        <v>0.70537870472008812</v>
       </c>
       <c r="K2" s="11">
-        <v>1.8392262565403519E-2</v>
+        <v>1.5319258496395467E-2</v>
       </c>
       <c r="L2" s="13">
         <v>503000000</v>
@@ -5163,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="12">
-        <v>0.15788813967196411</v>
+        <v>0.13333518592368598</v>
       </c>
       <c r="Q2" s="12">
         <v>0.27162760557295607</v>
@@ -5183,13 +5749,13 @@
         <v>107</v>
       </c>
       <c r="E3">
-        <v>206.61</v>
+        <v>211.83</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="7">
-        <v>87313793024</v>
+        <v>89519775744</v>
       </c>
       <c r="H3" s="6">
         <v>236.53</v>
@@ -5199,10 +5765,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.99257401870961548</v>
+        <v>1.0429163853794967</v>
       </c>
       <c r="K3" s="11">
-        <v>4.8400367842795604E-3</v>
+        <v>4.720766652504366E-3</v>
       </c>
       <c r="L3" s="13">
         <v>7886000000</v>
@@ -5217,13 +5783,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12">
-        <v>9.42233048803722E-2</v>
+        <v>9.1803594690480092E-2</v>
       </c>
       <c r="Q3" s="12">
         <v>1.8365160689333955</v>
       </c>
       <c r="R3" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
@@ -5237,13 +5803,13 @@
         <v>87</v>
       </c>
       <c r="E4">
-        <v>164</v>
+        <v>167.93</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="7">
-        <v>4521332224</v>
+        <v>4629678592</v>
       </c>
       <c r="H4" s="6">
         <v>202.63</v>
@@ -5253,10 +5819,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>5.0339438965031569E-2</v>
+        <v>7.5509158447547131E-2</v>
       </c>
       <c r="K4" s="11">
-        <v>2.25609756097561E-2</v>
+        <v>2.2032989936282974E-2</v>
       </c>
       <c r="L4" s="13">
         <v>214237000</v>
@@ -5271,68 +5837,607 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>4.8518689182475233E-2</v>
+        <v>4.7356678364130433E-2</v>
       </c>
       <c r="Q4" s="12">
         <v>0.23141443033489886</v>
       </c>
       <c r="R4" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>212</v>
       </c>
+      <c r="C5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5">
+        <v>24.52</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="7">
+        <v>66273640448</v>
+      </c>
+      <c r="H5" s="6">
+        <v>29.03</v>
+      </c>
+      <c r="I5" s="6">
+        <v>21.41</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="0"/>
+        <v>0.14525922466137309</v>
+      </c>
+      <c r="K5" s="11">
+        <v>5.872756933115824E-2</v>
+      </c>
+      <c r="L5" s="13">
+        <v>32043000000</v>
+      </c>
+      <c r="M5" s="13">
+        <v>68927000000</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="6">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0.35420077546920636</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0.46488313723214414</v>
+      </c>
+      <c r="R5" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>213</v>
       </c>
+      <c r="C6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6">
+        <v>25.72</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="7">
+        <v>915956032</v>
+      </c>
+      <c r="H6" s="6">
+        <v>30.19</v>
+      </c>
+      <c r="I6" s="6">
+        <v>17.73</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="0"/>
+        <v>0.45064861816130852</v>
+      </c>
+      <c r="K6" s="11">
+        <v>7.2900466562986002E-2</v>
+      </c>
+      <c r="L6" s="13">
+        <v>394305000</v>
+      </c>
+      <c r="M6" s="13">
+        <v>2138821000</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="6">
+        <v>1</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0.27032409093251997</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0.18435624112536766</v>
+      </c>
+      <c r="R6" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="C7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7">
+        <v>18.55</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="7">
+        <v>478500928</v>
+      </c>
+      <c r="H7" s="6">
+        <v>25.75</v>
+      </c>
+      <c r="I7" s="6">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="0"/>
+        <v>8.163265306122458E-2</v>
+      </c>
+      <c r="K7" s="11">
+        <v>5.3908355795148244E-2</v>
+      </c>
+      <c r="L7" s="13">
+        <v>51916000</v>
+      </c>
+      <c r="M7" s="13">
+        <v>301980000</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="6">
+        <v>1</v>
+      </c>
+      <c r="P7" s="12">
+        <v>0.12332267292330092</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0.17191867011060336</v>
+      </c>
+      <c r="R7" s="14">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>215</v>
       </c>
+      <c r="C8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8">
+        <v>68.31</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2298740736</v>
+      </c>
+      <c r="H8" s="6">
+        <v>153.32</v>
+      </c>
+      <c r="I8" s="6">
+        <v>49.92</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="0"/>
+        <v>0.36838942307692313</v>
+      </c>
+      <c r="K8" s="11">
+        <v>1.8884497145366712E-2</v>
+      </c>
+      <c r="L8" s="13">
+        <v>622821000</v>
+      </c>
+      <c r="M8" s="13">
+        <v>2304738000</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0.21487257697834797</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0.27023505491730515</v>
+      </c>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>216</v>
       </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="7">
+        <v>10533276672</v>
+      </c>
+      <c r="H9" s="6">
+        <v>64.66</v>
+      </c>
+      <c r="I9" s="6">
+        <v>49.19</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
+        <v>5.712543199837361E-2</v>
+      </c>
+      <c r="K9" s="11">
+        <v>3.4423076923076924E-2</v>
+      </c>
+      <c r="L9" s="13">
+        <v>1785700000</v>
+      </c>
+      <c r="M9" s="13">
+        <v>19238500000</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="6">
+        <v>1</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0.11332901628117967</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>9.2819086727135694E-2</v>
+      </c>
+      <c r="R9" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>217</v>
       </c>
+      <c r="C10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="7">
+        <v>3126766336</v>
+      </c>
+      <c r="H10" s="6">
+        <v>13.12</v>
+      </c>
+      <c r="I10" s="6">
+        <v>9</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>5.1111111111111107E-2</v>
+      </c>
+      <c r="K10" s="11">
+        <v>9.9365750528541213E-2</v>
+      </c>
+      <c r="L10" s="13">
+        <v>738400000</v>
+      </c>
+      <c r="M10" s="13">
+        <v>3909700000</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="6">
+        <v>1</v>
+      </c>
+      <c r="P10" s="12">
+        <v>0.17779206038522605</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0.18886359567230221</v>
+      </c>
+      <c r="R10" s="14">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>218</v>
       </c>
+      <c r="C11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11">
+        <v>62.17</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="7">
+        <v>723714752</v>
+      </c>
+      <c r="H11" s="6">
+        <v>105.63</v>
+      </c>
+      <c r="I11" s="6">
+        <v>58.47</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="0"/>
+        <v>6.3280314691294803E-2</v>
+      </c>
+      <c r="K11" s="11">
+        <v>1.3672189158758242E-2</v>
+      </c>
+      <c r="L11" s="13">
+        <v>82486000</v>
+      </c>
+      <c r="M11" s="13">
+        <v>350680000</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="6">
+        <v>1</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0.10627245963290494</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0.23521729211817041</v>
+      </c>
+      <c r="R11" s="14">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="C12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12">
+        <v>140.21</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="7">
+        <v>242875990016</v>
+      </c>
+      <c r="H12" s="6">
+        <v>168.96</v>
+      </c>
+      <c r="I12" s="6">
+        <v>132.04</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="0"/>
+        <v>6.1875189336564773E-2</v>
+      </c>
+      <c r="K12" s="11">
+        <v>4.7072248769702583E-2</v>
+      </c>
+      <c r="L12" s="13">
+        <v>28100000000</v>
+      </c>
+      <c r="M12" s="13">
+        <v>176255000000</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O12" s="6">
+        <v>1</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0.1078131995442187</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0.1594281013304587</v>
+      </c>
+      <c r="R12" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="C13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13">
+        <v>17.04</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2599486208</v>
+      </c>
+      <c r="H13" s="6">
+        <v>20.81</v>
+      </c>
+      <c r="I13" s="6">
+        <v>15.43</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
+        <v>0.10434219053791316</v>
+      </c>
+      <c r="K13" s="11">
+        <v>3.6208920187793425E-2</v>
+      </c>
+      <c r="L13" s="13">
+        <v>408200000</v>
+      </c>
+      <c r="M13" s="13">
+        <v>4745800000</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1.1380999999999999</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0.10058007692432981</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>8.6012895612963047E-2</v>
+      </c>
+      <c r="R13" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>221</v>
       </c>
+      <c r="C14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14">
+        <v>15.62</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="7">
+        <v>347340384</v>
+      </c>
+      <c r="H14" s="6">
+        <v>26.59</v>
+      </c>
+      <c r="I14" s="6">
+        <v>12.85</v>
+      </c>
+      <c r="J14" s="12">
+        <f t="shared" si="0"/>
+        <v>0.21556420233463025</v>
+      </c>
+      <c r="K14" s="11">
+        <v>8.9628681177976954E-2</v>
+      </c>
+      <c r="L14" s="13">
+        <v>27140000</v>
+      </c>
+      <c r="M14" s="13">
+        <v>481329000</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14" s="6">
+        <v>1</v>
+      </c>
+      <c r="P14" s="12">
+        <v>0.11617634257216922</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>5.638554917738179E-2</v>
+      </c>
+      <c r="R14" s="14">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E15">
+        <v>22.18</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="7">
+        <v>781592128</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25.04</v>
+      </c>
+      <c r="I15" s="6">
+        <v>21.19</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="0"/>
+        <v>4.6720151014629563E-2</v>
+      </c>
+      <c r="K15" s="11">
+        <v>8.5031559963931469E-2</v>
+      </c>
+      <c r="L15" s="13">
+        <v>395695000</v>
+      </c>
+      <c r="M15" s="13">
+        <v>675803000</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15" s="6">
+        <v>1</v>
+      </c>
+      <c r="P15" s="12">
+        <v>0.35237094696693422</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0.58551826493815506</v>
+      </c>
+      <c r="R15" s="14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5773E-0C24-4006-9AFD-0CC0A5C9DF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2009CB-671F-4706-B5C5-ECA04EBD870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="362">
   <si>
     <t>Ticker</t>
   </si>
@@ -867,6 +867,324 @@
   </si>
   <si>
     <t>Chemicals</t>
+  </si>
+  <si>
+    <t>0382.HK</t>
+  </si>
+  <si>
+    <t>1890.HK</t>
+  </si>
+  <si>
+    <t>3993.HK</t>
+  </si>
+  <si>
+    <t>1339.HK</t>
+  </si>
+  <si>
+    <t>0966.HK</t>
+  </si>
+  <si>
+    <t>1186.HK</t>
+  </si>
+  <si>
+    <t>0001.HK</t>
+  </si>
+  <si>
+    <t>3900.HK</t>
+  </si>
+  <si>
+    <t>1045.HK</t>
+  </si>
+  <si>
+    <t>1618.HK</t>
+  </si>
+  <si>
+    <t>0116.HK</t>
+  </si>
+  <si>
+    <t>2318.HK</t>
+  </si>
+  <si>
+    <t>0179.HK</t>
+  </si>
+  <si>
+    <t>1876.HK</t>
+  </si>
+  <si>
+    <t>3709.HK</t>
+  </si>
+  <si>
+    <t>0636.HK</t>
+  </si>
+  <si>
+    <t>0345.HK</t>
+  </si>
+  <si>
+    <t>0546.HK</t>
+  </si>
+  <si>
+    <t>1286.HK</t>
+  </si>
+  <si>
+    <t>0662.HK</t>
+  </si>
+  <si>
+    <t>2386.HK</t>
+  </si>
+  <si>
+    <t>9898.HK</t>
+  </si>
+  <si>
+    <t>3899.HK</t>
+  </si>
+  <si>
+    <t>0411.HK</t>
+  </si>
+  <si>
+    <t>0551.HK</t>
+  </si>
+  <si>
+    <t>3813.HK</t>
+  </si>
+  <si>
+    <t>6963.HK</t>
+  </si>
+  <si>
+    <t>3339.HK</t>
+  </si>
+  <si>
+    <t>1866.HK</t>
+  </si>
+  <si>
+    <t>1448.HK</t>
+  </si>
+  <si>
+    <t>1109.HK</t>
+  </si>
+  <si>
+    <t>6690.HK</t>
+  </si>
+  <si>
+    <t>1070.HK</t>
+  </si>
+  <si>
+    <t>1882.HK</t>
+  </si>
+  <si>
+    <t>0811.HK</t>
+  </si>
+  <si>
+    <t>1263.HK</t>
+  </si>
+  <si>
+    <t>0552.HK</t>
+  </si>
+  <si>
+    <t>1368.HK</t>
+  </si>
+  <si>
+    <t>0315.HK</t>
+  </si>
+  <si>
+    <t>2368.HK</t>
+  </si>
+  <si>
+    <t>1133.HK</t>
+  </si>
+  <si>
+    <t>0288.HK</t>
+  </si>
+  <si>
+    <t>3393.HK</t>
+  </si>
+  <si>
+    <t>1999.HK</t>
+  </si>
+  <si>
+    <t>1308.HK</t>
+  </si>
+  <si>
+    <t>1837.HK</t>
+  </si>
+  <si>
+    <t>0816.HK</t>
+  </si>
+  <si>
+    <t>1361.HK</t>
+  </si>
+  <si>
+    <t>EDVANTAGE GROUP</t>
+  </si>
+  <si>
+    <t>Education &amp; Training Services</t>
+  </si>
+  <si>
+    <t>CHINA KEPEI</t>
+  </si>
+  <si>
+    <t>CMOC</t>
+  </si>
+  <si>
+    <t>Other Industrial Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t>PICC GROUP</t>
+  </si>
+  <si>
+    <t>Insurance - Property &amp; Casualty</t>
+  </si>
+  <si>
+    <t>CHINA TAIPING</t>
+  </si>
+  <si>
+    <t>Insurance - Life</t>
+  </si>
+  <si>
+    <t>CHINA RAIL CONS</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>CKH HOLDINGS</t>
+  </si>
+  <si>
+    <t>GREENTOWN CHINA</t>
+  </si>
+  <si>
+    <t>APT SATELLITE</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>CHOW SANG SANG</t>
+  </si>
+  <si>
+    <t>PING AN</t>
+  </si>
+  <si>
+    <t>JOHNSON ELEC H</t>
+  </si>
+  <si>
+    <t>BUD APAC</t>
+  </si>
+  <si>
+    <t>EEKA FASHION</t>
+  </si>
+  <si>
+    <t>KLN</t>
+  </si>
+  <si>
+    <t>Integrated Freight &amp; Logistics</t>
+  </si>
+  <si>
+    <t>VITASOY INT'L</t>
+  </si>
+  <si>
+    <t>FUFENG GROUP</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>IMPRO PRECISION</t>
+  </si>
+  <si>
+    <t>ASIA FINANCIAL</t>
+  </si>
+  <si>
+    <t>SINOPEC SEG</t>
+  </si>
+  <si>
+    <t>WB-SW</t>
+  </si>
+  <si>
+    <t>CIMC ENRIC</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>LAM SOON (HK)</t>
+  </si>
+  <si>
+    <t>YUE YUEN IND</t>
+  </si>
+  <si>
+    <t>POU SHENG INT'L</t>
+  </si>
+  <si>
+    <t>SUNSHINE INS</t>
+  </si>
+  <si>
+    <t>LONKING</t>
+  </si>
+  <si>
+    <t>CHINA XLX FERT</t>
+  </si>
+  <si>
+    <t>Agricultural Inputs</t>
+  </si>
+  <si>
+    <t>FU SHOU YUAN</t>
+  </si>
+  <si>
+    <t>Personal Services</t>
+  </si>
+  <si>
+    <t>CHINA RES LAND</t>
+  </si>
+  <si>
+    <t>HAIER SMARTHOME</t>
+  </si>
+  <si>
+    <t>TCL ELECTRONICS</t>
+  </si>
+  <si>
+    <t>HAITIAN INT'L</t>
+  </si>
+  <si>
+    <t>XINHUA WINSHARE</t>
+  </si>
+  <si>
+    <t>PC PARTNER</t>
+  </si>
+  <si>
+    <t>CHINACOMSERVICE</t>
+  </si>
+  <si>
+    <t>XTEP INT'L</t>
+  </si>
+  <si>
+    <t>SMARTONE TELE</t>
+  </si>
+  <si>
+    <t>EAGLE NICE</t>
+  </si>
+  <si>
+    <t>HARBIN ELECTRIC</t>
+  </si>
+  <si>
+    <t>WH GROUP</t>
+  </si>
+  <si>
+    <t>WASION HOLDINGS</t>
+  </si>
+  <si>
+    <t>MAN WAH HLDGS</t>
+  </si>
+  <si>
+    <t>SITC</t>
+  </si>
+  <si>
+    <t>NATURAL FOOD IH</t>
+  </si>
+  <si>
+    <t>JINMAO SERVICES</t>
+  </si>
+  <si>
+    <t>361 DEGREES</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V68"/>
+  <dimension ref="B1:V118"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1423,13 +1741,13 @@
         <v>149</v>
       </c>
       <c r="E2">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>8755299328</v>
+        <v>8671382528</v>
       </c>
       <c r="H2" s="6">
         <v>3.35</v>
@@ -1438,11 +1756,11 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.32627118644067798</v>
+        <f>E2/I2-1</f>
+        <v>0.31355932203389836</v>
       </c>
       <c r="K2" s="11">
-        <v>4.8881789137380192E-2</v>
+        <v>4.9354838709677419E-2</v>
       </c>
       <c r="L2" s="13">
         <v>1871151000</v>
@@ -1457,7 +1775,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.43860503555673142</v>
+        <v>0.44683188783843514</v>
       </c>
       <c r="Q2" s="12">
         <v>0.28956319566547578</v>
@@ -1468,53 +1786,53 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E3">
-        <v>13.16</v>
+        <v>6.32</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>257500397568</v>
+        <v>24660893696</v>
       </c>
       <c r="H3" s="6">
-        <v>15.14</v>
+        <v>7.28</v>
       </c>
       <c r="I3" s="6">
-        <v>9.52</v>
+        <v>4.22</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>0.38235294117647056</v>
+        <f>E3/I3-1</f>
+        <v>0.49763033175355464</v>
       </c>
       <c r="K3" s="11">
-        <v>0.11778115501519756</v>
+        <v>6.8037974683544293E-3</v>
       </c>
       <c r="L3" s="13">
-        <v>70144988000</v>
+        <v>786762000</v>
       </c>
       <c r="M3" s="13">
-        <v>269343749000</v>
+        <v>2279244000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O3" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P3" s="12">
-        <v>0.52719360007237348</v>
+        <v>0.35201451099625231</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.26042924055386191</v>
+        <v>0.34518550887925997</v>
       </c>
       <c r="R3" s="14">
         <v>2</v>
@@ -1522,41 +1840,41 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="E4">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>17859514368</v>
+        <v>2640231936</v>
       </c>
       <c r="H4" s="6">
-        <v>5.19</v>
+        <v>3.55</v>
       </c>
       <c r="I4" s="6">
-        <v>2.11</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.36492890995260674</v>
+        <f>E4/I4-1</f>
+        <v>0.25862068965517238</v>
       </c>
       <c r="K4" s="11">
-        <v>5.5555555555555559E-2</v>
+        <v>5.7876712328767128E-2</v>
       </c>
       <c r="L4" s="13">
-        <v>2906500000</v>
+        <v>504294000</v>
       </c>
       <c r="M4" s="13">
-        <v>10569000000</v>
+        <v>1704754000</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>51</v>
@@ -1565,52 +1883,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.16638325081256819</v>
+        <v>0.38959157993148558</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.27500236540826944</v>
+        <v>0.29581628786323422</v>
       </c>
       <c r="R4" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>15.26</v>
+        <v>13.26</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>31766437888</v>
+        <v>259457089536</v>
       </c>
       <c r="H5" s="6">
-        <v>15.48</v>
+        <v>15.14</v>
       </c>
       <c r="I5" s="6">
-        <v>7.96</v>
+        <v>9.52</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.91708542713567831</v>
+        <f>E5/I5-1</f>
+        <v>0.39285714285714279</v>
       </c>
       <c r="K5" s="11">
-        <v>7.3394495412844041E-2</v>
+        <v>0.11689291101055807</v>
       </c>
       <c r="L5" s="13">
-        <v>5451928473.2399998</v>
+        <v>70144988000</v>
       </c>
       <c r="M5" s="13">
-        <v>25994816572.18</v>
+        <v>269343749000</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>51</v>
@@ -1619,160 +1937,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P5" s="12">
-        <v>0.16532397994525591</v>
+        <v>0.52003538584734221</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.26042924055386191</v>
       </c>
       <c r="R5" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>2.68</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>13644067840</v>
+        <v>84659814400</v>
       </c>
       <c r="H6" s="6">
-        <v>3.35</v>
+        <v>149.5</v>
       </c>
       <c r="I6" s="6">
-        <v>2.23</v>
+        <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20179372197309431</v>
+        <f>E6/I6-1</f>
+        <v>0.40879120879120867</v>
       </c>
       <c r="K6" s="11">
-        <v>0.11194029850746268</v>
+        <v>1.5210608424336974E-2</v>
       </c>
       <c r="L6" s="13">
-        <v>2527643000</v>
+        <v>2635100000</v>
       </c>
       <c r="M6" s="13">
-        <v>16480074000</v>
+        <v>13245550000</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O6" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.42044234972482353</v>
+        <v>0.58877997253592906</v>
       </c>
       <c r="Q6" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.19894228627727803</v>
       </c>
       <c r="R6" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="E7">
-        <v>9.1300000000000008</v>
+        <v>1.67</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>113254916096</v>
+        <v>1670000000</v>
       </c>
       <c r="H7" s="6">
-        <v>13.6</v>
+        <v>1.88</v>
       </c>
       <c r="I7" s="6">
-        <v>6.57</v>
+        <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0.38964992389649922</v>
+        <f>E7/I7-1</f>
+        <v>0.23703703703703694</v>
       </c>
       <c r="K7" s="11">
-        <v>5.4764512595837896E-3</v>
+        <v>0.12574850299401197</v>
       </c>
       <c r="L7" s="13">
-        <v>2125459000</v>
+        <v>315190000</v>
       </c>
       <c r="M7" s="13">
-        <v>9202253000</v>
+        <v>607806000</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O7" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>0.14052624188977578</v>
+        <v>0.17142533923116124</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.23097158924015673</v>
+        <v>0.51857007005524791</v>
       </c>
       <c r="R7" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>308</v>
       </c>
       <c r="E8">
-        <v>6.36</v>
+        <v>6.76</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>7920871424</v>
+        <v>171674943488</v>
       </c>
       <c r="H8" s="6">
-        <v>8.6</v>
+        <v>8.49</v>
       </c>
       <c r="I8" s="6">
-        <v>3.46</v>
+        <v>4.58</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.83815028901734112</v>
+        <f>E8/I8-1</f>
+        <v>0.47598253275109159</v>
       </c>
       <c r="K8" s="11">
-        <v>2.2169811320754712E-2</v>
+        <v>3.7721893491124266E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>921702000</v>
+        <v>29168443138.220001</v>
       </c>
       <c r="M8" s="13">
-        <v>5262544000</v>
+        <v>100996030941.41</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>51</v>
@@ -1781,160 +2099,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.18022120457207247</v>
+        <v>0.18172499139277135</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.2888078161719172</v>
       </c>
       <c r="R8" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="E9">
-        <v>14.18</v>
+        <v>2.69</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>11801843712</v>
+        <v>13694978048</v>
       </c>
       <c r="H9" s="6">
-        <v>19.440000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="I9" s="6">
-        <v>12.12</v>
+        <v>2.23</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>0.16996699669966997</v>
+        <f>E9/I9-1</f>
+        <v>0.20627802690582953</v>
       </c>
       <c r="K9" s="11">
-        <v>1.0437235543018335E-2</v>
+        <v>0.11152416356877323</v>
       </c>
       <c r="L9" s="13">
-        <v>199557000</v>
+        <v>2527643000</v>
       </c>
       <c r="M9" s="13">
-        <v>1108087000</v>
+        <v>16480074000</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O9" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>0.1777488698356014</v>
+        <v>0.41691182058981441</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R9" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>305</v>
       </c>
       <c r="E10">
-        <v>2.3199999999999998</v>
+        <v>1.33</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>2412359168</v>
+        <v>2678952448</v>
       </c>
       <c r="H10" s="6">
-        <v>3.34</v>
+        <v>1.62</v>
       </c>
       <c r="I10" s="6">
-        <v>1.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20833333333333326</v>
+        <f>E10/I10-1</f>
+        <v>0.17699115044247815</v>
       </c>
       <c r="K10" s="11">
-        <v>0.12586206896551724</v>
+        <v>8.9473684210526302E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>762183000</v>
+        <v>929863000</v>
       </c>
       <c r="M10" s="13">
-        <v>5008319000</v>
+        <v>6026676000</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O10" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.24139590873418154</v>
+        <v>0.40223989942011568</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.15218339726363278</v>
+        <v>0.15429118804462028</v>
       </c>
       <c r="R10" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>310</v>
       </c>
       <c r="E11">
-        <v>4.3899999999999997</v>
+        <v>5.26</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>50623721472</v>
+        <v>370706939904</v>
       </c>
       <c r="H11" s="6">
-        <v>5.14</v>
+        <v>5.44</v>
       </c>
       <c r="I11" s="6">
-        <v>3.46</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>0.26878612716762995</v>
+        <f>E11/I11-1</f>
+        <v>1.095617529880478</v>
       </c>
       <c r="K11" s="11">
-        <v>5.3758542141230069E-2</v>
+        <v>3.4220532319391636E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>4734613000</v>
+        <v>72477000000</v>
       </c>
       <c r="M11" s="13">
-        <v>16213395000</v>
+        <v>319355000000</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>51</v>
@@ -1943,10 +2261,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P11" s="12">
-        <v>0.10669492405071343</v>
+        <v>0.19343619083097988</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.22694806719794586</v>
       </c>
       <c r="R11" s="14">
         <v>8</v>
@@ -1954,41 +2272,41 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E12">
-        <v>8.5500000000000007</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>140669730816</v>
+        <v>9345913856</v>
       </c>
       <c r="H12" s="6">
-        <v>10.76</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="I12" s="6">
-        <v>7.16</v>
+        <v>3.15</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.19413407821229067</v>
+        <f>E12/I12-1</f>
+        <v>0.43492063492063493</v>
       </c>
       <c r="K12" s="11">
-        <v>5.6023391812865489E-2</v>
+        <v>5.5309734513274339E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>32866046000</v>
+        <v>1576240000</v>
       </c>
       <c r="M12" s="13">
-        <v>215280386000</v>
+        <v>9636462000</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>51</v>
@@ -1997,52 +2315,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.19770691217459413</v>
+        <v>0.3312787531704886</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.16357040581906512</v>
       </c>
       <c r="R12" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E13">
-        <v>7.9</v>
+        <v>2.81</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>68406104064</v>
+        <v>17425428480</v>
       </c>
       <c r="H13" s="6">
-        <v>9.23</v>
+        <v>5.19</v>
       </c>
       <c r="I13" s="6">
-        <v>7.08</v>
+        <v>2.11</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
-        <v>0.11581920903954801</v>
+        <f>E13/I13-1</f>
+        <v>0.33175355450236976</v>
       </c>
       <c r="K13" s="11">
-        <v>0.04</v>
+        <v>5.6939501779359428E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>13438000000</v>
+        <v>2906500000</v>
       </c>
       <c r="M13" s="13">
-        <v>88611000000</v>
+        <v>10569000000</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>51</v>
@@ -2051,52 +2369,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.22218873682092952</v>
+        <v>0.17034531014964546</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.27500236540826944</v>
       </c>
       <c r="R13" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>304</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="E14">
-        <v>5.21</v>
+        <v>1.51</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>61494153216</v>
+        <v>1786028032</v>
       </c>
       <c r="H14" s="6">
-        <v>5.77</v>
+        <v>2.77</v>
       </c>
       <c r="I14" s="6">
-        <v>4.12</v>
+        <v>1.36</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
-        <v>0.2645631067961165</v>
+        <f>E14/I14-1</f>
+        <v>0.11029411764705865</v>
       </c>
       <c r="K14" s="11">
-        <v>4.5681381957773513E-2</v>
+        <v>4.0397350993377483E-2</v>
       </c>
       <c r="L14" s="13">
-        <v>5687261000</v>
+        <v>841215000</v>
       </c>
       <c r="M14" s="13">
-        <v>21716551000</v>
+        <v>5774434000</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>51</v>
@@ -2105,226 +2423,226 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.10402155086679897</v>
+        <v>0.63895008648350404</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.26188601495697911</v>
+        <v>0.14567921288909008</v>
       </c>
       <c r="R14" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c r="E15">
-        <v>5.36</v>
+        <v>15.96</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>5679349248</v>
+        <v>144769499136</v>
       </c>
       <c r="H15" s="6">
-        <v>5.99</v>
+        <v>17.88</v>
       </c>
       <c r="I15" s="6">
-        <v>3.97</v>
+        <v>10.6</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
-        <v>0.35012594458438295</v>
+        <f>E15/I15-1</f>
+        <v>0.50566037735849068</v>
       </c>
       <c r="K15" s="11">
-        <v>9.141791044776118E-2</v>
+        <v>4.5050125313283201E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>866801000</v>
+        <v>21175963859.630001</v>
       </c>
       <c r="M15" s="13">
-        <v>7530053000</v>
+        <v>104071284594.97</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.32300218808614228</v>
+        <v>0.19851010441398781</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.20347556909712136</v>
       </c>
       <c r="R15" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>311</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>312</v>
       </c>
       <c r="E16">
-        <v>4.99</v>
+        <v>13.04</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>14235571200</v>
+        <v>46866022400</v>
       </c>
       <c r="H16" s="6">
-        <v>6.21</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="I16" s="6">
-        <v>3.22</v>
+        <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="0"/>
-        <v>0.54968944099378869</v>
+        <f>E16/I16-1</f>
+        <v>0.7271523178807946</v>
       </c>
       <c r="K16" s="11">
-        <v>8.4168336673346687E-3</v>
+        <v>2.6840490797546013E-2</v>
       </c>
       <c r="L16" s="13">
-        <v>259348000</v>
+        <v>25585077000</v>
       </c>
       <c r="M16" s="13">
-        <v>1677627000</v>
+        <v>167756547000</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O16" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.16223361728966321</v>
+        <v>0.30242053047122414</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>355</v>
       </c>
       <c r="D17" t="s">
         <v>87</v>
       </c>
       <c r="E17">
-        <v>5.75</v>
+        <v>7.39</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>52136685568</v>
+        <v>94815174656</v>
       </c>
       <c r="H17" s="6">
-        <v>7.38</v>
+        <v>7.45</v>
       </c>
       <c r="I17" s="6">
-        <v>3.39</v>
+        <v>4.84</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="0"/>
-        <v>0.69616519174041303</v>
+        <f>E17/I17-1</f>
+        <v>0.52685950413223148</v>
       </c>
       <c r="K17" s="11">
-        <v>5.3391304347826088E-2</v>
+        <v>8.6603518267929641E-3</v>
       </c>
       <c r="L17" s="13">
-        <v>5594372000</v>
+        <v>2553000000</v>
       </c>
       <c r="M17" s="13">
-        <v>26933044000</v>
+        <v>13971000000</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O17" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P17" s="12">
-        <v>0.13792889650292511</v>
+        <v>0.18242264945874517</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.18273566673824351</v>
       </c>
       <c r="R17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>4.84</v>
+        <v>15.66</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>7095295488</v>
+        <v>32599107584</v>
       </c>
       <c r="H18" s="6">
-        <v>5.04</v>
+        <v>15.84</v>
       </c>
       <c r="I18" s="6">
-        <v>3.45</v>
+        <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="0"/>
-        <v>0.40289855072463765</v>
+        <f>E18/I18-1</f>
+        <v>0.96733668341708556</v>
       </c>
       <c r="K18" s="11">
-        <v>9.9173553719008267E-2</v>
+        <v>7.1519795657726704E-2</v>
       </c>
       <c r="L18" s="13">
-        <v>784607000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M18" s="13">
-        <v>7872586000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O18" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P18" s="12">
-        <v>0.57070898782144941</v>
+        <v>0.1615069503518686</v>
       </c>
       <c r="Q18" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R18" s="14">
         <v>14</v>
@@ -2332,95 +2650,95 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E19">
-        <v>96.85</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>270018756608</v>
+        <v>2412359168</v>
       </c>
       <c r="H19" s="6">
-        <v>107.5</v>
+        <v>3.34</v>
       </c>
       <c r="I19" s="6">
-        <v>65.55</v>
+        <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" si="0"/>
-        <v>0.47749809305873381</v>
+        <f>E19/I19-1</f>
+        <v>0.20833333333333326</v>
       </c>
       <c r="K19" s="11">
-        <v>2.2901393908105319E-2</v>
+        <v>0.12586206896551724</v>
       </c>
       <c r="L19" s="13">
-        <v>22510000000</v>
+        <v>762183000</v>
       </c>
       <c r="M19" s="13">
-        <v>82545000000</v>
+        <v>5008319000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O19" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P19" s="12">
-        <v>8.3535102773332204E-2</v>
+        <v>0.24139590873418154</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.27269973953601068</v>
+        <v>0.15218339726363278</v>
       </c>
       <c r="R19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>113</v>
+        <v>298</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>356</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>245</v>
       </c>
       <c r="E20">
-        <v>4.2</v>
+        <v>7.38</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>6028722176</v>
+        <v>7288001024</v>
       </c>
       <c r="H20" s="6">
-        <v>7.92</v>
+        <v>9.07</v>
       </c>
       <c r="I20" s="6">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="0"/>
-        <v>0.77966101694915269</v>
+        <f>E20/I20-1</f>
+        <v>0.47599999999999998</v>
       </c>
       <c r="K20" s="11">
-        <v>6.0476190476190475E-2</v>
+        <v>4.7967479674796747E-2</v>
       </c>
       <c r="L20" s="13">
-        <v>811880000</v>
+        <v>1333116000</v>
       </c>
       <c r="M20" s="13">
-        <v>5532140000</v>
+        <v>8019803000</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>51</v>
@@ -2429,52 +2747,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>0.14917127088890111</v>
+        <v>0.20035706568750702</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.14675695119790894</v>
+        <v>0.16622802330680692</v>
       </c>
       <c r="R20" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E21">
-        <v>13.12</v>
+        <v>15.66</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>73923854336</v>
+        <v>32599107584</v>
       </c>
       <c r="H21" s="6">
-        <v>14.24</v>
+        <v>15.84</v>
       </c>
       <c r="I21" s="6">
-        <v>8.81</v>
+        <v>7.96</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="0"/>
-        <v>0.48921679909194071</v>
+        <f>E21/I21-1</f>
+        <v>0.96733668341708556</v>
       </c>
       <c r="K21" s="11">
-        <v>2.5228658536585367E-2</v>
+        <v>7.1519795657726704E-2</v>
       </c>
       <c r="L21" s="13">
-        <v>6482967000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M21" s="13">
-        <v>27483863000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>51</v>
@@ -2483,322 +2801,322 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>8.6218742696708636E-2</v>
+        <v>0.1615069503518686</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R21" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>143</v>
+        <v>301</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E22">
-        <v>49.9</v>
+        <v>0.73</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>127685124096</v>
+        <v>1597612288</v>
       </c>
       <c r="H22" s="6">
-        <v>71.7</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="6">
-        <v>43.55</v>
+        <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="0"/>
-        <v>0.14580941446613083</v>
+        <f>E22/I22-1</f>
+        <v>0.73809523809523814</v>
       </c>
       <c r="K22" s="11">
-        <v>3.2865731462925853E-3</v>
+        <v>5.0684931506849315E-2</v>
       </c>
       <c r="L22" s="13">
-        <v>1279098000</v>
+        <v>219938000</v>
       </c>
       <c r="M22" s="13">
-        <v>4811702000</v>
+        <v>1520292000</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="O22" s="6">
-        <v>8.7546153846153842</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P22" s="12">
-        <v>7.8180749364385127E-2</v>
+        <v>0.32728377071537917</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.26583067696212276</v>
+        <v>0.14466826109721026</v>
       </c>
       <c r="R22" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>133</v>
+        <v>300</v>
       </c>
       <c r="C23" t="s">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="E23">
-        <v>18.34</v>
+        <v>24.25</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>518143541248</v>
+        <v>64338644992</v>
       </c>
       <c r="H23" s="6">
-        <v>19.260000000000002</v>
+        <v>25.8</v>
       </c>
       <c r="I23" s="6">
-        <v>13.52</v>
+        <v>15.7</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="0"/>
-        <v>0.35650887573964507</v>
+        <f>E23/I23-1</f>
+        <v>0.54458598726114649</v>
       </c>
       <c r="K23" s="11">
-        <v>2.0719738276990186E-2</v>
+        <v>1.1216494845360825E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>52374992116</v>
+        <v>1069250000</v>
       </c>
       <c r="M23" s="13">
-        <v>269573093476</v>
+        <v>2571093000</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O23" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P23" s="12">
-        <v>8.7100929788278658E-2</v>
+        <v>0.13351687759020417</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.19428864891763736</v>
+        <v>0.41587371596437778</v>
       </c>
       <c r="R23" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E24">
-        <v>6.25</v>
+        <v>14.1</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>4870012416</v>
+        <v>11735261184</v>
       </c>
       <c r="H24" s="6">
-        <v>8.09</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I24" s="6">
-        <v>4.0199999999999996</v>
+        <v>12.12</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="0"/>
-        <v>0.55472636815920406</v>
+        <f>E24/I24-1</f>
+        <v>0.16336633663366351</v>
       </c>
       <c r="K24" s="11">
-        <v>2.7200000000000002E-2</v>
+        <v>1.049645390070922E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>437453000</v>
+        <v>199557000</v>
       </c>
       <c r="M24" s="13">
-        <v>4911072000</v>
+        <v>1108087000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O24" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P24" s="12">
-        <v>0.16951840721592248</v>
+        <v>0.17912992702590763</v>
       </c>
       <c r="Q24" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R24" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E25">
-        <v>402.4</v>
+        <v>7.88</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>508569223168</v>
+        <v>68232925184</v>
       </c>
       <c r="H25" s="6">
-        <v>409.2</v>
+        <v>9.23</v>
       </c>
       <c r="I25" s="6">
-        <v>218.4</v>
+        <v>7.08</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="0"/>
-        <v>0.84249084249084238</v>
+        <f>E25/I25-1</f>
+        <v>0.11299435028248594</v>
       </c>
       <c r="K25" s="11">
-        <v>2.301192842942346E-2</v>
+        <v>4.0101522842639598E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>20744000000</v>
+        <v>13438000000</v>
       </c>
       <c r="M25" s="13">
-        <v>53852000000</v>
+        <v>88611000000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O25" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P25" s="12">
-        <v>5.5243936509172288E-2</v>
+        <v>0.22278583500850604</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R25" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E26">
-        <v>6.19</v>
+        <v>8.4</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>10069335040</v>
+        <v>138201825280</v>
       </c>
       <c r="H26" s="6">
-        <v>7.05</v>
+        <v>10.76</v>
       </c>
       <c r="I26" s="6">
-        <v>4.2699999999999996</v>
+        <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="0"/>
-        <v>0.44964871194379419</v>
+        <f>E26/I26-1</f>
+        <v>0.17318435754189943</v>
       </c>
       <c r="K26" s="11">
-        <v>4.5234248788368341E-2</v>
+        <v>5.7023809523809518E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>4094312000</v>
+        <v>32866046000</v>
       </c>
       <c r="M26" s="13">
-        <v>37637054000</v>
+        <v>215280386000</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O26" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P26" s="12">
-        <v>0.13430259995228902</v>
+        <v>0.20049289062485265</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R26" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="E27">
-        <v>21.95</v>
+        <v>6.41</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>24970758144</v>
+        <v>7983142400</v>
       </c>
       <c r="H27" s="6">
-        <v>28.75</v>
+        <v>8.6</v>
       </c>
       <c r="I27" s="6">
-        <v>19.52</v>
+        <v>3.46</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="0"/>
-        <v>0.12448770491803285</v>
+        <f>E27/I27-1</f>
+        <v>0.85260115606936426</v>
       </c>
       <c r="K27" s="11">
-        <v>6.3781321184510242E-2</v>
+        <v>2.1996879875195004E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>3446618000</v>
+        <v>921702000</v>
       </c>
       <c r="M27" s="13">
-        <v>34010798000</v>
+        <v>5262544000</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>51</v>
@@ -2807,106 +3125,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.15508657118243896</v>
+        <v>0.17819043213287719</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R27" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="E28">
-        <v>244.8</v>
+        <v>9.24</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>325133565952</v>
+        <v>114619424768</v>
       </c>
       <c r="H28" s="6">
-        <v>252.6</v>
+        <v>13.6</v>
       </c>
       <c r="I28" s="6">
-        <v>34.4</v>
+        <v>6.57</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
-        <v>6.1162790697674421</v>
+        <f>E28/I28-1</f>
+        <v>0.40639269406392686</v>
       </c>
       <c r="K28" s="11">
-        <v>3.3292483660130713E-3</v>
+        <v>5.411255411255411E-3</v>
       </c>
       <c r="L28" s="13">
-        <v>4414795000</v>
+        <v>2125459000</v>
       </c>
       <c r="M28" s="13">
-        <v>10683505000</v>
+        <v>9202253000</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O28" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P28" s="12">
-        <v>1.4756289561246224E-2</v>
+        <v>0.13889725341894968</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.41323470153287706</v>
+        <v>0.23097158924015673</v>
       </c>
       <c r="R28" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="E29">
-        <v>6.96</v>
+        <v>4.8</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>3992979968</v>
+        <v>7036656640</v>
       </c>
       <c r="H29" s="6">
-        <v>9.24</v>
+        <v>5.04</v>
       </c>
       <c r="I29" s="6">
-        <v>6.85</v>
+        <v>3.45</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="0"/>
-        <v>1.6058394160584077E-2</v>
+        <f>E29/I29-1</f>
+        <v>0.39130434782608692</v>
       </c>
       <c r="K29" s="11">
-        <v>8.1896551724137928E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L29" s="13">
-        <v>498120000</v>
+        <v>784607000</v>
       </c>
       <c r="M29" s="13">
-        <v>3284848000</v>
+        <v>7872586000</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>68</v>
@@ -2915,52 +3233,52 @@
         <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>9.6159211151065974E-2</v>
+        <v>0.59613587655626854</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.15164171979951585</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R29" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>336</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="E30">
-        <v>339.4</v>
+        <v>11</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>126199775232</v>
+        <v>17650051072</v>
       </c>
       <c r="H30" s="6">
-        <v>421.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I30" s="6">
-        <v>225.2</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
-        <v>0.50710479573712264</v>
+        <f>E30/I30-1</f>
+        <v>0.14226375908618882</v>
       </c>
       <c r="K30" s="11">
-        <v>2.1213906894519742E-3</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13">
-        <v>1200000000</v>
+        <v>634792000</v>
       </c>
       <c r="M30" s="13">
-        <v>5855000000</v>
+        <v>5195491000</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>72</v>
@@ -2969,106 +3287,106 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P30" s="12">
-        <v>6.6327765757611262E-2</v>
+        <v>0.25311951005732741</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.20495303159692571</v>
+        <v>0.12218132992627646</v>
       </c>
       <c r="R30" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="E31">
-        <v>12.54</v>
+        <v>5.49</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>58221084672</v>
+        <v>5817094144</v>
       </c>
       <c r="H31" s="6">
-        <v>13.44</v>
+        <v>5.99</v>
       </c>
       <c r="I31" s="6">
-        <v>7.51</v>
+        <v>3.97</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="0"/>
-        <v>0.66977363515312915</v>
+        <f>E31/I31-1</f>
+        <v>0.38287153652392947</v>
       </c>
       <c r="K31" s="11">
-        <v>3.4928229665071774E-2</v>
+        <v>8.9253187613843349E-2</v>
       </c>
       <c r="L31" s="13">
-        <v>3967214824.1399999</v>
+        <v>866801000</v>
       </c>
       <c r="M31" s="13">
-        <v>41038539262.660004</v>
+        <v>7530053000</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O31" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P31" s="12">
-        <v>0.12952645270905808</v>
+        <v>0.30723230563220139</v>
       </c>
       <c r="Q31" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R31" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>126</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>353</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="E32">
-        <v>11.88</v>
+        <v>3.8</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>118649241600</v>
+        <v>2181883904</v>
       </c>
       <c r="H32" s="6">
-        <v>12.16</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I32" s="6">
-        <v>5.83</v>
+        <v>2.8</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
-        <v>1.0377358490566038</v>
+        <f>E32/I32-1</f>
+        <v>0.35714285714285721</v>
       </c>
       <c r="K32" s="11">
-        <v>4.2087542087542083E-2</v>
+        <v>7.8947368421052627E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>9432900000</v>
+        <v>424258000</v>
       </c>
       <c r="M32" s="13">
-        <v>54338700000</v>
+        <v>2485347000</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>68</v>
@@ -3077,160 +3395,160 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>6.6973746359587194E-2</v>
+        <v>0.16286464989656568</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.17359450999011755</v>
+        <v>0.17070372869462494</v>
       </c>
       <c r="R32" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="E33">
-        <v>14.48</v>
+        <v>0.69</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>60787183616</v>
+        <v>1643724928</v>
       </c>
       <c r="H33" s="6">
-        <v>15.38</v>
+        <v>1.03</v>
       </c>
       <c r="I33" s="6">
-        <v>10.98</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
-        <v>0.31876138433515488</v>
+        <f>E33/I33-1</f>
+        <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
-        <v>6.1187845303867401E-2</v>
+        <v>1.4492753623188408E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>11996000000</v>
+        <v>54195000</v>
       </c>
       <c r="M33" s="13">
-        <v>138296000000</v>
+        <v>586711000</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O33" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P33" s="12">
-        <v>0.14293683353601874</v>
+        <v>1.2095413323209785</v>
       </c>
       <c r="Q33" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>9.2370860611101543E-2</v>
       </c>
       <c r="R33" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>61</v>
       </c>
       <c r="E34">
-        <v>35</v>
+        <v>11.3</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>24208799744</v>
+        <v>18075480064</v>
       </c>
       <c r="H34" s="6">
-        <v>39.200000000000003</v>
+        <v>11.84</v>
       </c>
       <c r="I34" s="6">
-        <v>13.48</v>
+        <v>8.67</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>1.5964391691394657</v>
+        <f>E34/I34-1</f>
+        <v>0.30334486735870825</v>
       </c>
       <c r="K34" s="11">
-        <v>1.3142857142857144E-2</v>
+        <v>5.3097345132743355E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>1323087000</v>
+        <v>1721368005.75</v>
       </c>
       <c r="M34" s="13">
-        <v>5952918000</v>
+        <v>14620942286.52</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O34" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>4.9606487183200106E-2</v>
+        <v>0.21588350738749548</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.222258562943417</v>
+        <v>0.11773304155211949</v>
       </c>
       <c r="R34" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="E35">
-        <v>57.05</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>161359642624</v>
+        <v>52122832896</v>
       </c>
       <c r="H35" s="6">
-        <v>60</v>
+        <v>5.14</v>
       </c>
       <c r="I35" s="6">
-        <v>38.4</v>
+        <v>3.46</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="1"/>
-        <v>0.48567708333333326</v>
+        <f>E35/I35-1</f>
+        <v>0.30635838150289008</v>
       </c>
       <c r="K35" s="11">
-        <v>3.15512708150745E-2</v>
+        <v>5.2212389380530973E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>8955723006</v>
+        <v>4734613000</v>
       </c>
       <c r="M35" s="13">
-        <v>47495870210</v>
+        <v>16213395000</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>51</v>
@@ -3239,106 +3557,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>6.0822593303914124E-2</v>
+        <v>0.10342458469693973</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R35" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="E36">
-        <v>515</v>
+        <v>4.99</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>4683229822976</v>
+        <v>14235571200</v>
       </c>
       <c r="H36" s="6">
-        <v>547</v>
+        <v>6.21</v>
       </c>
       <c r="I36" s="6">
-        <v>349</v>
+        <v>3.22</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="1"/>
-        <v>0.47564469914040108</v>
+        <f>E36/I36-1</f>
+        <v>0.54968944099378869</v>
       </c>
       <c r="K36" s="11">
-        <v>8.211650485436893E-3</v>
+        <v>8.4168336673346687E-3</v>
       </c>
       <c r="L36" s="13">
-        <v>253932000000</v>
+        <v>259348000</v>
       </c>
       <c r="M36" s="13">
-        <v>1312163000000</v>
+        <v>1677627000</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O36" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P36" s="12">
-        <v>5.5093665591363035E-2</v>
+        <v>0.16223361728966321</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R36" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E37">
-        <v>19.760000000000002</v>
+        <v>5.88</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>125902422016</v>
+        <v>53315428352</v>
       </c>
       <c r="H37" s="6">
-        <v>26.6</v>
+        <v>7.38</v>
       </c>
       <c r="I37" s="6">
-        <v>16.02</v>
+        <v>3.39</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="1"/>
-        <v>0.23345817727840212</v>
+        <f>E37/I37-1</f>
+        <v>0.734513274336283</v>
       </c>
       <c r="K37" s="11">
-        <v>3.5931174089068818E-2</v>
+        <v>5.2210884353741494E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>10795274825</v>
+        <v>5594372000</v>
       </c>
       <c r="M37" s="13">
-        <v>215275428010</v>
+        <v>26933044000</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>51</v>
@@ -3347,52 +3665,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P37" s="12">
-        <v>0.13990093886262106</v>
+        <v>0.13427632879892507</v>
       </c>
       <c r="Q37" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R37" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
+        <v>354</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="E38">
-        <v>32.049999999999997</v>
+        <v>5.66</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>72215052288</v>
+        <v>12657344512</v>
       </c>
       <c r="H38" s="6">
-        <v>61.55</v>
+        <v>5.69</v>
       </c>
       <c r="I38" s="6">
-        <v>24.85</v>
+        <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="1"/>
-        <v>0.28973843058350091</v>
+        <f>E38/I38-1</f>
+        <v>1.6203703703703702</v>
       </c>
       <c r="K38" s="11">
-        <v>1.7722308892355695E-2</v>
+        <v>4.0812720848056538E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>5261270000</v>
+        <v>2184074765.02</v>
       </c>
       <c r="M38" s="13">
-        <v>43208997000</v>
+        <v>23493408528.349998</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>51</v>
@@ -3401,106 +3719,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>7.2071431632998909E-2</v>
+        <v>0.57129919158069953</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.12176329850933591</v>
+        <v>9.29654274042198E-2</v>
       </c>
       <c r="R38" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>294</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>352</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="E39">
-        <v>5.88</v>
+        <v>4.38</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>45912571904</v>
+        <v>4822161408</v>
       </c>
       <c r="H39" s="6">
-        <v>11.72</v>
+        <v>4.49</v>
       </c>
       <c r="I39" s="6">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="1"/>
-        <v>0.17599999999999993</v>
+        <f>E39/I39-1</f>
+        <v>0.22346368715083798</v>
       </c>
       <c r="K39" s="11">
-        <v>7.312925170068027E-2</v>
+        <v>7.3059360730593617E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>6749146000</v>
+        <v>765224000</v>
       </c>
       <c r="M39" s="13">
-        <v>70848374000</v>
+        <v>5249449000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O39" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P39" s="12">
-        <v>9.1852537312565388E-2</v>
+        <v>0.18183155724704525</v>
       </c>
       <c r="Q39" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>0.14577225152582682</v>
       </c>
       <c r="R39" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
+        <v>351</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="E40">
-        <v>8.18</v>
+        <v>5.69</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>19273961472</v>
+        <v>15182114816</v>
       </c>
       <c r="H40" s="6">
-        <v>11.68</v>
+        <v>7.13</v>
       </c>
       <c r="I40" s="6">
-        <v>5.19</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="1"/>
-        <v>0.57610789980732169</v>
+        <f>E40/I40-1</f>
+        <v>0.3710843373493975</v>
       </c>
       <c r="K40" s="11">
-        <v>0</v>
+        <v>4.0421792618629174E-2</v>
       </c>
       <c r="L40" s="13">
-        <v>13493113000</v>
+        <v>2030839000</v>
       </c>
       <c r="M40" s="13">
-        <v>208027754000</v>
+        <v>11587361000</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>51</v>
@@ -3509,52 +3827,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.12171940299349211</v>
+        <v>0.14242928543114775</v>
       </c>
       <c r="Q40" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>0.17526328902672489</v>
       </c>
       <c r="R40" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E41">
-        <v>9.2899999999999991</v>
+        <v>5.29</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>284255420416</v>
+        <v>62438400000</v>
       </c>
       <c r="H41" s="6">
-        <v>11.56</v>
+        <v>5.77</v>
       </c>
       <c r="I41" s="6">
-        <v>5.88</v>
+        <v>4.12</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="1"/>
-        <v>0.57993197278911546</v>
+        <f>E41/I41-1</f>
+        <v>0.28398058252427183</v>
       </c>
       <c r="K41" s="11">
-        <v>0</v>
+        <v>4.4990548204158785E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>26994000000</v>
+        <v>5687261000</v>
       </c>
       <c r="M41" s="13">
-        <v>363169000000</v>
+        <v>21716551000</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>51</v>
@@ -3563,160 +3881,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>9.7328961612878989E-2</v>
+        <v>0.10236676985946681</v>
       </c>
       <c r="Q41" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>0.26188601495697911</v>
       </c>
       <c r="R41" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>338</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="E42">
-        <v>9.8000000000000007</v>
+        <v>3.25</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>30576001024</v>
+        <v>37379874816</v>
       </c>
       <c r="H42" s="6">
-        <v>10.1</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="I42" s="6">
-        <v>5.6</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="1"/>
-        <v>0.75000000000000022</v>
+        <f>E42/I42-1</f>
+        <v>0.46396396396396389</v>
       </c>
       <c r="K42" s="11">
-        <v>3.2653061224489792E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>1990539000</v>
+        <v>9414000000</v>
       </c>
       <c r="M42" s="13">
-        <v>18620709000</v>
+        <v>81589000000</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O42" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>5.9723296140694736E-2</v>
+        <v>0.1945742319089287</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.10689920561026972</v>
+        <v>0.11538320116682396</v>
       </c>
       <c r="R42" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>122</v>
+        <v>286</v>
       </c>
       <c r="C43" t="s">
-        <v>163</v>
+        <v>344</v>
       </c>
       <c r="D43" t="s">
         <v>152</v>
       </c>
       <c r="E43">
-        <v>32.950000000000003</v>
+        <v>26.65</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>115317760000</v>
+        <v>190039539712</v>
       </c>
       <c r="H43" s="6">
-        <v>37.25</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="I43" s="6">
-        <v>28.1</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="1"/>
-        <v>0.17259786476868322</v>
+        <f>E43/I43-1</f>
+        <v>0.43588362068965525</v>
       </c>
       <c r="K43" s="11">
-        <v>5.2807283763277688E-2</v>
+        <v>4.9493433395872422E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>16863000000</v>
+        <v>61181051000</v>
       </c>
       <c r="M43" s="13">
-        <v>448320000000</v>
+        <v>532289194000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O43" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>0.12319481569213964</v>
+        <v>0.19554337009103015</v>
       </c>
       <c r="Q43" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>0.11493949471384535</v>
       </c>
       <c r="R43" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>18</v>
+        <v>278</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="D44" t="s">
-        <v>66</v>
+        <v>334</v>
       </c>
       <c r="E44">
-        <v>50.45</v>
+        <v>6.01</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>137381412864</v>
+        <v>12189963264</v>
       </c>
       <c r="H44" s="6">
-        <v>82.25</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I44" s="6">
-        <v>37.85</v>
+        <v>5.31</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="1"/>
-        <v>0.33289299867899613</v>
+        <f>E44/I44-1</f>
+        <v>0.13182674199623357</v>
       </c>
       <c r="K44" s="11">
-        <v>2.0812685827552031E-2</v>
+        <v>4.4925124792013313E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>6350637223.7200003</v>
+        <v>1537565000</v>
       </c>
       <c r="M44" s="13">
-        <v>57896384836.860001</v>
+        <v>14484935000</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>51</v>
@@ -3725,52 +4043,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>6.4192410583388496E-2</v>
+        <v>0.21048977508140268</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.10968970241604512</v>
+        <v>0.10614925092863724</v>
       </c>
       <c r="R44" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>117</v>
+        <v>283</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>339</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="E45">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>6015335424</v>
+        <v>8474598400</v>
       </c>
       <c r="H45" s="6">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="I45" s="6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="J45" s="12">
-        <f t="shared" si="1"/>
-        <v>0.23357664233576636</v>
+        <f>E45/I45-1</f>
+        <v>0.488721804511278</v>
       </c>
       <c r="K45" s="11">
-        <v>5.562130177514793E-2</v>
+        <v>6.1616161616161617E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>2220197000</v>
+        <v>1230913000</v>
       </c>
       <c r="M45" s="13">
-        <v>71097505000</v>
+        <v>10701340000</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>51</v>
@@ -3779,52 +4097,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>0.12289415093467723</v>
+        <v>0.18317201071359485</v>
       </c>
       <c r="Q45" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>0.11502419323187564</v>
       </c>
       <c r="R45" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>346</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E46">
-        <v>24</v>
+        <v>9.81</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>26599440384</v>
+        <v>24729440256</v>
       </c>
       <c r="H46" s="6">
-        <v>24.55</v>
+        <v>11.22</v>
       </c>
       <c r="I46" s="6">
-        <v>14.52</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J46" s="12">
-        <f t="shared" si="1"/>
-        <v>0.65289256198347112</v>
+        <f>E46/I46-1</f>
+        <v>1.2551724137931037</v>
       </c>
       <c r="K46" s="11">
-        <v>3.9166666666666662E-2</v>
+        <v>3.2415902140672782E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>3838344000</v>
+        <v>3301437000</v>
       </c>
       <c r="M46" s="13">
-        <v>81520873000</v>
+        <v>21814427000</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>68</v>
@@ -3833,160 +4151,160 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>8.6415332705047476E-2</v>
+        <v>0.15777310630951955</v>
       </c>
       <c r="Q46" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>0.15134190781174311</v>
       </c>
       <c r="R46" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>129</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>350</v>
       </c>
       <c r="D47" t="s">
         <v>98</v>
       </c>
       <c r="E47">
-        <v>11.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>87116636160</v>
+        <v>31859691520</v>
       </c>
       <c r="H47" s="6">
-        <v>11.6</v>
+        <v>6.15</v>
       </c>
       <c r="I47" s="6">
-        <v>8.5399999999999991</v>
+        <v>3.71</v>
       </c>
       <c r="J47" s="12">
-        <f t="shared" si="1"/>
-        <v>0.34660421545667464</v>
+        <f>E47/I47-1</f>
+        <v>0.23989218328840956</v>
       </c>
       <c r="K47" s="11">
-        <v>6.8521739130434786E-2</v>
+        <v>4.7608695652173919E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>8154000000</v>
+        <v>4216348000</v>
       </c>
       <c r="M47" s="13">
-        <v>79588000000</v>
+        <v>46142120000</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O47" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>6.3491996176225127E-2</v>
+        <v>0.34525881172915157</v>
       </c>
       <c r="Q47" s="12">
-        <v>0.10245263104990703</v>
+        <v>9.1377422623841298E-2</v>
       </c>
       <c r="R47" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="C48" t="s">
-        <v>150</v>
+        <v>330</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="E48">
-        <v>5.76</v>
+        <v>4.05</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>760584994816</v>
+        <v>3743698688</v>
       </c>
       <c r="H48" s="6">
-        <v>6.98</v>
+        <v>4.2</v>
       </c>
       <c r="I48" s="6">
-        <v>4.08</v>
+        <v>3.4</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="1"/>
-        <v>0.41176470588235281</v>
+        <f>E48/I48-1</f>
+        <v>0.19117647058823528</v>
       </c>
       <c r="K48" s="11">
-        <v>4.5138888888888895E-2</v>
+        <v>3.580246913580247E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>44563000000</v>
+        <v>754477000</v>
       </c>
       <c r="M48" s="13">
-        <v>463922000000</v>
+        <v>11677999000</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O48" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P48" s="12">
-        <v>6.4542567843163007E-2</v>
+        <v>0.61635761447571313</v>
       </c>
       <c r="Q48" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>6.460670188445812E-2</v>
       </c>
       <c r="R48" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>345</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="E49">
-        <v>1.37</v>
+        <v>23.35</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>7483666432</v>
+        <v>237231341568</v>
       </c>
       <c r="H49" s="6">
-        <v>1.82</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I49" s="6">
-        <v>0.81</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="J49" s="12">
-        <f t="shared" si="1"/>
-        <v>0.69135802469135799</v>
+        <f>E49/I49-1</f>
+        <v>0.2136174636174637</v>
       </c>
       <c r="K49" s="11">
-        <v>2.4817518248175182E-2</v>
+        <v>4.1327623126338323E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>1384865000</v>
+        <v>25459748125.549999</v>
       </c>
       <c r="M49" s="13">
-        <v>23827484000</v>
+        <v>134815560756.77</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>51</v>
@@ -3995,52 +4313,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>7.9558472213253753E-2</v>
+        <v>0.12070587695549247</v>
       </c>
       <c r="Q49" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>0.18884873513587705</v>
       </c>
       <c r="R49" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>139</v>
+        <v>289</v>
       </c>
       <c r="C50" t="s">
-        <v>187</v>
+        <v>347</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E50">
-        <v>1.96</v>
+        <v>19.3</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>3485154560</v>
+        <v>30802798592</v>
       </c>
       <c r="H50" s="6">
-        <v>2.73</v>
+        <v>27.5</v>
       </c>
       <c r="I50" s="6">
-        <v>1.79</v>
+        <v>16.18</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="1"/>
-        <v>9.4972067039106101E-2</v>
+        <f>E50/I50-1</f>
+        <v>0.19283065512979003</v>
       </c>
       <c r="K50" s="11">
-        <v>2.8571428571428574E-2</v>
+        <v>3.5544041450777206E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>364157000</v>
+        <v>3811007000</v>
       </c>
       <c r="M50" s="13">
-        <v>7859317000</v>
+        <v>22856317000</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>51</v>
@@ -4049,52 +4367,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>8.469165949285995E-2</v>
+        <v>0.13527560979095485</v>
       </c>
       <c r="Q50" s="12">
-        <v>4.6334433386514377E-2</v>
+        <v>0.1667375806872122</v>
       </c>
       <c r="R50" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
-        <v>134</v>
+        <v>291</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>349</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="E51">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>40253509632</v>
+        <v>2676399616</v>
       </c>
       <c r="H51" s="6">
-        <v>5.49</v>
+        <v>14.18</v>
       </c>
       <c r="I51" s="6">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>E51/I51-1</f>
+        <v>1.1904761904761907</v>
       </c>
       <c r="K51" s="11">
-        <v>7.3653846153846153E-2</v>
+        <v>5.0724637681159417E-2</v>
       </c>
       <c r="L51" s="13">
-        <v>5474000000</v>
+        <v>348303000</v>
       </c>
       <c r="M51" s="13">
-        <v>59407000000</v>
+        <v>3681615000</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>68</v>
@@ -4103,106 +4421,106 @@
         <v>1</v>
       </c>
       <c r="P51" s="12">
-        <v>5.9560525385179718E-2</v>
+        <v>0.27355952913847126</v>
       </c>
       <c r="Q51" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>9.4606035666412708E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>332</v>
       </c>
       <c r="D52" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E52">
-        <v>2.23</v>
+        <v>77.2</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>9577849856</v>
+        <v>18900488192</v>
       </c>
       <c r="H52" s="6">
-        <v>3.04</v>
+        <v>95.5</v>
       </c>
       <c r="I52" s="6">
-        <v>1.93</v>
+        <v>55.05</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="1"/>
-        <v>0.15544041450777213</v>
+        <f>E52/I52-1</f>
+        <v>0.4023614895549501</v>
       </c>
       <c r="K52" s="11">
-        <v>4.7982062780269057E-2</v>
+        <v>1.0621761658031087E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>1938532000</v>
+        <v>526052000</v>
       </c>
       <c r="M52" s="13">
-        <v>49986396000</v>
+        <v>5343547000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O52" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P52" s="12">
-        <v>6.4389413076261628E-2</v>
+        <v>0.21280855756026237</v>
       </c>
       <c r="Q52" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>9.8446219337080781E-2</v>
       </c>
       <c r="R52" s="14">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E53">
-        <v>11.42</v>
+        <v>96.7</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>201001140224</v>
+        <v>269600555008</v>
       </c>
       <c r="H53" s="6">
-        <v>12.46</v>
+        <v>107.5</v>
       </c>
       <c r="I53" s="6">
-        <v>9.1999999999999993</v>
+        <v>65.55</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="1"/>
-        <v>0.24130434782608701</v>
+        <f>E53/I53-1</f>
+        <v>0.47520976353928313</v>
       </c>
       <c r="K53" s="11">
-        <v>3.6514886164623464E-2</v>
+        <v>2.2936918304033091E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>16758000000</v>
+        <v>22510000000</v>
       </c>
       <c r="M53" s="13">
-        <v>269590000000</v>
+        <v>82545000000</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>51</v>
@@ -4211,214 +4529,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>6.0262352193499312E-2</v>
+        <v>8.3656624909245095E-2</v>
       </c>
       <c r="Q53" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>0.27269973953601068</v>
       </c>
       <c r="R53" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="E54">
-        <v>7</v>
+        <v>4.07</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>7304779776</v>
+        <v>5842119168</v>
       </c>
       <c r="H54" s="6">
-        <v>7</v>
+        <v>7.92</v>
       </c>
       <c r="I54" s="6">
-        <v>4.0199999999999996</v>
+        <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="1"/>
-        <v>0.74129353233830875</v>
+        <f>E54/I54-1</f>
+        <v>0.72457627118644097</v>
       </c>
       <c r="K54" s="11">
-        <v>0</v>
+        <v>6.2407862407862405E-2</v>
       </c>
       <c r="L54" s="13">
-        <v>303335000</v>
+        <v>811880000</v>
       </c>
       <c r="M54" s="13">
-        <v>3620162000</v>
+        <v>5532140000</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O54" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>4.8839744900169083E-2</v>
+        <v>0.15411709479421579</v>
       </c>
       <c r="Q54" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R54" s="14">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="E55">
-        <v>14.04</v>
+        <v>12.96</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>14419220480</v>
+        <v>73022341120</v>
       </c>
       <c r="H55" s="6">
-        <v>14.5</v>
+        <v>14.24</v>
       </c>
       <c r="I55" s="6">
-        <v>10.36</v>
+        <v>8.81</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="1"/>
-        <v>0.35521235521235517</v>
+        <f>E55/I55-1</f>
+        <v>0.47105561861520995</v>
       </c>
       <c r="K55" s="11">
-        <v>7.6923076923076927E-2</v>
+        <v>2.5540123456790124E-2</v>
       </c>
       <c r="L55" s="13">
-        <v>984000000</v>
+        <v>6482967000</v>
       </c>
       <c r="M55" s="13">
-        <v>101944000000</v>
+        <v>27483863000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O55" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>2.4994144867559236E-2</v>
+        <v>8.7197283127823225E-2</v>
       </c>
       <c r="Q55" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R55" s="14">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="E56">
-        <v>40.200000000000003</v>
+        <v>50.15</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>424905965568</v>
+        <v>128324829184</v>
       </c>
       <c r="H56" s="6">
-        <v>59.7</v>
+        <v>71.7</v>
       </c>
       <c r="I56" s="6">
-        <v>15.24</v>
+        <v>43.55</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="1"/>
-        <v>1.6377952755905514</v>
+        <f>E56/I56-1</f>
+        <v>0.15154994259471866</v>
       </c>
       <c r="K56" s="11">
-        <v>0</v>
+        <v>3.2701894317048855E-3</v>
       </c>
       <c r="L56" s="13">
-        <v>984027000</v>
+        <v>1279098000</v>
       </c>
       <c r="M56" s="13">
-        <v>32183526000</v>
+        <v>4811702000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6">
-        <v>7.6923076923076916</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P56" s="12">
-        <v>1.6273090414324575E-2</v>
+        <v>7.7833130575827761E-2</v>
       </c>
       <c r="Q56" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R56" s="14">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>331</v>
       </c>
       <c r="D57" t="s">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="E57">
-        <v>29.1</v>
+        <v>5.73</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>29713719296</v>
+        <v>25178537984</v>
       </c>
       <c r="H57" s="6">
-        <v>36</v>
+        <v>6.87</v>
       </c>
       <c r="I57" s="6">
-        <v>22.4</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="1"/>
-        <v>0.29910714285714302</v>
+        <f>E57/I57-1</f>
+        <v>0.2012578616352203</v>
       </c>
       <c r="K57" s="11">
-        <v>0</v>
+        <v>6.2478184991273993E-2</v>
       </c>
       <c r="L57" s="13">
-        <v>-90314000</v>
+        <v>2919921000</v>
       </c>
       <c r="M57" s="13">
-        <v>18374441000</v>
+        <v>31662140000</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>51</v>
@@ -4427,361 +4745,376 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>-3.6543561486810142E-3</v>
+        <v>0.22992373749325898</v>
       </c>
       <c r="Q57" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>9.2221214358852555E-2</v>
       </c>
       <c r="R57" s="14">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="C58" t="s">
-        <v>223</v>
+        <v>335</v>
       </c>
       <c r="D58" t="s">
-        <v>224</v>
+        <v>87</v>
       </c>
       <c r="E58">
-        <v>6.35</v>
+        <v>10.6</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>24777953280</v>
+        <v>2488053248</v>
       </c>
       <c r="H58" s="6">
-        <v>7.28</v>
+        <v>10.88</v>
       </c>
       <c r="I58" s="6">
-        <v>4.22</v>
+        <v>7.36</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="1"/>
-        <v>0.50473933649289093</v>
+        <f>E58/I58-1</f>
+        <v>0.44021739130434767</v>
       </c>
       <c r="K58" s="11">
-        <v>6.7716535433070867E-3</v>
+        <v>3.962264150943396E-2</v>
       </c>
       <c r="L58" s="13">
-        <v>786762000</v>
+        <v>244811000</v>
       </c>
       <c r="M58" s="13">
-        <v>2279244000</v>
+        <v>2904223000</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O58" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P58" s="12">
-        <v>0.34963394018564992</v>
+        <v>0.31163992264507756</v>
       </c>
       <c r="Q58" s="12">
-        <v>0.34518550887925997</v>
+        <v>8.4294835486117978E-2</v>
       </c>
       <c r="R58" s="14">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
-        <v>225</v>
+        <v>337</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E59">
-        <v>127.7</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>84329627648</v>
+        <v>2514099456</v>
       </c>
       <c r="H59" s="6">
-        <v>149.5</v>
+        <v>0.68</v>
       </c>
       <c r="I59" s="6">
-        <v>91</v>
+        <v>0.46</v>
       </c>
       <c r="J59" s="12">
-        <f t="shared" si="1"/>
-        <v>0.40329670329670342</v>
+        <f>E59/I59-1</f>
+        <v>5.4347826086956541E-2</v>
       </c>
       <c r="K59" s="11">
-        <v>1.5270164447924823E-2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="13">
-        <v>2635100000</v>
+        <v>756004000</v>
       </c>
       <c r="M59" s="13">
-        <v>13245550000</v>
+        <v>8813758000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O59" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P59" s="12">
-        <v>0.59448158016822761</v>
+        <v>0.30962476292169461</v>
       </c>
       <c r="Q59" s="12">
-        <v>0.19894228627727803</v>
+        <v>8.5775443346640556E-2</v>
       </c>
       <c r="R59" s="14">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="C60" t="s">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="D60" t="s">
-        <v>227</v>
+        <v>341</v>
       </c>
       <c r="E60">
-        <v>1.64</v>
+        <v>5.31</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>1640000000</v>
+        <v>6814004224</v>
       </c>
       <c r="H60" s="6">
-        <v>1.88</v>
+        <v>5.33</v>
       </c>
       <c r="I60" s="6">
-        <v>1.35</v>
+        <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="1"/>
-        <v>0.21481481481481457</v>
+        <f>E60/I60-1</f>
+        <v>0.58035714285714279</v>
       </c>
       <c r="K60" s="11">
-        <v>0.12804878048780488</v>
+        <v>4.8964218455743884E-2</v>
       </c>
       <c r="L60" s="13">
-        <v>315190000</v>
+        <v>2871477000</v>
       </c>
       <c r="M60" s="13">
-        <v>607806000</v>
+        <v>21784665000</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O60" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P60" s="12">
-        <v>0.1742687749876565</v>
+        <v>0.15471463459515128</v>
       </c>
       <c r="Q60" s="12">
-        <v>0.51857007005524791</v>
+        <v>0.1318118502166547</v>
       </c>
       <c r="R60" s="14">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>229</v>
+        <v>101</v>
       </c>
       <c r="E61">
-        <v>15.8</v>
+        <v>415.8</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>143318171648</v>
+        <v>525504643072</v>
       </c>
       <c r="H61" s="6">
-        <v>17.88</v>
+        <v>416.2</v>
       </c>
       <c r="I61" s="6">
-        <v>10.6</v>
+        <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="1"/>
-        <v>0.49056603773584917</v>
+        <f>E61/I61-1</f>
+        <v>0.90384615384615374</v>
       </c>
       <c r="K61" s="11">
-        <v>4.5506329113924049E-2</v>
+        <v>2.227032227032227E-2</v>
       </c>
       <c r="L61" s="13">
-        <v>21175963859.630001</v>
+        <v>20744000000</v>
       </c>
       <c r="M61" s="13">
-        <v>104071284594.97</v>
+        <v>53852000000</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O61" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P61" s="12">
-        <v>0.20107063130825906</v>
+        <v>5.2859892025603136E-2</v>
       </c>
       <c r="Q61" s="12">
-        <v>0.20347556909712136</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R61" s="14">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="D62" t="s">
-        <v>231</v>
+        <v>343</v>
       </c>
       <c r="E62">
-        <v>0.69</v>
+        <v>3.76</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>1643724928</v>
+        <v>8539185664</v>
       </c>
       <c r="H62" s="6">
-        <v>1.03</v>
+        <v>5.22</v>
       </c>
       <c r="I62" s="6">
-        <v>0.55000000000000004</v>
+        <v>3.34</v>
       </c>
       <c r="J62" s="12">
-        <f t="shared" si="1"/>
-        <v>0.25454545454545441</v>
+        <f>E62/I62-1</f>
+        <v>0.12574850299401197</v>
       </c>
       <c r="K62" s="11">
-        <v>1.4492753623188408E-2</v>
+        <v>3.9893617021276598E-2</v>
       </c>
       <c r="L62" s="13">
-        <v>54195000</v>
+        <v>826931000</v>
       </c>
       <c r="M62" s="13">
-        <v>586711000</v>
+        <v>5591620000</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O62" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>1.2095413323209785</v>
+        <v>0.13561106154278804</v>
       </c>
       <c r="Q62" s="12">
-        <v>9.2370860611101543E-2</v>
+        <v>0.14788755315990715</v>
       </c>
       <c r="R62" s="14">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="E63">
-        <v>34.200000000000003</v>
+        <v>18.04</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>361589768192</v>
+        <v>509667934208</v>
       </c>
       <c r="H63" s="6">
-        <v>34.6</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="I63" s="6">
-        <v>21.5</v>
+        <v>13.52</v>
       </c>
       <c r="J63" s="12">
-        <f t="shared" si="1"/>
-        <v>0.59069767441860477</v>
+        <f>E63/I63-1</f>
+        <v>0.33431952662721898</v>
       </c>
       <c r="K63" s="11">
-        <v>5.8157894736842103E-2</v>
+        <v>2.1064301552106431E-2</v>
+      </c>
+      <c r="L63" s="13">
+        <v>52374992116</v>
       </c>
       <c r="M63" s="13">
-        <v>415994000000</v>
+        <v>269573093476</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O63" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P63" s="12">
+        <v>8.8265420630244076E-2</v>
+      </c>
+      <c r="Q63" s="12">
+        <v>0.19428864891763736</v>
+      </c>
+      <c r="R63" s="14">
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>327</v>
       </c>
       <c r="D64" t="s">
-        <v>235</v>
+        <v>328</v>
       </c>
       <c r="E64">
-        <v>7.07</v>
+        <v>6.86</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>577521451008</v>
+        <v>17195620352</v>
       </c>
       <c r="H64" s="6">
-        <v>7.27</v>
+        <v>7.03</v>
       </c>
       <c r="I64" s="6">
-        <v>5.08</v>
+        <v>3.99</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="1"/>
-        <v>0.3917322834645669</v>
+        <f>E64/I64-1</f>
+        <v>0.7192982456140351</v>
       </c>
       <c r="K64" s="11">
-        <v>5.3606789250353608E-2</v>
+        <v>4.6793002915451895E-2</v>
+      </c>
+      <c r="L64" s="13">
+        <v>3040816000</v>
       </c>
       <c r="M64" s="13">
-        <v>2314289000000</v>
+        <v>29707522000</v>
       </c>
       <c r="N64" s="9" t="s">
         <v>51</v>
@@ -4789,41 +5122,53 @@
       <c r="O64" s="6">
         <v>1.0683760683760684</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="P64" s="12">
+        <v>0.17317195498769494</v>
+      </c>
+      <c r="Q64" s="12">
+        <v>0.102358453189061</v>
+      </c>
+      <c r="R64" s="14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
-        <v>208</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>236</v>
+        <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>235</v>
+        <v>85</v>
       </c>
       <c r="E65">
-        <v>5.88</v>
+        <v>250.8</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>2603111415808</v>
+        <v>333102546944</v>
       </c>
       <c r="H65" s="6">
-        <v>5.97</v>
+        <v>253</v>
       </c>
       <c r="I65" s="6">
-        <v>4.0599999999999996</v>
+        <v>34.4</v>
       </c>
       <c r="J65" s="12">
-        <f t="shared" si="1"/>
-        <v>0.44827586206896552</v>
+        <f>E65/I65-1</f>
+        <v>6.2906976744186052</v>
       </c>
       <c r="K65" s="11">
-        <v>5.2380952380952382E-2</v>
+        <v>3.2496012759170652E-3</v>
+      </c>
+      <c r="L65" s="13">
+        <v>4414795000</v>
       </c>
       <c r="M65" s="13">
-        <v>6434377000000</v>
+        <v>10683505000</v>
       </c>
       <c r="N65" s="9" t="s">
         <v>51</v>
@@ -4831,136 +5176,2794 @@
       <c r="O65" s="6">
         <v>1.0683760683760684</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="P65" s="12">
+        <v>1.4397344757424192E-2</v>
+      </c>
+      <c r="Q65" s="12">
+        <v>0.41323470153287706</v>
+      </c>
+      <c r="R65" s="14">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C66" t="s">
+        <v>329</v>
+      </c>
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66">
+        <v>2.66</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="7">
+        <v>5020191744</v>
+      </c>
+      <c r="H66" s="6">
+        <v>4.18</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1.74</v>
+      </c>
+      <c r="J66" s="12">
+        <f>E66/I66-1</f>
+        <v>0.52873563218390807</v>
+      </c>
+      <c r="K66" s="11">
+        <v>6.0150375939849621E-2</v>
+      </c>
+      <c r="L66" s="13">
+        <v>896597000</v>
+      </c>
+      <c r="M66" s="13">
+        <v>6906279000</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+      <c r="P66" s="12">
+        <v>0.13554896525280663</v>
+      </c>
+      <c r="Q66" s="12">
+        <v>0.12982345485897689</v>
+      </c>
+      <c r="R66" s="14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" t="s">
+        <v>185</v>
+      </c>
+      <c r="D67" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67">
+        <v>349.2</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G67" s="7">
+        <v>129843740672</v>
+      </c>
+      <c r="H67" s="6">
+        <v>421.4</v>
+      </c>
+      <c r="I67" s="6">
+        <v>225.2</v>
+      </c>
+      <c r="J67" s="12">
+        <f>E67/I67-1</f>
+        <v>0.55062166962699832</v>
+      </c>
+      <c r="K67" s="11">
+        <v>2.0618556701030928E-3</v>
+      </c>
+      <c r="L67" s="13">
+        <v>1200000000</v>
+      </c>
+      <c r="M67" s="13">
+        <v>5855000000</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O67" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P67" s="12">
+        <v>6.463536986601949E-2</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>0.20495303159692571</v>
+      </c>
+      <c r="R67" s="14">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B68" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C68" t="s">
+        <v>324</v>
+      </c>
+      <c r="D68" t="s">
+        <v>325</v>
+      </c>
+      <c r="E68">
+        <v>7.85</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G68" s="7">
+        <v>14188325888</v>
+      </c>
+      <c r="H68" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="I68" s="6">
+        <v>5.49</v>
+      </c>
+      <c r="J68" s="12">
+        <f>E68/I68-1</f>
+        <v>0.42987249544626582</v>
+      </c>
+      <c r="K68" s="11">
+        <v>3.1847133757961783E-2</v>
+      </c>
+      <c r="L68" s="13">
+        <v>2897428000</v>
+      </c>
+      <c r="M68" s="13">
+        <v>25970601000</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O68" s="6">
+        <v>1</v>
+      </c>
+      <c r="P68" s="12">
+        <v>0.15167608287440104</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>0.11156568921912897</v>
+      </c>
+      <c r="R68" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B69" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69">
+        <v>21.95</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="7">
+        <v>24970758144</v>
+      </c>
+      <c r="H69" s="6">
+        <v>28.75</v>
+      </c>
+      <c r="I69" s="6">
+        <v>19.52</v>
+      </c>
+      <c r="J69" s="12">
+        <f>E69/I69-1</f>
+        <v>0.12448770491803285</v>
+      </c>
+      <c r="K69" s="11">
+        <v>6.3781321184510242E-2</v>
+      </c>
+      <c r="L69" s="13">
+        <v>3446618000</v>
+      </c>
+      <c r="M69" s="13">
+        <v>34010798000</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O69" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P69" s="12">
+        <v>0.15508657118243896</v>
+      </c>
+      <c r="Q69" s="12">
+        <v>0.10133893359397213</v>
+      </c>
+      <c r="R69" s="14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" t="s">
+        <v>183</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70">
+        <v>34.35</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G70" s="7">
+        <v>23759206400</v>
+      </c>
+      <c r="H70" s="6">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="I70" s="6">
+        <v>13.48</v>
+      </c>
+      <c r="J70" s="12">
+        <f>E70/I70-1</f>
+        <v>1.5482195845697331</v>
+      </c>
+      <c r="K70" s="11">
+        <v>1.3391557496360991E-2</v>
+      </c>
+      <c r="L70" s="13">
+        <v>1323087000</v>
+      </c>
+      <c r="M70" s="13">
+        <v>5952918000</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O70" s="6">
+        <v>1</v>
+      </c>
+      <c r="P70" s="12">
+        <v>5.0457020931010475E-2</v>
+      </c>
+      <c r="Q70" s="12">
+        <v>0.222258562943417</v>
+      </c>
+      <c r="R70" s="14">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C71" t="s">
+        <v>169</v>
+      </c>
+      <c r="D71" t="s">
+        <v>109</v>
+      </c>
+      <c r="E71">
+        <v>11.8</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G71" s="7">
+        <v>117850251264</v>
+      </c>
+      <c r="H71" s="6">
+        <v>12.16</v>
+      </c>
+      <c r="I71" s="6">
+        <v>5.83</v>
+      </c>
+      <c r="J71" s="12">
+        <f>E71/I71-1</f>
+        <v>1.0240137221269299</v>
+      </c>
+      <c r="K71" s="11">
+        <v>4.2372881355932202E-2</v>
+      </c>
+      <c r="L71" s="13">
+        <v>9432900000</v>
+      </c>
+      <c r="M71" s="13">
+        <v>54338700000</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O71" s="6">
+        <v>1</v>
+      </c>
+      <c r="P71" s="12">
+        <v>6.7355845606612202E-2</v>
+      </c>
+      <c r="Q71" s="12">
+        <v>0.17359450999011755</v>
+      </c>
+      <c r="R71" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B72" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72">
+        <v>6.37</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72" s="7">
+        <v>4963516416</v>
+      </c>
+      <c r="H72" s="6">
+        <v>8.09</v>
+      </c>
+      <c r="I72" s="6">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="J72" s="12">
+        <f>E72/I72-1</f>
+        <v>0.58457711442786087</v>
+      </c>
+      <c r="K72" s="11">
+        <v>2.6687598116169546E-2</v>
+      </c>
+      <c r="L72" s="13">
+        <v>437453000</v>
+      </c>
+      <c r="M72" s="13">
+        <v>4911072000</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O72" s="6">
+        <v>1</v>
+      </c>
+      <c r="P72" s="12">
+        <v>0.16359086438230622</v>
+      </c>
+      <c r="Q72" s="12">
+        <v>8.9074849645861431E-2</v>
+      </c>
+      <c r="R72" s="14">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B73" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" t="s">
+        <v>186</v>
+      </c>
+      <c r="E73">
+        <v>7.1</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" s="7">
+        <v>4073298432</v>
+      </c>
+      <c r="H73" s="6">
+        <v>9.24</v>
+      </c>
+      <c r="I73" s="6">
+        <v>6.85</v>
+      </c>
+      <c r="J73" s="12">
+        <f>E73/I73-1</f>
+        <v>3.649635036496357E-2</v>
+      </c>
+      <c r="K73" s="11">
+        <v>8.0281690140845074E-2</v>
+      </c>
+      <c r="L73" s="13">
+        <v>498120000</v>
+      </c>
+      <c r="M73" s="13">
+        <v>3284848000</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O73" s="6">
+        <v>1</v>
+      </c>
+      <c r="P73" s="12">
+        <v>9.4691024995162451E-2</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0.15164171979951585</v>
+      </c>
+      <c r="R73" s="14">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B74" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74">
+        <v>57.3</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G74" s="7">
+        <v>162066743296</v>
+      </c>
+      <c r="H74" s="6">
+        <v>60</v>
+      </c>
+      <c r="I74" s="6">
+        <v>38.4</v>
+      </c>
+      <c r="J74" s="12">
+        <f>E74/I74-1</f>
+        <v>0.4921875</v>
+      </c>
+      <c r="K74" s="11">
+        <v>3.1413612565445032E-2</v>
+      </c>
+      <c r="L74" s="13">
+        <v>8955723006</v>
+      </c>
+      <c r="M74" s="13">
+        <v>47495870210</v>
+      </c>
+      <c r="N74" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O74" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P74" s="12">
+        <v>6.0550424358519428E-2</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0.18855793075067021</v>
+      </c>
+      <c r="R74" s="14">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B75" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" t="s">
+        <v>174</v>
+      </c>
+      <c r="D75" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75">
+        <v>518</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G75" s="7">
+        <v>4710511149056</v>
+      </c>
+      <c r="H75" s="6">
+        <v>547</v>
+      </c>
+      <c r="I75" s="6">
+        <v>349</v>
+      </c>
+      <c r="J75" s="12">
+        <f>E75/I75-1</f>
+        <v>0.48424068767908302</v>
+      </c>
+      <c r="K75" s="11">
+        <v>8.1640926640926641E-3</v>
+      </c>
+      <c r="L75" s="13">
+        <v>253932000000</v>
+      </c>
+      <c r="M75" s="13">
+        <v>1312163000000</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O75" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P75" s="12">
+        <v>5.4790117301248893E-2</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0.19352168899747973</v>
+      </c>
+      <c r="R75" s="14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B76" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C76" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76">
+        <v>6.27</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G76" s="7">
+        <v>10199472128</v>
+      </c>
+      <c r="H76" s="6">
+        <v>7.05</v>
+      </c>
+      <c r="I76" s="6">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="J76" s="12">
+        <f>E76/I76-1</f>
+        <v>0.46838407494145207</v>
+      </c>
+      <c r="K76" s="11">
+        <v>4.4657097288676242E-2</v>
+      </c>
+      <c r="L76" s="13">
+        <v>4094312000</v>
+      </c>
+      <c r="M76" s="13">
+        <v>37637054000</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O76" s="6">
+        <v>1</v>
+      </c>
+      <c r="P76" s="12">
+        <v>0.13373172758010426</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0.10878407220713927</v>
+      </c>
+      <c r="R76" s="14">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B77" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" t="s">
+        <v>323</v>
+      </c>
+      <c r="D77" t="s">
+        <v>75</v>
+      </c>
+      <c r="E77">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G77" s="7">
+        <v>5736426496</v>
+      </c>
+      <c r="H77" s="6">
+        <v>11.32</v>
+      </c>
+      <c r="I77" s="6">
+        <v>6.56</v>
+      </c>
+      <c r="J77" s="12">
+        <f>E77/I77-1</f>
+        <v>0.29115853658536595</v>
+      </c>
+      <c r="K77" s="11">
+        <v>4.2148760330578509E-2</v>
+      </c>
+      <c r="L77" s="13">
+        <v>618033000</v>
+      </c>
+      <c r="M77" s="13">
+        <v>5033024000</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O77" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P77" s="12">
+        <v>9.7757623133383695E-2</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0.12279555988606453</v>
+      </c>
+      <c r="R77" s="14">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B78" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" t="s">
+        <v>322</v>
+      </c>
+      <c r="D78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78">
+        <v>8.56</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G78" s="7">
+        <v>112932945920</v>
+      </c>
+      <c r="H78" s="6">
+        <v>11</v>
+      </c>
+      <c r="I78" s="6">
+        <v>6.84</v>
+      </c>
+      <c r="J78" s="12">
+        <f>E78/I78-1</f>
+        <v>0.25146198830409361</v>
+      </c>
+      <c r="K78" s="11">
+        <v>0</v>
+      </c>
+      <c r="L78" s="13">
+        <v>1187000000</v>
+      </c>
+      <c r="M78" s="13">
+        <v>10278000000</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O78" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P78" s="12">
+        <v>9.8766188398333774E-2</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0.1154893948238957</v>
+      </c>
+      <c r="R78" s="14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B79" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" t="s">
+        <v>180</v>
+      </c>
+      <c r="D79" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79">
+        <v>14.3</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G79" s="7">
+        <v>60031545344</v>
+      </c>
+      <c r="H79" s="6">
+        <v>15.38</v>
+      </c>
+      <c r="I79" s="6">
+        <v>10.98</v>
+      </c>
+      <c r="J79" s="12">
+        <f>E79/I79-1</f>
+        <v>0.30236794171220405</v>
+      </c>
+      <c r="K79" s="11">
+        <v>6.1958041958041957E-2</v>
+      </c>
+      <c r="L79" s="13">
+        <v>11996000000</v>
+      </c>
+      <c r="M79" s="13">
+        <v>138296000000</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O79" s="6">
+        <v>1</v>
+      </c>
+      <c r="P79" s="12">
+        <v>0.14423548848779913</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>8.6741482038526066E-2</v>
+      </c>
+      <c r="R79" s="14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B80" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C80" t="s">
+        <v>180</v>
+      </c>
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80">
+        <v>14.3</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G80" s="7">
+        <v>60031545344</v>
+      </c>
+      <c r="H80" s="6">
+        <v>15.38</v>
+      </c>
+      <c r="I80" s="6">
+        <v>10.98</v>
+      </c>
+      <c r="J80" s="12">
+        <f>E80/I80-1</f>
+        <v>0.30236794171220405</v>
+      </c>
+      <c r="K80" s="11">
+        <v>6.1958041958041957E-2</v>
+      </c>
+      <c r="L80" s="13">
+        <v>11996000000</v>
+      </c>
+      <c r="M80" s="13">
+        <v>138296000000</v>
+      </c>
+      <c r="N80" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O80" s="6">
+        <v>1</v>
+      </c>
+      <c r="P80" s="12">
+        <v>0.14423548848779913</v>
+      </c>
+      <c r="Q80" s="12">
+        <v>8.6741482038526066E-2</v>
+      </c>
+      <c r="R80" s="14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B81" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" t="s">
+        <v>102</v>
+      </c>
+      <c r="D81" t="s">
+        <v>50</v>
+      </c>
+      <c r="E81">
+        <v>13.14</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G81" s="7">
+        <v>61006786560</v>
+      </c>
+      <c r="H81" s="6">
+        <v>13.44</v>
+      </c>
+      <c r="I81" s="6">
+        <v>7.51</v>
+      </c>
+      <c r="J81" s="12">
+        <f>E81/I81-1</f>
+        <v>0.74966711051930779</v>
+      </c>
+      <c r="K81" s="11">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="L81" s="13">
+        <v>3967214824.1399999</v>
+      </c>
+      <c r="M81" s="13">
+        <v>41038539262.660004</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O81" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P81" s="12">
+        <v>0.1193649041978434</v>
+      </c>
+      <c r="Q81" s="12">
+        <v>9.6670468672106824E-2</v>
+      </c>
+      <c r="R81" s="14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B82" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C82" t="s">
+        <v>321</v>
+      </c>
+      <c r="D82" t="s">
+        <v>156</v>
+      </c>
+      <c r="E82">
+        <v>22.6</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G82" s="7">
+        <v>20811075584</v>
+      </c>
+      <c r="H82" s="6">
+        <v>23.3</v>
+      </c>
+      <c r="I82" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="J82" s="12">
+        <f>E82/I82-1</f>
+        <v>1.2828282828282829</v>
+      </c>
+      <c r="K82" s="11">
+        <v>3.4513274336283183E-3</v>
+      </c>
+      <c r="L82" s="13">
+        <v>302705000</v>
+      </c>
+      <c r="M82" s="13">
+        <v>3112813000</v>
+      </c>
+      <c r="N82" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O82" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P82" s="12">
+        <v>0.11686432780141277</v>
+      </c>
+      <c r="Q82" s="12">
+        <v>9.7244839314150899E-2</v>
+      </c>
+      <c r="R82" s="14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C83" t="s">
+        <v>191</v>
+      </c>
+      <c r="D83" t="s">
+        <v>104</v>
+      </c>
+      <c r="E83">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G83" s="7">
+        <v>73679634432</v>
+      </c>
+      <c r="H83" s="6">
+        <v>61.55</v>
+      </c>
+      <c r="I83" s="6">
+        <v>24.85</v>
+      </c>
+      <c r="J83" s="12">
+        <f>E83/I83-1</f>
+        <v>0.31589537223340036</v>
+      </c>
+      <c r="K83" s="11">
+        <v>1.7370030581039753E-2</v>
+      </c>
+      <c r="L83" s="13">
+        <v>5261270000</v>
+      </c>
+      <c r="M83" s="13">
+        <v>43208997000</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O83" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P83" s="12">
+        <v>7.0742980761826516E-2</v>
+      </c>
+      <c r="Q83" s="12">
+        <v>0.12176329850933591</v>
+      </c>
+      <c r="R83" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B84" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C84" t="s">
+        <v>320</v>
+      </c>
+      <c r="D84" t="s">
+        <v>312</v>
+      </c>
+      <c r="E84">
+        <v>47.2</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G84" s="7">
+        <v>1000592769024</v>
+      </c>
+      <c r="H84" s="6">
+        <v>59.8</v>
+      </c>
+      <c r="I84" s="6">
+        <v>32.65</v>
+      </c>
+      <c r="J84" s="12">
+        <f>E84/I84-1</f>
+        <v>0.44563552833078113</v>
+      </c>
+      <c r="K84" s="11">
+        <v>5.4025423728813554E-2</v>
+      </c>
+      <c r="L84" s="13">
+        <v>189900000000</v>
+      </c>
+      <c r="M84" s="13">
+        <v>2315380000000</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O84" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P84" s="12">
+        <v>0.13743293766692002</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>8.2016774784268678E-2</v>
+      </c>
+      <c r="R84" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B85" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85">
+        <v>1.99</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="7">
+        <v>1847860224</v>
+      </c>
+      <c r="H85" s="6">
+        <v>2.54</v>
+      </c>
+      <c r="I85" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="J85" s="12">
+        <f>E85/I85-1</f>
+        <v>0.15697674418604657</v>
+      </c>
+      <c r="K85" s="11">
+        <v>5.5276381909547742E-2</v>
+      </c>
+      <c r="L85" s="13">
+        <v>238321000</v>
+      </c>
+      <c r="M85" s="13">
+        <v>6087917000</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O85" s="6">
+        <v>1</v>
+      </c>
+      <c r="P85" s="12">
+        <v>0.15959509688418372</v>
+      </c>
+      <c r="Q85" s="12">
+        <v>3.9146558666946343E-2</v>
+      </c>
+      <c r="R85" s="14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B86" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" t="s">
+        <v>157</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G86" s="7">
+        <v>126921875456</v>
+      </c>
+      <c r="H86" s="6">
+        <v>26.6</v>
+      </c>
+      <c r="I86" s="6">
+        <v>16.02</v>
+      </c>
+      <c r="J86" s="12">
+        <f>E86/I86-1</f>
+        <v>0.24344569288389528</v>
+      </c>
+      <c r="K86" s="11">
+        <v>3.564257028112449E-2</v>
+      </c>
+      <c r="L86" s="13">
+        <v>10795274825</v>
+      </c>
+      <c r="M86" s="13">
+        <v>215275428010</v>
+      </c>
+      <c r="N86" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O86" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P86" s="12">
+        <v>0.13819205229155279</v>
+      </c>
+      <c r="Q86" s="12">
+        <v>5.0146340085309396E-2</v>
+      </c>
+      <c r="R86" s="14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B87" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C87" t="s">
+        <v>164</v>
+      </c>
+      <c r="D87" t="s">
+        <v>165</v>
+      </c>
+      <c r="E87">
+        <v>6.06</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G87" s="7">
+        <v>47318056960</v>
+      </c>
+      <c r="H87" s="6">
+        <v>11.72</v>
+      </c>
+      <c r="I87" s="6">
+        <v>5</v>
+      </c>
+      <c r="J87" s="12">
+        <f>E87/I87-1</f>
+        <v>0.21199999999999997</v>
+      </c>
+      <c r="K87" s="11">
+        <v>7.0957095709570955E-2</v>
+      </c>
+      <c r="L87" s="13">
+        <v>6749146000</v>
+      </c>
+      <c r="M87" s="13">
+        <v>70848374000</v>
+      </c>
+      <c r="N87" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O87" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P87" s="12">
+        <v>9.0236955885900208E-2</v>
+      </c>
+      <c r="Q87" s="12">
+        <v>9.5261833390841127E-2</v>
+      </c>
+      <c r="R87" s="14">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B88" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" t="s">
+        <v>182</v>
+      </c>
+      <c r="E88">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88" s="7">
+        <v>19721644032</v>
+      </c>
+      <c r="H88" s="6">
+        <v>11.68</v>
+      </c>
+      <c r="I88" s="6">
+        <v>5.19</v>
+      </c>
+      <c r="J88" s="12">
+        <f>E88/I88-1</f>
+        <v>0.61271676300578015</v>
+      </c>
+      <c r="K88" s="11">
+        <v>0</v>
+      </c>
+      <c r="L88" s="13">
+        <v>13493113000</v>
+      </c>
+      <c r="M88" s="13">
+        <v>208027754000</v>
+      </c>
+      <c r="N88" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O88" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P88" s="12">
+        <v>0.12126103429826435</v>
+      </c>
+      <c r="Q88" s="12">
+        <v>6.4862080854845933E-2</v>
+      </c>
+      <c r="R88" s="14">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89" t="s">
+        <v>66</v>
+      </c>
+      <c r="E89">
+        <v>51.15</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G89" s="7">
+        <v>139287592960</v>
+      </c>
+      <c r="H89" s="6">
+        <v>82.25</v>
+      </c>
+      <c r="I89" s="6">
+        <v>37.85</v>
+      </c>
+      <c r="J89" s="12">
+        <f>E89/I89-1</f>
+        <v>0.35138705416116234</v>
+      </c>
+      <c r="K89" s="11">
+        <v>2.0527859237536659E-2</v>
+      </c>
+      <c r="L89" s="13">
+        <v>6350637223.7200003</v>
+      </c>
+      <c r="M89" s="13">
+        <v>57896384836.860001</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O89" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P89" s="12">
+        <v>6.3055235561581296E-2</v>
+      </c>
+      <c r="Q89" s="12">
+        <v>0.10968970241604512</v>
+      </c>
+      <c r="R89" s="14">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B90" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90">
+        <v>11.42</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G90" s="7">
+        <v>86510608384</v>
+      </c>
+      <c r="H90" s="6">
+        <v>11.6</v>
+      </c>
+      <c r="I90" s="6">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="J90" s="12">
+        <f>E90/I90-1</f>
+        <v>0.33723653395784559</v>
+      </c>
+      <c r="K90" s="11">
+        <v>6.9001751313485113E-2</v>
+      </c>
+      <c r="L90" s="13">
+        <v>8154000000</v>
+      </c>
+      <c r="M90" s="13">
+        <v>79588000000</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O90" s="6">
+        <v>1</v>
+      </c>
+      <c r="P90" s="12">
+        <v>6.3793029121975375E-2</v>
+      </c>
+      <c r="Q90" s="12">
+        <v>0.10245263104990703</v>
+      </c>
+      <c r="R90" s="14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B91" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C91" t="s">
+        <v>318</v>
+      </c>
+      <c r="D91" t="s">
+        <v>314</v>
+      </c>
+      <c r="E91">
+        <v>1.57</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G91" s="7">
+        <v>62827003904</v>
+      </c>
+      <c r="H91" s="6">
+        <v>2.08</v>
+      </c>
+      <c r="I91" s="6">
+        <v>1.18</v>
+      </c>
+      <c r="J91" s="12">
+        <f>E91/I91-1</f>
+        <v>0.33050847457627142</v>
+      </c>
+      <c r="K91" s="11">
+        <v>3.5668789808917196E-2</v>
+      </c>
+      <c r="L91" s="13">
+        <v>12616717000</v>
+      </c>
+      <c r="M91" s="13">
+        <v>231208465000</v>
+      </c>
+      <c r="N91" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O91" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P91" s="12">
+        <v>0.12616891030563587</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>5.4568577322633927E-2</v>
+      </c>
+      <c r="R91" s="14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B92" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" t="s">
+        <v>319</v>
+      </c>
+      <c r="D92" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92">
+        <v>8.1</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G92" s="7">
+        <v>5440867328</v>
+      </c>
+      <c r="H92" s="6">
+        <v>8.32</v>
+      </c>
+      <c r="I92" s="6">
+        <v>5.6</v>
+      </c>
+      <c r="J92" s="12">
+        <f>E92/I92-1</f>
+        <v>0.4464285714285714</v>
+      </c>
+      <c r="K92" s="11">
+        <v>6.2962962962962971E-2</v>
+      </c>
+      <c r="L92" s="13">
+        <v>1136392000</v>
+      </c>
+      <c r="M92" s="13">
+        <v>17458813000</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O92" s="6">
+        <v>1</v>
+      </c>
+      <c r="P92" s="12">
+        <v>0.11296033854832702</v>
+      </c>
+      <c r="Q92" s="12">
+        <v>6.5089877530620205E-2</v>
+      </c>
+      <c r="R92" s="14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B93" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C93" t="s">
+        <v>170</v>
+      </c>
+      <c r="D93" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93">
+        <v>9.93</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G93" s="7">
+        <v>30981601280</v>
+      </c>
+      <c r="H93" s="6">
+        <v>10.1</v>
+      </c>
+      <c r="I93" s="6">
+        <v>5.6</v>
+      </c>
+      <c r="J93" s="12">
+        <f>E93/I93-1</f>
+        <v>0.77321428571428585</v>
+      </c>
+      <c r="K93" s="11">
+        <v>3.2225579053373615E-2</v>
+      </c>
+      <c r="L93" s="13">
+        <v>1990539000</v>
+      </c>
+      <c r="M93" s="13">
+        <v>18620709000</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O93" s="6">
+        <v>1</v>
+      </c>
+      <c r="P93" s="12">
+        <v>5.9005234317736605E-2</v>
+      </c>
+      <c r="Q93" s="12">
+        <v>0.10689920561026972</v>
+      </c>
+      <c r="R93" s="14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="94" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" t="s">
+        <v>150</v>
+      </c>
+      <c r="D94" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94">
+        <v>5.78</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G94" s="7">
+        <v>763225899008</v>
+      </c>
+      <c r="H94" s="6">
+        <v>6.98</v>
+      </c>
+      <c r="I94" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="J94" s="12">
+        <f>E94/I94-1</f>
+        <v>0.41666666666666674</v>
+      </c>
+      <c r="K94" s="11">
+        <v>4.4982698961937718E-2</v>
+      </c>
+      <c r="L94" s="13">
+        <v>44563000000</v>
+      </c>
+      <c r="M94" s="13">
+        <v>463922000000</v>
+      </c>
+      <c r="N94" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O94" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P94" s="12">
+        <v>6.4312320570263509E-2</v>
+      </c>
+      <c r="Q94" s="12">
+        <v>9.605709580489824E-2</v>
+      </c>
+      <c r="R94" s="14">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B95" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" t="s">
+        <v>98</v>
+      </c>
+      <c r="E95">
+        <v>9.56</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G95" s="7">
+        <v>292516888576</v>
+      </c>
+      <c r="H95" s="6">
+        <v>11.56</v>
+      </c>
+      <c r="I95" s="6">
+        <v>5.88</v>
+      </c>
+      <c r="J95" s="12">
+        <f>E95/I95-1</f>
+        <v>0.62585034013605445</v>
+      </c>
+      <c r="K95" s="11">
+        <v>0</v>
+      </c>
+      <c r="L95" s="13">
+        <v>26994000000</v>
+      </c>
+      <c r="M95" s="13">
+        <v>363169000000</v>
+      </c>
+      <c r="N95" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O95" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P95" s="12">
+        <v>9.4688941767454848E-2</v>
+      </c>
+      <c r="Q95" s="12">
+        <v>7.4329031387590908E-2</v>
+      </c>
+      <c r="R95" s="14">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="96" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B96" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" t="s">
+        <v>316</v>
+      </c>
+      <c r="D96" t="s">
+        <v>152</v>
+      </c>
+      <c r="E96">
+        <v>9.4</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G96" s="7">
+        <v>23822137344</v>
+      </c>
+      <c r="H96" s="6">
+        <v>13.78</v>
+      </c>
+      <c r="I96" s="6">
+        <v>5.44</v>
+      </c>
+      <c r="J96" s="12">
+        <f>E96/I96-1</f>
+        <v>0.72794117647058809</v>
+      </c>
+      <c r="K96" s="11">
+        <v>3.1914893617021274E-2</v>
+      </c>
+      <c r="L96" s="13">
+        <v>9652467000</v>
+      </c>
+      <c r="M96" s="13">
+        <v>173514401000</v>
+      </c>
+      <c r="N96" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O96" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P96" s="12">
+        <v>0.10591812417369922</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>5.5629198178196171E-2</v>
+      </c>
+      <c r="R96" s="14">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="97" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B97" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" t="s">
+        <v>152</v>
+      </c>
+      <c r="E97">
+        <v>33.1</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G97" s="7">
+        <v>115842719744</v>
+      </c>
+      <c r="H97" s="6">
+        <v>37.25</v>
+      </c>
+      <c r="I97" s="6">
+        <v>28.1</v>
+      </c>
+      <c r="J97" s="12">
+        <f>E97/I97-1</f>
+        <v>0.17793594306049831</v>
+      </c>
+      <c r="K97" s="11">
+        <v>5.2567975830815711E-2</v>
+      </c>
+      <c r="L97" s="13">
+        <v>16863000000</v>
+      </c>
+      <c r="M97" s="13">
+        <v>448320000000</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O97" s="6">
+        <v>1</v>
+      </c>
+      <c r="P97" s="12">
+        <v>0.12272414883032076</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>3.7613758029978586E-2</v>
+      </c>
+      <c r="R97" s="14">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B98" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98" t="s">
+        <v>158</v>
+      </c>
+      <c r="D98" t="s">
+        <v>152</v>
+      </c>
+      <c r="E98">
+        <v>1.68</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G98" s="7">
+        <v>5979741184</v>
+      </c>
+      <c r="H98" s="6">
+        <v>2.95</v>
+      </c>
+      <c r="I98" s="6">
+        <v>1.37</v>
+      </c>
+      <c r="J98" s="12">
+        <f>E98/I98-1</f>
+        <v>0.22627737226277356</v>
+      </c>
+      <c r="K98" s="11">
+        <v>5.5952380952380955E-2</v>
+      </c>
+      <c r="L98" s="13">
+        <v>2220197000</v>
+      </c>
+      <c r="M98" s="13">
+        <v>71097505000</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O98" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P98" s="12">
+        <v>0.12312120439777445</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>3.1227495254580313E-2</v>
+      </c>
+      <c r="R98" s="14">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B99" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C99" t="s">
+        <v>315</v>
+      </c>
+      <c r="D99" t="s">
+        <v>172</v>
+      </c>
+      <c r="E99">
+        <v>46.1</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G99" s="7">
+        <v>176564846592</v>
+      </c>
+      <c r="H99" s="6">
+        <v>52.95</v>
+      </c>
+      <c r="I99" s="6">
+        <v>36.15</v>
+      </c>
+      <c r="J99" s="12">
+        <f>E99/I99-1</f>
+        <v>0.27524204702627952</v>
+      </c>
+      <c r="K99" s="11">
+        <v>4.7765726681127982E-2</v>
+      </c>
+      <c r="L99" s="13">
+        <v>41737000000</v>
+      </c>
+      <c r="M99" s="13">
+        <v>794927000000</v>
+      </c>
+      <c r="N99" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O99" s="6">
+        <v>1</v>
+      </c>
+      <c r="P99" s="12">
+        <v>0.10983627816766035</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>5.2504192208844336E-2</v>
+      </c>
+      <c r="R99" s="14">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B100" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C100" t="s">
+        <v>313</v>
+      </c>
+      <c r="D100" t="s">
+        <v>314</v>
+      </c>
+      <c r="E100">
+        <v>5.35</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G100" s="7">
+        <v>111841214464</v>
+      </c>
+      <c r="H100" s="6">
+        <v>7.03</v>
+      </c>
+      <c r="I100" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="J100" s="12">
+        <f>E100/I100-1</f>
+        <v>0.26777251184834117</v>
+      </c>
+      <c r="K100" s="11">
+        <v>5.6074766355140186E-2</v>
+      </c>
+      <c r="L100" s="13">
+        <v>42109966000</v>
+      </c>
+      <c r="M100" s="13">
+        <v>746176876000</v>
+      </c>
+      <c r="N100" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O100" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P100" s="12">
+        <v>0.10083557927878818</v>
+      </c>
+      <c r="Q100" s="12">
+        <v>5.643429507724386E-2</v>
+      </c>
+      <c r="R100" s="14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B101" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C101" t="s">
+        <v>179</v>
+      </c>
+      <c r="D101" t="s">
+        <v>98</v>
+      </c>
+      <c r="E101">
+        <v>5.19</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G101" s="7">
+        <v>40176103424</v>
+      </c>
+      <c r="H101" s="6">
+        <v>5.49</v>
+      </c>
+      <c r="I101" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="J101" s="12">
+        <f>E101/I101-1</f>
+        <v>0.36578947368421066</v>
+      </c>
+      <c r="K101" s="11">
+        <v>7.3795761078998073E-2</v>
+      </c>
+      <c r="L101" s="13">
+        <v>5474000000</v>
+      </c>
+      <c r="M101" s="13">
+        <v>59407000000</v>
+      </c>
+      <c r="N101" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O101" s="6">
+        <v>1</v>
+      </c>
+      <c r="P101" s="12">
+        <v>5.9610731194064369E-2</v>
+      </c>
+      <c r="Q101" s="12">
+        <v>9.2144023431582137E-2</v>
+      </c>
+      <c r="R101" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="102" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B102" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" t="s">
+        <v>92</v>
+      </c>
+      <c r="D102" t="s">
+        <v>93</v>
+      </c>
+      <c r="E102">
+        <v>1.35</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G102" s="7">
+        <v>7374415872</v>
+      </c>
+      <c r="H102" s="6">
+        <v>1.82</v>
+      </c>
+      <c r="I102" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="J102" s="12">
+        <f>E102/I102-1</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="K102" s="11">
+        <v>2.5185185185185185E-2</v>
+      </c>
+      <c r="L102" s="13">
+        <v>1384865000</v>
+      </c>
+      <c r="M102" s="13">
+        <v>23827484000</v>
+      </c>
+      <c r="N102" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O102" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P102" s="12">
+        <v>8.0028608509338919E-2</v>
+      </c>
+      <c r="Q102" s="12">
+        <v>5.8120488088461209E-2</v>
+      </c>
+      <c r="R102" s="14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="103" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B103" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C103" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" t="s">
+        <v>172</v>
+      </c>
+      <c r="E103">
+        <v>24.7</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G103" s="7">
+        <v>27375257600</v>
+      </c>
+      <c r="H103" s="6">
+        <v>24.8</v>
+      </c>
+      <c r="I103" s="6">
+        <v>14.52</v>
+      </c>
+      <c r="J103" s="12">
+        <f>E103/I103-1</f>
+        <v>0.70110192837465557</v>
+      </c>
+      <c r="K103" s="11">
+        <v>3.8056680161943315E-2</v>
+      </c>
+      <c r="L103" s="13">
+        <v>3838344000</v>
+      </c>
+      <c r="M103" s="13">
+        <v>81520873000</v>
+      </c>
+      <c r="N103" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O103" s="6">
+        <v>1</v>
+      </c>
+      <c r="P103" s="12">
+        <v>8.4931868729332158E-2</v>
+      </c>
+      <c r="Q103" s="12">
+        <v>4.7084186647510511E-2</v>
+      </c>
+      <c r="R103" s="14">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B104" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104" t="s">
+        <v>187</v>
+      </c>
+      <c r="D104" t="s">
+        <v>87</v>
+      </c>
+      <c r="E104">
+        <v>1.95</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G104" s="7">
+        <v>3467373056</v>
+      </c>
+      <c r="H104" s="6">
+        <v>2.73</v>
+      </c>
+      <c r="I104" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="J104" s="12">
+        <f>E104/I104-1</f>
+        <v>8.9385474860335101E-2</v>
+      </c>
+      <c r="K104" s="11">
+        <v>2.8717948717948718E-2</v>
+      </c>
+      <c r="L104" s="13">
+        <v>364157000</v>
+      </c>
+      <c r="M104" s="13">
+        <v>7859317000</v>
+      </c>
+      <c r="N104" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O104" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P104" s="12">
+        <v>8.5020754486272387E-2</v>
+      </c>
+      <c r="Q104" s="12">
+        <v>4.6334433386514377E-2</v>
+      </c>
+      <c r="R104" s="14">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C105" t="s">
+        <v>97</v>
+      </c>
+      <c r="D105" t="s">
+        <v>98</v>
+      </c>
+      <c r="E105">
+        <v>11.6</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G105" s="7">
+        <v>204169297920</v>
+      </c>
+      <c r="H105" s="6">
+        <v>12.46</v>
+      </c>
+      <c r="I105" s="6">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="J105" s="12">
+        <f>E105/I105-1</f>
+        <v>0.26086956521739135</v>
+      </c>
+      <c r="K105" s="11">
+        <v>3.5948275862068967E-2</v>
+      </c>
+      <c r="L105" s="13">
+        <v>16758000000</v>
+      </c>
+      <c r="M105" s="13">
+        <v>269590000000</v>
+      </c>
+      <c r="N105" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O105" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P105" s="12">
+        <v>5.9626514955333471E-2</v>
+      </c>
+      <c r="Q105" s="12">
+        <v>6.2161059386475759E-2</v>
+      </c>
+      <c r="R105" s="14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>86</v>
+      </c>
+      <c r="D106" t="s">
+        <v>87</v>
+      </c>
+      <c r="E106">
+        <v>6.86</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G106" s="7">
+        <v>7158684160</v>
+      </c>
+      <c r="H106" s="6">
+        <v>7</v>
+      </c>
+      <c r="I106" s="6">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="J106" s="12">
+        <f>E106/I106-1</f>
+        <v>0.70646766169154263</v>
+      </c>
+      <c r="K106" s="11">
+        <v>0</v>
+      </c>
+      <c r="L106" s="13">
+        <v>303335000</v>
+      </c>
+      <c r="M106" s="13">
+        <v>3620162000</v>
+      </c>
+      <c r="N106" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O106" s="6">
+        <v>1</v>
+      </c>
+      <c r="P106" s="12">
+        <v>5.0016264870190799E-2</v>
+      </c>
+      <c r="Q106" s="12">
+        <v>8.3790449156695201E-2</v>
+      </c>
+      <c r="R106" s="14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="107" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C107" t="s">
+        <v>189</v>
+      </c>
+      <c r="D107" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G107" s="7">
+        <v>9706699776</v>
+      </c>
+      <c r="H107" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="I107" s="6">
+        <v>1.93</v>
+      </c>
+      <c r="J107" s="12">
+        <f>E107/I107-1</f>
+        <v>0.17098445595854916</v>
+      </c>
+      <c r="K107" s="11">
+        <v>4.7345132743362835E-2</v>
+      </c>
+      <c r="L107" s="13">
+        <v>1938532000</v>
+      </c>
+      <c r="M107" s="13">
+        <v>49986396000</v>
+      </c>
+      <c r="N107" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O107" s="6">
+        <v>1</v>
+      </c>
+      <c r="P107" s="12">
+        <v>6.4115012275143504E-2</v>
+      </c>
+      <c r="Q107" s="12">
+        <v>3.8781191586606881E-2</v>
+      </c>
+      <c r="R107" s="14">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B108" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C108" t="s">
+        <v>198</v>
+      </c>
+      <c r="D108" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108">
+        <v>42.25</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G108" s="7">
+        <v>446574034944</v>
+      </c>
+      <c r="H108" s="6">
+        <v>59.7</v>
+      </c>
+      <c r="I108" s="6">
+        <v>15.24</v>
+      </c>
+      <c r="J108" s="12">
+        <f>E108/I108-1</f>
+        <v>1.7723097112860891</v>
+      </c>
+      <c r="K108" s="11">
+        <v>0</v>
+      </c>
+      <c r="L108" s="13">
+        <v>984027000</v>
+      </c>
+      <c r="M108" s="13">
+        <v>32183526000</v>
+      </c>
+      <c r="N108" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O108" s="6">
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P108" s="12">
+        <v>1.5548782898068332E-2</v>
+      </c>
+      <c r="Q108" s="12">
+        <v>3.0575487595734537E-2</v>
+      </c>
+      <c r="R108" s="14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B109" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" t="s">
+        <v>153</v>
+      </c>
+      <c r="D109" t="s">
+        <v>154</v>
+      </c>
+      <c r="E109">
+        <v>13.66</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G109" s="7">
+        <v>14028956672</v>
+      </c>
+      <c r="H109" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="I109" s="6">
+        <v>10.36</v>
+      </c>
+      <c r="J109" s="12">
+        <f>E109/I109-1</f>
+        <v>0.31853281853281867</v>
+      </c>
+      <c r="K109" s="11">
+        <v>7.9062957540263545E-2</v>
+      </c>
+      <c r="L109" s="13">
+        <v>984000000</v>
+      </c>
+      <c r="M109" s="13">
+        <v>101944000000</v>
+      </c>
+      <c r="N109" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O109" s="6">
+        <v>1</v>
+      </c>
+      <c r="P109" s="12">
+        <v>2.5244390409937343E-2</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>9.6523581574197593E-3</v>
+      </c>
+      <c r="R109" s="14">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="110" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B110" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C110" t="s">
+        <v>326</v>
+      </c>
+      <c r="D110" t="s">
+        <v>87</v>
+      </c>
+      <c r="E110">
+        <v>9.74</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G110" s="7">
+        <v>10350211072</v>
+      </c>
+      <c r="H110" s="6">
+        <v>12.88</v>
+      </c>
+      <c r="I110" s="6">
+        <v>4.47</v>
+      </c>
+      <c r="J110" s="12">
+        <f>E110/I110-1</f>
+        <v>1.1789709172259508</v>
+      </c>
+      <c r="K110" s="11">
+        <v>1.0574948665297741E-2</v>
+      </c>
+      <c r="L110" s="13">
+        <v>81340000</v>
+      </c>
+      <c r="M110" s="13">
+        <v>3509401000</v>
+      </c>
+      <c r="N110" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O110" s="6">
+        <v>1</v>
+      </c>
+      <c r="P110" s="12">
+        <v>7.7794209390644568E-3</v>
+      </c>
+      <c r="Q110" s="12">
+        <v>2.3177744578063323E-2</v>
+      </c>
+      <c r="R110" s="14">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B111" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C111" t="s">
+        <v>176</v>
+      </c>
+      <c r="D111" t="s">
+        <v>175</v>
+      </c>
+      <c r="E111">
+        <v>29.2</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G111" s="7">
+        <v>29815828480</v>
+      </c>
+      <c r="H111" s="6">
+        <v>36</v>
+      </c>
+      <c r="I111" s="6">
+        <v>22.4</v>
+      </c>
+      <c r="J111" s="12">
+        <f>E111/I111-1</f>
+        <v>0.3035714285714286</v>
+      </c>
+      <c r="K111" s="11">
+        <v>0</v>
+      </c>
+      <c r="L111" s="13">
+        <v>-90314000</v>
+      </c>
+      <c r="M111" s="13">
+        <v>18374441000</v>
+      </c>
+      <c r="N111" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O111" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P111" s="12">
+        <v>-3.6402784697953479E-3</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>-4.9151971480384084E-3</v>
+      </c>
+      <c r="R111" s="14">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B112" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C112" t="s">
+        <v>232</v>
+      </c>
+      <c r="D112" t="s">
+        <v>233</v>
+      </c>
+      <c r="E112">
+        <v>34.4</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112" s="7">
+        <v>363704320000</v>
+      </c>
+      <c r="H112" s="6">
+        <v>34.6</v>
+      </c>
+      <c r="I112" s="6">
+        <v>21.5</v>
+      </c>
+      <c r="J112" s="12">
+        <f>E112/I112-1</f>
+        <v>0.59999999999999987</v>
+      </c>
+      <c r="K112" s="11">
+        <v>5.7819767441860473E-2</v>
+      </c>
+      <c r="M112" s="13">
+        <v>415994000000</v>
+      </c>
+      <c r="N112" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O112" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B113" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C113" t="s">
+        <v>234</v>
+      </c>
+      <c r="D113" t="s">
+        <v>235</v>
+      </c>
+      <c r="E113">
+        <v>7.2</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G113" s="7">
+        <v>588140642304</v>
+      </c>
+      <c r="H113" s="6">
+        <v>7.27</v>
+      </c>
+      <c r="I113" s="6">
+        <v>5.08</v>
+      </c>
+      <c r="J113" s="12">
+        <f>E113/I113-1</f>
+        <v>0.41732283464566922</v>
+      </c>
+      <c r="K113" s="11">
+        <v>5.2638888888888888E-2</v>
+      </c>
+      <c r="M113" s="13">
+        <v>2314289000000</v>
+      </c>
+      <c r="N113" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O113" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="114" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B114" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C114" t="s">
+        <v>236</v>
+      </c>
+      <c r="D114" t="s">
+        <v>235</v>
+      </c>
+      <c r="E114">
+        <v>5.95</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G114" s="7">
+        <v>2634100506624</v>
+      </c>
+      <c r="H114" s="6">
+        <v>5.97</v>
+      </c>
+      <c r="I114" s="6">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="J114" s="12">
+        <f>E114/I114-1</f>
+        <v>0.4655172413793105</v>
+      </c>
+      <c r="K114" s="11">
+        <v>5.1764705882352942E-2</v>
+      </c>
+      <c r="M114" s="13">
+        <v>6434377000000</v>
+      </c>
+      <c r="N114" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O114" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="115" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B115" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C115" t="s">
         <v>237</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D115" t="s">
         <v>233</v>
       </c>
-      <c r="E66">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" s="7">
-        <v>566177759232</v>
-      </c>
-      <c r="H66" s="6">
+      <c r="E115">
+        <v>5.18</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" s="7">
+        <v>573933617152</v>
+      </c>
+      <c r="H115" s="6">
         <v>5.39</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I115" s="6">
         <v>3.89</v>
       </c>
-      <c r="J66" s="12">
-        <f t="shared" ref="J66:J68" si="2">E66/I66-1</f>
-        <v>0.31362467866323906</v>
-      </c>
-      <c r="K66" s="11">
+      <c r="J115" s="12">
+        <f>E115/I115-1</f>
+        <v>0.3316195372750641</v>
+      </c>
+      <c r="K115" s="11">
         <v>0</v>
       </c>
-      <c r="M66" s="13">
+      <c r="M115" s="13">
         <v>1271649000000</v>
       </c>
-      <c r="N66" s="9" t="s">
+      <c r="N115" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O66" s="6">
+      <c r="O115" s="6">
         <v>1.0683760683760684</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.5">
-      <c r="B67" s="1" t="s">
+    <row r="116" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B116" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C116" t="s">
         <v>238</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D116" t="s">
         <v>235</v>
       </c>
-      <c r="E67">
-        <v>7.28</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G67" s="7">
-        <v>1844635631616</v>
-      </c>
-      <c r="H67" s="6">
-        <v>7.32</v>
-      </c>
-      <c r="I67" s="6">
+      <c r="E116">
+        <v>7.44</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G116" s="7">
+        <v>1885176987648</v>
+      </c>
+      <c r="H116" s="6">
+        <v>7.44</v>
+      </c>
+      <c r="I116" s="6">
         <v>5.23</v>
       </c>
-      <c r="J67" s="12">
-        <f t="shared" si="2"/>
-        <v>0.39196940726577423</v>
-      </c>
-      <c r="K67" s="11">
-        <v>5.5357142857142862E-2</v>
-      </c>
-      <c r="M67" s="13">
+      <c r="J116" s="12">
+        <f>E116/I116-1</f>
+        <v>0.42256214149139582</v>
+      </c>
+      <c r="K116" s="11">
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="M116" s="13">
         <v>6128626000000</v>
       </c>
-      <c r="N67" s="9" t="s">
+      <c r="N116" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O67" s="6">
+      <c r="O116" s="6">
         <v>1.0683760683760684</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.5">
-      <c r="B68" s="1" t="s">
+    <row r="117" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B117" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C117" t="s">
         <v>239</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D117" t="s">
         <v>233</v>
       </c>
-      <c r="E68">
-        <v>7.21</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G68" s="7">
-        <v>482087305216</v>
-      </c>
-      <c r="H68" s="6">
+      <c r="E117">
+        <v>7.22</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G117" s="7">
+        <v>482755903488</v>
+      </c>
+      <c r="H117" s="6">
         <v>7.3</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I117" s="6">
         <v>4.26</v>
       </c>
-      <c r="J68" s="12">
-        <f t="shared" si="2"/>
-        <v>0.69248826291079824</v>
-      </c>
-      <c r="K68" s="11">
-        <v>4.9237170596393896E-2</v>
-      </c>
-      <c r="M68" s="13">
+      <c r="J117" s="12">
+        <f>E117/I117-1</f>
+        <v>0.69483568075117375</v>
+      </c>
+      <c r="K117" s="11">
+        <v>4.916897506925208E-2</v>
+      </c>
+      <c r="M117" s="13">
         <v>2066897000000</v>
       </c>
-      <c r="N68" s="9" t="s">
+      <c r="N117" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O68" s="6">
+      <c r="O117" s="6">
         <v>1.0683760683760684</v>
+      </c>
+    </row>
+    <row r="118" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B118" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C118" t="s">
+        <v>357</v>
+      </c>
+      <c r="D118" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118">
+        <v>4.17</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G118" s="7">
+        <v>16171593728</v>
+      </c>
+      <c r="H118" s="6">
+        <v>6.97</v>
+      </c>
+      <c r="I118" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="J118" s="12">
+        <f>E118/I118-1</f>
+        <v>0.25225225225225212</v>
+      </c>
+      <c r="K118" s="11">
+        <v>6.4748201438848921E-2</v>
+      </c>
+      <c r="N118" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O118" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:R21" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R58">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R118">
       <sortCondition ref="R1:R21"/>
     </sortState>
   </autoFilter>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2009CB-671F-4706-B5C5-ECA04EBD870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FB9C9E-D338-4320-BD50-683445BC6B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="2" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="377">
   <si>
     <t>Ticker</t>
   </si>
@@ -1185,6 +1185,51 @@
   </si>
   <si>
     <t>361 DEGREES</t>
+  </si>
+  <si>
+    <t>603279.SS</t>
+  </si>
+  <si>
+    <t>600132.SS</t>
+  </si>
+  <si>
+    <t>603338.SS</t>
+  </si>
+  <si>
+    <t>600583.SS</t>
+  </si>
+  <si>
+    <t>002304.SZ</t>
+  </si>
+  <si>
+    <t>600373.SS</t>
+  </si>
+  <si>
+    <t>002557.SZ</t>
+  </si>
+  <si>
+    <t>601166.SS</t>
+  </si>
+  <si>
+    <t>600007.SS</t>
+  </si>
+  <si>
+    <t>300481.SZ</t>
+  </si>
+  <si>
+    <t>KHC</t>
+  </si>
+  <si>
+    <t>SIRI</t>
+  </si>
+  <si>
+    <t>The Kraft Heinz Company</t>
+  </si>
+  <si>
+    <t>SiriusXM Holdings Inc.</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1349,35 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1756,7 +1829,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
         <v>0.31355932203389836</v>
       </c>
       <c r="K2" s="11">
@@ -1810,7 +1883,7 @@
         <v>4.22</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.49763033175355464</v>
       </c>
       <c r="K3" s="11">
@@ -1864,7 +1937,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.25862068965517238</v>
       </c>
       <c r="K4" s="11">
@@ -1918,7 +1991,7 @@
         <v>9.52</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>0.39285714285714279</v>
       </c>
       <c r="K5" s="11">
@@ -1972,7 +2045,7 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.40879120879120867</v>
       </c>
       <c r="K6" s="11">
@@ -2026,7 +2099,7 @@
         <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>0.23703703703703694</v>
       </c>
       <c r="K7" s="11">
@@ -2080,7 +2153,7 @@
         <v>4.58</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>0.47598253275109159</v>
       </c>
       <c r="K8" s="11">
@@ -2134,7 +2207,7 @@
         <v>2.23</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>0.20627802690582953</v>
       </c>
       <c r="K9" s="11">
@@ -2188,7 +2261,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>0.17699115044247815</v>
       </c>
       <c r="K10" s="11">
@@ -2242,7 +2315,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>1.095617529880478</v>
       </c>
       <c r="K11" s="11">
@@ -2296,7 +2369,7 @@
         <v>3.15</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>0.43492063492063493</v>
       </c>
       <c r="K12" s="11">
@@ -2350,7 +2423,7 @@
         <v>2.11</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>0.33175355450236976</v>
       </c>
       <c r="K13" s="11">
@@ -2404,7 +2477,7 @@
         <v>1.36</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>0.11029411764705865</v>
       </c>
       <c r="K14" s="11">
@@ -2458,7 +2531,7 @@
         <v>10.6</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.50566037735849068</v>
       </c>
       <c r="K15" s="11">
@@ -2512,7 +2585,7 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>0.7271523178807946</v>
       </c>
       <c r="K16" s="11">
@@ -2566,7 +2639,7 @@
         <v>4.84</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.52685950413223148</v>
       </c>
       <c r="K17" s="11">
@@ -2620,7 +2693,7 @@
         <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
+        <f t="shared" si="0"/>
         <v>0.96733668341708556</v>
       </c>
       <c r="K18" s="11">
@@ -2674,7 +2747,7 @@
         <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
+        <f t="shared" si="0"/>
         <v>0.20833333333333326</v>
       </c>
       <c r="K19" s="11">
@@ -2728,7 +2801,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
+        <f t="shared" si="0"/>
         <v>0.47599999999999998</v>
       </c>
       <c r="K20" s="11">
@@ -2782,7 +2855,7 @@
         <v>7.96</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
+        <f t="shared" si="0"/>
         <v>0.96733668341708556</v>
       </c>
       <c r="K21" s="11">
@@ -2836,7 +2909,7 @@
         <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f>E22/I22-1</f>
+        <f t="shared" si="0"/>
         <v>0.73809523809523814</v>
       </c>
       <c r="K22" s="11">
@@ -2890,7 +2963,7 @@
         <v>15.7</v>
       </c>
       <c r="J23" s="12">
-        <f>E23/I23-1</f>
+        <f t="shared" si="0"/>
         <v>0.54458598726114649</v>
       </c>
       <c r="K23" s="11">
@@ -2944,7 +3017,7 @@
         <v>12.12</v>
       </c>
       <c r="J24" s="12">
-        <f>E24/I24-1</f>
+        <f t="shared" si="0"/>
         <v>0.16336633663366351</v>
       </c>
       <c r="K24" s="11">
@@ -2998,7 +3071,7 @@
         <v>7.08</v>
       </c>
       <c r="J25" s="12">
-        <f>E25/I25-1</f>
+        <f t="shared" si="0"/>
         <v>0.11299435028248594</v>
       </c>
       <c r="K25" s="11">
@@ -3052,7 +3125,7 @@
         <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f>E26/I26-1</f>
+        <f t="shared" si="0"/>
         <v>0.17318435754189943</v>
       </c>
       <c r="K26" s="11">
@@ -3106,7 +3179,7 @@
         <v>3.46</v>
       </c>
       <c r="J27" s="12">
-        <f>E27/I27-1</f>
+        <f t="shared" si="0"/>
         <v>0.85260115606936426</v>
       </c>
       <c r="K27" s="11">
@@ -3160,7 +3233,7 @@
         <v>6.57</v>
       </c>
       <c r="J28" s="12">
-        <f>E28/I28-1</f>
+        <f t="shared" si="0"/>
         <v>0.40639269406392686</v>
       </c>
       <c r="K28" s="11">
@@ -3214,7 +3287,7 @@
         <v>3.45</v>
       </c>
       <c r="J29" s="12">
-        <f>E29/I29-1</f>
+        <f t="shared" si="0"/>
         <v>0.39130434782608692</v>
       </c>
       <c r="K29" s="11">
@@ -3268,7 +3341,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="J30" s="12">
-        <f>E30/I30-1</f>
+        <f t="shared" si="0"/>
         <v>0.14226375908618882</v>
       </c>
       <c r="K30" s="11">
@@ -3322,7 +3395,7 @@
         <v>3.97</v>
       </c>
       <c r="J31" s="12">
-        <f>E31/I31-1</f>
+        <f t="shared" si="0"/>
         <v>0.38287153652392947</v>
       </c>
       <c r="K31" s="11">
@@ -3376,7 +3449,7 @@
         <v>2.8</v>
       </c>
       <c r="J32" s="12">
-        <f>E32/I32-1</f>
+        <f t="shared" si="0"/>
         <v>0.35714285714285721</v>
       </c>
       <c r="K32" s="11">
@@ -3430,7 +3503,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f>E33/I33-1</f>
+        <f t="shared" si="0"/>
         <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
@@ -3484,7 +3557,7 @@
         <v>8.67</v>
       </c>
       <c r="J34" s="12">
-        <f>E34/I34-1</f>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
         <v>0.30334486735870825</v>
       </c>
       <c r="K34" s="11">
@@ -3538,7 +3611,7 @@
         <v>3.46</v>
       </c>
       <c r="J35" s="12">
-        <f>E35/I35-1</f>
+        <f t="shared" si="1"/>
         <v>0.30635838150289008</v>
       </c>
       <c r="K35" s="11">
@@ -3592,7 +3665,7 @@
         <v>3.22</v>
       </c>
       <c r="J36" s="12">
-        <f>E36/I36-1</f>
+        <f t="shared" si="1"/>
         <v>0.54968944099378869</v>
       </c>
       <c r="K36" s="11">
@@ -3646,7 +3719,7 @@
         <v>3.39</v>
       </c>
       <c r="J37" s="12">
-        <f>E37/I37-1</f>
+        <f t="shared" si="1"/>
         <v>0.734513274336283</v>
       </c>
       <c r="K37" s="11">
@@ -3700,7 +3773,7 @@
         <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f>E38/I38-1</f>
+        <f t="shared" si="1"/>
         <v>1.6203703703703702</v>
       </c>
       <c r="K38" s="11">
@@ -3754,7 +3827,7 @@
         <v>3.58</v>
       </c>
       <c r="J39" s="12">
-        <f>E39/I39-1</f>
+        <f t="shared" si="1"/>
         <v>0.22346368715083798</v>
       </c>
       <c r="K39" s="11">
@@ -3808,7 +3881,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f>E40/I40-1</f>
+        <f t="shared" si="1"/>
         <v>0.3710843373493975</v>
       </c>
       <c r="K40" s="11">
@@ -3862,7 +3935,7 @@
         <v>4.12</v>
       </c>
       <c r="J41" s="12">
-        <f>E41/I41-1</f>
+        <f t="shared" si="1"/>
         <v>0.28398058252427183</v>
       </c>
       <c r="K41" s="11">
@@ -3916,7 +3989,7 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="J42" s="12">
-        <f>E42/I42-1</f>
+        <f t="shared" si="1"/>
         <v>0.46396396396396389</v>
       </c>
       <c r="K42" s="11">
@@ -3970,7 +4043,7 @@
         <v>18.559999999999999</v>
       </c>
       <c r="J43" s="12">
-        <f>E43/I43-1</f>
+        <f t="shared" si="1"/>
         <v>0.43588362068965525</v>
       </c>
       <c r="K43" s="11">
@@ -4024,7 +4097,7 @@
         <v>5.31</v>
       </c>
       <c r="J44" s="12">
-        <f>E44/I44-1</f>
+        <f t="shared" si="1"/>
         <v>0.13182674199623357</v>
       </c>
       <c r="K44" s="11">
@@ -4078,7 +4151,7 @@
         <v>1.33</v>
       </c>
       <c r="J45" s="12">
-        <f>E45/I45-1</f>
+        <f t="shared" si="1"/>
         <v>0.488721804511278</v>
       </c>
       <c r="K45" s="11">
@@ -4132,7 +4205,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="J46" s="12">
-        <f>E46/I46-1</f>
+        <f t="shared" si="1"/>
         <v>1.2551724137931037</v>
       </c>
       <c r="K46" s="11">
@@ -4186,7 +4259,7 @@
         <v>3.71</v>
       </c>
       <c r="J47" s="12">
-        <f>E47/I47-1</f>
+        <f t="shared" si="1"/>
         <v>0.23989218328840956</v>
       </c>
       <c r="K47" s="11">
@@ -4240,7 +4313,7 @@
         <v>3.4</v>
       </c>
       <c r="J48" s="12">
-        <f>E48/I48-1</f>
+        <f t="shared" si="1"/>
         <v>0.19117647058823528</v>
       </c>
       <c r="K48" s="11">
@@ -4294,7 +4367,7 @@
         <v>19.239999999999998</v>
       </c>
       <c r="J49" s="12">
-        <f>E49/I49-1</f>
+        <f t="shared" si="1"/>
         <v>0.2136174636174637</v>
       </c>
       <c r="K49" s="11">
@@ -4348,7 +4421,7 @@
         <v>16.18</v>
       </c>
       <c r="J50" s="12">
-        <f>E50/I50-1</f>
+        <f t="shared" si="1"/>
         <v>0.19283065512979003</v>
       </c>
       <c r="K50" s="11">
@@ -4402,7 +4475,7 @@
         <v>3.15</v>
       </c>
       <c r="J51" s="12">
-        <f>E51/I51-1</f>
+        <f t="shared" si="1"/>
         <v>1.1904761904761907</v>
       </c>
       <c r="K51" s="11">
@@ -4456,7 +4529,7 @@
         <v>55.05</v>
       </c>
       <c r="J52" s="12">
-        <f>E52/I52-1</f>
+        <f t="shared" si="1"/>
         <v>0.4023614895549501</v>
       </c>
       <c r="K52" s="11">
@@ -4510,7 +4583,7 @@
         <v>65.55</v>
       </c>
       <c r="J53" s="12">
-        <f>E53/I53-1</f>
+        <f t="shared" si="1"/>
         <v>0.47520976353928313</v>
       </c>
       <c r="K53" s="11">
@@ -4564,7 +4637,7 @@
         <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f>E54/I54-1</f>
+        <f t="shared" si="1"/>
         <v>0.72457627118644097</v>
       </c>
       <c r="K54" s="11">
@@ -4618,7 +4691,7 @@
         <v>8.81</v>
       </c>
       <c r="J55" s="12">
-        <f>E55/I55-1</f>
+        <f t="shared" si="1"/>
         <v>0.47105561861520995</v>
       </c>
       <c r="K55" s="11">
@@ -4672,7 +4745,7 @@
         <v>43.55</v>
       </c>
       <c r="J56" s="12">
-        <f>E56/I56-1</f>
+        <f t="shared" si="1"/>
         <v>0.15154994259471866</v>
       </c>
       <c r="K56" s="11">
@@ -4726,7 +4799,7 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="J57" s="12">
-        <f>E57/I57-1</f>
+        <f t="shared" si="1"/>
         <v>0.2012578616352203</v>
       </c>
       <c r="K57" s="11">
@@ -4780,7 +4853,7 @@
         <v>7.36</v>
       </c>
       <c r="J58" s="12">
-        <f>E58/I58-1</f>
+        <f t="shared" si="1"/>
         <v>0.44021739130434767</v>
       </c>
       <c r="K58" s="11">
@@ -4834,7 +4907,7 @@
         <v>0.46</v>
       </c>
       <c r="J59" s="12">
-        <f>E59/I59-1</f>
+        <f t="shared" si="1"/>
         <v>5.4347826086956541E-2</v>
       </c>
       <c r="K59" s="11">
@@ -4888,7 +4961,7 @@
         <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f>E60/I60-1</f>
+        <f t="shared" si="1"/>
         <v>0.58035714285714279</v>
       </c>
       <c r="K60" s="11">
@@ -4942,7 +5015,7 @@
         <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f>E61/I61-1</f>
+        <f t="shared" si="1"/>
         <v>0.90384615384615374</v>
       </c>
       <c r="K61" s="11">
@@ -4996,7 +5069,7 @@
         <v>3.34</v>
       </c>
       <c r="J62" s="12">
-        <f>E62/I62-1</f>
+        <f t="shared" si="1"/>
         <v>0.12574850299401197</v>
       </c>
       <c r="K62" s="11">
@@ -5050,7 +5123,7 @@
         <v>13.52</v>
       </c>
       <c r="J63" s="12">
-        <f>E63/I63-1</f>
+        <f t="shared" si="1"/>
         <v>0.33431952662721898</v>
       </c>
       <c r="K63" s="11">
@@ -5104,7 +5177,7 @@
         <v>3.99</v>
       </c>
       <c r="J64" s="12">
-        <f>E64/I64-1</f>
+        <f t="shared" si="1"/>
         <v>0.7192982456140351</v>
       </c>
       <c r="K64" s="11">
@@ -5158,7 +5231,7 @@
         <v>34.4</v>
       </c>
       <c r="J65" s="12">
-        <f>E65/I65-1</f>
+        <f t="shared" si="1"/>
         <v>6.2906976744186052</v>
       </c>
       <c r="K65" s="11">
@@ -5212,7 +5285,7 @@
         <v>1.74</v>
       </c>
       <c r="J66" s="12">
-        <f>E66/I66-1</f>
+        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
         <v>0.52873563218390807</v>
       </c>
       <c r="K66" s="11">
@@ -5266,7 +5339,7 @@
         <v>225.2</v>
       </c>
       <c r="J67" s="12">
-        <f>E67/I67-1</f>
+        <f t="shared" si="2"/>
         <v>0.55062166962699832</v>
       </c>
       <c r="K67" s="11">
@@ -5320,7 +5393,7 @@
         <v>5.49</v>
       </c>
       <c r="J68" s="12">
-        <f>E68/I68-1</f>
+        <f t="shared" si="2"/>
         <v>0.42987249544626582</v>
       </c>
       <c r="K68" s="11">
@@ -5374,7 +5447,7 @@
         <v>19.52</v>
       </c>
       <c r="J69" s="12">
-        <f>E69/I69-1</f>
+        <f t="shared" si="2"/>
         <v>0.12448770491803285</v>
       </c>
       <c r="K69" s="11">
@@ -5428,7 +5501,7 @@
         <v>13.48</v>
       </c>
       <c r="J70" s="12">
-        <f>E70/I70-1</f>
+        <f t="shared" si="2"/>
         <v>1.5482195845697331</v>
       </c>
       <c r="K70" s="11">
@@ -5482,7 +5555,7 @@
         <v>5.83</v>
       </c>
       <c r="J71" s="12">
-        <f>E71/I71-1</f>
+        <f t="shared" si="2"/>
         <v>1.0240137221269299</v>
       </c>
       <c r="K71" s="11">
@@ -5536,7 +5609,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J72" s="12">
-        <f>E72/I72-1</f>
+        <f t="shared" si="2"/>
         <v>0.58457711442786087</v>
       </c>
       <c r="K72" s="11">
@@ -5590,7 +5663,7 @@
         <v>6.85</v>
       </c>
       <c r="J73" s="12">
-        <f>E73/I73-1</f>
+        <f t="shared" si="2"/>
         <v>3.649635036496357E-2</v>
       </c>
       <c r="K73" s="11">
@@ -5644,7 +5717,7 @@
         <v>38.4</v>
       </c>
       <c r="J74" s="12">
-        <f>E74/I74-1</f>
+        <f t="shared" si="2"/>
         <v>0.4921875</v>
       </c>
       <c r="K74" s="11">
@@ -5698,7 +5771,7 @@
         <v>349</v>
       </c>
       <c r="J75" s="12">
-        <f>E75/I75-1</f>
+        <f t="shared" si="2"/>
         <v>0.48424068767908302</v>
       </c>
       <c r="K75" s="11">
@@ -5752,7 +5825,7 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="J76" s="12">
-        <f>E76/I76-1</f>
+        <f t="shared" si="2"/>
         <v>0.46838407494145207</v>
       </c>
       <c r="K76" s="11">
@@ -5806,7 +5879,7 @@
         <v>6.56</v>
       </c>
       <c r="J77" s="12">
-        <f>E77/I77-1</f>
+        <f t="shared" si="2"/>
         <v>0.29115853658536595</v>
       </c>
       <c r="K77" s="11">
@@ -5860,7 +5933,7 @@
         <v>6.84</v>
       </c>
       <c r="J78" s="12">
-        <f>E78/I78-1</f>
+        <f t="shared" si="2"/>
         <v>0.25146198830409361</v>
       </c>
       <c r="K78" s="11">
@@ -5914,7 +5987,7 @@
         <v>10.98</v>
       </c>
       <c r="J79" s="12">
-        <f>E79/I79-1</f>
+        <f t="shared" si="2"/>
         <v>0.30236794171220405</v>
       </c>
       <c r="K79" s="11">
@@ -5968,7 +6041,7 @@
         <v>10.98</v>
       </c>
       <c r="J80" s="12">
-        <f>E80/I80-1</f>
+        <f t="shared" si="2"/>
         <v>0.30236794171220405</v>
       </c>
       <c r="K80" s="11">
@@ -6022,7 +6095,7 @@
         <v>7.51</v>
       </c>
       <c r="J81" s="12">
-        <f>E81/I81-1</f>
+        <f t="shared" si="2"/>
         <v>0.74966711051930779</v>
       </c>
       <c r="K81" s="11">
@@ -6076,7 +6149,7 @@
         <v>9.9</v>
       </c>
       <c r="J82" s="12">
-        <f>E82/I82-1</f>
+        <f t="shared" si="2"/>
         <v>1.2828282828282829</v>
       </c>
       <c r="K82" s="11">
@@ -6130,7 +6203,7 @@
         <v>24.85</v>
       </c>
       <c r="J83" s="12">
-        <f>E83/I83-1</f>
+        <f t="shared" si="2"/>
         <v>0.31589537223340036</v>
       </c>
       <c r="K83" s="11">
@@ -6184,7 +6257,7 @@
         <v>32.65</v>
       </c>
       <c r="J84" s="12">
-        <f>E84/I84-1</f>
+        <f t="shared" si="2"/>
         <v>0.44563552833078113</v>
       </c>
       <c r="K84" s="11">
@@ -6238,7 +6311,7 @@
         <v>1.72</v>
       </c>
       <c r="J85" s="12">
-        <f>E85/I85-1</f>
+        <f t="shared" si="2"/>
         <v>0.15697674418604657</v>
       </c>
       <c r="K85" s="11">
@@ -6292,7 +6365,7 @@
         <v>16.02</v>
       </c>
       <c r="J86" s="12">
-        <f>E86/I86-1</f>
+        <f t="shared" si="2"/>
         <v>0.24344569288389528</v>
       </c>
       <c r="K86" s="11">
@@ -6346,7 +6419,7 @@
         <v>5</v>
       </c>
       <c r="J87" s="12">
-        <f>E87/I87-1</f>
+        <f t="shared" si="2"/>
         <v>0.21199999999999997</v>
       </c>
       <c r="K87" s="11">
@@ -6400,7 +6473,7 @@
         <v>5.19</v>
       </c>
       <c r="J88" s="12">
-        <f>E88/I88-1</f>
+        <f t="shared" si="2"/>
         <v>0.61271676300578015</v>
       </c>
       <c r="K88" s="11">
@@ -6454,7 +6527,7 @@
         <v>37.85</v>
       </c>
       <c r="J89" s="12">
-        <f>E89/I89-1</f>
+        <f t="shared" si="2"/>
         <v>0.35138705416116234</v>
       </c>
       <c r="K89" s="11">
@@ -6508,7 +6581,7 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="J90" s="12">
-        <f>E90/I90-1</f>
+        <f t="shared" si="2"/>
         <v>0.33723653395784559</v>
       </c>
       <c r="K90" s="11">
@@ -6562,7 +6635,7 @@
         <v>1.18</v>
       </c>
       <c r="J91" s="12">
-        <f>E91/I91-1</f>
+        <f t="shared" si="2"/>
         <v>0.33050847457627142</v>
       </c>
       <c r="K91" s="11">
@@ -6616,7 +6689,7 @@
         <v>5.6</v>
       </c>
       <c r="J92" s="12">
-        <f>E92/I92-1</f>
+        <f t="shared" si="2"/>
         <v>0.4464285714285714</v>
       </c>
       <c r="K92" s="11">
@@ -6670,7 +6743,7 @@
         <v>5.6</v>
       </c>
       <c r="J93" s="12">
-        <f>E93/I93-1</f>
+        <f t="shared" si="2"/>
         <v>0.77321428571428585</v>
       </c>
       <c r="K93" s="11">
@@ -6724,7 +6797,7 @@
         <v>4.08</v>
       </c>
       <c r="J94" s="12">
-        <f>E94/I94-1</f>
+        <f t="shared" si="2"/>
         <v>0.41666666666666674</v>
       </c>
       <c r="K94" s="11">
@@ -6778,7 +6851,7 @@
         <v>5.88</v>
       </c>
       <c r="J95" s="12">
-        <f>E95/I95-1</f>
+        <f t="shared" si="2"/>
         <v>0.62585034013605445</v>
       </c>
       <c r="K95" s="11">
@@ -6832,7 +6905,7 @@
         <v>5.44</v>
       </c>
       <c r="J96" s="12">
-        <f>E96/I96-1</f>
+        <f t="shared" si="2"/>
         <v>0.72794117647058809</v>
       </c>
       <c r="K96" s="11">
@@ -6886,7 +6959,7 @@
         <v>28.1</v>
       </c>
       <c r="J97" s="12">
-        <f>E97/I97-1</f>
+        <f t="shared" si="2"/>
         <v>0.17793594306049831</v>
       </c>
       <c r="K97" s="11">
@@ -6940,7 +7013,7 @@
         <v>1.37</v>
       </c>
       <c r="J98" s="12">
-        <f>E98/I98-1</f>
+        <f t="shared" ref="J98:J118" si="3">E98/I98-1</f>
         <v>0.22627737226277356</v>
       </c>
       <c r="K98" s="11">
@@ -6994,7 +7067,7 @@
         <v>36.15</v>
       </c>
       <c r="J99" s="12">
-        <f>E99/I99-1</f>
+        <f t="shared" si="3"/>
         <v>0.27524204702627952</v>
       </c>
       <c r="K99" s="11">
@@ -7048,7 +7121,7 @@
         <v>4.22</v>
       </c>
       <c r="J100" s="12">
-        <f>E100/I100-1</f>
+        <f t="shared" si="3"/>
         <v>0.26777251184834117</v>
       </c>
       <c r="K100" s="11">
@@ -7102,7 +7175,7 @@
         <v>3.8</v>
       </c>
       <c r="J101" s="12">
-        <f>E101/I101-1</f>
+        <f t="shared" si="3"/>
         <v>0.36578947368421066</v>
       </c>
       <c r="K101" s="11">
@@ -7156,7 +7229,7 @@
         <v>0.81</v>
       </c>
       <c r="J102" s="12">
-        <f>E102/I102-1</f>
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K102" s="11">
@@ -7210,7 +7283,7 @@
         <v>14.52</v>
       </c>
       <c r="J103" s="12">
-        <f>E103/I103-1</f>
+        <f t="shared" si="3"/>
         <v>0.70110192837465557</v>
       </c>
       <c r="K103" s="11">
@@ -7264,7 +7337,7 @@
         <v>1.79</v>
       </c>
       <c r="J104" s="12">
-        <f>E104/I104-1</f>
+        <f t="shared" si="3"/>
         <v>8.9385474860335101E-2</v>
       </c>
       <c r="K104" s="11">
@@ -7318,7 +7391,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="J105" s="12">
-        <f>E105/I105-1</f>
+        <f t="shared" si="3"/>
         <v>0.26086956521739135</v>
       </c>
       <c r="K105" s="11">
@@ -7372,7 +7445,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J106" s="12">
-        <f>E106/I106-1</f>
+        <f t="shared" si="3"/>
         <v>0.70646766169154263</v>
       </c>
       <c r="K106" s="11">
@@ -7426,7 +7499,7 @@
         <v>1.93</v>
       </c>
       <c r="J107" s="12">
-        <f>E107/I107-1</f>
+        <f t="shared" si="3"/>
         <v>0.17098445595854916</v>
       </c>
       <c r="K107" s="11">
@@ -7480,7 +7553,7 @@
         <v>15.24</v>
       </c>
       <c r="J108" s="12">
-        <f>E108/I108-1</f>
+        <f t="shared" si="3"/>
         <v>1.7723097112860891</v>
       </c>
       <c r="K108" s="11">
@@ -7534,7 +7607,7 @@
         <v>10.36</v>
       </c>
       <c r="J109" s="12">
-        <f>E109/I109-1</f>
+        <f t="shared" si="3"/>
         <v>0.31853281853281867</v>
       </c>
       <c r="K109" s="11">
@@ -7588,7 +7661,7 @@
         <v>4.47</v>
       </c>
       <c r="J110" s="12">
-        <f>E110/I110-1</f>
+        <f t="shared" si="3"/>
         <v>1.1789709172259508</v>
       </c>
       <c r="K110" s="11">
@@ -7642,7 +7715,7 @@
         <v>22.4</v>
       </c>
       <c r="J111" s="12">
-        <f>E111/I111-1</f>
+        <f t="shared" si="3"/>
         <v>0.3035714285714286</v>
       </c>
       <c r="K111" s="11">
@@ -7696,7 +7769,7 @@
         <v>21.5</v>
       </c>
       <c r="J112" s="12">
-        <f>E112/I112-1</f>
+        <f t="shared" si="3"/>
         <v>0.59999999999999987</v>
       </c>
       <c r="K112" s="11">
@@ -7738,7 +7811,7 @@
         <v>5.08</v>
       </c>
       <c r="J113" s="12">
-        <f>E113/I113-1</f>
+        <f t="shared" si="3"/>
         <v>0.41732283464566922</v>
       </c>
       <c r="K113" s="11">
@@ -7780,7 +7853,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="J114" s="12">
-        <f>E114/I114-1</f>
+        <f t="shared" si="3"/>
         <v>0.4655172413793105</v>
       </c>
       <c r="K114" s="11">
@@ -7822,7 +7895,7 @@
         <v>3.89</v>
       </c>
       <c r="J115" s="12">
-        <f>E115/I115-1</f>
+        <f t="shared" si="3"/>
         <v>0.3316195372750641</v>
       </c>
       <c r="K115" s="11">
@@ -7864,7 +7937,7 @@
         <v>5.23</v>
       </c>
       <c r="J116" s="12">
-        <f>E116/I116-1</f>
+        <f t="shared" si="3"/>
         <v>0.42256214149139582</v>
       </c>
       <c r="K116" s="11">
@@ -7906,7 +7979,7 @@
         <v>4.26</v>
       </c>
       <c r="J117" s="12">
-        <f>E117/I117-1</f>
+        <f t="shared" si="3"/>
         <v>0.69483568075117375</v>
       </c>
       <c r="K117" s="11">
@@ -7948,7 +8021,7 @@
         <v>3.33</v>
       </c>
       <c r="J118" s="12">
-        <f>E118/I118-1</f>
+        <f t="shared" si="3"/>
         <v>0.25225225225225212</v>
       </c>
       <c r="K118" s="11">
@@ -7968,11 +8041,11 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J2:J1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="between">
       <formula>0.001%</formula>
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
       <formula>0.10001</formula>
       <formula>0.2</formula>
     </cfRule>
@@ -7983,7 +8056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B46D05-099C-4A4C-836A-6062A20AA7D3}">
-  <dimension ref="B1:V11"/>
+  <dimension ref="B1:V21"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -8599,19 +8672,79 @@
         <v>8</v>
       </c>
     </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B12" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B13" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B14" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B15" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B16" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="B17" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="B18" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="B19" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="B20" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.5">
+      <c r="B21" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:R11" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R11">
       <sortCondition ref="R1"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="J2:J1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="between">
+      <formula>0.100001</formula>
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+      <formula>0.00001</formula>
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FA5E83-3B3C-124C-A85B-B3DA799E441B}">
-  <dimension ref="B1:V15"/>
+  <dimension ref="B1:V17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -8689,41 +8822,41 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>254</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
       <c r="E2">
-        <v>77.680000000000007</v>
+        <v>22.28</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G2" s="7">
-        <v>3196547584</v>
+        <v>785116032</v>
       </c>
       <c r="H2" s="6">
-        <v>109.52</v>
+        <v>25.04</v>
       </c>
       <c r="I2" s="6">
-        <v>45.55</v>
+        <v>21.19</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J15" si="0">E2/I2-1</f>
-        <v>0.70537870472008812</v>
+        <f>E2/I2-1</f>
+        <v>5.1439358187824524E-2</v>
       </c>
       <c r="K2" s="11">
-        <v>1.5319258496395467E-2</v>
+        <v>8.4649910233393175E-2</v>
       </c>
       <c r="L2" s="13">
-        <v>503000000</v>
+        <v>395695000</v>
       </c>
       <c r="M2" s="13">
-        <v>1851800000</v>
+        <v>675803000</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>72</v>
@@ -8732,52 +8865,52 @@
         <v>1</v>
       </c>
       <c r="P2" s="12">
-        <v>0.13333518592368598</v>
+        <v>0.35126863892056415</v>
       </c>
       <c r="Q2" s="12">
-        <v>0.27162760557295607</v>
+        <v>0.58551826493815506</v>
       </c>
       <c r="R2" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="E3">
-        <v>211.83</v>
+        <v>25.22</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="7">
-        <v>89519775744</v>
+        <v>68255408128</v>
       </c>
       <c r="H3" s="6">
-        <v>236.53</v>
+        <v>29.03</v>
       </c>
       <c r="I3" s="6">
-        <v>103.69</v>
+        <v>21.41</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>1.0429163853794967</v>
+        <f>E3/I3-1</f>
+        <v>0.17795422699673047</v>
       </c>
       <c r="K3" s="11">
-        <v>4.720766652504366E-3</v>
+        <v>5.7097541633624106E-2</v>
       </c>
       <c r="L3" s="13">
-        <v>7886000000</v>
+        <v>32043000000</v>
       </c>
       <c r="M3" s="13">
-        <v>4294000000</v>
+        <v>68927000000</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>72</v>
@@ -8786,52 +8919,52 @@
         <v>1</v>
       </c>
       <c r="P3" s="12">
-        <v>9.1803594690480092E-2</v>
+        <v>0.34660787845597785</v>
       </c>
       <c r="Q3" s="12">
-        <v>1.8365160689333955</v>
+        <v>0.46488313723214414</v>
       </c>
       <c r="R3" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>245</v>
       </c>
       <c r="E4">
-        <v>167.93</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="7">
-        <v>4629678592</v>
+        <v>2375802880</v>
       </c>
       <c r="H4" s="6">
-        <v>202.63</v>
+        <v>153.32</v>
       </c>
       <c r="I4" s="6">
-        <v>156.13999999999999</v>
+        <v>49.92</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>7.5509158447547131E-2</v>
+        <f>E4/I4-1</f>
+        <v>0.41426282051282026</v>
       </c>
       <c r="K4" s="11">
-        <v>2.2032989936282974E-2</v>
+        <v>1.8271954674220964E-2</v>
       </c>
       <c r="L4" s="13">
-        <v>214237000</v>
+        <v>622821000</v>
       </c>
       <c r="M4" s="13">
-        <v>925772000</v>
+        <v>2304738000</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>72</v>
@@ -8840,52 +8973,52 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>4.7356678364130433E-2</v>
+        <v>0.20930784391194221</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.23141443033489886</v>
+        <v>0.27023505491730515</v>
       </c>
       <c r="R4" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>212</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="E5">
-        <v>24.52</v>
+        <v>79.94</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G5" s="7">
-        <v>66273640448</v>
+        <v>3289547008</v>
       </c>
       <c r="H5" s="6">
-        <v>29.03</v>
+        <v>109.52</v>
       </c>
       <c r="I5" s="6">
-        <v>21.41</v>
+        <v>45.55</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.14525922466137309</v>
+        <f>E5/I5-1</f>
+        <v>0.75499451152579589</v>
       </c>
       <c r="K5" s="11">
-        <v>5.872756933115824E-2</v>
+        <v>1.4886164623467601E-2</v>
       </c>
       <c r="L5" s="13">
-        <v>32043000000</v>
+        <v>503000000</v>
       </c>
       <c r="M5" s="13">
-        <v>68927000000</v>
+        <v>1851800000</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>72</v>
@@ -8894,13 +9027,13 @@
         <v>1</v>
       </c>
       <c r="P5" s="12">
-        <v>0.35420077546920636</v>
+        <v>0.13012725280128842</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.46488313723214414</v>
+        <v>0.27162760557295607</v>
       </c>
       <c r="R5" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -8914,13 +9047,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>25.72</v>
+        <v>25.24</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G6" s="7">
-        <v>915956032</v>
+        <v>898862016</v>
       </c>
       <c r="H6" s="6">
         <v>30.19</v>
@@ -8929,11 +9062,11 @@
         <v>17.73</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.45064861816130852</v>
+        <f>E6/I6-1</f>
+        <v>0.42357586012408333</v>
       </c>
       <c r="K6" s="11">
-        <v>7.2900466562986002E-2</v>
+        <v>7.4286846275752771E-2</v>
       </c>
       <c r="L6" s="13">
         <v>394305000</v>
@@ -8948,52 +9081,52 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>0.27032409093251997</v>
+        <v>0.27352962908071204</v>
       </c>
       <c r="Q6" s="12">
         <v>0.18435624112536766</v>
       </c>
       <c r="R6" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>249</v>
       </c>
       <c r="E7">
-        <v>18.55</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G7" s="7">
-        <v>478500928</v>
+        <v>3067271936</v>
       </c>
       <c r="H7" s="6">
-        <v>25.75</v>
+        <v>13.12</v>
       </c>
       <c r="I7" s="6">
-        <v>17.149999999999999</v>
+        <v>9</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>8.163265306122458E-2</v>
+        <f>E7/I7-1</f>
+        <v>3.1111111111111089E-2</v>
       </c>
       <c r="K7" s="11">
-        <v>5.3908355795148244E-2</v>
+        <v>0.10129310344827587</v>
       </c>
       <c r="L7" s="13">
-        <v>51916000</v>
+        <v>738400000</v>
       </c>
       <c r="M7" s="13">
-        <v>301980000</v>
+        <v>3909700000</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>72</v>
@@ -9002,52 +9135,52 @@
         <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>0.12332267292330092</v>
+        <v>0.18037595868551787</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.17191867011060336</v>
+        <v>0.18886359567230221</v>
       </c>
       <c r="R7" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>215</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>68.31</v>
+        <v>205.05</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G8" s="7">
-        <v>2298740736</v>
+        <v>86654541824</v>
       </c>
       <c r="H8" s="6">
-        <v>153.32</v>
+        <v>236.53</v>
       </c>
       <c r="I8" s="6">
-        <v>49.92</v>
+        <v>103.69</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.36838942307692313</v>
+        <f>E8/I8-1</f>
+        <v>0.97752917349792656</v>
       </c>
       <c r="K8" s="11">
-        <v>1.8884497145366712E-2</v>
+        <v>4.8768593026091191E-3</v>
       </c>
       <c r="L8" s="13">
-        <v>622821000</v>
+        <v>7886000000</v>
       </c>
       <c r="M8" s="13">
-        <v>2304738000</v>
+        <v>4294000000</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>72</v>
@@ -9056,52 +9189,52 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.21487257697834797</v>
+        <v>9.4971380047293039E-2</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.27023505491730515</v>
+        <v>1.8365160689333955</v>
       </c>
       <c r="R8" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>89</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>18.79</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="7">
-        <v>10533276672</v>
+        <v>484691840</v>
       </c>
       <c r="H9" s="6">
-        <v>64.66</v>
+        <v>25.75</v>
       </c>
       <c r="I9" s="6">
-        <v>49.19</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>5.712543199837361E-2</v>
+        <f>E9/I9-1</f>
+        <v>9.5626822157434344E-2</v>
       </c>
       <c r="K9" s="11">
-        <v>3.4423076923076924E-2</v>
+        <v>5.3219797764768498E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>1785700000</v>
+        <v>51916000</v>
       </c>
       <c r="M9" s="13">
-        <v>19238500000</v>
+        <v>301980000</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>72</v>
@@ -9110,10 +9243,10 @@
         <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>0.11332901628117967</v>
+        <v>0.12153536652010133</v>
       </c>
       <c r="Q9" s="12">
-        <v>9.2819086727135694E-2</v>
+        <v>0.17191867011060336</v>
       </c>
       <c r="R9" s="14">
         <v>8</v>
@@ -9121,41 +9254,41 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D10" t="s">
-        <v>249</v>
+        <v>87</v>
       </c>
       <c r="E10">
-        <v>9.4600000000000009</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G10" s="7">
-        <v>3126766336</v>
+        <v>754912320</v>
       </c>
       <c r="H10" s="6">
-        <v>13.12</v>
+        <v>105.63</v>
       </c>
       <c r="I10" s="6">
-        <v>9</v>
+        <v>58.47</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>5.1111111111111107E-2</v>
+        <f>E10/I10-1</f>
+        <v>0.10911578587309734</v>
       </c>
       <c r="K10" s="11">
-        <v>9.9365750528541213E-2</v>
+        <v>1.3107170393215113E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>738400000</v>
+        <v>82486000</v>
       </c>
       <c r="M10" s="13">
-        <v>3909700000</v>
+        <v>350680000</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
@@ -9164,52 +9297,52 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.17779206038522605</v>
+        <v>0.10216599944868063</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.18886359567230221</v>
+        <v>0.23521729211817041</v>
       </c>
       <c r="R10" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C11" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="E11">
-        <v>62.17</v>
+        <v>52.21</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="7">
-        <v>723714752</v>
+        <v>10575187968</v>
       </c>
       <c r="H11" s="6">
-        <v>105.63</v>
+        <v>64.66</v>
       </c>
       <c r="I11" s="6">
-        <v>58.47</v>
+        <v>49.19</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>6.3280314691294803E-2</v>
+        <f>E11/I11-1</f>
+        <v>6.1394592396828651E-2</v>
       </c>
       <c r="K11" s="11">
-        <v>1.3672189158758242E-2</v>
+        <v>3.4284619804635125E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>82486000</v>
+        <v>1785700000</v>
       </c>
       <c r="M11" s="13">
-        <v>350680000</v>
+        <v>19238500000</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>72</v>
@@ -9218,52 +9351,52 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.10627245963290494</v>
+        <v>0.11302837321788417</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.23521729211817041</v>
+        <v>9.2819086727135694E-2</v>
       </c>
       <c r="R11" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>140.21</v>
+        <v>170.37</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G12" s="7">
-        <v>242875990016</v>
+        <v>4696947200</v>
       </c>
       <c r="H12" s="6">
-        <v>168.96</v>
+        <v>202.63</v>
       </c>
       <c r="I12" s="6">
-        <v>132.04</v>
+        <v>156.13999999999999</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
-        <v>6.1875189336564773E-2</v>
+        <f>E12/I12-1</f>
+        <v>9.1136159856539223E-2</v>
       </c>
       <c r="K12" s="11">
-        <v>4.7072248769702583E-2</v>
+        <v>2.1717438516170688E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>28100000000</v>
+        <v>214237000</v>
       </c>
       <c r="M12" s="13">
-        <v>176255000000</v>
+        <v>925772000</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>72</v>
@@ -9272,64 +9405,64 @@
         <v>1</v>
       </c>
       <c r="P12" s="12">
-        <v>0.1078131995442187</v>
+        <v>4.6662821024840026E-2</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.1594281013304587</v>
+        <v>0.23141443033489886</v>
       </c>
       <c r="R12" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="E13">
-        <v>17.04</v>
+        <v>143.35</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="7">
-        <v>2599486208</v>
+        <v>248315183104</v>
       </c>
       <c r="H13" s="6">
-        <v>20.81</v>
+        <v>168.96</v>
       </c>
       <c r="I13" s="6">
-        <v>15.43</v>
+        <v>132.04</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
-        <v>0.10434219053791316</v>
+        <f>E13/I13-1</f>
+        <v>8.5655861860042481E-2</v>
       </c>
       <c r="K13" s="11">
-        <v>3.6208920187793425E-2</v>
+        <v>4.6041158004883155E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>408200000</v>
+        <v>28100000000</v>
       </c>
       <c r="M13" s="13">
-        <v>4745800000</v>
+        <v>176255000000</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="O13" s="6">
-        <v>1.1380999999999999</v>
+        <v>1</v>
       </c>
       <c r="P13" s="12">
-        <v>0.10058007692432981</v>
+        <v>0.10560924800347365</v>
       </c>
       <c r="Q13" s="12">
-        <v>8.6012895612963047E-2</v>
+        <v>0.1594281013304587</v>
       </c>
       <c r="R13" s="14">
         <v>10</v>
@@ -9346,13 +9479,13 @@
         <v>109</v>
       </c>
       <c r="E14">
-        <v>15.62</v>
+        <v>16.05</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G14" s="7">
-        <v>347340384</v>
+        <v>356902240</v>
       </c>
       <c r="H14" s="6">
         <v>26.59</v>
@@ -9361,11 +9494,11 @@
         <v>12.85</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
-        <v>0.21556420233463025</v>
+        <f>E14/I14-1</f>
+        <v>0.24902723735408561</v>
       </c>
       <c r="K14" s="11">
-        <v>8.9628681177976954E-2</v>
+        <v>8.7227414330218064E-2</v>
       </c>
       <c r="L14" s="13">
         <v>27140000</v>
@@ -9380,75 +9513,193 @@
         <v>1</v>
       </c>
       <c r="P14" s="12">
-        <v>0.11617634257216922</v>
+        <v>0.11160813421795185</v>
       </c>
       <c r="Q14" s="12">
         <v>5.638554917738179E-2</v>
       </c>
       <c r="R14" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>87</v>
       </c>
       <c r="E15">
-        <v>22.18</v>
+        <v>17.34</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G15" s="7">
-        <v>781592128</v>
+        <v>2645251584</v>
       </c>
       <c r="H15" s="6">
-        <v>25.04</v>
+        <v>20.81</v>
       </c>
       <c r="I15" s="6">
-        <v>21.19</v>
+        <v>15.43</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
-        <v>4.6720151014629563E-2</v>
+        <f>E15/I15-1</f>
+        <v>0.12378483473752433</v>
       </c>
       <c r="K15" s="11">
-        <v>8.5031559963931469E-2</v>
+        <v>3.5582468281430218E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>395695000</v>
+        <v>408200000</v>
       </c>
       <c r="M15" s="13">
-        <v>675803000</v>
+        <v>4745800000</v>
       </c>
       <c r="N15" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="O15" s="6">
+        <v>1.1380999999999999</v>
+      </c>
+      <c r="P15" s="12">
+        <v>9.9593284898116433E-2</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>8.6012895612963047E-2</v>
+      </c>
+      <c r="R15" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+      <c r="B16" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" t="s">
+        <v>374</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16">
+        <v>26.59</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O15" s="6">
+      <c r="G16" s="7">
+        <v>31470327808</v>
+      </c>
+      <c r="H16" s="6">
+        <v>36.53</v>
+      </c>
+      <c r="I16" s="6">
+        <v>26.01</v>
+      </c>
+      <c r="J16" s="12">
+        <f>E16/I16-1</f>
+        <v>2.2299115724721208E-2</v>
+      </c>
+      <c r="K16" s="11">
+        <v>6.0172997367431369E-2</v>
+      </c>
+      <c r="L16" s="13">
+        <v>1768000000</v>
+      </c>
+      <c r="M16" s="13">
+        <v>69054000000</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16" s="6">
         <v>1</v>
       </c>
-      <c r="P15" s="12">
-        <v>0.35237094696693422</v>
-      </c>
-      <c r="Q15" s="12">
-        <v>0.58551826493815506</v>
-      </c>
-      <c r="R15" s="14">
+      <c r="P16" s="12">
+        <v>3.5356232575624674E-2</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>2.5603151157065487E-2</v>
+      </c>
+      <c r="R16" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B17" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17">
+        <v>22.81</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="7">
+        <v>7708068864</v>
+      </c>
+      <c r="H17" s="6">
+        <v>41.6</v>
+      </c>
+      <c r="I17" s="6">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="J17" s="12">
+        <f>E17/I17-1</f>
+        <v>0.22043873729266972</v>
+      </c>
+      <c r="K17" s="11">
+        <v>4.6996931170539241E-2</v>
+      </c>
+      <c r="L17" s="13">
+        <v>-1369000000</v>
+      </c>
+      <c r="M17" s="13">
+        <v>21449000000</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O17" s="6">
         <v>1</v>
+      </c>
+      <c r="P17" s="12">
+        <v>-7.6390532863252328E-2</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>-6.3825819385519136E-2</v>
+      </c>
+      <c r="R17" s="14">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:R4" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R4">
-      <sortCondition ref="R1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R17">
+      <sortCondition ref="R1:R4"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="J2:J1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+      <formula>0.10001</formula>
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+      <formula>0.0000001</formula>
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FB9C9E-D338-4320-BD50-683445BC6B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF7E77-E0C4-4293-BE7A-86B2F13ED349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="2" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="373">
   <si>
     <t>Ticker</t>
   </si>
@@ -452,9 +452,6 @@
     <t>9987.HK</t>
   </si>
   <si>
-    <t>1717.HK</t>
-  </si>
-  <si>
     <t>0322.HK</t>
   </si>
   <si>
@@ -594,9 +591,6 @@
   </si>
   <si>
     <t>Restaurants</t>
-  </si>
-  <si>
-    <t>AUSNUTRIA</t>
   </si>
   <si>
     <t>TINGYI</t>
@@ -692,16 +686,10 @@
     <t>0981.HK</t>
   </si>
   <si>
-    <t>0341.HK</t>
-  </si>
-  <si>
     <t>SMIC</t>
   </si>
   <si>
     <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>CAFE DE CORAL H</t>
   </si>
   <si>
     <t>1258.HK</t>
@@ -1727,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V118"/>
+  <dimension ref="B1:V116"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1808,10 +1796,10 @@
         <v>111</v>
       </c>
       <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
         <v>148</v>
-      </c>
-      <c r="D2" t="s">
-        <v>149</v>
       </c>
       <c r="E2">
         <v>3.1</v>
@@ -1829,7 +1817,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
+        <f>E2/I2-1</f>
         <v>0.31355932203389836</v>
       </c>
       <c r="K2" s="11">
@@ -1859,13 +1847,13 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E3">
         <v>6.32</v>
@@ -1883,7 +1871,7 @@
         <v>4.22</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
+        <f>E3/I3-1</f>
         <v>0.49763033175355464</v>
       </c>
       <c r="K3" s="11">
@@ -1913,13 +1901,13 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4">
         <v>2.92</v>
@@ -1937,7 +1925,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
+        <f>E4/I4-1</f>
         <v>0.25862068965517238</v>
       </c>
       <c r="K4" s="11">
@@ -1991,7 +1979,7 @@
         <v>9.52</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
+        <f>E5/I5-1</f>
         <v>0.39285714285714279</v>
       </c>
       <c r="K5" s="11">
@@ -2021,10 +2009,10 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
         <v>77</v>
@@ -2045,7 +2033,7 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
+        <f>E6/I6-1</f>
         <v>0.40879120879120867</v>
       </c>
       <c r="K6" s="11">
@@ -2075,13 +2063,13 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E7">
         <v>1.67</v>
@@ -2099,7 +2087,7 @@
         <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
+        <f>E7/I7-1</f>
         <v>0.23703703703703694</v>
       </c>
       <c r="K7" s="11">
@@ -2129,13 +2117,13 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E8">
         <v>6.76</v>
@@ -2153,7 +2141,7 @@
         <v>4.58</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
+        <f>E8/I8-1</f>
         <v>0.47598253275109159</v>
       </c>
       <c r="K8" s="11">
@@ -2186,10 +2174,10 @@
         <v>110</v>
       </c>
       <c r="C9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" t="s">
         <v>146</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
       </c>
       <c r="E9">
         <v>2.69</v>
@@ -2207,7 +2195,7 @@
         <v>2.23</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
+        <f>E9/I9-1</f>
         <v>0.20627802690582953</v>
       </c>
       <c r="K9" s="11">
@@ -2237,13 +2225,13 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E10">
         <v>1.33</v>
@@ -2261,7 +2249,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
+        <f>E10/I10-1</f>
         <v>0.17699115044247815</v>
       </c>
       <c r="K10" s="11">
@@ -2291,13 +2279,13 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E11">
         <v>5.26</v>
@@ -2315,7 +2303,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
+        <f>E11/I11-1</f>
         <v>1.095617529880478</v>
       </c>
       <c r="K11" s="11">
@@ -2345,10 +2333,10 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -2369,7 +2357,7 @@
         <v>3.15</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
+        <f>E12/I12-1</f>
         <v>0.43492063492063493</v>
       </c>
       <c r="K12" s="11">
@@ -2423,7 +2411,7 @@
         <v>2.11</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
+        <f>E13/I13-1</f>
         <v>0.33175355450236976</v>
       </c>
       <c r="K13" s="11">
@@ -2453,13 +2441,13 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D14" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E14">
         <v>1.51</v>
@@ -2477,7 +2465,7 @@
         <v>1.36</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
+        <f>E14/I14-1</f>
         <v>0.11029411764705865</v>
       </c>
       <c r="K14" s="11">
@@ -2507,13 +2495,13 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E15">
         <v>15.96</v>
@@ -2531,7 +2519,7 @@
         <v>10.6</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
+        <f>E15/I15-1</f>
         <v>0.50566037735849068</v>
       </c>
       <c r="K15" s="11">
@@ -2561,13 +2549,13 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E16">
         <v>13.04</v>
@@ -2585,7 +2573,7 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="0"/>
+        <f>E16/I16-1</f>
         <v>0.7271523178807946</v>
       </c>
       <c r="K16" s="11">
@@ -2615,10 +2603,10 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
         <v>87</v>
@@ -2639,7 +2627,7 @@
         <v>4.84</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="0"/>
+        <f>E17/I17-1</f>
         <v>0.52685950413223148</v>
       </c>
       <c r="K17" s="11">
@@ -2693,7 +2681,7 @@
         <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="0"/>
+        <f>E18/I18-1</f>
         <v>0.96733668341708556</v>
       </c>
       <c r="K18" s="11">
@@ -2747,7 +2735,7 @@
         <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" si="0"/>
+        <f>E19/I19-1</f>
         <v>0.20833333333333326</v>
       </c>
       <c r="K19" s="11">
@@ -2777,13 +2765,13 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D20" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E20">
         <v>7.38</v>
@@ -2801,7 +2789,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="0"/>
+        <f>E20/I20-1</f>
         <v>0.47599999999999998</v>
       </c>
       <c r="K20" s="11">
@@ -2855,7 +2843,7 @@
         <v>7.96</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="0"/>
+        <f>E21/I21-1</f>
         <v>0.96733668341708556</v>
       </c>
       <c r="K21" s="11">
@@ -2885,10 +2873,10 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s">
         <v>87</v>
@@ -2909,7 +2897,7 @@
         <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="0"/>
+        <f>E22/I22-1</f>
         <v>0.73809523809523814</v>
       </c>
       <c r="K22" s="11">
@@ -2939,10 +2927,10 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C23" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D23" t="s">
         <v>77</v>
@@ -2963,7 +2951,7 @@
         <v>15.7</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="0"/>
+        <f>E23/I23-1</f>
         <v>0.54458598726114649</v>
       </c>
       <c r="K23" s="11">
@@ -3017,7 +3005,7 @@
         <v>12.12</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="0"/>
+        <f>E24/I24-1</f>
         <v>0.16336633663366351</v>
       </c>
       <c r="K24" s="11">
@@ -3071,7 +3059,7 @@
         <v>7.08</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="0"/>
+        <f>E25/I25-1</f>
         <v>0.11299435028248594</v>
       </c>
       <c r="K25" s="11">
@@ -3125,7 +3113,7 @@
         <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="0"/>
+        <f>E26/I26-1</f>
         <v>0.17318435754189943</v>
       </c>
       <c r="K26" s="11">
@@ -3179,7 +3167,7 @@
         <v>3.46</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="0"/>
+        <f>E27/I27-1</f>
         <v>0.85260115606936426</v>
       </c>
       <c r="K27" s="11">
@@ -3209,13 +3197,13 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28">
         <v>9.24</v>
@@ -3233,7 +3221,7 @@
         <v>6.57</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
+        <f>E28/I28-1</f>
         <v>0.40639269406392686</v>
       </c>
       <c r="K28" s="11">
@@ -3266,7 +3254,7 @@
         <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" t="s">
         <v>77</v>
@@ -3287,7 +3275,7 @@
         <v>3.45</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="0"/>
+        <f>E29/I29-1</f>
         <v>0.39130434782608692</v>
       </c>
       <c r="K29" s="11">
@@ -3317,10 +3305,10 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C30" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D30" t="s">
         <v>96</v>
@@ -3341,7 +3329,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
+        <f>E30/I30-1</f>
         <v>0.14226375908618882</v>
       </c>
       <c r="K30" s="11">
@@ -3395,7 +3383,7 @@
         <v>3.97</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="0"/>
+        <f>E31/I31-1</f>
         <v>0.38287153652392947</v>
       </c>
       <c r="K31" s="11">
@@ -3425,10 +3413,10 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C32" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D32" t="s">
         <v>71</v>
@@ -3449,7 +3437,7 @@
         <v>2.8</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
+        <f>E32/I32-1</f>
         <v>0.35714285714285721</v>
       </c>
       <c r="K32" s="11">
@@ -3479,13 +3467,13 @@
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D33" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E33">
         <v>0.69</v>
@@ -3503,7 +3491,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
+        <f>E33/I33-1</f>
         <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
@@ -3533,10 +3521,10 @@
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C34" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D34" t="s">
         <v>61</v>
@@ -3557,7 +3545,7 @@
         <v>8.67</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
+        <f>E34/I34-1</f>
         <v>0.30334486735870825</v>
       </c>
       <c r="K34" s="11">
@@ -3611,7 +3599,7 @@
         <v>3.46</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="1"/>
+        <f>E35/I35-1</f>
         <v>0.30635838150289008</v>
       </c>
       <c r="K35" s="11">
@@ -3665,7 +3653,7 @@
         <v>3.22</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="1"/>
+        <f>E36/I36-1</f>
         <v>0.54968944099378869</v>
       </c>
       <c r="K36" s="11">
@@ -3719,7 +3707,7 @@
         <v>3.39</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="1"/>
+        <f>E37/I37-1</f>
         <v>0.734513274336283</v>
       </c>
       <c r="K37" s="11">
@@ -3749,10 +3737,10 @@
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C38" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D38" t="s">
         <v>50</v>
@@ -3773,7 +3761,7 @@
         <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="1"/>
+        <f>E38/I38-1</f>
         <v>1.6203703703703702</v>
       </c>
       <c r="K38" s="11">
@@ -3803,10 +3791,10 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C39" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D39" t="s">
         <v>98</v>
@@ -3827,7 +3815,7 @@
         <v>3.58</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="1"/>
+        <f>E39/I39-1</f>
         <v>0.22346368715083798</v>
       </c>
       <c r="K39" s="11">
@@ -3857,10 +3845,10 @@
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D40" t="s">
         <v>75</v>
@@ -3881,7 +3869,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="1"/>
+        <f>E40/I40-1</f>
         <v>0.3710843373493975</v>
       </c>
       <c r="K40" s="11">
@@ -3935,7 +3923,7 @@
         <v>4.12</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="1"/>
+        <f>E41/I41-1</f>
         <v>0.28398058252427183</v>
       </c>
       <c r="K41" s="11">
@@ -3965,13 +3953,13 @@
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C42" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E42">
         <v>3.25</v>
@@ -3989,7 +3977,7 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="1"/>
+        <f>E42/I42-1</f>
         <v>0.46396396396396389</v>
       </c>
       <c r="K42" s="11">
@@ -4019,13 +4007,13 @@
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C43" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E43">
         <v>26.65</v>
@@ -4043,7 +4031,7 @@
         <v>18.559999999999999</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="1"/>
+        <f>E43/I43-1</f>
         <v>0.43588362068965525</v>
       </c>
       <c r="K43" s="11">
@@ -4073,13 +4061,13 @@
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C44" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D44" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E44">
         <v>6.01</v>
@@ -4097,7 +4085,7 @@
         <v>5.31</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="1"/>
+        <f>E44/I44-1</f>
         <v>0.13182674199623357</v>
       </c>
       <c r="K44" s="11">
@@ -4127,10 +4115,10 @@
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C45" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D45" t="s">
         <v>83</v>
@@ -4151,7 +4139,7 @@
         <v>1.33</v>
       </c>
       <c r="J45" s="12">
-        <f t="shared" si="1"/>
+        <f>E45/I45-1</f>
         <v>0.488721804511278</v>
       </c>
       <c r="K45" s="11">
@@ -4181,10 +4169,10 @@
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C46" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
@@ -4205,7 +4193,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="J46" s="12">
-        <f t="shared" si="1"/>
+        <f>E46/I46-1</f>
         <v>1.2551724137931037</v>
       </c>
       <c r="K46" s="11">
@@ -4235,10 +4223,10 @@
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D47" t="s">
         <v>98</v>
@@ -4259,7 +4247,7 @@
         <v>3.71</v>
       </c>
       <c r="J47" s="12">
-        <f t="shared" si="1"/>
+        <f>E47/I47-1</f>
         <v>0.23989218328840956</v>
       </c>
       <c r="K47" s="11">
@@ -4289,13 +4277,13 @@
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E48">
         <v>4.05</v>
@@ -4313,7 +4301,7 @@
         <v>3.4</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="1"/>
+        <f>E48/I48-1</f>
         <v>0.19117647058823528</v>
       </c>
       <c r="K48" s="11">
@@ -4343,10 +4331,10 @@
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D49" t="s">
         <v>54</v>
@@ -4367,7 +4355,7 @@
         <v>19.239999999999998</v>
       </c>
       <c r="J49" s="12">
-        <f t="shared" si="1"/>
+        <f>E49/I49-1</f>
         <v>0.2136174636174637</v>
       </c>
       <c r="K49" s="11">
@@ -4397,10 +4385,10 @@
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D50" t="s">
         <v>50</v>
@@ -4421,7 +4409,7 @@
         <v>16.18</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="1"/>
+        <f>E50/I50-1</f>
         <v>0.19283065512979003</v>
       </c>
       <c r="K50" s="11">
@@ -4451,13 +4439,13 @@
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C51" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51">
         <v>6.9</v>
@@ -4475,7 +4463,7 @@
         <v>3.15</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="1"/>
+        <f>E51/I51-1</f>
         <v>1.1904761904761907</v>
       </c>
       <c r="K51" s="11">
@@ -4505,13 +4493,13 @@
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C52" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E52">
         <v>77.2</v>
@@ -4529,7 +4517,7 @@
         <v>55.05</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="1"/>
+        <f>E52/I52-1</f>
         <v>0.4023614895549501</v>
       </c>
       <c r="K52" s="11">
@@ -4562,7 +4550,7 @@
         <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D53" t="s">
         <v>85</v>
@@ -4583,7 +4571,7 @@
         <v>65.55</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="1"/>
+        <f>E53/I53-1</f>
         <v>0.47520976353928313</v>
       </c>
       <c r="K53" s="11">
@@ -4616,10 +4604,10 @@
         <v>113</v>
       </c>
       <c r="C54" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" t="s">
         <v>151</v>
-      </c>
-      <c r="D54" t="s">
-        <v>152</v>
       </c>
       <c r="E54">
         <v>4.07</v>
@@ -4637,7 +4625,7 @@
         <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="1"/>
+        <f>E54/I54-1</f>
         <v>0.72457627118644097</v>
       </c>
       <c r="K54" s="11">
@@ -4667,10 +4655,10 @@
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D55" t="s">
         <v>87</v>
@@ -4691,7 +4679,7 @@
         <v>8.81</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="1"/>
+        <f>E55/I55-1</f>
         <v>0.47105561861520995</v>
       </c>
       <c r="K55" s="11">
@@ -4721,10 +4709,10 @@
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D56" t="s">
         <v>109</v>
@@ -4745,7 +4733,7 @@
         <v>43.55</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="1"/>
+        <f>E56/I56-1</f>
         <v>0.15154994259471866</v>
       </c>
       <c r="K56" s="11">
@@ -4758,7 +4746,7 @@
         <v>4811702000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6">
         <v>8.7546153846153842</v>
@@ -4775,13 +4763,13 @@
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C57" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E57">
         <v>5.73</v>
@@ -4799,7 +4787,7 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="1"/>
+        <f>E57/I57-1</f>
         <v>0.2012578616352203</v>
       </c>
       <c r="K57" s="11">
@@ -4829,10 +4817,10 @@
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C58" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D58" t="s">
         <v>87</v>
@@ -4853,7 +4841,7 @@
         <v>7.36</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="1"/>
+        <f>E58/I58-1</f>
         <v>0.44021739130434767</v>
       </c>
       <c r="K58" s="11">
@@ -4883,10 +4871,10 @@
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -4907,7 +4895,7 @@
         <v>0.46</v>
       </c>
       <c r="J59" s="12">
-        <f t="shared" si="1"/>
+        <f>E59/I59-1</f>
         <v>5.4347826086956541E-2</v>
       </c>
       <c r="K59" s="11">
@@ -4937,13 +4925,13 @@
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D60" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E60">
         <v>5.31</v>
@@ -4961,7 +4949,7 @@
         <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="1"/>
+        <f>E60/I60-1</f>
         <v>0.58035714285714279</v>
       </c>
       <c r="K60" s="11">
@@ -5015,7 +5003,7 @@
         <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="1"/>
+        <f>E61/I61-1</f>
         <v>0.90384615384615374</v>
       </c>
       <c r="K61" s="11">
@@ -5045,13 +5033,13 @@
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D62" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E62">
         <v>3.76</v>
@@ -5069,7 +5057,7 @@
         <v>3.34</v>
       </c>
       <c r="J62" s="12">
-        <f t="shared" si="1"/>
+        <f>E62/I62-1</f>
         <v>0.12574850299401197</v>
       </c>
       <c r="K62" s="11">
@@ -5102,10 +5090,10 @@
         <v>133</v>
       </c>
       <c r="C63" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" t="s">
         <v>177</v>
-      </c>
-      <c r="D63" t="s">
-        <v>178</v>
       </c>
       <c r="E63">
         <v>18.04</v>
@@ -5123,7 +5111,7 @@
         <v>13.52</v>
       </c>
       <c r="J63" s="12">
-        <f t="shared" si="1"/>
+        <f>E63/I63-1</f>
         <v>0.33431952662721898</v>
       </c>
       <c r="K63" s="11">
@@ -5153,13 +5141,13 @@
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C64" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E64">
         <v>6.86</v>
@@ -5177,7 +5165,7 @@
         <v>3.99</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="1"/>
+        <f>E64/I64-1</f>
         <v>0.7192982456140351</v>
       </c>
       <c r="K64" s="11">
@@ -5210,7 +5198,7 @@
         <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D65" t="s">
         <v>85</v>
@@ -5231,7 +5219,7 @@
         <v>34.4</v>
       </c>
       <c r="J65" s="12">
-        <f t="shared" si="1"/>
+        <f>E65/I65-1</f>
         <v>6.2906976744186052</v>
       </c>
       <c r="K65" s="11">
@@ -5261,10 +5249,10 @@
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C66" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D66" t="s">
         <v>50</v>
@@ -5285,7 +5273,7 @@
         <v>1.74</v>
       </c>
       <c r="J66" s="12">
-        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
+        <f>E66/I66-1</f>
         <v>0.52873563218390807</v>
       </c>
       <c r="K66" s="11">
@@ -5318,10 +5306,10 @@
         <v>138</v>
       </c>
       <c r="C67" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" t="s">
         <v>185</v>
-      </c>
-      <c r="D67" t="s">
-        <v>186</v>
       </c>
       <c r="E67">
         <v>349.2</v>
@@ -5339,7 +5327,7 @@
         <v>225.2</v>
       </c>
       <c r="J67" s="12">
-        <f t="shared" si="2"/>
+        <f>E67/I67-1</f>
         <v>0.55062166962699832</v>
       </c>
       <c r="K67" s="11">
@@ -5369,13 +5357,13 @@
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C68" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E68">
         <v>7.85</v>
@@ -5393,7 +5381,7 @@
         <v>5.49</v>
       </c>
       <c r="J68" s="12">
-        <f t="shared" si="2"/>
+        <f>E68/I68-1</f>
         <v>0.42987249544626582</v>
       </c>
       <c r="K68" s="11">
@@ -5426,10 +5414,10 @@
         <v>125</v>
       </c>
       <c r="C69" t="s">
+        <v>166</v>
+      </c>
+      <c r="D69" t="s">
         <v>167</v>
-      </c>
-      <c r="D69" t="s">
-        <v>168</v>
       </c>
       <c r="E69">
         <v>21.95</v>
@@ -5447,7 +5435,7 @@
         <v>19.52</v>
       </c>
       <c r="J69" s="12">
-        <f t="shared" si="2"/>
+        <f>E69/I69-1</f>
         <v>0.12448770491803285</v>
       </c>
       <c r="K69" s="11">
@@ -5480,10 +5468,10 @@
         <v>137</v>
       </c>
       <c r="C70" t="s">
+        <v>182</v>
+      </c>
+      <c r="D70" t="s">
         <v>183</v>
-      </c>
-      <c r="D70" t="s">
-        <v>184</v>
       </c>
       <c r="E70">
         <v>34.35</v>
@@ -5501,7 +5489,7 @@
         <v>13.48</v>
       </c>
       <c r="J70" s="12">
-        <f t="shared" si="2"/>
+        <f>E70/I70-1</f>
         <v>1.5482195845697331</v>
       </c>
       <c r="K70" s="11">
@@ -5534,7 +5522,7 @@
         <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D71" t="s">
         <v>109</v>
@@ -5555,7 +5543,7 @@
         <v>5.83</v>
       </c>
       <c r="J71" s="12">
-        <f t="shared" si="2"/>
+        <f>E71/I71-1</f>
         <v>1.0240137221269299</v>
       </c>
       <c r="K71" s="11">
@@ -5609,7 +5597,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J72" s="12">
-        <f t="shared" si="2"/>
+        <f>E72/I72-1</f>
         <v>0.58457711442786087</v>
       </c>
       <c r="K72" s="11">
@@ -5639,53 +5627,53 @@
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B73" s="1" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="E73">
-        <v>7.1</v>
+        <v>57.3</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>4073298432</v>
+        <v>162066743296</v>
       </c>
       <c r="H73" s="6">
-        <v>9.24</v>
+        <v>60</v>
       </c>
       <c r="I73" s="6">
-        <v>6.85</v>
+        <v>38.4</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" si="2"/>
-        <v>3.649635036496357E-2</v>
+        <f>E73/I73-1</f>
+        <v>0.4921875</v>
       </c>
       <c r="K73" s="11">
-        <v>8.0281690140845074E-2</v>
+        <v>3.1413612565445032E-2</v>
       </c>
       <c r="L73" s="13">
-        <v>498120000</v>
+        <v>8955723006</v>
       </c>
       <c r="M73" s="13">
-        <v>3284848000</v>
+        <v>47495870210</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O73" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>9.4691024995162451E-2</v>
+        <v>6.0550424358519428E-2</v>
       </c>
       <c r="Q73" s="12">
-        <v>0.15164171979951585</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R73" s="14">
         <v>51</v>
@@ -5693,41 +5681,41 @@
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B74" s="1" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E74">
-        <v>57.3</v>
+        <v>518</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>162066743296</v>
+        <v>4710511149056</v>
       </c>
       <c r="H74" s="6">
-        <v>60</v>
+        <v>547</v>
       </c>
       <c r="I74" s="6">
-        <v>38.4</v>
+        <v>349</v>
       </c>
       <c r="J74" s="12">
-        <f t="shared" si="2"/>
-        <v>0.4921875</v>
+        <f>E74/I74-1</f>
+        <v>0.48424068767908302</v>
       </c>
       <c r="K74" s="11">
-        <v>3.1413612565445032E-2</v>
+        <v>8.1640926640926641E-3</v>
       </c>
       <c r="L74" s="13">
-        <v>8955723006</v>
+        <v>253932000000</v>
       </c>
       <c r="M74" s="13">
-        <v>47495870210</v>
+        <v>1312163000000</v>
       </c>
       <c r="N74" s="9" t="s">
         <v>51</v>
@@ -5736,229 +5724,229 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P74" s="12">
-        <v>6.0550424358519428E-2</v>
+        <v>5.4790117301248893E-2</v>
       </c>
       <c r="Q74" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R74" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B75" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="E75">
-        <v>518</v>
+        <v>6.27</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>4710511149056</v>
+        <v>10199472128</v>
       </c>
       <c r="H75" s="6">
-        <v>547</v>
+        <v>7.05</v>
       </c>
       <c r="I75" s="6">
-        <v>349</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J75" s="12">
-        <f t="shared" si="2"/>
-        <v>0.48424068767908302</v>
+        <f>E75/I75-1</f>
+        <v>0.46838407494145207</v>
       </c>
       <c r="K75" s="11">
-        <v>8.1640926640926641E-3</v>
+        <v>4.4657097288676242E-2</v>
       </c>
       <c r="L75" s="13">
-        <v>253932000000</v>
+        <v>4094312000</v>
       </c>
       <c r="M75" s="13">
-        <v>1312163000000</v>
+        <v>37637054000</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O75" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P75" s="12">
-        <v>5.4790117301248893E-2</v>
+        <v>0.13373172758010426</v>
       </c>
       <c r="Q75" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R75" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B76" s="1" t="s">
-        <v>120</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="D76" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E76">
-        <v>6.27</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>10199472128</v>
+        <v>5736426496</v>
       </c>
       <c r="H76" s="6">
-        <v>7.05</v>
+        <v>11.32</v>
       </c>
       <c r="I76" s="6">
-        <v>4.2699999999999996</v>
+        <v>6.56</v>
       </c>
       <c r="J76" s="12">
-        <f t="shared" si="2"/>
-        <v>0.46838407494145207</v>
+        <f>E76/I76-1</f>
+        <v>0.29115853658536595</v>
       </c>
       <c r="K76" s="11">
-        <v>4.4657097288676242E-2</v>
+        <v>4.2148760330578509E-2</v>
       </c>
       <c r="L76" s="13">
-        <v>4094312000</v>
+        <v>618033000</v>
       </c>
       <c r="M76" s="13">
-        <v>37637054000</v>
+        <v>5033024000</v>
       </c>
       <c r="N76" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O76" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>0.13373172758010426</v>
+        <v>9.7757623133383695E-2</v>
       </c>
       <c r="Q76" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.12279555988606453</v>
       </c>
       <c r="R76" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B77" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C77" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D77" t="s">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="E77">
-        <v>8.4700000000000006</v>
+        <v>8.56</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>5736426496</v>
+        <v>112932945920</v>
       </c>
       <c r="H77" s="6">
-        <v>11.32</v>
+        <v>11</v>
       </c>
       <c r="I77" s="6">
-        <v>6.56</v>
+        <v>6.84</v>
       </c>
       <c r="J77" s="12">
-        <f t="shared" si="2"/>
-        <v>0.29115853658536595</v>
+        <f>E77/I77-1</f>
+        <v>0.25146198830409361</v>
       </c>
       <c r="K77" s="11">
-        <v>4.2148760330578509E-2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="13">
-        <v>618033000</v>
+        <v>1187000000</v>
       </c>
       <c r="M77" s="13">
-        <v>5033024000</v>
+        <v>10278000000</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O77" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P77" s="12">
-        <v>9.7757623133383695E-2</v>
+        <v>9.8766188398333774E-2</v>
       </c>
       <c r="Q77" s="12">
-        <v>0.12279555988606453</v>
+        <v>0.1154893948238957</v>
       </c>
       <c r="R77" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B78" s="1" t="s">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
       <c r="D78" t="s">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="E78">
-        <v>8.56</v>
+        <v>14.3</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>112932945920</v>
+        <v>60031545344</v>
       </c>
       <c r="H78" s="6">
-        <v>11</v>
+        <v>15.38</v>
       </c>
       <c r="I78" s="6">
-        <v>6.84</v>
+        <v>10.98</v>
       </c>
       <c r="J78" s="12">
-        <f t="shared" si="2"/>
-        <v>0.25146198830409361</v>
+        <f>E78/I78-1</f>
+        <v>0.30236794171220405</v>
       </c>
       <c r="K78" s="11">
-        <v>0</v>
+        <v>6.1958041958041957E-2</v>
       </c>
       <c r="L78" s="13">
-        <v>1187000000</v>
+        <v>11996000000</v>
       </c>
       <c r="M78" s="13">
-        <v>10278000000</v>
+        <v>138296000000</v>
       </c>
       <c r="N78" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O78" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P78" s="12">
-        <v>9.8766188398333774E-2</v>
+        <v>0.14423548848779913</v>
       </c>
       <c r="Q78" s="12">
-        <v>0.1154893948238957</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R78" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
@@ -5966,7 +5954,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D79" t="s">
         <v>77</v>
@@ -5987,7 +5975,7 @@
         <v>10.98</v>
       </c>
       <c r="J79" s="12">
-        <f t="shared" si="2"/>
+        <f>E79/I79-1</f>
         <v>0.30236794171220405</v>
       </c>
       <c r="K79" s="11">
@@ -6017,107 +6005,107 @@
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B80" s="1" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E80">
-        <v>14.3</v>
+        <v>13.14</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>60031545344</v>
+        <v>61006786560</v>
       </c>
       <c r="H80" s="6">
-        <v>15.38</v>
+        <v>13.44</v>
       </c>
       <c r="I80" s="6">
-        <v>10.98</v>
+        <v>7.51</v>
       </c>
       <c r="J80" s="12">
-        <f t="shared" si="2"/>
-        <v>0.30236794171220405</v>
+        <f>E80/I80-1</f>
+        <v>0.74966711051930779</v>
       </c>
       <c r="K80" s="11">
-        <v>6.1958041958041957E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="L80" s="13">
-        <v>11996000000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M80" s="13">
-        <v>138296000000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N80" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O80" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P80" s="12">
-        <v>0.14423548848779913</v>
+        <v>0.1193649041978434</v>
       </c>
       <c r="Q80" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R80" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B81" s="1" t="s">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>317</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="E81">
-        <v>13.14</v>
+        <v>22.6</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>61006786560</v>
+        <v>20811075584</v>
       </c>
       <c r="H81" s="6">
-        <v>13.44</v>
+        <v>23.3</v>
       </c>
       <c r="I81" s="6">
-        <v>7.51</v>
+        <v>9.9</v>
       </c>
       <c r="J81" s="12">
-        <f t="shared" si="2"/>
-        <v>0.74966711051930779</v>
+        <f>E81/I81-1</f>
+        <v>1.2828282828282829</v>
       </c>
       <c r="K81" s="11">
-        <v>3.3333333333333333E-2</v>
+        <v>3.4513274336283183E-3</v>
       </c>
       <c r="L81" s="13">
-        <v>3967214824.1399999</v>
+        <v>302705000</v>
       </c>
       <c r="M81" s="13">
-        <v>41038539262.660004</v>
+        <v>3112813000</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O81" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P81" s="12">
-        <v>0.1193649041978434</v>
+        <v>0.11686432780141277</v>
       </c>
       <c r="Q81" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>9.7244839314150899E-2</v>
       </c>
       <c r="R81" s="14">
         <v>57</v>
@@ -6125,95 +6113,95 @@
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B82" s="1" t="s">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="C82" t="s">
-        <v>321</v>
+        <v>189</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="E82">
-        <v>22.6</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>20811075584</v>
+        <v>73679634432</v>
       </c>
       <c r="H82" s="6">
-        <v>23.3</v>
+        <v>61.55</v>
       </c>
       <c r="I82" s="6">
-        <v>9.9</v>
+        <v>24.85</v>
       </c>
       <c r="J82" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2828282828282829</v>
+        <f>E82/I82-1</f>
+        <v>0.31589537223340036</v>
       </c>
       <c r="K82" s="11">
-        <v>3.4513274336283183E-3</v>
+        <v>1.7370030581039753E-2</v>
       </c>
       <c r="L82" s="13">
-        <v>302705000</v>
+        <v>5261270000</v>
       </c>
       <c r="M82" s="13">
-        <v>3112813000</v>
+        <v>43208997000</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O82" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P82" s="12">
-        <v>0.11686432780141277</v>
+        <v>7.0742980761826516E-2</v>
       </c>
       <c r="Q82" s="12">
-        <v>9.7244839314150899E-2</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R82" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B83" s="1" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>316</v>
       </c>
       <c r="D83" t="s">
-        <v>104</v>
+        <v>308</v>
       </c>
       <c r="E83">
-        <v>32.700000000000003</v>
+        <v>47.2</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>73679634432</v>
+        <v>1000592769024</v>
       </c>
       <c r="H83" s="6">
-        <v>61.55</v>
+        <v>59.8</v>
       </c>
       <c r="I83" s="6">
-        <v>24.85</v>
+        <v>32.65</v>
       </c>
       <c r="J83" s="12">
-        <f t="shared" si="2"/>
-        <v>0.31589537223340036</v>
+        <f>E83/I83-1</f>
+        <v>0.44563552833078113</v>
       </c>
       <c r="K83" s="11">
-        <v>1.7370030581039753E-2</v>
+        <v>5.4025423728813554E-2</v>
       </c>
       <c r="L83" s="13">
-        <v>5261270000</v>
+        <v>189900000000</v>
       </c>
       <c r="M83" s="13">
-        <v>43208997000</v>
+        <v>2315380000000</v>
       </c>
       <c r="N83" s="9" t="s">
         <v>51</v>
@@ -6222,160 +6210,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P83" s="12">
-        <v>7.0742980761826516E-2</v>
+        <v>0.13743293766692002</v>
       </c>
       <c r="Q83" s="12">
-        <v>0.12176329850933591</v>
+        <v>8.2016774784268678E-2</v>
       </c>
       <c r="R83" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B84" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D84" t="s">
-        <v>312</v>
+        <v>98</v>
       </c>
       <c r="E84">
-        <v>47.2</v>
+        <v>1.99</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>1000592769024</v>
+        <v>1847860224</v>
       </c>
       <c r="H84" s="6">
-        <v>59.8</v>
+        <v>2.54</v>
       </c>
       <c r="I84" s="6">
-        <v>32.65</v>
+        <v>1.72</v>
       </c>
       <c r="J84" s="12">
-        <f t="shared" si="2"/>
-        <v>0.44563552833078113</v>
+        <f>E84/I84-1</f>
+        <v>0.15697674418604657</v>
       </c>
       <c r="K84" s="11">
-        <v>5.4025423728813554E-2</v>
+        <v>5.5276381909547742E-2</v>
       </c>
       <c r="L84" s="13">
-        <v>189900000000</v>
+        <v>238321000</v>
       </c>
       <c r="M84" s="13">
-        <v>2315380000000</v>
+        <v>6087917000</v>
       </c>
       <c r="N84" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O84" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P84" s="12">
-        <v>0.13743293766692002</v>
+        <v>0.15959509688418372</v>
       </c>
       <c r="Q84" s="12">
-        <v>8.2016774784268678E-2</v>
+        <v>3.9146558666946343E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B85" s="1" t="s">
-        <v>264</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
-        <v>317</v>
+        <v>156</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E85">
-        <v>1.99</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>1847860224</v>
+        <v>126921875456</v>
       </c>
       <c r="H85" s="6">
-        <v>2.54</v>
+        <v>26.6</v>
       </c>
       <c r="I85" s="6">
-        <v>1.72</v>
+        <v>16.02</v>
       </c>
       <c r="J85" s="12">
-        <f t="shared" si="2"/>
-        <v>0.15697674418604657</v>
+        <f>E85/I85-1</f>
+        <v>0.24344569288389528</v>
       </c>
       <c r="K85" s="11">
-        <v>5.5276381909547742E-2</v>
+        <v>3.564257028112449E-2</v>
       </c>
       <c r="L85" s="13">
-        <v>238321000</v>
+        <v>10795274825</v>
       </c>
       <c r="M85" s="13">
-        <v>6087917000</v>
+        <v>215275428010</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O85" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>0.15959509688418372</v>
+        <v>0.13819205229155279</v>
       </c>
       <c r="Q85" s="12">
-        <v>3.9146558666946343E-2</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R85" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B86" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="E86">
-        <v>19.920000000000002</v>
+        <v>6.06</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>126921875456</v>
+        <v>47318056960</v>
       </c>
       <c r="H86" s="6">
-        <v>26.6</v>
+        <v>11.72</v>
       </c>
       <c r="I86" s="6">
-        <v>16.02</v>
+        <v>5</v>
       </c>
       <c r="J86" s="12">
-        <f t="shared" si="2"/>
-        <v>0.24344569288389528</v>
+        <f>E86/I86-1</f>
+        <v>0.21199999999999997</v>
       </c>
       <c r="K86" s="11">
-        <v>3.564257028112449E-2</v>
+        <v>7.0957095709570955E-2</v>
       </c>
       <c r="L86" s="13">
-        <v>10795274825</v>
+        <v>6749146000</v>
       </c>
       <c r="M86" s="13">
-        <v>215275428010</v>
+        <v>70848374000</v>
       </c>
       <c r="N86" s="9" t="s">
         <v>51</v>
@@ -6384,52 +6372,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>0.13819205229155279</v>
+        <v>9.0236955885900208E-2</v>
       </c>
       <c r="Q86" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B87" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D87" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E87">
-        <v>6.06</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>47318056960</v>
+        <v>19721644032</v>
       </c>
       <c r="H87" s="6">
-        <v>11.72</v>
+        <v>11.68</v>
       </c>
       <c r="I87" s="6">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="J87" s="12">
-        <f t="shared" si="2"/>
-        <v>0.21199999999999997</v>
+        <f>E87/I87-1</f>
+        <v>0.61271676300578015</v>
       </c>
       <c r="K87" s="11">
-        <v>7.0957095709570955E-2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="13">
-        <v>6749146000</v>
+        <v>13493113000</v>
       </c>
       <c r="M87" s="13">
-        <v>70848374000</v>
+        <v>208027754000</v>
       </c>
       <c r="N87" s="9" t="s">
         <v>51</v>
@@ -6438,52 +6426,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>9.0236955885900208E-2</v>
+        <v>0.12126103429826435</v>
       </c>
       <c r="Q87" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R87" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B88" s="1" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="D88" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="E88">
-        <v>8.3699999999999992</v>
+        <v>51.15</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>19721644032</v>
+        <v>139287592960</v>
       </c>
       <c r="H88" s="6">
-        <v>11.68</v>
+        <v>82.25</v>
       </c>
       <c r="I88" s="6">
-        <v>5.19</v>
+        <v>37.85</v>
       </c>
       <c r="J88" s="12">
-        <f t="shared" si="2"/>
-        <v>0.61271676300578015</v>
+        <f>E88/I88-1</f>
+        <v>0.35138705416116234</v>
       </c>
       <c r="K88" s="11">
-        <v>0</v>
+        <v>2.0527859237536659E-2</v>
       </c>
       <c r="L88" s="13">
-        <v>13493113000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M88" s="13">
-        <v>208027754000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N88" s="9" t="s">
         <v>51</v>
@@ -6492,10 +6480,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>0.12126103429826435</v>
+        <v>6.3055235561581296E-2</v>
       </c>
       <c r="Q88" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R88" s="14">
         <v>63</v>
@@ -6503,107 +6491,107 @@
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B89" s="1" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="D89" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="E89">
-        <v>51.15</v>
+        <v>11.42</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>139287592960</v>
+        <v>86510608384</v>
       </c>
       <c r="H89" s="6">
-        <v>82.25</v>
+        <v>11.6</v>
       </c>
       <c r="I89" s="6">
-        <v>37.85</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="J89" s="12">
-        <f t="shared" si="2"/>
-        <v>0.35138705416116234</v>
+        <f>E89/I89-1</f>
+        <v>0.33723653395784559</v>
       </c>
       <c r="K89" s="11">
-        <v>2.0527859237536659E-2</v>
+        <v>6.9001751313485113E-2</v>
       </c>
       <c r="L89" s="13">
-        <v>6350637223.7200003</v>
+        <v>8154000000</v>
       </c>
       <c r="M89" s="13">
-        <v>57896384836.860001</v>
+        <v>79588000000</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O89" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P89" s="12">
-        <v>6.3055235561581296E-2</v>
+        <v>6.3793029121975375E-2</v>
       </c>
       <c r="Q89" s="12">
-        <v>0.10968970241604512</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R89" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B90" s="1" t="s">
-        <v>129</v>
+        <v>261</v>
       </c>
       <c r="C90" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="D90" t="s">
-        <v>98</v>
+        <v>310</v>
       </c>
       <c r="E90">
-        <v>11.42</v>
+        <v>1.57</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>86510608384</v>
+        <v>62827003904</v>
       </c>
       <c r="H90" s="6">
-        <v>11.6</v>
+        <v>2.08</v>
       </c>
       <c r="I90" s="6">
-        <v>8.5399999999999991</v>
+        <v>1.18</v>
       </c>
       <c r="J90" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33723653395784559</v>
+        <f>E90/I90-1</f>
+        <v>0.33050847457627142</v>
       </c>
       <c r="K90" s="11">
-        <v>6.9001751313485113E-2</v>
+        <v>3.5668789808917196E-2</v>
       </c>
       <c r="L90" s="13">
-        <v>8154000000</v>
+        <v>12616717000</v>
       </c>
       <c r="M90" s="13">
-        <v>79588000000</v>
+        <v>231208465000</v>
       </c>
       <c r="N90" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O90" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>6.3793029121975375E-2</v>
+        <v>0.12616891030563587</v>
       </c>
       <c r="Q90" s="12">
-        <v>0.10245263104990703</v>
+        <v>5.4568577322633927E-2</v>
       </c>
       <c r="R90" s="14">
         <v>64</v>
@@ -6611,53 +6599,53 @@
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B91" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D91" t="s">
-        <v>314</v>
+        <v>109</v>
       </c>
       <c r="E91">
-        <v>1.57</v>
+        <v>8.1</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>62827003904</v>
+        <v>5440867328</v>
       </c>
       <c r="H91" s="6">
-        <v>2.08</v>
+        <v>8.32</v>
       </c>
       <c r="I91" s="6">
-        <v>1.18</v>
+        <v>5.6</v>
       </c>
       <c r="J91" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33050847457627142</v>
+        <f>E91/I91-1</f>
+        <v>0.4464285714285714</v>
       </c>
       <c r="K91" s="11">
-        <v>3.5668789808917196E-2</v>
+        <v>6.2962962962962971E-2</v>
       </c>
       <c r="L91" s="13">
-        <v>12616717000</v>
+        <v>1136392000</v>
       </c>
       <c r="M91" s="13">
-        <v>231208465000</v>
+        <v>17458813000</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O91" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P91" s="12">
-        <v>0.12616891030563587</v>
+        <v>0.11296033854832702</v>
       </c>
       <c r="Q91" s="12">
-        <v>5.4568577322633927E-2</v>
+        <v>6.5089877530620205E-2</v>
       </c>
       <c r="R91" s="14">
         <v>64</v>
@@ -6665,41 +6653,41 @@
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B92" s="1" t="s">
-        <v>266</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>319</v>
+        <v>169</v>
       </c>
       <c r="D92" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E92">
-        <v>8.1</v>
+        <v>9.93</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>5440867328</v>
+        <v>30981601280</v>
       </c>
       <c r="H92" s="6">
-        <v>8.32</v>
+        <v>10.1</v>
       </c>
       <c r="I92" s="6">
         <v>5.6</v>
       </c>
       <c r="J92" s="12">
-        <f t="shared" si="2"/>
-        <v>0.4464285714285714</v>
+        <f>E92/I92-1</f>
+        <v>0.77321428571428585</v>
       </c>
       <c r="K92" s="11">
-        <v>6.2962962962962971E-2</v>
+        <v>3.2225579053373615E-2</v>
       </c>
       <c r="L92" s="13">
-        <v>1136392000</v>
+        <v>1990539000</v>
       </c>
       <c r="M92" s="13">
-        <v>17458813000</v>
+        <v>18620709000</v>
       </c>
       <c r="N92" s="9" t="s">
         <v>68</v>
@@ -6708,106 +6696,106 @@
         <v>1</v>
       </c>
       <c r="P92" s="12">
-        <v>0.11296033854832702</v>
+        <v>5.9005234317736605E-2</v>
       </c>
       <c r="Q92" s="12">
-        <v>6.5089877530620205E-2</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R92" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B93" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D93" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E93">
-        <v>9.93</v>
+        <v>5.78</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>30981601280</v>
+        <v>763225899008</v>
       </c>
       <c r="H93" s="6">
-        <v>10.1</v>
+        <v>6.98</v>
       </c>
       <c r="I93" s="6">
-        <v>5.6</v>
+        <v>4.08</v>
       </c>
       <c r="J93" s="12">
-        <f t="shared" si="2"/>
-        <v>0.77321428571428585</v>
+        <f>E93/I93-1</f>
+        <v>0.41666666666666674</v>
       </c>
       <c r="K93" s="11">
-        <v>3.2225579053373615E-2</v>
+        <v>4.4982698961937718E-2</v>
       </c>
       <c r="L93" s="13">
-        <v>1990539000</v>
+        <v>44563000000</v>
       </c>
       <c r="M93" s="13">
-        <v>18620709000</v>
+        <v>463922000000</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O93" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P93" s="12">
-        <v>5.9005234317736605E-2</v>
+        <v>6.4312320570263509E-2</v>
       </c>
       <c r="Q93" s="12">
-        <v>0.10689920561026972</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R93" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B94" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C94" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D94" t="s">
         <v>98</v>
       </c>
       <c r="E94">
-        <v>5.78</v>
+        <v>9.56</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>763225899008</v>
+        <v>292516888576</v>
       </c>
       <c r="H94" s="6">
-        <v>6.98</v>
+        <v>11.56</v>
       </c>
       <c r="I94" s="6">
-        <v>4.08</v>
+        <v>5.88</v>
       </c>
       <c r="J94" s="12">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666674</v>
+        <f>E94/I94-1</f>
+        <v>0.62585034013605445</v>
       </c>
       <c r="K94" s="11">
-        <v>4.4982698961937718E-2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="13">
-        <v>44563000000</v>
+        <v>26994000000</v>
       </c>
       <c r="M94" s="13">
-        <v>463922000000</v>
+        <v>363169000000</v>
       </c>
       <c r="N94" s="9" t="s">
         <v>51</v>
@@ -6816,52 +6804,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>6.4312320570263509E-2</v>
+        <v>9.4688941767454848E-2</v>
       </c>
       <c r="Q94" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B95" s="1" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>162</v>
+        <v>312</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E95">
-        <v>9.56</v>
+        <v>9.4</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>292516888576</v>
+        <v>23822137344</v>
       </c>
       <c r="H95" s="6">
-        <v>11.56</v>
+        <v>13.78</v>
       </c>
       <c r="I95" s="6">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="J95" s="12">
-        <f t="shared" si="2"/>
-        <v>0.62585034013605445</v>
+        <f>E95/I95-1</f>
+        <v>0.72794117647058809</v>
       </c>
       <c r="K95" s="11">
-        <v>0</v>
+        <v>3.1914893617021274E-2</v>
       </c>
       <c r="L95" s="13">
-        <v>26994000000</v>
+        <v>9652467000</v>
       </c>
       <c r="M95" s="13">
-        <v>363169000000</v>
+        <v>173514401000</v>
       </c>
       <c r="N95" s="9" t="s">
         <v>51</v>
@@ -6870,10 +6858,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P95" s="12">
-        <v>9.4688941767454848E-2</v>
+        <v>0.10591812417369922</v>
       </c>
       <c r="Q95" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>5.5629198178196171E-2</v>
       </c>
       <c r="R95" s="14">
         <v>67</v>
@@ -6881,107 +6869,107 @@
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B96" s="1" t="s">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="C96" t="s">
-        <v>316</v>
+        <v>162</v>
       </c>
       <c r="D96" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E96">
-        <v>9.4</v>
+        <v>33.1</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>23822137344</v>
+        <v>115842719744</v>
       </c>
       <c r="H96" s="6">
-        <v>13.78</v>
+        <v>37.25</v>
       </c>
       <c r="I96" s="6">
-        <v>5.44</v>
+        <v>28.1</v>
       </c>
       <c r="J96" s="12">
-        <f t="shared" si="2"/>
-        <v>0.72794117647058809</v>
+        <f>E96/I96-1</f>
+        <v>0.17793594306049831</v>
       </c>
       <c r="K96" s="11">
-        <v>3.1914893617021274E-2</v>
+        <v>5.2567975830815711E-2</v>
       </c>
       <c r="L96" s="13">
-        <v>9652467000</v>
+        <v>16863000000</v>
       </c>
       <c r="M96" s="13">
-        <v>173514401000</v>
+        <v>448320000000</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O96" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P96" s="12">
-        <v>0.10591812417369922</v>
+        <v>0.12272414883032076</v>
       </c>
       <c r="Q96" s="12">
-        <v>5.5629198178196171E-2</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B97" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C97" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D97" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E97">
-        <v>33.1</v>
+        <v>1.68</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>115842719744</v>
+        <v>5979741184</v>
       </c>
       <c r="H97" s="6">
-        <v>37.25</v>
+        <v>2.95</v>
       </c>
       <c r="I97" s="6">
-        <v>28.1</v>
+        <v>1.37</v>
       </c>
       <c r="J97" s="12">
-        <f t="shared" si="2"/>
-        <v>0.17793594306049831</v>
+        <f>E97/I97-1</f>
+        <v>0.22627737226277356</v>
       </c>
       <c r="K97" s="11">
-        <v>5.2567975830815711E-2</v>
+        <v>5.5952380952380955E-2</v>
       </c>
       <c r="L97" s="13">
-        <v>16863000000</v>
+        <v>2220197000</v>
       </c>
       <c r="M97" s="13">
-        <v>448320000000</v>
+        <v>71097505000</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O97" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>0.12272414883032076</v>
+        <v>0.12312120439777445</v>
       </c>
       <c r="Q97" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R97" s="14">
         <v>68</v>
@@ -6989,53 +6977,53 @@
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B98" s="1" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>158</v>
+        <v>311</v>
       </c>
       <c r="D98" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E98">
-        <v>1.68</v>
+        <v>46.1</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>5979741184</v>
+        <v>176564846592</v>
       </c>
       <c r="H98" s="6">
-        <v>2.95</v>
+        <v>52.95</v>
       </c>
       <c r="I98" s="6">
-        <v>1.37</v>
+        <v>36.15</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J118" si="3">E98/I98-1</f>
-        <v>0.22627737226277356</v>
+        <f>E98/I98-1</f>
+        <v>0.27524204702627952</v>
       </c>
       <c r="K98" s="11">
-        <v>5.5952380952380955E-2</v>
+        <v>4.7765726681127982E-2</v>
       </c>
       <c r="L98" s="13">
-        <v>2220197000</v>
+        <v>41737000000</v>
       </c>
       <c r="M98" s="13">
-        <v>71097505000</v>
+        <v>794927000000</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O98" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P98" s="12">
-        <v>0.12312120439777445</v>
+        <v>0.10983627816766035</v>
       </c>
       <c r="Q98" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>5.2504192208844336E-2</v>
       </c>
       <c r="R98" s="14">
         <v>68</v>
@@ -7043,473 +7031,473 @@
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B99" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D99" t="s">
-        <v>172</v>
+        <v>310</v>
       </c>
       <c r="E99">
-        <v>46.1</v>
+        <v>5.35</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>176564846592</v>
+        <v>111841214464</v>
       </c>
       <c r="H99" s="6">
-        <v>52.95</v>
+        <v>7.03</v>
       </c>
       <c r="I99" s="6">
-        <v>36.15</v>
+        <v>4.22</v>
       </c>
       <c r="J99" s="12">
-        <f t="shared" si="3"/>
-        <v>0.27524204702627952</v>
+        <f>E99/I99-1</f>
+        <v>0.26777251184834117</v>
       </c>
       <c r="K99" s="11">
-        <v>4.7765726681127982E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
       <c r="L99" s="13">
-        <v>41737000000</v>
+        <v>42109966000</v>
       </c>
       <c r="M99" s="13">
-        <v>794927000000</v>
+        <v>746176876000</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O99" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>0.10983627816766035</v>
+        <v>0.10083557927878818</v>
       </c>
       <c r="Q99" s="12">
-        <v>5.2504192208844336E-2</v>
+        <v>5.643429507724386E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B100" s="1" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="C100" t="s">
-        <v>313</v>
+        <v>178</v>
       </c>
       <c r="D100" t="s">
-        <v>314</v>
+        <v>98</v>
       </c>
       <c r="E100">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>111841214464</v>
+        <v>40176103424</v>
       </c>
       <c r="H100" s="6">
-        <v>7.03</v>
+        <v>5.49</v>
       </c>
       <c r="I100" s="6">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="J100" s="12">
-        <f t="shared" si="3"/>
-        <v>0.26777251184834117</v>
+        <f>E100/I100-1</f>
+        <v>0.36578947368421066</v>
       </c>
       <c r="K100" s="11">
-        <v>5.6074766355140186E-2</v>
+        <v>7.3795761078998073E-2</v>
       </c>
       <c r="L100" s="13">
-        <v>42109966000</v>
+        <v>5474000000</v>
       </c>
       <c r="M100" s="13">
-        <v>746176876000</v>
+        <v>59407000000</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O100" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P100" s="12">
-        <v>0.10083557927878818</v>
+        <v>5.9610731194064369E-2</v>
       </c>
       <c r="Q100" s="12">
-        <v>5.643429507724386E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B101" s="1" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="C101" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="D101" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E101">
-        <v>5.19</v>
+        <v>1.35</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>40176103424</v>
+        <v>7374415872</v>
       </c>
       <c r="H101" s="6">
-        <v>5.49</v>
+        <v>1.82</v>
       </c>
       <c r="I101" s="6">
-        <v>3.8</v>
+        <v>0.81</v>
       </c>
       <c r="J101" s="12">
-        <f t="shared" si="3"/>
-        <v>0.36578947368421066</v>
+        <f>E101/I101-1</f>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K101" s="11">
-        <v>7.3795761078998073E-2</v>
+        <v>2.5185185185185185E-2</v>
       </c>
       <c r="L101" s="13">
-        <v>5474000000</v>
+        <v>1384865000</v>
       </c>
       <c r="M101" s="13">
-        <v>59407000000</v>
+        <v>23827484000</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O101" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P101" s="12">
-        <v>5.9610731194064369E-2</v>
+        <v>8.0028608509338919E-2</v>
       </c>
       <c r="Q101" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="C102" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="E102">
-        <v>1.35</v>
+        <v>24.7</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>7374415872</v>
+        <v>27375257600</v>
       </c>
       <c r="H102" s="6">
-        <v>1.82</v>
+        <v>24.8</v>
       </c>
       <c r="I102" s="6">
-        <v>0.81</v>
+        <v>14.52</v>
       </c>
       <c r="J102" s="12">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <f>E102/I102-1</f>
+        <v>0.70110192837465557</v>
       </c>
       <c r="K102" s="11">
-        <v>2.5185185185185185E-2</v>
+        <v>3.8056680161943315E-2</v>
       </c>
       <c r="L102" s="13">
-        <v>1384865000</v>
+        <v>3838344000</v>
       </c>
       <c r="M102" s="13">
-        <v>23827484000</v>
+        <v>81520873000</v>
       </c>
       <c r="N102" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O102" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>8.0028608509338919E-2</v>
+        <v>8.4931868729332158E-2</v>
       </c>
       <c r="Q102" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B103" s="1" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="D103" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="E103">
-        <v>24.7</v>
+        <v>11.6</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>27375257600</v>
+        <v>204169297920</v>
       </c>
       <c r="H103" s="6">
-        <v>24.8</v>
+        <v>12.46</v>
       </c>
       <c r="I103" s="6">
-        <v>14.52</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J103" s="12">
-        <f t="shared" si="3"/>
-        <v>0.70110192837465557</v>
+        <f>E103/I103-1</f>
+        <v>0.26086956521739135</v>
       </c>
       <c r="K103" s="11">
-        <v>3.8056680161943315E-2</v>
+        <v>3.5948275862068967E-2</v>
       </c>
       <c r="L103" s="13">
-        <v>3838344000</v>
+        <v>16758000000</v>
       </c>
       <c r="M103" s="13">
-        <v>81520873000</v>
+        <v>269590000000</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O103" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P103" s="12">
-        <v>8.4931868729332158E-2</v>
+        <v>5.9626514955333471E-2</v>
       </c>
       <c r="Q103" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B104" s="1" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="D104" t="s">
         <v>87</v>
       </c>
       <c r="E104">
-        <v>1.95</v>
+        <v>6.86</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>3467373056</v>
+        <v>7158684160</v>
       </c>
       <c r="H104" s="6">
-        <v>2.73</v>
+        <v>7</v>
       </c>
       <c r="I104" s="6">
-        <v>1.79</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J104" s="12">
-        <f t="shared" si="3"/>
-        <v>8.9385474860335101E-2</v>
+        <f>E104/I104-1</f>
+        <v>0.70646766169154263</v>
       </c>
       <c r="K104" s="11">
-        <v>2.8717948717948718E-2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="13">
-        <v>364157000</v>
+        <v>303335000</v>
       </c>
       <c r="M104" s="13">
-        <v>7859317000</v>
+        <v>3620162000</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O104" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P104" s="12">
-        <v>8.5020754486272387E-2</v>
+        <v>5.0016264870190799E-2</v>
       </c>
       <c r="Q104" s="12">
-        <v>4.6334433386514377E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B105" s="1" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="D105" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E105">
-        <v>11.6</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>204169297920</v>
+        <v>9706699776</v>
       </c>
       <c r="H105" s="6">
-        <v>12.46</v>
+        <v>3.04</v>
       </c>
       <c r="I105" s="6">
-        <v>9.1999999999999993</v>
+        <v>1.93</v>
       </c>
       <c r="J105" s="12">
-        <f t="shared" si="3"/>
-        <v>0.26086956521739135</v>
+        <f>E105/I105-1</f>
+        <v>0.17098445595854916</v>
       </c>
       <c r="K105" s="11">
-        <v>3.5948275862068967E-2</v>
+        <v>4.7345132743362835E-2</v>
       </c>
       <c r="L105" s="13">
-        <v>16758000000</v>
+        <v>1938532000</v>
       </c>
       <c r="M105" s="13">
-        <v>269590000000</v>
+        <v>49986396000</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O105" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P105" s="12">
-        <v>5.9626514955333471E-2</v>
+        <v>6.4115012275143504E-2</v>
       </c>
       <c r="Q105" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B106" s="1" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
-        <v>86</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>196</v>
       </c>
       <c r="E106">
-        <v>6.86</v>
+        <v>42.25</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>7158684160</v>
+        <v>446574034944</v>
       </c>
       <c r="H106" s="6">
-        <v>7</v>
+        <v>59.7</v>
       </c>
       <c r="I106" s="6">
-        <v>4.0199999999999996</v>
+        <v>15.24</v>
       </c>
       <c r="J106" s="12">
-        <f t="shared" si="3"/>
-        <v>0.70646766169154263</v>
+        <f>E106/I106-1</f>
+        <v>1.7723097112860891</v>
       </c>
       <c r="K106" s="11">
         <v>0</v>
       </c>
       <c r="L106" s="13">
-        <v>303335000</v>
+        <v>984027000</v>
       </c>
       <c r="M106" s="13">
-        <v>3620162000</v>
+        <v>32183526000</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O106" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P106" s="12">
-        <v>5.0016264870190799E-2</v>
+        <v>1.5548782898068332E-2</v>
       </c>
       <c r="Q106" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>3.0575487595734537E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B107" s="1" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D107" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="E107">
-        <v>2.2599999999999998</v>
+        <v>13.66</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>9706699776</v>
+        <v>14028956672</v>
       </c>
       <c r="H107" s="6">
-        <v>3.04</v>
+        <v>14.5</v>
       </c>
       <c r="I107" s="6">
-        <v>1.93</v>
+        <v>10.36</v>
       </c>
       <c r="J107" s="12">
-        <f t="shared" si="3"/>
-        <v>0.17098445595854916</v>
+        <f>E107/I107-1</f>
+        <v>0.31853281853281867</v>
       </c>
       <c r="K107" s="11">
-        <v>4.7345132743362835E-2</v>
+        <v>7.9062957540263545E-2</v>
       </c>
       <c r="L107" s="13">
-        <v>1938532000</v>
+        <v>984000000</v>
       </c>
       <c r="M107" s="13">
-        <v>49986396000</v>
+        <v>101944000000</v>
       </c>
       <c r="N107" s="9" t="s">
         <v>68</v>
@@ -7518,160 +7506,157 @@
         <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>6.4115012275143504E-2</v>
+        <v>2.5244390409937343E-2</v>
       </c>
       <c r="Q107" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>9.6523581574197593E-3</v>
       </c>
       <c r="R107" s="14">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B108" s="1" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s">
-        <v>198</v>
+        <v>322</v>
       </c>
       <c r="D108" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="E108">
-        <v>42.25</v>
+        <v>9.74</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>446574034944</v>
+        <v>10350211072</v>
       </c>
       <c r="H108" s="6">
-        <v>59.7</v>
+        <v>12.88</v>
       </c>
       <c r="I108" s="6">
-        <v>15.24</v>
+        <v>4.47</v>
       </c>
       <c r="J108" s="12">
-        <f t="shared" si="3"/>
-        <v>1.7723097112860891</v>
+        <f>E108/I108-1</f>
+        <v>1.1789709172259508</v>
       </c>
       <c r="K108" s="11">
-        <v>0</v>
+        <v>1.0574948665297741E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>984027000</v>
+        <v>81340000</v>
       </c>
       <c r="M108" s="13">
-        <v>32183526000</v>
+        <v>3509401000</v>
       </c>
       <c r="N108" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O108" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>1.5548782898068332E-2</v>
+        <v>7.7794209390644568E-3</v>
       </c>
       <c r="Q108" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>2.3177744578063323E-2</v>
       </c>
       <c r="R108" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B109" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C109" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D109" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="E109">
-        <v>13.66</v>
+        <v>29.2</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>14028956672</v>
+        <v>29815828480</v>
       </c>
       <c r="H109" s="6">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="I109" s="6">
-        <v>10.36</v>
+        <v>22.4</v>
       </c>
       <c r="J109" s="12">
-        <f t="shared" si="3"/>
-        <v>0.31853281853281867</v>
+        <f>E109/I109-1</f>
+        <v>0.3035714285714286</v>
       </c>
       <c r="K109" s="11">
-        <v>7.9062957540263545E-2</v>
+        <v>0</v>
       </c>
       <c r="L109" s="13">
-        <v>984000000</v>
+        <v>-90314000</v>
       </c>
       <c r="M109" s="13">
-        <v>101944000000</v>
+        <v>18374441000</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O109" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P109" s="12">
-        <v>2.5244390409937343E-2</v>
+        <v>-3.6402784697953479E-3</v>
       </c>
       <c r="Q109" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R109" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B110" s="1" t="s">
-        <v>272</v>
+        <v>202</v>
       </c>
       <c r="C110" t="s">
-        <v>326</v>
+        <v>228</v>
       </c>
       <c r="D110" t="s">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="E110">
-        <v>9.74</v>
+        <v>34.4</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>10350211072</v>
+        <v>363704320000</v>
       </c>
       <c r="H110" s="6">
-        <v>12.88</v>
+        <v>34.6</v>
       </c>
       <c r="I110" s="6">
-        <v>4.47</v>
+        <v>21.5</v>
       </c>
       <c r="J110" s="12">
-        <f t="shared" si="3"/>
-        <v>1.1789709172259508</v>
+        <f>E110/I110-1</f>
+        <v>0.59999999999999987</v>
       </c>
       <c r="K110" s="11">
-        <v>1.0574948665297741E-2</v>
-      </c>
-      <c r="L110" s="13">
-        <v>81340000</v>
+        <v>5.7819767441860473E-2</v>
       </c>
       <c r="M110" s="13">
-        <v>3509401000</v>
+        <v>415994000000</v>
       </c>
       <c r="N110" s="9" t="s">
         <v>68</v>
@@ -7679,53 +7664,41 @@
       <c r="O110" s="6">
         <v>1</v>
       </c>
-      <c r="P110" s="12">
-        <v>7.7794209390644568E-3</v>
-      </c>
-      <c r="Q110" s="12">
-        <v>2.3177744578063323E-2</v>
-      </c>
-      <c r="R110" s="14">
-        <v>77</v>
-      </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B111" s="1" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C111" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="E111">
-        <v>29.2</v>
+        <v>7.2</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>29815828480</v>
+        <v>588140642304</v>
       </c>
       <c r="H111" s="6">
-        <v>36</v>
+        <v>7.27</v>
       </c>
       <c r="I111" s="6">
-        <v>22.4</v>
+        <v>5.08</v>
       </c>
       <c r="J111" s="12">
-        <f t="shared" si="3"/>
-        <v>0.3035714285714286</v>
+        <f>E111/I111-1</f>
+        <v>0.41732283464566922</v>
       </c>
       <c r="K111" s="11">
-        <v>0</v>
-      </c>
-      <c r="L111" s="13">
-        <v>-90314000</v>
+        <v>5.2638888888888888E-2</v>
       </c>
       <c r="M111" s="13">
-        <v>18374441000</v>
+        <v>2314289000000</v>
       </c>
       <c r="N111" s="9" t="s">
         <v>51</v>
@@ -7733,92 +7706,83 @@
       <c r="O111" s="6">
         <v>1.0683760683760684</v>
       </c>
-      <c r="P111" s="12">
-        <v>-3.6402784697953479E-3</v>
-      </c>
-      <c r="Q111" s="12">
-        <v>-4.9151971480384084E-3</v>
-      </c>
-      <c r="R111" s="14">
-        <v>78</v>
-      </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B112" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C112" t="s">
         <v>232</v>
       </c>
       <c r="D112" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E112">
-        <v>34.4</v>
+        <v>5.95</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>363704320000</v>
+        <v>2634100506624</v>
       </c>
       <c r="H112" s="6">
-        <v>34.6</v>
+        <v>5.97</v>
       </c>
       <c r="I112" s="6">
-        <v>21.5</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J112" s="12">
-        <f t="shared" si="3"/>
-        <v>0.59999999999999987</v>
+        <f>E112/I112-1</f>
+        <v>0.4655172413793105</v>
       </c>
       <c r="K112" s="11">
-        <v>5.7819767441860473E-2</v>
+        <v>5.1764705882352942E-2</v>
       </c>
       <c r="M112" s="13">
-        <v>415994000000</v>
+        <v>6434377000000</v>
       </c>
       <c r="N112" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O112" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
     </row>
     <row r="113" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B113" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C113" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D113" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E113">
-        <v>7.2</v>
+        <v>5.18</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>588140642304</v>
+        <v>573933617152</v>
       </c>
       <c r="H113" s="6">
-        <v>7.27</v>
+        <v>5.39</v>
       </c>
       <c r="I113" s="6">
-        <v>5.08</v>
+        <v>3.89</v>
       </c>
       <c r="J113" s="12">
-        <f t="shared" si="3"/>
-        <v>0.41732283464566922</v>
+        <f>E113/I113-1</f>
+        <v>0.3316195372750641</v>
       </c>
       <c r="K113" s="11">
-        <v>5.2638888888888888E-2</v>
+        <v>0</v>
       </c>
       <c r="M113" s="13">
-        <v>2314289000000</v>
+        <v>1271649000000</v>
       </c>
       <c r="N113" s="9" t="s">
         <v>51</v>
@@ -7829,38 +7793,38 @@
     </row>
     <row r="114" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B114" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C114" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D114" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E114">
-        <v>5.95</v>
+        <v>7.44</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>2634100506624</v>
+        <v>1885176987648</v>
       </c>
       <c r="H114" s="6">
-        <v>5.97</v>
+        <v>7.44</v>
       </c>
       <c r="I114" s="6">
-        <v>4.0599999999999996</v>
+        <v>5.23</v>
       </c>
       <c r="J114" s="12">
-        <f t="shared" si="3"/>
-        <v>0.4655172413793105</v>
+        <f>E114/I114-1</f>
+        <v>0.42256214149139582</v>
       </c>
       <c r="K114" s="11">
-        <v>5.1764705882352942E-2</v>
+        <v>5.4166666666666669E-2</v>
       </c>
       <c r="M114" s="13">
-        <v>6434377000000</v>
+        <v>6128626000000</v>
       </c>
       <c r="N114" s="9" t="s">
         <v>51</v>
@@ -7871,38 +7835,38 @@
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B115" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C115" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D115" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E115">
-        <v>5.18</v>
+        <v>7.22</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>573933617152</v>
+        <v>482755903488</v>
       </c>
       <c r="H115" s="6">
-        <v>5.39</v>
+        <v>7.3</v>
       </c>
       <c r="I115" s="6">
-        <v>3.89</v>
+        <v>4.26</v>
       </c>
       <c r="J115" s="12">
-        <f t="shared" si="3"/>
-        <v>0.3316195372750641</v>
+        <f>E115/I115-1</f>
+        <v>0.69483568075117375</v>
       </c>
       <c r="K115" s="11">
-        <v>0</v>
+        <v>4.916897506925208E-2</v>
       </c>
       <c r="M115" s="13">
-        <v>1271649000000</v>
+        <v>2066897000000</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>51</v>
@@ -7913,124 +7877,40 @@
     </row>
     <row r="116" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B116" s="1" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="C116" t="s">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="D116" t="s">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="E116">
-        <v>7.44</v>
+        <v>4.17</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>1885176987648</v>
+        <v>16171593728</v>
       </c>
       <c r="H116" s="6">
-        <v>7.44</v>
+        <v>6.97</v>
       </c>
       <c r="I116" s="6">
-        <v>5.23</v>
+        <v>3.33</v>
       </c>
       <c r="J116" s="12">
-        <f t="shared" si="3"/>
-        <v>0.42256214149139582</v>
+        <f>E116/I116-1</f>
+        <v>0.25225225225225212</v>
       </c>
       <c r="K116" s="11">
-        <v>5.4166666666666669E-2</v>
-      </c>
-      <c r="M116" s="13">
-        <v>6128626000000</v>
+        <v>6.4748201438848921E-2</v>
       </c>
       <c r="N116" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O116" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-    </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.5">
-      <c r="B117" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C117" t="s">
-        <v>239</v>
-      </c>
-      <c r="D117" t="s">
-        <v>233</v>
-      </c>
-      <c r="E117">
-        <v>7.22</v>
-      </c>
-      <c r="F117" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G117" s="7">
-        <v>482755903488</v>
-      </c>
-      <c r="H117" s="6">
-        <v>7.3</v>
-      </c>
-      <c r="I117" s="6">
-        <v>4.26</v>
-      </c>
-      <c r="J117" s="12">
-        <f t="shared" si="3"/>
-        <v>0.69483568075117375</v>
-      </c>
-      <c r="K117" s="11">
-        <v>4.916897506925208E-2</v>
-      </c>
-      <c r="M117" s="13">
-        <v>2066897000000</v>
-      </c>
-      <c r="N117" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O117" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-    </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.5">
-      <c r="B118" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C118" t="s">
-        <v>357</v>
-      </c>
-      <c r="D118" t="s">
-        <v>54</v>
-      </c>
-      <c r="E118">
-        <v>4.17</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G118" s="7">
-        <v>16171593728</v>
-      </c>
-      <c r="H118" s="6">
-        <v>6.97</v>
-      </c>
-      <c r="I118" s="6">
-        <v>3.33</v>
-      </c>
-      <c r="J118" s="12">
-        <f t="shared" si="3"/>
-        <v>0.25225225225225212</v>
-      </c>
-      <c r="K118" s="11">
-        <v>6.4748201438848921E-2</v>
-      </c>
-      <c r="N118" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O118" s="6">
         <v>1</v>
       </c>
     </row>
@@ -8674,52 +8554,52 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -8822,13 +8702,13 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E2">
         <v>22.28</v>
@@ -8846,7 +8726,7 @@
         <v>21.19</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J17" si="0">E2/I2-1</f>
         <v>5.1439358187824524E-2</v>
       </c>
       <c r="K2" s="11">
@@ -8876,13 +8756,13 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E3">
         <v>25.22</v>
@@ -8900,7 +8780,7 @@
         <v>21.41</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.17795422699673047</v>
       </c>
       <c r="K3" s="11">
@@ -8930,13 +8810,13 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E4">
         <v>70.599999999999994</v>
@@ -8954,7 +8834,7 @@
         <v>49.92</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.41426282051282026</v>
       </c>
       <c r="K4" s="11">
@@ -9008,7 +8888,7 @@
         <v>45.55</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>0.75499451152579589</v>
       </c>
       <c r="K5" s="11">
@@ -9038,10 +8918,10 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
         <v>77</v>
@@ -9062,7 +8942,7 @@
         <v>17.73</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.42357586012408333</v>
       </c>
       <c r="K6" s="11">
@@ -9092,13 +8972,13 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E7">
         <v>9.2799999999999994</v>
@@ -9116,7 +8996,7 @@
         <v>9</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>3.1111111111111089E-2</v>
       </c>
       <c r="K7" s="11">
@@ -9170,7 +9050,7 @@
         <v>103.69</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>0.97752917349792656</v>
       </c>
       <c r="K8" s="11">
@@ -9200,10 +9080,10 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
         <v>89</v>
@@ -9224,7 +9104,7 @@
         <v>17.149999999999999</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>9.5626822157434344E-2</v>
       </c>
       <c r="K9" s="11">
@@ -9254,10 +9134,10 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -9278,7 +9158,7 @@
         <v>58.47</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>0.10911578587309734</v>
       </c>
       <c r="K10" s="11">
@@ -9308,13 +9188,13 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E11">
         <v>52.21</v>
@@ -9332,7 +9212,7 @@
         <v>49.19</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>6.1394592396828651E-2</v>
       </c>
       <c r="K11" s="11">
@@ -9386,7 +9266,7 @@
         <v>156.13999999999999</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>9.1136159856539223E-2</v>
       </c>
       <c r="K12" s="11">
@@ -9416,13 +9296,13 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E13">
         <v>143.35</v>
@@ -9440,7 +9320,7 @@
         <v>132.04</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>8.5655861860042481E-2</v>
       </c>
       <c r="K13" s="11">
@@ -9470,10 +9350,10 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -9494,7 +9374,7 @@
         <v>12.85</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>0.24902723735408561</v>
       </c>
       <c r="K14" s="11">
@@ -9524,10 +9404,10 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
         <v>87</v>
@@ -9548,7 +9428,7 @@
         <v>15.43</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.12378483473752433</v>
       </c>
       <c r="K15" s="11">
@@ -9561,7 +9441,7 @@
         <v>4745800000</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O15" s="6">
         <v>1.1380999999999999</v>
@@ -9578,10 +9458,10 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C16" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D16" t="s">
         <v>87</v>
@@ -9602,7 +9482,7 @@
         <v>26.01</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>2.2299115724721208E-2</v>
       </c>
       <c r="K16" s="11">
@@ -9632,13 +9512,13 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C17" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D17" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E17">
         <v>22.81</v>
@@ -9656,7 +9536,7 @@
         <v>18.690000000000001</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.22043873729266972</v>
       </c>
       <c r="K17" s="11">
@@ -9720,12 +9600,12 @@
     </row>
     <row r="3" spans="2:2" ht="409.5" x14ac:dyDescent="0.5">
       <c r="B3" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF7E77-E0C4-4293-BE7A-86B2F13ED349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445C1F60-9B94-4298-B704-CFA83046C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="375">
   <si>
     <t>Ticker</t>
   </si>
@@ -1218,6 +1218,12 @@
   </si>
   <si>
     <t>Entertainment</t>
+  </si>
+  <si>
+    <t>2390.HK</t>
+  </si>
+  <si>
+    <t>9959.HK</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V116"/>
+  <dimension ref="B1:V118"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1817,7 +1823,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
         <v>0.31355932203389836</v>
       </c>
       <c r="K2" s="11">
@@ -1871,7 +1877,7 @@
         <v>4.22</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.49763033175355464</v>
       </c>
       <c r="K3" s="11">
@@ -1925,7 +1931,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.25862068965517238</v>
       </c>
       <c r="K4" s="11">
@@ -1979,7 +1985,7 @@
         <v>9.52</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>0.39285714285714279</v>
       </c>
       <c r="K5" s="11">
@@ -2033,7 +2039,7 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.40879120879120867</v>
       </c>
       <c r="K6" s="11">
@@ -2087,7 +2093,7 @@
         <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>0.23703703703703694</v>
       </c>
       <c r="K7" s="11">
@@ -2141,7 +2147,7 @@
         <v>4.58</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>0.47598253275109159</v>
       </c>
       <c r="K8" s="11">
@@ -2195,7 +2201,7 @@
         <v>2.23</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>0.20627802690582953</v>
       </c>
       <c r="K9" s="11">
@@ -2249,7 +2255,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>0.17699115044247815</v>
       </c>
       <c r="K10" s="11">
@@ -2303,7 +2309,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>1.095617529880478</v>
       </c>
       <c r="K11" s="11">
@@ -2357,7 +2363,7 @@
         <v>3.15</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>0.43492063492063493</v>
       </c>
       <c r="K12" s="11">
@@ -2411,7 +2417,7 @@
         <v>2.11</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>0.33175355450236976</v>
       </c>
       <c r="K13" s="11">
@@ -2465,7 +2471,7 @@
         <v>1.36</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>0.11029411764705865</v>
       </c>
       <c r="K14" s="11">
@@ -2519,7 +2525,7 @@
         <v>10.6</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.50566037735849068</v>
       </c>
       <c r="K15" s="11">
@@ -2573,7 +2579,7 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>0.7271523178807946</v>
       </c>
       <c r="K16" s="11">
@@ -2627,7 +2633,7 @@
         <v>4.84</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.52685950413223148</v>
       </c>
       <c r="K17" s="11">
@@ -2681,7 +2687,7 @@
         <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
+        <f t="shared" si="0"/>
         <v>0.96733668341708556</v>
       </c>
       <c r="K18" s="11">
@@ -2735,7 +2741,7 @@
         <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
+        <f t="shared" si="0"/>
         <v>0.20833333333333326</v>
       </c>
       <c r="K19" s="11">
@@ -2789,7 +2795,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
+        <f t="shared" si="0"/>
         <v>0.47599999999999998</v>
       </c>
       <c r="K20" s="11">
@@ -2843,7 +2849,7 @@
         <v>7.96</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
+        <f t="shared" si="0"/>
         <v>0.96733668341708556</v>
       </c>
       <c r="K21" s="11">
@@ -2897,7 +2903,7 @@
         <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f>E22/I22-1</f>
+        <f t="shared" si="0"/>
         <v>0.73809523809523814</v>
       </c>
       <c r="K22" s="11">
@@ -2951,7 +2957,7 @@
         <v>15.7</v>
       </c>
       <c r="J23" s="12">
-        <f>E23/I23-1</f>
+        <f t="shared" si="0"/>
         <v>0.54458598726114649</v>
       </c>
       <c r="K23" s="11">
@@ -3005,7 +3011,7 @@
         <v>12.12</v>
       </c>
       <c r="J24" s="12">
-        <f>E24/I24-1</f>
+        <f t="shared" si="0"/>
         <v>0.16336633663366351</v>
       </c>
       <c r="K24" s="11">
@@ -3059,7 +3065,7 @@
         <v>7.08</v>
       </c>
       <c r="J25" s="12">
-        <f>E25/I25-1</f>
+        <f t="shared" si="0"/>
         <v>0.11299435028248594</v>
       </c>
       <c r="K25" s="11">
@@ -3113,7 +3119,7 @@
         <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f>E26/I26-1</f>
+        <f t="shared" si="0"/>
         <v>0.17318435754189943</v>
       </c>
       <c r="K26" s="11">
@@ -3167,7 +3173,7 @@
         <v>3.46</v>
       </c>
       <c r="J27" s="12">
-        <f>E27/I27-1</f>
+        <f t="shared" si="0"/>
         <v>0.85260115606936426</v>
       </c>
       <c r="K27" s="11">
@@ -3221,7 +3227,7 @@
         <v>6.57</v>
       </c>
       <c r="J28" s="12">
-        <f>E28/I28-1</f>
+        <f t="shared" si="0"/>
         <v>0.40639269406392686</v>
       </c>
       <c r="K28" s="11">
@@ -3275,7 +3281,7 @@
         <v>3.45</v>
       </c>
       <c r="J29" s="12">
-        <f>E29/I29-1</f>
+        <f t="shared" si="0"/>
         <v>0.39130434782608692</v>
       </c>
       <c r="K29" s="11">
@@ -3329,7 +3335,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="J30" s="12">
-        <f>E30/I30-1</f>
+        <f t="shared" si="0"/>
         <v>0.14226375908618882</v>
       </c>
       <c r="K30" s="11">
@@ -3383,7 +3389,7 @@
         <v>3.97</v>
       </c>
       <c r="J31" s="12">
-        <f>E31/I31-1</f>
+        <f t="shared" si="0"/>
         <v>0.38287153652392947</v>
       </c>
       <c r="K31" s="11">
@@ -3437,7 +3443,7 @@
         <v>2.8</v>
       </c>
       <c r="J32" s="12">
-        <f>E32/I32-1</f>
+        <f t="shared" si="0"/>
         <v>0.35714285714285721</v>
       </c>
       <c r="K32" s="11">
@@ -3491,7 +3497,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f>E33/I33-1</f>
+        <f t="shared" si="0"/>
         <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
@@ -3545,7 +3551,7 @@
         <v>8.67</v>
       </c>
       <c r="J34" s="12">
-        <f>E34/I34-1</f>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
         <v>0.30334486735870825</v>
       </c>
       <c r="K34" s="11">
@@ -3599,7 +3605,7 @@
         <v>3.46</v>
       </c>
       <c r="J35" s="12">
-        <f>E35/I35-1</f>
+        <f t="shared" si="1"/>
         <v>0.30635838150289008</v>
       </c>
       <c r="K35" s="11">
@@ -3653,7 +3659,7 @@
         <v>3.22</v>
       </c>
       <c r="J36" s="12">
-        <f>E36/I36-1</f>
+        <f t="shared" si="1"/>
         <v>0.54968944099378869</v>
       </c>
       <c r="K36" s="11">
@@ -3707,7 +3713,7 @@
         <v>3.39</v>
       </c>
       <c r="J37" s="12">
-        <f>E37/I37-1</f>
+        <f t="shared" si="1"/>
         <v>0.734513274336283</v>
       </c>
       <c r="K37" s="11">
@@ -3761,7 +3767,7 @@
         <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f>E38/I38-1</f>
+        <f t="shared" si="1"/>
         <v>1.6203703703703702</v>
       </c>
       <c r="K38" s="11">
@@ -3815,7 +3821,7 @@
         <v>3.58</v>
       </c>
       <c r="J39" s="12">
-        <f>E39/I39-1</f>
+        <f t="shared" si="1"/>
         <v>0.22346368715083798</v>
       </c>
       <c r="K39" s="11">
@@ -3869,7 +3875,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f>E40/I40-1</f>
+        <f t="shared" si="1"/>
         <v>0.3710843373493975</v>
       </c>
       <c r="K40" s="11">
@@ -3923,7 +3929,7 @@
         <v>4.12</v>
       </c>
       <c r="J41" s="12">
-        <f>E41/I41-1</f>
+        <f t="shared" si="1"/>
         <v>0.28398058252427183</v>
       </c>
       <c r="K41" s="11">
@@ -3977,7 +3983,7 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="J42" s="12">
-        <f>E42/I42-1</f>
+        <f t="shared" si="1"/>
         <v>0.46396396396396389</v>
       </c>
       <c r="K42" s="11">
@@ -4031,7 +4037,7 @@
         <v>18.559999999999999</v>
       </c>
       <c r="J43" s="12">
-        <f>E43/I43-1</f>
+        <f t="shared" si="1"/>
         <v>0.43588362068965525</v>
       </c>
       <c r="K43" s="11">
@@ -4085,7 +4091,7 @@
         <v>5.31</v>
       </c>
       <c r="J44" s="12">
-        <f>E44/I44-1</f>
+        <f t="shared" si="1"/>
         <v>0.13182674199623357</v>
       </c>
       <c r="K44" s="11">
@@ -4139,7 +4145,7 @@
         <v>1.33</v>
       </c>
       <c r="J45" s="12">
-        <f>E45/I45-1</f>
+        <f t="shared" si="1"/>
         <v>0.488721804511278</v>
       </c>
       <c r="K45" s="11">
@@ -4193,7 +4199,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="J46" s="12">
-        <f>E46/I46-1</f>
+        <f t="shared" si="1"/>
         <v>1.2551724137931037</v>
       </c>
       <c r="K46" s="11">
@@ -4247,7 +4253,7 @@
         <v>3.71</v>
       </c>
       <c r="J47" s="12">
-        <f>E47/I47-1</f>
+        <f t="shared" si="1"/>
         <v>0.23989218328840956</v>
       </c>
       <c r="K47" s="11">
@@ -4301,7 +4307,7 @@
         <v>3.4</v>
       </c>
       <c r="J48" s="12">
-        <f>E48/I48-1</f>
+        <f t="shared" si="1"/>
         <v>0.19117647058823528</v>
       </c>
       <c r="K48" s="11">
@@ -4355,7 +4361,7 @@
         <v>19.239999999999998</v>
       </c>
       <c r="J49" s="12">
-        <f>E49/I49-1</f>
+        <f t="shared" si="1"/>
         <v>0.2136174636174637</v>
       </c>
       <c r="K49" s="11">
@@ -4409,7 +4415,7 @@
         <v>16.18</v>
       </c>
       <c r="J50" s="12">
-        <f>E50/I50-1</f>
+        <f t="shared" si="1"/>
         <v>0.19283065512979003</v>
       </c>
       <c r="K50" s="11">
@@ -4463,7 +4469,7 @@
         <v>3.15</v>
       </c>
       <c r="J51" s="12">
-        <f>E51/I51-1</f>
+        <f t="shared" si="1"/>
         <v>1.1904761904761907</v>
       </c>
       <c r="K51" s="11">
@@ -4517,7 +4523,7 @@
         <v>55.05</v>
       </c>
       <c r="J52" s="12">
-        <f>E52/I52-1</f>
+        <f t="shared" si="1"/>
         <v>0.4023614895549501</v>
       </c>
       <c r="K52" s="11">
@@ -4571,7 +4577,7 @@
         <v>65.55</v>
       </c>
       <c r="J53" s="12">
-        <f>E53/I53-1</f>
+        <f t="shared" si="1"/>
         <v>0.47520976353928313</v>
       </c>
       <c r="K53" s="11">
@@ -4625,7 +4631,7 @@
         <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f>E54/I54-1</f>
+        <f t="shared" si="1"/>
         <v>0.72457627118644097</v>
       </c>
       <c r="K54" s="11">
@@ -4679,7 +4685,7 @@
         <v>8.81</v>
       </c>
       <c r="J55" s="12">
-        <f>E55/I55-1</f>
+        <f t="shared" si="1"/>
         <v>0.47105561861520995</v>
       </c>
       <c r="K55" s="11">
@@ -4733,7 +4739,7 @@
         <v>43.55</v>
       </c>
       <c r="J56" s="12">
-        <f>E56/I56-1</f>
+        <f t="shared" si="1"/>
         <v>0.15154994259471866</v>
       </c>
       <c r="K56" s="11">
@@ -4787,7 +4793,7 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="J57" s="12">
-        <f>E57/I57-1</f>
+        <f t="shared" si="1"/>
         <v>0.2012578616352203</v>
       </c>
       <c r="K57" s="11">
@@ -4841,7 +4847,7 @@
         <v>7.36</v>
       </c>
       <c r="J58" s="12">
-        <f>E58/I58-1</f>
+        <f t="shared" si="1"/>
         <v>0.44021739130434767</v>
       </c>
       <c r="K58" s="11">
@@ -4895,7 +4901,7 @@
         <v>0.46</v>
       </c>
       <c r="J59" s="12">
-        <f>E59/I59-1</f>
+        <f t="shared" si="1"/>
         <v>5.4347826086956541E-2</v>
       </c>
       <c r="K59" s="11">
@@ -4949,7 +4955,7 @@
         <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f>E60/I60-1</f>
+        <f t="shared" si="1"/>
         <v>0.58035714285714279</v>
       </c>
       <c r="K60" s="11">
@@ -5003,7 +5009,7 @@
         <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f>E61/I61-1</f>
+        <f t="shared" si="1"/>
         <v>0.90384615384615374</v>
       </c>
       <c r="K61" s="11">
@@ -5057,7 +5063,7 @@
         <v>3.34</v>
       </c>
       <c r="J62" s="12">
-        <f>E62/I62-1</f>
+        <f t="shared" si="1"/>
         <v>0.12574850299401197</v>
       </c>
       <c r="K62" s="11">
@@ -5111,7 +5117,7 @@
         <v>13.52</v>
       </c>
       <c r="J63" s="12">
-        <f>E63/I63-1</f>
+        <f t="shared" si="1"/>
         <v>0.33431952662721898</v>
       </c>
       <c r="K63" s="11">
@@ -5165,7 +5171,7 @@
         <v>3.99</v>
       </c>
       <c r="J64" s="12">
-        <f>E64/I64-1</f>
+        <f t="shared" si="1"/>
         <v>0.7192982456140351</v>
       </c>
       <c r="K64" s="11">
@@ -5219,7 +5225,7 @@
         <v>34.4</v>
       </c>
       <c r="J65" s="12">
-        <f>E65/I65-1</f>
+        <f t="shared" si="1"/>
         <v>6.2906976744186052</v>
       </c>
       <c r="K65" s="11">
@@ -5273,7 +5279,7 @@
         <v>1.74</v>
       </c>
       <c r="J66" s="12">
-        <f>E66/I66-1</f>
+        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
         <v>0.52873563218390807</v>
       </c>
       <c r="K66" s="11">
@@ -5327,7 +5333,7 @@
         <v>225.2</v>
       </c>
       <c r="J67" s="12">
-        <f>E67/I67-1</f>
+        <f t="shared" si="2"/>
         <v>0.55062166962699832</v>
       </c>
       <c r="K67" s="11">
@@ -5381,7 +5387,7 @@
         <v>5.49</v>
       </c>
       <c r="J68" s="12">
-        <f>E68/I68-1</f>
+        <f t="shared" si="2"/>
         <v>0.42987249544626582</v>
       </c>
       <c r="K68" s="11">
@@ -5435,7 +5441,7 @@
         <v>19.52</v>
       </c>
       <c r="J69" s="12">
-        <f>E69/I69-1</f>
+        <f t="shared" si="2"/>
         <v>0.12448770491803285</v>
       </c>
       <c r="K69" s="11">
@@ -5489,7 +5495,7 @@
         <v>13.48</v>
       </c>
       <c r="J70" s="12">
-        <f>E70/I70-1</f>
+        <f t="shared" si="2"/>
         <v>1.5482195845697331</v>
       </c>
       <c r="K70" s="11">
@@ -5543,7 +5549,7 @@
         <v>5.83</v>
       </c>
       <c r="J71" s="12">
-        <f>E71/I71-1</f>
+        <f t="shared" si="2"/>
         <v>1.0240137221269299</v>
       </c>
       <c r="K71" s="11">
@@ -5597,7 +5603,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J72" s="12">
-        <f>E72/I72-1</f>
+        <f t="shared" si="2"/>
         <v>0.58457711442786087</v>
       </c>
       <c r="K72" s="11">
@@ -5651,7 +5657,7 @@
         <v>38.4</v>
       </c>
       <c r="J73" s="12">
-        <f>E73/I73-1</f>
+        <f t="shared" si="2"/>
         <v>0.4921875</v>
       </c>
       <c r="K73" s="11">
@@ -5705,7 +5711,7 @@
         <v>349</v>
       </c>
       <c r="J74" s="12">
-        <f>E74/I74-1</f>
+        <f t="shared" si="2"/>
         <v>0.48424068767908302</v>
       </c>
       <c r="K74" s="11">
@@ -5759,7 +5765,7 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="J75" s="12">
-        <f>E75/I75-1</f>
+        <f t="shared" si="2"/>
         <v>0.46838407494145207</v>
       </c>
       <c r="K75" s="11">
@@ -5813,7 +5819,7 @@
         <v>6.56</v>
       </c>
       <c r="J76" s="12">
-        <f>E76/I76-1</f>
+        <f t="shared" si="2"/>
         <v>0.29115853658536595</v>
       </c>
       <c r="K76" s="11">
@@ -5867,7 +5873,7 @@
         <v>6.84</v>
       </c>
       <c r="J77" s="12">
-        <f>E77/I77-1</f>
+        <f t="shared" si="2"/>
         <v>0.25146198830409361</v>
       </c>
       <c r="K77" s="11">
@@ -5921,7 +5927,7 @@
         <v>10.98</v>
       </c>
       <c r="J78" s="12">
-        <f>E78/I78-1</f>
+        <f t="shared" si="2"/>
         <v>0.30236794171220405</v>
       </c>
       <c r="K78" s="11">
@@ -5975,7 +5981,7 @@
         <v>10.98</v>
       </c>
       <c r="J79" s="12">
-        <f>E79/I79-1</f>
+        <f t="shared" si="2"/>
         <v>0.30236794171220405</v>
       </c>
       <c r="K79" s="11">
@@ -6029,7 +6035,7 @@
         <v>7.51</v>
       </c>
       <c r="J80" s="12">
-        <f>E80/I80-1</f>
+        <f t="shared" si="2"/>
         <v>0.74966711051930779</v>
       </c>
       <c r="K80" s="11">
@@ -6083,7 +6089,7 @@
         <v>9.9</v>
       </c>
       <c r="J81" s="12">
-        <f>E81/I81-1</f>
+        <f t="shared" si="2"/>
         <v>1.2828282828282829</v>
       </c>
       <c r="K81" s="11">
@@ -6137,7 +6143,7 @@
         <v>24.85</v>
       </c>
       <c r="J82" s="12">
-        <f>E82/I82-1</f>
+        <f t="shared" si="2"/>
         <v>0.31589537223340036</v>
       </c>
       <c r="K82" s="11">
@@ -6191,7 +6197,7 @@
         <v>32.65</v>
       </c>
       <c r="J83" s="12">
-        <f>E83/I83-1</f>
+        <f t="shared" si="2"/>
         <v>0.44563552833078113</v>
       </c>
       <c r="K83" s="11">
@@ -6245,7 +6251,7 @@
         <v>1.72</v>
       </c>
       <c r="J84" s="12">
-        <f>E84/I84-1</f>
+        <f t="shared" si="2"/>
         <v>0.15697674418604657</v>
       </c>
       <c r="K84" s="11">
@@ -6299,7 +6305,7 @@
         <v>16.02</v>
       </c>
       <c r="J85" s="12">
-        <f>E85/I85-1</f>
+        <f t="shared" si="2"/>
         <v>0.24344569288389528</v>
       </c>
       <c r="K85" s="11">
@@ -6353,7 +6359,7 @@
         <v>5</v>
       </c>
       <c r="J86" s="12">
-        <f>E86/I86-1</f>
+        <f t="shared" si="2"/>
         <v>0.21199999999999997</v>
       </c>
       <c r="K86" s="11">
@@ -6407,7 +6413,7 @@
         <v>5.19</v>
       </c>
       <c r="J87" s="12">
-        <f>E87/I87-1</f>
+        <f t="shared" si="2"/>
         <v>0.61271676300578015</v>
       </c>
       <c r="K87" s="11">
@@ -6461,7 +6467,7 @@
         <v>37.85</v>
       </c>
       <c r="J88" s="12">
-        <f>E88/I88-1</f>
+        <f t="shared" si="2"/>
         <v>0.35138705416116234</v>
       </c>
       <c r="K88" s="11">
@@ -6515,7 +6521,7 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="J89" s="12">
-        <f>E89/I89-1</f>
+        <f t="shared" si="2"/>
         <v>0.33723653395784559</v>
       </c>
       <c r="K89" s="11">
@@ -6569,7 +6575,7 @@
         <v>1.18</v>
       </c>
       <c r="J90" s="12">
-        <f>E90/I90-1</f>
+        <f t="shared" si="2"/>
         <v>0.33050847457627142</v>
       </c>
       <c r="K90" s="11">
@@ -6623,7 +6629,7 @@
         <v>5.6</v>
       </c>
       <c r="J91" s="12">
-        <f>E91/I91-1</f>
+        <f t="shared" si="2"/>
         <v>0.4464285714285714</v>
       </c>
       <c r="K91" s="11">
@@ -6677,7 +6683,7 @@
         <v>5.6</v>
       </c>
       <c r="J92" s="12">
-        <f>E92/I92-1</f>
+        <f t="shared" si="2"/>
         <v>0.77321428571428585</v>
       </c>
       <c r="K92" s="11">
@@ -6731,7 +6737,7 @@
         <v>4.08</v>
       </c>
       <c r="J93" s="12">
-        <f>E93/I93-1</f>
+        <f t="shared" si="2"/>
         <v>0.41666666666666674</v>
       </c>
       <c r="K93" s="11">
@@ -6785,7 +6791,7 @@
         <v>5.88</v>
       </c>
       <c r="J94" s="12">
-        <f>E94/I94-1</f>
+        <f t="shared" si="2"/>
         <v>0.62585034013605445</v>
       </c>
       <c r="K94" s="11">
@@ -6839,7 +6845,7 @@
         <v>5.44</v>
       </c>
       <c r="J95" s="12">
-        <f>E95/I95-1</f>
+        <f t="shared" si="2"/>
         <v>0.72794117647058809</v>
       </c>
       <c r="K95" s="11">
@@ -6893,7 +6899,7 @@
         <v>28.1</v>
       </c>
       <c r="J96" s="12">
-        <f>E96/I96-1</f>
+        <f t="shared" si="2"/>
         <v>0.17793594306049831</v>
       </c>
       <c r="K96" s="11">
@@ -6947,7 +6953,7 @@
         <v>1.37</v>
       </c>
       <c r="J97" s="12">
-        <f>E97/I97-1</f>
+        <f t="shared" si="2"/>
         <v>0.22627737226277356</v>
       </c>
       <c r="K97" s="11">
@@ -7001,7 +7007,7 @@
         <v>36.15</v>
       </c>
       <c r="J98" s="12">
-        <f>E98/I98-1</f>
+        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
         <v>0.27524204702627952</v>
       </c>
       <c r="K98" s="11">
@@ -7055,7 +7061,7 @@
         <v>4.22</v>
       </c>
       <c r="J99" s="12">
-        <f>E99/I99-1</f>
+        <f t="shared" si="3"/>
         <v>0.26777251184834117</v>
       </c>
       <c r="K99" s="11">
@@ -7109,7 +7115,7 @@
         <v>3.8</v>
       </c>
       <c r="J100" s="12">
-        <f>E100/I100-1</f>
+        <f t="shared" si="3"/>
         <v>0.36578947368421066</v>
       </c>
       <c r="K100" s="11">
@@ -7163,7 +7169,7 @@
         <v>0.81</v>
       </c>
       <c r="J101" s="12">
-        <f>E101/I101-1</f>
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K101" s="11">
@@ -7217,7 +7223,7 @@
         <v>14.52</v>
       </c>
       <c r="J102" s="12">
-        <f>E102/I102-1</f>
+        <f t="shared" si="3"/>
         <v>0.70110192837465557</v>
       </c>
       <c r="K102" s="11">
@@ -7271,7 +7277,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="J103" s="12">
-        <f>E103/I103-1</f>
+        <f t="shared" si="3"/>
         <v>0.26086956521739135</v>
       </c>
       <c r="K103" s="11">
@@ -7325,7 +7331,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J104" s="12">
-        <f>E104/I104-1</f>
+        <f t="shared" si="3"/>
         <v>0.70646766169154263</v>
       </c>
       <c r="K104" s="11">
@@ -7379,7 +7385,7 @@
         <v>1.93</v>
       </c>
       <c r="J105" s="12">
-        <f>E105/I105-1</f>
+        <f t="shared" si="3"/>
         <v>0.17098445595854916</v>
       </c>
       <c r="K105" s="11">
@@ -7433,7 +7439,7 @@
         <v>15.24</v>
       </c>
       <c r="J106" s="12">
-        <f>E106/I106-1</f>
+        <f t="shared" si="3"/>
         <v>1.7723097112860891</v>
       </c>
       <c r="K106" s="11">
@@ -7487,7 +7493,7 @@
         <v>10.36</v>
       </c>
       <c r="J107" s="12">
-        <f>E107/I107-1</f>
+        <f t="shared" si="3"/>
         <v>0.31853281853281867</v>
       </c>
       <c r="K107" s="11">
@@ -7541,7 +7547,7 @@
         <v>4.47</v>
       </c>
       <c r="J108" s="12">
-        <f>E108/I108-1</f>
+        <f t="shared" si="3"/>
         <v>1.1789709172259508</v>
       </c>
       <c r="K108" s="11">
@@ -7595,7 +7601,7 @@
         <v>22.4</v>
       </c>
       <c r="J109" s="12">
-        <f>E109/I109-1</f>
+        <f t="shared" si="3"/>
         <v>0.3035714285714286</v>
       </c>
       <c r="K109" s="11">
@@ -7649,7 +7655,7 @@
         <v>21.5</v>
       </c>
       <c r="J110" s="12">
-        <f>E110/I110-1</f>
+        <f t="shared" si="3"/>
         <v>0.59999999999999987</v>
       </c>
       <c r="K110" s="11">
@@ -7691,7 +7697,7 @@
         <v>5.08</v>
       </c>
       <c r="J111" s="12">
-        <f>E111/I111-1</f>
+        <f t="shared" si="3"/>
         <v>0.41732283464566922</v>
       </c>
       <c r="K111" s="11">
@@ -7733,7 +7739,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="J112" s="12">
-        <f>E112/I112-1</f>
+        <f t="shared" si="3"/>
         <v>0.4655172413793105</v>
       </c>
       <c r="K112" s="11">
@@ -7775,7 +7781,7 @@
         <v>3.89</v>
       </c>
       <c r="J113" s="12">
-        <f>E113/I113-1</f>
+        <f t="shared" si="3"/>
         <v>0.3316195372750641</v>
       </c>
       <c r="K113" s="11">
@@ -7817,7 +7823,7 @@
         <v>5.23</v>
       </c>
       <c r="J114" s="12">
-        <f>E114/I114-1</f>
+        <f t="shared" si="3"/>
         <v>0.42256214149139582</v>
       </c>
       <c r="K114" s="11">
@@ -7859,7 +7865,7 @@
         <v>4.26</v>
       </c>
       <c r="J115" s="12">
-        <f>E115/I115-1</f>
+        <f t="shared" si="3"/>
         <v>0.69483568075117375</v>
       </c>
       <c r="K115" s="11">
@@ -7901,7 +7907,7 @@
         <v>3.33</v>
       </c>
       <c r="J116" s="12">
-        <f>E116/I116-1</f>
+        <f t="shared" si="3"/>
         <v>0.25225225225225212</v>
       </c>
       <c r="K116" s="11">
@@ -7912,6 +7918,16 @@
       </c>
       <c r="O116" s="6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B117" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="118" spans="2:15" x14ac:dyDescent="0.5">
+      <c r="B118" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445C1F60-9B94-4298-B704-CFA83046C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FEBD13-20B9-48E0-8AC1-B726DC376CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="378">
   <si>
     <t>Ticker</t>
   </si>
@@ -1224,6 +1224,15 @@
   </si>
   <si>
     <t>9959.HK</t>
+  </si>
+  <si>
+    <t>ZHIHU-W</t>
+  </si>
+  <si>
+    <t>LINKLOGIS-W</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
   </si>
 </sst>
 </file>
@@ -1808,13 +1817,13 @@
         <v>148</v>
       </c>
       <c r="E2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>8671382528</v>
+        <v>8111938560</v>
       </c>
       <c r="H2" s="6">
         <v>3.35</v>
@@ -1823,11 +1832,11 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.31355932203389836</v>
+        <f>E2/I2-1</f>
+        <v>0.22881355932203395</v>
       </c>
       <c r="K2" s="11">
-        <v>4.9354838709677419E-2</v>
+        <v>5.2758620689655172E-2</v>
       </c>
       <c r="L2" s="13">
         <v>1871151000</v>
@@ -1842,7 +1851,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.44683188783843514</v>
+        <v>0.51069152013549879</v>
       </c>
       <c r="Q2" s="12">
         <v>0.28956319566547578</v>
@@ -1853,53 +1862,53 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="E3">
-        <v>6.32</v>
+        <v>2.89</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>24660893696</v>
+        <v>2613106176</v>
       </c>
       <c r="H3" s="6">
-        <v>7.28</v>
+        <v>3.55</v>
       </c>
       <c r="I3" s="6">
-        <v>4.22</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>0.49763033175355464</v>
+        <f>E3/I3-1</f>
+        <v>0.24568965517241392</v>
       </c>
       <c r="K3" s="11">
-        <v>6.8037974683544293E-3</v>
+        <v>5.8477508650519032E-2</v>
       </c>
       <c r="L3" s="13">
-        <v>786762000</v>
+        <v>504294000</v>
       </c>
       <c r="M3" s="13">
-        <v>2279244000</v>
+        <v>1704754000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O3" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.35201451099625231</v>
+        <v>0.39738622480117308</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.34518550887925997</v>
+        <v>0.29581628786323422</v>
       </c>
       <c r="R3" s="14">
         <v>2</v>
@@ -1907,41 +1916,41 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>356</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>2.92</v>
+        <v>13.82</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>2640231936</v>
+        <v>264646082560</v>
       </c>
       <c r="H4" s="6">
-        <v>3.55</v>
+        <v>15.1</v>
       </c>
       <c r="I4" s="6">
-        <v>2.3199999999999998</v>
+        <v>9.52</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.25862068965517238</v>
+        <f>E4/I4-1</f>
+        <v>0.45168067226890773</v>
       </c>
       <c r="K4" s="11">
-        <v>5.7876712328767128E-2</v>
+        <v>0.11215629522431259</v>
       </c>
       <c r="L4" s="13">
-        <v>504294000</v>
+        <v>70144988000</v>
       </c>
       <c r="M4" s="13">
-        <v>1704754000</v>
+        <v>269343749000</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>51</v>
@@ -1950,67 +1959,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.38959157993148558</v>
+        <v>0.50196093519834883</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.29581628786323422</v>
+        <v>0.26042924055386191</v>
       </c>
       <c r="R4" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E5">
-        <v>13.26</v>
+        <v>6.95</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>259457089536</v>
+        <v>27119177728</v>
       </c>
       <c r="H5" s="6">
-        <v>15.14</v>
+        <v>7.26</v>
       </c>
       <c r="I5" s="6">
-        <v>9.52</v>
+        <v>4.22</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.39285714285714279</v>
+        <f>E5/I5-1</f>
+        <v>0.64691943127962093</v>
       </c>
       <c r="K5" s="11">
-        <v>0.11689291101055807</v>
+        <v>6.18705035971223E-3</v>
       </c>
       <c r="L5" s="13">
-        <v>70144988000</v>
+        <v>786762000</v>
       </c>
       <c r="M5" s="13">
-        <v>269343749000</v>
+        <v>2279244000</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O5" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.52003538584734221</v>
+        <v>0.30797805365261161</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.26042924055386191</v>
+        <v>0.34518550887925997</v>
       </c>
       <c r="R5" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -2024,13 +2033,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>128.19999999999999</v>
+        <v>133.4</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>84659814400</v>
+        <v>88093753344</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2039,11 +2048,11 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.40879120879120867</v>
+        <f>E6/I6-1</f>
+        <v>0.46593406593406606</v>
       </c>
       <c r="K6" s="11">
-        <v>1.5210608424336974E-2</v>
+        <v>1.4617691154422787E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2058,13 +2067,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.58877997253592906</v>
+        <v>0.53537855108079613</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
       </c>
       <c r="R6" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
@@ -2078,13 +2087,13 @@
         <v>223</v>
       </c>
       <c r="E7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>1670000000</v>
+        <v>1660000000</v>
       </c>
       <c r="H7" s="6">
         <v>1.88</v>
@@ -2093,11 +2102,11 @@
         <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0.23703703703703694</v>
+        <f>E7/I7-1</f>
+        <v>0.22962962962962941</v>
       </c>
       <c r="K7" s="11">
-        <v>0.12574850299401197</v>
+        <v>0.12650602409638553</v>
       </c>
       <c r="L7" s="13">
         <v>315190000</v>
@@ -2112,160 +2121,160 @@
         <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>0.17142533923116124</v>
+        <v>0.17236278486287374</v>
       </c>
       <c r="Q7" s="12">
         <v>0.51857007005524791</v>
       </c>
       <c r="R7" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="E8">
-        <v>6.76</v>
+        <v>2.61</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>171674943488</v>
+        <v>13287692288</v>
       </c>
       <c r="H8" s="6">
-        <v>8.49</v>
+        <v>3.3023729999999998</v>
       </c>
       <c r="I8" s="6">
-        <v>4.58</v>
+        <v>2.23</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.47598253275109159</v>
+        <f>E8/I8-1</f>
+        <v>0.17040358744394624</v>
       </c>
       <c r="K8" s="11">
-        <v>3.7721893491124266E-2</v>
+        <v>0.11494252873563218</v>
       </c>
       <c r="L8" s="13">
-        <v>29168443138.220001</v>
+        <v>2527643000</v>
       </c>
       <c r="M8" s="13">
-        <v>100996030941.41</v>
+        <v>16480074000</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O8" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.18172499139277135</v>
+        <v>0.44693614015450328</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.2888078161719172</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R8" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="E9">
-        <v>2.69</v>
+        <v>1.35</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>13694978048</v>
+        <v>2719237632</v>
       </c>
       <c r="H9" s="6">
-        <v>3.35</v>
+        <v>1.62</v>
       </c>
       <c r="I9" s="6">
-        <v>2.23</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20627802690582953</v>
+        <f>E9/I9-1</f>
+        <v>0.19469026548672574</v>
       </c>
       <c r="K9" s="11">
-        <v>0.11152416356877323</v>
+        <v>8.8148148148148142E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>2527643000</v>
+        <v>929863000</v>
       </c>
       <c r="M9" s="13">
-        <v>16480074000</v>
+        <v>6026676000</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O9" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.41691182058981441</v>
+        <v>0.39578416296319474</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.15429118804462028</v>
       </c>
       <c r="R9" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E10">
-        <v>1.33</v>
+        <v>6.89</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>2678952448</v>
+        <v>176142155776</v>
       </c>
       <c r="H10" s="6">
-        <v>1.62</v>
+        <v>8.49</v>
       </c>
       <c r="I10" s="6">
-        <v>1.1299999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.17699115044247815</v>
+        <f>E10/I10-1</f>
+        <v>0.50436681222707413</v>
       </c>
       <c r="K10" s="11">
-        <v>8.9473684210526302E-2</v>
+        <v>3.7010159651669088E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>929863000</v>
+        <v>29168443138.220001</v>
       </c>
       <c r="M10" s="13">
-        <v>6026676000</v>
+        <v>100996030941.41</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>51</v>
@@ -2274,52 +2283,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.40223989942011568</v>
+        <v>0.17711118013417754</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.15429118804462028</v>
+        <v>0.2888078161719172</v>
       </c>
       <c r="R10" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="D11" t="s">
-        <v>306</v>
+        <v>96</v>
       </c>
       <c r="E11">
-        <v>5.26</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>370706939904</v>
+        <v>9511327744</v>
       </c>
       <c r="H11" s="6">
-        <v>5.44</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="I11" s="6">
-        <v>2.5099999999999998</v>
+        <v>3.15</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>1.095617529880478</v>
+        <f>E11/I11-1</f>
+        <v>0.46031746031746024</v>
       </c>
       <c r="K11" s="11">
-        <v>3.4220532319391636E-2</v>
+        <v>5.4347826086956527E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>72477000000</v>
+        <v>1576240000</v>
       </c>
       <c r="M11" s="13">
-        <v>319355000000</v>
+        <v>9636462000</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>51</v>
@@ -2328,52 +2337,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P11" s="12">
-        <v>0.19343619083097988</v>
+        <v>0.32083862795437695</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.22694806719794586</v>
+        <v>0.16357040581906512</v>
       </c>
       <c r="R11" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>300</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="E12">
-        <v>4.5199999999999996</v>
+        <v>1.45</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>9345913856</v>
+        <v>1715060096</v>
       </c>
       <c r="H12" s="6">
-        <v>4.9800000000000004</v>
+        <v>2.77</v>
       </c>
       <c r="I12" s="6">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.43492063492063493</v>
+        <f>E12/I12-1</f>
+        <v>6.6176470588235281E-2</v>
       </c>
       <c r="K12" s="11">
-        <v>5.5309734513274339E-2</v>
+        <v>4.2068965517241382E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>1576240000</v>
+        <v>841215000</v>
       </c>
       <c r="M12" s="13">
-        <v>9636462000</v>
+        <v>5774434000</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>51</v>
@@ -2382,52 +2391,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.3312787531704886</v>
+        <v>0.67290080717211942</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.16357040581906512</v>
+        <v>0.14567921288909008</v>
       </c>
       <c r="R12" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>305</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>306</v>
       </c>
       <c r="E13">
-        <v>2.81</v>
+        <v>5.72</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>17425428480</v>
+        <v>385840873472</v>
       </c>
       <c r="H13" s="6">
-        <v>5.19</v>
+        <v>5.87</v>
       </c>
       <c r="I13" s="6">
-        <v>2.11</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
-        <v>0.33175355450236976</v>
+        <f>E13/I13-1</f>
+        <v>1.2788844621513946</v>
       </c>
       <c r="K13" s="11">
-        <v>5.6939501779359428E-2</v>
+        <v>3.1468531468531472E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>2906500000</v>
+        <v>72477000000</v>
       </c>
       <c r="M13" s="13">
-        <v>10569000000</v>
+        <v>319355000000</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>51</v>
@@ -2436,52 +2445,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.17034531014964546</v>
+        <v>0.18638947778842715</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.27500236540826944</v>
+        <v>0.22694806719794586</v>
       </c>
       <c r="R13" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="D14" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E14">
-        <v>1.51</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>1786028032</v>
+        <v>147296157696</v>
       </c>
       <c r="H14" s="6">
-        <v>2.77</v>
+        <v>17.88</v>
       </c>
       <c r="I14" s="6">
-        <v>1.36</v>
+        <v>10.6</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
-        <v>0.11029411764705865</v>
+        <f>E14/I14-1</f>
+        <v>0.55094339622641519</v>
       </c>
       <c r="K14" s="11">
-        <v>4.0397350993377483E-2</v>
+        <v>4.373479318734793E-2</v>
       </c>
       <c r="L14" s="13">
-        <v>841215000</v>
+        <v>21175963859.630001</v>
       </c>
       <c r="M14" s="13">
-        <v>5774434000</v>
+        <v>104071284594.97</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>51</v>
@@ -2490,52 +2499,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.63895008648350404</v>
+        <v>0.19420462608297778</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.14567921288909008</v>
+        <v>0.20347556909712136</v>
       </c>
       <c r="R14" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>15.96</v>
+        <v>5.93</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>144769499136</v>
+        <v>7385340416</v>
       </c>
       <c r="H15" s="6">
-        <v>17.88</v>
+        <v>8.6</v>
       </c>
       <c r="I15" s="6">
-        <v>10.6</v>
+        <v>3.46</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
-        <v>0.50566037735849068</v>
+        <f>E15/I15-1</f>
+        <v>0.71387283236994215</v>
       </c>
       <c r="K15" s="11">
-        <v>4.5050125313283201E-2</v>
+        <v>2.3777403035413151E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>21175963859.630001</v>
+        <v>921702000</v>
       </c>
       <c r="M15" s="13">
-        <v>104071284594.97</v>
+        <v>5262544000</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>51</v>
@@ -2544,13 +2553,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.19851010441398781</v>
+        <v>0.19980426597563555</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.20347556909712136</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2564,13 +2573,13 @@
         <v>308</v>
       </c>
       <c r="E16">
-        <v>13.04</v>
+        <v>14.14</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>46866022400</v>
+        <v>50819444736</v>
       </c>
       <c r="H16" s="6">
         <v>16.600000000000001</v>
@@ -2579,11 +2588,11 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="0"/>
-        <v>0.7271523178807946</v>
+        <f>E16/I16-1</f>
+        <v>0.87284768211920549</v>
       </c>
       <c r="K16" s="11">
-        <v>2.6840490797546013E-2</v>
+        <v>2.475247524752475E-2</v>
       </c>
       <c r="L16" s="13">
         <v>25585077000</v>
@@ -2598,67 +2607,67 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.30242053047122414</v>
+        <v>0.28891927157188818</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="E17">
-        <v>7.39</v>
+        <v>7.34</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>94815174656</v>
+        <v>7248499712</v>
       </c>
       <c r="H17" s="6">
-        <v>7.45</v>
+        <v>9.07</v>
       </c>
       <c r="I17" s="6">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="0"/>
-        <v>0.52685950413223148</v>
+        <f>E17/I17-1</f>
+        <v>0.46799999999999997</v>
       </c>
       <c r="K17" s="11">
-        <v>8.6603518267929641E-3</v>
+        <v>4.8228882833787463E-2</v>
       </c>
       <c r="L17" s="13">
-        <v>2553000000</v>
+        <v>1333116000</v>
       </c>
       <c r="M17" s="13">
-        <v>13971000000</v>
+        <v>8019803000</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O17" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.18242264945874517</v>
+        <v>0.2014766292813687</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.18273566673824351</v>
+        <v>0.16622802330680692</v>
       </c>
       <c r="R17" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
@@ -2672,26 +2681,26 @@
         <v>83</v>
       </c>
       <c r="E18">
-        <v>15.66</v>
+        <v>15.78</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>32599107584</v>
+        <v>32412909568</v>
       </c>
       <c r="H18" s="6">
-        <v>15.84</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I18" s="6">
         <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="0"/>
-        <v>0.96733668341708556</v>
+        <f>E18/I18-1</f>
+        <v>0.98241206030150741</v>
       </c>
       <c r="K18" s="11">
-        <v>7.1519795657726704E-2</v>
+        <v>7.0975918884664146E-2</v>
       </c>
       <c r="L18" s="13">
         <v>5451928473.2399998</v>
@@ -2706,13 +2715,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P18" s="12">
-        <v>0.1615069503518686</v>
+        <v>0.16234511859062811</v>
       </c>
       <c r="Q18" s="12">
         <v>0.20973136925592797</v>
       </c>
       <c r="R18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
@@ -2726,13 +2735,13 @@
         <v>74</v>
       </c>
       <c r="E19">
-        <v>2.3199999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>2412359168</v>
+        <v>2381164800</v>
       </c>
       <c r="H19" s="6">
         <v>3.34</v>
@@ -2741,11 +2750,11 @@
         <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20833333333333326</v>
+        <f>E19/I19-1</f>
+        <v>0.19270833333333348</v>
       </c>
       <c r="K19" s="11">
-        <v>0.12586206896551724</v>
+        <v>0.12751091703056769</v>
       </c>
       <c r="L19" s="13">
         <v>762183000</v>
@@ -2760,52 +2769,52 @@
         <v>1</v>
       </c>
       <c r="P19" s="12">
-        <v>0.24139590873418154</v>
+        <v>0.24380464255081513</v>
       </c>
       <c r="Q19" s="12">
         <v>0.15218339726363278</v>
       </c>
       <c r="R19" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>294</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>83</v>
       </c>
       <c r="E20">
-        <v>7.38</v>
+        <v>15.78</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>7288001024</v>
+        <v>32412909568</v>
       </c>
       <c r="H20" s="6">
-        <v>9.07</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I20" s="6">
-        <v>5</v>
+        <v>7.96</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="0"/>
-        <v>0.47599999999999998</v>
+        <f>E20/I20-1</f>
+        <v>0.98241206030150741</v>
       </c>
       <c r="K20" s="11">
-        <v>4.7967479674796747E-2</v>
+        <v>7.0975918884664146E-2</v>
       </c>
       <c r="L20" s="13">
-        <v>1333116000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M20" s="13">
-        <v>8019803000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>51</v>
@@ -2814,67 +2823,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>0.20035706568750702</v>
+        <v>0.16234511859062811</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.16622802330680692</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E21">
-        <v>15.66</v>
+        <v>7.32</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>32599107584</v>
+        <v>93917061120</v>
       </c>
       <c r="H21" s="6">
-        <v>15.84</v>
+        <v>7.75</v>
       </c>
       <c r="I21" s="6">
-        <v>7.96</v>
+        <v>4.84</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="0"/>
-        <v>0.96733668341708556</v>
+        <f>E21/I21-1</f>
+        <v>0.5123966942148761</v>
       </c>
       <c r="K21" s="11">
-        <v>7.1519795657726704E-2</v>
+        <v>8.7431693989071038E-3</v>
       </c>
       <c r="L21" s="13">
-        <v>5451928473.2399998</v>
+        <v>2553000000</v>
       </c>
       <c r="M21" s="13">
-        <v>25994816572.18</v>
+        <v>13971000000</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O21" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P21" s="12">
-        <v>0.1615069503518686</v>
+        <v>0.18395733587750812</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.18273566673824351</v>
       </c>
       <c r="R21" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
@@ -2888,26 +2897,26 @@
         <v>87</v>
       </c>
       <c r="E22">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>1597612288</v>
+        <v>1663267584</v>
       </c>
       <c r="H22" s="6">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="I22" s="6">
         <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="0"/>
-        <v>0.73809523809523814</v>
+        <f>E22/I22-1</f>
+        <v>0.80952380952380953</v>
       </c>
       <c r="K22" s="11">
-        <v>5.0684931506849315E-2</v>
+        <v>4.8684210526315788E-2</v>
       </c>
       <c r="L22" s="13">
         <v>219938000</v>
@@ -2922,52 +2931,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P22" s="12">
-        <v>0.32728377071537917</v>
+        <v>0.29986224591557764</v>
       </c>
       <c r="Q22" s="12">
         <v>0.14466826109721026</v>
       </c>
       <c r="R22" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>354</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E23">
-        <v>24.25</v>
+        <v>13.92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>64338644992</v>
+        <v>11585448960</v>
       </c>
       <c r="H23" s="6">
-        <v>25.8</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I23" s="6">
-        <v>15.7</v>
+        <v>12.12</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="0"/>
-        <v>0.54458598726114649</v>
+        <f>E23/I23-1</f>
+        <v>0.14851485148514865</v>
       </c>
       <c r="K23" s="11">
-        <v>1.1216494845360825E-2</v>
+        <v>1.0632183908045977E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>1069250000</v>
+        <v>199557000</v>
       </c>
       <c r="M23" s="13">
-        <v>2571093000</v>
+        <v>1108087000</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>72</v>
@@ -2976,121 +2985,121 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P23" s="12">
-        <v>0.13351687759020417</v>
+        <v>0.18231720125702217</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.41587371596437778</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E24">
-        <v>14.1</v>
+        <v>7.76</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>11735261184</v>
+        <v>67193843712</v>
       </c>
       <c r="H24" s="6">
-        <v>19.440000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="I24" s="6">
-        <v>12.12</v>
+        <v>7.08</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="0"/>
-        <v>0.16336633663366351</v>
+        <f>E24/I24-1</f>
+        <v>9.6045197740112886E-2</v>
       </c>
       <c r="K24" s="11">
-        <v>1.049645390070922E-2</v>
+        <v>4.0721649484536084E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>199557000</v>
+        <v>13438000000</v>
       </c>
       <c r="M24" s="13">
-        <v>1108087000</v>
+        <v>88611000000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O24" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>0.17912992702590763</v>
+        <v>0.22643695147490772</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R24" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E25">
-        <v>7.88</v>
+        <v>25.2</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>68232925184</v>
+        <v>66859130880</v>
       </c>
       <c r="H25" s="6">
-        <v>9.23</v>
+        <v>26.15</v>
       </c>
       <c r="I25" s="6">
-        <v>7.08</v>
+        <v>15.7</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="0"/>
-        <v>0.11299435028248594</v>
+        <f>E25/I25-1</f>
+        <v>0.60509554140127397</v>
       </c>
       <c r="K25" s="11">
-        <v>4.0101522842639598E-2</v>
+        <v>1.0793650793650795E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>13438000000</v>
+        <v>1069250000</v>
       </c>
       <c r="M25" s="13">
-        <v>88611000000</v>
+        <v>2571093000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O25" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P25" s="12">
-        <v>0.22278583500850604</v>
+        <v>0.12826873829061827</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.41587371596437778</v>
       </c>
       <c r="R25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
@@ -3104,13 +3113,13 @@
         <v>79</v>
       </c>
       <c r="E26">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>138201825280</v>
+        <v>148746600448</v>
       </c>
       <c r="H26" s="6">
         <v>10.76</v>
@@ -3119,11 +3128,11 @@
         <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="0"/>
-        <v>0.17318435754189943</v>
+        <f>E26/I26-1</f>
+        <v>0.25698324022346375</v>
       </c>
       <c r="K26" s="11">
-        <v>5.7023809523809518E-2</v>
+        <v>5.3222222222222219E-2</v>
       </c>
       <c r="L26" s="13">
         <v>32866046000</v>
@@ -3138,106 +3147,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P26" s="12">
-        <v>0.20049289062485265</v>
+        <v>0.18910686920992248</v>
       </c>
       <c r="Q26" s="12">
         <v>0.15266623500015464</v>
       </c>
       <c r="R26" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="E27">
-        <v>6.41</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>7983142400</v>
+        <v>112262537216</v>
       </c>
       <c r="H27" s="6">
-        <v>8.6</v>
+        <v>13.6</v>
       </c>
       <c r="I27" s="6">
-        <v>3.46</v>
+        <v>6.57</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="0"/>
-        <v>0.85260115606936426</v>
+        <f>E27/I27-1</f>
+        <v>0.37747336377473362</v>
       </c>
       <c r="K27" s="11">
-        <v>2.1996879875195004E-2</v>
+        <v>5.5248618784530384E-3</v>
       </c>
       <c r="L27" s="13">
-        <v>921702000</v>
+        <v>2125459000</v>
       </c>
       <c r="M27" s="13">
-        <v>5262544000</v>
+        <v>9202253000</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O27" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P27" s="12">
-        <v>0.17819043213287719</v>
+        <v>0.14173517763216131</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.23097158924015673</v>
       </c>
       <c r="R27" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>332</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="E28">
-        <v>9.24</v>
+        <v>11.16</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>114619424768</v>
+        <v>17906778112</v>
       </c>
       <c r="H28" s="6">
-        <v>13.6</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I28" s="6">
-        <v>6.57</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
-        <v>0.40639269406392686</v>
+        <f>E28/I28-1</f>
+        <v>0.1588785046728971</v>
       </c>
       <c r="K28" s="11">
-        <v>5.411255411255411E-3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="13">
-        <v>2125459000</v>
+        <v>634792000</v>
       </c>
       <c r="M28" s="13">
-        <v>9202253000</v>
+        <v>5195491000</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>72</v>
@@ -3246,52 +3255,52 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P28" s="12">
-        <v>0.13889725341894968</v>
+        <v>0.24979526264118315</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.23097158924015673</v>
+        <v>0.12218132992627646</v>
       </c>
       <c r="R28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>124</v>
+        <v>291</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E29">
-        <v>4.8</v>
+        <v>3.63</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>7036656640</v>
+        <v>2084273408</v>
       </c>
       <c r="H29" s="6">
-        <v>5.04</v>
+        <v>4.84</v>
       </c>
       <c r="I29" s="6">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="0"/>
-        <v>0.39130434782608692</v>
+        <f>E29/I29-1</f>
+        <v>0.29642857142857149</v>
       </c>
       <c r="K29" s="11">
-        <v>0.1</v>
+        <v>7.1625344352617082E-2</v>
       </c>
       <c r="L29" s="13">
-        <v>784607000</v>
+        <v>424258000</v>
       </c>
       <c r="M29" s="13">
-        <v>7872586000</v>
+        <v>2485347000</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>68</v>
@@ -3300,64 +3309,64 @@
         <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>0.59613587655626854</v>
+        <v>0.16920489780271125</v>
       </c>
       <c r="Q29" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>0.17070372869462494</v>
       </c>
       <c r="R29" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>276</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>332</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>5.57</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>17650051072</v>
+        <v>50504581120</v>
       </c>
       <c r="H30" s="6">
-        <v>18.399999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="I30" s="6">
-        <v>9.6300000000000008</v>
+        <v>3.39</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
-        <v>0.14226375908618882</v>
+        <f>E30/I30-1</f>
+        <v>0.64306784660766958</v>
       </c>
       <c r="K30" s="11">
-        <v>0</v>
+        <v>5.5116696588868939E-2</v>
       </c>
       <c r="L30" s="13">
-        <v>634792000</v>
+        <v>5594372000</v>
       </c>
       <c r="M30" s="13">
-        <v>5195491000</v>
+        <v>26933044000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O30" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.25311951005732741</v>
+        <v>0.14332718755607407</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.12218132992627646</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R30" s="14">
         <v>22</v>
@@ -3365,53 +3374,53 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E31">
-        <v>5.49</v>
+        <v>4.59</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>5817094144</v>
+        <v>13094444032</v>
       </c>
       <c r="H31" s="6">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="I31" s="6">
-        <v>3.97</v>
+        <v>3.22</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="0"/>
-        <v>0.38287153652392947</v>
+        <f>E31/I31-1</f>
+        <v>0.42546583850931663</v>
       </c>
       <c r="K31" s="11">
-        <v>8.9253187613843349E-2</v>
+        <v>9.1503267973856214E-3</v>
       </c>
       <c r="L31" s="13">
-        <v>866801000</v>
+        <v>259348000</v>
       </c>
       <c r="M31" s="13">
-        <v>7530053000</v>
+        <v>1677627000</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O31" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P31" s="12">
-        <v>0.30723230563220139</v>
+        <v>0.17882841123054241</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R31" s="14">
         <v>23</v>
@@ -3419,41 +3428,41 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>291</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E32">
-        <v>3.8</v>
+        <v>5.58</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>2181883904</v>
+        <v>5912791040</v>
       </c>
       <c r="H32" s="6">
-        <v>4.9000000000000004</v>
+        <v>5.99</v>
       </c>
       <c r="I32" s="6">
-        <v>2.8</v>
+        <v>3.97</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
-        <v>0.35714285714285721</v>
+        <f>E32/I32-1</f>
+        <v>0.40554156171284639</v>
       </c>
       <c r="K32" s="11">
-        <v>7.8947368421052627E-2</v>
+        <v>8.7813620071684584E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>424258000</v>
+        <v>866801000</v>
       </c>
       <c r="M32" s="13">
-        <v>2485347000</v>
+        <v>7530053000</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>68</v>
@@ -3462,13 +3471,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.16286464989656568</v>
+        <v>0.29715311599512767</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.17070372869462494</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R32" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
@@ -3497,7 +3506,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
+        <f>E33/I33-1</f>
         <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
@@ -3527,95 +3536,95 @@
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C34" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E34">
-        <v>11.3</v>
+        <v>4.05</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>18075480064</v>
+        <v>15706224640</v>
       </c>
       <c r="H34" s="6">
-        <v>11.84</v>
+        <v>6.97</v>
       </c>
       <c r="I34" s="6">
-        <v>8.67</v>
+        <v>3.33</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>0.30334486735870825</v>
+        <f>E34/I34-1</f>
+        <v>0.21621621621621623</v>
       </c>
       <c r="K34" s="11">
-        <v>5.3097345132743355E-2</v>
+        <v>6.666666666666668E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>1721368005.75</v>
+        <v>2823432000</v>
       </c>
       <c r="M34" s="13">
-        <v>14620942286.52</v>
+        <v>16925205000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O34" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P34" s="12">
-        <v>0.21588350738749548</v>
+        <v>0.16876870365102881</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.11773304155211949</v>
+        <v>0.16681818624944278</v>
       </c>
       <c r="R34" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>344</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E35">
-        <v>4.5199999999999996</v>
+        <v>11.06</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>52122832896</v>
+        <v>17625880576</v>
       </c>
       <c r="H35" s="6">
-        <v>5.14</v>
+        <v>11.84</v>
       </c>
       <c r="I35" s="6">
-        <v>3.46</v>
+        <v>8.67</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="1"/>
-        <v>0.30635838150289008</v>
+        <f>E35/I35-1</f>
+        <v>0.27566320645905429</v>
       </c>
       <c r="K35" s="11">
-        <v>5.2212389380530973E-2</v>
+        <v>5.4249547920433995E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>4734613000</v>
+        <v>1721368005.75</v>
       </c>
       <c r="M35" s="13">
-        <v>16213395000</v>
+        <v>14620942286.52</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>51</v>
@@ -3624,64 +3633,64 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>0.10342458469693973</v>
+        <v>0.22791209888208908</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.11773304155211949</v>
       </c>
       <c r="R35" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E36">
-        <v>4.99</v>
+        <v>5.32</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>14235571200</v>
+        <v>7798961152</v>
       </c>
       <c r="H36" s="6">
-        <v>6.21</v>
+        <v>5.42</v>
       </c>
       <c r="I36" s="6">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="1"/>
-        <v>0.54968944099378869</v>
+        <f>E36/I36-1</f>
+        <v>0.54202898550724643</v>
       </c>
       <c r="K36" s="11">
-        <v>8.4168336673346687E-3</v>
+        <v>9.0225563909774431E-2</v>
       </c>
       <c r="L36" s="13">
-        <v>259348000</v>
+        <v>784607000</v>
       </c>
       <c r="M36" s="13">
-        <v>1677627000</v>
+        <v>7872586000</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O36" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P36" s="12">
-        <v>0.16223361728966321</v>
+        <v>0.37749454890417783</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.15459217096529801</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R36" s="14">
         <v>26</v>
@@ -3689,56 +3698,56 @@
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>28</v>
+        <v>290</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>348</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E37">
-        <v>5.88</v>
+        <v>4.26</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>53315428352</v>
+        <v>4690047488</v>
       </c>
       <c r="H37" s="6">
-        <v>7.38</v>
+        <v>4.49</v>
       </c>
       <c r="I37" s="6">
-        <v>3.39</v>
+        <v>3.58</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="1"/>
-        <v>0.734513274336283</v>
+        <f>E37/I37-1</f>
+        <v>0.1899441340782122</v>
       </c>
       <c r="K37" s="11">
-        <v>5.2210884353741494E-2</v>
+        <v>7.5117370892018781E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>5594372000</v>
+        <v>765224000</v>
       </c>
       <c r="M37" s="13">
-        <v>26933044000</v>
+        <v>5249449000</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O37" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.13427632879892507</v>
+        <v>0.18772475200360744</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.14577225152582682</v>
       </c>
       <c r="R37" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
@@ -3752,26 +3761,26 @@
         <v>50</v>
       </c>
       <c r="E38">
-        <v>5.66</v>
+        <v>6.07</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>12657344512</v>
+        <v>13574220800</v>
       </c>
       <c r="H38" s="6">
-        <v>5.69</v>
+        <v>6.4</v>
       </c>
       <c r="I38" s="6">
         <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="1"/>
-        <v>1.6203703703703702</v>
+        <f>E38/I38-1</f>
+        <v>1.8101851851851851</v>
       </c>
       <c r="K38" s="11">
-        <v>4.0812720848056538E-2</v>
+        <v>3.8056013179571663E-2</v>
       </c>
       <c r="L38" s="13">
         <v>2184074765.02</v>
@@ -3786,7 +3795,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>0.57129919158069953</v>
+        <v>0.4665637453990078</v>
       </c>
       <c r="Q38" s="12">
         <v>9.29654274042198E-2</v>
@@ -3797,53 +3806,53 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C39" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>306</v>
       </c>
       <c r="E39">
-        <v>4.38</v>
+        <v>3.03</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>4822161408</v>
+        <v>34849546240</v>
       </c>
       <c r="H39" s="6">
-        <v>4.49</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="I39" s="6">
-        <v>3.58</v>
+        <v>2.35</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="1"/>
-        <v>0.22346368715083798</v>
+        <f>E39/I39-1</f>
+        <v>0.28936170212765955</v>
       </c>
       <c r="K39" s="11">
-        <v>7.3059360730593617E-2</v>
+        <v>6.2706270627062716E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>765224000</v>
+        <v>9414000000</v>
       </c>
       <c r="M39" s="13">
-        <v>5249449000</v>
+        <v>81589000000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O39" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P39" s="12">
-        <v>0.18183155724704525</v>
+        <v>0.20458912808029497</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.14577225152582682</v>
+        <v>0.11538320116682396</v>
       </c>
       <c r="R39" s="14">
         <v>28</v>
@@ -3860,13 +3869,13 @@
         <v>75</v>
       </c>
       <c r="E40">
-        <v>5.69</v>
+        <v>5.42</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>15182114816</v>
+        <v>14461698048</v>
       </c>
       <c r="H40" s="6">
         <v>7.13</v>
@@ -3875,11 +3884,11 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="1"/>
-        <v>0.3710843373493975</v>
+        <f>E40/I40-1</f>
+        <v>0.30602409638554207</v>
       </c>
       <c r="K40" s="11">
-        <v>4.0421792618629174E-2</v>
+        <v>4.2435424354243544E-2</v>
       </c>
       <c r="L40" s="13">
         <v>2030839000</v>
@@ -3894,7 +3903,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.14242928543114775</v>
+        <v>0.14949933951147382</v>
       </c>
       <c r="Q40" s="12">
         <v>0.17526328902672489</v>
@@ -3905,41 +3914,41 @@
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E41">
-        <v>5.29</v>
+        <v>4.68</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>62438400000</v>
+        <v>53967884288</v>
       </c>
       <c r="H41" s="6">
-        <v>5.77</v>
+        <v>5.14</v>
       </c>
       <c r="I41" s="6">
-        <v>4.12</v>
+        <v>3.46</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="1"/>
-        <v>0.28398058252427183</v>
+        <f>E41/I41-1</f>
+        <v>0.35260115606936404</v>
       </c>
       <c r="K41" s="11">
-        <v>4.4990548204158785E-2</v>
+        <v>5.0427350427350429E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>5687261000</v>
+        <v>4734613000</v>
       </c>
       <c r="M41" s="13">
-        <v>21716551000</v>
+        <v>16213395000</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>51</v>
@@ -3948,10 +3957,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>0.10236676985946681</v>
+        <v>9.9664779649589932E-2</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.26188601495697911</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R41" s="14">
         <v>30</v>
@@ -3959,41 +3968,41 @@
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>334</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>87</v>
       </c>
       <c r="E42">
-        <v>3.25</v>
+        <v>5.36</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>37379874816</v>
+        <v>63264616448</v>
       </c>
       <c r="H42" s="6">
-        <v>4.1100000000000003</v>
+        <v>5.77</v>
       </c>
       <c r="I42" s="6">
-        <v>2.2200000000000002</v>
+        <v>4.12</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="1"/>
-        <v>0.46396396396396389</v>
+        <f>E42/I42-1</f>
+        <v>0.30097087378640786</v>
       </c>
       <c r="K42" s="11">
-        <v>5.8461538461538461E-2</v>
+        <v>4.4402985074626859E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>9414000000</v>
+        <v>5687261000</v>
       </c>
       <c r="M42" s="13">
-        <v>81589000000</v>
+        <v>21716551000</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>51</v>
@@ -4002,10 +4011,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.1945742319089287</v>
+        <v>0.1009614311032022</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.11538320116682396</v>
+        <v>0.26188601495697911</v>
       </c>
       <c r="R42" s="14">
         <v>31</v>
@@ -4013,149 +4022,149 @@
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C43" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D43" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="E43">
-        <v>26.65</v>
+        <v>9.33</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>190039539712</v>
+        <v>23519436800</v>
       </c>
       <c r="H43" s="6">
-        <v>32.299999999999997</v>
+        <v>11.22</v>
       </c>
       <c r="I43" s="6">
-        <v>18.559999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="1"/>
-        <v>0.43588362068965525</v>
+        <f>E43/I43-1</f>
+        <v>1.1448275862068966</v>
       </c>
       <c r="K43" s="11">
-        <v>4.9493433395872422E-2</v>
+        <v>3.4083601286173631E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>61181051000</v>
+        <v>3301437000</v>
       </c>
       <c r="M43" s="13">
-        <v>532289194000</v>
+        <v>21814427000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O43" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P43" s="12">
-        <v>0.19554337009103015</v>
+        <v>0.16745628686162864</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.11493949471384535</v>
+        <v>0.15134190781174311</v>
       </c>
       <c r="R43" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C44" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="D44" t="s">
-        <v>330</v>
+        <v>181</v>
       </c>
       <c r="E44">
-        <v>6.01</v>
+        <v>6.5</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>12189963264</v>
+        <v>2521245952</v>
       </c>
       <c r="H44" s="6">
-        <v>8.0399999999999991</v>
+        <v>14.18</v>
       </c>
       <c r="I44" s="6">
-        <v>5.31</v>
+        <v>3.64</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="1"/>
-        <v>0.13182674199623357</v>
+        <f>E44/I44-1</f>
+        <v>0.78571428571428559</v>
       </c>
       <c r="K44" s="11">
-        <v>4.4925124792013313E-2</v>
+        <v>5.3846153846153842E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>1537565000</v>
+        <v>348303000</v>
       </c>
       <c r="M44" s="13">
-        <v>14484935000</v>
+        <v>3681615000</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O44" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P44" s="12">
-        <v>0.21048977508140268</v>
+        <v>0.31152109609489603</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.10614925092863724</v>
+        <v>9.4606035666412708E-2</v>
       </c>
       <c r="R44" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="E45">
-        <v>1.98</v>
+        <v>26.6</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>8474598400</v>
+        <v>189683007488</v>
       </c>
       <c r="H45" s="6">
-        <v>2.14</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="I45" s="6">
-        <v>1.33</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J45" s="12">
-        <f t="shared" si="1"/>
-        <v>0.488721804511278</v>
+        <f>E45/I45-1</f>
+        <v>0.43318965517241392</v>
       </c>
       <c r="K45" s="11">
-        <v>6.1616161616161617E-2</v>
+        <v>4.9586466165413533E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>1230913000</v>
+        <v>61181051000</v>
       </c>
       <c r="M45" s="13">
-        <v>10701340000</v>
+        <v>532289194000</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>51</v>
@@ -4164,214 +4173,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>0.18317201071359485</v>
+        <v>0.19575215896886974</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.11502419323187564</v>
+        <v>0.11493949471384535</v>
       </c>
       <c r="R45" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C46" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="E46">
-        <v>9.81</v>
+        <v>4.47</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>24729440256</v>
+        <v>30959308800</v>
       </c>
       <c r="H46" s="6">
-        <v>11.22</v>
+        <v>6.15</v>
       </c>
       <c r="I46" s="6">
-        <v>4.3499999999999996</v>
+        <v>3.71</v>
       </c>
       <c r="J46" s="12">
-        <f t="shared" si="1"/>
-        <v>1.2551724137931037</v>
+        <f>E46/I46-1</f>
+        <v>0.20485175202156336</v>
       </c>
       <c r="K46" s="11">
-        <v>3.2415902140672782E-2</v>
+        <v>4.8993288590604027E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>3301437000</v>
+        <v>4216348000</v>
       </c>
       <c r="M46" s="13">
-        <v>21814427000</v>
+        <v>46142120000</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O46" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P46" s="12">
-        <v>0.15777310630951955</v>
+        <v>0.37085121239714819</v>
       </c>
       <c r="Q46" s="12">
-        <v>0.15134190781174311</v>
+        <v>9.1377422623841298E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C47" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="E47">
-        <v>4.5999999999999996</v>
+        <v>4</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>31859691520</v>
+        <v>3696568064</v>
       </c>
       <c r="H47" s="6">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="I47" s="6">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="J47" s="12">
-        <f t="shared" si="1"/>
-        <v>0.23989218328840956</v>
+        <f>E47/I47-1</f>
+        <v>0.17647058823529416</v>
       </c>
       <c r="K47" s="11">
-        <v>4.7608695652173919E-2</v>
+        <v>3.6249999999999998E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>4216348000</v>
+        <v>754477000</v>
       </c>
       <c r="M47" s="13">
-        <v>46142120000</v>
+        <v>11677999000</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O47" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>0.34525881172915157</v>
+        <v>0.64103928766718776</v>
       </c>
       <c r="Q47" s="12">
-        <v>9.1377422623841298E-2</v>
+        <v>6.460670188445812E-2</v>
       </c>
       <c r="R47" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>326</v>
+        <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="E48">
-        <v>4.05</v>
+        <v>91</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>3743698688</v>
+        <v>253708910592</v>
       </c>
       <c r="H48" s="6">
-        <v>4.2</v>
+        <v>107.5</v>
       </c>
       <c r="I48" s="6">
-        <v>3.4</v>
+        <v>65.55</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="1"/>
-        <v>0.19117647058823528</v>
+        <f>E48/I48-1</f>
+        <v>0.38825324180015253</v>
       </c>
       <c r="K48" s="11">
-        <v>3.580246913580247E-2</v>
+        <v>2.4373626373626372E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>754477000</v>
+        <v>22510000000</v>
       </c>
       <c r="M48" s="13">
-        <v>11677999000</v>
+        <v>82545000000</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O48" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>0.61635761447571313</v>
+        <v>8.8551784431301322E-2</v>
       </c>
       <c r="Q48" s="12">
-        <v>6.460670188445812E-2</v>
+        <v>0.27269973953601068</v>
       </c>
       <c r="R48" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C49" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E49">
-        <v>23.35</v>
+        <v>1.96</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>237231341568</v>
+        <v>8388996096</v>
       </c>
       <c r="H49" s="6">
-        <v>36.450000000000003</v>
+        <v>2.14</v>
       </c>
       <c r="I49" s="6">
-        <v>19.239999999999998</v>
+        <v>1.33</v>
       </c>
       <c r="J49" s="12">
-        <f t="shared" si="1"/>
-        <v>0.2136174636174637</v>
+        <f>E49/I49-1</f>
+        <v>0.47368421052631571</v>
       </c>
       <c r="K49" s="11">
-        <v>4.1327623126338323E-2</v>
+        <v>6.224489795918367E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>25459748125.549999</v>
+        <v>1230913000</v>
       </c>
       <c r="M49" s="13">
-        <v>134815560756.77</v>
+        <v>10701340000</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>51</v>
@@ -4380,52 +4389,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>0.12070587695549247</v>
+        <v>0.18538236286373469</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.18884873513587705</v>
+        <v>0.11502419323187564</v>
       </c>
       <c r="R49" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>285</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>343</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E50">
-        <v>19.3</v>
+        <v>11.52</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>30802798592</v>
+        <v>64908754944</v>
       </c>
       <c r="H50" s="6">
-        <v>27.5</v>
+        <v>14.24</v>
       </c>
       <c r="I50" s="6">
-        <v>16.18</v>
+        <v>8.81</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="1"/>
-        <v>0.19283065512979003</v>
+        <f>E50/I50-1</f>
+        <v>0.30760499432463106</v>
       </c>
       <c r="K50" s="11">
-        <v>3.5544041450777206E-2</v>
+        <v>2.8732638888888891E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>3811007000</v>
+        <v>6482967000</v>
       </c>
       <c r="M50" s="13">
-        <v>22856317000</v>
+        <v>27483863000</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>51</v>
@@ -4434,52 +4443,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>0.13527560979095485</v>
+        <v>9.7117351736239615E-2</v>
       </c>
       <c r="Q50" s="12">
-        <v>0.1667375806872122</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R50" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C51" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="D51" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="E51">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>2676399616</v>
+        <v>2347219968</v>
       </c>
       <c r="H51" s="6">
-        <v>14.18</v>
+        <v>17</v>
       </c>
       <c r="I51" s="6">
-        <v>3.15</v>
+        <v>7.36</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="1"/>
-        <v>1.1904761904761907</v>
+        <f>E51/I51-1</f>
+        <v>0.35869565217391308</v>
       </c>
       <c r="K51" s="11">
-        <v>5.0724637681159417E-2</v>
+        <v>4.1999999999999996E-2</v>
       </c>
       <c r="L51" s="13">
-        <v>348303000</v>
+        <v>244811000</v>
       </c>
       <c r="M51" s="13">
-        <v>3681615000</v>
+        <v>2904223000</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>68</v>
@@ -4488,121 +4497,121 @@
         <v>1</v>
       </c>
       <c r="P51" s="12">
-        <v>0.27355952913847126</v>
+        <v>0.37971443928078069</v>
       </c>
       <c r="Q51" s="12">
-        <v>9.4606035666412708E-2</v>
+        <v>8.4294835486117978E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C52" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D52" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="E52">
-        <v>77.2</v>
+        <v>22.75</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>18900488192</v>
+        <v>235542134784</v>
       </c>
       <c r="H52" s="6">
-        <v>95.5</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I52" s="6">
-        <v>55.05</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="1"/>
-        <v>0.4023614895549501</v>
+        <f>E52/I52-1</f>
+        <v>0.18243243243243246</v>
       </c>
       <c r="K52" s="11">
-        <v>1.0621761658031087E-2</v>
+        <v>4.2417582417582415E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>526052000</v>
+        <v>25459748125.549999</v>
       </c>
       <c r="M52" s="13">
-        <v>5343547000</v>
+        <v>134815560756.77</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O52" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.21280855756026237</v>
+        <v>0.12161752909188051</v>
       </c>
       <c r="Q52" s="12">
-        <v>9.8446219337080781E-2</v>
+        <v>0.18884873513587705</v>
       </c>
       <c r="R52" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>273</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
+        <v>328</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="E53">
-        <v>96.7</v>
+        <v>74.45</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>269600555008</v>
+        <v>18227220480</v>
       </c>
       <c r="H53" s="6">
-        <v>107.5</v>
+        <v>95.5</v>
       </c>
       <c r="I53" s="6">
-        <v>65.55</v>
+        <v>55.05</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="1"/>
-        <v>0.47520976353928313</v>
+        <f>E53/I53-1</f>
+        <v>0.35240690281562226</v>
       </c>
       <c r="K53" s="11">
-        <v>2.2936918304033091E-2</v>
+        <v>1.1014103425117527E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>22510000000</v>
+        <v>526052000</v>
       </c>
       <c r="M53" s="13">
-        <v>82545000000</v>
+        <v>5343547000</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O53" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P53" s="12">
-        <v>8.3656624909245095E-2</v>
+        <v>0.22062009687087855</v>
       </c>
       <c r="Q53" s="12">
-        <v>0.27269973953601068</v>
+        <v>9.8446219337080781E-2</v>
       </c>
       <c r="R53" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
@@ -4616,13 +4625,13 @@
         <v>151</v>
       </c>
       <c r="E54">
-        <v>4.07</v>
+        <v>3.95</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>5842119168</v>
+        <v>5669869568</v>
       </c>
       <c r="H54" s="6">
         <v>7.92</v>
@@ -4631,11 +4640,11 @@
         <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="1"/>
-        <v>0.72457627118644097</v>
+        <f>E54/I54-1</f>
+        <v>0.67372881355932224</v>
       </c>
       <c r="K54" s="11">
-        <v>6.2407862407862405E-2</v>
+        <v>6.4303797468354434E-2</v>
       </c>
       <c r="L54" s="13">
         <v>811880000</v>
@@ -4650,52 +4659,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>0.15411709479421579</v>
+        <v>0.15898276983246079</v>
       </c>
       <c r="Q54" s="12">
         <v>0.14675695119790894</v>
       </c>
       <c r="R54" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>139</v>
+        <v>274</v>
       </c>
       <c r="C55" t="s">
-        <v>186</v>
+        <v>329</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>330</v>
       </c>
       <c r="E55">
-        <v>12.96</v>
+        <v>6.32</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>73022341120</v>
+        <v>12818729984</v>
       </c>
       <c r="H55" s="6">
-        <v>14.24</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I55" s="6">
-        <v>8.81</v>
+        <v>5.31</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="1"/>
-        <v>0.47105561861520995</v>
+        <f>E55/I55-1</f>
+        <v>0.19020715630885143</v>
       </c>
       <c r="K55" s="11">
-        <v>2.5540123456790124E-2</v>
+        <v>4.2721518987341771E-2</v>
       </c>
       <c r="L55" s="13">
-        <v>6482967000</v>
+        <v>1537565000</v>
       </c>
       <c r="M55" s="13">
-        <v>27483863000</v>
+        <v>14484935000</v>
       </c>
       <c r="N55" s="9" t="s">
         <v>51</v>
@@ -4704,229 +4713,229 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>8.7197283127823225E-2</v>
+        <v>0.19479548078048717</v>
       </c>
       <c r="Q55" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.10614925092863724</v>
       </c>
       <c r="R55" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="C56" t="s">
-        <v>190</v>
+        <v>343</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="E56">
-        <v>50.15</v>
+        <v>19.14</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>128324829184</v>
+        <v>30547439616</v>
       </c>
       <c r="H56" s="6">
-        <v>71.7</v>
+        <v>27.5</v>
       </c>
       <c r="I56" s="6">
-        <v>43.55</v>
+        <v>16.18</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="1"/>
-        <v>0.15154994259471866</v>
+        <f>E56/I56-1</f>
+        <v>0.18294190358467244</v>
       </c>
       <c r="K56" s="11">
-        <v>3.2701894317048855E-3</v>
+        <v>3.5841170323928945E-2</v>
       </c>
       <c r="L56" s="13">
-        <v>1279098000</v>
+        <v>3811007000</v>
       </c>
       <c r="M56" s="13">
-        <v>4811702000</v>
+        <v>22856317000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="O56" s="6">
-        <v>8.7546153846153842</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P56" s="12">
-        <v>7.7833130575827761E-2</v>
+        <v>0.13643312460046628</v>
       </c>
       <c r="Q56" s="12">
-        <v>0.26583067696212276</v>
+        <v>0.1667375806872122</v>
       </c>
       <c r="R56" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="C57" t="s">
-        <v>327</v>
+        <v>190</v>
       </c>
       <c r="D57" t="s">
-        <v>310</v>
+        <v>109</v>
       </c>
       <c r="E57">
-        <v>5.73</v>
+        <v>47.7</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>25178537984</v>
+        <v>122055720960</v>
       </c>
       <c r="H57" s="6">
-        <v>6.87</v>
+        <v>71.7</v>
       </c>
       <c r="I57" s="6">
-        <v>4.7699999999999996</v>
+        <v>43.55</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="1"/>
-        <v>0.2012578616352203</v>
+        <f>E57/I57-1</f>
+        <v>9.5292766934558015E-2</v>
       </c>
       <c r="K57" s="11">
-        <v>6.2478184991273993E-2</v>
+        <v>3.4381551362683439E-3</v>
       </c>
       <c r="L57" s="13">
-        <v>2919921000</v>
+        <v>1279098000</v>
       </c>
       <c r="M57" s="13">
-        <v>31662140000</v>
+        <v>4811702000</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="O57" s="6">
-        <v>1.0683760683760684</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P57" s="12">
-        <v>0.22992373749325898</v>
+        <v>8.1379162073239308E-2</v>
       </c>
       <c r="Q57" s="12">
-        <v>9.2221214358852555E-2</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R57" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E58">
-        <v>10.6</v>
+        <v>0.52</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>2488053248</v>
+        <v>2695529216</v>
       </c>
       <c r="H58" s="6">
-        <v>10.88</v>
+        <v>0.68</v>
       </c>
       <c r="I58" s="6">
-        <v>7.36</v>
+        <v>0.46</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="1"/>
-        <v>0.44021739130434767</v>
+        <f>E58/I58-1</f>
+        <v>0.13043478260869557</v>
       </c>
       <c r="K58" s="11">
-        <v>3.962264150943396E-2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="13">
-        <v>244811000</v>
+        <v>756004000</v>
       </c>
       <c r="M58" s="13">
-        <v>2904223000</v>
+        <v>8813758000</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O58" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.31163992264507756</v>
+        <v>0.28949073626199495</v>
       </c>
       <c r="Q58" s="12">
-        <v>8.4294835486117978E-2</v>
+        <v>8.5775443346640556E-2</v>
       </c>
       <c r="R58" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>277</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E59">
-        <v>0.48499999999999999</v>
+        <v>392.6</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>2514099456</v>
+        <v>496183607296</v>
       </c>
       <c r="H59" s="6">
-        <v>0.68</v>
+        <v>422.4</v>
       </c>
       <c r="I59" s="6">
-        <v>0.46</v>
+        <v>218.4</v>
       </c>
       <c r="J59" s="12">
-        <f t="shared" si="1"/>
-        <v>5.4347826086956541E-2</v>
+        <f>E59/I59-1</f>
+        <v>0.79761904761904767</v>
       </c>
       <c r="K59" s="11">
-        <v>0</v>
+        <v>2.3586347427407027E-2</v>
       </c>
       <c r="L59" s="13">
-        <v>756004000</v>
+        <v>20744000000</v>
       </c>
       <c r="M59" s="13">
-        <v>8813758000</v>
+        <v>53852000000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O59" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P59" s="12">
-        <v>0.30962476292169461</v>
+        <v>5.7128283577028288E-2</v>
       </c>
       <c r="Q59" s="12">
-        <v>8.5775443346640556E-2</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R59" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
@@ -4940,26 +4949,26 @@
         <v>337</v>
       </c>
       <c r="E60">
-        <v>5.31</v>
+        <v>5.72</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>6814004224</v>
+        <v>7334412288</v>
       </c>
       <c r="H60" s="6">
-        <v>5.33</v>
+        <v>5.92</v>
       </c>
       <c r="I60" s="6">
         <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="1"/>
-        <v>0.58035714285714279</v>
+        <f>E60/I60-1</f>
+        <v>0.70238095238095233</v>
       </c>
       <c r="K60" s="11">
-        <v>4.8964218455743884E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="L60" s="13">
         <v>2871477000</v>
@@ -4974,106 +4983,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P60" s="12">
-        <v>0.15471463459515128</v>
+        <v>0.15075799694960876</v>
       </c>
       <c r="Q60" s="12">
         <v>0.1318118502166547</v>
       </c>
       <c r="R60" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>264</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="E61">
-        <v>415.8</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>525504643072</v>
+        <v>18011709440</v>
       </c>
       <c r="H61" s="6">
-        <v>416.2</v>
+        <v>23.35</v>
       </c>
       <c r="I61" s="6">
-        <v>218.4</v>
+        <v>9.9</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="1"/>
-        <v>0.90384615384615374</v>
+        <f>E61/I61-1</f>
+        <v>0.9757575757575756</v>
       </c>
       <c r="K61" s="11">
-        <v>2.227032227032227E-2</v>
+        <v>3.9877300613496936E-3</v>
       </c>
       <c r="L61" s="13">
-        <v>20744000000</v>
+        <v>334940000</v>
       </c>
       <c r="M61" s="13">
-        <v>53852000000</v>
+        <v>3025375000</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O61" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P61" s="12">
-        <v>5.2859892025603136E-2</v>
+        <v>0.1696388129526302</v>
       </c>
       <c r="Q61" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.11071024253191752</v>
       </c>
       <c r="R61" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C62" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D62" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E62">
-        <v>3.76</v>
+        <v>6.18</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>8539185664</v>
+        <v>27155908608</v>
       </c>
       <c r="H62" s="6">
-        <v>5.22</v>
+        <v>6.87</v>
       </c>
       <c r="I62" s="6">
-        <v>3.34</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J62" s="12">
-        <f t="shared" si="1"/>
-        <v>0.12574850299401197</v>
+        <f>E62/I62-1</f>
+        <v>0.29559748427672972</v>
       </c>
       <c r="K62" s="11">
-        <v>3.9893617021276598E-2</v>
+        <v>5.7928802588996763E-2</v>
       </c>
       <c r="L62" s="13">
-        <v>826931000</v>
+        <v>2919921000</v>
       </c>
       <c r="M62" s="13">
-        <v>5591620000</v>
+        <v>31662140000</v>
       </c>
       <c r="N62" s="9" t="s">
         <v>51</v>
@@ -5082,52 +5091,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>0.13561106154278804</v>
+        <v>0.2006771875864922</v>
       </c>
       <c r="Q62" s="12">
-        <v>0.14788755315990715</v>
+        <v>9.2221214358852555E-2</v>
       </c>
       <c r="R62" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
-        <v>176</v>
+        <v>338</v>
       </c>
       <c r="D63" t="s">
-        <v>177</v>
+        <v>339</v>
       </c>
       <c r="E63">
-        <v>18.04</v>
+        <v>3.64</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>509667934208</v>
+        <v>8266658304</v>
       </c>
       <c r="H63" s="6">
-        <v>19.260000000000002</v>
+        <v>5.09</v>
       </c>
       <c r="I63" s="6">
-        <v>13.52</v>
+        <v>3.34</v>
       </c>
       <c r="J63" s="12">
-        <f t="shared" si="1"/>
-        <v>0.33431952662721898</v>
+        <f>E63/I63-1</f>
+        <v>8.9820359281437279E-2</v>
       </c>
       <c r="K63" s="11">
-        <v>2.1064301552106431E-2</v>
+        <v>4.1208791208791208E-2</v>
       </c>
       <c r="L63" s="13">
-        <v>52374992116</v>
+        <v>826931000</v>
       </c>
       <c r="M63" s="13">
-        <v>269573093476</v>
+        <v>5591620000</v>
       </c>
       <c r="N63" s="9" t="s">
         <v>51</v>
@@ -5136,106 +5145,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>8.8265420630244076E-2</v>
+        <v>0.14153165705806631</v>
       </c>
       <c r="Q63" s="12">
-        <v>0.19428864891763736</v>
+        <v>0.14788755315990715</v>
       </c>
       <c r="R63" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>50</v>
       </c>
       <c r="E64">
-        <v>6.86</v>
+        <v>2.48</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>17195620352</v>
+        <v>4680479232</v>
       </c>
       <c r="H64" s="6">
-        <v>7.03</v>
+        <v>4.18</v>
       </c>
       <c r="I64" s="6">
-        <v>3.99</v>
+        <v>1.74</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="1"/>
-        <v>0.7192982456140351</v>
+        <f>E64/I64-1</f>
+        <v>0.42528735632183912</v>
       </c>
       <c r="K64" s="11">
-        <v>4.6793002915451895E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="L64" s="13">
-        <v>3040816000</v>
+        <v>896597000</v>
       </c>
       <c r="M64" s="13">
-        <v>29707522000</v>
+        <v>6906279000</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O64" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P64" s="12">
-        <v>0.17317195498769494</v>
+        <v>0.14288741718726924</v>
       </c>
       <c r="Q64" s="12">
-        <v>0.102358453189061</v>
+        <v>0.12982345485897689</v>
       </c>
       <c r="R64" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D65" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="E65">
-        <v>250.8</v>
+        <v>19.18</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>333102546944</v>
+        <v>531698384896</v>
       </c>
       <c r="H65" s="6">
-        <v>253</v>
+        <v>20.7</v>
       </c>
       <c r="I65" s="6">
-        <v>34.4</v>
+        <v>13.52</v>
       </c>
       <c r="J65" s="12">
-        <f t="shared" si="1"/>
-        <v>6.2906976744186052</v>
+        <f>E65/I65-1</f>
+        <v>0.41863905325443795</v>
       </c>
       <c r="K65" s="11">
-        <v>3.2496012759170652E-3</v>
+        <v>1.9812304483837331E-2</v>
       </c>
       <c r="L65" s="13">
-        <v>4414795000</v>
+        <v>52374992116</v>
       </c>
       <c r="M65" s="13">
-        <v>10683505000</v>
+        <v>269573093476</v>
       </c>
       <c r="N65" s="9" t="s">
         <v>51</v>
@@ -5244,67 +5253,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P65" s="12">
-        <v>1.4397344757424192E-2</v>
+        <v>8.5301130934902492E-2</v>
       </c>
       <c r="Q65" s="12">
-        <v>0.41323470153287706</v>
+        <v>0.19428864891763736</v>
       </c>
       <c r="R65" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>325</v>
+        <v>159</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E66">
-        <v>2.66</v>
+        <v>239.6</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>5020191744</v>
+        <v>318227152896</v>
       </c>
       <c r="H66" s="6">
-        <v>4.18</v>
+        <v>283.39999999999998</v>
       </c>
       <c r="I66" s="6">
-        <v>1.74</v>
+        <v>34.4</v>
       </c>
       <c r="J66" s="12">
-        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
-        <v>0.52873563218390807</v>
+        <f>E66/I66-1</f>
+        <v>5.9651162790697674</v>
       </c>
       <c r="K66" s="11">
-        <v>6.0150375939849621E-2</v>
+        <v>3.4015025041736224E-3</v>
       </c>
       <c r="L66" s="13">
-        <v>896597000</v>
+        <v>4408440000</v>
       </c>
       <c r="M66" s="13">
-        <v>6906279000</v>
+        <v>10683505000</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O66" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P66" s="12">
-        <v>0.13554896525280663</v>
+        <v>1.5060459980733311E-2</v>
       </c>
       <c r="Q66" s="12">
-        <v>0.12982345485897689</v>
+        <v>0.41263985929711272</v>
       </c>
       <c r="R66" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
@@ -5318,13 +5327,13 @@
         <v>185</v>
       </c>
       <c r="E67">
-        <v>349.2</v>
+        <v>338</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>129843740672</v>
+        <v>126311620608</v>
       </c>
       <c r="H67" s="6">
         <v>421.4</v>
@@ -5333,11 +5342,11 @@
         <v>225.2</v>
       </c>
       <c r="J67" s="12">
-        <f t="shared" si="2"/>
-        <v>0.55062166962699832</v>
+        <f>E67/I67-1</f>
+        <v>0.5008880994671403</v>
       </c>
       <c r="K67" s="11">
-        <v>2.0618556701030928E-3</v>
+        <v>2.1301775147928993E-3</v>
       </c>
       <c r="L67" s="13">
         <v>1200000000</v>
@@ -5352,106 +5361,106 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P67" s="12">
-        <v>6.463536986601949E-2</v>
+        <v>6.6274503203376092E-2</v>
       </c>
       <c r="Q67" s="12">
         <v>0.20495303159692571</v>
       </c>
       <c r="R67" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
-        <v>267</v>
+        <v>374</v>
       </c>
       <c r="C68" t="s">
-        <v>320</v>
+        <v>376</v>
       </c>
       <c r="D68" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="E68">
-        <v>7.85</v>
+        <v>1.8</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>14188325888</v>
+        <v>3845754112</v>
       </c>
       <c r="H68" s="6">
-        <v>9.1</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I68" s="6">
-        <v>5.49</v>
+        <v>0.99</v>
       </c>
       <c r="J68" s="12">
-        <f t="shared" si="2"/>
-        <v>0.42987249544626582</v>
+        <f>E68/I68-1</f>
+        <v>0.81818181818181834</v>
       </c>
       <c r="K68" s="11">
-        <v>3.1847133757961783E-2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="13">
-        <v>2897428000</v>
+        <v>-732033000</v>
       </c>
       <c r="M68" s="13">
-        <v>25970601000</v>
+        <v>7864121000</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O68" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P68" s="12">
-        <v>0.15167608287440104</v>
+        <v>0.61884859302803386</v>
       </c>
       <c r="Q68" s="12">
-        <v>0.11156568921912897</v>
+        <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R68" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B69" s="1" t="s">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>323</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>324</v>
       </c>
       <c r="E69">
-        <v>21.95</v>
+        <v>7.07</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>24970758144</v>
+        <v>17722015744</v>
       </c>
       <c r="H69" s="6">
-        <v>28.75</v>
+        <v>7.23</v>
       </c>
       <c r="I69" s="6">
-        <v>19.52</v>
+        <v>3.99</v>
       </c>
       <c r="J69" s="12">
-        <f t="shared" si="2"/>
-        <v>0.12448770491803285</v>
+        <f>E69/I69-1</f>
+        <v>0.77192982456140347</v>
       </c>
       <c r="K69" s="11">
-        <v>6.3781321184510242E-2</v>
+        <v>4.54031117397454E-2</v>
       </c>
       <c r="L69" s="13">
-        <v>3446618000</v>
+        <v>3040816000</v>
       </c>
       <c r="M69" s="13">
-        <v>34010798000</v>
+        <v>29707522000</v>
       </c>
       <c r="N69" s="9" t="s">
         <v>51</v>
@@ -5460,52 +5469,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P69" s="12">
-        <v>0.15508657118243896</v>
+        <v>0.16844550812159936</v>
       </c>
       <c r="Q69" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.102358453189061</v>
       </c>
       <c r="R69" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B70" s="1" t="s">
-        <v>137</v>
+        <v>267</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>320</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>321</v>
       </c>
       <c r="E70">
-        <v>34.35</v>
+        <v>7.52</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>23759206400</v>
+        <v>13591873536</v>
       </c>
       <c r="H70" s="6">
-        <v>39.200000000000003</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I70" s="6">
-        <v>13.48</v>
+        <v>5.49</v>
       </c>
       <c r="J70" s="12">
-        <f t="shared" si="2"/>
-        <v>1.5482195845697331</v>
+        <f>E70/I70-1</f>
+        <v>0.36976320582877942</v>
       </c>
       <c r="K70" s="11">
-        <v>1.3391557496360991E-2</v>
+        <v>3.3244680851063829E-2</v>
       </c>
       <c r="L70" s="13">
-        <v>1323087000</v>
+        <v>2897428000</v>
       </c>
       <c r="M70" s="13">
-        <v>5952918000</v>
+        <v>25970601000</v>
       </c>
       <c r="N70" s="9" t="s">
         <v>68</v>
@@ -5514,52 +5523,52 @@
         <v>1</v>
       </c>
       <c r="P70" s="12">
-        <v>5.0457020931010475E-2</v>
+        <v>0.15656456094646107</v>
       </c>
       <c r="Q70" s="12">
-        <v>0.222258562943417</v>
+        <v>0.11156568921912897</v>
       </c>
       <c r="R70" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B71" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="E71">
-        <v>11.8</v>
+        <v>31</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>117850251264</v>
+        <v>21442080768</v>
       </c>
       <c r="H71" s="6">
-        <v>12.16</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="I71" s="6">
-        <v>5.83</v>
+        <v>13.48</v>
       </c>
       <c r="J71" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0240137221269299</v>
+        <f>E71/I71-1</f>
+        <v>1.2997032640949553</v>
       </c>
       <c r="K71" s="11">
-        <v>4.2372881355932202E-2</v>
+        <v>1.4838709677419355E-2</v>
       </c>
       <c r="L71" s="13">
-        <v>9432900000</v>
+        <v>1323087000</v>
       </c>
       <c r="M71" s="13">
-        <v>54338700000</v>
+        <v>5952918000</v>
       </c>
       <c r="N71" s="9" t="s">
         <v>68</v>
@@ -5568,67 +5577,67 @@
         <v>1</v>
       </c>
       <c r="P71" s="12">
-        <v>6.7355845606612202E-2</v>
+        <v>5.5347863032824282E-2</v>
       </c>
       <c r="Q71" s="12">
-        <v>0.17359450999011755</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R71" s="14">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B72" s="1" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="E72">
-        <v>6.37</v>
+        <v>21.6</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>4963516416</v>
+        <v>24572592128</v>
       </c>
       <c r="H72" s="6">
-        <v>8.09</v>
+        <v>28.75</v>
       </c>
       <c r="I72" s="6">
-        <v>4.0199999999999996</v>
+        <v>19.52</v>
       </c>
       <c r="J72" s="12">
-        <f t="shared" si="2"/>
-        <v>0.58457711442786087</v>
+        <f>E72/I72-1</f>
+        <v>0.10655737704918034</v>
       </c>
       <c r="K72" s="11">
-        <v>2.6687598116169546E-2</v>
+        <v>6.4814814814814811E-2</v>
       </c>
       <c r="L72" s="13">
-        <v>437453000</v>
+        <v>3446618000</v>
       </c>
       <c r="M72" s="13">
-        <v>4911072000</v>
+        <v>34010798000</v>
       </c>
       <c r="N72" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O72" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P72" s="12">
-        <v>0.16359086438230622</v>
+        <v>0.15773165811264842</v>
       </c>
       <c r="Q72" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R72" s="14">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
@@ -5642,13 +5651,13 @@
         <v>155</v>
       </c>
       <c r="E73">
-        <v>57.3</v>
+        <v>55.6</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>162066743296</v>
+        <v>159410749440</v>
       </c>
       <c r="H73" s="6">
         <v>60</v>
@@ -5657,11 +5666,11 @@
         <v>38.4</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" si="2"/>
-        <v>0.4921875</v>
+        <f>E73/I73-1</f>
+        <v>0.44791666666666674</v>
       </c>
       <c r="K73" s="11">
-        <v>3.1413612565445032E-2</v>
+        <v>3.237410071942446E-2</v>
       </c>
       <c r="L73" s="13">
         <v>8955723006</v>
@@ -5676,121 +5685,121 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>6.0550424358519428E-2</v>
+        <v>6.1585562632163901E-2</v>
       </c>
       <c r="Q73" s="12">
         <v>0.18855793075067021</v>
       </c>
       <c r="R73" s="14">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B74" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="E74">
-        <v>518</v>
+        <v>12.76</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>4710511149056</v>
+        <v>125876633600</v>
       </c>
       <c r="H74" s="6">
-        <v>547</v>
+        <v>13.86</v>
       </c>
       <c r="I74" s="6">
-        <v>349</v>
+        <v>5.83</v>
       </c>
       <c r="J74" s="12">
-        <f t="shared" si="2"/>
-        <v>0.48424068767908302</v>
+        <f>E74/I74-1</f>
+        <v>1.1886792452830188</v>
       </c>
       <c r="K74" s="11">
-        <v>8.1640926640926641E-3</v>
+        <v>4.0752351097178688E-2</v>
       </c>
       <c r="L74" s="13">
-        <v>253932000000</v>
+        <v>8510100000</v>
       </c>
       <c r="M74" s="13">
-        <v>1312163000000</v>
+        <v>46117200000</v>
       </c>
       <c r="N74" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O74" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P74" s="12">
-        <v>5.4790117301248893E-2</v>
+        <v>6.1187058001319003E-2</v>
       </c>
       <c r="Q74" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.18453201842262756</v>
       </c>
       <c r="R74" s="14">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B75" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D75" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="E75">
-        <v>6.27</v>
+        <v>505.5</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>10199472128</v>
+        <v>4592068198400</v>
       </c>
       <c r="H75" s="6">
-        <v>7.05</v>
+        <v>547</v>
       </c>
       <c r="I75" s="6">
-        <v>4.2699999999999996</v>
+        <v>349</v>
       </c>
       <c r="J75" s="12">
-        <f t="shared" si="2"/>
-        <v>0.46838407494145207</v>
+        <f>E75/I75-1</f>
+        <v>0.44842406876790841</v>
       </c>
       <c r="K75" s="11">
-        <v>4.4657097288676242E-2</v>
+        <v>8.3659742828882302E-3</v>
       </c>
       <c r="L75" s="13">
-        <v>4094312000</v>
+        <v>253932000000</v>
       </c>
       <c r="M75" s="13">
-        <v>37637054000</v>
+        <v>1312163000000</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O75" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P75" s="12">
-        <v>0.13373172758010426</v>
+        <v>5.613284173766539E-2</v>
       </c>
       <c r="Q75" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R75" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
@@ -5804,26 +5813,26 @@
         <v>75</v>
       </c>
       <c r="E76">
-        <v>8.4700000000000006</v>
+        <v>7.38</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>5736426496</v>
+        <v>4998208512</v>
       </c>
       <c r="H76" s="6">
-        <v>11.32</v>
+        <v>10.88</v>
       </c>
       <c r="I76" s="6">
         <v>6.56</v>
       </c>
       <c r="J76" s="12">
-        <f t="shared" si="2"/>
-        <v>0.29115853658536595</v>
+        <f>E76/I76-1</f>
+        <v>0.125</v>
       </c>
       <c r="K76" s="11">
-        <v>4.2148760330578509E-2</v>
+        <v>4.8373983739837395E-2</v>
       </c>
       <c r="L76" s="13">
         <v>618033000</v>
@@ -5838,160 +5847,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>9.7757623133383695E-2</v>
+        <v>0.10975306020589076</v>
       </c>
       <c r="Q76" s="12">
         <v>0.12279555988606453</v>
       </c>
       <c r="R76" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B77" s="1" t="s">
-        <v>265</v>
+        <v>373</v>
       </c>
       <c r="C77" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="D77" t="s">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="E77">
-        <v>8.56</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>112932945920</v>
+        <v>2557555712</v>
       </c>
       <c r="H77" s="6">
-        <v>11</v>
+        <v>15.58</v>
       </c>
       <c r="I77" s="6">
-        <v>6.84</v>
+        <v>6.65</v>
       </c>
       <c r="J77" s="12">
-        <f t="shared" si="2"/>
-        <v>0.25146198830409361</v>
+        <f>E77/I77-1</f>
+        <v>0.46165413533834587</v>
       </c>
       <c r="K77" s="11">
         <v>0</v>
       </c>
       <c r="L77" s="13">
-        <v>1187000000</v>
+        <v>-481083000</v>
       </c>
       <c r="M77" s="13">
-        <v>10278000000</v>
+        <v>4136123000</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O77" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P77" s="12">
-        <v>9.8766188398333774E-2</v>
+        <v>0.3033010253165202</v>
       </c>
       <c r="Q77" s="12">
-        <v>0.1154893948238957</v>
+        <v>-0.11631254679805218</v>
       </c>
       <c r="R77" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B78" s="1" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E78">
-        <v>14.3</v>
+        <v>2.71</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>60031545344</v>
+        <v>16805306368</v>
       </c>
       <c r="H78" s="6">
-        <v>15.38</v>
+        <v>4.68</v>
       </c>
       <c r="I78" s="6">
-        <v>10.98</v>
+        <v>2.11</v>
       </c>
       <c r="J78" s="12">
-        <f t="shared" si="2"/>
-        <v>0.30236794171220405</v>
+        <f>E78/I78-1</f>
+        <v>0.28436018957345977</v>
       </c>
       <c r="K78" s="11">
-        <v>6.1958041958041957E-2</v>
+        <v>5.9040590405904064E-2</v>
       </c>
       <c r="L78" s="13">
-        <v>11996000000</v>
+        <v>1677300000</v>
       </c>
       <c r="M78" s="13">
-        <v>138296000000</v>
+        <v>11188800000</v>
       </c>
       <c r="N78" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O78" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P78" s="12">
-        <v>0.14423548848779913</v>
+        <v>9.7476259498421966E-2</v>
       </c>
       <c r="Q78" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>0.1499088374088374</v>
       </c>
       <c r="R78" s="14">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B79" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E79">
-        <v>14.3</v>
+        <v>6.15</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>60031545344</v>
+        <v>10004267008</v>
       </c>
       <c r="H79" s="6">
-        <v>15.38</v>
+        <v>7.05</v>
       </c>
       <c r="I79" s="6">
-        <v>10.98</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J79" s="12">
-        <f t="shared" si="2"/>
-        <v>0.30236794171220405</v>
+        <f>E79/I79-1</f>
+        <v>0.44028103044496514</v>
       </c>
       <c r="K79" s="11">
-        <v>6.1958041958041957E-2</v>
+        <v>4.5528455284552849E-2</v>
       </c>
       <c r="L79" s="13">
-        <v>11996000000</v>
+        <v>4094312000</v>
       </c>
       <c r="M79" s="13">
-        <v>138296000000</v>
+        <v>37637054000</v>
       </c>
       <c r="N79" s="9" t="s">
         <v>68</v>
@@ -6000,268 +6009,268 @@
         <v>1</v>
       </c>
       <c r="P79" s="12">
-        <v>0.14423548848779913</v>
+        <v>0.13458986548229865</v>
       </c>
       <c r="Q79" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R79" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B80" s="1" t="s">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>243</v>
       </c>
       <c r="E80">
-        <v>13.14</v>
+        <v>8.01</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>61006786560</v>
+        <v>105676734464</v>
       </c>
       <c r="H80" s="6">
-        <v>13.44</v>
+        <v>11</v>
       </c>
       <c r="I80" s="6">
-        <v>7.51</v>
+        <v>6.84</v>
       </c>
       <c r="J80" s="12">
-        <f t="shared" si="2"/>
-        <v>0.74966711051930779</v>
+        <f>E80/I80-1</f>
+        <v>0.17105263157894735</v>
       </c>
       <c r="K80" s="11">
-        <v>3.3333333333333333E-2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="13">
-        <v>3967214824.1399999</v>
+        <v>1187000000</v>
       </c>
       <c r="M80" s="13">
-        <v>41038539262.660004</v>
+        <v>10278000000</v>
       </c>
       <c r="N80" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O80" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P80" s="12">
-        <v>0.1193649041978434</v>
+        <v>0.10717856686087243</v>
       </c>
       <c r="Q80" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>0.1154893948238957</v>
       </c>
       <c r="R80" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B81" s="1" t="s">
-        <v>264</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="E81">
-        <v>22.6</v>
+        <v>13.2</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>20811075584</v>
+        <v>56920907776</v>
       </c>
       <c r="H81" s="6">
-        <v>23.3</v>
+        <v>14.7</v>
       </c>
       <c r="I81" s="6">
-        <v>9.9</v>
+        <v>7.51</v>
       </c>
       <c r="J81" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2828282828282829</v>
+        <f>E81/I81-1</f>
+        <v>0.7576564580559253</v>
       </c>
       <c r="K81" s="11">
-        <v>3.4513274336283183E-3</v>
+        <v>3.318181818181818E-2</v>
       </c>
       <c r="L81" s="13">
-        <v>302705000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M81" s="13">
-        <v>3112813000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O81" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P81" s="12">
-        <v>0.11686432780141277</v>
+        <v>0.13488586911643227</v>
       </c>
       <c r="Q81" s="12">
-        <v>9.7244839314150899E-2</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R81" s="14">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B82" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D82" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E82">
-        <v>32.700000000000003</v>
+        <v>14.64</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>73679634432</v>
+        <v>61458870272</v>
       </c>
       <c r="H82" s="6">
-        <v>61.55</v>
+        <v>15.38</v>
       </c>
       <c r="I82" s="6">
-        <v>24.85</v>
+        <v>10.98</v>
       </c>
       <c r="J82" s="12">
-        <f t="shared" si="2"/>
-        <v>0.31589537223340036</v>
+        <f>E82/I82-1</f>
+        <v>0.33333333333333326</v>
       </c>
       <c r="K82" s="11">
-        <v>1.7370030581039753E-2</v>
+        <v>6.0519125683060108E-2</v>
       </c>
       <c r="L82" s="13">
-        <v>5261270000</v>
+        <v>11996000000</v>
       </c>
       <c r="M82" s="13">
-        <v>43208997000</v>
+        <v>138296000000</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O82" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P82" s="12">
-        <v>7.0742980761826516E-2</v>
+        <v>0.14180193618782672</v>
       </c>
       <c r="Q82" s="12">
-        <v>0.12176329850933591</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B83" s="1" t="s">
-        <v>263</v>
+        <v>135</v>
       </c>
       <c r="C83" t="s">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="D83" t="s">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="E83">
-        <v>47.2</v>
+        <v>14.64</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>1000592769024</v>
+        <v>61458870272</v>
       </c>
       <c r="H83" s="6">
-        <v>59.8</v>
+        <v>15.38</v>
       </c>
       <c r="I83" s="6">
-        <v>32.65</v>
+        <v>10.98</v>
       </c>
       <c r="J83" s="12">
-        <f t="shared" si="2"/>
-        <v>0.44563552833078113</v>
+        <f>E83/I83-1</f>
+        <v>0.33333333333333326</v>
       </c>
       <c r="K83" s="11">
-        <v>5.4025423728813554E-2</v>
+        <v>6.0519125683060108E-2</v>
       </c>
       <c r="L83" s="13">
-        <v>189900000000</v>
+        <v>11996000000</v>
       </c>
       <c r="M83" s="13">
-        <v>2315380000000</v>
+        <v>138296000000</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O83" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P83" s="12">
-        <v>0.13743293766692002</v>
+        <v>0.14180193618782672</v>
       </c>
       <c r="Q83" s="12">
-        <v>8.2016774784268678E-2</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R83" s="14">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B84" s="1" t="s">
-        <v>260</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>313</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E84">
-        <v>1.99</v>
+        <v>6.9</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>1847860224</v>
+        <v>5376493568</v>
       </c>
       <c r="H84" s="6">
-        <v>2.54</v>
+        <v>8.09</v>
       </c>
       <c r="I84" s="6">
-        <v>1.72</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J84" s="12">
-        <f t="shared" si="2"/>
-        <v>0.15697674418604657</v>
+        <f>E84/I84-1</f>
+        <v>0.71641791044776149</v>
       </c>
       <c r="K84" s="11">
-        <v>5.5276381909547742E-2</v>
+        <v>2.4637681159420291E-2</v>
       </c>
       <c r="L84" s="13">
-        <v>238321000</v>
+        <v>437453000</v>
       </c>
       <c r="M84" s="13">
-        <v>6087917000</v>
+        <v>4911072000</v>
       </c>
       <c r="N84" s="9" t="s">
         <v>68</v>
@@ -6270,52 +6279,52 @@
         <v>1</v>
       </c>
       <c r="P84" s="12">
-        <v>0.15959509688418372</v>
+        <v>0.14170608501561485</v>
       </c>
       <c r="Q84" s="12">
-        <v>3.9146558666946343E-2</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B85" s="1" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E85">
-        <v>19.920000000000002</v>
+        <v>30.1</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>126921875456</v>
+        <v>67821318144</v>
       </c>
       <c r="H85" s="6">
-        <v>26.6</v>
+        <v>61.55</v>
       </c>
       <c r="I85" s="6">
-        <v>16.02</v>
+        <v>24.85</v>
       </c>
       <c r="J85" s="12">
-        <f t="shared" si="2"/>
-        <v>0.24344569288389528</v>
+        <f>E85/I85-1</f>
+        <v>0.21126760563380276</v>
       </c>
       <c r="K85" s="11">
-        <v>3.564257028112449E-2</v>
+        <v>1.8870431893687704E-2</v>
       </c>
       <c r="L85" s="13">
-        <v>10795274825</v>
+        <v>5261270000</v>
       </c>
       <c r="M85" s="13">
-        <v>215275428010</v>
+        <v>43208997000</v>
       </c>
       <c r="N85" s="9" t="s">
         <v>51</v>
@@ -6324,52 +6333,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>0.13819205229155279</v>
+        <v>7.6373999371440626E-2</v>
       </c>
       <c r="Q85" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R85" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B86" s="1" t="s">
-        <v>123</v>
+        <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="D86" t="s">
-        <v>164</v>
+        <v>308</v>
       </c>
       <c r="E86">
-        <v>6.06</v>
+        <v>47.35</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>47318056960</v>
+        <v>996101980160</v>
       </c>
       <c r="H86" s="6">
-        <v>11.72</v>
+        <v>59.8</v>
       </c>
       <c r="I86" s="6">
-        <v>5</v>
+        <v>32.65</v>
       </c>
       <c r="J86" s="12">
-        <f t="shared" si="2"/>
-        <v>0.21199999999999997</v>
+        <f>E86/I86-1</f>
+        <v>0.45022970903522208</v>
       </c>
       <c r="K86" s="11">
-        <v>7.0957095709570955E-2</v>
+        <v>5.3854276663146773E-2</v>
       </c>
       <c r="L86" s="13">
-        <v>6749146000</v>
+        <v>189900000000</v>
       </c>
       <c r="M86" s="13">
-        <v>70848374000</v>
+        <v>2315380000000</v>
       </c>
       <c r="N86" s="9" t="s">
         <v>51</v>
@@ -6378,106 +6387,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>9.0236955885900208E-2</v>
+        <v>0.13785228929511617</v>
       </c>
       <c r="Q86" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>8.2016774784268678E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B87" s="1" t="s">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="C87" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="D87" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="E87">
-        <v>8.3699999999999992</v>
+        <v>1.99</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>19721644032</v>
+        <v>1847860224</v>
       </c>
       <c r="H87" s="6">
-        <v>11.68</v>
+        <v>2.54</v>
       </c>
       <c r="I87" s="6">
-        <v>5.19</v>
+        <v>1.72</v>
       </c>
       <c r="J87" s="12">
-        <f t="shared" si="2"/>
-        <v>0.61271676300578015</v>
+        <f>E87/I87-1</f>
+        <v>0.15697674418604657</v>
       </c>
       <c r="K87" s="11">
-        <v>0</v>
+        <v>5.5276381909547742E-2</v>
       </c>
       <c r="L87" s="13">
-        <v>13493113000</v>
+        <v>238321000</v>
       </c>
       <c r="M87" s="13">
-        <v>208027754000</v>
+        <v>6087917000</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O87" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P87" s="12">
-        <v>0.12126103429826435</v>
+        <v>0.15959509688418372</v>
       </c>
       <c r="Q87" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>3.9146558666946343E-2</v>
       </c>
       <c r="R87" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B88" s="1" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E88">
-        <v>51.15</v>
+        <v>18.86</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>139287592960</v>
+        <v>117225472000</v>
       </c>
       <c r="H88" s="6">
-        <v>82.25</v>
+        <v>26.6</v>
       </c>
       <c r="I88" s="6">
-        <v>37.85</v>
+        <v>16.02</v>
       </c>
       <c r="J88" s="12">
-        <f t="shared" si="2"/>
-        <v>0.35138705416116234</v>
+        <f>E88/I88-1</f>
+        <v>0.17727840199750311</v>
       </c>
       <c r="K88" s="11">
-        <v>2.0527859237536659E-2</v>
+        <v>3.7645811240721104E-2</v>
       </c>
       <c r="L88" s="13">
-        <v>6350637223.7200003</v>
+        <v>10795274825</v>
       </c>
       <c r="M88" s="13">
-        <v>57896384836.860001</v>
+        <v>215275428010</v>
       </c>
       <c r="N88" s="9" t="s">
         <v>51</v>
@@ -6486,52 +6495,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>6.3055235561581296E-2</v>
+        <v>0.15635790236074304</v>
       </c>
       <c r="Q88" s="12">
-        <v>0.10968970241604512</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R88" s="14">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B89" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E89">
-        <v>11.42</v>
+        <v>8.9</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>86510608384</v>
+        <v>27767998464</v>
       </c>
       <c r="H89" s="6">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="I89" s="6">
-        <v>8.5399999999999991</v>
+        <v>5.6</v>
       </c>
       <c r="J89" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33723653395784559</v>
+        <f>E89/I89-1</f>
+        <v>0.58928571428571441</v>
       </c>
       <c r="K89" s="11">
-        <v>6.9001751313485113E-2</v>
+        <v>3.5955056179775277E-2</v>
       </c>
       <c r="L89" s="13">
-        <v>8154000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M89" s="13">
-        <v>79588000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N89" s="9" t="s">
         <v>68</v>
@@ -6540,52 +6549,52 @@
         <v>1</v>
       </c>
       <c r="P89" s="12">
-        <v>6.3793029121975375E-2</v>
+        <v>6.521791382377079E-2</v>
       </c>
       <c r="Q89" s="12">
-        <v>0.10245263104990703</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R89" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B90" s="1" t="s">
-        <v>261</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>314</v>
+        <v>67</v>
       </c>
       <c r="D90" t="s">
-        <v>310</v>
+        <v>66</v>
       </c>
       <c r="E90">
-        <v>1.57</v>
+        <v>53.55</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>62827003904</v>
+        <v>138702520320</v>
       </c>
       <c r="H90" s="6">
-        <v>2.08</v>
+        <v>82.25</v>
       </c>
       <c r="I90" s="6">
-        <v>1.18</v>
+        <v>37.85</v>
       </c>
       <c r="J90" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33050847457627142</v>
+        <f>E90/I90-1</f>
+        <v>0.41479524438573301</v>
       </c>
       <c r="K90" s="11">
-        <v>3.5668789808917196E-2</v>
+        <v>1.9607843137254905E-2</v>
       </c>
       <c r="L90" s="13">
-        <v>12616717000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M90" s="13">
-        <v>231208465000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N90" s="9" t="s">
         <v>51</v>
@@ -6594,214 +6603,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>0.12616891030563587</v>
+        <v>6.3399965105589054E-2</v>
       </c>
       <c r="Q90" s="12">
-        <v>5.4568577322633927E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R90" s="14">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B91" s="1" t="s">
-        <v>262</v>
+        <v>123</v>
       </c>
       <c r="C91" t="s">
-        <v>315</v>
+        <v>163</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="E91">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>5440867328</v>
+        <v>51699572736</v>
       </c>
       <c r="H91" s="6">
-        <v>8.32</v>
+        <v>10.72</v>
       </c>
       <c r="I91" s="6">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J91" s="12">
-        <f t="shared" si="2"/>
-        <v>0.4464285714285714</v>
+        <f>E91/I91-1</f>
+        <v>0.41999999999999993</v>
       </c>
       <c r="K91" s="11">
-        <v>6.2962962962962971E-2</v>
+        <v>6.0563380281690143E-2</v>
       </c>
       <c r="L91" s="13">
-        <v>1136392000</v>
+        <v>6749146000</v>
       </c>
       <c r="M91" s="13">
-        <v>17458813000</v>
+        <v>70848374000</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O91" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P91" s="12">
-        <v>0.11296033854832702</v>
+        <v>8.5546264179245129E-2</v>
       </c>
       <c r="Q91" s="12">
-        <v>6.5089877530620205E-2</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B92" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="E92">
-        <v>9.93</v>
+        <v>8.1</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>30981601280</v>
+        <v>19085463552</v>
       </c>
       <c r="H92" s="6">
-        <v>10.1</v>
+        <v>11.68</v>
       </c>
       <c r="I92" s="6">
-        <v>5.6</v>
+        <v>5.19</v>
       </c>
       <c r="J92" s="12">
-        <f t="shared" si="2"/>
-        <v>0.77321428571428585</v>
+        <f>E92/I92-1</f>
+        <v>0.56069364161849689</v>
       </c>
       <c r="K92" s="11">
-        <v>3.2225579053373615E-2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="13">
-        <v>1990539000</v>
+        <v>13493113000</v>
       </c>
       <c r="M92" s="13">
-        <v>18620709000</v>
+        <v>208027754000</v>
       </c>
       <c r="N92" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O92" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P92" s="12">
-        <v>5.9005234317736605E-2</v>
+        <v>0.1219134386964545</v>
       </c>
       <c r="Q92" s="12">
-        <v>0.10689920561026972</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R92" s="14">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B93" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D93" t="s">
         <v>98</v>
       </c>
       <c r="E93">
-        <v>5.78</v>
+        <v>11.24</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>763225899008</v>
+        <v>85147041792</v>
       </c>
       <c r="H93" s="6">
-        <v>6.98</v>
+        <v>11.6</v>
       </c>
       <c r="I93" s="6">
-        <v>4.08</v>
+        <v>8.66</v>
       </c>
       <c r="J93" s="12">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666674</v>
+        <f>E93/I93-1</f>
+        <v>0.2979214780600461</v>
       </c>
       <c r="K93" s="11">
-        <v>4.4982698961937718E-2</v>
+        <v>7.0106761565836298E-2</v>
       </c>
       <c r="L93" s="13">
-        <v>44563000000</v>
+        <v>8154000000</v>
       </c>
       <c r="M93" s="13">
-        <v>463922000000</v>
+        <v>79588000000</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O93" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P93" s="12">
-        <v>6.4312320570263509E-2</v>
+        <v>6.4480904861881003E-2</v>
       </c>
       <c r="Q93" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R93" s="14">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B94" s="1" t="s">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="C94" t="s">
-        <v>161</v>
+        <v>314</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>310</v>
       </c>
       <c r="E94">
-        <v>9.56</v>
+        <v>1.52</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>292516888576</v>
+        <v>60497518592</v>
       </c>
       <c r="H94" s="6">
-        <v>11.56</v>
+        <v>2.08</v>
       </c>
       <c r="I94" s="6">
-        <v>5.88</v>
+        <v>1.18</v>
       </c>
       <c r="J94" s="12">
-        <f t="shared" si="2"/>
-        <v>0.62585034013605445</v>
+        <f>E94/I94-1</f>
+        <v>0.2881355932203391</v>
       </c>
       <c r="K94" s="11">
-        <v>0</v>
+        <v>3.6842105263157898E-2</v>
       </c>
       <c r="L94" s="13">
-        <v>26994000000</v>
+        <v>12616717000</v>
       </c>
       <c r="M94" s="13">
-        <v>363169000000</v>
+        <v>231208465000</v>
       </c>
       <c r="N94" s="9" t="s">
         <v>51</v>
@@ -6810,160 +6819,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>9.4688941767454848E-2</v>
+        <v>0.12898125410759451</v>
       </c>
       <c r="Q94" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>5.4568577322633927E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B95" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C95" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D95" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="E95">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>23822137344</v>
+        <v>5823742976</v>
       </c>
       <c r="H95" s="6">
-        <v>13.78</v>
+        <v>9.06</v>
       </c>
       <c r="I95" s="6">
-        <v>5.44</v>
+        <v>5.6</v>
       </c>
       <c r="J95" s="12">
-        <f t="shared" si="2"/>
-        <v>0.72794117647058809</v>
+        <f>E95/I95-1</f>
+        <v>0.54821428571428577</v>
       </c>
       <c r="K95" s="11">
-        <v>3.1914893617021274E-2</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="L95" s="13">
-        <v>9652467000</v>
+        <v>1136392000</v>
       </c>
       <c r="M95" s="13">
-        <v>173514401000</v>
+        <v>17458813000</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O95" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P95" s="12">
-        <v>0.10591812417369922</v>
+        <v>0.10881882033130333</v>
       </c>
       <c r="Q95" s="12">
-        <v>5.5629198178196171E-2</v>
+        <v>6.5089877530620205E-2</v>
       </c>
       <c r="R95" s="14">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B96" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C96" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D96" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E96">
-        <v>33.1</v>
+        <v>5.6</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>115842719744</v>
+        <v>743366393856</v>
       </c>
       <c r="H96" s="6">
-        <v>37.25</v>
+        <v>6.98</v>
       </c>
       <c r="I96" s="6">
-        <v>28.1</v>
+        <v>4.08</v>
       </c>
       <c r="J96" s="12">
-        <f t="shared" si="2"/>
-        <v>0.17793594306049831</v>
+        <f>E96/I96-1</f>
+        <v>0.37254901960784292</v>
       </c>
       <c r="K96" s="11">
-        <v>5.2567975830815711E-2</v>
+        <v>4.642857142857143E-2</v>
       </c>
       <c r="L96" s="13">
-        <v>16863000000</v>
+        <v>44563000000</v>
       </c>
       <c r="M96" s="13">
-        <v>448320000000</v>
+        <v>463922000000</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O96" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P96" s="12">
-        <v>0.12272414883032076</v>
+        <v>6.6085154024479342E-2</v>
       </c>
       <c r="Q96" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B97" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D97" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E97">
-        <v>1.68</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>5979741184</v>
+        <v>281501597696</v>
       </c>
       <c r="H97" s="6">
-        <v>2.95</v>
+        <v>11.56</v>
       </c>
       <c r="I97" s="6">
-        <v>1.37</v>
+        <v>5.88</v>
       </c>
       <c r="J97" s="12">
-        <f t="shared" si="2"/>
-        <v>0.22627737226277356</v>
+        <f>E97/I97-1</f>
+        <v>0.56462585034013602</v>
       </c>
       <c r="K97" s="11">
-        <v>5.5952380952380955E-2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="13">
-        <v>2220197000</v>
+        <v>26994000000</v>
       </c>
       <c r="M97" s="13">
-        <v>71097505000</v>
+        <v>363169000000</v>
       </c>
       <c r="N97" s="9" t="s">
         <v>51</v>
@@ -6972,64 +6981,64 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>0.12312120439777445</v>
+        <v>9.82419890331893E-2</v>
       </c>
       <c r="Q97" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B98" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E98">
-        <v>46.1</v>
+        <v>9.39</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>176564846592</v>
+        <v>23796795392</v>
       </c>
       <c r="H98" s="6">
-        <v>52.95</v>
+        <v>13.78</v>
       </c>
       <c r="I98" s="6">
-        <v>36.15</v>
+        <v>5.44</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
-        <v>0.27524204702627952</v>
+        <f>E98/I98-1</f>
+        <v>0.72610294117647056</v>
       </c>
       <c r="K98" s="11">
-        <v>4.7765726681127982E-2</v>
+        <v>3.1948881789137379E-2</v>
       </c>
       <c r="L98" s="13">
-        <v>41737000000</v>
+        <v>9652467000</v>
       </c>
       <c r="M98" s="13">
-        <v>794927000000</v>
+        <v>173514401000</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O98" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P98" s="12">
-        <v>0.10983627816766035</v>
+        <v>0.10594570016944529</v>
       </c>
       <c r="Q98" s="12">
-        <v>5.2504192208844336E-2</v>
+        <v>5.5629198178196171E-2</v>
       </c>
       <c r="R98" s="14">
         <v>68</v>
@@ -7037,95 +7046,95 @@
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B99" s="1" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="D99" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="E99">
-        <v>5.35</v>
+        <v>32.950000000000003</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>111841214464</v>
+        <v>115317760000</v>
       </c>
       <c r="H99" s="6">
-        <v>7.03</v>
+        <v>37.25</v>
       </c>
       <c r="I99" s="6">
-        <v>4.22</v>
+        <v>28.1</v>
       </c>
       <c r="J99" s="12">
-        <f t="shared" si="3"/>
-        <v>0.26777251184834117</v>
+        <f>E99/I99-1</f>
+        <v>0.17259786476868322</v>
       </c>
       <c r="K99" s="11">
-        <v>5.6074766355140186E-2</v>
+        <v>5.2807283763277688E-2</v>
       </c>
       <c r="L99" s="13">
-        <v>42109966000</v>
+        <v>16863000000</v>
       </c>
       <c r="M99" s="13">
-        <v>746176876000</v>
+        <v>448320000000</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O99" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P99" s="12">
-        <v>0.10083557927878818</v>
+        <v>0.12319481569213964</v>
       </c>
       <c r="Q99" s="12">
-        <v>5.643429507724386E-2</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B100" s="1" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="C100" t="s">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="D100" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="E100">
-        <v>5.19</v>
+        <v>47.4</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>40176103424</v>
+        <v>181543911424</v>
       </c>
       <c r="H100" s="6">
-        <v>5.49</v>
+        <v>52.95</v>
       </c>
       <c r="I100" s="6">
-        <v>3.8</v>
+        <v>36.15</v>
       </c>
       <c r="J100" s="12">
-        <f t="shared" si="3"/>
-        <v>0.36578947368421066</v>
+        <f>E100/I100-1</f>
+        <v>0.31120331950207469</v>
       </c>
       <c r="K100" s="11">
-        <v>7.3795761078998073E-2</v>
+        <v>4.6455696202531649E-2</v>
       </c>
       <c r="L100" s="13">
-        <v>5474000000</v>
+        <v>41737000000</v>
       </c>
       <c r="M100" s="13">
-        <v>59407000000</v>
+        <v>794927000000</v>
       </c>
       <c r="N100" s="9" t="s">
         <v>68</v>
@@ -7134,52 +7143,52 @@
         <v>1</v>
       </c>
       <c r="P100" s="12">
-        <v>5.9610731194064369E-2</v>
+        <v>0.10841570192904734</v>
       </c>
       <c r="Q100" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>5.2504192208844336E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B101" s="1" t="s">
-        <v>30</v>
+        <v>257</v>
       </c>
       <c r="C101" t="s">
-        <v>92</v>
+        <v>309</v>
       </c>
       <c r="D101" t="s">
-        <v>93</v>
+        <v>310</v>
       </c>
       <c r="E101">
-        <v>1.35</v>
+        <v>5.36</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>7374415872</v>
+        <v>109019193344</v>
       </c>
       <c r="H101" s="6">
-        <v>1.82</v>
+        <v>7.03</v>
       </c>
       <c r="I101" s="6">
-        <v>0.81</v>
+        <v>4.22</v>
       </c>
       <c r="J101" s="12">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <f>E101/I101-1</f>
+        <v>0.27014218009478697</v>
       </c>
       <c r="K101" s="11">
-        <v>2.5185185185185185E-2</v>
+        <v>5.5970149253731338E-2</v>
       </c>
       <c r="L101" s="13">
-        <v>1384865000</v>
+        <v>42109966000</v>
       </c>
       <c r="M101" s="13">
-        <v>23827484000</v>
+        <v>746176876000</v>
       </c>
       <c r="N101" s="9" t="s">
         <v>51</v>
@@ -7188,214 +7197,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P101" s="12">
-        <v>8.0028608509338919E-2</v>
+        <v>0.1014774306566779</v>
       </c>
       <c r="Q101" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>5.643429507724386E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C102" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D102" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E102">
-        <v>24.7</v>
+        <v>1.72</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>27375257600</v>
+        <v>6122116608</v>
       </c>
       <c r="H102" s="6">
-        <v>24.8</v>
+        <v>2.95</v>
       </c>
       <c r="I102" s="6">
-        <v>14.52</v>
+        <v>1.37</v>
       </c>
       <c r="J102" s="12">
-        <f t="shared" si="3"/>
-        <v>0.70110192837465557</v>
+        <f>E102/I102-1</f>
+        <v>0.25547445255474432</v>
       </c>
       <c r="K102" s="11">
-        <v>3.8056680161943315E-2</v>
+        <v>5.4651162790697677E-2</v>
       </c>
       <c r="L102" s="13">
-        <v>3838344000</v>
+        <v>2220197000</v>
       </c>
       <c r="M102" s="13">
-        <v>81520873000</v>
+        <v>71097505000</v>
       </c>
       <c r="N102" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O102" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P102" s="12">
-        <v>8.4931868729332158E-2</v>
+        <v>0.12221799720903279</v>
       </c>
       <c r="Q102" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B103" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="C103" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="D103" t="s">
         <v>98</v>
       </c>
       <c r="E103">
-        <v>11.6</v>
+        <v>5.15</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>204169297920</v>
+        <v>39866462208</v>
       </c>
       <c r="H103" s="6">
-        <v>12.46</v>
+        <v>5.49</v>
       </c>
       <c r="I103" s="6">
-        <v>9.1999999999999993</v>
+        <v>3.8</v>
       </c>
       <c r="J103" s="12">
-        <f t="shared" si="3"/>
-        <v>0.26086956521739135</v>
+        <f>E103/I103-1</f>
+        <v>0.35526315789473695</v>
       </c>
       <c r="K103" s="11">
-        <v>3.5948275862068967E-2</v>
+        <v>7.4368932038834948E-2</v>
       </c>
       <c r="L103" s="13">
-        <v>16758000000</v>
+        <v>5474000000</v>
       </c>
       <c r="M103" s="13">
-        <v>269590000000</v>
+        <v>59407000000</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O103" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P103" s="12">
-        <v>5.9626514955333471E-2</v>
+        <v>5.9812414408194597E-2</v>
       </c>
       <c r="Q103" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B104" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D104" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E104">
-        <v>6.86</v>
+        <v>1.29</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>7158684160</v>
+        <v>7046663680</v>
       </c>
       <c r="H104" s="6">
-        <v>7</v>
+        <v>1.82</v>
       </c>
       <c r="I104" s="6">
-        <v>4.0199999999999996</v>
+        <v>0.81</v>
       </c>
       <c r="J104" s="12">
-        <f t="shared" si="3"/>
-        <v>0.70646766169154263</v>
+        <f>E104/I104-1</f>
+        <v>0.59259259259259256</v>
       </c>
       <c r="K104" s="11">
-        <v>0</v>
+        <v>2.6356589147286821E-2</v>
       </c>
       <c r="L104" s="13">
-        <v>303335000</v>
+        <v>1384865000</v>
       </c>
       <c r="M104" s="13">
-        <v>3620162000</v>
+        <v>23827484000</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O104" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P104" s="12">
-        <v>5.0016264870190799E-2</v>
+        <v>8.1472959597027175E-2</v>
       </c>
       <c r="Q104" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B105" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D105" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E105">
-        <v>2.2599999999999998</v>
+        <v>23.35</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>9706699776</v>
+        <v>25879040000</v>
       </c>
       <c r="H105" s="6">
-        <v>3.04</v>
+        <v>25.15</v>
       </c>
       <c r="I105" s="6">
-        <v>1.93</v>
+        <v>14.52</v>
       </c>
       <c r="J105" s="12">
-        <f t="shared" si="3"/>
-        <v>0.17098445595854916</v>
+        <f>E105/I105-1</f>
+        <v>0.60812672176308546</v>
       </c>
       <c r="K105" s="11">
-        <v>4.7345132743362835E-2</v>
+        <v>4.0256959314775159E-2</v>
       </c>
       <c r="L105" s="13">
-        <v>1938532000</v>
+        <v>3838344000</v>
       </c>
       <c r="M105" s="13">
-        <v>49986396000</v>
+        <v>81520873000</v>
       </c>
       <c r="N105" s="9" t="s">
         <v>68</v>
@@ -7404,160 +7413,160 @@
         <v>1</v>
       </c>
       <c r="P105" s="12">
-        <v>6.4115012275143504E-2</v>
+        <v>8.7839999066297345E-2</v>
       </c>
       <c r="Q105" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B106" s="1" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="D106" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="E106">
-        <v>42.25</v>
+        <v>6.86</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>446574034944</v>
+        <v>7158684160</v>
       </c>
       <c r="H106" s="6">
-        <v>59.7</v>
+        <v>7</v>
       </c>
       <c r="I106" s="6">
-        <v>15.24</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J106" s="12">
-        <f t="shared" si="3"/>
-        <v>1.7723097112860891</v>
+        <f>E106/I106-1</f>
+        <v>0.70646766169154263</v>
       </c>
       <c r="K106" s="11">
         <v>0</v>
       </c>
       <c r="L106" s="13">
-        <v>984027000</v>
+        <v>303335000</v>
       </c>
       <c r="M106" s="13">
-        <v>32183526000</v>
+        <v>3620162000</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O106" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P106" s="12">
-        <v>1.5548782898068332E-2</v>
+        <v>5.0016264870190799E-2</v>
       </c>
       <c r="Q106" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B107" s="1" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="C107" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="D107" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="E107">
-        <v>13.66</v>
+        <v>11.36</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>14028956672</v>
+        <v>199945093120</v>
       </c>
       <c r="H107" s="6">
-        <v>14.5</v>
+        <v>12.46</v>
       </c>
       <c r="I107" s="6">
-        <v>10.36</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J107" s="12">
-        <f t="shared" si="3"/>
-        <v>0.31853281853281867</v>
+        <f>E107/I107-1</f>
+        <v>0.23478260869565215</v>
       </c>
       <c r="K107" s="11">
-        <v>7.9062957540263545E-2</v>
+        <v>3.6707746478873239E-2</v>
       </c>
       <c r="L107" s="13">
-        <v>984000000</v>
+        <v>16758000000</v>
       </c>
       <c r="M107" s="13">
-        <v>101944000000</v>
+        <v>269590000000</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O107" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P107" s="12">
-        <v>2.5244390409937343E-2</v>
+        <v>6.0477321065231737E-2</v>
       </c>
       <c r="Q107" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B108" s="1" t="s">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
       <c r="D108" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="E108">
-        <v>9.74</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>10350211072</v>
+        <v>9363100672</v>
       </c>
       <c r="H108" s="6">
-        <v>12.88</v>
+        <v>3.04</v>
       </c>
       <c r="I108" s="6">
-        <v>4.47</v>
+        <v>1.93</v>
       </c>
       <c r="J108" s="12">
-        <f t="shared" si="3"/>
-        <v>1.1789709172259508</v>
+        <f>E108/I108-1</f>
+        <v>0.1295336787564767</v>
       </c>
       <c r="K108" s="11">
-        <v>1.0574948665297741E-2</v>
+        <v>4.9082568807339445E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>81340000</v>
+        <v>1938532000</v>
       </c>
       <c r="M108" s="13">
-        <v>3509401000</v>
+        <v>49986396000</v>
       </c>
       <c r="N108" s="9" t="s">
         <v>68</v>
@@ -7566,103 +7575,106 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>7.7794209390644568E-3</v>
+        <v>6.4852003257214824E-2</v>
       </c>
       <c r="Q108" s="12">
-        <v>2.3177744578063323E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R108" s="14">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B109" s="1" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="D109" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="E109">
-        <v>29.2</v>
+        <v>9.34</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>29815828480</v>
+        <v>9925150720</v>
       </c>
       <c r="H109" s="6">
-        <v>36</v>
+        <v>12.88</v>
       </c>
       <c r="I109" s="6">
-        <v>22.4</v>
+        <v>4.47</v>
       </c>
       <c r="J109" s="12">
-        <f t="shared" si="3"/>
-        <v>0.3035714285714286</v>
+        <f>E109/I109-1</f>
+        <v>1.0894854586129754</v>
       </c>
       <c r="K109" s="11">
-        <v>0</v>
+        <v>1.1027837259100642E-2</v>
       </c>
       <c r="L109" s="13">
-        <v>-90314000</v>
+        <v>161696000</v>
       </c>
       <c r="M109" s="13">
-        <v>18374441000</v>
+        <v>3260547000</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O109" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>-3.6402784697953479E-3</v>
+        <v>1.668766743397572E-2</v>
       </c>
       <c r="Q109" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>4.95916789422143E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B110" s="1" t="s">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="D110" t="s">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="E110">
-        <v>34.4</v>
+        <v>13.6</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>363704320000</v>
+        <v>13967336448</v>
       </c>
       <c r="H110" s="6">
-        <v>34.6</v>
+        <v>14.5</v>
       </c>
       <c r="I110" s="6">
-        <v>21.5</v>
+        <v>10.36</v>
       </c>
       <c r="J110" s="12">
-        <f t="shared" si="3"/>
-        <v>0.59999999999999987</v>
+        <f>E110/I110-1</f>
+        <v>0.31274131274131278</v>
       </c>
       <c r="K110" s="11">
-        <v>5.7819767441860473E-2</v>
+        <v>7.9411764705882362E-2</v>
+      </c>
+      <c r="L110" s="13">
+        <v>984000000</v>
       </c>
       <c r="M110" s="13">
-        <v>415994000000</v>
+        <v>101944000000</v>
       </c>
       <c r="N110" s="9" t="s">
         <v>68</v>
@@ -7670,83 +7682,107 @@
       <c r="O110" s="6">
         <v>1</v>
       </c>
+      <c r="P110" s="12">
+        <v>2.5284361413448395E-2</v>
+      </c>
+      <c r="Q110" s="12">
+        <v>9.6523581574197593E-3</v>
+      </c>
+      <c r="R110" s="14">
+        <v>77</v>
+      </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B111" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D111" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="E111">
-        <v>7.2</v>
+        <v>39.5</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>588140642304</v>
+        <v>417104199680</v>
       </c>
       <c r="H111" s="6">
-        <v>7.27</v>
+        <v>59.7</v>
       </c>
       <c r="I111" s="6">
-        <v>5.08</v>
+        <v>15.24</v>
       </c>
       <c r="J111" s="12">
-        <f t="shared" si="3"/>
-        <v>0.41732283464566922</v>
+        <f>E111/I111-1</f>
+        <v>1.5918635170603674</v>
       </c>
       <c r="K111" s="11">
-        <v>5.2638888888888888E-2</v>
+        <v>0</v>
+      </c>
+      <c r="L111" s="13">
+        <v>984027000</v>
       </c>
       <c r="M111" s="13">
-        <v>2314289000000</v>
+        <v>32183526000</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O111" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
+      </c>
+      <c r="P111" s="12">
+        <v>1.6550687776386103E-2</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>3.0575487595734537E-2</v>
+      </c>
+      <c r="R111" s="14">
+        <v>78</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B112" s="1" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="C112" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="D112" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="E112">
-        <v>5.95</v>
+        <v>29.05</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>2634100506624</v>
+        <v>29662662656</v>
       </c>
       <c r="H112" s="6">
-        <v>5.97</v>
+        <v>36</v>
       </c>
       <c r="I112" s="6">
-        <v>4.0599999999999996</v>
+        <v>22.4</v>
       </c>
       <c r="J112" s="12">
-        <f t="shared" si="3"/>
-        <v>0.4655172413793105</v>
+        <f>E112/I112-1</f>
+        <v>0.29687500000000022</v>
       </c>
       <c r="K112" s="11">
-        <v>5.1764705882352942E-2</v>
+        <v>0</v>
+      </c>
+      <c r="L112" s="13">
+        <v>-90314000</v>
       </c>
       <c r="M112" s="13">
-        <v>6434377000000</v>
+        <v>18374441000</v>
       </c>
       <c r="N112" s="9" t="s">
         <v>51</v>
@@ -7754,83 +7790,92 @@
       <c r="O112" s="6">
         <v>1.0683760683760684</v>
       </c>
+      <c r="P112" s="12">
+        <v>-3.6614361826565116E-3</v>
+      </c>
+      <c r="Q112" s="12">
+        <v>-4.9151971480384084E-3</v>
+      </c>
+      <c r="R112" s="14">
+        <v>79</v>
+      </c>
     </row>
     <row r="113" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B113" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C113" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D113" t="s">
         <v>229</v>
       </c>
       <c r="E113">
-        <v>5.18</v>
+        <v>35.4</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>573933617152</v>
+        <v>374277144576</v>
       </c>
       <c r="H113" s="6">
-        <v>5.39</v>
+        <v>35.65</v>
       </c>
       <c r="I113" s="6">
-        <v>3.89</v>
+        <v>21.5</v>
       </c>
       <c r="J113" s="12">
-        <f t="shared" si="3"/>
-        <v>0.3316195372750641</v>
+        <f>E113/I113-1</f>
+        <v>0.64651162790697669</v>
       </c>
       <c r="K113" s="11">
-        <v>0</v>
+        <v>5.6186440677966104E-2</v>
       </c>
       <c r="M113" s="13">
-        <v>1271649000000</v>
+        <v>415994000000</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O113" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B114" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C114" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D114" t="s">
         <v>231</v>
       </c>
       <c r="E114">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>1885176987648</v>
+        <v>718260862976</v>
       </c>
       <c r="H114" s="6">
-        <v>7.44</v>
+        <v>7.43</v>
       </c>
       <c r="I114" s="6">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
       <c r="J114" s="12">
-        <f t="shared" si="3"/>
-        <v>0.42256214149139582</v>
+        <f>E114/I114-1</f>
+        <v>0.43700787401574792</v>
       </c>
       <c r="K114" s="11">
-        <v>5.4166666666666669E-2</v>
+        <v>5.1917808219178081E-2</v>
       </c>
       <c r="M114" s="13">
-        <v>6128626000000</v>
+        <v>2314289000000</v>
       </c>
       <c r="N114" s="9" t="s">
         <v>51</v>
@@ -7841,38 +7886,38 @@
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B115" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C115" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D115" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E115">
-        <v>7.22</v>
+        <v>6.2</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>482755903488</v>
+        <v>2747480408064</v>
       </c>
       <c r="H115" s="6">
-        <v>7.3</v>
+        <v>6.24</v>
       </c>
       <c r="I115" s="6">
-        <v>4.26</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J115" s="12">
-        <f t="shared" si="3"/>
-        <v>0.69483568075117375</v>
+        <f>E115/I115-1</f>
+        <v>0.52709359605911343</v>
       </c>
       <c r="K115" s="11">
-        <v>4.916897506925208E-2</v>
+        <v>4.9677419354838707E-2</v>
       </c>
       <c r="M115" s="13">
-        <v>2066897000000</v>
+        <v>6434377000000</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>51</v>
@@ -7883,51 +7928,128 @@
     </row>
     <row r="116" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B116" s="1" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="C116" t="s">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>229</v>
       </c>
       <c r="E116">
-        <v>4.17</v>
+        <v>5.46</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>16171593728</v>
+        <v>594359222272</v>
       </c>
       <c r="H116" s="6">
-        <v>6.97</v>
+        <v>5.48</v>
       </c>
       <c r="I116" s="6">
-        <v>3.33</v>
+        <v>3.89</v>
       </c>
       <c r="J116" s="12">
-        <f t="shared" si="3"/>
-        <v>0.25225225225225212</v>
+        <f>E116/I116-1</f>
+        <v>0.40359897172236492</v>
       </c>
       <c r="K116" s="11">
-        <v>6.4748201438848921E-2</v>
+        <v>0</v>
+      </c>
+      <c r="M116" s="13">
+        <v>1271649000000</v>
       </c>
       <c r="N116" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O116" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
     </row>
     <row r="117" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B117" s="1" t="s">
-        <v>373</v>
+        <v>206</v>
+      </c>
+      <c r="C117" t="s">
+        <v>234</v>
+      </c>
+      <c r="D117" t="s">
+        <v>231</v>
+      </c>
+      <c r="E117">
+        <v>7.73</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G117" s="7">
+        <v>1958225379328</v>
+      </c>
+      <c r="H117" s="6">
+        <v>7.8</v>
+      </c>
+      <c r="I117" s="6">
+        <v>5.23</v>
+      </c>
+      <c r="J117" s="12">
+        <f>E117/I117-1</f>
+        <v>0.47801147227533458</v>
+      </c>
+      <c r="K117" s="11">
+        <v>5.2134540750323415E-2</v>
+      </c>
+      <c r="M117" s="13">
+        <v>6128626000000</v>
+      </c>
+      <c r="N117" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O117" s="6">
+        <v>1.0683760683760684</v>
       </c>
     </row>
     <row r="118" spans="2:15" x14ac:dyDescent="0.5">
       <c r="B118" s="1" t="s">
-        <v>374</v>
+        <v>207</v>
+      </c>
+      <c r="C118" t="s">
+        <v>235</v>
+      </c>
+      <c r="D118" t="s">
+        <v>229</v>
+      </c>
+      <c r="E118">
+        <v>7.82</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G118" s="7">
+        <v>510649139200</v>
+      </c>
+      <c r="H118" s="6">
+        <v>7.97</v>
+      </c>
+      <c r="I118" s="6">
+        <v>4.26</v>
+      </c>
+      <c r="J118" s="12">
+        <f>E118/I118-1</f>
+        <v>0.83568075117370899</v>
+      </c>
+      <c r="K118" s="11">
+        <v>4.5396419437340151E-2</v>
+      </c>
+      <c r="M118" s="13">
+        <v>2066897000000</v>
+      </c>
+      <c r="N118" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O118" s="6">
+        <v>1.0683760683760684</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FEBD13-20B9-48E0-8AC1-B726DC376CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50432CD5-27F5-4B6E-A850-E3A55DFA741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="389">
   <si>
     <t>Ticker</t>
   </si>
@@ -1233,6 +1233,39 @@
   </si>
   <si>
     <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>JINGJIN EQUIPMENT INC</t>
+  </si>
+  <si>
+    <t>Pollution &amp; Treatment Controls</t>
+  </si>
+  <si>
+    <t>CHONG QING BREWERY CO.LTD</t>
+  </si>
+  <si>
+    <t>ZHEJIANG DINGLI MACHINERY CO LT</t>
+  </si>
+  <si>
+    <t>OFFSHORE OIL ENGINEERING CO</t>
+  </si>
+  <si>
+    <t>JIANGSU YANGHE DIS</t>
+  </si>
+  <si>
+    <t>CHINESE UNIVERSE PUBLISHING&amp;MED</t>
+  </si>
+  <si>
+    <t>CHACHA FOOD CO LTD</t>
+  </si>
+  <si>
+    <t>INDUSTRIAL BANK CO LTD</t>
+  </si>
+  <si>
+    <t>CHINA WORLD TRADE CENTER</t>
+  </si>
+  <si>
+    <t>PUYANG HUICHENG EL</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +1865,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
         <v>0.22881355932203395</v>
       </c>
       <c r="K2" s="11">
@@ -1886,7 +1919,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.24568965517241392</v>
       </c>
       <c r="K3" s="11">
@@ -1940,7 +1973,7 @@
         <v>9.52</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.45168067226890773</v>
       </c>
       <c r="K4" s="11">
@@ -1994,7 +2027,7 @@
         <v>4.22</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>0.64691943127962093</v>
       </c>
       <c r="K5" s="11">
@@ -2048,7 +2081,7 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.46593406593406606</v>
       </c>
       <c r="K6" s="11">
@@ -2102,7 +2135,7 @@
         <v>1.35</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>0.22962962962962941</v>
       </c>
       <c r="K7" s="11">
@@ -2156,7 +2189,7 @@
         <v>2.23</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>0.17040358744394624</v>
       </c>
       <c r="K8" s="11">
@@ -2210,7 +2243,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>0.19469026548672574</v>
       </c>
       <c r="K9" s="11">
@@ -2264,7 +2297,7 @@
         <v>4.58</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>0.50436681222707413</v>
       </c>
       <c r="K10" s="11">
@@ -2318,7 +2351,7 @@
         <v>3.15</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>0.46031746031746024</v>
       </c>
       <c r="K11" s="11">
@@ -2372,7 +2405,7 @@
         <v>1.36</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>6.6176470588235281E-2</v>
       </c>
       <c r="K12" s="11">
@@ -2426,7 +2459,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>1.2788844621513946</v>
       </c>
       <c r="K13" s="11">
@@ -2480,7 +2513,7 @@
         <v>10.6</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>0.55094339622641519</v>
       </c>
       <c r="K14" s="11">
@@ -2534,7 +2567,7 @@
         <v>3.46</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.71387283236994215</v>
       </c>
       <c r="K15" s="11">
@@ -2588,7 +2621,7 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>0.87284768211920549</v>
       </c>
       <c r="K16" s="11">
@@ -2642,7 +2675,7 @@
         <v>5</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.46799999999999997</v>
       </c>
       <c r="K17" s="11">
@@ -2696,7 +2729,7 @@
         <v>7.96</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
+        <f t="shared" si="0"/>
         <v>0.98241206030150741</v>
       </c>
       <c r="K18" s="11">
@@ -2750,7 +2783,7 @@
         <v>1.92</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
+        <f t="shared" si="0"/>
         <v>0.19270833333333348</v>
       </c>
       <c r="K19" s="11">
@@ -2804,7 +2837,7 @@
         <v>7.96</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
+        <f t="shared" si="0"/>
         <v>0.98241206030150741</v>
       </c>
       <c r="K20" s="11">
@@ -2858,7 +2891,7 @@
         <v>4.84</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
+        <f t="shared" si="0"/>
         <v>0.5123966942148761</v>
       </c>
       <c r="K21" s="11">
@@ -2912,7 +2945,7 @@
         <v>0.42</v>
       </c>
       <c r="J22" s="12">
-        <f>E22/I22-1</f>
+        <f t="shared" si="0"/>
         <v>0.80952380952380953</v>
       </c>
       <c r="K22" s="11">
@@ -2966,7 +2999,7 @@
         <v>12.12</v>
       </c>
       <c r="J23" s="12">
-        <f>E23/I23-1</f>
+        <f t="shared" si="0"/>
         <v>0.14851485148514865</v>
       </c>
       <c r="K23" s="11">
@@ -3020,7 +3053,7 @@
         <v>7.08</v>
       </c>
       <c r="J24" s="12">
-        <f>E24/I24-1</f>
+        <f t="shared" si="0"/>
         <v>9.6045197740112886E-2</v>
       </c>
       <c r="K24" s="11">
@@ -3074,7 +3107,7 @@
         <v>15.7</v>
       </c>
       <c r="J25" s="12">
-        <f>E25/I25-1</f>
+        <f t="shared" si="0"/>
         <v>0.60509554140127397</v>
       </c>
       <c r="K25" s="11">
@@ -3128,7 +3161,7 @@
         <v>7.16</v>
       </c>
       <c r="J26" s="12">
-        <f>E26/I26-1</f>
+        <f t="shared" si="0"/>
         <v>0.25698324022346375</v>
       </c>
       <c r="K26" s="11">
@@ -3182,7 +3215,7 @@
         <v>6.57</v>
       </c>
       <c r="J27" s="12">
-        <f>E27/I27-1</f>
+        <f t="shared" si="0"/>
         <v>0.37747336377473362</v>
       </c>
       <c r="K27" s="11">
@@ -3236,7 +3269,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="J28" s="12">
-        <f>E28/I28-1</f>
+        <f t="shared" si="0"/>
         <v>0.1588785046728971</v>
       </c>
       <c r="K28" s="11">
@@ -3290,7 +3323,7 @@
         <v>2.8</v>
       </c>
       <c r="J29" s="12">
-        <f>E29/I29-1</f>
+        <f t="shared" si="0"/>
         <v>0.29642857142857149</v>
       </c>
       <c r="K29" s="11">
@@ -3344,7 +3377,7 @@
         <v>3.39</v>
       </c>
       <c r="J30" s="12">
-        <f>E30/I30-1</f>
+        <f t="shared" si="0"/>
         <v>0.64306784660766958</v>
       </c>
       <c r="K30" s="11">
@@ -3398,7 +3431,7 @@
         <v>3.22</v>
       </c>
       <c r="J31" s="12">
-        <f>E31/I31-1</f>
+        <f t="shared" si="0"/>
         <v>0.42546583850931663</v>
       </c>
       <c r="K31" s="11">
@@ -3452,7 +3485,7 @@
         <v>3.97</v>
       </c>
       <c r="J32" s="12">
-        <f>E32/I32-1</f>
+        <f t="shared" si="0"/>
         <v>0.40554156171284639</v>
       </c>
       <c r="K32" s="11">
@@ -3506,7 +3539,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J33" s="12">
-        <f>E33/I33-1</f>
+        <f t="shared" si="0"/>
         <v>0.25454545454545441</v>
       </c>
       <c r="K33" s="11">
@@ -3560,7 +3593,7 @@
         <v>3.33</v>
       </c>
       <c r="J34" s="12">
-        <f>E34/I34-1</f>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
         <v>0.21621621621621623</v>
       </c>
       <c r="K34" s="11">
@@ -3614,7 +3647,7 @@
         <v>8.67</v>
       </c>
       <c r="J35" s="12">
-        <f>E35/I35-1</f>
+        <f t="shared" si="1"/>
         <v>0.27566320645905429</v>
       </c>
       <c r="K35" s="11">
@@ -3668,7 +3701,7 @@
         <v>3.45</v>
       </c>
       <c r="J36" s="12">
-        <f>E36/I36-1</f>
+        <f t="shared" si="1"/>
         <v>0.54202898550724643</v>
       </c>
       <c r="K36" s="11">
@@ -3722,7 +3755,7 @@
         <v>3.58</v>
       </c>
       <c r="J37" s="12">
-        <f>E37/I37-1</f>
+        <f t="shared" si="1"/>
         <v>0.1899441340782122</v>
       </c>
       <c r="K37" s="11">
@@ -3776,7 +3809,7 @@
         <v>2.16</v>
       </c>
       <c r="J38" s="12">
-        <f>E38/I38-1</f>
+        <f t="shared" si="1"/>
         <v>1.8101851851851851</v>
       </c>
       <c r="K38" s="11">
@@ -3830,7 +3863,7 @@
         <v>2.35</v>
       </c>
       <c r="J39" s="12">
-        <f>E39/I39-1</f>
+        <f t="shared" si="1"/>
         <v>0.28936170212765955</v>
       </c>
       <c r="K39" s="11">
@@ -3884,7 +3917,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="J40" s="12">
-        <f>E40/I40-1</f>
+        <f t="shared" si="1"/>
         <v>0.30602409638554207</v>
       </c>
       <c r="K40" s="11">
@@ -3938,7 +3971,7 @@
         <v>3.46</v>
       </c>
       <c r="J41" s="12">
-        <f>E41/I41-1</f>
+        <f t="shared" si="1"/>
         <v>0.35260115606936404</v>
       </c>
       <c r="K41" s="11">
@@ -3992,7 +4025,7 @@
         <v>4.12</v>
       </c>
       <c r="J42" s="12">
-        <f>E42/I42-1</f>
+        <f t="shared" si="1"/>
         <v>0.30097087378640786</v>
       </c>
       <c r="K42" s="11">
@@ -4046,7 +4079,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="J43" s="12">
-        <f>E43/I43-1</f>
+        <f t="shared" si="1"/>
         <v>1.1448275862068966</v>
       </c>
       <c r="K43" s="11">
@@ -4100,7 +4133,7 @@
         <v>3.64</v>
       </c>
       <c r="J44" s="12">
-        <f>E44/I44-1</f>
+        <f t="shared" si="1"/>
         <v>0.78571428571428559</v>
       </c>
       <c r="K44" s="11">
@@ -4154,7 +4187,7 @@
         <v>18.559999999999999</v>
       </c>
       <c r="J45" s="12">
-        <f>E45/I45-1</f>
+        <f t="shared" si="1"/>
         <v>0.43318965517241392</v>
       </c>
       <c r="K45" s="11">
@@ -4208,7 +4241,7 @@
         <v>3.71</v>
       </c>
       <c r="J46" s="12">
-        <f>E46/I46-1</f>
+        <f t="shared" si="1"/>
         <v>0.20485175202156336</v>
       </c>
       <c r="K46" s="11">
@@ -4262,7 +4295,7 @@
         <v>3.4</v>
       </c>
       <c r="J47" s="12">
-        <f>E47/I47-1</f>
+        <f t="shared" si="1"/>
         <v>0.17647058823529416</v>
       </c>
       <c r="K47" s="11">
@@ -4316,7 +4349,7 @@
         <v>65.55</v>
       </c>
       <c r="J48" s="12">
-        <f>E48/I48-1</f>
+        <f t="shared" si="1"/>
         <v>0.38825324180015253</v>
       </c>
       <c r="K48" s="11">
@@ -4370,7 +4403,7 @@
         <v>1.33</v>
       </c>
       <c r="J49" s="12">
-        <f>E49/I49-1</f>
+        <f t="shared" si="1"/>
         <v>0.47368421052631571</v>
       </c>
       <c r="K49" s="11">
@@ -4424,7 +4457,7 @@
         <v>8.81</v>
       </c>
       <c r="J50" s="12">
-        <f>E50/I50-1</f>
+        <f t="shared" si="1"/>
         <v>0.30760499432463106</v>
       </c>
       <c r="K50" s="11">
@@ -4478,7 +4511,7 @@
         <v>7.36</v>
       </c>
       <c r="J51" s="12">
-        <f>E51/I51-1</f>
+        <f t="shared" si="1"/>
         <v>0.35869565217391308</v>
       </c>
       <c r="K51" s="11">
@@ -4532,7 +4565,7 @@
         <v>19.239999999999998</v>
       </c>
       <c r="J52" s="12">
-        <f>E52/I52-1</f>
+        <f t="shared" si="1"/>
         <v>0.18243243243243246</v>
       </c>
       <c r="K52" s="11">
@@ -4586,7 +4619,7 @@
         <v>55.05</v>
       </c>
       <c r="J53" s="12">
-        <f>E53/I53-1</f>
+        <f t="shared" si="1"/>
         <v>0.35240690281562226</v>
       </c>
       <c r="K53" s="11">
@@ -4640,7 +4673,7 @@
         <v>2.36</v>
       </c>
       <c r="J54" s="12">
-        <f>E54/I54-1</f>
+        <f t="shared" si="1"/>
         <v>0.67372881355932224</v>
       </c>
       <c r="K54" s="11">
@@ -4694,7 +4727,7 @@
         <v>5.31</v>
       </c>
       <c r="J55" s="12">
-        <f>E55/I55-1</f>
+        <f t="shared" si="1"/>
         <v>0.19020715630885143</v>
       </c>
       <c r="K55" s="11">
@@ -4748,7 +4781,7 @@
         <v>16.18</v>
       </c>
       <c r="J56" s="12">
-        <f>E56/I56-1</f>
+        <f t="shared" si="1"/>
         <v>0.18294190358467244</v>
       </c>
       <c r="K56" s="11">
@@ -4802,7 +4835,7 @@
         <v>43.55</v>
       </c>
       <c r="J57" s="12">
-        <f>E57/I57-1</f>
+        <f t="shared" si="1"/>
         <v>9.5292766934558015E-2</v>
       </c>
       <c r="K57" s="11">
@@ -4856,7 +4889,7 @@
         <v>0.46</v>
       </c>
       <c r="J58" s="12">
-        <f>E58/I58-1</f>
+        <f t="shared" si="1"/>
         <v>0.13043478260869557</v>
       </c>
       <c r="K58" s="11">
@@ -4910,7 +4943,7 @@
         <v>218.4</v>
       </c>
       <c r="J59" s="12">
-        <f>E59/I59-1</f>
+        <f t="shared" si="1"/>
         <v>0.79761904761904767</v>
       </c>
       <c r="K59" s="11">
@@ -4964,7 +4997,7 @@
         <v>3.36</v>
       </c>
       <c r="J60" s="12">
-        <f>E60/I60-1</f>
+        <f t="shared" si="1"/>
         <v>0.70238095238095233</v>
       </c>
       <c r="K60" s="11">
@@ -5018,7 +5051,7 @@
         <v>9.9</v>
       </c>
       <c r="J61" s="12">
-        <f>E61/I61-1</f>
+        <f t="shared" si="1"/>
         <v>0.9757575757575756</v>
       </c>
       <c r="K61" s="11">
@@ -5072,7 +5105,7 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="J62" s="12">
-        <f>E62/I62-1</f>
+        <f t="shared" si="1"/>
         <v>0.29559748427672972</v>
       </c>
       <c r="K62" s="11">
@@ -5126,7 +5159,7 @@
         <v>3.34</v>
       </c>
       <c r="J63" s="12">
-        <f>E63/I63-1</f>
+        <f t="shared" si="1"/>
         <v>8.9820359281437279E-2</v>
       </c>
       <c r="K63" s="11">
@@ -5180,7 +5213,7 @@
         <v>1.74</v>
       </c>
       <c r="J64" s="12">
-        <f>E64/I64-1</f>
+        <f t="shared" si="1"/>
         <v>0.42528735632183912</v>
       </c>
       <c r="K64" s="11">
@@ -5234,7 +5267,7 @@
         <v>13.52</v>
       </c>
       <c r="J65" s="12">
-        <f>E65/I65-1</f>
+        <f t="shared" si="1"/>
         <v>0.41863905325443795</v>
       </c>
       <c r="K65" s="11">
@@ -5288,7 +5321,7 @@
         <v>34.4</v>
       </c>
       <c r="J66" s="12">
-        <f>E66/I66-1</f>
+        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
         <v>5.9651162790697674</v>
       </c>
       <c r="K66" s="11">
@@ -5342,7 +5375,7 @@
         <v>225.2</v>
       </c>
       <c r="J67" s="12">
-        <f>E67/I67-1</f>
+        <f t="shared" si="2"/>
         <v>0.5008880994671403</v>
       </c>
       <c r="K67" s="11">
@@ -5396,7 +5429,7 @@
         <v>0.99</v>
       </c>
       <c r="J68" s="12">
-        <f>E68/I68-1</f>
+        <f t="shared" si="2"/>
         <v>0.81818181818181834</v>
       </c>
       <c r="K68" s="11">
@@ -5450,7 +5483,7 @@
         <v>3.99</v>
       </c>
       <c r="J69" s="12">
-        <f>E69/I69-1</f>
+        <f t="shared" si="2"/>
         <v>0.77192982456140347</v>
       </c>
       <c r="K69" s="11">
@@ -5504,7 +5537,7 @@
         <v>5.49</v>
       </c>
       <c r="J70" s="12">
-        <f>E70/I70-1</f>
+        <f t="shared" si="2"/>
         <v>0.36976320582877942</v>
       </c>
       <c r="K70" s="11">
@@ -5558,7 +5591,7 @@
         <v>13.48</v>
       </c>
       <c r="J71" s="12">
-        <f>E71/I71-1</f>
+        <f t="shared" si="2"/>
         <v>1.2997032640949553</v>
       </c>
       <c r="K71" s="11">
@@ -5612,7 +5645,7 @@
         <v>19.52</v>
       </c>
       <c r="J72" s="12">
-        <f>E72/I72-1</f>
+        <f t="shared" si="2"/>
         <v>0.10655737704918034</v>
       </c>
       <c r="K72" s="11">
@@ -5666,7 +5699,7 @@
         <v>38.4</v>
       </c>
       <c r="J73" s="12">
-        <f>E73/I73-1</f>
+        <f t="shared" si="2"/>
         <v>0.44791666666666674</v>
       </c>
       <c r="K73" s="11">
@@ -5720,7 +5753,7 @@
         <v>5.83</v>
       </c>
       <c r="J74" s="12">
-        <f>E74/I74-1</f>
+        <f t="shared" si="2"/>
         <v>1.1886792452830188</v>
       </c>
       <c r="K74" s="11">
@@ -5774,7 +5807,7 @@
         <v>349</v>
       </c>
       <c r="J75" s="12">
-        <f>E75/I75-1</f>
+        <f t="shared" si="2"/>
         <v>0.44842406876790841</v>
       </c>
       <c r="K75" s="11">
@@ -5828,7 +5861,7 @@
         <v>6.56</v>
       </c>
       <c r="J76" s="12">
-        <f>E76/I76-1</f>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="K76" s="11">
@@ -5882,7 +5915,7 @@
         <v>6.65</v>
       </c>
       <c r="J77" s="12">
-        <f>E77/I77-1</f>
+        <f t="shared" si="2"/>
         <v>0.46165413533834587</v>
       </c>
       <c r="K77" s="11">
@@ -5936,7 +5969,7 @@
         <v>2.11</v>
       </c>
       <c r="J78" s="12">
-        <f>E78/I78-1</f>
+        <f t="shared" si="2"/>
         <v>0.28436018957345977</v>
       </c>
       <c r="K78" s="11">
@@ -5990,7 +6023,7 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="J79" s="12">
-        <f>E79/I79-1</f>
+        <f t="shared" si="2"/>
         <v>0.44028103044496514</v>
       </c>
       <c r="K79" s="11">
@@ -6044,7 +6077,7 @@
         <v>6.84</v>
       </c>
       <c r="J80" s="12">
-        <f>E80/I80-1</f>
+        <f t="shared" si="2"/>
         <v>0.17105263157894735</v>
       </c>
       <c r="K80" s="11">
@@ -6098,7 +6131,7 @@
         <v>7.51</v>
       </c>
       <c r="J81" s="12">
-        <f>E81/I81-1</f>
+        <f t="shared" si="2"/>
         <v>0.7576564580559253</v>
       </c>
       <c r="K81" s="11">
@@ -6152,7 +6185,7 @@
         <v>10.98</v>
       </c>
       <c r="J82" s="12">
-        <f>E82/I82-1</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="K82" s="11">
@@ -6206,7 +6239,7 @@
         <v>10.98</v>
       </c>
       <c r="J83" s="12">
-        <f>E83/I83-1</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="K83" s="11">
@@ -6260,7 +6293,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J84" s="12">
-        <f>E84/I84-1</f>
+        <f t="shared" si="2"/>
         <v>0.71641791044776149</v>
       </c>
       <c r="K84" s="11">
@@ -6314,7 +6347,7 @@
         <v>24.85</v>
       </c>
       <c r="J85" s="12">
-        <f>E85/I85-1</f>
+        <f t="shared" si="2"/>
         <v>0.21126760563380276</v>
       </c>
       <c r="K85" s="11">
@@ -6368,7 +6401,7 @@
         <v>32.65</v>
       </c>
       <c r="J86" s="12">
-        <f>E86/I86-1</f>
+        <f t="shared" si="2"/>
         <v>0.45022970903522208</v>
       </c>
       <c r="K86" s="11">
@@ -6422,7 +6455,7 @@
         <v>1.72</v>
       </c>
       <c r="J87" s="12">
-        <f>E87/I87-1</f>
+        <f t="shared" si="2"/>
         <v>0.15697674418604657</v>
       </c>
       <c r="K87" s="11">
@@ -6476,7 +6509,7 @@
         <v>16.02</v>
       </c>
       <c r="J88" s="12">
-        <f>E88/I88-1</f>
+        <f t="shared" si="2"/>
         <v>0.17727840199750311</v>
       </c>
       <c r="K88" s="11">
@@ -6530,7 +6563,7 @@
         <v>5.6</v>
       </c>
       <c r="J89" s="12">
-        <f>E89/I89-1</f>
+        <f t="shared" si="2"/>
         <v>0.58928571428571441</v>
       </c>
       <c r="K89" s="11">
@@ -6584,7 +6617,7 @@
         <v>37.85</v>
       </c>
       <c r="J90" s="12">
-        <f>E90/I90-1</f>
+        <f t="shared" si="2"/>
         <v>0.41479524438573301</v>
       </c>
       <c r="K90" s="11">
@@ -6638,7 +6671,7 @@
         <v>5</v>
       </c>
       <c r="J91" s="12">
-        <f>E91/I91-1</f>
+        <f t="shared" si="2"/>
         <v>0.41999999999999993</v>
       </c>
       <c r="K91" s="11">
@@ -6692,7 +6725,7 @@
         <v>5.19</v>
       </c>
       <c r="J92" s="12">
-        <f>E92/I92-1</f>
+        <f t="shared" si="2"/>
         <v>0.56069364161849689</v>
       </c>
       <c r="K92" s="11">
@@ -6746,7 +6779,7 @@
         <v>8.66</v>
       </c>
       <c r="J93" s="12">
-        <f>E93/I93-1</f>
+        <f t="shared" si="2"/>
         <v>0.2979214780600461</v>
       </c>
       <c r="K93" s="11">
@@ -6800,7 +6833,7 @@
         <v>1.18</v>
       </c>
       <c r="J94" s="12">
-        <f>E94/I94-1</f>
+        <f t="shared" si="2"/>
         <v>0.2881355932203391</v>
       </c>
       <c r="K94" s="11">
@@ -6854,7 +6887,7 @@
         <v>5.6</v>
       </c>
       <c r="J95" s="12">
-        <f>E95/I95-1</f>
+        <f t="shared" si="2"/>
         <v>0.54821428571428577</v>
       </c>
       <c r="K95" s="11">
@@ -6908,7 +6941,7 @@
         <v>4.08</v>
       </c>
       <c r="J96" s="12">
-        <f>E96/I96-1</f>
+        <f t="shared" si="2"/>
         <v>0.37254901960784292</v>
       </c>
       <c r="K96" s="11">
@@ -6962,7 +6995,7 @@
         <v>5.88</v>
       </c>
       <c r="J97" s="12">
-        <f>E97/I97-1</f>
+        <f t="shared" si="2"/>
         <v>0.56462585034013602</v>
       </c>
       <c r="K97" s="11">
@@ -7016,7 +7049,7 @@
         <v>5.44</v>
       </c>
       <c r="J98" s="12">
-        <f>E98/I98-1</f>
+        <f t="shared" ref="J98:J118" si="3">E98/I98-1</f>
         <v>0.72610294117647056</v>
       </c>
       <c r="K98" s="11">
@@ -7070,7 +7103,7 @@
         <v>28.1</v>
       </c>
       <c r="J99" s="12">
-        <f>E99/I99-1</f>
+        <f t="shared" si="3"/>
         <v>0.17259786476868322</v>
       </c>
       <c r="K99" s="11">
@@ -7124,7 +7157,7 @@
         <v>36.15</v>
       </c>
       <c r="J100" s="12">
-        <f>E100/I100-1</f>
+        <f t="shared" si="3"/>
         <v>0.31120331950207469</v>
       </c>
       <c r="K100" s="11">
@@ -7178,7 +7211,7 @@
         <v>4.22</v>
       </c>
       <c r="J101" s="12">
-        <f>E101/I101-1</f>
+        <f t="shared" si="3"/>
         <v>0.27014218009478697</v>
       </c>
       <c r="K101" s="11">
@@ -7232,7 +7265,7 @@
         <v>1.37</v>
       </c>
       <c r="J102" s="12">
-        <f>E102/I102-1</f>
+        <f t="shared" si="3"/>
         <v>0.25547445255474432</v>
       </c>
       <c r="K102" s="11">
@@ -7286,7 +7319,7 @@
         <v>3.8</v>
       </c>
       <c r="J103" s="12">
-        <f>E103/I103-1</f>
+        <f t="shared" si="3"/>
         <v>0.35526315789473695</v>
       </c>
       <c r="K103" s="11">
@@ -7340,7 +7373,7 @@
         <v>0.81</v>
       </c>
       <c r="J104" s="12">
-        <f>E104/I104-1</f>
+        <f t="shared" si="3"/>
         <v>0.59259259259259256</v>
       </c>
       <c r="K104" s="11">
@@ -7394,7 +7427,7 @@
         <v>14.52</v>
       </c>
       <c r="J105" s="12">
-        <f>E105/I105-1</f>
+        <f t="shared" si="3"/>
         <v>0.60812672176308546</v>
       </c>
       <c r="K105" s="11">
@@ -7448,7 +7481,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J106" s="12">
-        <f>E106/I106-1</f>
+        <f t="shared" si="3"/>
         <v>0.70646766169154263</v>
       </c>
       <c r="K106" s="11">
@@ -7502,7 +7535,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="J107" s="12">
-        <f>E107/I107-1</f>
+        <f t="shared" si="3"/>
         <v>0.23478260869565215</v>
       </c>
       <c r="K107" s="11">
@@ -7556,7 +7589,7 @@
         <v>1.93</v>
       </c>
       <c r="J108" s="12">
-        <f>E108/I108-1</f>
+        <f t="shared" si="3"/>
         <v>0.1295336787564767</v>
       </c>
       <c r="K108" s="11">
@@ -7610,7 +7643,7 @@
         <v>4.47</v>
       </c>
       <c r="J109" s="12">
-        <f>E109/I109-1</f>
+        <f t="shared" si="3"/>
         <v>1.0894854586129754</v>
       </c>
       <c r="K109" s="11">
@@ -7664,7 +7697,7 @@
         <v>10.36</v>
       </c>
       <c r="J110" s="12">
-        <f>E110/I110-1</f>
+        <f t="shared" si="3"/>
         <v>0.31274131274131278</v>
       </c>
       <c r="K110" s="11">
@@ -7718,7 +7751,7 @@
         <v>15.24</v>
       </c>
       <c r="J111" s="12">
-        <f>E111/I111-1</f>
+        <f t="shared" si="3"/>
         <v>1.5918635170603674</v>
       </c>
       <c r="K111" s="11">
@@ -7772,7 +7805,7 @@
         <v>22.4</v>
       </c>
       <c r="J112" s="12">
-        <f>E112/I112-1</f>
+        <f t="shared" si="3"/>
         <v>0.29687500000000022</v>
       </c>
       <c r="K112" s="11">
@@ -7826,7 +7859,7 @@
         <v>21.5</v>
       </c>
       <c r="J113" s="12">
-        <f>E113/I113-1</f>
+        <f t="shared" si="3"/>
         <v>0.64651162790697669</v>
       </c>
       <c r="K113" s="11">
@@ -7868,7 +7901,7 @@
         <v>5.08</v>
       </c>
       <c r="J114" s="12">
-        <f>E114/I114-1</f>
+        <f t="shared" si="3"/>
         <v>0.43700787401574792</v>
       </c>
       <c r="K114" s="11">
@@ -7910,7 +7943,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="J115" s="12">
-        <f>E115/I115-1</f>
+        <f t="shared" si="3"/>
         <v>0.52709359605911343</v>
       </c>
       <c r="K115" s="11">
@@ -7952,7 +7985,7 @@
         <v>3.89</v>
       </c>
       <c r="J116" s="12">
-        <f>E116/I116-1</f>
+        <f t="shared" si="3"/>
         <v>0.40359897172236492</v>
       </c>
       <c r="K116" s="11">
@@ -7994,7 +8027,7 @@
         <v>5.23</v>
       </c>
       <c r="J117" s="12">
-        <f>E117/I117-1</f>
+        <f t="shared" si="3"/>
         <v>0.47801147227533458</v>
       </c>
       <c r="K117" s="11">
@@ -8036,7 +8069,7 @@
         <v>4.26</v>
       </c>
       <c r="J118" s="12">
-        <f>E118/I118-1</f>
+        <f t="shared" si="3"/>
         <v>0.83568075117370899</v>
       </c>
       <c r="K118" s="11">
@@ -8152,41 +8185,41 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>378</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>379</v>
       </c>
       <c r="E2">
-        <v>125.09</v>
+        <v>14.67</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="7">
-        <v>485550587904</v>
+        <v>8456624640</v>
       </c>
       <c r="H2" s="6">
-        <v>178.76</v>
+        <v>22.97</v>
       </c>
       <c r="I2" s="6">
-        <v>106.33</v>
+        <v>14.63</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J11" si="0">E2/I2-1</f>
-        <v>0.17643186306780789</v>
+        <f>E2/I2-1</f>
+        <v>2.7341079972658111E-3</v>
       </c>
       <c r="K2" s="11">
-        <v>4.5926932608521862E-2</v>
+        <v>7.2256305385139746E-2</v>
       </c>
       <c r="L2" s="13">
-        <v>44203762134.690002</v>
+        <v>1115194928.8599999</v>
       </c>
       <c r="M2" s="13">
-        <v>133285282015.97</v>
+        <v>4734235892.8000002</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>51</v>
@@ -8195,10 +8228,10 @@
         <v>1</v>
       </c>
       <c r="P2" s="12">
-        <v>0.12314594309994076</v>
+        <v>0.15876583501828892</v>
       </c>
       <c r="Q2" s="12">
-        <v>0.33164773684009302</v>
+        <v>0.23555964555041065</v>
       </c>
       <c r="R2" s="14">
         <v>1</v>
@@ -8206,41 +8239,41 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E3">
-        <v>8.68</v>
+        <v>119.56</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="7">
-        <v>14978208768</v>
+        <v>464085286912</v>
       </c>
       <c r="H3" s="6">
-        <v>9.76</v>
+        <v>178.76</v>
       </c>
       <c r="I3" s="6">
-        <v>7.06</v>
+        <v>106.33</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>0.22946175637393762</v>
+        <f>E3/I3-1</f>
+        <v>0.12442396313364057</v>
       </c>
       <c r="K3" s="11">
-        <v>0</v>
+        <v>4.8051187688190028E-2</v>
       </c>
       <c r="L3" s="13">
-        <v>1541495041.8099999</v>
+        <v>44203762134.690002</v>
       </c>
       <c r="M3" s="13">
-        <v>11970268017.99</v>
+        <v>133285282015.97</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>51</v>
@@ -8249,52 +8282,52 @@
         <v>1</v>
       </c>
       <c r="P3" s="12">
-        <v>0.19160856410336488</v>
+        <v>0.13097839090027466</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.1287769864044232</v>
+        <v>0.33164773684009302</v>
       </c>
       <c r="R3" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>13.16</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G4" s="7">
-        <v>13465312256</v>
+        <v>15132065792</v>
       </c>
       <c r="H4" s="6">
-        <v>13.58</v>
+        <v>9.76</v>
       </c>
       <c r="I4" s="6">
-        <v>9.18</v>
+        <v>7.06</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.43355119825708077</v>
+        <f>E4/I4-1</f>
+        <v>0.24362606232294626</v>
       </c>
       <c r="K4" s="11">
-        <v>4.5592705167173252E-2</v>
+        <v>5.1252847380410027E-2</v>
       </c>
       <c r="L4" s="13">
-        <v>1324661161.8800001</v>
+        <v>1541495041.8099999</v>
       </c>
       <c r="M4" s="13">
-        <v>11491269147.950001</v>
+        <v>11970268017.99</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>51</v>
@@ -8303,52 +8336,52 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>0.15914534730349833</v>
+        <v>0.18801291100167322</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.11527544475940803</v>
+        <v>0.1287769864044232</v>
       </c>
       <c r="R4" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>243</v>
       </c>
       <c r="E5">
-        <v>13.84</v>
+        <v>54.82</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G5" s="7">
-        <v>24856639488</v>
+        <v>26531291136</v>
       </c>
       <c r="H5" s="6">
-        <v>15.58</v>
+        <v>77</v>
       </c>
       <c r="I5" s="6">
-        <v>11.47</v>
+        <v>50.85</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.20662598081952921</v>
+        <f>E5/I5-1</f>
+        <v>7.807276302851518E-2</v>
       </c>
       <c r="K5" s="11">
-        <v>3.9739884393063585E-2</v>
+        <v>4.3779642466253189E-2</v>
       </c>
       <c r="L5" s="13">
-        <v>1789808265.4000001</v>
+        <v>2927600473.4699998</v>
       </c>
       <c r="M5" s="13">
-        <v>15580673812.24</v>
+        <v>1185220264.01</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>51</v>
@@ -8357,10 +8390,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="12">
-        <v>0.14373303315463123</v>
+        <v>0.11426165027253582</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.11487361117809598</v>
+        <v>2.4700897903693781</v>
       </c>
       <c r="R5" s="14">
         <v>3</v>
@@ -8368,41 +8401,41 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6">
-        <v>105.42</v>
+        <v>12.78</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G6" s="7">
-        <v>56034734080</v>
+        <v>13076495360</v>
       </c>
       <c r="H6" s="6">
-        <v>121.53</v>
+        <v>13.65</v>
       </c>
       <c r="I6" s="6">
-        <v>50.21</v>
+        <v>9.18</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>1.0995817566221868</v>
+        <f>E6/I6-1</f>
+        <v>0.39215686274509798</v>
       </c>
       <c r="K6" s="11">
-        <v>1.9920318725099601E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="L6" s="13">
-        <v>2351242906.4000001</v>
+        <v>1324661161.8800001</v>
       </c>
       <c r="M6" s="13">
-        <v>10336332783.18</v>
+        <v>11491269147.950001</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>51</v>
@@ -8411,10 +8444,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>4.264214464208986E-2</v>
+        <v>0.16694372699931267</v>
       </c>
       <c r="Q6" s="12">
-        <v>0.22747360748931247</v>
+        <v>0.11527544475940803</v>
       </c>
       <c r="R6" s="14">
         <v>4</v>
@@ -8422,41 +8455,41 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>383</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>222.7</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G7" s="7">
-        <v>41166761984</v>
+        <v>99320250368</v>
       </c>
       <c r="H7" s="6">
-        <v>333.5</v>
+        <v>109</v>
       </c>
       <c r="I7" s="6">
-        <v>173</v>
+        <v>63.17</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0.28728323699421954</v>
+        <f>E7/I7-1</f>
+        <v>4.3691625771727249E-2</v>
       </c>
       <c r="K7" s="11">
-        <v>4.8046699595868884E-3</v>
+        <v>7.0483846503867728E-2</v>
       </c>
       <c r="L7" s="13">
-        <v>2107869808</v>
+        <v>9146031692.1700001</v>
       </c>
       <c r="M7" s="13">
-        <v>12869225664</v>
+        <v>51588243128.650002</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>51</v>
@@ -8465,52 +8498,52 @@
         <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>5.2828479318259083E-2</v>
+        <v>0.1178070730450875</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.16379150253744434</v>
+        <v>0.1772890708714728</v>
       </c>
       <c r="R7" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>385</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>9.74</v>
+        <v>21.5</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G8" s="7">
-        <v>11820951552</v>
+        <v>10875882496</v>
       </c>
       <c r="H8" s="6">
-        <v>10.27</v>
+        <v>36.86</v>
       </c>
       <c r="I8" s="6">
-        <v>7.54</v>
+        <v>21.48</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.29177718832891242</v>
+        <f>E8/I8-1</f>
+        <v>9.3109869646190724E-4</v>
       </c>
       <c r="K8" s="11">
-        <v>4.1067761806981518E-2</v>
+        <v>6.0465116279069767E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>1074859531.29</v>
+        <v>1139111857.1300001</v>
       </c>
       <c r="M8" s="13">
-        <v>9527311896.5100002</v>
+        <v>7932700024.4300003</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>51</v>
@@ -8519,52 +8552,52 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.10578965566101749</v>
+        <v>0.13239740807001091</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.1128187617835559</v>
+        <v>0.14359699139283291</v>
       </c>
       <c r="R8" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E9">
-        <v>13.02</v>
+        <v>13.53</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="7">
-        <v>4602869760</v>
+        <v>24299880448</v>
       </c>
       <c r="H9" s="6">
-        <v>14.68</v>
+        <v>15.58</v>
       </c>
       <c r="I9" s="6">
-        <v>9.73</v>
+        <v>11.47</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>0.33812949640287759</v>
+        <f>E9/I9-1</f>
+        <v>0.17959895379250201</v>
       </c>
       <c r="K9" s="11">
-        <v>3.6866359447004608E-2</v>
+        <v>4.0650406504065047E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>339663210.94999999</v>
+        <v>1789808265.4000001</v>
       </c>
       <c r="M9" s="13">
-        <v>2751572515.0799999</v>
+        <v>15580673812.24</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>51</v>
@@ -8573,52 +8606,52 @@
         <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>9.2294210563736004E-2</v>
+        <v>0.15046031016706551</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.12344330708657501</v>
+        <v>0.11487361117809598</v>
       </c>
       <c r="R9" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>381</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E10">
-        <v>8.26</v>
+        <v>42.71</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="7">
-        <v>18355537920</v>
+        <v>21626122240</v>
       </c>
       <c r="H10" s="6">
-        <v>10.53</v>
+        <v>71.2</v>
       </c>
       <c r="I10" s="6">
-        <v>7.15</v>
+        <v>39.03</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.15524475524475512</v>
+        <f>E10/I10-1</f>
+        <v>9.4286446323341044E-2</v>
       </c>
       <c r="K10" s="11">
-        <v>3.6319612590799029E-2</v>
+        <v>2.3413720440177945E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>1357643494.6700001</v>
+        <v>1949016683.5799999</v>
       </c>
       <c r="M10" s="13">
-        <v>13696300546.360001</v>
+        <v>10523421872.709999</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>51</v>
@@ -8627,52 +8660,52 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.10979074265151259</v>
+        <v>0.11045980042056196</v>
       </c>
       <c r="Q10" s="12">
-        <v>9.9124832291360196E-2</v>
+        <v>0.18520750257426369</v>
       </c>
       <c r="R10" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>384</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E11">
-        <v>53.03</v>
+        <v>10.08</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="7">
-        <v>30507945984</v>
+        <v>14061801472</v>
       </c>
       <c r="H11" s="6">
-        <v>68.39</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="I11" s="6">
-        <v>36.25</v>
+        <v>10.08</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46289655172413791</v>
+        <f>E11/I11-1</f>
+        <v>0</v>
       </c>
       <c r="K11" s="11">
-        <v>8.4857627757872894E-3</v>
+        <v>3.9682539682539687E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>939613185.05999994</v>
+        <v>1310024443.6900001</v>
       </c>
       <c r="M11" s="13">
-        <v>9067794807.8099995</v>
+        <v>19473263524.830002</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>51</v>
@@ -8681,69 +8714,547 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>3.4295239856469741E-2</v>
+        <v>0.20965076363001239</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.10362091390188061</v>
+        <v>6.7272978770076819E-2</v>
       </c>
       <c r="R11" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>358</v>
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>107.68</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="7">
+        <v>57236008960</v>
+      </c>
+      <c r="H12" s="6">
+        <v>121.53</v>
+      </c>
+      <c r="I12" s="6">
+        <v>50.21</v>
+      </c>
+      <c r="J12" s="12">
+        <f>E12/I12-1</f>
+        <v>1.1445927106154152</v>
+      </c>
+      <c r="K12" s="11">
+        <v>1.950222882615156E-2</v>
+      </c>
+      <c r="L12" s="13">
+        <v>2351242906.4000001</v>
+      </c>
+      <c r="M12" s="13">
+        <v>10336332783.18</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O12" s="6">
+        <v>1</v>
+      </c>
+      <c r="P12" s="12">
+        <v>4.1732937392270866E-2</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0.22747360748931247</v>
+      </c>
+      <c r="R12" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
+      </c>
+      <c r="C13" t="s">
+        <v>382</v>
+      </c>
+      <c r="D13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13">
+        <v>5.48</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="7">
+        <v>24229054464</v>
+      </c>
+      <c r="H13" s="6">
+        <v>6.4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="J13" s="12">
+        <f>E13/I13-1</f>
+        <v>0.15368421052631587</v>
+      </c>
+      <c r="K13" s="11">
+        <v>3.6678832116788324E-2</v>
+      </c>
+      <c r="L13" s="13">
+        <v>2697498300</v>
+      </c>
+      <c r="M13" s="13">
+        <v>26396524300</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0.13909048640312721</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0.10219141995145171</v>
+      </c>
+      <c r="R13" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
+      </c>
+      <c r="C14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14">
+        <v>21.78</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="7">
+        <v>21938558976</v>
+      </c>
+      <c r="H14" s="6">
+        <v>30.34</v>
+      </c>
+      <c r="I14" s="6">
+        <v>20.53</v>
+      </c>
+      <c r="J14" s="12">
+        <f>E14/I14-1</f>
+        <v>6.0886507549926971E-2</v>
+      </c>
+      <c r="K14" s="11">
+        <v>5.0505050505050504E-2</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1686709166</v>
+      </c>
+      <c r="M14" s="13">
+        <v>10738080107</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="6">
+        <v>1</v>
+      </c>
+      <c r="P14" s="12">
+        <v>8.8418515522175958E-2</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>0.15707734987937541</v>
+      </c>
+      <c r="R14" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>361</v>
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>208.54</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="7">
+        <v>38549241856</v>
+      </c>
+      <c r="H15" s="6">
+        <v>333.5</v>
+      </c>
+      <c r="I15" s="6">
+        <v>173</v>
+      </c>
+      <c r="J15" s="12">
+        <f>E15/I15-1</f>
+        <v>0.20543352601156073</v>
+      </c>
+      <c r="K15" s="11">
+        <v>5.130910137143954E-3</v>
+      </c>
+      <c r="L15" s="13">
+        <v>2107869808</v>
+      </c>
+      <c r="M15" s="13">
+        <v>12869225664</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O15" s="6">
+        <v>1</v>
+      </c>
+      <c r="P15" s="12">
+        <v>5.6537424157839612E-2</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0.16379150253744434</v>
+      </c>
+      <c r="R15" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.5">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16">
+        <v>12.18</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="7">
+        <v>4305910272</v>
+      </c>
+      <c r="H16" s="6">
+        <v>14.68</v>
+      </c>
+      <c r="I16" s="6">
+        <v>9.73</v>
+      </c>
+      <c r="J16" s="12">
+        <f>E16/I16-1</f>
+        <v>0.25179856115107913</v>
+      </c>
+      <c r="K16" s="11">
+        <v>3.9408866995073892E-2</v>
+      </c>
+      <c r="L16" s="13">
+        <v>339663210.94999999</v>
+      </c>
+      <c r="M16" s="13">
+        <v>2751572515.0799999</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O16" s="6">
+        <v>1</v>
+      </c>
+      <c r="P16" s="12">
+        <v>0.10039516018508211</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>0.12344330708657501</v>
+      </c>
+      <c r="R16" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.5">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="7">
+        <v>11165580288</v>
+      </c>
+      <c r="H17" s="6">
+        <v>10.27</v>
+      </c>
+      <c r="I17" s="6">
+        <v>7.54</v>
+      </c>
+      <c r="J17" s="12">
+        <f>E17/I17-1</f>
+        <v>0.22015915119363383</v>
+      </c>
+      <c r="K17" s="11">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="L17" s="13">
+        <v>1074859531.29</v>
+      </c>
+      <c r="M17" s="13">
+        <v>9527311896.5100002</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O17" s="6">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12">
+        <v>0.11308388846473458</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>0.1128187617835559</v>
+      </c>
+      <c r="R17" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.5">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18">
+        <v>7.76</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="7">
+        <v>17244428288</v>
+      </c>
+      <c r="H18" s="6">
+        <v>10.53</v>
+      </c>
+      <c r="I18" s="6">
+        <v>7.15</v>
+      </c>
+      <c r="J18" s="12">
+        <f>E18/I18-1</f>
+        <v>8.5314685314685335E-2</v>
+      </c>
+      <c r="K18" s="11">
+        <v>3.8659793814432991E-2</v>
+      </c>
+      <c r="L18" s="13">
+        <v>1357643494.6700001</v>
+      </c>
+      <c r="M18" s="13">
+        <v>13696300546.360001</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O18" s="6">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12">
+        <v>0.12062979961304117</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>9.9124832291360196E-2</v>
+      </c>
+      <c r="R18" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>53.88</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="7">
+        <v>30996948992</v>
+      </c>
+      <c r="H19" s="6">
+        <v>68.39</v>
+      </c>
+      <c r="I19" s="6">
+        <v>36.25</v>
+      </c>
+      <c r="J19" s="12">
+        <f>E19/I19-1</f>
+        <v>0.48634482758620701</v>
+      </c>
+      <c r="K19" s="11">
+        <v>8.3518930957683733E-3</v>
+      </c>
+      <c r="L19" s="13">
+        <v>939613185.05999994</v>
+      </c>
+      <c r="M19" s="13">
+        <v>9067794807.8099995</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O19" s="6">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12">
+        <v>3.3693862499442798E-2</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>0.10362091390188061</v>
+      </c>
+      <c r="R19" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B20" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20" t="s">
+        <v>388</v>
+      </c>
+      <c r="D20" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20">
+        <v>13.87</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="7">
+        <v>4048028928</v>
+      </c>
+      <c r="H20" s="6">
+        <v>18.78</v>
+      </c>
+      <c r="I20" s="6">
+        <v>11.7</v>
+      </c>
+      <c r="J20" s="12">
+        <f>E20/I20-1</f>
+        <v>0.18547008547008548</v>
+      </c>
+      <c r="K20" s="11">
+        <v>2.8839221341023794E-2</v>
+      </c>
+      <c r="L20" s="13">
+        <v>225008130.19999999</v>
+      </c>
+      <c r="M20" s="13">
+        <v>2512019918.8400002</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O20" s="6">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12">
+        <v>6.9519589342282306E-2</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>8.957258997528339E-2</v>
+      </c>
+      <c r="R20" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B21" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B20" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B21" s="1" t="s">
-        <v>367</v>
+      <c r="C21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D21" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21">
+        <v>23.16</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="7">
+        <v>490130440192</v>
+      </c>
+      <c r="H21" s="6">
+        <v>24.33</v>
+      </c>
+      <c r="I21" s="6">
+        <v>15.68</v>
+      </c>
+      <c r="J21" s="12">
+        <f>E21/I21-1</f>
+        <v>0.47704081632653073</v>
+      </c>
+      <c r="K21" s="11">
+        <v>4.5768566493955096E-2</v>
+      </c>
+      <c r="M21" s="13">
+        <v>2415915000000</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O21" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:R11" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R11">
-      <sortCondition ref="R1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R21">
+      <sortCondition ref="R1:R11"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J2:J1048576">

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50432CD5-27F5-4B6E-A850-E3A55DFA741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B49268-F178-42C7-A140-1CD4F26EF225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cn_screener!$B$1:$R$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">hk_screener!$B$1:$R$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">hk_screener!$B$1:$R$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">us_screener!$B$1:$R$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="391">
   <si>
     <t>Ticker</t>
   </si>
@@ -1266,6 +1266,12 @@
   </si>
   <si>
     <t>PUYANG HUICHENG EL</t>
+  </si>
+  <si>
+    <t>0308.HK</t>
+  </si>
+  <si>
+    <t>CHINA TRAVEL HK</t>
   </si>
 </sst>
 </file>
@@ -1841,41 +1847,41 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E2">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>8111938560</v>
+        <v>2631190016</v>
       </c>
       <c r="H2" s="6">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I2" s="6">
-        <v>2.36</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J2" s="12">
-        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.22881355932203395</v>
+        <f>E2/I2-1</f>
+        <v>0.2543103448275863</v>
       </c>
       <c r="K2" s="11">
-        <v>5.2758620689655172E-2</v>
+        <v>5.8075601374570449E-2</v>
       </c>
       <c r="L2" s="13">
-        <v>1871151000</v>
+        <v>504294000</v>
       </c>
       <c r="M2" s="13">
-        <v>6461978000</v>
+        <v>1704754000</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>51</v>
@@ -1884,10 +1890,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.51069152013549879</v>
+        <v>0.39215559566825331</v>
       </c>
       <c r="Q2" s="12">
-        <v>0.28956319566547578</v>
+        <v>0.29581628786323422</v>
       </c>
       <c r="R2" s="14">
         <v>1</v>
@@ -1895,41 +1901,41 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E3">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>2613106176</v>
+        <v>9035021312</v>
       </c>
       <c r="H3" s="6">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I3" s="6">
-        <v>2.3199999999999998</v>
+        <v>2.36</v>
       </c>
       <c r="J3" s="12">
-        <f t="shared" si="0"/>
-        <v>0.24568965517241392</v>
+        <f>E3/I3-1</f>
+        <v>0.3686440677966103</v>
       </c>
       <c r="K3" s="11">
-        <v>5.8477508650519032E-2</v>
+        <v>4.736842105263158E-2</v>
       </c>
       <c r="L3" s="13">
-        <v>504294000</v>
+        <v>1871151000</v>
       </c>
       <c r="M3" s="13">
-        <v>1704754000</v>
+        <v>6461978000</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>51</v>
@@ -1938,10 +1944,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.39738622480117308</v>
+        <v>0.4132436258782804</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.29581628786323422</v>
+        <v>0.28956319566547578</v>
       </c>
       <c r="R3" s="14">
         <v>2</v>
@@ -1958,13 +1964,13 @@
         <v>77</v>
       </c>
       <c r="E4">
-        <v>13.82</v>
+        <v>13.74</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>264646082560</v>
+        <v>250628603904</v>
       </c>
       <c r="H4" s="6">
         <v>15.1</v>
@@ -1973,11 +1979,11 @@
         <v>9.52</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.45168067226890773</v>
+        <f>E4/I4-1</f>
+        <v>0.44327731092436973</v>
       </c>
       <c r="K4" s="11">
-        <v>0.11215629522431259</v>
+        <v>0.11280931586608442</v>
       </c>
       <c r="L4" s="13">
         <v>70144988000</v>
@@ -1992,7 +1998,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.50196093519834883</v>
+        <v>0.55397346656738511</v>
       </c>
       <c r="Q4" s="12">
         <v>0.26042924055386191</v>
@@ -2012,26 +2018,26 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>6.95</v>
+        <v>7.49</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>27119177728</v>
+        <v>29226278912</v>
       </c>
       <c r="H5" s="6">
-        <v>7.26</v>
+        <v>7.8</v>
       </c>
       <c r="I5" s="6">
         <v>4.22</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>0.64691943127962093</v>
+        <f>E5/I5-1</f>
+        <v>0.7748815165876779</v>
       </c>
       <c r="K5" s="11">
-        <v>6.18705035971223E-3</v>
+        <v>5.7409879839786376E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2046,7 +2052,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.30797805365261161</v>
+        <v>0.2781525253536144</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
@@ -2066,13 +2072,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>133.4</v>
+        <v>136.6</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>88093753344</v>
+        <v>90206953472</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2081,11 +2087,11 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46593406593406606</v>
+        <f>E6/I6-1</f>
+        <v>0.50109890109890109</v>
       </c>
       <c r="K6" s="11">
-        <v>1.4617691154422787E-2</v>
+        <v>1.4275256222547585E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2100,7 +2106,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.53537855108079613</v>
+        <v>0.50707628883204281</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
@@ -2111,53 +2117,53 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>306</v>
       </c>
       <c r="E7">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>1660000000</v>
+        <v>377214009344</v>
       </c>
       <c r="H7" s="6">
-        <v>1.88</v>
+        <v>6.24</v>
       </c>
       <c r="I7" s="6">
-        <v>1.35</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0.22962962962962941</v>
+        <f>E7/I7-1</f>
+        <v>1.310756972111554</v>
       </c>
       <c r="K7" s="11">
-        <v>0.12650602409638553</v>
+        <v>3.1034482758620689E-2</v>
       </c>
       <c r="L7" s="13">
-        <v>315190000</v>
+        <v>72477000000</v>
       </c>
       <c r="M7" s="13">
-        <v>607806000</v>
+        <v>319355000000</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.17236278486287374</v>
+        <v>0.19034209571941735</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.51857007005524791</v>
+        <v>0.22694806719794586</v>
       </c>
       <c r="R7" s="14">
         <v>6</v>
@@ -2165,53 +2171,53 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="E8">
-        <v>2.61</v>
+        <v>1.39</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>13287692288</v>
+        <v>2799807488</v>
       </c>
       <c r="H8" s="6">
-        <v>3.3023729999999998</v>
+        <v>1.62</v>
       </c>
       <c r="I8" s="6">
-        <v>2.23</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>0.17040358744394624</v>
+        <f>E8/I8-1</f>
+        <v>0.23008849557522137</v>
       </c>
       <c r="K8" s="11">
-        <v>0.11494252873563218</v>
+        <v>8.5611510791366904E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>2527643000</v>
+        <v>929863000</v>
       </c>
       <c r="M8" s="13">
-        <v>16480074000</v>
+        <v>6026676000</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O8" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.44693614015450328</v>
+        <v>0.38347509842232841</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.15429118804462028</v>
       </c>
       <c r="R8" s="14">
         <v>7</v>
@@ -2219,41 +2225,41 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E9">
-        <v>1.35</v>
+        <v>15.68</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>2719237632</v>
+        <v>143679127552</v>
       </c>
       <c r="H9" s="6">
-        <v>1.62</v>
+        <v>17.88</v>
       </c>
       <c r="I9" s="6">
-        <v>1.1299999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>0.19469026548672574</v>
+        <f>E9/I9-1</f>
+        <v>0.47924528301886804</v>
       </c>
       <c r="K9" s="11">
-        <v>8.8148148148148142E-2</v>
+        <v>4.5854591836734696E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>929863000</v>
+        <v>21175963859.630001</v>
       </c>
       <c r="M9" s="13">
-        <v>6026676000</v>
+        <v>104071284594.97</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>51</v>
@@ -2262,106 +2268,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.39578416296319474</v>
+        <v>0.20042765776352378</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.15429118804462028</v>
+        <v>0.20347556909712136</v>
       </c>
       <c r="R9" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="E10">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>176142155776</v>
+        <v>14560459776</v>
       </c>
       <c r="H10" s="6">
-        <v>8.49</v>
+        <v>3.3023729999999998</v>
       </c>
       <c r="I10" s="6">
-        <v>4.58</v>
+        <v>2.23</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.50436681222707413</v>
+        <f>E10/I10-1</f>
+        <v>0.28251121076233177</v>
       </c>
       <c r="K10" s="11">
-        <v>3.7010159651669088E-2</v>
+        <v>0.1048951048951049</v>
       </c>
       <c r="L10" s="13">
-        <v>29168443138.220001</v>
+        <v>2527643000</v>
       </c>
       <c r="M10" s="13">
-        <v>100996030941.41</v>
+        <v>16480074000</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O10" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.17711118013417754</v>
+        <v>0.36483096930312597</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.2888078161719172</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R10" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>357</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="E11">
-        <v>4.5999999999999996</v>
+        <v>1.53</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>9511327744</v>
+        <v>1809683968</v>
       </c>
       <c r="H11" s="6">
-        <v>4.9800000000000004</v>
+        <v>2.77</v>
       </c>
       <c r="I11" s="6">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46031746031746024</v>
+        <f>E11/I11-1</f>
+        <v>0.125</v>
       </c>
       <c r="K11" s="11">
-        <v>5.4347826086956527E-2</v>
+        <v>3.9869281045751631E-2</v>
       </c>
       <c r="L11" s="13">
-        <v>1576240000</v>
+        <v>841215000</v>
       </c>
       <c r="M11" s="13">
-        <v>9636462000</v>
+        <v>5774434000</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>51</v>
@@ -2370,64 +2376,64 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P11" s="12">
-        <v>0.32083862795437695</v>
+        <v>0.62838192131451776</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.16357040581906512</v>
+        <v>0.14567921288909008</v>
       </c>
       <c r="R11" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="E12">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>1715060096</v>
+        <v>1910000000</v>
       </c>
       <c r="H12" s="6">
-        <v>2.77</v>
+        <v>1.94</v>
       </c>
       <c r="I12" s="6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
-        <v>6.6176470588235281E-2</v>
+        <f>E12/I12-1</f>
+        <v>0.41481481481481475</v>
       </c>
       <c r="K12" s="11">
-        <v>4.2068965517241382E-2</v>
+        <v>0.1099476439790576</v>
       </c>
       <c r="L12" s="13">
-        <v>841215000</v>
+        <v>315190000</v>
       </c>
       <c r="M12" s="13">
-        <v>5774434000</v>
+        <v>607806000</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O12" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P12" s="12">
-        <v>0.67290080717211942</v>
+        <v>0.1516325795242377</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.14567921288909008</v>
+        <v>0.51857007005524791</v>
       </c>
       <c r="R12" s="14">
         <v>10</v>
@@ -2435,41 +2441,41 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s">
-        <v>306</v>
+        <v>96</v>
       </c>
       <c r="E13">
-        <v>5.72</v>
+        <v>5.03</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>385840873472</v>
+        <v>10400431104</v>
       </c>
       <c r="H13" s="6">
-        <v>5.87</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I13" s="6">
-        <v>2.5099999999999998</v>
+        <v>3.15</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
-        <v>1.2788844621513946</v>
+        <f>E13/I13-1</f>
+        <v>0.59682539682539693</v>
       </c>
       <c r="K13" s="11">
-        <v>3.1468531468531472E-2</v>
+        <v>4.9701789264413515E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>72477000000</v>
+        <v>1576240000</v>
       </c>
       <c r="M13" s="13">
-        <v>319355000000</v>
+        <v>9636462000</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>51</v>
@@ -2478,10 +2484,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.18638947778842715</v>
+        <v>0.27436366960519337</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.22694806719794586</v>
+        <v>0.16357040581906512</v>
       </c>
       <c r="R13" s="14">
         <v>11</v>
@@ -2489,41 +2495,41 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="D14" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="E14">
-        <v>16.440000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>147296157696</v>
+        <v>199459127296</v>
       </c>
       <c r="H14" s="6">
-        <v>17.88</v>
+        <v>8.49</v>
       </c>
       <c r="I14" s="6">
-        <v>10.6</v>
+        <v>4.58</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="0"/>
-        <v>0.55094339622641519</v>
+        <f>E14/I14-1</f>
+        <v>0.81441048034934505</v>
       </c>
       <c r="K14" s="11">
-        <v>4.373479318734793E-2</v>
+        <v>3.0685920577617327E-2</v>
       </c>
       <c r="L14" s="13">
-        <v>21175963859.630001</v>
+        <v>29168443138.220001</v>
       </c>
       <c r="M14" s="13">
-        <v>104071284594.97</v>
+        <v>100996030941.41</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>51</v>
@@ -2532,10 +2538,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.19420462608297778</v>
+        <v>0.15638683109549151</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.20347556909712136</v>
+        <v>0.2888078161719172</v>
       </c>
       <c r="R14" s="14">
         <v>12</v>
@@ -2543,41 +2549,41 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E15">
-        <v>5.93</v>
+        <v>14.66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>7385340416</v>
+        <v>31433093120</v>
       </c>
       <c r="H15" s="6">
-        <v>8.6</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I15" s="6">
-        <v>3.46</v>
+        <v>7.96</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="0"/>
-        <v>0.71387283236994215</v>
+        <f>E15/I15-1</f>
+        <v>0.84170854271356776</v>
       </c>
       <c r="K15" s="11">
-        <v>2.3777403035413151E-2</v>
+        <v>7.6398362892223751E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>921702000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M15" s="13">
-        <v>5262544000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>51</v>
@@ -2586,13 +2592,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.19980426597563555</v>
+        <v>0.1669031163285318</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R15" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2606,13 +2612,13 @@
         <v>308</v>
       </c>
       <c r="E16">
-        <v>14.14</v>
+        <v>15.08</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>50819444736</v>
+        <v>54197821440</v>
       </c>
       <c r="H16" s="6">
         <v>16.600000000000001</v>
@@ -2621,11 +2627,11 @@
         <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="0"/>
-        <v>0.87284768211920549</v>
+        <f>E16/I16-1</f>
+        <v>0.99735099337748356</v>
       </c>
       <c r="K16" s="11">
-        <v>2.475247524752475E-2</v>
+        <v>2.3209549071618034E-2</v>
       </c>
       <c r="L16" s="13">
         <v>25585077000</v>
@@ -2640,322 +2646,322 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.28891927157188818</v>
+        <v>0.27830197037689341</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>87</v>
       </c>
       <c r="E17">
-        <v>7.34</v>
+        <v>7.67</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>7248499712</v>
+        <v>98407636992</v>
       </c>
       <c r="H17" s="6">
-        <v>9.07</v>
+        <v>7.8</v>
       </c>
       <c r="I17" s="6">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46799999999999997</v>
+        <f>E17/I17-1</f>
+        <v>0.584710743801653</v>
       </c>
       <c r="K17" s="11">
-        <v>4.8228882833787463E-2</v>
+        <v>8.344198174706649E-3</v>
       </c>
       <c r="L17" s="13">
-        <v>1333116000</v>
+        <v>2553000000</v>
       </c>
       <c r="M17" s="13">
-        <v>8019803000</v>
+        <v>13971000000</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O17" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P17" s="12">
-        <v>0.2014766292813687</v>
+        <v>0.17653168783338599</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.16622802330680692</v>
+        <v>0.18273566673824351</v>
       </c>
       <c r="R17" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E18">
-        <v>15.78</v>
+        <v>2.52</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>32412909568</v>
+        <v>2620321024</v>
       </c>
       <c r="H18" s="6">
-        <v>17.059999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="I18" s="6">
-        <v>7.96</v>
+        <v>1.92</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="0"/>
-        <v>0.98241206030150741</v>
+        <f>E18/I18-1</f>
+        <v>0.3125</v>
       </c>
       <c r="K18" s="11">
-        <v>7.0975918884664146E-2</v>
+        <v>0.11587301587301586</v>
       </c>
       <c r="L18" s="13">
-        <v>5451928473.2399998</v>
+        <v>762183000</v>
       </c>
       <c r="M18" s="13">
-        <v>25994816572.18</v>
+        <v>5008319000</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O18" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P18" s="12">
-        <v>0.16234511859062811</v>
+        <v>0.22647888920190015</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.15218339726363278</v>
       </c>
       <c r="R18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E19">
-        <v>2.29</v>
+        <v>14.42</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>2381164800</v>
+        <v>12001593344</v>
       </c>
       <c r="H19" s="6">
-        <v>3.34</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I19" s="6">
-        <v>1.92</v>
+        <v>12.12</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" si="0"/>
-        <v>0.19270833333333348</v>
+        <f>E19/I19-1</f>
+        <v>0.18976897689768979</v>
       </c>
       <c r="K19" s="11">
-        <v>0.12751091703056769</v>
+        <v>1.0263522884882107E-2</v>
       </c>
       <c r="L19" s="13">
-        <v>762183000</v>
+        <v>199557000</v>
       </c>
       <c r="M19" s="13">
-        <v>5008319000</v>
+        <v>1108087000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O19" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P19" s="12">
-        <v>0.24380464255081513</v>
+        <v>0.17373054172349067</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.15218339726363278</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E20">
-        <v>15.78</v>
+        <v>25.2</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>32412909568</v>
+        <v>66859130880</v>
       </c>
       <c r="H20" s="6">
-        <v>17.059999999999999</v>
+        <v>26.15</v>
       </c>
       <c r="I20" s="6">
-        <v>7.96</v>
+        <v>15.7</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="0"/>
-        <v>0.98241206030150741</v>
+        <f>E20/I20-1</f>
+        <v>0.60509554140127397</v>
       </c>
       <c r="K20" s="11">
-        <v>7.0975918884664146E-2</v>
+        <v>1.0793650793650795E-2</v>
       </c>
       <c r="L20" s="13">
-        <v>5451928473.2399998</v>
+        <v>1069250000</v>
       </c>
       <c r="M20" s="13">
-        <v>25994816572.18</v>
+        <v>2571093000</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O20" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P20" s="12">
-        <v>0.16234511859062811</v>
+        <v>0.12826873829061827</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.41587371596437778</v>
       </c>
       <c r="R20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>293</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E21">
-        <v>7.32</v>
+        <v>7.78</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>93917061120</v>
+        <v>67367022592</v>
       </c>
       <c r="H21" s="6">
-        <v>7.75</v>
+        <v>9.23</v>
       </c>
       <c r="I21" s="6">
-        <v>4.84</v>
+        <v>7.08</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="0"/>
-        <v>0.5123966942148761</v>
+        <f>E21/I21-1</f>
+        <v>9.8870056497175174E-2</v>
       </c>
       <c r="K21" s="11">
-        <v>8.7431693989071038E-3</v>
+        <v>4.0616966580976861E-2</v>
       </c>
       <c r="L21" s="13">
-        <v>2553000000</v>
+        <v>13438000000</v>
       </c>
       <c r="M21" s="13">
-        <v>13971000000</v>
+        <v>88611000000</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O21" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>0.18395733587750812</v>
+        <v>0.22582014897181107</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.18273566673824351</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R21" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>297</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E22">
-        <v>0.76</v>
+        <v>6.56</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>1663267584</v>
+        <v>8169955328</v>
       </c>
       <c r="H22" s="6">
-        <v>0.82</v>
+        <v>8.6</v>
       </c>
       <c r="I22" s="6">
-        <v>0.42</v>
+        <v>3.46</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="0"/>
-        <v>0.80952380952380953</v>
+        <f>E22/I22-1</f>
+        <v>0.89595375722543347</v>
       </c>
       <c r="K22" s="11">
-        <v>4.8684210526315788E-2</v>
+        <v>2.1493902439024389E-2</v>
       </c>
       <c r="L22" s="13">
-        <v>219938000</v>
+        <v>921702000</v>
       </c>
       <c r="M22" s="13">
-        <v>1520292000</v>
+        <v>5262544000</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>51</v>
@@ -2964,64 +2970,64 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P22" s="12">
-        <v>0.29986224591557764</v>
+        <v>0.1723637339710864</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.14466826109721026</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R22" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>297</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>355</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E23">
-        <v>13.92</v>
+        <v>0.79</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>11585448960</v>
+        <v>1728922880</v>
       </c>
       <c r="H23" s="6">
-        <v>19.440000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I23" s="6">
-        <v>12.12</v>
+        <v>0.42</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="0"/>
-        <v>0.14851485148514865</v>
+        <f>E23/I23-1</f>
+        <v>0.88095238095238115</v>
       </c>
       <c r="K23" s="11">
-        <v>1.0632183908045977E-2</v>
+        <v>4.6835443037974676E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>199557000</v>
+        <v>219938000</v>
       </c>
       <c r="M23" s="13">
-        <v>1108087000</v>
+        <v>1520292000</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O23" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.18231720125702217</v>
+        <v>0.27668052261777509</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.14466826109721026</v>
       </c>
       <c r="R23" s="14">
         <v>18</v>
@@ -3029,41 +3035,41 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E24">
-        <v>7.76</v>
+        <v>9.07</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>67193843712</v>
+        <v>147125370880</v>
       </c>
       <c r="H24" s="6">
-        <v>9.23</v>
+        <v>10.76</v>
       </c>
       <c r="I24" s="6">
-        <v>7.08</v>
+        <v>7.16</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="0"/>
-        <v>9.6045197740112886E-2</v>
+        <f>E24/I24-1</f>
+        <v>0.26675977653631278</v>
       </c>
       <c r="K24" s="11">
-        <v>4.0721649484536084E-2</v>
+        <v>5.2811466372657108E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>13438000000</v>
+        <v>32866046000</v>
       </c>
       <c r="M24" s="13">
-        <v>88611000000</v>
+        <v>215280386000</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>51</v>
@@ -3072,106 +3078,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>0.22643695147490772</v>
+        <v>0.19077256670755657</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E25">
-        <v>25.2</v>
+        <v>3.66</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>66859130880</v>
+        <v>2101498752</v>
       </c>
       <c r="H25" s="6">
-        <v>26.15</v>
+        <v>4.84</v>
       </c>
       <c r="I25" s="6">
-        <v>15.7</v>
+        <v>2.8</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="0"/>
-        <v>0.60509554140127397</v>
+        <f>E25/I25-1</f>
+        <v>0.30714285714285738</v>
       </c>
       <c r="K25" s="11">
-        <v>1.0793650793650795E-2</v>
+        <v>7.1038251366120214E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>1069250000</v>
+        <v>424258000</v>
       </c>
       <c r="M25" s="13">
-        <v>2571093000</v>
+        <v>2485347000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O25" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>0.12826873829061827</v>
+        <v>0.16805040730467743</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.41587371596437778</v>
+        <v>0.17070372869462494</v>
       </c>
       <c r="R25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>148746600448</v>
+        <v>8611297280</v>
       </c>
       <c r="H26" s="6">
-        <v>10.76</v>
+        <v>9.07</v>
       </c>
       <c r="I26" s="6">
-        <v>7.16</v>
+        <v>5</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="0"/>
-        <v>0.25698324022346375</v>
+        <f>E26/I26-1</f>
+        <v>0.74400000000000022</v>
       </c>
       <c r="K26" s="11">
-        <v>5.3222222222222219E-2</v>
+        <v>4.0596330275229353E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>32866046000</v>
+        <v>1333116000</v>
       </c>
       <c r="M26" s="13">
-        <v>215280386000</v>
+        <v>8019803000</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>51</v>
@@ -3180,52 +3186,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P26" s="12">
-        <v>0.18910686920992248</v>
+        <v>0.16891336411468238</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.16622802330680692</v>
       </c>
       <c r="R26" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>192</v>
+        <v>332</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="E27">
-        <v>9.0500000000000007</v>
+        <v>12.32</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>112262537216</v>
+        <v>19768055808</v>
       </c>
       <c r="H27" s="6">
-        <v>13.6</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I27" s="6">
-        <v>6.57</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="0"/>
-        <v>0.37747336377473362</v>
+        <f>E27/I27-1</f>
+        <v>0.27933541017653152</v>
       </c>
       <c r="K27" s="11">
-        <v>5.5248618784530384E-3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="13">
-        <v>2125459000</v>
+        <v>634792000</v>
       </c>
       <c r="M27" s="13">
-        <v>9202253000</v>
+        <v>5195491000</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>72</v>
@@ -3234,52 +3240,52 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P27" s="12">
-        <v>0.14173517763216131</v>
+        <v>0.22807865789413284</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.23097158924015673</v>
+        <v>0.12218132992627646</v>
       </c>
       <c r="R27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>332</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E28">
-        <v>11.16</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>17906778112</v>
+        <v>13864705024</v>
       </c>
       <c r="H28" s="6">
-        <v>18.399999999999999</v>
+        <v>6.21</v>
       </c>
       <c r="I28" s="6">
-        <v>9.6300000000000008</v>
+        <v>3.22</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
-        <v>0.1588785046728971</v>
+        <f>E28/I28-1</f>
+        <v>0.50931677018633548</v>
       </c>
       <c r="K28" s="11">
-        <v>0</v>
+        <v>8.6419753086419745E-3</v>
       </c>
       <c r="L28" s="13">
-        <v>634792000</v>
+        <v>259348000</v>
       </c>
       <c r="M28" s="13">
-        <v>5195491000</v>
+        <v>1677627000</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>72</v>
@@ -3288,67 +3294,67 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P28" s="12">
-        <v>0.24979526264118315</v>
+        <v>0.16727859077654839</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.12218132992627646</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>291</v>
+        <v>201</v>
       </c>
       <c r="C29" t="s">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="E29">
-        <v>3.63</v>
+        <v>0.68</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>2084273408</v>
+        <v>1619902848</v>
       </c>
       <c r="H29" s="6">
-        <v>4.84</v>
+        <v>1.02</v>
       </c>
       <c r="I29" s="6">
-        <v>2.8</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="0"/>
-        <v>0.29642857142857149</v>
+        <f>E29/I29-1</f>
+        <v>0.23636363636363633</v>
       </c>
       <c r="K29" s="11">
-        <v>7.1625344352617082E-2</v>
+        <v>1.4705882352941176E-2</v>
       </c>
       <c r="L29" s="13">
-        <v>424258000</v>
+        <v>54195000</v>
       </c>
       <c r="M29" s="13">
-        <v>2485347000</v>
+        <v>586711000</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O29" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P29" s="12">
-        <v>0.16920489780271125</v>
+        <v>1.2993483164132273</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.17070372869462494</v>
+        <v>9.2370860611101543E-2</v>
       </c>
       <c r="R29" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
@@ -3362,13 +3368,13 @@
         <v>87</v>
       </c>
       <c r="E30">
-        <v>5.57</v>
+        <v>5.68</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>50504581120</v>
+        <v>51501977600</v>
       </c>
       <c r="H30" s="6">
         <v>7.38</v>
@@ -3377,11 +3383,11 @@
         <v>3.39</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="0"/>
-        <v>0.64306784660766958</v>
+        <f>E30/I30-1</f>
+        <v>0.67551622418879043</v>
       </c>
       <c r="K30" s="11">
-        <v>5.5116696588868939E-2</v>
+        <v>5.4049295774647892E-2</v>
       </c>
       <c r="L30" s="13">
         <v>5594372000</v>
@@ -3396,106 +3402,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.14332718755607407</v>
+        <v>0.13997919556289698</v>
       </c>
       <c r="Q30" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R30" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E31">
-        <v>4.59</v>
+        <v>5.87</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>13094444032</v>
+        <v>6220086784</v>
       </c>
       <c r="H31" s="6">
-        <v>6.21</v>
+        <v>6.88</v>
       </c>
       <c r="I31" s="6">
-        <v>3.22</v>
+        <v>3.97</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="0"/>
-        <v>0.42546583850931663</v>
+        <f>E31/I31-1</f>
+        <v>0.47858942065491172</v>
       </c>
       <c r="K31" s="11">
-        <v>9.1503267973856214E-3</v>
+        <v>8.3475298126064731E-2</v>
       </c>
       <c r="L31" s="13">
-        <v>259348000</v>
+        <v>866801000</v>
       </c>
       <c r="M31" s="13">
-        <v>1677627000</v>
+        <v>7530053000</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O31" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P31" s="12">
-        <v>0.17882841123054241</v>
+        <v>0.26883270614086113</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R31" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>353</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="E32">
-        <v>5.58</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>5912791040</v>
+        <v>16869647360</v>
       </c>
       <c r="H32" s="6">
-        <v>5.99</v>
+        <v>6.97</v>
       </c>
       <c r="I32" s="6">
-        <v>3.97</v>
+        <v>3.33</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
-        <v>0.40554156171284639</v>
+        <f>E32/I32-1</f>
+        <v>0.30630630630630606</v>
       </c>
       <c r="K32" s="11">
-        <v>8.7813620071684584E-2</v>
+        <v>6.2068965517241385E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>866801000</v>
+        <v>2823432000</v>
       </c>
       <c r="M32" s="13">
-        <v>7530053000</v>
+        <v>16925205000</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>68</v>
@@ -3504,106 +3510,106 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.29715311599512767</v>
+        <v>0.15779518586461597</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.16681818624944278</v>
       </c>
       <c r="R32" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>201</v>
+        <v>286</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>344</v>
       </c>
       <c r="D33" t="s">
-        <v>227</v>
+        <v>61</v>
       </c>
       <c r="E33">
-        <v>0.69</v>
+        <v>11.52</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>1643724928</v>
+        <v>17861414912</v>
       </c>
       <c r="H33" s="6">
-        <v>1.03</v>
+        <v>11.84</v>
       </c>
       <c r="I33" s="6">
-        <v>0.55000000000000004</v>
+        <v>8.67</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="0"/>
-        <v>0.25454545454545441</v>
+        <f>E33/I33-1</f>
+        <v>0.32871972318339093</v>
       </c>
       <c r="K33" s="11">
-        <v>1.4492753623188408E-2</v>
+        <v>5.2083333333333336E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>54195000</v>
+        <v>1721368005.75</v>
       </c>
       <c r="M33" s="13">
-        <v>586711000</v>
+        <v>14620942286.52</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O33" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P33" s="12">
-        <v>1.2095413323209785</v>
+        <v>0.22144818075919365</v>
       </c>
       <c r="Q33" s="12">
-        <v>9.2370860611101543E-2</v>
+        <v>0.11773304155211949</v>
       </c>
       <c r="R33" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C34" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="E34">
-        <v>4.05</v>
+        <v>4.47</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>15706224640</v>
+        <v>4921246208</v>
       </c>
       <c r="H34" s="6">
-        <v>6.97</v>
+        <v>4.55</v>
       </c>
       <c r="I34" s="6">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>0.21621621621621623</v>
+        <f>E34/I34-1</f>
+        <v>0.24166666666666647</v>
       </c>
       <c r="K34" s="11">
-        <v>6.666666666666668E-2</v>
+        <v>7.1588366890380326E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>2823432000</v>
+        <v>765224000</v>
       </c>
       <c r="M34" s="13">
-        <v>16925205000</v>
+        <v>5249449000</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>68</v>
@@ -3612,160 +3618,160 @@
         <v>1</v>
       </c>
       <c r="P34" s="12">
-        <v>0.16876870365102881</v>
+        <v>0.17764891921220902</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.16681818624944278</v>
+        <v>0.14577225152582682</v>
       </c>
       <c r="R34" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>286</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>192</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="E35">
-        <v>11.06</v>
+        <v>9.49</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>17625880576</v>
+        <v>117720604672</v>
       </c>
       <c r="H35" s="6">
-        <v>11.84</v>
+        <v>13.6</v>
       </c>
       <c r="I35" s="6">
-        <v>8.67</v>
+        <v>6.57</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="1"/>
-        <v>0.27566320645905429</v>
+        <f>E35/I35-1</f>
+        <v>0.44444444444444442</v>
       </c>
       <c r="K35" s="11">
-        <v>5.4249547920433995E-2</v>
+        <v>5.268703898840885E-3</v>
       </c>
       <c r="L35" s="13">
-        <v>1721368005.75</v>
+        <v>2250990000</v>
       </c>
       <c r="M35" s="13">
-        <v>14620942286.52</v>
+        <v>11437145000</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O35" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P35" s="12">
-        <v>0.22791209888208908</v>
+        <v>0.13802546278709271</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.11773304155211949</v>
+        <v>0.19681397761416858</v>
       </c>
       <c r="R35" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E36">
-        <v>5.32</v>
+        <v>5.9</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>7798961152</v>
+        <v>13194052608</v>
       </c>
       <c r="H36" s="6">
-        <v>5.42</v>
+        <v>6.4</v>
       </c>
       <c r="I36" s="6">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="1"/>
-        <v>0.54202898550724643</v>
+        <f>E36/I36-1</f>
+        <v>1.7314814814814814</v>
       </c>
       <c r="K36" s="11">
-        <v>9.0225563909774431E-2</v>
+        <v>3.9152542372881356E-2</v>
       </c>
       <c r="L36" s="13">
-        <v>784607000</v>
+        <v>2184074765.02</v>
       </c>
       <c r="M36" s="13">
-        <v>7872586000</v>
+        <v>23493408528.349998</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O36" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>0.37749454890417783</v>
+        <v>0.50494691519072832</v>
       </c>
       <c r="Q36" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>9.29654274042198E-2</v>
       </c>
       <c r="R36" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>348</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E37">
-        <v>4.26</v>
+        <v>5.67</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>4690047488</v>
+        <v>8312050176</v>
       </c>
       <c r="H37" s="6">
-        <v>4.49</v>
+        <v>5.69</v>
       </c>
       <c r="I37" s="6">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="1"/>
-        <v>0.1899441340782122</v>
+        <f>E37/I37-1</f>
+        <v>0.64347826086956506</v>
       </c>
       <c r="K37" s="11">
-        <v>7.5117370892018781E-2</v>
+        <v>8.4656084656084651E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>765224000</v>
+        <v>784607000</v>
       </c>
       <c r="M37" s="13">
-        <v>5249449000</v>
+        <v>7872586000</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>68</v>
@@ -3774,52 +3780,52 @@
         <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.18772475200360744</v>
+        <v>0.30275609277348042</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.14577225152582682</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R37" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>350</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E38">
-        <v>6.07</v>
+        <v>4.47</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>13574220800</v>
+        <v>51546247168</v>
       </c>
       <c r="H38" s="6">
-        <v>6.4</v>
+        <v>5.14</v>
       </c>
       <c r="I38" s="6">
-        <v>2.16</v>
+        <v>3.46</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="1"/>
-        <v>1.8101851851851851</v>
+        <f>E38/I38-1</f>
+        <v>0.29190751445086693</v>
       </c>
       <c r="K38" s="11">
-        <v>3.8056013179571663E-2</v>
+        <v>5.8389261744966447E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>2184074765.02</v>
+        <v>4734613000</v>
       </c>
       <c r="M38" s="13">
-        <v>23493408528.349998</v>
+        <v>16213395000</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>51</v>
@@ -3828,52 +3834,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P38" s="12">
-        <v>0.4665637453990078</v>
+        <v>0.10465840855258983</v>
       </c>
       <c r="Q38" s="12">
-        <v>9.29654274042198E-2</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R38" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="E39">
-        <v>3.03</v>
+        <v>5.62</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>34849546240</v>
+        <v>15039906816</v>
       </c>
       <c r="H39" s="6">
-        <v>4.1100000000000003</v>
+        <v>7.13</v>
       </c>
       <c r="I39" s="6">
-        <v>2.35</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="1"/>
-        <v>0.28936170212765955</v>
+        <f>E39/I39-1</f>
+        <v>0.35421686746987935</v>
       </c>
       <c r="K39" s="11">
-        <v>6.2706270627062716E-2</v>
+        <v>4.0925266903914591E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>9414000000</v>
+        <v>2030839000</v>
       </c>
       <c r="M39" s="13">
-        <v>81589000000</v>
+        <v>11587361000</v>
       </c>
       <c r="N39" s="9" t="s">
         <v>51</v>
@@ -3882,52 +3888,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P39" s="12">
-        <v>0.20458912808029497</v>
+        <v>0.1437714205538291</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.11538320116682396</v>
+        <v>0.17526328902672489</v>
       </c>
       <c r="R39" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C40" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>306</v>
       </c>
       <c r="E40">
-        <v>5.42</v>
+        <v>3.2</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>14461698048</v>
+        <v>36804800512</v>
       </c>
       <c r="H40" s="6">
-        <v>7.13</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="I40" s="6">
-        <v>4.1500000000000004</v>
+        <v>2.35</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="1"/>
-        <v>0.30602409638554207</v>
+        <f>E40/I40-1</f>
+        <v>0.36170212765957444</v>
       </c>
       <c r="K40" s="11">
-        <v>4.2435424354243544E-2</v>
+        <v>5.9374999999999997E-2</v>
       </c>
       <c r="L40" s="13">
-        <v>2030839000</v>
+        <v>9414000000</v>
       </c>
       <c r="M40" s="13">
-        <v>11587361000</v>
+        <v>81589000000</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>51</v>
@@ -3936,52 +3942,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.14949933951147382</v>
+        <v>0.19676327843442887</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.17526328902672489</v>
+        <v>0.11538320116682396</v>
       </c>
       <c r="R40" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>346</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E41">
-        <v>4.68</v>
+        <v>4.25</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>53967884288</v>
+        <v>29435584512</v>
       </c>
       <c r="H41" s="6">
-        <v>5.14</v>
+        <v>6.15</v>
       </c>
       <c r="I41" s="6">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="1"/>
-        <v>0.35260115606936404</v>
+        <f>E41/I41-1</f>
+        <v>0.14555256064690036</v>
       </c>
       <c r="K41" s="11">
-        <v>5.0427350427350429E-2</v>
+        <v>5.1529411764705879E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>4734613000</v>
+        <v>4216348000</v>
       </c>
       <c r="M41" s="13">
-        <v>16213395000</v>
+        <v>46142120000</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>51</v>
@@ -3990,52 +3996,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>9.9664779649589932E-2</v>
+        <v>0.42404451337868082</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.29201860560357656</v>
+        <v>9.1377422623841298E-2</v>
       </c>
       <c r="R41" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>29</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>340</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="E42">
-        <v>5.36</v>
+        <v>27.15</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>63264616448</v>
+        <v>193605009408</v>
       </c>
       <c r="H42" s="6">
-        <v>5.77</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="I42" s="6">
-        <v>4.12</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="1"/>
-        <v>0.30097087378640786</v>
+        <f>E42/I42-1</f>
+        <v>0.46282327586206895</v>
       </c>
       <c r="K42" s="11">
-        <v>4.4402985074626859E-2</v>
+        <v>4.8581952117863723E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>5687261000</v>
+        <v>61181051000</v>
       </c>
       <c r="M42" s="13">
-        <v>21716551000</v>
+        <v>532289194000</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>51</v>
@@ -4044,67 +4050,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.1009614311032022</v>
+        <v>0.19347963466409224</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.26188601495697911</v>
+        <v>0.11493949471384535</v>
       </c>
       <c r="R42" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>284</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>342</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E43">
-        <v>9.33</v>
+        <v>5.46</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>23519436800</v>
+        <v>64444928000</v>
       </c>
       <c r="H43" s="6">
-        <v>11.22</v>
+        <v>5.77</v>
       </c>
       <c r="I43" s="6">
-        <v>4.3499999999999996</v>
+        <v>4.34</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="1"/>
-        <v>1.1448275862068966</v>
+        <f>E43/I43-1</f>
+        <v>0.25806451612903225</v>
       </c>
       <c r="K43" s="11">
-        <v>3.4083601286173631E-2</v>
+        <v>2.7106227106227104E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>3301437000</v>
+        <v>5687261000</v>
       </c>
       <c r="M43" s="13">
-        <v>21814427000</v>
+        <v>21716551000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O43" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>0.16745628686162864</v>
+        <v>9.9019448442513563E-2</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.15134190781174311</v>
+        <v>0.26188601495697911</v>
       </c>
       <c r="R43" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
@@ -4118,13 +4124,13 @@
         <v>181</v>
       </c>
       <c r="E44">
-        <v>6.5</v>
+        <v>6.72</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>2521245952</v>
+        <v>2606580480</v>
       </c>
       <c r="H44" s="6">
         <v>14.18</v>
@@ -4133,11 +4139,11 @@
         <v>3.64</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="1"/>
-        <v>0.78571428571428559</v>
+        <f>E44/I44-1</f>
+        <v>0.84615384615384603</v>
       </c>
       <c r="K44" s="11">
-        <v>5.3846153846153842E-2</v>
+        <v>5.2083333333333329E-2</v>
       </c>
       <c r="L44" s="13">
         <v>348303000</v>
@@ -4152,175 +4158,175 @@
         <v>1</v>
       </c>
       <c r="P44" s="12">
-        <v>0.31152109609489603</v>
+        <v>0.28943088290500146</v>
       </c>
       <c r="Q44" s="12">
         <v>9.4606035666412708E-2</v>
       </c>
       <c r="R44" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="E45">
-        <v>26.6</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>189683007488</v>
+        <v>24905897984</v>
       </c>
       <c r="H45" s="6">
-        <v>32.299999999999997</v>
+        <v>11.22</v>
       </c>
       <c r="I45" s="6">
-        <v>18.559999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J45" s="12">
-        <f t="shared" si="1"/>
-        <v>0.43318965517241392</v>
+        <f>E45/I45-1</f>
+        <v>1.2712643678160922</v>
       </c>
       <c r="K45" s="11">
-        <v>4.9586466165413533E-2</v>
+        <v>3.2186234817813762E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>61181051000</v>
+        <v>3301437000</v>
       </c>
       <c r="M45" s="13">
-        <v>532289194000</v>
+        <v>21814427000</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O45" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P45" s="12">
-        <v>0.19575215896886974</v>
+        <v>0.15645376649682838</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.11493949471384535</v>
+        <v>0.15134190781174311</v>
       </c>
       <c r="R45" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="E46">
-        <v>4.47</v>
+        <v>3.97</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>30959308800</v>
+        <v>3668843776</v>
       </c>
       <c r="H46" s="6">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="I46" s="6">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="J46" s="12">
-        <f t="shared" si="1"/>
-        <v>0.20485175202156336</v>
+        <f>E46/I46-1</f>
+        <v>0.16764705882352948</v>
       </c>
       <c r="K46" s="11">
-        <v>4.8993288590604027E-2</v>
+        <v>3.6523929471032744E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>4216348000</v>
+        <v>754477000</v>
       </c>
       <c r="M46" s="13">
-        <v>46142120000</v>
+        <v>11677999000</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O46" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>0.37085121239714819</v>
+        <v>0.65650380214390591</v>
       </c>
       <c r="Q46" s="12">
-        <v>9.1377422623841298E-2</v>
+        <v>6.460670188445812E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>326</v>
+        <v>150</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>151</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>3696568064</v>
+        <v>5655515648</v>
       </c>
       <c r="H47" s="6">
-        <v>4.2</v>
+        <v>7.92</v>
       </c>
       <c r="I47" s="6">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="J47" s="12">
-        <f t="shared" si="1"/>
-        <v>0.17647058823529416</v>
+        <f>E47/I47-1</f>
+        <v>0.66949152542372881</v>
       </c>
       <c r="K47" s="11">
-        <v>3.6249999999999998E-2</v>
+        <v>6.4467005076142128E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>754477000</v>
+        <v>811880000</v>
       </c>
       <c r="M47" s="13">
-        <v>11677999000</v>
+        <v>5532140000</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O47" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>0.64103928766718776</v>
+        <v>0.15940214116245549</v>
       </c>
       <c r="Q47" s="12">
-        <v>6.460670188445812E-2</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R47" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
@@ -4334,13 +4340,13 @@
         <v>85</v>
       </c>
       <c r="E48">
-        <v>91</v>
+        <v>93.05</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>253708910592</v>
+        <v>259424337920</v>
       </c>
       <c r="H48" s="6">
         <v>107.5</v>
@@ -4349,11 +4355,11 @@
         <v>65.55</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="1"/>
-        <v>0.38825324180015253</v>
+        <f>E48/I48-1</f>
+        <v>0.41952707856598015</v>
       </c>
       <c r="K48" s="11">
-        <v>2.4373626373626372E-2</v>
+        <v>2.383664696399785E-2</v>
       </c>
       <c r="L48" s="13">
         <v>22510000000</v>
@@ -4368,52 +4374,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>8.8551784431301322E-2</v>
+        <v>8.6726633161824523E-2</v>
       </c>
       <c r="Q48" s="12">
         <v>0.27269973953601068</v>
       </c>
       <c r="R48" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>279</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>335</v>
+        <v>186</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E49">
-        <v>1.96</v>
+        <v>11.74</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>8388996096</v>
+        <v>66148327424</v>
       </c>
       <c r="H49" s="6">
-        <v>2.14</v>
+        <v>14.24</v>
       </c>
       <c r="I49" s="6">
-        <v>1.33</v>
+        <v>8.81</v>
       </c>
       <c r="J49" s="12">
-        <f t="shared" si="1"/>
-        <v>0.47368421052631571</v>
+        <f>E49/I49-1</f>
+        <v>0.33257661748013612</v>
       </c>
       <c r="K49" s="11">
-        <v>6.224489795918367E-2</v>
+        <v>2.8194207836456559E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>1230913000</v>
+        <v>6482967000</v>
       </c>
       <c r="M49" s="13">
-        <v>10701340000</v>
+        <v>27483863000</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>51</v>
@@ -4422,52 +4428,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>0.18538236286373469</v>
+        <v>9.5458207773439913E-2</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.11502419323187564</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R49" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="C50" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E50">
-        <v>11.52</v>
+        <v>23.3</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>64908754944</v>
+        <v>242187190272</v>
       </c>
       <c r="H50" s="6">
-        <v>14.24</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I50" s="6">
-        <v>8.81</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="1"/>
-        <v>0.30760499432463106</v>
+        <f>E50/I50-1</f>
+        <v>0.21101871101871117</v>
       </c>
       <c r="K50" s="11">
-        <v>2.8732638888888891E-2</v>
+        <v>4.1416309012875532E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>6482967000</v>
+        <v>25459748125.549999</v>
       </c>
       <c r="M50" s="13">
-        <v>27483863000</v>
+        <v>134815560756.77</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>51</v>
@@ -4476,214 +4482,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>9.7117351736239615E-2</v>
+        <v>0.11810841589489145</v>
       </c>
       <c r="Q50" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.18884873513587705</v>
       </c>
       <c r="R50" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B51" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C51" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>74.75</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>2347219968</v>
+        <v>18300667904</v>
       </c>
       <c r="H51" s="6">
-        <v>17</v>
+        <v>95.5</v>
       </c>
       <c r="I51" s="6">
-        <v>7.36</v>
+        <v>55.05</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="1"/>
-        <v>0.35869565217391308</v>
+        <f>E51/I51-1</f>
+        <v>0.35785649409627629</v>
       </c>
       <c r="K51" s="11">
-        <v>4.1999999999999996E-2</v>
+        <v>1.0969899665551839E-2</v>
       </c>
       <c r="L51" s="13">
-        <v>244811000</v>
+        <v>526052000</v>
       </c>
       <c r="M51" s="13">
-        <v>2904223000</v>
+        <v>5343547000</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O51" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P51" s="12">
-        <v>0.37971443928078069</v>
+        <v>0.21974017163133616</v>
       </c>
       <c r="Q51" s="12">
-        <v>8.4294835486117978E-2</v>
+        <v>9.8446219337080781E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C52" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E52">
-        <v>22.75</v>
+        <v>10.24</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>235542134784</v>
+        <v>2403553280</v>
       </c>
       <c r="H52" s="6">
-        <v>36.450000000000003</v>
+        <v>17</v>
       </c>
       <c r="I52" s="6">
-        <v>19.239999999999998</v>
+        <v>7.36</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="1"/>
-        <v>0.18243243243243246</v>
+        <f>E52/I52-1</f>
+        <v>0.39130434782608692</v>
       </c>
       <c r="K52" s="11">
-        <v>4.2417582417582415E-2</v>
+        <v>4.1015625E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>25459748125.549999</v>
+        <v>244811000</v>
       </c>
       <c r="M52" s="13">
-        <v>134815560756.77</v>
+        <v>2904223000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O52" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P52" s="12">
-        <v>0.12161752909188051</v>
+        <v>0.34920256444665976</v>
       </c>
       <c r="Q52" s="12">
-        <v>0.18884873513587705</v>
+        <v>8.4294835486117978E-2</v>
       </c>
       <c r="R52" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>273</v>
+        <v>142</v>
       </c>
       <c r="C53" t="s">
-        <v>328</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="E53">
-        <v>74.45</v>
+        <v>50.05</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>18227220480</v>
+        <v>128068943872</v>
       </c>
       <c r="H53" s="6">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="I53" s="6">
-        <v>55.05</v>
+        <v>43.55</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="1"/>
-        <v>0.35240690281562226</v>
+        <f>E53/I53-1</f>
+        <v>0.14925373134328357</v>
       </c>
       <c r="K53" s="11">
-        <v>1.1014103425117527E-2</v>
+        <v>3.2767232767232772E-3</v>
       </c>
       <c r="L53" s="13">
-        <v>526052000</v>
+        <v>1279098000</v>
       </c>
       <c r="M53" s="13">
-        <v>5343547000</v>
+        <v>4811702000</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="O53" s="6">
-        <v>7.6923076923076916</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P53" s="12">
-        <v>0.22062009687087855</v>
+        <v>7.7971808257203096E-2</v>
       </c>
       <c r="Q53" s="12">
-        <v>9.8446219337080781E-2</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R53" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="D54" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="E54">
-        <v>3.95</v>
+        <v>20.45</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>5669869568</v>
+        <v>32638201856</v>
       </c>
       <c r="H54" s="6">
-        <v>7.92</v>
+        <v>27.5</v>
       </c>
       <c r="I54" s="6">
-        <v>2.36</v>
+        <v>16.18</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="1"/>
-        <v>0.67372881355932224</v>
+        <f>E54/I54-1</f>
+        <v>0.26390605686032131</v>
       </c>
       <c r="K54" s="11">
-        <v>6.4303797468354434E-2</v>
+        <v>3.3545232273838634E-2</v>
       </c>
       <c r="L54" s="13">
-        <v>811880000</v>
+        <v>3811007000</v>
       </c>
       <c r="M54" s="13">
-        <v>5532140000</v>
+        <v>22856317000</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>51</v>
@@ -4692,13 +4698,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>0.15898276983246079</v>
+        <v>0.1275006272311732</v>
       </c>
       <c r="Q54" s="12">
-        <v>0.14675695119790894</v>
+        <v>0.1667375806872122</v>
       </c>
       <c r="R54" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
@@ -4712,26 +4718,26 @@
         <v>330</v>
       </c>
       <c r="E55">
-        <v>6.32</v>
+        <v>6.44</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>12818729984</v>
+        <v>13062123520</v>
       </c>
       <c r="H55" s="6">
-        <v>8.0399999999999991</v>
+        <v>7.86</v>
       </c>
       <c r="I55" s="6">
         <v>5.31</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="1"/>
-        <v>0.19020715630885143</v>
+        <f>E55/I55-1</f>
+        <v>0.21280602636534862</v>
       </c>
       <c r="K55" s="11">
-        <v>4.2721518987341771E-2</v>
+        <v>4.192546583850932E-2</v>
       </c>
       <c r="L55" s="13">
         <v>1537565000</v>
@@ -4746,52 +4752,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>0.19479548078048717</v>
+        <v>0.18933096199767332</v>
       </c>
       <c r="Q55" s="12">
         <v>0.10614925092863724</v>
       </c>
       <c r="R55" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C56" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="E56">
-        <v>19.14</v>
+        <v>0.52</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>30547439616</v>
+        <v>2695529216</v>
       </c>
       <c r="H56" s="6">
-        <v>27.5</v>
+        <v>0.68</v>
       </c>
       <c r="I56" s="6">
-        <v>16.18</v>
+        <v>0.46</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="1"/>
-        <v>0.18294190358467244</v>
+        <f>E56/I56-1</f>
+        <v>0.13043478260869557</v>
       </c>
       <c r="K56" s="11">
-        <v>3.5841170323928945E-2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="13">
-        <v>3811007000</v>
+        <v>756004000</v>
       </c>
       <c r="M56" s="13">
-        <v>22856317000</v>
+        <v>8813758000</v>
       </c>
       <c r="N56" s="9" t="s">
         <v>51</v>
@@ -4800,106 +4806,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P56" s="12">
-        <v>0.13643312460046628</v>
+        <v>0.28949073626199495</v>
       </c>
       <c r="Q56" s="12">
-        <v>0.1667375806872122</v>
+        <v>8.5775443346640556E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="C57" t="s">
-        <v>190</v>
+        <v>336</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>337</v>
       </c>
       <c r="E57">
-        <v>47.7</v>
+        <v>5.68</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>122055720960</v>
+        <v>7283123200</v>
       </c>
       <c r="H57" s="6">
-        <v>71.7</v>
+        <v>5.92</v>
       </c>
       <c r="I57" s="6">
-        <v>43.55</v>
+        <v>3.36</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="1"/>
-        <v>9.5292766934558015E-2</v>
+        <f>E57/I57-1</f>
+        <v>0.69047619047619047</v>
       </c>
       <c r="K57" s="11">
-        <v>3.4381551362683439E-3</v>
+        <v>4.5774647887323945E-2</v>
       </c>
       <c r="L57" s="13">
-        <v>1279098000</v>
+        <v>2871477000</v>
       </c>
       <c r="M57" s="13">
-        <v>4811702000</v>
+        <v>21784665000</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="O57" s="6">
-        <v>8.7546153846153842</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>8.1379162073239308E-2</v>
+        <v>0.15113893310484014</v>
       </c>
       <c r="Q57" s="12">
-        <v>0.26583067696212276</v>
+        <v>0.1318118502166547</v>
       </c>
       <c r="R57" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C58" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D58" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E58">
-        <v>0.52</v>
+        <v>2.23</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>2695529216</v>
+        <v>9544623104</v>
       </c>
       <c r="H58" s="6">
-        <v>0.68</v>
+        <v>2.39</v>
       </c>
       <c r="I58" s="6">
-        <v>0.46</v>
+        <v>1.33</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="1"/>
-        <v>0.13043478260869557</v>
+        <f>E58/I58-1</f>
+        <v>0.67669172932330812</v>
       </c>
       <c r="K58" s="11">
-        <v>0</v>
+        <v>5.4708520179372194E-2</v>
       </c>
       <c r="L58" s="13">
-        <v>756004000</v>
+        <v>1230913000</v>
       </c>
       <c r="M58" s="13">
-        <v>8813758000</v>
+        <v>10701340000</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>51</v>
@@ -4908,106 +4914,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.28949073626199495</v>
+        <v>0.15941315287471022</v>
       </c>
       <c r="Q58" s="12">
-        <v>8.5775443346640556E-2</v>
+        <v>0.11502419323187564</v>
       </c>
       <c r="R58" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>310</v>
       </c>
       <c r="E59">
-        <v>392.6</v>
+        <v>6.01</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>496183607296</v>
+        <v>26408902656</v>
       </c>
       <c r="H59" s="6">
-        <v>422.4</v>
+        <v>6.87</v>
       </c>
       <c r="I59" s="6">
-        <v>218.4</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J59" s="12">
-        <f t="shared" si="1"/>
-        <v>0.79761904761904767</v>
+        <f>E59/I59-1</f>
+        <v>0.25995807127882609</v>
       </c>
       <c r="K59" s="11">
-        <v>2.3586347427407027E-2</v>
+        <v>5.9567387687188021E-2</v>
       </c>
       <c r="L59" s="13">
-        <v>20744000000</v>
+        <v>2919921000</v>
       </c>
       <c r="M59" s="13">
-        <v>53852000000</v>
+        <v>31662140000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O59" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P59" s="12">
-        <v>5.7128283577028288E-2</v>
+        <v>0.21080725580864812</v>
       </c>
       <c r="Q59" s="12">
-        <v>0.38520389214885242</v>
+        <v>9.2221214358852555E-2</v>
       </c>
       <c r="R59" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C60" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="D60" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E60">
-        <v>5.72</v>
+        <v>6.99</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>7334412288</v>
+        <v>17521483776</v>
       </c>
       <c r="H60" s="6">
-        <v>5.92</v>
+        <v>7.26</v>
       </c>
       <c r="I60" s="6">
-        <v>3.36</v>
+        <v>3.99</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="1"/>
-        <v>0.70238095238095233</v>
+        <f>E60/I60-1</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="K60" s="11">
-        <v>4.5454545454545456E-2</v>
+        <v>4.5922746781115881E-2</v>
       </c>
       <c r="L60" s="13">
-        <v>2871477000</v>
+        <v>3040816000</v>
       </c>
       <c r="M60" s="13">
-        <v>21784665000</v>
+        <v>29707522000</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>51</v>
@@ -5016,106 +5022,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P60" s="12">
-        <v>0.15075799694960876</v>
+        <v>0.17021532122390806</v>
       </c>
       <c r="Q60" s="12">
-        <v>0.1318118502166547</v>
+        <v>0.102358453189061</v>
       </c>
       <c r="R60" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
-        <v>264</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>317</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="E61">
-        <v>19.559999999999999</v>
+        <v>416.8</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>18011709440</v>
+        <v>526768504832</v>
       </c>
       <c r="H61" s="6">
-        <v>23.35</v>
+        <v>426.8</v>
       </c>
       <c r="I61" s="6">
-        <v>9.9</v>
+        <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="1"/>
-        <v>0.9757575757575756</v>
+        <f>E61/I61-1</f>
+        <v>0.90842490842490853</v>
       </c>
       <c r="K61" s="11">
-        <v>3.9877300613496936E-3</v>
+        <v>2.2216890595009597E-2</v>
       </c>
       <c r="L61" s="13">
-        <v>334940000</v>
+        <v>20744000000</v>
       </c>
       <c r="M61" s="13">
-        <v>3025375000</v>
+        <v>53852000000</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O61" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P61" s="12">
-        <v>0.1696388129526302</v>
+        <v>5.2690199316482722E-2</v>
       </c>
       <c r="Q61" s="12">
-        <v>0.11071024253191752</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R61" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="D62" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="E62">
-        <v>6.18</v>
+        <v>3.78</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>27155908608</v>
+        <v>8584606720</v>
       </c>
       <c r="H62" s="6">
-        <v>6.87</v>
+        <v>5.09</v>
       </c>
       <c r="I62" s="6">
-        <v>4.7699999999999996</v>
+        <v>3.34</v>
       </c>
       <c r="J62" s="12">
-        <f t="shared" si="1"/>
-        <v>0.29559748427672972</v>
+        <f>E62/I62-1</f>
+        <v>0.13173652694610771</v>
       </c>
       <c r="K62" s="11">
-        <v>5.7928802588996763E-2</v>
+        <v>3.968253968253968E-2</v>
       </c>
       <c r="L62" s="13">
-        <v>2919921000</v>
+        <v>826931000</v>
       </c>
       <c r="M62" s="13">
-        <v>31662140000</v>
+        <v>5591620000</v>
       </c>
       <c r="N62" s="9" t="s">
         <v>51</v>
@@ -5124,52 +5130,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>0.2006771875864922</v>
+        <v>0.13467212416416638</v>
       </c>
       <c r="Q62" s="12">
-        <v>9.2221214358852555E-2</v>
+        <v>0.14788755315990715</v>
       </c>
       <c r="R62" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>338</v>
+        <v>176</v>
       </c>
       <c r="D63" t="s">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="E63">
-        <v>3.64</v>
+        <v>20.85</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>8266658304</v>
+        <v>585224093696</v>
       </c>
       <c r="H63" s="6">
-        <v>5.09</v>
+        <v>21.5</v>
       </c>
       <c r="I63" s="6">
-        <v>3.34</v>
+        <v>13.52</v>
       </c>
       <c r="J63" s="12">
-        <f t="shared" si="1"/>
-        <v>8.9820359281437279E-2</v>
+        <f>E63/I63-1</f>
+        <v>0.54215976331360971</v>
       </c>
       <c r="K63" s="11">
-        <v>4.1208791208791208E-2</v>
+        <v>1.8225419664268584E-2</v>
       </c>
       <c r="L63" s="13">
-        <v>826931000</v>
+        <v>52374992116</v>
       </c>
       <c r="M63" s="13">
-        <v>5591620000</v>
+        <v>269573093476</v>
       </c>
       <c r="N63" s="9" t="s">
         <v>51</v>
@@ -5178,376 +5184,376 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>0.14153165705806631</v>
+        <v>7.8865979164598199E-2</v>
       </c>
       <c r="Q63" s="12">
-        <v>0.14788755315990715</v>
+        <v>0.19428864891763736</v>
       </c>
       <c r="R63" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>159</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E64">
-        <v>2.48</v>
+        <v>254.8</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>4680479232</v>
+        <v>338415157248</v>
       </c>
       <c r="H64" s="6">
-        <v>4.18</v>
+        <v>283.39999999999998</v>
       </c>
       <c r="I64" s="6">
-        <v>1.74</v>
+        <v>34.4</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="1"/>
-        <v>0.42528735632183912</v>
+        <f>E64/I64-1</f>
+        <v>6.4069767441860472</v>
       </c>
       <c r="K64" s="11">
-        <v>6.4516129032258063E-2</v>
+        <v>3.1985871271585555E-3</v>
       </c>
       <c r="L64" s="13">
-        <v>896597000</v>
+        <v>4408440000</v>
       </c>
       <c r="M64" s="13">
-        <v>6906279000</v>
+        <v>10683505000</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O64" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P64" s="12">
-        <v>0.14288741718726924</v>
+        <v>1.4147202752498436E-2</v>
       </c>
       <c r="Q64" s="12">
-        <v>0.12982345485897689</v>
+        <v>0.41263985929711272</v>
       </c>
       <c r="R64" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
-        <v>133</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>176</v>
+        <v>320</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>321</v>
       </c>
       <c r="E65">
-        <v>19.18</v>
+        <v>7.66</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>531698384896</v>
+        <v>13844913152</v>
       </c>
       <c r="H65" s="6">
-        <v>20.7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I65" s="6">
-        <v>13.52</v>
+        <v>5.49</v>
       </c>
       <c r="J65" s="12">
-        <f t="shared" si="1"/>
-        <v>0.41863905325443795</v>
+        <f>E65/I65-1</f>
+        <v>0.39526411657559191</v>
       </c>
       <c r="K65" s="11">
-        <v>1.9812304483837331E-2</v>
+        <v>3.2637075718015662E-2</v>
       </c>
       <c r="L65" s="13">
-        <v>52374992116</v>
+        <v>2897428000</v>
       </c>
       <c r="M65" s="13">
-        <v>269573093476</v>
+        <v>25970601000</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O65" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P65" s="12">
-        <v>8.5301130934902492E-2</v>
+        <v>0.15445270231638378</v>
       </c>
       <c r="Q65" s="12">
-        <v>0.19428864891763736</v>
+        <v>0.11156568921912897</v>
       </c>
       <c r="R65" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="D66" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="E66">
-        <v>239.6</v>
+        <v>357</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>318227152896</v>
+        <v>132375248896</v>
       </c>
       <c r="H66" s="6">
-        <v>283.39999999999998</v>
+        <v>421.4</v>
       </c>
       <c r="I66" s="6">
-        <v>34.4</v>
+        <v>225.2</v>
       </c>
       <c r="J66" s="12">
-        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
-        <v>5.9651162790697674</v>
+        <f>E66/I66-1</f>
+        <v>0.58525754884547077</v>
       </c>
       <c r="K66" s="11">
-        <v>3.4015025041736224E-3</v>
+        <v>2.0168067226890756E-3</v>
       </c>
       <c r="L66" s="13">
-        <v>4408440000</v>
+        <v>1200000000</v>
       </c>
       <c r="M66" s="13">
-        <v>10683505000</v>
+        <v>5855000000</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O66" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P66" s="12">
-        <v>1.5060459980733311E-2</v>
+        <v>6.3509596319243009E-2</v>
       </c>
       <c r="Q66" s="12">
-        <v>0.41263985929711272</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R66" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B67" s="1" t="s">
-        <v>138</v>
+        <v>374</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>377</v>
       </c>
       <c r="E67">
-        <v>338</v>
+        <v>1.79</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>126311620608</v>
+        <v>3824388608</v>
       </c>
       <c r="H67" s="6">
-        <v>421.4</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I67" s="6">
-        <v>225.2</v>
+        <v>0.99</v>
       </c>
       <c r="J67" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5008880994671403</v>
+        <f>E67/I67-1</f>
+        <v>0.80808080808080818</v>
       </c>
       <c r="K67" s="11">
-        <v>2.1301775147928993E-3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="13">
-        <v>1200000000</v>
+        <v>-732033000</v>
       </c>
       <c r="M67" s="13">
-        <v>5855000000</v>
+        <v>7864121000</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O67" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P67" s="12">
-        <v>6.6274503203376092E-2</v>
+        <v>0.60856022938217547</v>
       </c>
       <c r="Q67" s="12">
-        <v>0.20495303159692571</v>
+        <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R67" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
-        <v>374</v>
+        <v>264</v>
       </c>
       <c r="C68" t="s">
-        <v>376</v>
+        <v>317</v>
       </c>
       <c r="D68" t="s">
-        <v>377</v>
+        <v>155</v>
       </c>
       <c r="E68">
-        <v>1.8</v>
+        <v>21.35</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>3845754112</v>
+        <v>19660019712</v>
       </c>
       <c r="H68" s="6">
-        <v>2.5499999999999998</v>
+        <v>23.35</v>
       </c>
       <c r="I68" s="6">
-        <v>0.99</v>
+        <v>9.9</v>
       </c>
       <c r="J68" s="12">
-        <f t="shared" si="2"/>
-        <v>0.81818181818181834</v>
+        <f>E68/I68-1</f>
+        <v>1.1565656565656566</v>
       </c>
       <c r="K68" s="11">
-        <v>0</v>
+        <v>3.6533957845433251E-3</v>
       </c>
       <c r="L68" s="13">
-        <v>-732033000</v>
+        <v>334940000</v>
       </c>
       <c r="M68" s="13">
-        <v>7864121000</v>
+        <v>3025375000</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O68" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P68" s="12">
-        <v>0.61884859302803386</v>
+        <v>0.15303074135496528</v>
       </c>
       <c r="Q68" s="12">
-        <v>-9.3085164890011229E-2</v>
+        <v>0.11071024253191752</v>
       </c>
       <c r="R68" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B69" s="1" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>323</v>
+        <v>182</v>
       </c>
       <c r="D69" t="s">
-        <v>324</v>
+        <v>183</v>
       </c>
       <c r="E69">
-        <v>7.07</v>
+        <v>29.8</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>17722015744</v>
+        <v>20612063232</v>
       </c>
       <c r="H69" s="6">
-        <v>7.23</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="I69" s="6">
-        <v>3.99</v>
+        <v>13.48</v>
       </c>
       <c r="J69" s="12">
-        <f t="shared" si="2"/>
-        <v>0.77192982456140347</v>
+        <f>E69/I69-1</f>
+        <v>1.2106824925816024</v>
       </c>
       <c r="K69" s="11">
-        <v>4.54031117397454E-2</v>
+        <v>1.5436241610738255E-2</v>
       </c>
       <c r="L69" s="13">
-        <v>3040816000</v>
+        <v>1323087000</v>
       </c>
       <c r="M69" s="13">
-        <v>29707522000</v>
+        <v>5952918000</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O69" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P69" s="12">
-        <v>0.16844550812159936</v>
+        <v>5.7338756366324739E-2</v>
       </c>
       <c r="Q69" s="12">
-        <v>0.102358453189061</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R69" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B70" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C70" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D70" t="s">
-        <v>321</v>
+        <v>50</v>
       </c>
       <c r="E70">
-        <v>7.52</v>
+        <v>3</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>13591873536</v>
+        <v>5661870080</v>
       </c>
       <c r="H70" s="6">
-        <v>8.8000000000000007</v>
+        <v>4.18</v>
       </c>
       <c r="I70" s="6">
-        <v>5.49</v>
+        <v>1.74</v>
       </c>
       <c r="J70" s="12">
-        <f t="shared" si="2"/>
-        <v>0.36976320582877942</v>
+        <f>E70/I70-1</f>
+        <v>0.72413793103448287</v>
       </c>
       <c r="K70" s="11">
-        <v>3.3244680851063829E-2</v>
+        <v>5.3333333333333337E-2</v>
       </c>
       <c r="L70" s="13">
-        <v>2897428000</v>
+        <v>896597000</v>
       </c>
       <c r="M70" s="13">
-        <v>25970601000</v>
+        <v>6906279000</v>
       </c>
       <c r="N70" s="9" t="s">
         <v>68</v>
@@ -5556,106 +5562,106 @@
         <v>1</v>
       </c>
       <c r="P70" s="12">
-        <v>0.15656456094646107</v>
+        <v>0.12356220165196077</v>
       </c>
       <c r="Q70" s="12">
-        <v>0.11156568921912897</v>
+        <v>0.12982345485897689</v>
       </c>
       <c r="R70" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B71" s="1" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="E71">
-        <v>31</v>
+        <v>56.7</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>21442080768</v>
+        <v>160336265216</v>
       </c>
       <c r="H71" s="6">
-        <v>39.200000000000003</v>
+        <v>60</v>
       </c>
       <c r="I71" s="6">
-        <v>13.48</v>
+        <v>38.4</v>
       </c>
       <c r="J71" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2997032640949553</v>
+        <f>E71/I71-1</f>
+        <v>0.47656250000000022</v>
       </c>
       <c r="K71" s="11">
-        <v>1.4838709677419355E-2</v>
+        <v>3.1746031746031744E-2</v>
       </c>
       <c r="L71" s="13">
-        <v>1323087000</v>
+        <v>8955723006</v>
       </c>
       <c r="M71" s="13">
-        <v>5952918000</v>
+        <v>47495870210</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O71" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P71" s="12">
-        <v>5.5347863032824282E-2</v>
+        <v>6.1220861282470472E-2</v>
       </c>
       <c r="Q71" s="12">
-        <v>0.222258562943417</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R71" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B72" s="1" t="s">
-        <v>125</v>
+        <v>373</v>
       </c>
       <c r="C72" t="s">
-        <v>166</v>
+        <v>375</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E72">
-        <v>21.6</v>
+        <v>10.76</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>24572592128</v>
+        <v>2831203584</v>
       </c>
       <c r="H72" s="6">
-        <v>28.75</v>
+        <v>15.58</v>
       </c>
       <c r="I72" s="6">
-        <v>19.52</v>
+        <v>7.4</v>
       </c>
       <c r="J72" s="12">
-        <f t="shared" si="2"/>
-        <v>0.10655737704918034</v>
+        <f>E72/I72-1</f>
+        <v>0.45405405405405386</v>
       </c>
       <c r="K72" s="11">
-        <v>6.4814814814814811E-2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="13">
-        <v>3446618000</v>
+        <v>-481083000</v>
       </c>
       <c r="M72" s="13">
-        <v>34010798000</v>
+        <v>4136123000</v>
       </c>
       <c r="N72" s="9" t="s">
         <v>51</v>
@@ -5664,52 +5670,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P72" s="12">
-        <v>0.15773165811264842</v>
+        <v>0.36171043704754685</v>
       </c>
       <c r="Q72" s="12">
-        <v>0.10133893359397213</v>
+        <v>-0.11631254679805218</v>
       </c>
       <c r="R72" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B73" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E73">
-        <v>55.6</v>
+        <v>22.85</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>159410749440</v>
+        <v>25994616832</v>
       </c>
       <c r="H73" s="6">
-        <v>60</v>
+        <v>28.75</v>
       </c>
       <c r="I73" s="6">
-        <v>38.4</v>
+        <v>19.52</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" si="2"/>
-        <v>0.44791666666666674</v>
+        <f>E73/I73-1</f>
+        <v>0.17059426229508201</v>
       </c>
       <c r="K73" s="11">
-        <v>3.237410071942446E-2</v>
+        <v>6.1269146608315089E-2</v>
       </c>
       <c r="L73" s="13">
-        <v>8955723006</v>
+        <v>3446618000</v>
       </c>
       <c r="M73" s="13">
-        <v>47495870210</v>
+        <v>34010798000</v>
       </c>
       <c r="N73" s="9" t="s">
         <v>51</v>
@@ -5718,52 +5724,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>6.1585562632163901E-2</v>
+        <v>0.14867541905307449</v>
       </c>
       <c r="Q73" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R73" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B74" s="1" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E74">
-        <v>12.76</v>
+        <v>6.38</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>125876633600</v>
+        <v>4971308544</v>
       </c>
       <c r="H74" s="6">
-        <v>13.86</v>
+        <v>8.09</v>
       </c>
       <c r="I74" s="6">
-        <v>5.83</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J74" s="12">
-        <f t="shared" si="2"/>
-        <v>1.1886792452830188</v>
+        <f>E74/I74-1</f>
+        <v>0.58706467661691564</v>
       </c>
       <c r="K74" s="11">
-        <v>4.0752351097178688E-2</v>
+        <v>2.6645768025078374E-2</v>
       </c>
       <c r="L74" s="13">
-        <v>8510100000</v>
+        <v>437453000</v>
       </c>
       <c r="M74" s="13">
-        <v>46117200000</v>
+        <v>4911072000</v>
       </c>
       <c r="N74" s="9" t="s">
         <v>68</v>
@@ -5772,13 +5778,13 @@
         <v>1</v>
       </c>
       <c r="P74" s="12">
-        <v>6.1187058001319003E-2</v>
+        <v>0.16311555203503975</v>
       </c>
       <c r="Q74" s="12">
-        <v>0.18453201842262756</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R74" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
@@ -5792,13 +5798,13 @@
         <v>174</v>
       </c>
       <c r="E75">
-        <v>505.5</v>
+        <v>495.6</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>4592068198400</v>
+        <v>4498987679744</v>
       </c>
       <c r="H75" s="6">
         <v>547</v>
@@ -5807,11 +5813,11 @@
         <v>349</v>
       </c>
       <c r="J75" s="12">
-        <f t="shared" si="2"/>
-        <v>0.44842406876790841</v>
+        <f>E75/I75-1</f>
+        <v>0.42005730659025797</v>
       </c>
       <c r="K75" s="11">
-        <v>8.3659742828882302E-3</v>
+        <v>8.533091202582728E-3</v>
       </c>
       <c r="L75" s="13">
         <v>253932000000</v>
@@ -5826,121 +5832,121 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P75" s="12">
-        <v>5.613284173766539E-2</v>
+        <v>5.7235134476659413E-2</v>
       </c>
       <c r="Q75" s="12">
         <v>0.19352168899747973</v>
       </c>
       <c r="R75" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B76" s="1" t="s">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>168</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E76">
-        <v>7.38</v>
+        <v>13.54</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>4998208512</v>
+        <v>133571280896</v>
       </c>
       <c r="H76" s="6">
-        <v>10.88</v>
+        <v>13.86</v>
       </c>
       <c r="I76" s="6">
-        <v>6.56</v>
+        <v>5.83</v>
       </c>
       <c r="J76" s="12">
-        <f t="shared" si="2"/>
-        <v>0.125</v>
+        <f>E76/I76-1</f>
+        <v>1.3224699828473412</v>
       </c>
       <c r="K76" s="11">
-        <v>4.8373983739837395E-2</v>
+        <v>3.8404726735598228E-2</v>
       </c>
       <c r="L76" s="13">
-        <v>618033000</v>
+        <v>8510100000</v>
       </c>
       <c r="M76" s="13">
-        <v>5033024000</v>
+        <v>46117200000</v>
       </c>
       <c r="N76" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O76" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P76" s="12">
-        <v>0.10975306020589076</v>
+        <v>5.79794050037373E-2</v>
       </c>
       <c r="Q76" s="12">
-        <v>0.12279555988606453</v>
+        <v>0.18453201842262756</v>
       </c>
       <c r="R76" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B77" s="1" t="s">
-        <v>373</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>375</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="E77">
-        <v>9.7200000000000006</v>
+        <v>6.08</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>2557555712</v>
+        <v>9890397184</v>
       </c>
       <c r="H77" s="6">
-        <v>15.58</v>
+        <v>7.05</v>
       </c>
       <c r="I77" s="6">
-        <v>6.65</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J77" s="12">
-        <f t="shared" si="2"/>
-        <v>0.46165413533834587</v>
+        <f>E77/I77-1</f>
+        <v>0.4238875878220143</v>
       </c>
       <c r="K77" s="11">
-        <v>0</v>
+        <v>4.6052631578947373E-2</v>
       </c>
       <c r="L77" s="13">
-        <v>-481083000</v>
+        <v>4094312000</v>
       </c>
       <c r="M77" s="13">
-        <v>4136123000</v>
+        <v>37637054000</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O77" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P77" s="12">
-        <v>0.3033010253165202</v>
+        <v>0.13509555170721232</v>
       </c>
       <c r="Q77" s="12">
-        <v>-0.11631254679805218</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R77" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
@@ -5954,26 +5960,26 @@
         <v>75</v>
       </c>
       <c r="E78">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>16805306368</v>
+        <v>19099756544</v>
       </c>
       <c r="H78" s="6">
-        <v>4.68</v>
+        <v>4.13</v>
       </c>
       <c r="I78" s="6">
         <v>2.11</v>
       </c>
       <c r="J78" s="12">
-        <f t="shared" si="2"/>
-        <v>0.28436018957345977</v>
+        <f>E78/I78-1</f>
+        <v>0.45971563981042673</v>
       </c>
       <c r="K78" s="11">
-        <v>5.9040590405904064E-2</v>
+        <v>5.1948051948051945E-2</v>
       </c>
       <c r="L78" s="13">
         <v>1677300000</v>
@@ -5988,67 +5994,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P78" s="12">
-        <v>9.7476259498421966E-2</v>
+        <v>8.6660350383692061E-2</v>
       </c>
       <c r="Q78" s="12">
         <v>0.1499088374088374</v>
       </c>
       <c r="R78" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B79" s="1" t="s">
-        <v>120</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>319</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E79">
-        <v>6.15</v>
+        <v>7.75</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>10004267008</v>
+        <v>5248796160</v>
       </c>
       <c r="H79" s="6">
-        <v>7.05</v>
+        <v>10.06</v>
       </c>
       <c r="I79" s="6">
-        <v>4.2699999999999996</v>
+        <v>6.56</v>
       </c>
       <c r="J79" s="12">
-        <f t="shared" si="2"/>
-        <v>0.44028103044496514</v>
+        <f>E79/I79-1</f>
+        <v>0.18140243902439024</v>
       </c>
       <c r="K79" s="11">
-        <v>4.5528455284552849E-2</v>
+        <v>4.6064516129032257E-2</v>
       </c>
       <c r="L79" s="13">
-        <v>4094312000</v>
+        <v>618033000</v>
       </c>
       <c r="M79" s="13">
-        <v>37637054000</v>
+        <v>5033024000</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O79" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P79" s="12">
-        <v>0.13458986548229865</v>
+        <v>0.10536437648676049</v>
       </c>
       <c r="Q79" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.12279555988606453</v>
       </c>
       <c r="R79" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
@@ -6077,7 +6083,7 @@
         <v>6.84</v>
       </c>
       <c r="J80" s="12">
-        <f t="shared" si="2"/>
+        <f>E80/I80-1</f>
         <v>0.17105263157894735</v>
       </c>
       <c r="K80" s="11">
@@ -6102,61 +6108,61 @@
         <v>0.1154893948238957</v>
       </c>
       <c r="R80" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B81" s="1" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E81">
-        <v>13.2</v>
+        <v>14.46</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>56920907776</v>
+        <v>60703227904</v>
       </c>
       <c r="H81" s="6">
-        <v>14.7</v>
+        <v>15.38</v>
       </c>
       <c r="I81" s="6">
-        <v>7.51</v>
+        <v>10.98</v>
       </c>
       <c r="J81" s="12">
-        <f t="shared" si="2"/>
-        <v>0.7576564580559253</v>
+        <f>E81/I81-1</f>
+        <v>0.31693989071038264</v>
       </c>
       <c r="K81" s="11">
-        <v>3.318181818181818E-2</v>
+        <v>6.1272475795297369E-2</v>
       </c>
       <c r="L81" s="13">
-        <v>3967214824.1399999</v>
+        <v>11996000000</v>
       </c>
       <c r="M81" s="13">
-        <v>41038539262.660004</v>
+        <v>138296000000</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O81" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P81" s="12">
-        <v>0.13488586911643227</v>
+        <v>0.14307996554792443</v>
       </c>
       <c r="Q81" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R81" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
@@ -6170,13 +6176,13 @@
         <v>77</v>
       </c>
       <c r="E82">
-        <v>14.64</v>
+        <v>14.46</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>61458870272</v>
+        <v>60703227904</v>
       </c>
       <c r="H82" s="6">
         <v>15.38</v>
@@ -6185,11 +6191,11 @@
         <v>10.98</v>
       </c>
       <c r="J82" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333326</v>
+        <f>E82/I82-1</f>
+        <v>0.31693989071038264</v>
       </c>
       <c r="K82" s="11">
-        <v>6.0519125683060108E-2</v>
+        <v>6.1272475795297369E-2</v>
       </c>
       <c r="L82" s="13">
         <v>11996000000</v>
@@ -6204,175 +6210,175 @@
         <v>1</v>
       </c>
       <c r="P82" s="12">
-        <v>0.14180193618782672</v>
+        <v>0.14307996554792443</v>
       </c>
       <c r="Q82" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B83" s="1" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E83">
-        <v>14.64</v>
+        <v>13.26</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>61458870272</v>
+        <v>58883948544</v>
       </c>
       <c r="H83" s="6">
-        <v>15.38</v>
+        <v>14.7</v>
       </c>
       <c r="I83" s="6">
-        <v>10.98</v>
+        <v>7.51</v>
       </c>
       <c r="J83" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333326</v>
+        <f>E83/I83-1</f>
+        <v>0.76564580559254325</v>
       </c>
       <c r="K83" s="11">
-        <v>6.0519125683060108E-2</v>
+        <v>3.3031674208144797E-2</v>
       </c>
       <c r="L83" s="13">
-        <v>11996000000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M83" s="13">
-        <v>138296000000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O83" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P83" s="12">
-        <v>0.14180193618782672</v>
+        <v>0.1269547433597869</v>
       </c>
       <c r="Q83" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R83" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B84" s="1" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D84" t="s">
         <v>104</v>
       </c>
       <c r="E84">
-        <v>6.9</v>
+        <v>31.9</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>5376493568</v>
+        <v>71877074944</v>
       </c>
       <c r="H84" s="6">
-        <v>8.09</v>
+        <v>61.55</v>
       </c>
       <c r="I84" s="6">
-        <v>4.0199999999999996</v>
+        <v>24.85</v>
       </c>
       <c r="J84" s="12">
-        <f t="shared" si="2"/>
-        <v>0.71641791044776149</v>
+        <f>E84/I84-1</f>
+        <v>0.28370221327967804</v>
       </c>
       <c r="K84" s="11">
-        <v>2.4637681159420291E-2</v>
+        <v>1.7805642633228841E-2</v>
       </c>
       <c r="L84" s="13">
-        <v>437453000</v>
+        <v>5261270000</v>
       </c>
       <c r="M84" s="13">
-        <v>4911072000</v>
+        <v>43208997000</v>
       </c>
       <c r="N84" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O84" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P84" s="12">
-        <v>0.14170608501561485</v>
+        <v>7.2385110483949439E-2</v>
       </c>
       <c r="Q84" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R84" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B85" s="1" t="s">
-        <v>141</v>
+        <v>260</v>
       </c>
       <c r="C85" t="s">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="D85" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E85">
-        <v>30.1</v>
+        <v>1.99</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>67821318144</v>
+        <v>1847860224</v>
       </c>
       <c r="H85" s="6">
-        <v>61.55</v>
+        <v>2.54</v>
       </c>
       <c r="I85" s="6">
-        <v>24.85</v>
+        <v>1.72</v>
       </c>
       <c r="J85" s="12">
-        <f t="shared" si="2"/>
-        <v>0.21126760563380276</v>
+        <f>E85/I85-1</f>
+        <v>0.15697674418604657</v>
       </c>
       <c r="K85" s="11">
-        <v>1.8870431893687704E-2</v>
+        <v>5.5276381909547742E-2</v>
       </c>
       <c r="L85" s="13">
-        <v>5261270000</v>
+        <v>238321000</v>
       </c>
       <c r="M85" s="13">
-        <v>43208997000</v>
+        <v>6087917000</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O85" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P85" s="12">
-        <v>7.6373999371440626E-2</v>
+        <v>0.15959509688418372</v>
       </c>
       <c r="Q85" s="12">
-        <v>0.12176329850933591</v>
+        <v>3.9146558666946343E-2</v>
       </c>
       <c r="R85" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
@@ -6386,13 +6392,13 @@
         <v>308</v>
       </c>
       <c r="E86">
-        <v>47.35</v>
+        <v>49.9</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>996101980160</v>
+        <v>1024941031424</v>
       </c>
       <c r="H86" s="6">
         <v>59.8</v>
@@ -6401,11 +6407,11 @@
         <v>32.65</v>
       </c>
       <c r="J86" s="12">
-        <f t="shared" si="2"/>
-        <v>0.45022970903522208</v>
+        <f>E86/I86-1</f>
+        <v>0.52833078101071984</v>
       </c>
       <c r="K86" s="11">
-        <v>5.3854276663146773E-2</v>
+        <v>5.1102204408817631E-2</v>
       </c>
       <c r="L86" s="13">
         <v>189900000000</v>
@@ -6420,67 +6426,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>0.13785228929511617</v>
+        <v>0.13520298337107575</v>
       </c>
       <c r="Q86" s="12">
         <v>8.2016774784268678E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B87" s="1" t="s">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>313</v>
+        <v>67</v>
       </c>
       <c r="D87" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E87">
-        <v>1.99</v>
+        <v>53.7</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>1847860224</v>
+        <v>137034342400</v>
       </c>
       <c r="H87" s="6">
-        <v>2.54</v>
+        <v>82.25</v>
       </c>
       <c r="I87" s="6">
-        <v>1.72</v>
+        <v>37.85</v>
       </c>
       <c r="J87" s="12">
-        <f t="shared" si="2"/>
-        <v>0.15697674418604657</v>
+        <f>E87/I87-1</f>
+        <v>0.41875825627476893</v>
       </c>
       <c r="K87" s="11">
-        <v>5.5276381909547742E-2</v>
+        <v>1.9553072625698324E-2</v>
       </c>
       <c r="L87" s="13">
-        <v>238321000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M87" s="13">
-        <v>6087917000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O87" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>0.15959509688418372</v>
+        <v>6.4403891896186186E-2</v>
       </c>
       <c r="Q87" s="12">
-        <v>3.9146558666946343E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R87" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
@@ -6494,13 +6500,13 @@
         <v>93</v>
       </c>
       <c r="E88">
-        <v>18.86</v>
+        <v>21.2</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>117225472000</v>
+        <v>124497641472</v>
       </c>
       <c r="H88" s="6">
         <v>26.6</v>
@@ -6509,11 +6515,11 @@
         <v>16.02</v>
       </c>
       <c r="J88" s="12">
-        <f t="shared" si="2"/>
-        <v>0.17727840199750311</v>
+        <f>E88/I88-1</f>
+        <v>0.3233458177278401</v>
       </c>
       <c r="K88" s="11">
-        <v>3.7645811240721104E-2</v>
+        <v>3.3490566037735849E-2</v>
       </c>
       <c r="L88" s="13">
         <v>10795274825</v>
@@ -6528,106 +6534,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>0.15635790236074304</v>
+        <v>0.14232618639328251</v>
       </c>
       <c r="Q88" s="12">
         <v>5.0146340085309396E-2</v>
       </c>
       <c r="R88" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B89" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C89" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="E89">
-        <v>8.9</v>
+        <v>6.63</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>27767998464</v>
+        <v>47864221696</v>
       </c>
       <c r="H89" s="6">
-        <v>10.1</v>
+        <v>10.72</v>
       </c>
       <c r="I89" s="6">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J89" s="12">
-        <f t="shared" si="2"/>
-        <v>0.58928571428571441</v>
+        <f>E89/I89-1</f>
+        <v>0.32600000000000007</v>
       </c>
       <c r="K89" s="11">
-        <v>3.5955056179775277E-2</v>
+        <v>6.485671191553545E-2</v>
       </c>
       <c r="L89" s="13">
-        <v>1990539000</v>
+        <v>6749146000</v>
       </c>
       <c r="M89" s="13">
-        <v>18620709000</v>
+        <v>70848374000</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O89" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P89" s="12">
-        <v>6.521791382377079E-2</v>
+        <v>8.9624378059502088E-2</v>
       </c>
       <c r="Q89" s="12">
-        <v>0.10689920561026972</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R89" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B90" s="1" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C90" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="E90">
-        <v>53.55</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>138702520320</v>
+        <v>20923322368</v>
       </c>
       <c r="H90" s="6">
-        <v>82.25</v>
+        <v>11.68</v>
       </c>
       <c r="I90" s="6">
-        <v>37.85</v>
+        <v>5.19</v>
       </c>
       <c r="J90" s="12">
-        <f t="shared" si="2"/>
-        <v>0.41479524438573301</v>
+        <f>E90/I90-1</f>
+        <v>0.71098265895953761</v>
       </c>
       <c r="K90" s="11">
-        <v>1.9607843137254905E-2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="13">
-        <v>6350637223.7200003</v>
+        <v>13493113000</v>
       </c>
       <c r="M90" s="13">
-        <v>57896384836.860001</v>
+        <v>208027754000</v>
       </c>
       <c r="N90" s="9" t="s">
         <v>51</v>
@@ -6636,160 +6642,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>6.3399965105589054E-2</v>
+        <v>0.12004757121312341</v>
       </c>
       <c r="Q90" s="12">
-        <v>0.10968970241604512</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R90" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B91" s="1" t="s">
-        <v>123</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>315</v>
       </c>
       <c r="D91" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="E91">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>51699572736</v>
+        <v>5978236416</v>
       </c>
       <c r="H91" s="6">
-        <v>10.72</v>
+        <v>9.15</v>
       </c>
       <c r="I91" s="6">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J91" s="12">
-        <f t="shared" si="2"/>
-        <v>0.41999999999999993</v>
+        <f>E91/I91-1</f>
+        <v>0.58928571428571441</v>
       </c>
       <c r="K91" s="11">
-        <v>6.0563380281690143E-2</v>
+        <v>5.7303370786516851E-2</v>
       </c>
       <c r="L91" s="13">
-        <v>6749146000</v>
+        <v>1136392000</v>
       </c>
       <c r="M91" s="13">
-        <v>70848374000</v>
+        <v>17458813000</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O91" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P91" s="12">
-        <v>8.5546264179245129E-2</v>
+        <v>0.10723242286328752</v>
       </c>
       <c r="Q91" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>6.5089877530620205E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B92" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D92" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="E92">
-        <v>8.1</v>
+        <v>11.88</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>19085463552</v>
+        <v>89995280384</v>
       </c>
       <c r="H92" s="6">
-        <v>11.68</v>
+        <v>11.9</v>
       </c>
       <c r="I92" s="6">
-        <v>5.19</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="J92" s="12">
-        <f t="shared" si="2"/>
-        <v>0.56069364161849689</v>
+        <f>E92/I92-1</f>
+        <v>0.33783783783783772</v>
       </c>
       <c r="K92" s="11">
-        <v>0</v>
+        <v>6.6329966329966322E-2</v>
       </c>
       <c r="L92" s="13">
-        <v>13493113000</v>
+        <v>8154000000</v>
       </c>
       <c r="M92" s="13">
-        <v>208027754000</v>
+        <v>79588000000</v>
       </c>
       <c r="N92" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O92" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P92" s="12">
-        <v>0.1219134386964545</v>
+        <v>6.2100031896550424E-2</v>
       </c>
       <c r="Q92" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R92" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B93" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E93">
-        <v>11.24</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>85147041792</v>
+        <v>30295199744</v>
       </c>
       <c r="H93" s="6">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="I93" s="6">
-        <v>8.66</v>
+        <v>5.6</v>
       </c>
       <c r="J93" s="12">
-        <f t="shared" si="2"/>
-        <v>0.2979214780600461</v>
+        <f>E93/I93-1</f>
+        <v>0.73392857142857171</v>
       </c>
       <c r="K93" s="11">
-        <v>7.0106761565836298E-2</v>
+        <v>3.2955715756951595E-2</v>
       </c>
       <c r="L93" s="13">
-        <v>8154000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M93" s="13">
-        <v>79588000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N93" s="9" t="s">
         <v>68</v>
@@ -6798,13 +6804,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="12">
-        <v>6.4480904861881003E-2</v>
+        <v>6.0230742778892156E-2</v>
       </c>
       <c r="Q93" s="12">
-        <v>0.10245263104990703</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R93" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
@@ -6818,13 +6824,13 @@
         <v>310</v>
       </c>
       <c r="E94">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>60497518592</v>
+        <v>64948293632</v>
       </c>
       <c r="H94" s="6">
         <v>2.08</v>
@@ -6833,11 +6839,11 @@
         <v>1.18</v>
       </c>
       <c r="J94" s="12">
-        <f t="shared" si="2"/>
-        <v>0.2881355932203391</v>
+        <f>E94/I94-1</f>
+        <v>0.42372881355932202</v>
       </c>
       <c r="K94" s="11">
-        <v>3.6842105263157898E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="L94" s="13">
         <v>12616717000</v>
@@ -6852,106 +6858,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>0.12898125410759451</v>
+        <v>0.12371253049885192</v>
       </c>
       <c r="Q94" s="12">
         <v>5.4568577322633927E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B95" s="1" t="s">
-        <v>262</v>
+        <v>112</v>
       </c>
       <c r="C95" t="s">
-        <v>315</v>
+        <v>149</v>
       </c>
       <c r="D95" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E95">
-        <v>8.67</v>
+        <v>5.53</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>5823742976</v>
+        <v>728101945344</v>
       </c>
       <c r="H95" s="6">
-        <v>9.06</v>
+        <v>6.98</v>
       </c>
       <c r="I95" s="6">
-        <v>5.6</v>
+        <v>4.08</v>
       </c>
       <c r="J95" s="12">
-        <f t="shared" si="2"/>
-        <v>0.54821428571428577</v>
+        <f>E95/I95-1</f>
+        <v>0.35539215686274517</v>
       </c>
       <c r="K95" s="11">
-        <v>5.8823529411764705E-2</v>
+        <v>4.701627486437613E-2</v>
       </c>
       <c r="L95" s="13">
-        <v>1136392000</v>
+        <v>44563000000</v>
       </c>
       <c r="M95" s="13">
-        <v>17458813000</v>
+        <v>463922000000</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O95" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P95" s="12">
-        <v>0.10881882033130333</v>
+        <v>6.751566435706656E-2</v>
       </c>
       <c r="Q95" s="12">
-        <v>6.5089877530620205E-2</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R95" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B96" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D96" t="s">
         <v>98</v>
       </c>
       <c r="E96">
-        <v>5.6</v>
+        <v>9.27</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>743366393856</v>
+        <v>283643478016</v>
       </c>
       <c r="H96" s="6">
-        <v>6.98</v>
+        <v>11.56</v>
       </c>
       <c r="I96" s="6">
-        <v>4.08</v>
+        <v>5.88</v>
       </c>
       <c r="J96" s="12">
-        <f t="shared" si="2"/>
-        <v>0.37254901960784292</v>
+        <f>E96/I96-1</f>
+        <v>0.57653061224489788</v>
       </c>
       <c r="K96" s="11">
-        <v>4.642857142857143E-2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="13">
-        <v>44563000000</v>
+        <v>26994000000</v>
       </c>
       <c r="M96" s="13">
-        <v>463922000000</v>
+        <v>363169000000</v>
       </c>
       <c r="N96" s="9" t="s">
         <v>51</v>
@@ -6960,52 +6966,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P96" s="12">
-        <v>6.6085154024479342E-2</v>
+        <v>9.75303809494521E-2</v>
       </c>
       <c r="Q96" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B97" s="1" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>161</v>
+        <v>312</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E97">
-        <v>9.1999999999999993</v>
+        <v>9.48</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>281501597696</v>
+        <v>24024877056</v>
       </c>
       <c r="H97" s="6">
-        <v>11.56</v>
+        <v>13.78</v>
       </c>
       <c r="I97" s="6">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="J97" s="12">
-        <f t="shared" si="2"/>
-        <v>0.56462585034013602</v>
+        <f>E97/I97-1</f>
+        <v>0.74264705882352944</v>
       </c>
       <c r="K97" s="11">
-        <v>0</v>
+        <v>3.164556962025316E-2</v>
       </c>
       <c r="L97" s="13">
-        <v>26994000000</v>
+        <v>9652467000</v>
       </c>
       <c r="M97" s="13">
-        <v>363169000000</v>
+        <v>173514401000</v>
       </c>
       <c r="N97" s="9" t="s">
         <v>51</v>
@@ -7014,445 +7020,445 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>9.82419890331893E-2</v>
+        <v>0.10569802748343256</v>
       </c>
       <c r="Q97" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>5.5629198178196171E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B98" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D98" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E98">
-        <v>9.39</v>
+        <v>49.3</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>23796795392</v>
+        <v>188820979712</v>
       </c>
       <c r="H98" s="6">
-        <v>13.78</v>
+        <v>52.95</v>
       </c>
       <c r="I98" s="6">
-        <v>5.44</v>
+        <v>36.9</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J118" si="3">E98/I98-1</f>
-        <v>0.72610294117647056</v>
+        <f>E98/I98-1</f>
+        <v>0.33604336043360439</v>
       </c>
       <c r="K98" s="11">
-        <v>3.1948881789137379E-2</v>
+        <v>4.4665314401622719E-2</v>
       </c>
       <c r="L98" s="13">
-        <v>9652467000</v>
+        <v>41737000000</v>
       </c>
       <c r="M98" s="13">
-        <v>173514401000</v>
+        <v>794927000000</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O98" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P98" s="12">
-        <v>0.10594570016944529</v>
+        <v>0.10640435580136998</v>
       </c>
       <c r="Q98" s="12">
-        <v>5.5629198178196171E-2</v>
+        <v>5.2504192208844336E-2</v>
       </c>
       <c r="R98" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B99" s="1" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="C99" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D99" t="s">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="E99">
-        <v>32.950000000000003</v>
+        <v>5.5</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>115317760000</v>
+        <v>113532649472</v>
       </c>
       <c r="H99" s="6">
-        <v>37.25</v>
+        <v>7.03</v>
       </c>
       <c r="I99" s="6">
-        <v>28.1</v>
+        <v>4.22</v>
       </c>
       <c r="J99" s="12">
-        <f t="shared" si="3"/>
-        <v>0.17259786476868322</v>
+        <f>E99/I99-1</f>
+        <v>0.30331753554502372</v>
       </c>
       <c r="K99" s="11">
-        <v>5.2807283763277688E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="L99" s="13">
-        <v>16863000000</v>
+        <v>42109966000</v>
       </c>
       <c r="M99" s="13">
-        <v>448320000000</v>
+        <v>746176876000</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O99" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>0.12319481569213964</v>
+        <v>0.10045474981002418</v>
       </c>
       <c r="Q99" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>5.643429507724386E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B100" s="1" t="s">
-        <v>258</v>
+        <v>117</v>
       </c>
       <c r="C100" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="D100" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E100">
-        <v>47.4</v>
+        <v>1.82</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>181543911424</v>
+        <v>6478053376</v>
       </c>
       <c r="H100" s="6">
-        <v>52.95</v>
+        <v>2.95</v>
       </c>
       <c r="I100" s="6">
-        <v>36.15</v>
+        <v>1.37</v>
       </c>
       <c r="J100" s="12">
-        <f t="shared" si="3"/>
-        <v>0.31120331950207469</v>
+        <f>E100/I100-1</f>
+        <v>0.32846715328467146</v>
       </c>
       <c r="K100" s="11">
-        <v>4.6455696202531649E-2</v>
+        <v>5.1648351648351645E-2</v>
       </c>
       <c r="L100" s="13">
-        <v>41737000000</v>
+        <v>2220197000</v>
       </c>
       <c r="M100" s="13">
-        <v>794927000000</v>
+        <v>71097505000</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O100" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P100" s="12">
-        <v>0.10841570192904734</v>
+        <v>0.12001692222552164</v>
       </c>
       <c r="Q100" s="12">
-        <v>5.2504192208844336E-2</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B101" s="1" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="D101" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="E101">
-        <v>5.36</v>
+        <v>35.4</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>109019193344</v>
+        <v>123892219904</v>
       </c>
       <c r="H101" s="6">
-        <v>7.03</v>
+        <v>37.25</v>
       </c>
       <c r="I101" s="6">
-        <v>4.22</v>
+        <v>28.1</v>
       </c>
       <c r="J101" s="12">
-        <f t="shared" si="3"/>
-        <v>0.27014218009478697</v>
+        <f>E101/I101-1</f>
+        <v>0.25978647686832734</v>
       </c>
       <c r="K101" s="11">
-        <v>5.5970149253731338E-2</v>
+        <v>4.9152542372881358E-2</v>
       </c>
       <c r="L101" s="13">
-        <v>42109966000</v>
+        <v>16863000000</v>
       </c>
       <c r="M101" s="13">
-        <v>746176876000</v>
+        <v>448320000000</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O101" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P101" s="12">
-        <v>0.1014774306566779</v>
+        <v>0.11593258743914125</v>
       </c>
       <c r="Q101" s="12">
-        <v>5.643429507724386E-2</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E102">
-        <v>1.72</v>
+        <v>5.36</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>6122116608</v>
+        <v>41492082688</v>
       </c>
       <c r="H102" s="6">
-        <v>2.95</v>
+        <v>5.49</v>
       </c>
       <c r="I102" s="6">
-        <v>1.37</v>
+        <v>3.87</v>
       </c>
       <c r="J102" s="12">
-        <f t="shared" si="3"/>
-        <v>0.25547445255474432</v>
+        <f>E102/I102-1</f>
+        <v>0.38501291989664077</v>
       </c>
       <c r="K102" s="11">
-        <v>5.4651162790697677E-2</v>
+        <v>7.145522388059701E-2</v>
       </c>
       <c r="L102" s="13">
-        <v>2220197000</v>
+        <v>5474000000</v>
       </c>
       <c r="M102" s="13">
-        <v>71097505000</v>
+        <v>59407000000</v>
       </c>
       <c r="N102" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O102" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>0.12221799720903279</v>
+        <v>5.8768534441434581E-2</v>
       </c>
       <c r="Q102" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B103" s="1" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="D103" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E103">
-        <v>5.15</v>
+        <v>1.6</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>39866462208</v>
+        <v>8740047872</v>
       </c>
       <c r="H103" s="6">
-        <v>5.49</v>
+        <v>1.82</v>
       </c>
       <c r="I103" s="6">
-        <v>3.8</v>
+        <v>0.81</v>
       </c>
       <c r="J103" s="12">
-        <f t="shared" si="3"/>
-        <v>0.35526315789473695</v>
+        <f>E103/I103-1</f>
+        <v>0.97530864197530853</v>
       </c>
       <c r="K103" s="11">
-        <v>7.4368932038834948E-2</v>
+        <v>2.1250000000000002E-2</v>
       </c>
       <c r="L103" s="13">
-        <v>5474000000</v>
+        <v>1384865000</v>
       </c>
       <c r="M103" s="13">
-        <v>59407000000</v>
+        <v>23827484000</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O103" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P103" s="12">
-        <v>5.9812414408194597E-2</v>
+        <v>7.4523798402907529E-2</v>
       </c>
       <c r="Q103" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B104" s="1" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="D104" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="E104">
-        <v>1.29</v>
+        <v>25.35</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>7046663680</v>
+        <v>28095660032</v>
       </c>
       <c r="H104" s="6">
-        <v>1.82</v>
+        <v>25.4</v>
       </c>
       <c r="I104" s="6">
-        <v>0.81</v>
+        <v>14.52</v>
       </c>
       <c r="J104" s="12">
-        <f t="shared" si="3"/>
-        <v>0.59259259259259256</v>
+        <f>E104/I104-1</f>
+        <v>0.74586776859504145</v>
       </c>
       <c r="K104" s="11">
-        <v>2.6356589147286821E-2</v>
+        <v>3.7080867850098613E-2</v>
       </c>
       <c r="L104" s="13">
-        <v>1384865000</v>
+        <v>3838344000</v>
       </c>
       <c r="M104" s="13">
-        <v>23827484000</v>
+        <v>81520873000</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O104" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P104" s="12">
-        <v>8.1472959597027175E-2</v>
+        <v>8.3599254759722658E-2</v>
       </c>
       <c r="Q104" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B105" s="1" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="D105" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="E105">
-        <v>23.35</v>
+        <v>11.28</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>25879040000</v>
+        <v>198537035776</v>
       </c>
       <c r="H105" s="6">
-        <v>25.15</v>
+        <v>12.46</v>
       </c>
       <c r="I105" s="6">
-        <v>14.52</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J105" s="12">
-        <f t="shared" si="3"/>
-        <v>0.60812672176308546</v>
+        <f>E105/I105-1</f>
+        <v>0.22608695652173916</v>
       </c>
       <c r="K105" s="11">
-        <v>4.0256959314775159E-2</v>
+        <v>3.6968085106382977E-2</v>
       </c>
       <c r="L105" s="13">
-        <v>3838344000</v>
+        <v>16758000000</v>
       </c>
       <c r="M105" s="13">
-        <v>81520873000</v>
+        <v>269590000000</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O105" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P105" s="12">
-        <v>8.7839999066297345E-2</v>
+        <v>6.0766342228791952E-2</v>
       </c>
       <c r="Q105" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
@@ -7466,13 +7472,13 @@
         <v>87</v>
       </c>
       <c r="E106">
-        <v>6.86</v>
+        <v>6.82</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>7158684160</v>
+        <v>7116942848</v>
       </c>
       <c r="H106" s="6">
         <v>7</v>
@@ -7481,8 +7487,8 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="J106" s="12">
-        <f t="shared" si="3"/>
-        <v>0.70646766169154263</v>
+        <f>E106/I106-1</f>
+        <v>0.69651741293532354</v>
       </c>
       <c r="K106" s="11">
         <v>0</v>
@@ -7500,106 +7506,106 @@
         <v>1</v>
       </c>
       <c r="P106" s="12">
-        <v>5.0016264870190799E-2</v>
+        <v>5.0362894360896727E-2</v>
       </c>
       <c r="Q106" s="12">
         <v>8.3790449156695201E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B107" s="1" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="D107" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E107">
-        <v>11.36</v>
+        <v>2.36</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>199945093120</v>
+        <v>10136200192</v>
       </c>
       <c r="H107" s="6">
-        <v>12.46</v>
+        <v>3.04</v>
       </c>
       <c r="I107" s="6">
-        <v>9.1999999999999993</v>
+        <v>1.93</v>
       </c>
       <c r="J107" s="12">
-        <f t="shared" si="3"/>
-        <v>0.23478260869565215</v>
+        <f>E107/I107-1</f>
+        <v>0.2227979274611398</v>
       </c>
       <c r="K107" s="11">
-        <v>3.6707746478873239E-2</v>
+        <v>4.5338983050847458E-2</v>
       </c>
       <c r="L107" s="13">
-        <v>16758000000</v>
+        <v>1938532000</v>
       </c>
       <c r="M107" s="13">
-        <v>269590000000</v>
+        <v>49986396000</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O107" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>6.0477321065231737E-2</v>
+        <v>6.3216996017780969E-2</v>
       </c>
       <c r="Q107" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B108" s="1" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>322</v>
       </c>
       <c r="D108" t="s">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="E108">
-        <v>2.1800000000000002</v>
+        <v>9.32</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>9363100672</v>
+        <v>9903897600</v>
       </c>
       <c r="H108" s="6">
-        <v>3.04</v>
+        <v>12.88</v>
       </c>
       <c r="I108" s="6">
-        <v>1.93</v>
+        <v>4.47</v>
       </c>
       <c r="J108" s="12">
-        <f t="shared" si="3"/>
-        <v>0.1295336787564767</v>
+        <f>E108/I108-1</f>
+        <v>1.085011185682327</v>
       </c>
       <c r="K108" s="11">
-        <v>4.9082568807339445E-2</v>
+        <v>1.5236051502145921E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>1938532000</v>
+        <v>161696000</v>
       </c>
       <c r="M108" s="13">
-        <v>49986396000</v>
+        <v>3260547000</v>
       </c>
       <c r="N108" s="9" t="s">
         <v>68</v>
@@ -7608,52 +7614,52 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>6.4852003257214824E-2</v>
+        <v>1.6724350727474503E-2</v>
       </c>
       <c r="Q108" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>4.95916789422143E-2</v>
       </c>
       <c r="R108" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B109" s="1" t="s">
-        <v>268</v>
+        <v>389</v>
       </c>
       <c r="C109" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="D109" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E109">
-        <v>9.34</v>
+        <v>1.45</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>9925150720</v>
+        <v>8028113408</v>
       </c>
       <c r="H109" s="6">
-        <v>12.88</v>
+        <v>2.99</v>
       </c>
       <c r="I109" s="6">
-        <v>4.47</v>
+        <v>0.91</v>
       </c>
       <c r="J109" s="12">
-        <f t="shared" si="3"/>
-        <v>1.0894854586129754</v>
+        <f>E109/I109-1</f>
+        <v>0.5934065934065933</v>
       </c>
       <c r="K109" s="11">
-        <v>1.1027837259100642E-2</v>
+        <v>1.0344827586206896E-2</v>
       </c>
       <c r="L109" s="13">
-        <v>161696000</v>
+        <v>429393000</v>
       </c>
       <c r="M109" s="13">
-        <v>3260547000</v>
+        <v>18333659000</v>
       </c>
       <c r="N109" s="9" t="s">
         <v>68</v>
@@ -7662,13 +7668,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>1.668766743397572E-2</v>
+        <v>5.2716539549671586E-2</v>
       </c>
       <c r="Q109" s="12">
-        <v>4.95916789422143E-2</v>
+        <v>2.3421020321148112E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
@@ -7682,26 +7688,26 @@
         <v>153</v>
       </c>
       <c r="E110">
-        <v>13.6</v>
+        <v>14.76</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>13967336448</v>
+        <v>15158667264</v>
       </c>
       <c r="H110" s="6">
-        <v>14.5</v>
+        <v>14.98</v>
       </c>
       <c r="I110" s="6">
         <v>10.36</v>
       </c>
       <c r="J110" s="12">
-        <f t="shared" si="3"/>
-        <v>0.31274131274131278</v>
+        <f>E110/I110-1</f>
+        <v>0.42471042471042475</v>
       </c>
       <c r="K110" s="11">
-        <v>7.9411764705882362E-2</v>
+        <v>7.3170731707317083E-2</v>
       </c>
       <c r="L110" s="13">
         <v>984000000</v>
@@ -7716,13 +7722,13 @@
         <v>1</v>
       </c>
       <c r="P110" s="12">
-        <v>2.5284361413448395E-2</v>
+        <v>2.4533350697573553E-2</v>
       </c>
       <c r="Q110" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R110" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
@@ -7736,13 +7742,13 @@
         <v>196</v>
       </c>
       <c r="E111">
-        <v>39.5</v>
+        <v>43.8</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>417104199680</v>
+        <v>451350233088</v>
       </c>
       <c r="H111" s="6">
         <v>59.7</v>
@@ -7751,8 +7757,8 @@
         <v>15.24</v>
       </c>
       <c r="J111" s="12">
-        <f t="shared" si="3"/>
-        <v>1.5918635170603674</v>
+        <f>E111/I111-1</f>
+        <v>1.8740157480314958</v>
       </c>
       <c r="K111" s="11">
         <v>0</v>
@@ -7770,13 +7776,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P111" s="12">
-        <v>1.6550687776386103E-2</v>
+        <v>1.5397715288321236E-2</v>
       </c>
       <c r="Q111" s="12">
         <v>3.0575487595734537E-2</v>
       </c>
       <c r="R111" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
@@ -7790,13 +7796,13 @@
         <v>174</v>
       </c>
       <c r="E112">
-        <v>29.05</v>
+        <v>28.95</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>29662662656</v>
+        <v>29560555520</v>
       </c>
       <c r="H112" s="6">
         <v>36</v>
@@ -7805,8 +7811,8 @@
         <v>22.4</v>
       </c>
       <c r="J112" s="12">
-        <f t="shared" si="3"/>
-        <v>0.29687500000000022</v>
+        <f>E112/I112-1</f>
+        <v>0.29241071428571441</v>
       </c>
       <c r="K112" s="11">
         <v>0</v>
@@ -7824,13 +7830,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P112" s="12">
-        <v>-3.6614361826565116E-3</v>
+        <v>-3.6756780125896493E-3</v>
       </c>
       <c r="Q112" s="12">
         <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R112" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="2:15" x14ac:dyDescent="0.5">
@@ -7844,26 +7850,26 @@
         <v>229</v>
       </c>
       <c r="E113">
-        <v>35.4</v>
+        <v>34.15</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>374277144576</v>
+        <v>361061122048</v>
       </c>
       <c r="H113" s="6">
-        <v>35.65</v>
+        <v>37</v>
       </c>
       <c r="I113" s="6">
         <v>21.5</v>
       </c>
       <c r="J113" s="12">
-        <f t="shared" si="3"/>
-        <v>0.64651162790697669</v>
+        <f>E113/I113-1</f>
+        <v>0.58837209302325566</v>
       </c>
       <c r="K113" s="11">
-        <v>5.6186440677966104E-2</v>
+        <v>5.8243045387994151E-2</v>
       </c>
       <c r="M113" s="13">
         <v>415994000000</v>
@@ -7886,26 +7892,26 @@
         <v>231</v>
       </c>
       <c r="E114">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>718260862976</v>
+        <v>725868216320</v>
       </c>
       <c r="H114" s="6">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="I114" s="6">
         <v>5.08</v>
       </c>
       <c r="J114" s="12">
-        <f t="shared" si="3"/>
-        <v>0.43700787401574792</v>
+        <f>E114/I114-1</f>
+        <v>0.44881889763779537</v>
       </c>
       <c r="K114" s="11">
-        <v>5.1917808219178081E-2</v>
+        <v>5.1494565217391305E-2</v>
       </c>
       <c r="M114" s="13">
         <v>2314289000000</v>
@@ -7928,26 +7934,26 @@
         <v>231</v>
       </c>
       <c r="E115">
-        <v>6.2</v>
+        <v>6.07</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>2747480408064</v>
+        <v>2698145431552</v>
       </c>
       <c r="H115" s="6">
-        <v>6.24</v>
+        <v>6.48</v>
       </c>
       <c r="I115" s="6">
         <v>4.0599999999999996</v>
       </c>
       <c r="J115" s="12">
-        <f t="shared" si="3"/>
-        <v>0.52709359605911343</v>
+        <f>E115/I115-1</f>
+        <v>0.49507389162561588</v>
       </c>
       <c r="K115" s="11">
-        <v>4.9677419354838707E-2</v>
+        <v>5.074135090609555E-2</v>
       </c>
       <c r="M115" s="13">
         <v>6434377000000</v>
@@ -7970,23 +7976,23 @@
         <v>229</v>
       </c>
       <c r="E116">
-        <v>5.46</v>
+        <v>5.51</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>594359222272</v>
+        <v>714343972864</v>
       </c>
       <c r="H116" s="6">
-        <v>5.48</v>
+        <v>5.64</v>
       </c>
       <c r="I116" s="6">
         <v>3.89</v>
       </c>
       <c r="J116" s="12">
-        <f t="shared" si="3"/>
-        <v>0.40359897172236492</v>
+        <f>E116/I116-1</f>
+        <v>0.41645244215938293</v>
       </c>
       <c r="K116" s="11">
         <v>0</v>
@@ -8012,26 +8018,26 @@
         <v>231</v>
       </c>
       <c r="E117">
-        <v>7.73</v>
+        <v>8.1</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G117" s="7">
-        <v>1958225379328</v>
+        <v>2172436348928</v>
       </c>
       <c r="H117" s="6">
-        <v>7.8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I117" s="6">
         <v>5.23</v>
       </c>
       <c r="J117" s="12">
-        <f t="shared" si="3"/>
-        <v>0.47801147227533458</v>
+        <f>E117/I117-1</f>
+        <v>0.54875717017208392</v>
       </c>
       <c r="K117" s="11">
-        <v>5.2134540750323415E-2</v>
+        <v>4.9753086419753088E-2</v>
       </c>
       <c r="M117" s="13">
         <v>6128626000000</v>
@@ -8054,13 +8060,13 @@
         <v>229</v>
       </c>
       <c r="E118">
-        <v>7.82</v>
+        <v>7.59</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="7">
-        <v>510649139200</v>
+        <v>487956545536</v>
       </c>
       <c r="H118" s="6">
         <v>7.97</v>
@@ -8069,11 +8075,11 @@
         <v>4.26</v>
       </c>
       <c r="J118" s="12">
-        <f t="shared" si="3"/>
-        <v>0.83568075117370899</v>
+        <f>E118/I118-1</f>
+        <v>0.78169014084507049</v>
       </c>
       <c r="K118" s="11">
-        <v>4.5396419437340151E-2</v>
+        <v>4.6772068511198944E-2</v>
       </c>
       <c r="M118" s="13">
         <v>2066897000000</v>
@@ -8086,9 +8092,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R21" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
+  <autoFilter ref="B1:R20" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R118">
-      <sortCondition ref="R1:R21"/>
+      <sortCondition ref="R1:R20"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J2:J1048576">
@@ -8209,7 +8215,7 @@
         <v>14.63</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
+        <f t="shared" ref="J2:J21" si="0">E2/I2-1</f>
         <v>2.7341079972658111E-3</v>
       </c>
       <c r="K2" s="11">
@@ -8263,7 +8269,7 @@
         <v>106.33</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
+        <f t="shared" si="0"/>
         <v>0.12442396313364057</v>
       </c>
       <c r="K3" s="11">
@@ -8317,7 +8323,7 @@
         <v>7.06</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
+        <f t="shared" si="0"/>
         <v>0.24362606232294626</v>
       </c>
       <c r="K4" s="11">
@@ -8371,7 +8377,7 @@
         <v>50.85</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
+        <f t="shared" si="0"/>
         <v>7.807276302851518E-2</v>
       </c>
       <c r="K5" s="11">
@@ -8425,7 +8431,7 @@
         <v>9.18</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
+        <f t="shared" si="0"/>
         <v>0.39215686274509798</v>
       </c>
       <c r="K6" s="11">
@@ -8479,7 +8485,7 @@
         <v>63.17</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
+        <f t="shared" si="0"/>
         <v>4.3691625771727249E-2</v>
       </c>
       <c r="K7" s="11">
@@ -8533,7 +8539,7 @@
         <v>21.48</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
+        <f t="shared" si="0"/>
         <v>9.3109869646190724E-4</v>
       </c>
       <c r="K8" s="11">
@@ -8587,7 +8593,7 @@
         <v>11.47</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
+        <f t="shared" si="0"/>
         <v>0.17959895379250201</v>
       </c>
       <c r="K9" s="11">
@@ -8641,7 +8647,7 @@
         <v>39.03</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
+        <f t="shared" si="0"/>
         <v>9.4286446323341044E-2</v>
       </c>
       <c r="K10" s="11">
@@ -8695,7 +8701,7 @@
         <v>10.08</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="11">
@@ -8749,7 +8755,7 @@
         <v>50.21</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
+        <f t="shared" si="0"/>
         <v>1.1445927106154152</v>
       </c>
       <c r="K12" s="11">
@@ -8803,7 +8809,7 @@
         <v>4.75</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
+        <f t="shared" si="0"/>
         <v>0.15368421052631587</v>
       </c>
       <c r="K13" s="11">
@@ -8857,7 +8863,7 @@
         <v>20.53</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
+        <f t="shared" si="0"/>
         <v>6.0886507549926971E-2</v>
       </c>
       <c r="K14" s="11">
@@ -8911,7 +8917,7 @@
         <v>173</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
+        <f t="shared" si="0"/>
         <v>0.20543352601156073</v>
       </c>
       <c r="K15" s="11">
@@ -8965,7 +8971,7 @@
         <v>9.73</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
+        <f t="shared" si="0"/>
         <v>0.25179856115107913</v>
       </c>
       <c r="K16" s="11">
@@ -9019,7 +9025,7 @@
         <v>7.54</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
+        <f t="shared" si="0"/>
         <v>0.22015915119363383</v>
       </c>
       <c r="K17" s="11">
@@ -9073,7 +9079,7 @@
         <v>7.15</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
+        <f t="shared" si="0"/>
         <v>8.5314685314685335E-2</v>
       </c>
       <c r="K18" s="11">
@@ -9127,7 +9133,7 @@
         <v>36.25</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
+        <f t="shared" si="0"/>
         <v>0.48634482758620701</v>
       </c>
       <c r="K19" s="11">
@@ -9181,7 +9187,7 @@
         <v>11.7</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
+        <f t="shared" si="0"/>
         <v>0.18547008547008548</v>
       </c>
       <c r="K20" s="11">
@@ -9235,7 +9241,7 @@
         <v>15.68</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
+        <f t="shared" si="0"/>
         <v>0.47704081632653073</v>
       </c>
       <c r="K21" s="11">

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B49268-F178-42C7-A140-1CD4F26EF225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F1FADD-4A6A-4A7A-8F54-141D028E49F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="393">
   <si>
     <t>Ticker</t>
   </si>
@@ -1272,6 +1272,12 @@
   </si>
   <si>
     <t>CHINA TRAVEL HK</t>
+  </si>
+  <si>
+    <t>0341.HK</t>
+  </si>
+  <si>
+    <t>CAFE DE CORAL H</t>
   </si>
 </sst>
 </file>
@@ -1769,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V118"/>
+  <dimension ref="B1:V119"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1856,13 +1862,13 @@
         <v>153</v>
       </c>
       <c r="E2">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>2631190016</v>
+        <v>2685441280</v>
       </c>
       <c r="H2" s="6">
         <v>3.55</v>
@@ -1872,10 +1878,10 @@
       </c>
       <c r="J2" s="12">
         <f>E2/I2-1</f>
-        <v>0.2543103448275863</v>
+        <v>0.28017241379310365</v>
       </c>
       <c r="K2" s="11">
-        <v>5.8075601374570449E-2</v>
+        <v>5.6902356902356906E-2</v>
       </c>
       <c r="L2" s="13">
         <v>504294000</v>
@@ -1890,7 +1896,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.39215559566825331</v>
+        <v>0.37725857417598985</v>
       </c>
       <c r="Q2" s="12">
         <v>0.29581628786323422</v>
@@ -1910,13 +1916,13 @@
         <v>148</v>
       </c>
       <c r="E3">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>9035021312</v>
+        <v>9007048704</v>
       </c>
       <c r="H3" s="6">
         <v>3.35</v>
@@ -1926,10 +1932,10 @@
       </c>
       <c r="J3" s="12">
         <f>E3/I3-1</f>
-        <v>0.3686440677966103</v>
+        <v>0.36440677966101709</v>
       </c>
       <c r="K3" s="11">
-        <v>4.736842105263158E-2</v>
+        <v>4.7515527950310554E-2</v>
       </c>
       <c r="L3" s="13">
         <v>1871151000</v>
@@ -1944,13 +1950,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.4132436258782804</v>
+        <v>0.41564705235097249</v>
       </c>
       <c r="Q3" s="12">
         <v>0.28956319566547578</v>
       </c>
       <c r="R3" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
@@ -1964,13 +1970,13 @@
         <v>77</v>
       </c>
       <c r="E4">
-        <v>13.74</v>
+        <v>13.72</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>250628603904</v>
+        <v>252361572352</v>
       </c>
       <c r="H4" s="6">
         <v>15.1</v>
@@ -1980,10 +1986,10 @@
       </c>
       <c r="J4" s="12">
         <f>E4/I4-1</f>
-        <v>0.44327731092436973</v>
+        <v>0.4411764705882355</v>
       </c>
       <c r="K4" s="11">
-        <v>0.11280931586608442</v>
+        <v>0.1129737609329446</v>
       </c>
       <c r="L4" s="13">
         <v>70144988000</v>
@@ -1998,13 +2004,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.55397346656738511</v>
+        <v>0.54696666717230991</v>
       </c>
       <c r="Q4" s="12">
         <v>0.26042924055386191</v>
       </c>
       <c r="R4" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
@@ -2018,13 +2024,13 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>7.49</v>
+        <v>7.29</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>29226278912</v>
+        <v>28445872128</v>
       </c>
       <c r="H5" s="6">
         <v>7.8</v>
@@ -2034,10 +2040,10 @@
       </c>
       <c r="J5" s="12">
         <f>E5/I5-1</f>
-        <v>0.7748815165876779</v>
+        <v>0.7274881516587679</v>
       </c>
       <c r="K5" s="11">
-        <v>5.7409879839786376E-3</v>
+        <v>5.8984910836762687E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2052,13 +2058,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.2781525253536144</v>
+        <v>0.28850038221889684</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
       </c>
       <c r="R5" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -2072,13 +2078,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>136.6</v>
+        <v>137.19999999999999</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>90206953472</v>
+        <v>90603175936</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2088,10 +2094,10 @@
       </c>
       <c r="J6" s="12">
         <f>E6/I6-1</f>
-        <v>0.50109890109890109</v>
+        <v>0.50769230769230766</v>
       </c>
       <c r="K6" s="11">
-        <v>1.4275256222547585E-2</v>
+        <v>1.4212827988338193E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2106,52 +2112,52 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.50707628883204281</v>
+        <v>0.50209950880515886</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
       </c>
       <c r="R6" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>305</v>
+        <v>224</v>
       </c>
       <c r="D7" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="E7">
-        <v>5.8</v>
+        <v>15.32</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>377214009344</v>
+        <v>140504465408</v>
       </c>
       <c r="H7" s="6">
-        <v>6.24</v>
+        <v>17.88</v>
       </c>
       <c r="I7" s="6">
-        <v>2.5099999999999998</v>
+        <v>10.6</v>
       </c>
       <c r="J7" s="12">
         <f>E7/I7-1</f>
-        <v>1.310756972111554</v>
+        <v>0.44528301886792465</v>
       </c>
       <c r="K7" s="11">
-        <v>3.1034482758620689E-2</v>
+        <v>4.6932114882506523E-2</v>
       </c>
       <c r="L7" s="13">
-        <v>72477000000</v>
+        <v>21175963859.630001</v>
       </c>
       <c r="M7" s="13">
-        <v>319355000000</v>
+        <v>104071284594.97</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>51</v>
@@ -2160,52 +2166,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.19034209571941735</v>
+        <v>0.20622775040833383</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.22694806719794586</v>
+        <v>0.20347556909712136</v>
       </c>
       <c r="R7" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D8" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E8">
-        <v>1.39</v>
+        <v>5.87</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>2799807488</v>
+        <v>391967473664</v>
       </c>
       <c r="H8" s="6">
-        <v>1.62</v>
+        <v>6.24</v>
       </c>
       <c r="I8" s="6">
-        <v>1.1299999999999999</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="J8" s="12">
         <f>E8/I8-1</f>
-        <v>0.23008849557522137</v>
+        <v>1.3386454183266934</v>
       </c>
       <c r="K8" s="11">
-        <v>8.5611510791366904E-2</v>
+        <v>3.0664395229982964E-2</v>
       </c>
       <c r="L8" s="13">
-        <v>929863000</v>
+        <v>72477000000</v>
       </c>
       <c r="M8" s="13">
-        <v>6026676000</v>
+        <v>319355000000</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>51</v>
@@ -2214,52 +2220,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P8" s="12">
-        <v>0.38347509842232841</v>
+        <v>0.18368065870641845</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.15429118804462028</v>
+        <v>0.22694806719794586</v>
       </c>
       <c r="R8" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="E9">
-        <v>15.68</v>
+        <v>1.48</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>143679127552</v>
+        <v>2981090048</v>
       </c>
       <c r="H9" s="6">
-        <v>17.88</v>
+        <v>1.62</v>
       </c>
       <c r="I9" s="6">
-        <v>10.6</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J9" s="12">
         <f>E9/I9-1</f>
-        <v>0.47924528301886804</v>
+        <v>0.30973451327433632</v>
       </c>
       <c r="K9" s="11">
-        <v>4.5854591836734696E-2</v>
+        <v>8.0405405405405403E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>21175963859.630001</v>
+        <v>929863000</v>
       </c>
       <c r="M9" s="13">
-        <v>104071284594.97</v>
+        <v>6026676000</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>51</v>
@@ -2268,13 +2274,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.20042765776352378</v>
+        <v>0.35839592936437953</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.20347556909712136</v>
+        <v>0.15429118804462028</v>
       </c>
       <c r="R9" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -2288,26 +2294,26 @@
         <v>146</v>
       </c>
       <c r="E10">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>14560459776</v>
+        <v>14713192448</v>
       </c>
       <c r="H10" s="6">
-        <v>3.3023729999999998</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="6">
         <v>2.23</v>
       </c>
       <c r="J10" s="12">
         <f>E10/I10-1</f>
-        <v>0.28251121076233177</v>
+        <v>0.29596412556053808</v>
       </c>
       <c r="K10" s="11">
-        <v>0.1048951048951049</v>
+        <v>0.10380622837370242</v>
       </c>
       <c r="L10" s="13">
         <v>2527643000</v>
@@ -2322,13 +2328,13 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.36483096930312597</v>
+        <v>0.35696178642832704</v>
       </c>
       <c r="Q10" s="12">
         <v>0.15337570692947131</v>
       </c>
       <c r="R10" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -2382,7 +2388,7 @@
         <v>0.14567921288909008</v>
       </c>
       <c r="R11" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
@@ -2396,26 +2402,26 @@
         <v>223</v>
       </c>
       <c r="E12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>1910000000</v>
+        <v>1920000000</v>
       </c>
       <c r="H12" s="6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I12" s="6">
         <v>1.35</v>
       </c>
       <c r="J12" s="12">
         <f>E12/I12-1</f>
-        <v>0.41481481481481475</v>
+        <v>0.42222222222222205</v>
       </c>
       <c r="K12" s="11">
-        <v>0.1099476439790576</v>
+        <v>0.109375</v>
       </c>
       <c r="L12" s="13">
         <v>315190000</v>
@@ -2430,13 +2436,13 @@
         <v>1</v>
       </c>
       <c r="P12" s="12">
-        <v>0.1516325795242377</v>
+        <v>0.15090659341974669</v>
       </c>
       <c r="Q12" s="12">
         <v>0.51857007005524791</v>
       </c>
       <c r="R12" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -2450,26 +2456,26 @@
         <v>96</v>
       </c>
       <c r="E13">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>10400431104</v>
+        <v>10648552448</v>
       </c>
       <c r="H13" s="6">
-        <v>5.0999999999999996</v>
+        <v>5.18</v>
       </c>
       <c r="I13" s="6">
         <v>3.15</v>
       </c>
       <c r="J13" s="12">
         <f>E13/I13-1</f>
-        <v>0.59682539682539693</v>
+        <v>0.63492063492063511</v>
       </c>
       <c r="K13" s="11">
-        <v>4.9701789264413515E-2</v>
+        <v>4.8543689320388349E-2</v>
       </c>
       <c r="L13" s="13">
         <v>1576240000</v>
@@ -2484,13 +2490,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.27436366960519337</v>
+        <v>0.26370359409020439</v>
       </c>
       <c r="Q13" s="12">
         <v>0.16357040581906512</v>
       </c>
       <c r="R13" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -2504,13 +2510,13 @@
         <v>304</v>
       </c>
       <c r="E14">
-        <v>8.31</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>199459127296</v>
+        <v>194991554560</v>
       </c>
       <c r="H14" s="6">
         <v>8.49</v>
@@ -2520,10 +2526,10 @@
       </c>
       <c r="J14" s="12">
         <f>E14/I14-1</f>
-        <v>0.81441048034934505</v>
+        <v>0.79475982532751099</v>
       </c>
       <c r="K14" s="11">
-        <v>3.0685920577617327E-2</v>
+        <v>3.1021897810218975E-2</v>
       </c>
       <c r="L14" s="13">
         <v>29168443138.220001</v>
@@ -2538,52 +2544,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.15638683109549151</v>
+        <v>0.15997342540438997</v>
       </c>
       <c r="Q14" s="12">
         <v>0.2888078161719172</v>
       </c>
       <c r="R14" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E15">
-        <v>14.66</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>31433093120</v>
+        <v>42888089600</v>
       </c>
       <c r="H15" s="6">
-        <v>17.059999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="I15" s="6">
-        <v>7.96</v>
+        <v>3.39</v>
       </c>
       <c r="J15" s="12">
         <f>E15/I15-1</f>
-        <v>0.84170854271356776</v>
+        <v>0.39528023598820061</v>
       </c>
       <c r="K15" s="11">
-        <v>7.6398362892223751E-2</v>
+        <v>6.4904862579281172E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>5451928473.2399998</v>
+        <v>5594372000</v>
       </c>
       <c r="M15" s="13">
-        <v>25994816572.18</v>
+        <v>26933044000</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>51</v>
@@ -2592,229 +2598,229 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.1669031163285318</v>
+        <v>0.17535490310883817</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R15" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="E16">
-        <v>15.08</v>
+        <v>14.18</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>54197821440</v>
+        <v>31481585664</v>
       </c>
       <c r="H16" s="6">
-        <v>16.600000000000001</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I16" s="6">
-        <v>7.55</v>
+        <v>7.96</v>
       </c>
       <c r="J16" s="12">
         <f>E16/I16-1</f>
-        <v>0.99735099337748356</v>
+        <v>0.78140703517587928</v>
       </c>
       <c r="K16" s="11">
-        <v>2.3209549071618034E-2</v>
+        <v>7.8984485190409043E-2</v>
       </c>
       <c r="L16" s="13">
-        <v>25585077000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M16" s="13">
-        <v>167756547000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O16" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P16" s="12">
-        <v>0.27830197037689341</v>
+        <v>0.16667152274822397</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.15251313559762292</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>308</v>
       </c>
       <c r="E17">
-        <v>7.67</v>
+        <v>15.72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>98407636992</v>
+        <v>56497995776</v>
       </c>
       <c r="H17" s="6">
-        <v>7.8</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="I17" s="6">
-        <v>4.84</v>
+        <v>7.55</v>
       </c>
       <c r="J17" s="12">
         <f>E17/I17-1</f>
-        <v>0.584710743801653</v>
+        <v>1.0821192052980133</v>
       </c>
       <c r="K17" s="11">
-        <v>8.344198174706649E-3</v>
+        <v>2.2264631043256995E-2</v>
       </c>
       <c r="L17" s="13">
-        <v>2553000000</v>
+        <v>25585077000</v>
       </c>
       <c r="M17" s="13">
-        <v>13971000000</v>
+        <v>167756547000</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O17" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P17" s="12">
-        <v>0.17653168783338599</v>
+        <v>0.27150877391270867</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.18273566673824351</v>
+        <v>0.15251313559762292</v>
       </c>
       <c r="R17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E18">
-        <v>2.52</v>
+        <v>7.59</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>2620321024</v>
+        <v>97381220352</v>
       </c>
       <c r="H18" s="6">
-        <v>3.34</v>
+        <v>7.8</v>
       </c>
       <c r="I18" s="6">
-        <v>1.92</v>
+        <v>4.84</v>
       </c>
       <c r="J18" s="12">
         <f>E18/I18-1</f>
-        <v>0.3125</v>
+        <v>0.56818181818181812</v>
       </c>
       <c r="K18" s="11">
-        <v>0.11587301587301586</v>
+        <v>8.4321475625823462E-3</v>
       </c>
       <c r="L18" s="13">
-        <v>762183000</v>
+        <v>2553000000</v>
       </c>
       <c r="M18" s="13">
-        <v>5008319000</v>
+        <v>13971000000</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O18" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P18" s="12">
-        <v>0.22647888920190015</v>
+        <v>0.17817563253338567</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.15218339726363278</v>
+        <v>0.18273566673824351</v>
       </c>
       <c r="R18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>14.42</v>
+        <v>6.21</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>12001593344</v>
+        <v>7734058496</v>
       </c>
       <c r="H19" s="6">
-        <v>19.440000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I19" s="6">
-        <v>12.12</v>
+        <v>3.46</v>
       </c>
       <c r="J19" s="12">
         <f>E19/I19-1</f>
-        <v>0.18976897689768979</v>
+        <v>0.7947976878612717</v>
       </c>
       <c r="K19" s="11">
-        <v>1.0263522884882107E-2</v>
+        <v>2.2705314009661835E-2</v>
       </c>
       <c r="L19" s="13">
-        <v>199557000</v>
+        <v>921702000</v>
       </c>
       <c r="M19" s="13">
-        <v>1108087000</v>
+        <v>5262544000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O19" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P19" s="12">
-        <v>0.17373054172349067</v>
+        <v>0.18660108134637093</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
@@ -2828,13 +2834,13 @@
         <v>77</v>
       </c>
       <c r="E20">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>66859130880</v>
+        <v>66593812480</v>
       </c>
       <c r="H20" s="6">
         <v>26.15</v>
@@ -2844,10 +2850,10 @@
       </c>
       <c r="J20" s="12">
         <f>E20/I20-1</f>
-        <v>0.60509554140127397</v>
+        <v>0.59872611464968162</v>
       </c>
       <c r="K20" s="11">
-        <v>1.0793650793650795E-2</v>
+        <v>1.0836653386454183E-2</v>
       </c>
       <c r="L20" s="13">
         <v>1069250000</v>
@@ -2862,13 +2868,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P20" s="12">
-        <v>0.12826873829061827</v>
+        <v>0.12880167273348653</v>
       </c>
       <c r="Q20" s="12">
         <v>0.41587371596437778</v>
       </c>
       <c r="R20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
@@ -2882,26 +2888,26 @@
         <v>81</v>
       </c>
       <c r="E21">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>67367022592</v>
+        <v>67540205568</v>
       </c>
       <c r="H21" s="6">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="I21" s="6">
         <v>7.08</v>
       </c>
       <c r="J21" s="12">
         <f>E21/I21-1</f>
-        <v>9.8870056497175174E-2</v>
+        <v>0.10169491525423724</v>
       </c>
       <c r="K21" s="11">
-        <v>4.0616966580976861E-2</v>
+        <v>4.0512820512820513E-2</v>
       </c>
       <c r="L21" s="13">
         <v>13438000000</v>
@@ -2916,52 +2922,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P21" s="12">
-        <v>0.22582014897181107</v>
+        <v>0.22520668314653117</v>
       </c>
       <c r="Q21" s="12">
         <v>0.15165160081705431</v>
       </c>
       <c r="R21" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E22">
-        <v>6.56</v>
+        <v>0.74</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>8169955328</v>
+        <v>1619497344</v>
       </c>
       <c r="H22" s="6">
-        <v>8.6</v>
+        <v>0.82</v>
       </c>
       <c r="I22" s="6">
-        <v>3.46</v>
+        <v>0.42</v>
       </c>
       <c r="J22" s="12">
         <f>E22/I22-1</f>
-        <v>0.89595375722543347</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="K22" s="11">
-        <v>2.1493902439024389E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="L22" s="13">
-        <v>921702000</v>
+        <v>219938000</v>
       </c>
       <c r="M22" s="13">
-        <v>5262544000</v>
+        <v>1520292000</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>51</v>
@@ -2970,322 +2976,322 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P22" s="12">
-        <v>0.1723637339710864</v>
+        <v>0.31760251606134982</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.14466826109721026</v>
       </c>
       <c r="R22" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>355</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E23">
-        <v>0.79</v>
+        <v>2.72</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>1728922880</v>
+        <v>2828283136</v>
       </c>
       <c r="H23" s="6">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
       <c r="I23" s="6">
-        <v>0.42</v>
+        <v>1.92</v>
       </c>
       <c r="J23" s="12">
         <f>E23/I23-1</f>
-        <v>0.88095238095238115</v>
+        <v>0.41666666666666674</v>
       </c>
       <c r="K23" s="11">
-        <v>4.6835443037974676E-2</v>
+        <v>0.10735294117647057</v>
       </c>
       <c r="L23" s="13">
-        <v>219938000</v>
+        <v>762183000</v>
       </c>
       <c r="M23" s="13">
-        <v>1520292000</v>
+        <v>5008319000</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O23" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P23" s="12">
-        <v>0.27668052261777509</v>
+        <v>0.21329814973054531</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.14466826109721026</v>
+        <v>0.15218339726363278</v>
       </c>
       <c r="R23" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E24">
-        <v>9.07</v>
+        <v>14.92</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>147125370880</v>
+        <v>12417736704</v>
       </c>
       <c r="H24" s="6">
-        <v>10.76</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I24" s="6">
-        <v>7.16</v>
+        <v>12.12</v>
       </c>
       <c r="J24" s="12">
         <f>E24/I24-1</f>
-        <v>0.26675977653631278</v>
+        <v>0.23102310231023115</v>
       </c>
       <c r="K24" s="11">
-        <v>5.2811466372657108E-2</v>
+        <v>9.9195710455764075E-3</v>
       </c>
       <c r="L24" s="13">
-        <v>32866046000</v>
+        <v>199557000</v>
       </c>
       <c r="M24" s="13">
-        <v>215280386000</v>
+        <v>1108087000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O24" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P24" s="12">
-        <v>0.19077256670755657</v>
+        <v>0.1659163388020731</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R24" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>291</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>349</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E25">
-        <v>3.66</v>
+        <v>9.25</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>2101498752</v>
+        <v>151007166464</v>
       </c>
       <c r="H25" s="6">
-        <v>4.84</v>
+        <v>10.76</v>
       </c>
       <c r="I25" s="6">
-        <v>2.8</v>
+        <v>7.16</v>
       </c>
       <c r="J25" s="12">
         <f>E25/I25-1</f>
-        <v>0.30714285714285738</v>
+        <v>0.29189944134078205</v>
       </c>
       <c r="K25" s="11">
-        <v>7.1038251366120214E-2</v>
+        <v>5.1783783783783781E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>424258000</v>
+        <v>32866046000</v>
       </c>
       <c r="M25" s="13">
-        <v>2485347000</v>
+        <v>215280386000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O25" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P25" s="12">
-        <v>0.16805040730467743</v>
+        <v>0.18683227054048748</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.17070372869462494</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C26" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="E26">
-        <v>8.7200000000000006</v>
+        <v>3.65</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>8611297280</v>
+        <v>2095756928</v>
       </c>
       <c r="H26" s="6">
-        <v>9.07</v>
+        <v>4.84</v>
       </c>
       <c r="I26" s="6">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J26" s="12">
         <f>E26/I26-1</f>
-        <v>0.74400000000000022</v>
+        <v>0.3035714285714286</v>
       </c>
       <c r="K26" s="11">
-        <v>4.0596330275229353E-2</v>
+        <v>7.1232876712328766E-2</v>
       </c>
       <c r="L26" s="13">
-        <v>1333116000</v>
+        <v>424258000</v>
       </c>
       <c r="M26" s="13">
-        <v>8019803000</v>
+        <v>2485347000</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O26" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P26" s="12">
-        <v>0.16891336411468238</v>
+        <v>0.16843348586106932</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.16622802330680692</v>
+        <v>0.17070372869462494</v>
       </c>
       <c r="R26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C27" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>241</v>
       </c>
       <c r="E27">
-        <v>12.32</v>
+        <v>8.67</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>19768055808</v>
+        <v>8561920000</v>
       </c>
       <c r="H27" s="6">
-        <v>18.399999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="I27" s="6">
-        <v>9.6300000000000008</v>
+        <v>5</v>
       </c>
       <c r="J27" s="12">
         <f>E27/I27-1</f>
-        <v>0.27933541017653152</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="K27" s="11">
-        <v>0</v>
+        <v>4.083044982698962E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>634792000</v>
+        <v>1333116000</v>
       </c>
       <c r="M27" s="13">
-        <v>5195491000</v>
+        <v>8019803000</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O27" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.22807865789413284</v>
+        <v>0.16990834282035278</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.12218132992627646</v>
+        <v>0.16622802330680692</v>
       </c>
       <c r="R27" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>332</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="E28">
-        <v>4.8600000000000003</v>
+        <v>12.46</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>13864705024</v>
+        <v>19992692736</v>
       </c>
       <c r="H28" s="6">
-        <v>6.21</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I28" s="6">
-        <v>3.22</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J28" s="12">
         <f>E28/I28-1</f>
-        <v>0.50931677018633548</v>
+        <v>0.29387331256490135</v>
       </c>
       <c r="K28" s="11">
-        <v>8.6419753086419745E-3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="13">
-        <v>259348000</v>
+        <v>634792000</v>
       </c>
       <c r="M28" s="13">
-        <v>1677627000</v>
+        <v>5195491000</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>72</v>
@@ -3294,13 +3300,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P28" s="12">
-        <v>0.16727859077654839</v>
+        <v>0.22571039846582011</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.12218132992627646</v>
       </c>
       <c r="R28" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
@@ -3314,26 +3320,26 @@
         <v>227</v>
       </c>
       <c r="E29">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>1619902848</v>
+        <v>1596080768</v>
       </c>
       <c r="H29" s="6">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="I29" s="6">
         <v>0.55000000000000004</v>
       </c>
       <c r="J29" s="12">
         <f>E29/I29-1</f>
-        <v>0.23636363636363633</v>
+        <v>0.21818181818181825</v>
       </c>
       <c r="K29" s="11">
-        <v>1.4705882352941176E-2</v>
+        <v>1.4925373134328358E-2</v>
       </c>
       <c r="L29" s="13">
         <v>54195000</v>
@@ -3348,106 +3354,106 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P29" s="12">
-        <v>1.2993483164132273</v>
+        <v>1.40356102880077</v>
       </c>
       <c r="Q29" s="12">
         <v>9.2370860611101543E-2</v>
       </c>
       <c r="R29" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30">
-        <v>5.68</v>
+        <v>6.13</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>51501977600</v>
+        <v>6495593472</v>
       </c>
       <c r="H30" s="6">
-        <v>7.38</v>
+        <v>6.88</v>
       </c>
       <c r="I30" s="6">
-        <v>3.39</v>
+        <v>3.97</v>
       </c>
       <c r="J30" s="12">
         <f>E30/I30-1</f>
-        <v>0.67551622418879043</v>
+        <v>0.54408060453400497</v>
       </c>
       <c r="K30" s="11">
-        <v>5.4049295774647892E-2</v>
+        <v>7.9934747145187598E-2</v>
       </c>
       <c r="L30" s="13">
-        <v>5594372000</v>
+        <v>866801000</v>
       </c>
       <c r="M30" s="13">
-        <v>26933044000</v>
+        <v>7530053000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O30" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P30" s="12">
-        <v>0.13997919556289698</v>
+        <v>0.24767013249244174</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R30" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>353</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="E31">
-        <v>5.87</v>
+        <v>4.34</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>6220086784</v>
+        <v>16830867456</v>
       </c>
       <c r="H31" s="6">
-        <v>6.88</v>
+        <v>6.97</v>
       </c>
       <c r="I31" s="6">
-        <v>3.97</v>
+        <v>3.33</v>
       </c>
       <c r="J31" s="12">
         <f>E31/I31-1</f>
-        <v>0.47858942065491172</v>
+        <v>0.30330330330330324</v>
       </c>
       <c r="K31" s="11">
-        <v>8.3475298126064731E-2</v>
+        <v>6.2211981566820285E-2</v>
       </c>
       <c r="L31" s="13">
-        <v>866801000</v>
+        <v>2823432000</v>
       </c>
       <c r="M31" s="13">
-        <v>7530053000</v>
+        <v>16925205000</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>68</v>
@@ -3456,268 +3462,268 @@
         <v>1</v>
       </c>
       <c r="P31" s="12">
-        <v>0.26883270614086113</v>
+        <v>0.15813792142946842</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.16681818624944278</v>
       </c>
       <c r="R31" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C32" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E32">
-        <v>4.3499999999999996</v>
+        <v>11.78</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>16869647360</v>
+        <v>18157338624</v>
       </c>
       <c r="H32" s="6">
-        <v>6.97</v>
+        <v>11.84</v>
       </c>
       <c r="I32" s="6">
-        <v>3.33</v>
+        <v>8.67</v>
       </c>
       <c r="J32" s="12">
         <f>E32/I32-1</f>
-        <v>0.30630630630630606</v>
+        <v>0.35870818915801617</v>
       </c>
       <c r="K32" s="11">
-        <v>6.2068965517241385E-2</v>
+        <v>5.0933786078098474E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>2823432000</v>
+        <v>1721368005.75</v>
       </c>
       <c r="M32" s="13">
-        <v>16925205000</v>
+        <v>14620942286.52</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O32" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P32" s="12">
-        <v>0.15779518586461597</v>
+        <v>0.2138287910765439</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.16681818624944278</v>
+        <v>0.11773304155211949</v>
       </c>
       <c r="R32" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>286</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s">
-        <v>344</v>
+        <v>192</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="E33">
-        <v>11.52</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>17861414912</v>
+        <v>118216785920</v>
       </c>
       <c r="H33" s="6">
-        <v>11.84</v>
+        <v>13.6</v>
       </c>
       <c r="I33" s="6">
-        <v>8.67</v>
+        <v>6.57</v>
       </c>
       <c r="J33" s="12">
         <f>E33/I33-1</f>
-        <v>0.32871972318339093</v>
+        <v>0.450532724505327</v>
       </c>
       <c r="K33" s="11">
-        <v>5.2083333333333336E-2</v>
+        <v>5.2465897166841559E-3</v>
       </c>
       <c r="L33" s="13">
-        <v>1721368005.75</v>
+        <v>2250990000</v>
       </c>
       <c r="M33" s="13">
-        <v>14620942286.52</v>
+        <v>11437145000</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O33" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P33" s="12">
-        <v>0.22144818075919365</v>
+        <v>0.13748169406803881</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.11773304155211949</v>
+        <v>0.19681397761416858</v>
       </c>
       <c r="R33" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>348</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E34">
-        <v>4.47</v>
+        <v>4.95</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>4921246208</v>
+        <v>14121458688</v>
       </c>
       <c r="H34" s="6">
-        <v>4.55</v>
+        <v>6.21</v>
       </c>
       <c r="I34" s="6">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="J34" s="12">
         <f>E34/I34-1</f>
-        <v>0.24166666666666647</v>
+        <v>0.53726708074534169</v>
       </c>
       <c r="K34" s="11">
-        <v>7.1588366890380326E-2</v>
+        <v>8.4848484848484857E-3</v>
       </c>
       <c r="L34" s="13">
-        <v>765224000</v>
+        <v>259348000</v>
       </c>
       <c r="M34" s="13">
-        <v>5249449000</v>
+        <v>1677627000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O34" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P34" s="12">
-        <v>0.17764891921220902</v>
+        <v>0.16375320006540439</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.14577225152582682</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R34" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
-        <v>143</v>
+        <v>292</v>
       </c>
       <c r="C35" t="s">
-        <v>192</v>
+        <v>350</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="E35">
-        <v>9.49</v>
+        <v>5.9</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>117720604672</v>
+        <v>13194052608</v>
       </c>
       <c r="H35" s="6">
-        <v>13.6</v>
+        <v>6.4</v>
       </c>
       <c r="I35" s="6">
-        <v>6.57</v>
+        <v>2.16</v>
       </c>
       <c r="J35" s="12">
         <f>E35/I35-1</f>
-        <v>0.44444444444444442</v>
+        <v>1.7314814814814814</v>
       </c>
       <c r="K35" s="11">
-        <v>5.268703898840885E-3</v>
+        <v>3.9152542372881356E-2</v>
       </c>
       <c r="L35" s="13">
-        <v>2250990000</v>
+        <v>2184074765.02</v>
       </c>
       <c r="M35" s="13">
-        <v>11437145000</v>
+        <v>23493408528.349998</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O35" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>0.13802546278709271</v>
+        <v>0.50494691519072832</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.19681397761416858</v>
+        <v>9.29654274042198E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>350</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E36">
-        <v>5.9</v>
+        <v>4.49</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>13194052608</v>
+        <v>51890479104</v>
       </c>
       <c r="H36" s="6">
-        <v>6.4</v>
+        <v>5.14</v>
       </c>
       <c r="I36" s="6">
-        <v>2.16</v>
+        <v>3.46</v>
       </c>
       <c r="J36" s="12">
         <f>E36/I36-1</f>
-        <v>1.7314814814814814</v>
+        <v>0.29768786127167646</v>
       </c>
       <c r="K36" s="11">
-        <v>3.9152542372881356E-2</v>
+        <v>5.8129175946547887E-2</v>
       </c>
       <c r="L36" s="13">
-        <v>2184074765.02</v>
+        <v>4734613000</v>
       </c>
       <c r="M36" s="13">
-        <v>23493408528.349998</v>
+        <v>16213395000</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>51</v>
@@ -3726,175 +3732,175 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P36" s="12">
-        <v>0.50494691519072832</v>
+        <v>0.10391827756389962</v>
       </c>
       <c r="Q36" s="12">
-        <v>9.29654274042198E-2</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R36" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>289</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>347</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37">
-        <v>5.67</v>
+        <v>5.44</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>8312050176</v>
+        <v>14558201856</v>
       </c>
       <c r="H37" s="6">
-        <v>5.69</v>
+        <v>7.13</v>
       </c>
       <c r="I37" s="6">
-        <v>3.45</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J37" s="12">
         <f>E37/I37-1</f>
-        <v>0.64347826086956506</v>
+        <v>0.31084337349397595</v>
       </c>
       <c r="K37" s="11">
-        <v>8.4656084656084651E-2</v>
+        <v>4.2279411764705878E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>784607000</v>
+        <v>2030839000</v>
       </c>
       <c r="M37" s="13">
-        <v>7872586000</v>
+        <v>11587361000</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O37" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P37" s="12">
-        <v>0.30275609277348042</v>
+        <v>0.14851182132444624</v>
       </c>
       <c r="Q37" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>0.17526328902672489</v>
       </c>
       <c r="R37" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>348</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E38">
-        <v>4.47</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>51546247168</v>
+        <v>4932256256</v>
       </c>
       <c r="H38" s="6">
-        <v>5.14</v>
+        <v>4.55</v>
       </c>
       <c r="I38" s="6">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="J38" s="12">
         <f>E38/I38-1</f>
-        <v>0.29190751445086693</v>
+        <v>0.24444444444444446</v>
       </c>
       <c r="K38" s="11">
-        <v>5.8389261744966447E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>4734613000</v>
+        <v>765224000</v>
       </c>
       <c r="M38" s="13">
-        <v>16213395000</v>
+        <v>5249449000</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O38" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P38" s="12">
-        <v>0.10465840855258983</v>
+        <v>0.17719600377579225</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.14577225152582682</v>
       </c>
       <c r="R38" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>289</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>347</v>
+        <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E39">
-        <v>5.62</v>
+        <v>5.66</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>15039906816</v>
+        <v>8297390080</v>
       </c>
       <c r="H39" s="6">
-        <v>7.13</v>
+        <v>5.73</v>
       </c>
       <c r="I39" s="6">
-        <v>4.1500000000000004</v>
+        <v>3.45</v>
       </c>
       <c r="J39" s="12">
         <f>E39/I39-1</f>
-        <v>0.35421686746987935</v>
+        <v>0.64057971014492754</v>
       </c>
       <c r="K39" s="11">
-        <v>4.0925266903914591E-2</v>
+        <v>8.4805653710247342E-2</v>
       </c>
       <c r="L39" s="13">
-        <v>2030839000</v>
+        <v>784607000</v>
       </c>
       <c r="M39" s="13">
-        <v>11587361000</v>
+        <v>7872586000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O39" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P39" s="12">
-        <v>0.1437714205538291</v>
+        <v>0.30447849329956156</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.17526328902672489</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R39" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
@@ -3908,13 +3914,13 @@
         <v>306</v>
       </c>
       <c r="E40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>36804800512</v>
+        <v>37379874816</v>
       </c>
       <c r="H40" s="6">
         <v>4.1100000000000003</v>
@@ -3924,10 +3930,10 @@
       </c>
       <c r="J40" s="12">
         <f>E40/I40-1</f>
-        <v>0.36170212765957444</v>
+        <v>0.38297872340425521</v>
       </c>
       <c r="K40" s="11">
-        <v>5.9374999999999997E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="L40" s="13">
         <v>9414000000</v>
@@ -3942,106 +3948,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.19676327843442887</v>
+        <v>0.1945742319089287</v>
       </c>
       <c r="Q40" s="12">
         <v>0.11538320116682396</v>
       </c>
       <c r="R40" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C41" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="E41">
-        <v>4.25</v>
+        <v>9.5</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>29435584512</v>
+        <v>23947978752</v>
       </c>
       <c r="H41" s="6">
-        <v>6.15</v>
+        <v>11.22</v>
       </c>
       <c r="I41" s="6">
-        <v>3.71</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J41" s="12">
         <f>E41/I41-1</f>
-        <v>0.14555256064690036</v>
+        <v>1.1839080459770117</v>
       </c>
       <c r="K41" s="11">
-        <v>5.1529411764705879E-2</v>
+        <v>3.3473684210526315E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>4216348000</v>
+        <v>3301437000</v>
       </c>
       <c r="M41" s="13">
-        <v>46142120000</v>
+        <v>21814427000</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O41" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P41" s="12">
-        <v>0.42404451337868082</v>
+        <v>0.16389379165257389</v>
       </c>
       <c r="Q41" s="12">
-        <v>9.1377422623841298E-2</v>
+        <v>0.15134190781174311</v>
       </c>
       <c r="R41" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C42" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E42">
-        <v>27.15</v>
+        <v>4.32</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>193605009408</v>
+        <v>29920407552</v>
       </c>
       <c r="H42" s="6">
-        <v>32.299999999999997</v>
+        <v>6.15</v>
       </c>
       <c r="I42" s="6">
-        <v>18.559999999999999</v>
+        <v>3.71</v>
       </c>
       <c r="J42" s="12">
         <f>E42/I42-1</f>
-        <v>0.46282327586206895</v>
+        <v>0.16442048517520225</v>
       </c>
       <c r="K42" s="11">
-        <v>4.8581952117863723E-2</v>
+        <v>5.0694444444444438E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>61181051000</v>
+        <v>4216348000</v>
       </c>
       <c r="M42" s="13">
-        <v>532289194000</v>
+        <v>46142120000</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>51</v>
@@ -4050,175 +4056,175 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.19347963466409224</v>
+        <v>0.40553632707851045</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.11493949471384535</v>
+        <v>9.1377422623841298E-2</v>
       </c>
       <c r="R42" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>29</v>
+        <v>287</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>345</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>5.46</v>
+        <v>6.43</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>64444928000</v>
+        <v>2494094080</v>
       </c>
       <c r="H43" s="6">
-        <v>5.77</v>
+        <v>14.18</v>
       </c>
       <c r="I43" s="6">
-        <v>4.34</v>
+        <v>3.64</v>
       </c>
       <c r="J43" s="12">
         <f>E43/I43-1</f>
-        <v>0.25806451612903225</v>
+        <v>0.76648351648351642</v>
       </c>
       <c r="K43" s="11">
-        <v>2.7106227106227104E-2</v>
+        <v>5.4432348367029551E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>5687261000</v>
+        <v>348303000</v>
       </c>
       <c r="M43" s="13">
-        <v>21716551000</v>
+        <v>3681615000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O43" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P43" s="12">
-        <v>9.9019448442513563E-2</v>
+        <v>0.31927453384119575</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.26188601495697911</v>
+        <v>9.4606035666412708E-2</v>
       </c>
       <c r="R43" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B44" s="1" t="s">
-        <v>287</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>345</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="E44">
-        <v>6.72</v>
+        <v>5.5</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>2606580480</v>
+        <v>64917049344</v>
       </c>
       <c r="H44" s="6">
-        <v>14.18</v>
+        <v>5.77</v>
       </c>
       <c r="I44" s="6">
-        <v>3.64</v>
+        <v>4.34</v>
       </c>
       <c r="J44" s="12">
         <f>E44/I44-1</f>
-        <v>0.84615384615384603</v>
+        <v>0.26728110599078336</v>
       </c>
       <c r="K44" s="11">
-        <v>5.2083333333333329E-2</v>
+        <v>2.6909090909090907E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>348303000</v>
+        <v>5687261000</v>
       </c>
       <c r="M44" s="13">
-        <v>3681615000</v>
+        <v>21716551000</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O44" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>0.28943088290500146</v>
+        <v>9.8263419018625814E-2</v>
       </c>
       <c r="Q44" s="12">
-        <v>9.4606035666412708E-2</v>
+        <v>0.26188601495697911</v>
       </c>
       <c r="R44" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="E45">
-        <v>9.8800000000000008</v>
+        <v>28.5</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>24905897984</v>
+        <v>203231789056</v>
       </c>
       <c r="H45" s="6">
-        <v>11.22</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="I45" s="6">
-        <v>4.3499999999999996</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J45" s="12">
         <f>E45/I45-1</f>
-        <v>1.2712643678160922</v>
+        <v>0.5355603448275863</v>
       </c>
       <c r="K45" s="11">
-        <v>3.2186234817813762E-2</v>
+        <v>4.6280701754385964E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>3301437000</v>
+        <v>61181051000</v>
       </c>
       <c r="M45" s="13">
-        <v>21814427000</v>
+        <v>532289194000</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O45" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>0.15645376649682838</v>
+        <v>0.18811910013328226</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.15134190781174311</v>
+        <v>0.11493949471384535</v>
       </c>
       <c r="R45" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
@@ -4272,46 +4278,46 @@
         <v>6.460670188445812E-2</v>
       </c>
       <c r="R46" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="E47">
-        <v>3.94</v>
+        <v>91</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>5655515648</v>
+        <v>253708910592</v>
       </c>
       <c r="H47" s="6">
-        <v>7.92</v>
+        <v>107.5</v>
       </c>
       <c r="I47" s="6">
-        <v>2.36</v>
+        <v>65.55</v>
       </c>
       <c r="J47" s="12">
         <f>E47/I47-1</f>
-        <v>0.66949152542372881</v>
+        <v>0.38825324180015253</v>
       </c>
       <c r="K47" s="11">
-        <v>6.4467005076142128E-2</v>
+        <v>2.4373626373626372E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>811880000</v>
+        <v>22510000000</v>
       </c>
       <c r="M47" s="13">
-        <v>5532140000</v>
+        <v>82545000000</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>51</v>
@@ -4320,52 +4326,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>0.15940214116245549</v>
+        <v>8.8551784431301322E-2</v>
       </c>
       <c r="Q47" s="12">
-        <v>0.14675695119790894</v>
+        <v>0.27269973953601068</v>
       </c>
       <c r="R47" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E48">
-        <v>93.05</v>
+        <v>11.52</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>259424337920</v>
+        <v>64908754944</v>
       </c>
       <c r="H48" s="6">
-        <v>107.5</v>
+        <v>14.24</v>
       </c>
       <c r="I48" s="6">
-        <v>65.55</v>
+        <v>8.81</v>
       </c>
       <c r="J48" s="12">
         <f>E48/I48-1</f>
-        <v>0.41952707856598015</v>
+        <v>0.30760499432463106</v>
       </c>
       <c r="K48" s="11">
-        <v>2.383664696399785E-2</v>
+        <v>2.8732638888888891E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>22510000000</v>
+        <v>6482967000</v>
       </c>
       <c r="M48" s="13">
-        <v>82545000000</v>
+        <v>27483863000</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>51</v>
@@ -4374,52 +4380,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>8.6726633161824523E-2</v>
+        <v>9.7117351736239615E-2</v>
       </c>
       <c r="Q48" s="12">
-        <v>0.27269973953601068</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R48" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E49">
-        <v>11.74</v>
+        <v>23.75</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>66148327424</v>
+        <v>246061875200</v>
       </c>
       <c r="H49" s="6">
-        <v>14.24</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I49" s="6">
-        <v>8.81</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="J49" s="12">
         <f>E49/I49-1</f>
-        <v>0.33257661748013612</v>
+        <v>0.2344074844074846</v>
       </c>
       <c r="K49" s="11">
-        <v>2.8194207836456559E-2</v>
+        <v>4.0631578947368421E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>6482967000</v>
+        <v>25459748125.549999</v>
       </c>
       <c r="M49" s="13">
-        <v>27483863000</v>
+        <v>134815560756.77</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>51</v>
@@ -4428,52 +4434,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P49" s="12">
-        <v>9.5458207773439913E-2</v>
+        <v>0.11615419397894375</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.18884873513587705</v>
       </c>
       <c r="R49" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>283</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>341</v>
+        <v>150</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="E50">
-        <v>23.3</v>
+        <v>3.98</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>242187190272</v>
+        <v>5712931840</v>
       </c>
       <c r="H50" s="6">
-        <v>36.450000000000003</v>
+        <v>7.92</v>
       </c>
       <c r="I50" s="6">
-        <v>19.239999999999998</v>
+        <v>2.36</v>
       </c>
       <c r="J50" s="12">
         <f>E50/I50-1</f>
-        <v>0.21101871101871117</v>
+        <v>0.68644067796610186</v>
       </c>
       <c r="K50" s="11">
-        <v>4.1416309012875532E-2</v>
+        <v>6.3819095477386942E-2</v>
       </c>
       <c r="L50" s="13">
-        <v>25459748125.549999</v>
+        <v>811880000</v>
       </c>
       <c r="M50" s="13">
-        <v>134815560756.77</v>
+        <v>5532140000</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>51</v>
@@ -4482,13 +4488,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P50" s="12">
-        <v>0.11810841589489145</v>
+        <v>0.15773777737132938</v>
       </c>
       <c r="Q50" s="12">
-        <v>0.18884873513587705</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R50" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -4502,13 +4508,13 @@
         <v>174</v>
       </c>
       <c r="E51">
-        <v>74.75</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>18300667904</v>
+        <v>18497005568</v>
       </c>
       <c r="H51" s="6">
         <v>95.5</v>
@@ -4518,10 +4524,10 @@
       </c>
       <c r="J51" s="12">
         <f>E51/I51-1</f>
-        <v>0.35785649409627629</v>
+        <v>0.36058128973660319</v>
       </c>
       <c r="K51" s="11">
-        <v>1.0969899665551839E-2</v>
+        <v>1.0947930574098796E-2</v>
       </c>
       <c r="L51" s="13">
         <v>526052000</v>
@@ -4536,229 +4542,229 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P51" s="12">
-        <v>0.21974017163133616</v>
+        <v>0.21742207576338402</v>
       </c>
       <c r="Q51" s="12">
         <v>9.8446219337080781E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>330</v>
       </c>
       <c r="E52">
-        <v>10.24</v>
+        <v>6.31</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>2403553280</v>
+        <v>12798446592</v>
       </c>
       <c r="H52" s="6">
-        <v>17</v>
+        <v>7.86</v>
       </c>
       <c r="I52" s="6">
-        <v>7.36</v>
+        <v>5.31</v>
       </c>
       <c r="J52" s="12">
         <f>E52/I52-1</f>
-        <v>0.39130434782608692</v>
+        <v>0.18832391713747643</v>
       </c>
       <c r="K52" s="11">
-        <v>4.1015625E-2</v>
+        <v>4.2789223454833603E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>244811000</v>
+        <v>1537565000</v>
       </c>
       <c r="M52" s="13">
-        <v>2904223000</v>
+        <v>14484935000</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O52" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.34920256444665976</v>
+        <v>0.19526514400058809</v>
       </c>
       <c r="Q52" s="12">
-        <v>8.4294835486117978E-2</v>
+        <v>0.10614925092863724</v>
       </c>
       <c r="R52" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>343</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="E53">
-        <v>50.05</v>
+        <v>20.45</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>128068943872</v>
+        <v>32638201856</v>
       </c>
       <c r="H53" s="6">
-        <v>71.7</v>
+        <v>27.5</v>
       </c>
       <c r="I53" s="6">
-        <v>43.55</v>
+        <v>16.18</v>
       </c>
       <c r="J53" s="12">
         <f>E53/I53-1</f>
-        <v>0.14925373134328357</v>
+        <v>0.26390605686032131</v>
       </c>
       <c r="K53" s="11">
-        <v>3.2767232767232772E-3</v>
+        <v>3.3545232273838634E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>1279098000</v>
+        <v>3811007000</v>
       </c>
       <c r="M53" s="13">
-        <v>4811702000</v>
+        <v>22856317000</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="O53" s="6">
-        <v>8.7546153846153842</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>7.7971808257203096E-2</v>
+        <v>0.1275006272311732</v>
       </c>
       <c r="Q53" s="12">
-        <v>0.26583067696212276</v>
+        <v>0.1667375806872122</v>
       </c>
       <c r="R53" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C54" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E54">
-        <v>20.45</v>
+        <v>10.28</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>32638201856</v>
+        <v>2412942080</v>
       </c>
       <c r="H54" s="6">
-        <v>27.5</v>
+        <v>17</v>
       </c>
       <c r="I54" s="6">
-        <v>16.18</v>
+        <v>7.36</v>
       </c>
       <c r="J54" s="12">
         <f>E54/I54-1</f>
-        <v>0.26390605686032131</v>
+        <v>0.39673913043478248</v>
       </c>
       <c r="K54" s="11">
-        <v>3.3545232273838634E-2</v>
+        <v>4.085603112840467E-2</v>
       </c>
       <c r="L54" s="13">
-        <v>3811007000</v>
+        <v>244811000</v>
       </c>
       <c r="M54" s="13">
-        <v>22856317000</v>
+        <v>2904223000</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O54" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P54" s="12">
-        <v>0.1275006272311732</v>
+        <v>0.34458772719247038</v>
       </c>
       <c r="Q54" s="12">
-        <v>0.1667375806872122</v>
+        <v>8.4294835486117978E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>329</v>
+        <v>190</v>
       </c>
       <c r="D55" t="s">
-        <v>330</v>
+        <v>109</v>
       </c>
       <c r="E55">
-        <v>6.44</v>
+        <v>49.5</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>13062123520</v>
+        <v>126661591040</v>
       </c>
       <c r="H55" s="6">
-        <v>7.86</v>
+        <v>71.7</v>
       </c>
       <c r="I55" s="6">
-        <v>5.31</v>
+        <v>43.55</v>
       </c>
       <c r="J55" s="12">
         <f>E55/I55-1</f>
-        <v>0.21280602636534862</v>
+        <v>0.13662456946039048</v>
       </c>
       <c r="K55" s="11">
-        <v>4.192546583850932E-2</v>
+        <v>3.3131313131313134E-3</v>
       </c>
       <c r="L55" s="13">
-        <v>1537565000</v>
+        <v>1279098000</v>
       </c>
       <c r="M55" s="13">
-        <v>14484935000</v>
+        <v>4811702000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="O55" s="6">
-        <v>1.0683760683760684</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P55" s="12">
-        <v>0.18933096199767332</v>
+        <v>7.8743447186556237E-2</v>
       </c>
       <c r="Q55" s="12">
-        <v>0.10614925092863724</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R55" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
@@ -4772,13 +4778,13 @@
         <v>96</v>
       </c>
       <c r="E56">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>2695529216</v>
+        <v>2643692032</v>
       </c>
       <c r="H56" s="6">
         <v>0.68</v>
@@ -4788,7 +4794,7 @@
       </c>
       <c r="J56" s="12">
         <f>E56/I56-1</f>
-        <v>0.13043478260869557</v>
+        <v>0.10869565217391308</v>
       </c>
       <c r="K56" s="11">
         <v>0</v>
@@ -4806,13 +4812,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P56" s="12">
-        <v>0.28949073626199495</v>
+        <v>0.29497107313748638</v>
       </c>
       <c r="Q56" s="12">
         <v>8.5775443346640556E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
@@ -4826,13 +4832,13 @@
         <v>337</v>
       </c>
       <c r="E57">
-        <v>5.68</v>
+        <v>5.54</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>7283123200</v>
+        <v>7103609344</v>
       </c>
       <c r="H57" s="6">
         <v>5.92</v>
@@ -4842,10 +4848,10 @@
       </c>
       <c r="J57" s="12">
         <f>E57/I57-1</f>
-        <v>0.69047619047619047</v>
+        <v>0.64880952380952395</v>
       </c>
       <c r="K57" s="11">
-        <v>4.5774647887323945E-2</v>
+        <v>4.6931407942238268E-2</v>
       </c>
       <c r="L57" s="13">
         <v>2871477000</v>
@@ -4860,52 +4866,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>0.15113893310484014</v>
+        <v>0.15248752062922108</v>
       </c>
       <c r="Q57" s="12">
         <v>0.1318118502166547</v>
       </c>
       <c r="R57" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="E58">
-        <v>2.23</v>
+        <v>6.02</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>9544623104</v>
+        <v>26452844544</v>
       </c>
       <c r="H58" s="6">
-        <v>2.39</v>
+        <v>6.87</v>
       </c>
       <c r="I58" s="6">
-        <v>1.33</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J58" s="12">
         <f>E58/I58-1</f>
-        <v>0.67669172932330812</v>
+        <v>0.26205450733752622</v>
       </c>
       <c r="K58" s="11">
-        <v>5.4708520179372194E-2</v>
+        <v>5.9468438538205985E-2</v>
       </c>
       <c r="L58" s="13">
-        <v>1230913000</v>
+        <v>2919921000</v>
       </c>
       <c r="M58" s="13">
-        <v>10701340000</v>
+        <v>31662140000</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>51</v>
@@ -4914,67 +4920,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.15941315287471022</v>
+        <v>0.21018313755354881</v>
       </c>
       <c r="Q58" s="12">
-        <v>0.11502419323187564</v>
+        <v>9.2221214358852555E-2</v>
       </c>
       <c r="R58" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>272</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>327</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>310</v>
+        <v>101</v>
       </c>
       <c r="E59">
-        <v>6.01</v>
+        <v>408.2</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>26408902656</v>
+        <v>515899490304</v>
       </c>
       <c r="H59" s="6">
-        <v>6.87</v>
+        <v>426.8</v>
       </c>
       <c r="I59" s="6">
-        <v>4.7699999999999996</v>
+        <v>218.4</v>
       </c>
       <c r="J59" s="12">
         <f>E59/I59-1</f>
-        <v>0.25995807127882609</v>
+        <v>0.86904761904761885</v>
       </c>
       <c r="K59" s="11">
-        <v>5.9567387687188021E-2</v>
+        <v>2.2684958353748164E-2</v>
       </c>
       <c r="L59" s="13">
-        <v>2919921000</v>
+        <v>20744000000</v>
       </c>
       <c r="M59" s="13">
-        <v>31662140000</v>
+        <v>53852000000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O59" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P59" s="12">
-        <v>0.21080725580864812</v>
+        <v>5.4186144776025971E-2</v>
       </c>
       <c r="Q59" s="12">
-        <v>9.2221214358852555E-2</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R59" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
@@ -4988,13 +4994,13 @@
         <v>324</v>
       </c>
       <c r="E60">
-        <v>6.99</v>
+        <v>6.78</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>17521483776</v>
+        <v>16995088384</v>
       </c>
       <c r="H60" s="6">
         <v>7.26</v>
@@ -5004,10 +5010,10 @@
       </c>
       <c r="J60" s="12">
         <f>E60/I60-1</f>
-        <v>0.75187969924812026</v>
+        <v>0.6992481203007519</v>
       </c>
       <c r="K60" s="11">
-        <v>4.5922746781115881E-2</v>
+        <v>4.7345132743362835E-2</v>
       </c>
       <c r="L60" s="13">
         <v>3040816000</v>
@@ -5022,106 +5028,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P60" s="12">
-        <v>0.17021532122390806</v>
+        <v>0.17504303220460088</v>
       </c>
       <c r="Q60" s="12">
         <v>0.102358453189061</v>
       </c>
       <c r="R60" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>339</v>
       </c>
       <c r="E61">
-        <v>416.8</v>
+        <v>3.78</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>526768504832</v>
+        <v>8584606720</v>
       </c>
       <c r="H61" s="6">
-        <v>426.8</v>
+        <v>5.09</v>
       </c>
       <c r="I61" s="6">
-        <v>218.4</v>
+        <v>3.34</v>
       </c>
       <c r="J61" s="12">
         <f>E61/I61-1</f>
-        <v>0.90842490842490853</v>
+        <v>0.13173652694610771</v>
       </c>
       <c r="K61" s="11">
-        <v>2.2216890595009597E-2</v>
+        <v>3.968253968253968E-2</v>
       </c>
       <c r="L61" s="13">
-        <v>20744000000</v>
+        <v>826931000</v>
       </c>
       <c r="M61" s="13">
-        <v>53852000000</v>
+        <v>5591620000</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O61" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P61" s="12">
-        <v>5.2690199316482722E-2</v>
+        <v>0.13467212416416638</v>
       </c>
       <c r="Q61" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.14788755315990715</v>
       </c>
       <c r="R61" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B62" s="1" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>338</v>
+        <v>176</v>
       </c>
       <c r="D62" t="s">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="E62">
-        <v>3.78</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>8584606720</v>
+        <v>558947368960</v>
       </c>
       <c r="H62" s="6">
-        <v>5.09</v>
+        <v>21.5</v>
       </c>
       <c r="I62" s="6">
-        <v>3.34</v>
+        <v>13.52</v>
       </c>
       <c r="J62" s="12">
         <f>E62/I62-1</f>
-        <v>0.13173652694610771</v>
+        <v>0.50517751479289963</v>
       </c>
       <c r="K62" s="11">
-        <v>3.968253968253968E-2</v>
+        <v>1.8673218673218674E-2</v>
       </c>
       <c r="L62" s="13">
-        <v>826931000</v>
+        <v>52374992116</v>
       </c>
       <c r="M62" s="13">
-        <v>5591620000</v>
+        <v>269573093476</v>
       </c>
       <c r="N62" s="9" t="s">
         <v>51</v>
@@ -5130,52 +5136,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>0.13467212416416638</v>
+        <v>8.1899116146847278E-2</v>
       </c>
       <c r="Q62" s="12">
-        <v>0.14788755315990715</v>
+        <v>0.19428864891763736</v>
       </c>
       <c r="R62" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
-        <v>133</v>
+        <v>374</v>
       </c>
       <c r="C63" t="s">
-        <v>176</v>
+        <v>376</v>
       </c>
       <c r="D63" t="s">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="E63">
-        <v>20.85</v>
+        <v>1.93</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>585224093696</v>
+        <v>4123502848</v>
       </c>
       <c r="H63" s="6">
-        <v>21.5</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I63" s="6">
-        <v>13.52</v>
+        <v>0.99</v>
       </c>
       <c r="J63" s="12">
         <f>E63/I63-1</f>
-        <v>0.54215976331360971</v>
+        <v>0.94949494949494939</v>
       </c>
       <c r="K63" s="11">
-        <v>1.8225419664268584E-2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="13">
-        <v>52374992116</v>
+        <v>-732033000</v>
       </c>
       <c r="M63" s="13">
-        <v>269573093476</v>
+        <v>7864121000</v>
       </c>
       <c r="N63" s="9" t="s">
         <v>51</v>
@@ -5184,52 +5190,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>7.8865979164598199E-2</v>
+        <v>0.79316858289861092</v>
       </c>
       <c r="Q63" s="12">
-        <v>0.19428864891763736</v>
+        <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R63" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>119</v>
+        <v>279</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>335</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E64">
-        <v>254.8</v>
+        <v>2.29</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>338415157248</v>
+        <v>9801428992</v>
       </c>
       <c r="H64" s="6">
-        <v>283.39999999999998</v>
+        <v>2.39</v>
       </c>
       <c r="I64" s="6">
-        <v>34.4</v>
+        <v>1.33</v>
       </c>
       <c r="J64" s="12">
         <f>E64/I64-1</f>
-        <v>6.4069767441860472</v>
+        <v>0.72180451127819545</v>
       </c>
       <c r="K64" s="11">
-        <v>3.1985871271585555E-3</v>
+        <v>5.3275109170305673E-2</v>
       </c>
       <c r="L64" s="13">
-        <v>4408440000</v>
+        <v>1230913000</v>
       </c>
       <c r="M64" s="13">
-        <v>10683505000</v>
+        <v>10701340000</v>
       </c>
       <c r="N64" s="9" t="s">
         <v>51</v>
@@ -5238,175 +5244,175 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P64" s="12">
-        <v>1.4147202752498436E-2</v>
+        <v>0.1546004572848656</v>
       </c>
       <c r="Q64" s="12">
-        <v>0.41263985929711272</v>
+        <v>0.11502419323187564</v>
       </c>
       <c r="R64" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>320</v>
+        <v>159</v>
       </c>
       <c r="D65" t="s">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="E65">
-        <v>7.66</v>
+        <v>259</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>13844913152</v>
+        <v>343993450496</v>
       </c>
       <c r="H65" s="6">
-        <v>8.8000000000000007</v>
+        <v>283.39999999999998</v>
       </c>
       <c r="I65" s="6">
-        <v>5.49</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="J65" s="12">
         <f>E65/I65-1</f>
-        <v>0.39526411657559191</v>
+        <v>6.4639769452449558</v>
       </c>
       <c r="K65" s="11">
-        <v>3.2637075718015662E-2</v>
+        <v>3.1467181467181465E-3</v>
       </c>
       <c r="L65" s="13">
-        <v>2897428000</v>
+        <v>4408440000</v>
       </c>
       <c r="M65" s="13">
-        <v>25970601000</v>
+        <v>10683505000</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O65" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P65" s="12">
-        <v>0.15445270231638378</v>
+        <v>1.3914062753089427E-2</v>
       </c>
       <c r="Q65" s="12">
-        <v>0.11156568921912897</v>
+        <v>0.41263985929711272</v>
       </c>
       <c r="R65" s="14">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B66" s="1" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>321</v>
       </c>
       <c r="E66">
-        <v>357</v>
+        <v>7.53</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>132375248896</v>
+        <v>13609948160</v>
       </c>
       <c r="H66" s="6">
-        <v>421.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I66" s="6">
-        <v>225.2</v>
+        <v>5.49</v>
       </c>
       <c r="J66" s="12">
         <f>E66/I66-1</f>
-        <v>0.58525754884547077</v>
+        <v>0.37158469945355188</v>
       </c>
       <c r="K66" s="11">
-        <v>2.0168067226890756E-3</v>
+        <v>3.3200531208499334E-2</v>
       </c>
       <c r="L66" s="13">
-        <v>1200000000</v>
+        <v>2897428000</v>
       </c>
       <c r="M66" s="13">
-        <v>5855000000</v>
+        <v>25970601000</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O66" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P66" s="12">
-        <v>6.3509596319243009E-2</v>
+        <v>0.15641179744992564</v>
       </c>
       <c r="Q66" s="12">
-        <v>0.20495303159692571</v>
+        <v>0.11156568921912897</v>
       </c>
       <c r="R66" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B67" s="1" t="s">
-        <v>374</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
-        <v>376</v>
+        <v>184</v>
       </c>
       <c r="D67" t="s">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="E67">
-        <v>1.79</v>
+        <v>370.6</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>3824388608</v>
+        <v>137391063040</v>
       </c>
       <c r="H67" s="6">
-        <v>2.5499999999999998</v>
+        <v>421.4</v>
       </c>
       <c r="I67" s="6">
-        <v>0.99</v>
+        <v>225.2</v>
       </c>
       <c r="J67" s="12">
         <f>E67/I67-1</f>
-        <v>0.80808080808080818</v>
+        <v>0.64564831261101263</v>
       </c>
       <c r="K67" s="11">
-        <v>0</v>
+        <v>1.9427954668105772E-3</v>
       </c>
       <c r="L67" s="13">
-        <v>-732033000</v>
+        <v>1200000000</v>
       </c>
       <c r="M67" s="13">
-        <v>7864121000</v>
+        <v>5855000000</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O67" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P67" s="12">
-        <v>0.60856022938217547</v>
+        <v>6.1391002883252832E-2</v>
       </c>
       <c r="Q67" s="12">
-        <v>-9.3085164890011229E-2</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R67" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
@@ -5420,13 +5426,13 @@
         <v>155</v>
       </c>
       <c r="E68">
-        <v>21.35</v>
+        <v>20.85</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>19660019712</v>
+        <v>19199598592</v>
       </c>
       <c r="H68" s="6">
         <v>23.35</v>
@@ -5436,10 +5442,10 @@
       </c>
       <c r="J68" s="12">
         <f>E68/I68-1</f>
-        <v>1.1565656565656566</v>
+        <v>1.106060606060606</v>
       </c>
       <c r="K68" s="11">
-        <v>3.6533957845433251E-3</v>
+        <v>3.7410071942446041E-3</v>
       </c>
       <c r="L68" s="13">
         <v>334940000</v>
@@ -5454,52 +5460,52 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P68" s="12">
-        <v>0.15303074135496528</v>
+        <v>0.15733334185040926</v>
       </c>
       <c r="Q68" s="12">
         <v>0.11071024253191752</v>
       </c>
       <c r="R68" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B69" s="1" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="E69">
-        <v>29.8</v>
+        <v>6.03</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>20612063232</v>
+        <v>4698588160</v>
       </c>
       <c r="H69" s="6">
-        <v>39.200000000000003</v>
+        <v>8.09</v>
       </c>
       <c r="I69" s="6">
-        <v>13.48</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J69" s="12">
         <f>E69/I69-1</f>
-        <v>1.2106824925816024</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="K69" s="11">
-        <v>1.5436241610738255E-2</v>
+        <v>2.8192371475953566E-2</v>
       </c>
       <c r="L69" s="13">
-        <v>1323087000</v>
+        <v>437453000</v>
       </c>
       <c r="M69" s="13">
-        <v>5952918000</v>
+        <v>4911072000</v>
       </c>
       <c r="N69" s="9" t="s">
         <v>68</v>
@@ -5508,52 +5514,52 @@
         <v>1</v>
       </c>
       <c r="P69" s="12">
-        <v>5.7338756366324739E-2</v>
+        <v>0.18158062733080144</v>
       </c>
       <c r="Q69" s="12">
-        <v>0.222258562943417</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R69" s="14">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B70" s="1" t="s">
-        <v>270</v>
+        <v>137</v>
       </c>
       <c r="C70" t="s">
-        <v>325</v>
+        <v>182</v>
       </c>
       <c r="D70" t="s">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>31.45</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>5661870080</v>
+        <v>21753335808</v>
       </c>
       <c r="H70" s="6">
-        <v>4.18</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="I70" s="6">
-        <v>1.74</v>
+        <v>13.48</v>
       </c>
       <c r="J70" s="12">
         <f>E70/I70-1</f>
-        <v>0.72413793103448287</v>
+        <v>1.3330860534124627</v>
       </c>
       <c r="K70" s="11">
-        <v>5.3333333333333337E-2</v>
+        <v>1.4626391096979333E-2</v>
       </c>
       <c r="L70" s="13">
-        <v>896597000</v>
+        <v>1323087000</v>
       </c>
       <c r="M70" s="13">
-        <v>6906279000</v>
+        <v>5952918000</v>
       </c>
       <c r="N70" s="9" t="s">
         <v>68</v>
@@ -5562,52 +5568,52 @@
         <v>1</v>
       </c>
       <c r="P70" s="12">
-        <v>0.12356220165196077</v>
+        <v>5.4636466972164843E-2</v>
       </c>
       <c r="Q70" s="12">
-        <v>0.12982345485897689</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R70" s="14">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B71" s="1" t="s">
-        <v>115</v>
+        <v>373</v>
       </c>
       <c r="C71" t="s">
-        <v>154</v>
+        <v>375</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="E71">
-        <v>56.7</v>
+        <v>11.56</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>160336265216</v>
+        <v>3041702144</v>
       </c>
       <c r="H71" s="6">
-        <v>60</v>
+        <v>15.58</v>
       </c>
       <c r="I71" s="6">
-        <v>38.4</v>
+        <v>7.51</v>
       </c>
       <c r="J71" s="12">
         <f>E71/I71-1</f>
-        <v>0.47656250000000022</v>
+        <v>0.53928095872170445</v>
       </c>
       <c r="K71" s="11">
-        <v>3.1746031746031744E-2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="13">
-        <v>8955723006</v>
+        <v>-481083000</v>
       </c>
       <c r="M71" s="13">
-        <v>47495870210</v>
+        <v>4136123000</v>
       </c>
       <c r="N71" s="9" t="s">
         <v>51</v>
@@ -5616,106 +5622,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P71" s="12">
-        <v>6.1220861282470472E-2</v>
+        <v>0.4246114618258639</v>
       </c>
       <c r="Q71" s="12">
-        <v>0.18855793075067021</v>
+        <v>-0.11631254679805218</v>
       </c>
       <c r="R71" s="14">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B72" s="1" t="s">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="C72" t="s">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="E72">
-        <v>10.76</v>
+        <v>2.98</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>2831203584</v>
+        <v>5624124416</v>
       </c>
       <c r="H72" s="6">
-        <v>15.58</v>
+        <v>4.18</v>
       </c>
       <c r="I72" s="6">
-        <v>7.4</v>
+        <v>1.74</v>
       </c>
       <c r="J72" s="12">
         <f>E72/I72-1</f>
-        <v>0.45405405405405386</v>
+        <v>0.71264367816091956</v>
       </c>
       <c r="K72" s="11">
-        <v>0</v>
+        <v>5.3691275167785234E-2</v>
       </c>
       <c r="L72" s="13">
-        <v>-481083000</v>
+        <v>896597000</v>
       </c>
       <c r="M72" s="13">
-        <v>4136123000</v>
+        <v>6906279000</v>
       </c>
       <c r="N72" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O72" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P72" s="12">
-        <v>0.36171043704754685</v>
+        <v>0.12420831108668132</v>
       </c>
       <c r="Q72" s="12">
-        <v>-0.11631254679805218</v>
+        <v>0.12982345485897689</v>
       </c>
       <c r="R72" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B73" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E73">
-        <v>22.85</v>
+        <v>57.5</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>25994616832</v>
+        <v>163077472256</v>
       </c>
       <c r="H73" s="6">
-        <v>28.75</v>
+        <v>60</v>
       </c>
       <c r="I73" s="6">
-        <v>19.52</v>
+        <v>38.4</v>
       </c>
       <c r="J73" s="12">
         <f>E73/I73-1</f>
-        <v>0.17059426229508201</v>
+        <v>0.49739583333333348</v>
       </c>
       <c r="K73" s="11">
-        <v>6.1269146608315089E-2</v>
+        <v>3.1304347826086959E-2</v>
       </c>
       <c r="L73" s="13">
-        <v>3446618000</v>
+        <v>8955723006</v>
       </c>
       <c r="M73" s="13">
-        <v>34010798000</v>
+        <v>47495870210</v>
       </c>
       <c r="N73" s="9" t="s">
         <v>51</v>
@@ -5724,175 +5730,175 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>0.14867541905307449</v>
+        <v>6.0165588734623306E-2</v>
       </c>
       <c r="Q73" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R73" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B74" s="1" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="E74">
-        <v>6.38</v>
+        <v>502</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>4971308544</v>
+        <v>4556146606080</v>
       </c>
       <c r="H74" s="6">
-        <v>8.09</v>
+        <v>547</v>
       </c>
       <c r="I74" s="6">
-        <v>4.0199999999999996</v>
+        <v>349</v>
       </c>
       <c r="J74" s="12">
         <f>E74/I74-1</f>
-        <v>0.58706467661691564</v>
+        <v>0.43839541547277938</v>
       </c>
       <c r="K74" s="11">
-        <v>2.6645768025078374E-2</v>
+        <v>8.4243027888446214E-3</v>
       </c>
       <c r="L74" s="13">
-        <v>437453000</v>
+        <v>253932000000</v>
       </c>
       <c r="M74" s="13">
-        <v>4911072000</v>
+        <v>1312163000000</v>
       </c>
       <c r="N74" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O74" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P74" s="12">
-        <v>0.16311555203503975</v>
+        <v>5.6553169400770709E-2</v>
       </c>
       <c r="Q74" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R74" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B75" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C75" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D75" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="E75">
-        <v>495.6</v>
+        <v>13.56</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>4498987679744</v>
+        <v>133768585216</v>
       </c>
       <c r="H75" s="6">
-        <v>547</v>
+        <v>13.86</v>
       </c>
       <c r="I75" s="6">
-        <v>349</v>
+        <v>5.83</v>
       </c>
       <c r="J75" s="12">
         <f>E75/I75-1</f>
-        <v>0.42005730659025797</v>
+        <v>1.32590051457976</v>
       </c>
       <c r="K75" s="11">
-        <v>8.533091202582728E-3</v>
+        <v>3.8348082595870206E-2</v>
       </c>
       <c r="L75" s="13">
-        <v>253932000000</v>
+        <v>8510100000</v>
       </c>
       <c r="M75" s="13">
-        <v>1312163000000</v>
+        <v>46117200000</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O75" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P75" s="12">
-        <v>5.7235134476659413E-2</v>
+        <v>5.7901571597518998E-2</v>
       </c>
       <c r="Q75" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.18453201842262756</v>
       </c>
       <c r="R75" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B76" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="E76">
-        <v>13.54</v>
+        <v>23.05</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>133571280896</v>
+        <v>26222139392</v>
       </c>
       <c r="H76" s="6">
-        <v>13.86</v>
+        <v>28.75</v>
       </c>
       <c r="I76" s="6">
-        <v>5.83</v>
+        <v>19.52</v>
       </c>
       <c r="J76" s="12">
         <f>E76/I76-1</f>
-        <v>1.3224699828473412</v>
+        <v>0.18084016393442637</v>
       </c>
       <c r="K76" s="11">
-        <v>3.8404726735598228E-2</v>
+        <v>6.0737527114967459E-2</v>
       </c>
       <c r="L76" s="13">
-        <v>8510100000</v>
+        <v>3446618000</v>
       </c>
       <c r="M76" s="13">
-        <v>46117200000</v>
+        <v>34010798000</v>
       </c>
       <c r="N76" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O76" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>5.79794050037373E-2</v>
+        <v>0.14732205665172873</v>
       </c>
       <c r="Q76" s="12">
-        <v>0.18453201842262756</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R76" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
@@ -5906,13 +5912,13 @@
         <v>69</v>
       </c>
       <c r="E77">
-        <v>6.08</v>
+        <v>5.94</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>9890397184</v>
+        <v>9662657536</v>
       </c>
       <c r="H77" s="6">
         <v>7.05</v>
@@ -5922,10 +5928,10 @@
       </c>
       <c r="J77" s="12">
         <f>E77/I77-1</f>
-        <v>0.4238875878220143</v>
+        <v>0.39110070257611262</v>
       </c>
       <c r="K77" s="11">
-        <v>4.6052631578947373E-2</v>
+        <v>4.7138047138047139E-2</v>
       </c>
       <c r="L77" s="13">
         <v>4094312000</v>
@@ -5940,67 +5946,67 @@
         <v>1</v>
       </c>
       <c r="P77" s="12">
-        <v>0.13509555170721232</v>
+        <v>0.13611841037247432</v>
       </c>
       <c r="Q77" s="12">
         <v>0.10878407220713927</v>
       </c>
       <c r="R77" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B78" s="1" t="s">
-        <v>31</v>
+        <v>391</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>392</v>
       </c>
       <c r="D78" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="E78">
-        <v>3.08</v>
+        <v>7.25</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>19099756544</v>
+        <v>4159354112</v>
       </c>
       <c r="H78" s="6">
-        <v>4.13</v>
+        <v>9.24</v>
       </c>
       <c r="I78" s="6">
-        <v>2.11</v>
+        <v>6.78</v>
       </c>
       <c r="J78" s="12">
         <f>E78/I78-1</f>
-        <v>0.45971563981042673</v>
+        <v>6.9321533923303758E-2</v>
       </c>
       <c r="K78" s="11">
-        <v>5.1948051948051945E-2</v>
+        <v>5.5172413793103454E-2</v>
       </c>
       <c r="L78" s="13">
-        <v>1677300000</v>
+        <v>498120000</v>
       </c>
       <c r="M78" s="13">
-        <v>11188800000</v>
+        <v>3284848000</v>
       </c>
       <c r="N78" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O78" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P78" s="12">
-        <v>8.6660350383692061E-2</v>
+        <v>9.3166915749945886E-2</v>
       </c>
       <c r="Q78" s="12">
-        <v>0.1499088374088374</v>
+        <v>0.15164171979951585</v>
       </c>
       <c r="R78" s="14">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
@@ -6014,13 +6020,13 @@
         <v>75</v>
       </c>
       <c r="E79">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>5248796160</v>
+        <v>5147206144</v>
       </c>
       <c r="H79" s="6">
         <v>10.06</v>
@@ -6030,10 +6036,10 @@
       </c>
       <c r="J79" s="12">
         <f>E79/I79-1</f>
-        <v>0.18140243902439024</v>
+        <v>0.15853658536585358</v>
       </c>
       <c r="K79" s="11">
-        <v>4.6064516129032257E-2</v>
+        <v>4.6973684210526313E-2</v>
       </c>
       <c r="L79" s="13">
         <v>618033000</v>
@@ -6048,121 +6054,121 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P79" s="12">
-        <v>0.10536437648676049</v>
+        <v>0.10710058083730889</v>
       </c>
       <c r="Q79" s="12">
         <v>0.12279555988606453</v>
       </c>
       <c r="R79" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B80" s="1" t="s">
-        <v>265</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>318</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>243</v>
+        <v>75</v>
       </c>
       <c r="E80">
-        <v>8.01</v>
+        <v>3.08</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>105676734464</v>
+        <v>19099756544</v>
       </c>
       <c r="H80" s="6">
-        <v>11</v>
+        <v>4.13</v>
       </c>
       <c r="I80" s="6">
-        <v>6.84</v>
+        <v>2.11</v>
       </c>
       <c r="J80" s="12">
         <f>E80/I80-1</f>
-        <v>0.17105263157894735</v>
+        <v>0.45971563981042673</v>
       </c>
       <c r="K80" s="11">
-        <v>0</v>
+        <v>5.1948051948051945E-2</v>
       </c>
       <c r="L80" s="13">
-        <v>1187000000</v>
+        <v>1677300000</v>
       </c>
       <c r="M80" s="13">
-        <v>10278000000</v>
+        <v>11188800000</v>
       </c>
       <c r="N80" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O80" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P80" s="12">
-        <v>0.10717856686087243</v>
+        <v>8.6660350383692061E-2</v>
       </c>
       <c r="Q80" s="12">
-        <v>0.1154893948238957</v>
+        <v>0.1499088374088374</v>
       </c>
       <c r="R80" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B81" s="1" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="D81" t="s">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="E81">
-        <v>14.46</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>60703227904</v>
+        <v>106072522752</v>
       </c>
       <c r="H81" s="6">
-        <v>15.38</v>
+        <v>11</v>
       </c>
       <c r="I81" s="6">
-        <v>10.98</v>
+        <v>6.84</v>
       </c>
       <c r="J81" s="12">
         <f>E81/I81-1</f>
-        <v>0.31693989071038264</v>
+        <v>0.17543859649122795</v>
       </c>
       <c r="K81" s="11">
-        <v>6.1272475795297369E-2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="13">
-        <v>11996000000</v>
+        <v>1187000000</v>
       </c>
       <c r="M81" s="13">
-        <v>138296000000</v>
+        <v>10278000000</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O81" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P81" s="12">
-        <v>0.14307996554792443</v>
+        <v>0.10668293584484501</v>
       </c>
       <c r="Q81" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>0.1154893948238957</v>
       </c>
       <c r="R81" s="14">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
@@ -6176,13 +6182,13 @@
         <v>77</v>
       </c>
       <c r="E82">
-        <v>14.46</v>
+        <v>14.84</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>60703227904</v>
+        <v>62298472448</v>
       </c>
       <c r="H82" s="6">
         <v>15.38</v>
@@ -6192,10 +6198,10 @@
       </c>
       <c r="J82" s="12">
         <f>E82/I82-1</f>
-        <v>0.31693989071038264</v>
+        <v>0.35154826958105634</v>
       </c>
       <c r="K82" s="11">
-        <v>6.1272475795297369E-2</v>
+        <v>5.9703504043126687E-2</v>
       </c>
       <c r="L82" s="13">
         <v>11996000000</v>
@@ -6210,106 +6216,106 @@
         <v>1</v>
       </c>
       <c r="P82" s="12">
-        <v>0.14307996554792443</v>
+        <v>0.14040841874998103</v>
       </c>
       <c r="Q82" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B83" s="1" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="D83" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E83">
-        <v>13.26</v>
+        <v>14.84</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>58883948544</v>
+        <v>62298472448</v>
       </c>
       <c r="H83" s="6">
-        <v>14.7</v>
+        <v>15.38</v>
       </c>
       <c r="I83" s="6">
-        <v>7.51</v>
+        <v>10.98</v>
       </c>
       <c r="J83" s="12">
         <f>E83/I83-1</f>
-        <v>0.76564580559254325</v>
+        <v>0.35154826958105634</v>
       </c>
       <c r="K83" s="11">
-        <v>3.3031674208144797E-2</v>
+        <v>5.9703504043126687E-2</v>
       </c>
       <c r="L83" s="13">
-        <v>3967214824.1399999</v>
+        <v>11996000000</v>
       </c>
       <c r="M83" s="13">
-        <v>41038539262.660004</v>
+        <v>138296000000</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O83" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P83" s="12">
-        <v>0.1269547433597869</v>
+        <v>0.14040841874998103</v>
       </c>
       <c r="Q83" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R83" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B84" s="1" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="D84" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="E84">
-        <v>31.9</v>
+        <v>13.86</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>71877074944</v>
+        <v>62332297216</v>
       </c>
       <c r="H84" s="6">
-        <v>61.55</v>
+        <v>14.7</v>
       </c>
       <c r="I84" s="6">
-        <v>24.85</v>
+        <v>7.51</v>
       </c>
       <c r="J84" s="12">
         <f>E84/I84-1</f>
-        <v>0.28370221327967804</v>
+        <v>0.84553928095872166</v>
       </c>
       <c r="K84" s="11">
-        <v>1.7805642633228841E-2</v>
+        <v>3.1601731601731603E-2</v>
       </c>
       <c r="L84" s="13">
-        <v>5261270000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M84" s="13">
-        <v>43208997000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N84" s="9" t="s">
         <v>51</v>
@@ -6318,160 +6324,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P84" s="12">
-        <v>7.2385110483949439E-2</v>
+        <v>0.11506944091670368</v>
       </c>
       <c r="Q84" s="12">
-        <v>0.12176329850933591</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B85" s="1" t="s">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s">
-        <v>313</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E85">
-        <v>1.99</v>
+        <v>31.65</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>1847860224</v>
+        <v>71313776640</v>
       </c>
       <c r="H85" s="6">
-        <v>2.54</v>
+        <v>61.55</v>
       </c>
       <c r="I85" s="6">
-        <v>1.72</v>
+        <v>24.85</v>
       </c>
       <c r="J85" s="12">
         <f>E85/I85-1</f>
-        <v>0.15697674418604657</v>
+        <v>0.27364185110663963</v>
       </c>
       <c r="K85" s="11">
-        <v>5.5276381909547742E-2</v>
+        <v>1.7946287519747233E-2</v>
       </c>
       <c r="L85" s="13">
-        <v>238321000</v>
+        <v>5261270000</v>
       </c>
       <c r="M85" s="13">
-        <v>6087917000</v>
+        <v>43208997000</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O85" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>0.15959509688418372</v>
+        <v>7.2914023197588759E-2</v>
       </c>
       <c r="Q85" s="12">
-        <v>3.9146558666946343E-2</v>
+        <v>0.12176329850933591</v>
       </c>
       <c r="R85" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B86" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="E86">
-        <v>49.9</v>
+        <v>1.94</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>1024941031424</v>
+        <v>1801431680</v>
       </c>
       <c r="H86" s="6">
-        <v>59.8</v>
+        <v>2.54</v>
       </c>
       <c r="I86" s="6">
-        <v>32.65</v>
+        <v>1.72</v>
       </c>
       <c r="J86" s="12">
         <f>E86/I86-1</f>
-        <v>0.52833078101071984</v>
+        <v>0.12790697674418605</v>
       </c>
       <c r="K86" s="11">
-        <v>5.1102204408817631E-2</v>
+        <v>5.6701030927835051E-2</v>
       </c>
       <c r="L86" s="13">
-        <v>189900000000</v>
+        <v>238321000</v>
       </c>
       <c r="M86" s="13">
-        <v>2315380000000</v>
+        <v>6087917000</v>
       </c>
       <c r="N86" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O86" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P86" s="12">
-        <v>0.13520298337107575</v>
+        <v>0.16471638365729493</v>
       </c>
       <c r="Q86" s="12">
-        <v>8.2016774784268678E-2</v>
+        <v>3.9146558666946343E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B87" s="1" t="s">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>67</v>
+        <v>316</v>
       </c>
       <c r="D87" t="s">
-        <v>66</v>
+        <v>308</v>
       </c>
       <c r="E87">
-        <v>53.7</v>
+        <v>49.7</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>137034342400</v>
+        <v>1032298889216</v>
       </c>
       <c r="H87" s="6">
-        <v>82.25</v>
+        <v>59.8</v>
       </c>
       <c r="I87" s="6">
-        <v>37.85</v>
+        <v>32.65</v>
       </c>
       <c r="J87" s="12">
         <f>E87/I87-1</f>
-        <v>0.41875825627476893</v>
+        <v>0.52220520673813176</v>
       </c>
       <c r="K87" s="11">
-        <v>1.9553072625698324E-2</v>
+        <v>5.1307847082494966E-2</v>
       </c>
       <c r="L87" s="13">
-        <v>6350637223.7200003</v>
+        <v>189900000000</v>
       </c>
       <c r="M87" s="13">
-        <v>57896384836.860001</v>
+        <v>2315380000000</v>
       </c>
       <c r="N87" s="9" t="s">
         <v>51</v>
@@ -6480,52 +6486,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>6.4403891896186186E-2</v>
+        <v>0.13454327719395667</v>
       </c>
       <c r="Q87" s="12">
-        <v>0.10968970241604512</v>
+        <v>8.2016774784268678E-2</v>
       </c>
       <c r="R87" s="14">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B88" s="1" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="E88">
-        <v>21.2</v>
+        <v>53.55</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>124497641472</v>
+        <v>135770128384</v>
       </c>
       <c r="H88" s="6">
-        <v>26.6</v>
+        <v>82.25</v>
       </c>
       <c r="I88" s="6">
-        <v>16.02</v>
+        <v>37.85</v>
       </c>
       <c r="J88" s="12">
         <f>E88/I88-1</f>
-        <v>0.3233458177278401</v>
+        <v>0.41479524438573301</v>
       </c>
       <c r="K88" s="11">
-        <v>3.3490566037735849E-2</v>
+        <v>1.9607843137254905E-2</v>
       </c>
       <c r="L88" s="13">
-        <v>10795274825</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M88" s="13">
-        <v>215275428010</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N88" s="9" t="s">
         <v>51</v>
@@ -6534,52 +6540,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>0.14232618639328251</v>
+        <v>6.5186143652232173E-2</v>
       </c>
       <c r="Q88" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R88" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B89" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D89" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="E89">
-        <v>6.63</v>
+        <v>21.45</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>47864221696</v>
+        <v>126326136832</v>
       </c>
       <c r="H89" s="6">
-        <v>10.72</v>
+        <v>26.6</v>
       </c>
       <c r="I89" s="6">
-        <v>5</v>
+        <v>16.02</v>
       </c>
       <c r="J89" s="12">
         <f>E89/I89-1</f>
-        <v>0.32600000000000007</v>
+        <v>0.33895131086142327</v>
       </c>
       <c r="K89" s="11">
-        <v>6.485671191553545E-2</v>
+        <v>3.3100233100233099E-2</v>
       </c>
       <c r="L89" s="13">
-        <v>6749146000</v>
+        <v>10795274825</v>
       </c>
       <c r="M89" s="13">
-        <v>70848374000</v>
+        <v>215275428010</v>
       </c>
       <c r="N89" s="9" t="s">
         <v>51</v>
@@ -6588,52 +6594,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P89" s="12">
-        <v>8.9624378059502088E-2</v>
+        <v>0.13918556900974152</v>
       </c>
       <c r="Q89" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R89" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B90" s="1" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="E90">
-        <v>8.8800000000000008</v>
+        <v>6.66</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>20923322368</v>
+        <v>48207273984</v>
       </c>
       <c r="H90" s="6">
-        <v>11.68</v>
+        <v>10.72</v>
       </c>
       <c r="I90" s="6">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="J90" s="12">
         <f>E90/I90-1</f>
-        <v>0.71098265895953761</v>
+        <v>0.33200000000000007</v>
       </c>
       <c r="K90" s="11">
-        <v>0</v>
+        <v>6.4564564564564567E-2</v>
       </c>
       <c r="L90" s="13">
-        <v>13493113000</v>
+        <v>6749146000</v>
       </c>
       <c r="M90" s="13">
-        <v>208027754000</v>
+        <v>70848374000</v>
       </c>
       <c r="N90" s="9" t="s">
         <v>51</v>
@@ -6642,24 +6648,24 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>0.12004757121312341</v>
+        <v>8.9243845539888608E-2</v>
       </c>
       <c r="Q90" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R90" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B91" s="1" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>315</v>
+        <v>180</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="E91">
         <v>8.9</v>
@@ -6668,80 +6674,80 @@
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>5978236416</v>
+        <v>20970444800</v>
       </c>
       <c r="H91" s="6">
-        <v>9.15</v>
+        <v>11.68</v>
       </c>
       <c r="I91" s="6">
-        <v>5.6</v>
+        <v>5.19</v>
       </c>
       <c r="J91" s="12">
         <f>E91/I91-1</f>
-        <v>0.58928571428571441</v>
+        <v>0.71483622350674358</v>
       </c>
       <c r="K91" s="11">
-        <v>5.7303370786516851E-2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="13">
-        <v>1136392000</v>
+        <v>13493113000</v>
       </c>
       <c r="M91" s="13">
-        <v>17458813000</v>
+        <v>208027754000</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O91" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P91" s="12">
-        <v>0.10723242286328752</v>
+        <v>0.12000048131470691</v>
       </c>
       <c r="Q91" s="12">
-        <v>6.5089877530620205E-2</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B92" s="1" t="s">
-        <v>129</v>
+        <v>262</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E92">
-        <v>11.88</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>89995280384</v>
+        <v>5736420352</v>
       </c>
       <c r="H92" s="6">
-        <v>11.9</v>
+        <v>9.15</v>
       </c>
       <c r="I92" s="6">
-        <v>8.8800000000000008</v>
+        <v>5.6</v>
       </c>
       <c r="J92" s="12">
         <f>E92/I92-1</f>
-        <v>0.33783783783783772</v>
+        <v>0.52499999999999991</v>
       </c>
       <c r="K92" s="11">
-        <v>6.6329966329966322E-2</v>
+        <v>5.9718969555035133E-2</v>
       </c>
       <c r="L92" s="13">
-        <v>8154000000</v>
+        <v>1136392000</v>
       </c>
       <c r="M92" s="13">
-        <v>79588000000</v>
+        <v>17458813000</v>
       </c>
       <c r="N92" s="9" t="s">
         <v>68</v>
@@ -6750,121 +6756,121 @@
         <v>1</v>
       </c>
       <c r="P92" s="12">
-        <v>6.2100031896550424E-2</v>
+        <v>0.10973642034761508</v>
       </c>
       <c r="Q92" s="12">
-        <v>0.10245263104990703</v>
+        <v>6.5089877530620205E-2</v>
       </c>
       <c r="R92" s="14">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B93" s="1" t="s">
-        <v>127</v>
+        <v>261</v>
       </c>
       <c r="C93" t="s">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="D93" t="s">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="E93">
-        <v>9.7100000000000009</v>
+        <v>1.63</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>30295199744</v>
+        <v>62819385344</v>
       </c>
       <c r="H93" s="6">
-        <v>10.1</v>
+        <v>2.08</v>
       </c>
       <c r="I93" s="6">
-        <v>5.6</v>
+        <v>1.18</v>
       </c>
       <c r="J93" s="12">
         <f>E93/I93-1</f>
-        <v>0.73392857142857171</v>
+        <v>0.3813559322033897</v>
       </c>
       <c r="K93" s="11">
-        <v>3.2955715756951595E-2</v>
+        <v>3.4355828220858899E-2</v>
       </c>
       <c r="L93" s="13">
-        <v>1990539000</v>
+        <v>12616717000</v>
       </c>
       <c r="M93" s="13">
-        <v>18620709000</v>
+        <v>231208465000</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O93" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P93" s="12">
-        <v>6.0230742778892156E-2</v>
+        <v>0.12617790814124877</v>
       </c>
       <c r="Q93" s="12">
-        <v>0.10689920561026972</v>
+        <v>5.4568577322633927E-2</v>
       </c>
       <c r="R93" s="14">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B94" s="1" t="s">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="D94" t="s">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="E94">
-        <v>1.68</v>
+        <v>12.16</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>64948293632</v>
+        <v>92116377600</v>
       </c>
       <c r="H94" s="6">
-        <v>2.08</v>
+        <v>12.16</v>
       </c>
       <c r="I94" s="6">
-        <v>1.18</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="J94" s="12">
         <f>E94/I94-1</f>
-        <v>0.42372881355932202</v>
+        <v>0.36936936936936937</v>
       </c>
       <c r="K94" s="11">
-        <v>3.3333333333333333E-2</v>
+        <v>6.4802631578947376E-2</v>
       </c>
       <c r="L94" s="13">
-        <v>12616717000</v>
+        <v>8154000000</v>
       </c>
       <c r="M94" s="13">
-        <v>231208465000</v>
+        <v>79588000000</v>
       </c>
       <c r="N94" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O94" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P94" s="12">
-        <v>0.12371253049885192</v>
+        <v>6.1112811870355915E-2</v>
       </c>
       <c r="Q94" s="12">
-        <v>5.4568577322633927E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R94" s="14">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
@@ -6884,7 +6890,7 @@
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>728101945344</v>
+        <v>729047564288</v>
       </c>
       <c r="H95" s="6">
         <v>6.98</v>
@@ -6912,106 +6918,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P95" s="12">
-        <v>6.751566435706656E-2</v>
+        <v>6.7425248481168668E-2</v>
       </c>
       <c r="Q95" s="12">
         <v>9.605709580489824E-2</v>
       </c>
       <c r="R95" s="14">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B96" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E96">
-        <v>9.27</v>
+        <v>10.64</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>283643478016</v>
+        <v>33196802048</v>
       </c>
       <c r="H96" s="6">
-        <v>11.56</v>
+        <v>10.8</v>
       </c>
       <c r="I96" s="6">
-        <v>5.88</v>
+        <v>5.6</v>
       </c>
       <c r="J96" s="12">
         <f>E96/I96-1</f>
-        <v>0.57653061224489788</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="K96" s="11">
-        <v>0</v>
+        <v>3.007518796992481E-2</v>
       </c>
       <c r="L96" s="13">
-        <v>26994000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M96" s="13">
-        <v>363169000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O96" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P96" s="12">
-        <v>9.75303809494521E-2</v>
+        <v>5.5369410412929997E-2</v>
       </c>
       <c r="Q96" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R96" s="14">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B97" s="1" t="s">
-        <v>259</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
-        <v>312</v>
+        <v>161</v>
       </c>
       <c r="D97" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E97">
-        <v>9.48</v>
+        <v>9.24</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>24024877056</v>
+        <v>282725515264</v>
       </c>
       <c r="H97" s="6">
-        <v>13.78</v>
+        <v>11.56</v>
       </c>
       <c r="I97" s="6">
-        <v>5.44</v>
+        <v>5.88</v>
       </c>
       <c r="J97" s="12">
         <f>E97/I97-1</f>
-        <v>0.74264705882352944</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K97" s="11">
-        <v>3.164556962025316E-2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="13">
-        <v>9652467000</v>
+        <v>26994000000</v>
       </c>
       <c r="M97" s="13">
-        <v>173514401000</v>
+        <v>363169000000</v>
       </c>
       <c r="N97" s="9" t="s">
         <v>51</v>
@@ -7020,13 +7026,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>0.10569802748343256</v>
+        <v>9.7834094251568249E-2</v>
       </c>
       <c r="Q97" s="12">
-        <v>5.5629198178196171E-2</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
@@ -7040,13 +7046,13 @@
         <v>171</v>
       </c>
       <c r="E98">
-        <v>49.3</v>
+        <v>48</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>188820979712</v>
+        <v>183841914880</v>
       </c>
       <c r="H98" s="6">
         <v>52.95</v>
@@ -7056,10 +7062,10 @@
       </c>
       <c r="J98" s="12">
         <f>E98/I98-1</f>
-        <v>0.33604336043360439</v>
+        <v>0.30081300813008127</v>
       </c>
       <c r="K98" s="11">
-        <v>4.4665314401622719E-2</v>
+        <v>4.5874999999999999E-2</v>
       </c>
       <c r="L98" s="13">
         <v>41737000000</v>
@@ -7074,52 +7080,52 @@
         <v>1</v>
       </c>
       <c r="P98" s="12">
-        <v>0.10640435580136998</v>
+        <v>0.10777237889220671</v>
       </c>
       <c r="Q98" s="12">
         <v>5.2504192208844336E-2</v>
       </c>
       <c r="R98" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B99" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D99" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="E99">
-        <v>5.5</v>
+        <v>9.77</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>113532649472</v>
+        <v>24759818240</v>
       </c>
       <c r="H99" s="6">
-        <v>7.03</v>
+        <v>13.78</v>
       </c>
       <c r="I99" s="6">
-        <v>4.22</v>
+        <v>5.44</v>
       </c>
       <c r="J99" s="12">
         <f>E99/I99-1</f>
-        <v>0.30331753554502372</v>
+        <v>0.7959558823529409</v>
       </c>
       <c r="K99" s="11">
-        <v>5.4545454545454543E-2</v>
+        <v>3.0706243602865915E-2</v>
       </c>
       <c r="L99" s="13">
-        <v>42109966000</v>
+        <v>9652467000</v>
       </c>
       <c r="M99" s="13">
-        <v>746176876000</v>
+        <v>173514401000</v>
       </c>
       <c r="N99" s="9" t="s">
         <v>51</v>
@@ -7128,13 +7134,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>0.10045474981002418</v>
+        <v>0.1049077771719794</v>
       </c>
       <c r="Q99" s="12">
-        <v>5.643429507724386E-2</v>
+        <v>5.5629198178196171E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
@@ -7188,100 +7194,100 @@
         <v>3.1227495254580313E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B101" s="1" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="C101" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D101" t="s">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="E101">
-        <v>35.4</v>
+        <v>5.51</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>123892219904</v>
+        <v>113926422528</v>
       </c>
       <c r="H101" s="6">
-        <v>37.25</v>
+        <v>7.03</v>
       </c>
       <c r="I101" s="6">
-        <v>28.1</v>
+        <v>4.22</v>
       </c>
       <c r="J101" s="12">
         <f>E101/I101-1</f>
-        <v>0.25978647686832734</v>
+        <v>0.3056872037914693</v>
       </c>
       <c r="K101" s="11">
-        <v>4.9152542372881358E-2</v>
+        <v>5.4446460980036297E-2</v>
       </c>
       <c r="L101" s="13">
-        <v>16863000000</v>
+        <v>42109966000</v>
       </c>
       <c r="M101" s="13">
-        <v>448320000000</v>
+        <v>746176876000</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O101" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P101" s="12">
-        <v>0.11593258743914125</v>
+        <v>0.10036650356687733</v>
       </c>
       <c r="Q101" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>5.643429507724386E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D102" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E102">
-        <v>5.36</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>41492082688</v>
+        <v>121442369536</v>
       </c>
       <c r="H102" s="6">
-        <v>5.49</v>
+        <v>37.25</v>
       </c>
       <c r="I102" s="6">
-        <v>3.87</v>
+        <v>28.1</v>
       </c>
       <c r="J102" s="12">
         <f>E102/I102-1</f>
-        <v>0.38501291989664077</v>
+        <v>0.23487544483985778</v>
       </c>
       <c r="K102" s="11">
-        <v>7.145522388059701E-2</v>
+        <v>5.0144092219020171E-2</v>
       </c>
       <c r="L102" s="13">
-        <v>5474000000</v>
+        <v>16863000000</v>
       </c>
       <c r="M102" s="13">
-        <v>59407000000</v>
+        <v>448320000000</v>
       </c>
       <c r="N102" s="9" t="s">
         <v>68</v>
@@ -7290,268 +7296,268 @@
         <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>5.8768534441434581E-2</v>
+        <v>0.1179186491718056</v>
       </c>
       <c r="Q102" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B103" s="1" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="C103" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="D103" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E103">
-        <v>1.6</v>
+        <v>5.55</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>8740047872</v>
+        <v>42962886656</v>
       </c>
       <c r="H103" s="6">
-        <v>1.82</v>
+        <v>5.59</v>
       </c>
       <c r="I103" s="6">
-        <v>0.81</v>
+        <v>3.87</v>
       </c>
       <c r="J103" s="12">
         <f>E103/I103-1</f>
-        <v>0.97530864197530853</v>
+        <v>0.43410852713178283</v>
       </c>
       <c r="K103" s="11">
-        <v>2.1250000000000002E-2</v>
+        <v>6.9009009009009012E-2</v>
       </c>
       <c r="L103" s="13">
-        <v>1384865000</v>
+        <v>5474000000</v>
       </c>
       <c r="M103" s="13">
-        <v>23827484000</v>
+        <v>59407000000</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O103" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P103" s="12">
-        <v>7.4523798402907529E-2</v>
+        <v>5.7854977567373143E-2</v>
       </c>
       <c r="Q103" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B104" s="1" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="D104" t="s">
-        <v>171</v>
+        <v>93</v>
       </c>
       <c r="E104">
-        <v>25.35</v>
+        <v>1.63</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>28095660032</v>
+        <v>8903923712</v>
       </c>
       <c r="H104" s="6">
-        <v>25.4</v>
+        <v>1.82</v>
       </c>
       <c r="I104" s="6">
-        <v>14.52</v>
+        <v>0.81</v>
       </c>
       <c r="J104" s="12">
         <f>E104/I104-1</f>
-        <v>0.74586776859504145</v>
+        <v>1.0123456790123453</v>
       </c>
       <c r="K104" s="11">
-        <v>3.7080867850098613E-2</v>
+        <v>2.0858895705521477E-2</v>
       </c>
       <c r="L104" s="13">
-        <v>3838344000</v>
+        <v>1384865000</v>
       </c>
       <c r="M104" s="13">
-        <v>81520873000</v>
+        <v>23827484000</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O104" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P104" s="12">
-        <v>8.3599254759722658E-2</v>
+        <v>7.3913695294373277E-2</v>
       </c>
       <c r="Q104" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B105" s="1" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="D105" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="E105">
-        <v>11.28</v>
+        <v>25.4</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>198537035776</v>
+        <v>28151074816</v>
       </c>
       <c r="H105" s="6">
-        <v>12.46</v>
+        <v>26.65</v>
       </c>
       <c r="I105" s="6">
-        <v>9.1999999999999993</v>
+        <v>14.52</v>
       </c>
       <c r="J105" s="12">
         <f>E105/I105-1</f>
-        <v>0.22608695652173916</v>
+        <v>0.74931129476584024</v>
       </c>
       <c r="K105" s="11">
-        <v>3.6968085106382977E-2</v>
+        <v>3.7007874015748031E-2</v>
       </c>
       <c r="L105" s="13">
-        <v>16758000000</v>
+        <v>3838344000</v>
       </c>
       <c r="M105" s="13">
-        <v>269590000000</v>
+        <v>81520873000</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O105" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P105" s="12">
-        <v>6.0766342228791952E-2</v>
+        <v>8.3498477461101964E-2</v>
       </c>
       <c r="Q105" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B106" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C106" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E106">
-        <v>6.82</v>
+        <v>11.28</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>7116942848</v>
+        <v>198537035776</v>
       </c>
       <c r="H106" s="6">
-        <v>7</v>
+        <v>12.46</v>
       </c>
       <c r="I106" s="6">
-        <v>4.0199999999999996</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J106" s="12">
         <f>E106/I106-1</f>
-        <v>0.69651741293532354</v>
+        <v>0.22608695652173916</v>
       </c>
       <c r="K106" s="11">
-        <v>0</v>
+        <v>3.6968085106382977E-2</v>
       </c>
       <c r="L106" s="13">
-        <v>303335000</v>
+        <v>16758000000</v>
       </c>
       <c r="M106" s="13">
-        <v>3620162000</v>
+        <v>269590000000</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O106" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P106" s="12">
-        <v>5.0362894360896727E-2</v>
+        <v>6.0766342228791952E-2</v>
       </c>
       <c r="Q106" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B107" s="1" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="D107" t="s">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="E107">
-        <v>2.36</v>
+        <v>6.85</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>10136200192</v>
+        <v>7148248576</v>
       </c>
       <c r="H107" s="6">
-        <v>3.04</v>
+        <v>7</v>
       </c>
       <c r="I107" s="6">
-        <v>1.93</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J107" s="12">
         <f>E107/I107-1</f>
-        <v>0.2227979274611398</v>
+        <v>0.70398009950248763</v>
       </c>
       <c r="K107" s="11">
-        <v>4.5338983050847458E-2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="13">
-        <v>1938532000</v>
+        <v>303335000</v>
       </c>
       <c r="M107" s="13">
-        <v>49986396000</v>
+        <v>3620162000</v>
       </c>
       <c r="N107" s="9" t="s">
         <v>68</v>
@@ -7560,52 +7566,52 @@
         <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>6.3216996017780969E-2</v>
+        <v>5.0102476266993719E-2</v>
       </c>
       <c r="Q107" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B108" s="1" t="s">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
       <c r="D108" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="E108">
-        <v>9.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>9903897600</v>
+        <v>9964399616</v>
       </c>
       <c r="H108" s="6">
-        <v>12.88</v>
+        <v>3.04</v>
       </c>
       <c r="I108" s="6">
-        <v>4.47</v>
+        <v>1.93</v>
       </c>
       <c r="J108" s="12">
         <f>E108/I108-1</f>
-        <v>1.085011185682327</v>
+        <v>0.20207253886010368</v>
       </c>
       <c r="K108" s="11">
-        <v>1.5236051502145921E-2</v>
+        <v>4.6120689655172416E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>161696000</v>
+        <v>1938532000</v>
       </c>
       <c r="M108" s="13">
-        <v>3260547000</v>
+        <v>49986396000</v>
       </c>
       <c r="N108" s="9" t="s">
         <v>68</v>
@@ -7614,52 +7620,52 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>1.6724350727474503E-2</v>
+        <v>6.3573167667339003E-2</v>
       </c>
       <c r="Q108" s="12">
-        <v>4.95916789422143E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R108" s="14">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B109" s="1" t="s">
-        <v>389</v>
+        <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>390</v>
+        <v>322</v>
       </c>
       <c r="D109" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E109">
-        <v>1.45</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>8028113408</v>
+        <v>10331874304</v>
       </c>
       <c r="H109" s="6">
-        <v>2.99</v>
+        <v>12.88</v>
       </c>
       <c r="I109" s="6">
-        <v>0.91</v>
+        <v>4.47</v>
       </c>
       <c r="J109" s="12">
         <f>E109/I109-1</f>
-        <v>0.5934065934065933</v>
+        <v>1.1744966442953024</v>
       </c>
       <c r="K109" s="11">
-        <v>1.0344827586206896E-2</v>
+        <v>1.4609053497942384E-2</v>
       </c>
       <c r="L109" s="13">
-        <v>429393000</v>
+        <v>161696000</v>
       </c>
       <c r="M109" s="13">
-        <v>18333659000</v>
+        <v>3260547000</v>
       </c>
       <c r="N109" s="9" t="s">
         <v>68</v>
@@ -7668,52 +7674,52 @@
         <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>5.2716539549671586E-2</v>
+        <v>1.6015412728627863E-2</v>
       </c>
       <c r="Q109" s="12">
-        <v>2.3421020321148112E-2</v>
+        <v>4.95916789422143E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B110" s="1" t="s">
-        <v>114</v>
+        <v>389</v>
       </c>
       <c r="C110" t="s">
-        <v>152</v>
+        <v>390</v>
       </c>
       <c r="D110" t="s">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="E110">
-        <v>14.76</v>
+        <v>1.51</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>15158667264</v>
+        <v>8360310784</v>
       </c>
       <c r="H110" s="6">
-        <v>14.98</v>
+        <v>2.99</v>
       </c>
       <c r="I110" s="6">
-        <v>10.36</v>
+        <v>0.91</v>
       </c>
       <c r="J110" s="12">
         <f>E110/I110-1</f>
-        <v>0.42471042471042475</v>
+        <v>0.65934065934065922</v>
       </c>
       <c r="K110" s="11">
-        <v>7.3170731707317083E-2</v>
+        <v>9.9337748344370865E-3</v>
       </c>
       <c r="L110" s="13">
-        <v>984000000</v>
+        <v>429393000</v>
       </c>
       <c r="M110" s="13">
-        <v>101944000000</v>
+        <v>18333659000</v>
       </c>
       <c r="N110" s="9" t="s">
         <v>68</v>
@@ -7722,241 +7728,253 @@
         <v>1</v>
       </c>
       <c r="P110" s="12">
-        <v>2.4533350697573553E-2</v>
+        <v>5.0650805134496227E-2</v>
       </c>
       <c r="Q110" s="12">
-        <v>9.6523581574197593E-3</v>
+        <v>2.3421020321148112E-2</v>
       </c>
       <c r="R110" s="14">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B111" s="1" t="s">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="C111" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="D111" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="E111">
-        <v>43.8</v>
+        <v>15.08</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>451350233088</v>
+        <v>15487310848</v>
       </c>
       <c r="H111" s="6">
-        <v>59.7</v>
+        <v>15.14</v>
       </c>
       <c r="I111" s="6">
-        <v>15.24</v>
+        <v>10.36</v>
       </c>
       <c r="J111" s="12">
         <f>E111/I111-1</f>
-        <v>1.8740157480314958</v>
+        <v>0.45559845559845558</v>
       </c>
       <c r="K111" s="11">
-        <v>0</v>
+        <v>7.161803713527852E-2</v>
       </c>
       <c r="L111" s="13">
-        <v>984027000</v>
+        <v>984000000</v>
       </c>
       <c r="M111" s="13">
-        <v>32183526000</v>
+        <v>101944000000</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O111" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P111" s="12">
-        <v>1.5397715288321236E-2</v>
+        <v>2.4333962357159761E-2</v>
       </c>
       <c r="Q111" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>9.6523581574197593E-3</v>
       </c>
       <c r="R111" s="14">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B112" s="1" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="D112" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="E112">
-        <v>28.95</v>
+        <v>44.3</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>29560555520</v>
+        <v>454030688256</v>
       </c>
       <c r="H112" s="6">
-        <v>36</v>
+        <v>59.7</v>
       </c>
       <c r="I112" s="6">
-        <v>22.4</v>
+        <v>15.24</v>
       </c>
       <c r="J112" s="12">
         <f>E112/I112-1</f>
-        <v>0.29241071428571441</v>
+        <v>1.9068241469816272</v>
       </c>
       <c r="K112" s="11">
         <v>0</v>
       </c>
       <c r="L112" s="13">
-        <v>-90314000</v>
+        <v>984027000</v>
       </c>
       <c r="M112" s="13">
-        <v>18374441000</v>
+        <v>32183526000</v>
       </c>
       <c r="N112" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O112" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P112" s="12">
-        <v>-3.6756780125896493E-3</v>
+        <v>1.5314213482591913E-2</v>
       </c>
       <c r="Q112" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>3.0575487595734537E-2</v>
       </c>
       <c r="R112" s="14">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="113" spans="2:15" x14ac:dyDescent="0.5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B113" s="1" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="D113" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="E113">
-        <v>34.15</v>
+        <v>29.1</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>361061122048</v>
+        <v>29713719296</v>
       </c>
       <c r="H113" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I113" s="6">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="J113" s="12">
         <f>E113/I113-1</f>
-        <v>0.58837209302325566</v>
+        <v>0.29910714285714302</v>
       </c>
       <c r="K113" s="11">
-        <v>5.8243045387994151E-2</v>
+        <v>0</v>
+      </c>
+      <c r="L113" s="13">
+        <v>-90314000</v>
       </c>
       <c r="M113" s="13">
-        <v>415994000000</v>
+        <v>18374441000</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O113" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="2:15" x14ac:dyDescent="0.5">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P113" s="12">
+        <v>-3.6543561486810142E-3</v>
+      </c>
+      <c r="Q113" s="12">
+        <v>-4.9151971480384084E-3</v>
+      </c>
+      <c r="R113" s="14">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="114" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B114" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C114" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D114" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E114">
-        <v>7.36</v>
+        <v>34.6</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>725868216320</v>
+        <v>365818871808</v>
       </c>
       <c r="H114" s="6">
-        <v>7.62</v>
+        <v>37</v>
       </c>
       <c r="I114" s="6">
-        <v>5.08</v>
+        <v>21.5</v>
       </c>
       <c r="J114" s="12">
         <f>E114/I114-1</f>
-        <v>0.44881889763779537</v>
+        <v>0.60930232558139541</v>
       </c>
       <c r="K114" s="11">
-        <v>5.1494565217391305E-2</v>
+        <v>5.7485549132947976E-2</v>
       </c>
       <c r="M114" s="13">
-        <v>2314289000000</v>
+        <v>415994000000</v>
       </c>
       <c r="N114" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O114" s="6">
-        <v>1.0683760683760684</v>
-      </c>
-    </row>
-    <row r="115" spans="2:15" x14ac:dyDescent="0.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B115" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C115" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D115" t="s">
         <v>231</v>
       </c>
       <c r="E115">
-        <v>6.07</v>
+        <v>7.34</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>2698145431552</v>
+        <v>736642465792</v>
       </c>
       <c r="H115" s="6">
-        <v>6.48</v>
+        <v>7.62</v>
       </c>
       <c r="I115" s="6">
-        <v>4.0599999999999996</v>
+        <v>5.08</v>
       </c>
       <c r="J115" s="12">
         <f>E115/I115-1</f>
-        <v>0.49507389162561588</v>
+        <v>0.4448818897637794</v>
       </c>
       <c r="K115" s="11">
-        <v>5.074135090609555E-2</v>
+        <v>5.1634877384196184E-2</v>
       </c>
       <c r="M115" s="13">
-        <v>6434377000000</v>
+        <v>2314289000000</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>51</v>
@@ -7965,40 +7983,40 @@
         <v>1.0683760683760684</v>
       </c>
     </row>
-    <row r="116" spans="2:15" x14ac:dyDescent="0.5">
+    <row r="116" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B116" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D116" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E116">
-        <v>5.51</v>
+        <v>6.13</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>714343972864</v>
+        <v>2820498784256</v>
       </c>
       <c r="H116" s="6">
-        <v>5.64</v>
+        <v>6.48</v>
       </c>
       <c r="I116" s="6">
-        <v>3.89</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J116" s="12">
         <f>E116/I116-1</f>
-        <v>0.41645244215938293</v>
+        <v>0.50985221674876868</v>
       </c>
       <c r="K116" s="11">
-        <v>0</v>
+        <v>5.0244698205546494E-2</v>
       </c>
       <c r="M116" s="13">
-        <v>1271649000000</v>
+        <v>6434377000000</v>
       </c>
       <c r="N116" s="9" t="s">
         <v>51</v>
@@ -8007,40 +8025,40 @@
         <v>1.0683760683760684</v>
       </c>
     </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.5">
+    <row r="117" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B117" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C117" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D117" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E117">
-        <v>8.1</v>
+        <v>5.69</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G117" s="7">
-        <v>2172436348928</v>
+        <v>745543630848</v>
       </c>
       <c r="H117" s="6">
-        <v>8.1999999999999993</v>
+        <v>5.69</v>
       </c>
       <c r="I117" s="6">
-        <v>5.23</v>
+        <v>3.89</v>
       </c>
       <c r="J117" s="12">
         <f>E117/I117-1</f>
-        <v>0.54875717017208392</v>
+        <v>0.46272493573264795</v>
       </c>
       <c r="K117" s="11">
-        <v>4.9753086419753088E-2</v>
+        <v>0</v>
       </c>
       <c r="M117" s="13">
-        <v>6128626000000</v>
+        <v>1271649000000</v>
       </c>
       <c r="N117" s="9" t="s">
         <v>51</v>
@@ -8049,40 +8067,40 @@
         <v>1.0683760683760684</v>
       </c>
     </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.5">
+    <row r="118" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B118" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C118" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D118" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E118">
-        <v>7.59</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="7">
-        <v>487956545536</v>
+        <v>2198501982208</v>
       </c>
       <c r="H118" s="6">
-        <v>7.97</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="I118" s="6">
-        <v>4.26</v>
+        <v>5.23</v>
       </c>
       <c r="J118" s="12">
         <f>E118/I118-1</f>
-        <v>0.78169014084507049</v>
+        <v>0.56787762906309736</v>
       </c>
       <c r="K118" s="11">
-        <v>4.6772068511198944E-2</v>
+        <v>4.9146341463414643E-2</v>
       </c>
       <c r="M118" s="13">
-        <v>2066897000000</v>
+        <v>6128626000000</v>
       </c>
       <c r="N118" s="9" t="s">
         <v>51</v>
@@ -8091,9 +8109,51 @@
         <v>1.0683760683760684</v>
       </c>
     </row>
+    <row r="119" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B119" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C119" t="s">
+        <v>235</v>
+      </c>
+      <c r="D119" t="s">
+        <v>229</v>
+      </c>
+      <c r="E119">
+        <v>7.84</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G119" s="7">
+        <v>517655592960</v>
+      </c>
+      <c r="H119" s="6">
+        <v>7.97</v>
+      </c>
+      <c r="I119" s="6">
+        <v>4.26</v>
+      </c>
+      <c r="J119" s="12">
+        <f>E119/I119-1</f>
+        <v>0.84037558685446023</v>
+      </c>
+      <c r="K119" s="11">
+        <v>4.5280612244897961E-2</v>
+      </c>
+      <c r="M119" s="13">
+        <v>2066897000000</v>
+      </c>
+      <c r="N119" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O119" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:R20" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R118">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R119">
       <sortCondition ref="R1:R20"/>
     </sortState>
   </autoFilter>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F1FADD-4A6A-4A7A-8F54-141D028E49F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D0FF65-BF30-4DD8-BC93-F53436035885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="395">
   <si>
     <t>Ticker</t>
   </si>
@@ -1278,6 +1278,12 @@
   </si>
   <si>
     <t>CAFE DE CORAL H</t>
+  </si>
+  <si>
+    <t>0083.HK</t>
+  </si>
+  <si>
+    <t>2331.HK</t>
   </si>
 </sst>
 </file>
@@ -1775,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V119"/>
+  <dimension ref="B1:V121"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -1853,41 +1859,41 @@
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>2.97</v>
+        <v>13.82</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>2685441280</v>
+        <v>247295082496</v>
       </c>
       <c r="H2" s="6">
-        <v>3.55</v>
+        <v>15.1</v>
       </c>
       <c r="I2" s="6">
-        <v>2.3199999999999998</v>
+        <v>9.52</v>
       </c>
       <c r="J2" s="12">
-        <f>E2/I2-1</f>
-        <v>0.28017241379310365</v>
+        <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
+        <v>0.45168067226890773</v>
       </c>
       <c r="K2" s="11">
-        <v>5.6902356902356906E-2</v>
+        <v>0.11215629522431259</v>
       </c>
       <c r="L2" s="13">
-        <v>504294000</v>
+        <v>70144988000</v>
       </c>
       <c r="M2" s="13">
-        <v>1704754000</v>
+        <v>269343749000</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>51</v>
@@ -1896,10 +1902,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.37725857417598985</v>
+        <v>0.56796921781344512</v>
       </c>
       <c r="Q2" s="12">
-        <v>0.29581628786323422</v>
+        <v>0.26042924055386191</v>
       </c>
       <c r="R2" s="14">
         <v>1</v>
@@ -1907,41 +1913,41 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E3">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>9007048704</v>
+        <v>2748734464</v>
       </c>
       <c r="H3" s="6">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I3" s="6">
-        <v>2.36</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J3" s="12">
-        <f>E3/I3-1</f>
-        <v>0.36440677966101709</v>
+        <f t="shared" si="0"/>
+        <v>0.31034482758620707</v>
       </c>
       <c r="K3" s="11">
-        <v>4.7515527950310554E-2</v>
+        <v>5.5592105263157901E-2</v>
       </c>
       <c r="L3" s="13">
-        <v>1871151000</v>
+        <v>504294000</v>
       </c>
       <c r="M3" s="13">
-        <v>6461978000</v>
+        <v>1704754000</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>51</v>
@@ -1950,52 +1956,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.41564705235097249</v>
+        <v>0.36124847109610175</v>
       </c>
       <c r="Q3" s="12">
-        <v>0.28956319566547578</v>
+        <v>0.29581628786323422</v>
       </c>
       <c r="R3" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="E4">
-        <v>13.72</v>
+        <v>3.15</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>252361572352</v>
+        <v>8923508736</v>
       </c>
       <c r="H4" s="6">
-        <v>15.1</v>
+        <v>3.35</v>
       </c>
       <c r="I4" s="6">
-        <v>9.52</v>
+        <v>2.36</v>
       </c>
       <c r="J4" s="12">
-        <f>E4/I4-1</f>
-        <v>0.4411764705882355</v>
+        <f t="shared" si="0"/>
+        <v>0.3347457627118644</v>
       </c>
       <c r="K4" s="11">
-        <v>0.1129737609329446</v>
+        <v>4.8571428571428571E-2</v>
       </c>
       <c r="L4" s="13">
-        <v>70144988000</v>
+        <v>1871151000</v>
       </c>
       <c r="M4" s="13">
-        <v>269343749000</v>
+        <v>6461978000</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>51</v>
@@ -2004,10 +2010,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.54696666717230991</v>
+        <v>0.42299422870228842</v>
       </c>
       <c r="Q4" s="12">
-        <v>0.26042924055386191</v>
+        <v>0.28956319566547578</v>
       </c>
       <c r="R4" s="14">
         <v>2</v>
@@ -2024,13 +2030,13 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>7.29</v>
+        <v>7.58</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>28445872128</v>
+        <v>29577463808</v>
       </c>
       <c r="H5" s="6">
         <v>7.8</v>
@@ -2039,11 +2045,11 @@
         <v>4.22</v>
       </c>
       <c r="J5" s="12">
-        <f>E5/I5-1</f>
-        <v>0.7274881516587679</v>
+        <f t="shared" si="0"/>
+        <v>0.79620853080568743</v>
       </c>
       <c r="K5" s="11">
-        <v>5.8984910836762687E-3</v>
+        <v>5.6728232189973606E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2058,7 +2064,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.28850038221889684</v>
+        <v>0.27373429830530244</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
@@ -2078,13 +2084,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>137.19999999999999</v>
+        <v>133.69999999999999</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>90603175936</v>
+        <v>88291868672</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2093,11 +2099,11 @@
         <v>91</v>
       </c>
       <c r="J6" s="12">
-        <f>E6/I6-1</f>
-        <v>0.50769230769230766</v>
+        <f t="shared" si="0"/>
+        <v>0.46923076923076912</v>
       </c>
       <c r="K6" s="11">
-        <v>1.4212827988338193E-2</v>
+        <v>1.4584891548242334E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2112,7 +2118,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.50209950880515886</v>
+        <v>0.53259166215192788</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
@@ -2123,41 +2129,41 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>306</v>
       </c>
       <c r="E7">
-        <v>15.32</v>
+        <v>5.64</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>140504465408</v>
+        <v>377978683392</v>
       </c>
       <c r="H7" s="6">
-        <v>17.88</v>
+        <v>6.24</v>
       </c>
       <c r="I7" s="6">
-        <v>10.6</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="J7" s="12">
-        <f>E7/I7-1</f>
-        <v>0.44528301886792465</v>
+        <f t="shared" si="0"/>
+        <v>1.2470119521912353</v>
       </c>
       <c r="K7" s="11">
-        <v>4.6932114882506523E-2</v>
+        <v>3.1914893617021274E-2</v>
       </c>
       <c r="L7" s="13">
-        <v>21175963859.630001</v>
+        <v>72477000000</v>
       </c>
       <c r="M7" s="13">
-        <v>104071284594.97</v>
+        <v>319355000000</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>51</v>
@@ -2166,10 +2172,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.20622775040833383</v>
+        <v>0.18998498234880884</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.20347556909712136</v>
+        <v>0.22694806719794586</v>
       </c>
       <c r="R7" s="14">
         <v>5</v>
@@ -2177,53 +2183,53 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>305</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>146</v>
       </c>
       <c r="E8">
-        <v>5.87</v>
+        <v>2.62</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>391967473664</v>
+        <v>13338602496</v>
       </c>
       <c r="H8" s="6">
-        <v>6.24</v>
+        <v>3.1128110000000002</v>
       </c>
       <c r="I8" s="6">
-        <v>2.5099999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="J8" s="12">
-        <f>E8/I8-1</f>
-        <v>1.3386454183266934</v>
+        <f t="shared" si="0"/>
+        <v>0.17488789237668168</v>
       </c>
       <c r="K8" s="11">
-        <v>3.0664395229982964E-2</v>
+        <v>0.11450381679389313</v>
       </c>
       <c r="L8" s="13">
-        <v>72477000000</v>
+        <v>2527643000</v>
       </c>
       <c r="M8" s="13">
-        <v>319355000000</v>
+        <v>16480074000</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O8" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.18368065870641845</v>
+        <v>0.44294875583510041</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.22694806719794586</v>
+        <v>0.15337570692947131</v>
       </c>
       <c r="R8" s="14">
         <v>6</v>
@@ -2231,41 +2237,41 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E9">
-        <v>1.48</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>2981090048</v>
+        <v>147142721536</v>
       </c>
       <c r="H9" s="6">
-        <v>1.62</v>
+        <v>17.88</v>
       </c>
       <c r="I9" s="6">
-        <v>1.1299999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="J9" s="12">
-        <f>E9/I9-1</f>
-        <v>0.30973451327433632</v>
+        <f t="shared" si="0"/>
+        <v>0.5622641509433961</v>
       </c>
       <c r="K9" s="11">
-        <v>8.0405405405405403E-2</v>
+        <v>4.3417874396135266E-2</v>
       </c>
       <c r="L9" s="13">
-        <v>929863000</v>
+        <v>21175963859.630001</v>
       </c>
       <c r="M9" s="13">
-        <v>6026676000</v>
+        <v>104071284594.97</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>51</v>
@@ -2274,118 +2280,118 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.35839592936437953</v>
+        <v>0.19446075104810709</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.15429118804462028</v>
+        <v>0.20347556909712136</v>
       </c>
       <c r="R9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>304</v>
       </c>
       <c r="E10">
-        <v>2.89</v>
+        <v>7.88</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>14713192448</v>
+        <v>185906544640</v>
       </c>
       <c r="H10" s="6">
-        <v>3.3</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="I10" s="6">
-        <v>2.23</v>
+        <v>4.58</v>
       </c>
       <c r="J10" s="12">
-        <f>E10/I10-1</f>
-        <v>0.29596412556053808</v>
+        <f t="shared" si="0"/>
+        <v>0.72052401746724892</v>
       </c>
       <c r="K10" s="11">
-        <v>0.10380622837370242</v>
+        <v>3.2360406091370558E-2</v>
       </c>
       <c r="L10" s="13">
-        <v>2527643000</v>
+        <v>29168443138.220001</v>
       </c>
       <c r="M10" s="13">
-        <v>16480074000</v>
+        <v>100996030941.41</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O10" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.35696178642832704</v>
+        <v>0.16779916976867329</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.15337570692947131</v>
+        <v>0.2888078161719172</v>
       </c>
       <c r="R10" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="D11" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="E11">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>1809683968</v>
+        <v>1970000000</v>
       </c>
       <c r="H11" s="6">
-        <v>2.77</v>
+        <v>1.97</v>
       </c>
       <c r="I11" s="6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J11" s="12">
-        <f>E11/I11-1</f>
-        <v>0.125</v>
+        <f t="shared" si="0"/>
+        <v>0.45925925925925903</v>
       </c>
       <c r="K11" s="11">
-        <v>3.9869281045751631E-2</v>
+        <v>0.1065989847715736</v>
       </c>
       <c r="L11" s="13">
-        <v>841215000</v>
+        <v>315190000</v>
       </c>
       <c r="M11" s="13">
-        <v>5774434000</v>
+        <v>607806000</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O11" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.62838192131451776</v>
+        <v>0.14737850122718005</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.14567921288909008</v>
+        <v>0.51857007005524791</v>
       </c>
       <c r="R11" s="14">
         <v>8</v>
@@ -2393,95 +2399,95 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="E12">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>1920000000</v>
+        <v>3303369984</v>
       </c>
       <c r="H12" s="6">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="I12" s="6">
-        <v>1.35</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J12" s="12">
-        <f>E12/I12-1</f>
-        <v>0.42222222222222205</v>
+        <f t="shared" si="0"/>
+        <v>0.45132743362831862</v>
       </c>
       <c r="K12" s="11">
-        <v>0.109375</v>
+        <v>7.2560975609756093E-2</v>
       </c>
       <c r="L12" s="13">
-        <v>315190000</v>
+        <v>929863000</v>
       </c>
       <c r="M12" s="13">
-        <v>607806000</v>
+        <v>6026676000</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O12" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.15090659341974669</v>
+        <v>0.32106674168545463</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.51857007005524791</v>
+        <v>0.15429118804462028</v>
       </c>
       <c r="R12" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
-        <v>299</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>357</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E13">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>10648552448</v>
+        <v>41159970816</v>
       </c>
       <c r="H13" s="6">
-        <v>5.18</v>
+        <v>7.38</v>
       </c>
       <c r="I13" s="6">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="J13" s="12">
-        <f>E13/I13-1</f>
-        <v>0.63492063492063511</v>
+        <f t="shared" si="0"/>
+        <v>0.32743362831858391</v>
       </c>
       <c r="K13" s="11">
-        <v>4.8543689320388349E-2</v>
+        <v>6.8222222222222226E-2</v>
       </c>
       <c r="L13" s="13">
-        <v>1576240000</v>
+        <v>5594372000</v>
       </c>
       <c r="M13" s="13">
-        <v>9636462000</v>
+        <v>26933044000</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>51</v>
@@ -2490,52 +2496,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.26370359409020439</v>
+        <v>0.18472040109109944</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.16357040581906512</v>
+        <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E14">
-        <v>8.2200000000000006</v>
+        <v>1.75</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>194991554560</v>
+        <v>2069900032</v>
       </c>
       <c r="H14" s="6">
-        <v>8.49</v>
+        <v>2.77</v>
       </c>
       <c r="I14" s="6">
-        <v>4.58</v>
+        <v>1.36</v>
       </c>
       <c r="J14" s="12">
-        <f>E14/I14-1</f>
-        <v>0.79475982532751099</v>
+        <f t="shared" si="0"/>
+        <v>0.28676470588235281</v>
       </c>
       <c r="K14" s="11">
-        <v>3.1021897810218975E-2</v>
+        <v>3.4857142857142857E-2</v>
       </c>
       <c r="L14" s="13">
-        <v>29168443138.220001</v>
+        <v>841215000</v>
       </c>
       <c r="M14" s="13">
-        <v>100996030941.41</v>
+        <v>5774434000</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>51</v>
@@ -2544,10 +2550,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.15997342540438997</v>
+        <v>0.53165327323452871</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.2888078161719172</v>
+        <v>0.14567921288909008</v>
       </c>
       <c r="R14" s="14">
         <v>10</v>
@@ -2555,41 +2561,41 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>357</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E15">
-        <v>4.7300000000000004</v>
+        <v>5.07</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>42888089600</v>
+        <v>10483137536</v>
       </c>
       <c r="H15" s="6">
-        <v>7.38</v>
+        <v>5.19</v>
       </c>
       <c r="I15" s="6">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="J15" s="12">
-        <f>E15/I15-1</f>
-        <v>0.39528023598820061</v>
+        <f t="shared" si="0"/>
+        <v>0.60952380952380958</v>
       </c>
       <c r="K15" s="11">
-        <v>6.4904862579281172E-2</v>
+        <v>4.9309664694280074E-2</v>
       </c>
       <c r="L15" s="13">
-        <v>5594372000</v>
+        <v>1576240000</v>
       </c>
       <c r="M15" s="13">
-        <v>26933044000</v>
+        <v>9636462000</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>51</v>
@@ -2598,160 +2604,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.17535490310883817</v>
+        <v>0.27071585229147094</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.20771406306691512</v>
+        <v>0.16357040581906512</v>
       </c>
       <c r="R15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="E16">
-        <v>14.18</v>
+        <v>15.3</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>31481585664</v>
+        <v>54988509184</v>
       </c>
       <c r="H16" s="6">
-        <v>17.059999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="I16" s="6">
-        <v>7.96</v>
+        <v>7.55</v>
       </c>
       <c r="J16" s="12">
-        <f>E16/I16-1</f>
-        <v>0.78140703517587928</v>
+        <f t="shared" si="0"/>
+        <v>1.0264900662251657</v>
       </c>
       <c r="K16" s="11">
-        <v>7.8984485190409043E-2</v>
+        <v>2.2875816993464051E-2</v>
       </c>
       <c r="L16" s="13">
-        <v>5451928473.2399998</v>
+        <v>25585077000</v>
       </c>
       <c r="M16" s="13">
-        <v>25994816572.18</v>
+        <v>167756547000</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O16" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.16667152274822397</v>
+        <v>0.27592878551536126</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.20973136925592797</v>
+        <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="E17">
-        <v>15.72</v>
+        <v>15.52</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>56497995776</v>
+        <v>32660598784</v>
       </c>
       <c r="H17" s="6">
-        <v>16.600000000000001</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I17" s="6">
-        <v>7.55</v>
+        <v>7.96</v>
       </c>
       <c r="J17" s="12">
-        <f>E17/I17-1</f>
-        <v>1.0821192052980133</v>
+        <f t="shared" si="0"/>
+        <v>0.94974874371859297</v>
       </c>
       <c r="K17" s="11">
-        <v>2.2264631043256995E-2</v>
+        <v>7.2164948453608255E-2</v>
       </c>
       <c r="L17" s="13">
-        <v>25585077000</v>
+        <v>5451928473.2399998</v>
       </c>
       <c r="M17" s="13">
-        <v>167756547000</v>
+        <v>25994816572.18</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O17" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.27150877391270867</v>
+        <v>0.16123204623099219</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.15251313559762292</v>
+        <v>0.20973136925592797</v>
       </c>
       <c r="R17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E18">
-        <v>7.59</v>
+        <v>23.7</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>97381220352</v>
+        <v>62879420416</v>
       </c>
       <c r="H18" s="6">
-        <v>7.8</v>
+        <v>26.15</v>
       </c>
       <c r="I18" s="6">
-        <v>4.84</v>
+        <v>15.7</v>
       </c>
       <c r="J18" s="12">
-        <f>E18/I18-1</f>
-        <v>0.56818181818181812</v>
+        <f t="shared" si="0"/>
+        <v>0.50955414012738864</v>
       </c>
       <c r="K18" s="11">
-        <v>8.4321475625823462E-3</v>
+        <v>1.1476793248945148E-2</v>
       </c>
       <c r="L18" s="13">
-        <v>2553000000</v>
+        <v>1069250000</v>
       </c>
       <c r="M18" s="13">
-        <v>13971000000</v>
+        <v>2571093000</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>72</v>
@@ -2760,484 +2766,484 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P18" s="12">
-        <v>0.17817563253338567</v>
+        <v>0.13675631647331854</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.18273566673824351</v>
+        <v>0.41587371596437778</v>
       </c>
       <c r="R18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>351</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E19">
-        <v>6.21</v>
+        <v>7.73</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>7734058496</v>
+        <v>99177447424</v>
       </c>
       <c r="H19" s="6">
-        <v>8.6</v>
+        <v>7.88</v>
       </c>
       <c r="I19" s="6">
-        <v>3.46</v>
+        <v>4.84</v>
       </c>
       <c r="J19" s="12">
-        <f>E19/I19-1</f>
-        <v>0.7947976878612717</v>
+        <f t="shared" si="0"/>
+        <v>0.5971074380165291</v>
       </c>
       <c r="K19" s="11">
-        <v>2.2705314009661835E-2</v>
+        <v>8.2794307891332474E-3</v>
       </c>
       <c r="L19" s="13">
-        <v>921702000</v>
+        <v>2553000000</v>
       </c>
       <c r="M19" s="13">
-        <v>5262544000</v>
+        <v>13971000000</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O19" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P19" s="12">
-        <v>0.18660108134637093</v>
+        <v>0.17531850359793735</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.17514380877385538</v>
+        <v>0.18273566673824351</v>
       </c>
       <c r="R19" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>25.1</v>
+        <v>0.76</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>66593812480</v>
+        <v>1663267584</v>
       </c>
       <c r="H20" s="6">
-        <v>26.15</v>
+        <v>0.82</v>
       </c>
       <c r="I20" s="6">
-        <v>15.7</v>
+        <v>0.42</v>
       </c>
       <c r="J20" s="12">
-        <f>E20/I20-1</f>
-        <v>0.59872611464968162</v>
+        <f t="shared" si="0"/>
+        <v>0.80952380952380953</v>
       </c>
       <c r="K20" s="11">
-        <v>1.0836653386454183E-2</v>
+        <v>4.8684210526315788E-2</v>
       </c>
       <c r="L20" s="13">
-        <v>1069250000</v>
+        <v>219938000</v>
       </c>
       <c r="M20" s="13">
-        <v>2571093000</v>
+        <v>1520292000</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O20" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>0.12880167273348653</v>
+        <v>0.29986224591557764</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.41587371596437778</v>
+        <v>0.14466826109721026</v>
       </c>
       <c r="R20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E21">
-        <v>7.8</v>
+        <v>14.34</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>67540205568</v>
+        <v>12000945152</v>
       </c>
       <c r="H21" s="6">
-        <v>9.09</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I21" s="6">
-        <v>7.08</v>
+        <v>12.12</v>
       </c>
       <c r="J21" s="12">
-        <f>E21/I21-1</f>
-        <v>0.10169491525423724</v>
+        <f t="shared" si="0"/>
+        <v>0.18316831683168333</v>
       </c>
       <c r="K21" s="11">
-        <v>4.0512820512820513E-2</v>
+        <v>1.0320781032078103E-2</v>
       </c>
       <c r="L21" s="13">
-        <v>13438000000</v>
+        <v>199557000</v>
       </c>
       <c r="M21" s="13">
-        <v>88611000000</v>
+        <v>1108087000</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O21" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P21" s="12">
-        <v>0.22520668314653117</v>
+        <v>0.1737432874401873</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.15165160081705431</v>
+        <v>0.18009145491283626</v>
       </c>
       <c r="R21" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E22">
-        <v>0.74</v>
+        <v>2.69</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>1619497344</v>
+        <v>2797089024</v>
       </c>
       <c r="H22" s="6">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
       <c r="I22" s="6">
-        <v>0.42</v>
+        <v>1.92</v>
       </c>
       <c r="J22" s="12">
-        <f>E22/I22-1</f>
-        <v>0.76190476190476186</v>
+        <f t="shared" si="0"/>
+        <v>0.40104166666666674</v>
       </c>
       <c r="K22" s="11">
-        <v>4.9999999999999996E-2</v>
+        <v>0.10855018587360594</v>
       </c>
       <c r="L22" s="13">
-        <v>219938000</v>
+        <v>762183000</v>
       </c>
       <c r="M22" s="13">
-        <v>1520292000</v>
+        <v>5008319000</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P22" s="12">
-        <v>0.31760251606134982</v>
+        <v>0.21517658165819023</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.14466826109721026</v>
+        <v>0.15218339726363278</v>
       </c>
       <c r="R22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E23">
-        <v>2.72</v>
+        <v>7.74</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>2828283136</v>
+        <v>67453009920</v>
       </c>
       <c r="H23" s="6">
-        <v>3.34</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I23" s="6">
-        <v>1.92</v>
+        <v>7.08</v>
       </c>
       <c r="J23" s="12">
-        <f>E23/I23-1</f>
-        <v>0.41666666666666674</v>
+        <f t="shared" si="0"/>
+        <v>9.3220338983050821E-2</v>
       </c>
       <c r="K23" s="11">
-        <v>0.10735294117647057</v>
+        <v>4.0826873385012917E-2</v>
       </c>
       <c r="L23" s="13">
-        <v>762183000</v>
+        <v>13438000000</v>
       </c>
       <c r="M23" s="13">
-        <v>5008319000</v>
+        <v>88611000000</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O23" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.21329814973054531</v>
+        <v>0.22551513898677181</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.15218339726363278</v>
+        <v>0.15165160081705431</v>
       </c>
       <c r="R23" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E24">
-        <v>14.92</v>
+        <v>9.23</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>12417736704</v>
+        <v>150141632512</v>
       </c>
       <c r="H24" s="6">
-        <v>19.440000000000001</v>
+        <v>10.76</v>
       </c>
       <c r="I24" s="6">
-        <v>12.12</v>
+        <v>7.16</v>
       </c>
       <c r="J24" s="12">
-        <f>E24/I24-1</f>
-        <v>0.23102310231023115</v>
+        <f t="shared" si="0"/>
+        <v>0.28910614525139677</v>
       </c>
       <c r="K24" s="11">
-        <v>9.9195710455764075E-3</v>
+        <v>5.1895991332611045E-2</v>
       </c>
       <c r="L24" s="13">
-        <v>199557000</v>
+        <v>32866046000</v>
       </c>
       <c r="M24" s="13">
-        <v>1108087000</v>
+        <v>215280386000</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O24" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>0.1659163388020731</v>
+        <v>0.18769668293971206</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.18009145491283626</v>
+        <v>0.15266623500015464</v>
       </c>
       <c r="R24" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
-        <v>22</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E25">
-        <v>9.25</v>
+        <v>3.58</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>151007166464</v>
+        <v>2090304768</v>
       </c>
       <c r="H25" s="6">
-        <v>10.76</v>
+        <v>4.84</v>
       </c>
       <c r="I25" s="6">
-        <v>7.16</v>
+        <v>2.8</v>
       </c>
       <c r="J25" s="12">
-        <f>E25/I25-1</f>
-        <v>0.29189944134078205</v>
+        <f t="shared" si="0"/>
+        <v>0.27857142857142869</v>
       </c>
       <c r="K25" s="11">
-        <v>5.1783783783783781E-2</v>
+        <v>7.2625698324022353E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>32866046000</v>
+        <v>424258000</v>
       </c>
       <c r="M25" s="13">
-        <v>215280386000</v>
+        <v>2485347000</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O25" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>0.18683227054048748</v>
+        <v>0.16879885889810164</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.15266623500015464</v>
+        <v>0.17070372869462494</v>
       </c>
       <c r="R25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="E26">
-        <v>3.65</v>
+        <v>12.1</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>2095756928</v>
+        <v>19798263808</v>
       </c>
       <c r="H26" s="6">
-        <v>4.84</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I26" s="6">
-        <v>2.8</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J26" s="12">
-        <f>E26/I26-1</f>
-        <v>0.3035714285714286</v>
+        <f t="shared" si="0"/>
+        <v>0.25649013499480766</v>
       </c>
       <c r="K26" s="11">
-        <v>7.1232876712328766E-2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="13">
-        <v>424258000</v>
+        <v>634792000</v>
       </c>
       <c r="M26" s="13">
-        <v>2485347000</v>
+        <v>5195491000</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O26" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P26" s="12">
-        <v>0.16843348586106932</v>
+        <v>0.22775729862435659</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.17070372869462494</v>
+        <v>0.12218132992627646</v>
       </c>
       <c r="R26" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C27" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E27">
-        <v>8.67</v>
+        <v>5.36</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>8561920000</v>
+        <v>14344111104</v>
       </c>
       <c r="H27" s="6">
-        <v>9.07</v>
+        <v>7.13</v>
       </c>
       <c r="I27" s="6">
-        <v>5</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J27" s="12">
-        <f>E27/I27-1</f>
-        <v>0.73399999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.29156626506024086</v>
       </c>
       <c r="K27" s="11">
-        <v>4.083044982698962E-2</v>
+        <v>4.2910447761194029E-2</v>
       </c>
       <c r="L27" s="13">
-        <v>1333116000</v>
+        <v>2030839000</v>
       </c>
       <c r="M27" s="13">
-        <v>8019803000</v>
+        <v>11587361000</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>51</v>
@@ -3246,391 +3252,391 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.16990834282035278</v>
+        <v>0.15072049521902778</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.16622802330680692</v>
+        <v>0.17526328902672489</v>
       </c>
       <c r="R27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E28">
-        <v>12.46</v>
+        <v>11.44</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>19992692736</v>
+        <v>17492789248</v>
       </c>
       <c r="H28" s="6">
-        <v>18.399999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="I28" s="6">
-        <v>9.6300000000000008</v>
+        <v>8.67</v>
       </c>
       <c r="J28" s="12">
-        <f>E28/I28-1</f>
-        <v>0.29387331256490135</v>
+        <f t="shared" si="0"/>
+        <v>0.31949250288350628</v>
       </c>
       <c r="K28" s="11">
-        <v>0</v>
+        <v>5.2447552447552448E-2</v>
       </c>
       <c r="L28" s="13">
-        <v>634792000</v>
+        <v>1721368005.75</v>
       </c>
       <c r="M28" s="13">
-        <v>5195491000</v>
+        <v>14620942286.52</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O28" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>0.22571039846582011</v>
+        <v>0.23173426462119645</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.12218132992627646</v>
+        <v>0.11773304155211949</v>
       </c>
       <c r="R28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
-        <v>201</v>
+        <v>295</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>54</v>
       </c>
       <c r="E29">
-        <v>0.67</v>
+        <v>4.46</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>1596080768</v>
+        <v>17296236544</v>
       </c>
       <c r="H29" s="6">
-        <v>0.96</v>
+        <v>6.97</v>
       </c>
       <c r="I29" s="6">
-        <v>0.55000000000000004</v>
+        <v>3.33</v>
       </c>
       <c r="J29" s="12">
-        <f>E29/I29-1</f>
-        <v>0.21818181818181825</v>
+        <f t="shared" si="0"/>
+        <v>0.33933933933933935</v>
       </c>
       <c r="K29" s="11">
-        <v>1.4925373134328358E-2</v>
+        <v>6.0538116591928252E-2</v>
       </c>
       <c r="L29" s="13">
-        <v>54195000</v>
+        <v>2823432000</v>
       </c>
       <c r="M29" s="13">
-        <v>586711000</v>
+        <v>16925205000</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O29" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>1.40356102880077</v>
+        <v>0.15412077727863235</v>
       </c>
       <c r="Q29" s="12">
-        <v>9.2370860611101543E-2</v>
+        <v>0.16681818624944278</v>
       </c>
       <c r="R29" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>294</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>352</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="E30">
-        <v>6.13</v>
+        <v>9.49</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>6495593472</v>
+        <v>9371697152</v>
       </c>
       <c r="H30" s="6">
-        <v>6.88</v>
+        <v>9.65</v>
       </c>
       <c r="I30" s="6">
-        <v>3.97</v>
+        <v>5</v>
       </c>
       <c r="J30" s="12">
-        <f>E30/I30-1</f>
-        <v>0.54408060453400497</v>
+        <f t="shared" si="0"/>
+        <v>0.89800000000000013</v>
       </c>
       <c r="K30" s="11">
-        <v>7.9934747145187598E-2</v>
+        <v>3.7302423603793461E-2</v>
       </c>
       <c r="L30" s="13">
-        <v>866801000</v>
+        <v>1333116000</v>
       </c>
       <c r="M30" s="13">
-        <v>7530053000</v>
+        <v>8019803000</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O30" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.24767013249244174</v>
+        <v>0.15494069265362856</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.11511220438953086</v>
+        <v>0.16622802330680692</v>
       </c>
       <c r="R30" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
-        <v>295</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>353</v>
+        <v>226</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="E31">
-        <v>4.34</v>
+        <v>0.69</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>16830867456</v>
+        <v>1643724928</v>
       </c>
       <c r="H31" s="6">
-        <v>6.97</v>
+        <v>0.84</v>
       </c>
       <c r="I31" s="6">
-        <v>3.33</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J31" s="12">
-        <f>E31/I31-1</f>
-        <v>0.30330330330330324</v>
+        <f t="shared" si="0"/>
+        <v>0.25454545454545441</v>
       </c>
       <c r="K31" s="11">
-        <v>6.2211981566820285E-2</v>
+        <v>1.4492753623188408E-2</v>
       </c>
       <c r="L31" s="13">
-        <v>2823432000</v>
+        <v>54195000</v>
       </c>
       <c r="M31" s="13">
-        <v>16925205000</v>
+        <v>586711000</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O31" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P31" s="12">
-        <v>0.15813792142946842</v>
+        <v>1.2095413323209785</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.16681818624944278</v>
+        <v>9.2370860611101543E-2</v>
       </c>
       <c r="R31" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
-        <v>286</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="E32">
-        <v>11.78</v>
+        <v>6.09</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>18157338624</v>
+        <v>6550951936</v>
       </c>
       <c r="H32" s="6">
-        <v>11.84</v>
+        <v>6.88</v>
       </c>
       <c r="I32" s="6">
-        <v>8.67</v>
+        <v>3.97</v>
       </c>
       <c r="J32" s="12">
-        <f>E32/I32-1</f>
-        <v>0.35870818915801617</v>
+        <f t="shared" si="0"/>
+        <v>0.53400503778337516</v>
       </c>
       <c r="K32" s="11">
-        <v>5.0933786078098474E-2</v>
+        <v>8.0459770114942528E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>1721368005.75</v>
+        <v>866801000</v>
       </c>
       <c r="M32" s="13">
-        <v>14620942286.52</v>
+        <v>7530053000</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O32" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.2138287910765439</v>
+        <v>0.24381360702346375</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.11773304155211949</v>
+        <v>0.11511220438953086</v>
       </c>
       <c r="R32" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="E33">
-        <v>9.5299999999999994</v>
+        <v>7.23</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>118216785920</v>
+        <v>9267341312</v>
       </c>
       <c r="H33" s="6">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
       <c r="I33" s="6">
-        <v>6.57</v>
+        <v>3.46</v>
       </c>
       <c r="J33" s="12">
-        <f>E33/I33-1</f>
-        <v>0.450532724505327</v>
+        <f t="shared" si="0"/>
+        <v>1.0895953757225434</v>
       </c>
       <c r="K33" s="11">
-        <v>5.2465897166841559E-3</v>
+        <v>1.9502074688796677E-2</v>
       </c>
       <c r="L33" s="13">
-        <v>2250990000</v>
+        <v>921702000</v>
       </c>
       <c r="M33" s="13">
-        <v>11437145000</v>
+        <v>5262544000</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O33" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P33" s="12">
-        <v>0.13748169406803881</v>
+        <v>0.14459028925795669</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.19681397761416858</v>
+        <v>0.17514380877385538</v>
       </c>
       <c r="R33" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>71</v>
       </c>
       <c r="E34">
-        <v>4.95</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>14121458688</v>
+        <v>49839546368</v>
       </c>
       <c r="H34" s="6">
-        <v>6.21</v>
+        <v>5.14</v>
       </c>
       <c r="I34" s="6">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="J34" s="12">
-        <f>E34/I34-1</f>
-        <v>0.53726708074534169</v>
+        <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
+        <v>0.24566473988439297</v>
       </c>
       <c r="K34" s="11">
-        <v>8.4848484848484857E-3</v>
+        <v>6.0556844547563812E-2</v>
       </c>
       <c r="L34" s="13">
-        <v>259348000</v>
+        <v>4734613000</v>
       </c>
       <c r="M34" s="13">
-        <v>1677627000</v>
+        <v>16213395000</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O34" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>0.16375320006540439</v>
+        <v>0.10848939091083475</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.15459217096529801</v>
+        <v>0.29201860560357656</v>
       </c>
       <c r="R34" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
@@ -3644,13 +3650,13 @@
         <v>50</v>
       </c>
       <c r="E35">
-        <v>5.9</v>
+        <v>5.81</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>13194052608</v>
+        <v>12992787456</v>
       </c>
       <c r="H35" s="6">
         <v>6.4</v>
@@ -3659,11 +3665,11 @@
         <v>2.16</v>
       </c>
       <c r="J35" s="12">
-        <f>E35/I35-1</f>
-        <v>1.7314814814814814</v>
+        <f t="shared" si="1"/>
+        <v>1.6898148148148144</v>
       </c>
       <c r="K35" s="11">
-        <v>3.9152542372881356E-2</v>
+        <v>3.9759036144578319E-2</v>
       </c>
       <c r="L35" s="13">
         <v>2184074765.02</v>
@@ -3678,160 +3684,160 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>0.50494691519072832</v>
+        <v>0.52794055264095585</v>
       </c>
       <c r="Q35" s="12">
         <v>9.29654274042198E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="E36">
-        <v>4.49</v>
+        <v>10.14</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>51890479104</v>
+        <v>125783662592</v>
       </c>
       <c r="H36" s="6">
-        <v>5.14</v>
+        <v>13.6</v>
       </c>
       <c r="I36" s="6">
-        <v>3.46</v>
+        <v>6.57</v>
       </c>
       <c r="J36" s="12">
-        <f>E36/I36-1</f>
-        <v>0.29768786127167646</v>
+        <f t="shared" si="1"/>
+        <v>0.54337899543378998</v>
       </c>
       <c r="K36" s="11">
-        <v>5.8129175946547887E-2</v>
+        <v>4.9309664694280079E-3</v>
       </c>
       <c r="L36" s="13">
-        <v>4734613000</v>
+        <v>2250990000</v>
       </c>
       <c r="M36" s="13">
-        <v>16213395000</v>
+        <v>11437145000</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O36" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P36" s="12">
-        <v>0.10391827756389962</v>
+        <v>0.12968989988527038</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.29201860560357656</v>
+        <v>0.19681397761416858</v>
       </c>
       <c r="R36" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E37">
-        <v>5.44</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>14558201856</v>
+        <v>5119417856</v>
       </c>
       <c r="H37" s="6">
-        <v>7.13</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="I37" s="6">
-        <v>4.1500000000000004</v>
+        <v>3.69</v>
       </c>
       <c r="J37" s="12">
-        <f>E37/I37-1</f>
-        <v>0.31084337349397595</v>
+        <f t="shared" si="1"/>
+        <v>0.26016260162601634</v>
       </c>
       <c r="K37" s="11">
-        <v>4.2279411764705878E-2</v>
+        <v>6.8817204301075269E-2</v>
       </c>
       <c r="L37" s="13">
-        <v>2030839000</v>
+        <v>765224000</v>
       </c>
       <c r="M37" s="13">
-        <v>11587361000</v>
+        <v>5249449000</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O37" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.14851182132444624</v>
+        <v>0.16983545087350985</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.17526328902672489</v>
+        <v>0.14577225152582682</v>
       </c>
       <c r="R37" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>348</v>
+        <v>165</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E38">
-        <v>4.4800000000000004</v>
+        <v>5.76</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>4932256256</v>
+        <v>8443987968</v>
       </c>
       <c r="H38" s="6">
-        <v>4.55</v>
+        <v>6.07</v>
       </c>
       <c r="I38" s="6">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J38" s="12">
-        <f>E38/I38-1</f>
-        <v>0.24444444444444446</v>
+        <f t="shared" si="1"/>
+        <v>0.66956521739130426</v>
       </c>
       <c r="K38" s="11">
-        <v>7.1428571428571425E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="L38" s="13">
-        <v>765224000</v>
+        <v>784607000</v>
       </c>
       <c r="M38" s="13">
-        <v>5249449000</v>
+        <v>7872586000</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>68</v>
@@ -3840,106 +3846,106 @@
         <v>1</v>
       </c>
       <c r="P38" s="12">
-        <v>0.17719600377579225</v>
+        <v>0.28808923901898364</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.14577225152582682</v>
+        <v>9.9663185641922489E-2</v>
       </c>
       <c r="R38" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>5.66</v>
+        <v>5.39</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>8297390080</v>
+        <v>15806228480</v>
       </c>
       <c r="H39" s="6">
-        <v>5.73</v>
+        <v>6.21</v>
       </c>
       <c r="I39" s="6">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="J39" s="12">
-        <f>E39/I39-1</f>
-        <v>0.64057971014492754</v>
+        <f t="shared" si="1"/>
+        <v>0.67391304347826075</v>
       </c>
       <c r="K39" s="11">
-        <v>8.4805653710247342E-2</v>
+        <v>7.7922077922077931E-3</v>
       </c>
       <c r="L39" s="13">
-        <v>784607000</v>
+        <v>259348000</v>
       </c>
       <c r="M39" s="13">
-        <v>7872586000</v>
+        <v>1677627000</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O39" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P39" s="12">
-        <v>0.30447849329956156</v>
+        <v>0.14385894495567547</v>
       </c>
       <c r="Q39" s="12">
-        <v>9.9663185641922489E-2</v>
+        <v>0.15459217096529801</v>
       </c>
       <c r="R39" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B40" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C40" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D40" t="s">
-        <v>306</v>
+        <v>98</v>
       </c>
       <c r="E40">
-        <v>3.25</v>
+        <v>4.47</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>37379874816</v>
+        <v>31096895488</v>
       </c>
       <c r="H40" s="6">
-        <v>4.1100000000000003</v>
+        <v>6.15</v>
       </c>
       <c r="I40" s="6">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="J40" s="12">
-        <f>E40/I40-1</f>
-        <v>0.38297872340425521</v>
+        <f t="shared" si="1"/>
+        <v>0.20485175202156336</v>
       </c>
       <c r="K40" s="11">
-        <v>5.8461538461538461E-2</v>
+        <v>4.8993288590604027E-2</v>
       </c>
       <c r="L40" s="13">
-        <v>9414000000</v>
+        <v>4216348000</v>
       </c>
       <c r="M40" s="13">
-        <v>81589000000</v>
+        <v>46142120000</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>51</v>
@@ -3948,106 +3954,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.1945742319089287</v>
+        <v>0.36669762250478299</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.11538320116682396</v>
+        <v>9.1377422623841298E-2</v>
       </c>
       <c r="R40" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B41" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C41" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>306</v>
       </c>
       <c r="E41">
-        <v>9.5</v>
+        <v>3.48</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>23947978752</v>
+        <v>40025223168</v>
       </c>
       <c r="H41" s="6">
-        <v>11.22</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="I41" s="6">
-        <v>4.3499999999999996</v>
+        <v>2.35</v>
       </c>
       <c r="J41" s="12">
-        <f>E41/I41-1</f>
-        <v>1.1839080459770117</v>
+        <f t="shared" si="1"/>
+        <v>0.48085106382978715</v>
       </c>
       <c r="K41" s="11">
-        <v>3.3473684210526315E-2</v>
+        <v>5.459770114942529E-2</v>
       </c>
       <c r="L41" s="13">
-        <v>3301437000</v>
+        <v>9414000000</v>
       </c>
       <c r="M41" s="13">
-        <v>21814427000</v>
+        <v>81589000000</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O41" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>0.16389379165257389</v>
+        <v>0.1851014057667357</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.15134190781174311</v>
+        <v>0.11538320116682396</v>
       </c>
       <c r="R41" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B42" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E42">
-        <v>4.32</v>
+        <v>28.6</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>29920407552</v>
+        <v>208246046720</v>
       </c>
       <c r="H42" s="6">
-        <v>6.15</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="I42" s="6">
-        <v>3.71</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J42" s="12">
-        <f>E42/I42-1</f>
-        <v>0.16442048517520225</v>
+        <f t="shared" si="1"/>
+        <v>0.54094827586206917</v>
       </c>
       <c r="K42" s="11">
-        <v>5.0694444444444438E-2</v>
+        <v>4.6118881118881114E-2</v>
       </c>
       <c r="L42" s="13">
-        <v>4216348000</v>
+        <v>61181051000</v>
       </c>
       <c r="M42" s="13">
-        <v>46142120000</v>
+        <v>532289194000</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>51</v>
@@ -4056,67 +4062,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.40553632707851045</v>
+        <v>0.1854429602744915</v>
       </c>
       <c r="Q42" s="12">
-        <v>9.1377422623841298E-2</v>
+        <v>0.11493949471384535</v>
       </c>
       <c r="R42" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B43" s="1" t="s">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
-        <v>345</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="E43">
-        <v>6.43</v>
+        <v>11.26</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>2494094080</v>
+        <v>63443795968</v>
       </c>
       <c r="H43" s="6">
-        <v>14.18</v>
+        <v>14.24</v>
       </c>
       <c r="I43" s="6">
-        <v>3.64</v>
+        <v>8.81</v>
       </c>
       <c r="J43" s="12">
-        <f>E43/I43-1</f>
-        <v>0.76648351648351642</v>
+        <f t="shared" si="1"/>
+        <v>0.27809307604994316</v>
       </c>
       <c r="K43" s="11">
-        <v>5.4432348367029551E-2</v>
+        <v>2.9396092362344584E-2</v>
       </c>
       <c r="L43" s="13">
-        <v>348303000</v>
+        <v>6482967000</v>
       </c>
       <c r="M43" s="13">
-        <v>3681615000</v>
+        <v>27483863000</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O43" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>0.31927453384119575</v>
+        <v>9.9154088768325502E-2</v>
       </c>
       <c r="Q43" s="12">
-        <v>9.4606035666412708E-2</v>
+        <v>0.23588267049650188</v>
       </c>
       <c r="R43" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
@@ -4130,13 +4136,13 @@
         <v>87</v>
       </c>
       <c r="E44">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>64917049344</v>
+        <v>65625235456</v>
       </c>
       <c r="H44" s="6">
         <v>5.77</v>
@@ -4145,11 +4151,11 @@
         <v>4.34</v>
       </c>
       <c r="J44" s="12">
-        <f>E44/I44-1</f>
-        <v>0.26728110599078336</v>
+        <f t="shared" si="1"/>
+        <v>0.28110599078341014</v>
       </c>
       <c r="K44" s="11">
-        <v>2.6909090909090907E-2</v>
+        <v>2.6618705035971222E-2</v>
       </c>
       <c r="L44" s="13">
         <v>5687261000</v>
@@ -4164,52 +4170,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>9.8263419018625814E-2</v>
+        <v>9.7150769939110218E-2</v>
       </c>
       <c r="Q44" s="12">
         <v>0.26188601495697911</v>
       </c>
       <c r="R44" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B45" s="1" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="E45">
-        <v>28.5</v>
+        <v>92.6</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>203231789056</v>
+        <v>258169716736</v>
       </c>
       <c r="H45" s="6">
-        <v>32.299999999999997</v>
+        <v>107.5</v>
       </c>
       <c r="I45" s="6">
-        <v>18.559999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="J45" s="12">
-        <f>E45/I45-1</f>
-        <v>0.5355603448275863</v>
+        <f t="shared" si="1"/>
+        <v>0.41266209000762766</v>
       </c>
       <c r="K45" s="11">
-        <v>4.6280701754385964E-2</v>
+        <v>2.3952483801295898E-2</v>
       </c>
       <c r="L45" s="13">
-        <v>61181051000</v>
+        <v>22510000000</v>
       </c>
       <c r="M45" s="13">
-        <v>532289194000</v>
+        <v>82545000000</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>51</v>
@@ -4218,52 +4224,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>0.18811910013328226</v>
+        <v>8.7120806589933791E-2</v>
       </c>
       <c r="Q45" s="12">
-        <v>0.11493949471384535</v>
+        <v>0.27269973953601068</v>
       </c>
       <c r="R45" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B46" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="E46">
-        <v>3.97</v>
+        <v>10.58</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>3668843776</v>
+        <v>26670485504</v>
       </c>
       <c r="H46" s="6">
-        <v>4.2</v>
+        <v>11.22</v>
       </c>
       <c r="I46" s="6">
-        <v>3.4</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J46" s="12">
-        <f>E46/I46-1</f>
-        <v>0.16764705882352948</v>
+        <f t="shared" si="1"/>
+        <v>1.4321839080459773</v>
       </c>
       <c r="K46" s="11">
-        <v>3.6523929471032744E-2</v>
+        <v>3.0056710775047259E-2</v>
       </c>
       <c r="L46" s="13">
-        <v>754477000</v>
+        <v>3301437000</v>
       </c>
       <c r="M46" s="13">
-        <v>11677999000</v>
+        <v>21814427000</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>68</v>
@@ -4272,52 +4278,52 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>0.65650380214390591</v>
+        <v>0.14438024431328672</v>
       </c>
       <c r="Q46" s="12">
-        <v>6.460670188445812E-2</v>
+        <v>0.15134190781174311</v>
       </c>
       <c r="R46" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B47" s="1" t="s">
-        <v>118</v>
+        <v>283</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>341</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E47">
-        <v>91</v>
+        <v>24.9</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>253708910592</v>
+        <v>250182746112</v>
       </c>
       <c r="H47" s="6">
-        <v>107.5</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I47" s="6">
-        <v>65.55</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="J47" s="12">
-        <f>E47/I47-1</f>
-        <v>0.38825324180015253</v>
+        <f t="shared" si="1"/>
+        <v>0.29417879417879411</v>
       </c>
       <c r="K47" s="11">
-        <v>2.4373626373626372E-2</v>
+        <v>3.8755020080321285E-2</v>
       </c>
       <c r="L47" s="13">
-        <v>22510000000</v>
+        <v>25459748125.549999</v>
       </c>
       <c r="M47" s="13">
-        <v>82545000000</v>
+        <v>134815560756.77</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>51</v>
@@ -4326,52 +4332,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>8.8551784431301322E-2</v>
+        <v>0.11414554241220609</v>
       </c>
       <c r="Q47" s="12">
-        <v>0.27269973953601068</v>
+        <v>0.18884873513587705</v>
       </c>
       <c r="R47" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>337</v>
       </c>
       <c r="E48">
-        <v>11.52</v>
+        <v>5.69</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>64908754944</v>
+        <v>7295945728</v>
       </c>
       <c r="H48" s="6">
-        <v>14.24</v>
+        <v>5.92</v>
       </c>
       <c r="I48" s="6">
-        <v>8.81</v>
+        <v>3.36</v>
       </c>
       <c r="J48" s="12">
-        <f>E48/I48-1</f>
-        <v>0.30760499432463106</v>
+        <f t="shared" si="1"/>
+        <v>0.69345238095238115</v>
       </c>
       <c r="K48" s="11">
-        <v>2.8732638888888891E-2</v>
+        <v>4.5694200351493845E-2</v>
       </c>
       <c r="L48" s="13">
-        <v>6482967000</v>
+        <v>2871477000</v>
       </c>
       <c r="M48" s="13">
-        <v>27483863000</v>
+        <v>21784665000</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>51</v>
@@ -4380,121 +4386,121 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>9.7117351736239615E-2</v>
+        <v>0.15104351679776906</v>
       </c>
       <c r="Q48" s="12">
-        <v>0.23588267049650188</v>
+        <v>0.1318118502166547</v>
       </c>
       <c r="R48" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B49" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C49" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E49">
-        <v>23.75</v>
+        <v>10.7</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>246061875200</v>
+        <v>2511525376</v>
       </c>
       <c r="H49" s="6">
-        <v>36.450000000000003</v>
+        <v>17</v>
       </c>
       <c r="I49" s="6">
-        <v>19.239999999999998</v>
+        <v>7.36</v>
       </c>
       <c r="J49" s="12">
-        <f>E49/I49-1</f>
-        <v>0.2344074844074846</v>
+        <f t="shared" si="1"/>
+        <v>0.4538043478260867</v>
       </c>
       <c r="K49" s="11">
-        <v>4.0631578947368421E-2</v>
+        <v>3.925233644859813E-2</v>
       </c>
       <c r="L49" s="13">
-        <v>25459748125.549999</v>
+        <v>244811000</v>
       </c>
       <c r="M49" s="13">
-        <v>134815560756.77</v>
+        <v>2904223000</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O49" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P49" s="12">
-        <v>0.11615419397894375</v>
+        <v>0.30259840651323888</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.18884873513587705</v>
+        <v>8.4294835486117978E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="E50">
-        <v>3.98</v>
+        <v>49.25</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>5712931840</v>
+        <v>127422554112</v>
       </c>
       <c r="H50" s="6">
-        <v>7.92</v>
+        <v>71.7</v>
       </c>
       <c r="I50" s="6">
-        <v>2.36</v>
+        <v>43.55</v>
       </c>
       <c r="J50" s="12">
-        <f>E50/I50-1</f>
-        <v>0.68644067796610186</v>
+        <f t="shared" si="1"/>
+        <v>0.13088404133180265</v>
       </c>
       <c r="K50" s="11">
-        <v>6.3819095477386942E-2</v>
+        <v>3.3299492385786803E-3</v>
       </c>
       <c r="L50" s="13">
-        <v>811880000</v>
+        <v>1279098000</v>
       </c>
       <c r="M50" s="13">
-        <v>5532140000</v>
+        <v>4811702000</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="O50" s="6">
-        <v>1.0683760683760684</v>
+        <v>8.7546153846153842</v>
       </c>
       <c r="P50" s="12">
-        <v>0.15773777737132938</v>
+        <v>7.8324331600632152E-2</v>
       </c>
       <c r="Q50" s="12">
-        <v>0.14675695119790894</v>
+        <v>0.26583067696212276</v>
       </c>
       <c r="R50" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -4508,13 +4514,13 @@
         <v>174</v>
       </c>
       <c r="E51">
-        <v>74.900000000000006</v>
+        <v>79.5</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>18497005568</v>
+        <v>19463587840</v>
       </c>
       <c r="H51" s="6">
         <v>95.5</v>
@@ -4523,11 +4529,11 @@
         <v>55.05</v>
       </c>
       <c r="J51" s="12">
-        <f>E51/I51-1</f>
-        <v>0.36058128973660319</v>
+        <f t="shared" si="1"/>
+        <v>0.44414168937329701</v>
       </c>
       <c r="K51" s="11">
-        <v>1.0947930574098796E-2</v>
+        <v>1.0314465408805032E-2</v>
       </c>
       <c r="L51" s="13">
         <v>526052000</v>
@@ -4542,52 +4548,52 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P51" s="12">
-        <v>0.21742207576338402</v>
+        <v>0.2066878179992655</v>
       </c>
       <c r="Q51" s="12">
         <v>9.8446219337080781E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B52" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C52" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D52" t="s">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="E52">
-        <v>6.31</v>
+        <v>20.95</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>12798446592</v>
+        <v>33596887040</v>
       </c>
       <c r="H52" s="6">
-        <v>7.86</v>
+        <v>27.5</v>
       </c>
       <c r="I52" s="6">
-        <v>5.31</v>
+        <v>16.18</v>
       </c>
       <c r="J52" s="12">
-        <f>E52/I52-1</f>
-        <v>0.18832391713747643</v>
+        <f t="shared" si="1"/>
+        <v>0.29480840543881337</v>
       </c>
       <c r="K52" s="11">
-        <v>4.2789223454833603E-2</v>
+        <v>3.274463007159905E-2</v>
       </c>
       <c r="L52" s="13">
-        <v>1537565000</v>
+        <v>3811007000</v>
       </c>
       <c r="M52" s="13">
-        <v>14484935000</v>
+        <v>22856317000</v>
       </c>
       <c r="N52" s="9" t="s">
         <v>51</v>
@@ -4596,52 +4602,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.19526514400058809</v>
+        <v>0.12378449891056212</v>
       </c>
       <c r="Q52" s="12">
-        <v>0.10614925092863724</v>
+        <v>0.1667375806872122</v>
       </c>
       <c r="R52" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C53" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="E53">
-        <v>20.45</v>
+        <v>6.48</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>32638201856</v>
+        <v>13244472320</v>
       </c>
       <c r="H53" s="6">
-        <v>27.5</v>
+        <v>7.86</v>
       </c>
       <c r="I53" s="6">
-        <v>16.18</v>
+        <v>5.31</v>
       </c>
       <c r="J53" s="12">
-        <f>E53/I53-1</f>
-        <v>0.26390605686032131</v>
+        <f t="shared" si="1"/>
+        <v>0.22033898305084754</v>
       </c>
       <c r="K53" s="11">
-        <v>3.3545232273838634E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="L53" s="13">
-        <v>3811007000</v>
+        <v>1537565000</v>
       </c>
       <c r="M53" s="13">
-        <v>22856317000</v>
+        <v>14484935000</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>51</v>
@@ -4650,214 +4656,214 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>0.1275006272311732</v>
+        <v>0.1854337353602912</v>
       </c>
       <c r="Q53" s="12">
-        <v>0.1667375806872122</v>
+        <v>0.10614925092863724</v>
       </c>
       <c r="R53" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B54" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C54" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E54">
-        <v>10.28</v>
+        <v>0.52</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>2412942080</v>
+        <v>2695529216</v>
       </c>
       <c r="H54" s="6">
-        <v>17</v>
+        <v>0.68</v>
       </c>
       <c r="I54" s="6">
-        <v>7.36</v>
+        <v>0.46</v>
       </c>
       <c r="J54" s="12">
-        <f>E54/I54-1</f>
-        <v>0.39673913043478248</v>
+        <f t="shared" si="1"/>
+        <v>0.13043478260869557</v>
       </c>
       <c r="K54" s="11">
-        <v>4.085603112840467E-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="13">
-        <v>244811000</v>
+        <v>756004000</v>
       </c>
       <c r="M54" s="13">
-        <v>2904223000</v>
+        <v>8813758000</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O54" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>0.34458772719247038</v>
+        <v>0.28949073626199495</v>
       </c>
       <c r="Q54" s="12">
-        <v>8.4294835486117978E-2</v>
+        <v>8.5775443346640556E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B55" s="1" t="s">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>190</v>
+        <v>338</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>339</v>
       </c>
       <c r="E55">
-        <v>49.5</v>
+        <v>3.66</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>126661591040</v>
+        <v>8357280256</v>
       </c>
       <c r="H55" s="6">
-        <v>71.7</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="I55" s="6">
-        <v>43.55</v>
+        <v>3.34</v>
       </c>
       <c r="J55" s="12">
-        <f>E55/I55-1</f>
-        <v>0.13662456946039048</v>
+        <f t="shared" si="1"/>
+        <v>9.5808383233533023E-2</v>
       </c>
       <c r="K55" s="11">
-        <v>3.3131313131313134E-3</v>
+        <v>4.0983606557377046E-2</v>
       </c>
       <c r="L55" s="13">
-        <v>1279098000</v>
+        <v>826931000</v>
       </c>
       <c r="M55" s="13">
-        <v>4811702000</v>
+        <v>5591620000</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="O55" s="6">
-        <v>8.7546153846153842</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>7.8743447186556237E-2</v>
+        <v>0.13950636526246654</v>
       </c>
       <c r="Q55" s="12">
-        <v>0.26583067696212276</v>
+        <v>0.14788755315990715</v>
       </c>
       <c r="R55" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B56" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C56" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D56" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="E56">
-        <v>0.51</v>
+        <v>8.11</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>2643692032</v>
+        <v>3145739008</v>
       </c>
       <c r="H56" s="6">
-        <v>0.68</v>
+        <v>14.18</v>
       </c>
       <c r="I56" s="6">
-        <v>0.46</v>
+        <v>3.64</v>
       </c>
       <c r="J56" s="12">
-        <f>E56/I56-1</f>
-        <v>0.10869565217391308</v>
+        <f t="shared" si="1"/>
+        <v>1.2280219780219777</v>
       </c>
       <c r="K56" s="11">
-        <v>0</v>
+        <v>4.3156596794081382E-2</v>
       </c>
       <c r="L56" s="13">
-        <v>756004000</v>
+        <v>348303000</v>
       </c>
       <c r="M56" s="13">
-        <v>8813758000</v>
+        <v>3681615000</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O56" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P56" s="12">
-        <v>0.29497107313748638</v>
+        <v>0.19987948707851019</v>
       </c>
       <c r="Q56" s="12">
-        <v>8.5775443346640556E-2</v>
+        <v>9.4606035666412708E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B57" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C57" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D57" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="E57">
-        <v>5.54</v>
+        <v>6.06</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>7103609344</v>
+        <v>26235072512</v>
       </c>
       <c r="H57" s="6">
-        <v>5.92</v>
+        <v>6.87</v>
       </c>
       <c r="I57" s="6">
-        <v>3.36</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J57" s="12">
-        <f>E57/I57-1</f>
-        <v>0.64880952380952395</v>
+        <f t="shared" si="1"/>
+        <v>0.27044025157232698</v>
       </c>
       <c r="K57" s="11">
-        <v>4.6931407942238268E-2</v>
+        <v>5.9075907590759077E-2</v>
       </c>
       <c r="L57" s="13">
-        <v>2871477000</v>
+        <v>2919921000</v>
       </c>
       <c r="M57" s="13">
-        <v>21784665000</v>
+        <v>31662140000</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>51</v>
@@ -4866,52 +4872,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>0.15248752062922108</v>
+        <v>0.21331297654954046</v>
       </c>
       <c r="Q57" s="12">
-        <v>0.1318118502166547</v>
+        <v>9.2221214358852555E-2</v>
       </c>
       <c r="R57" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B58" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C58" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E58">
-        <v>6.02</v>
+        <v>6.9</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>26452844544</v>
+        <v>17295886336</v>
       </c>
       <c r="H58" s="6">
-        <v>6.87</v>
+        <v>7.26</v>
       </c>
       <c r="I58" s="6">
-        <v>4.7699999999999996</v>
+        <v>3.99</v>
       </c>
       <c r="J58" s="12">
-        <f>E58/I58-1</f>
-        <v>0.26205450733752622</v>
+        <f t="shared" si="1"/>
+        <v>0.72932330827067671</v>
       </c>
       <c r="K58" s="11">
-        <v>5.9468438538205985E-2</v>
+        <v>4.652173913043478E-2</v>
       </c>
       <c r="L58" s="13">
-        <v>2919921000</v>
+        <v>3040816000</v>
       </c>
       <c r="M58" s="13">
-        <v>31662140000</v>
+        <v>29707522000</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>51</v>
@@ -4920,175 +4926,175 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.21018313755354881</v>
+        <v>0.17225133693150912</v>
       </c>
       <c r="Q58" s="12">
-        <v>9.2221214358852555E-2</v>
+        <v>0.102358453189061</v>
       </c>
       <c r="R58" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="E59">
-        <v>408.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>515899490304</v>
+        <v>6661116416</v>
       </c>
       <c r="H59" s="6">
-        <v>426.8</v>
+        <v>7.92</v>
       </c>
       <c r="I59" s="6">
-        <v>218.4</v>
+        <v>2.36</v>
       </c>
       <c r="J59" s="12">
-        <f>E59/I59-1</f>
-        <v>0.86904761904761885</v>
+        <f t="shared" si="1"/>
+        <v>0.86440677966101709</v>
       </c>
       <c r="K59" s="11">
-        <v>2.2684958353748164E-2</v>
+        <v>5.7727272727272724E-2</v>
       </c>
       <c r="L59" s="13">
-        <v>20744000000</v>
+        <v>811880000</v>
       </c>
       <c r="M59" s="13">
-        <v>53852000000</v>
+        <v>5532140000</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O59" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P59" s="12">
-        <v>5.4186144776025971E-2</v>
+        <v>0.13453919557835634</v>
       </c>
       <c r="Q59" s="12">
-        <v>0.38520389214885242</v>
+        <v>0.14675695119790894</v>
       </c>
       <c r="R59" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B60" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="E60">
-        <v>6.78</v>
+        <v>5.54</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>16995088384</v>
+        <v>5119746560</v>
       </c>
       <c r="H60" s="6">
-        <v>7.26</v>
+        <v>5.59</v>
       </c>
       <c r="I60" s="6">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="J60" s="12">
-        <f>E60/I60-1</f>
-        <v>0.6992481203007519</v>
+        <f t="shared" si="1"/>
+        <v>0.62941176470588234</v>
       </c>
       <c r="K60" s="11">
-        <v>4.7345132743362835E-2</v>
+        <v>2.6173285198555954E-2</v>
       </c>
       <c r="L60" s="13">
-        <v>3040816000</v>
+        <v>754477000</v>
       </c>
       <c r="M60" s="13">
-        <v>29707522000</v>
+        <v>11677999000</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O60" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P60" s="12">
-        <v>0.17504303220460088</v>
+        <v>0.2901681094134112</v>
       </c>
       <c r="Q60" s="12">
-        <v>0.102358453189061</v>
+        <v>6.460670188445812E-2</v>
       </c>
       <c r="R60" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B61" s="1" t="s">
-        <v>281</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>338</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>339</v>
+        <v>101</v>
       </c>
       <c r="E61">
-        <v>3.78</v>
+        <v>426.2</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>8584606720</v>
+        <v>542454611968</v>
       </c>
       <c r="H61" s="6">
-        <v>5.09</v>
+        <v>432.2</v>
       </c>
       <c r="I61" s="6">
-        <v>3.34</v>
+        <v>218.4</v>
       </c>
       <c r="J61" s="12">
-        <f>E61/I61-1</f>
-        <v>0.13173652694610771</v>
+        <f t="shared" si="1"/>
+        <v>0.95146520146520142</v>
       </c>
       <c r="K61" s="11">
-        <v>3.968253968253968E-2</v>
+        <v>2.1726888784608166E-2</v>
       </c>
       <c r="L61" s="13">
-        <v>826931000</v>
+        <v>20744000000</v>
       </c>
       <c r="M61" s="13">
-        <v>5591620000</v>
+        <v>53852000000</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O61" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P61" s="12">
-        <v>0.13467212416416638</v>
+        <v>5.0671300446734742E-2</v>
       </c>
       <c r="Q61" s="12">
-        <v>0.14788755315990715</v>
+        <v>0.38520389214885242</v>
       </c>
       <c r="R61" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
@@ -5102,13 +5108,13 @@
         <v>177</v>
       </c>
       <c r="E62">
-        <v>20.350000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>558947368960</v>
+        <v>550624428032</v>
       </c>
       <c r="H62" s="6">
         <v>21.5</v>
@@ -5117,11 +5123,11 @@
         <v>13.52</v>
       </c>
       <c r="J62" s="12">
-        <f>E62/I62-1</f>
-        <v>0.50517751479289963</v>
+        <f t="shared" si="1"/>
+        <v>0.51257396449704151</v>
       </c>
       <c r="K62" s="11">
-        <v>1.8673218673218674E-2</v>
+        <v>1.8581907090464547E-2</v>
       </c>
       <c r="L62" s="13">
         <v>52374992116</v>
@@ -5136,52 +5142,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>8.1899116146847278E-2</v>
+        <v>8.2909089818828094E-2</v>
       </c>
       <c r="Q62" s="12">
         <v>0.19428864891763736</v>
       </c>
       <c r="R62" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B63" s="1" t="s">
-        <v>374</v>
+        <v>279</v>
       </c>
       <c r="C63" t="s">
-        <v>376</v>
+        <v>335</v>
       </c>
       <c r="D63" t="s">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="E63">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>4123502848</v>
+        <v>10229439488</v>
       </c>
       <c r="H63" s="6">
-        <v>2.5499999999999998</v>
+        <v>2.42</v>
       </c>
       <c r="I63" s="6">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="J63" s="12">
-        <f>E63/I63-1</f>
-        <v>0.94949494949494939</v>
+        <f t="shared" si="1"/>
+        <v>0.78358208955223874</v>
       </c>
       <c r="K63" s="11">
-        <v>0</v>
+        <v>5.1046025104602509E-2</v>
       </c>
       <c r="L63" s="13">
-        <v>-732033000</v>
+        <v>1230913000</v>
       </c>
       <c r="M63" s="13">
-        <v>7864121000</v>
+        <v>10701340000</v>
       </c>
       <c r="N63" s="9" t="s">
         <v>51</v>
@@ -5190,52 +5196,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>0.79316858289861092</v>
+        <v>0.14719410929571736</v>
       </c>
       <c r="Q63" s="12">
-        <v>-9.3085164890011229E-2</v>
+        <v>0.11502419323187564</v>
       </c>
       <c r="R63" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B64" s="1" t="s">
-        <v>279</v>
+        <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>335</v>
+        <v>159</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E64">
-        <v>2.29</v>
+        <v>247.8</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>9801428992</v>
+        <v>329118056448</v>
       </c>
       <c r="H64" s="6">
-        <v>2.39</v>
+        <v>283.39999999999998</v>
       </c>
       <c r="I64" s="6">
-        <v>1.33</v>
+        <v>36.5</v>
       </c>
       <c r="J64" s="12">
-        <f>E64/I64-1</f>
-        <v>0.72180451127819545</v>
+        <f t="shared" si="1"/>
+        <v>5.7890410958904113</v>
       </c>
       <c r="K64" s="11">
-        <v>5.3275109170305673E-2</v>
+        <v>3.2889426957223565E-3</v>
       </c>
       <c r="L64" s="13">
-        <v>1230913000</v>
+        <v>4408440000</v>
       </c>
       <c r="M64" s="13">
-        <v>10701340000</v>
+        <v>10683505000</v>
       </c>
       <c r="N64" s="9" t="s">
         <v>51</v>
@@ -5244,67 +5250,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P64" s="12">
-        <v>0.1546004572848656</v>
+        <v>1.4553627636866826E-2</v>
       </c>
       <c r="Q64" s="12">
-        <v>0.11502419323187564</v>
+        <v>0.41263985929711272</v>
       </c>
       <c r="R64" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B65" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="E65">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>343993450496</v>
+        <v>136447959040</v>
       </c>
       <c r="H65" s="6">
-        <v>283.39999999999998</v>
+        <v>421.4</v>
       </c>
       <c r="I65" s="6">
-        <v>34.700000000000003</v>
+        <v>225.2</v>
       </c>
       <c r="J65" s="12">
-        <f>E65/I65-1</f>
-        <v>6.4639769452449558</v>
+        <f t="shared" si="1"/>
+        <v>0.62078152753108351</v>
       </c>
       <c r="K65" s="11">
-        <v>3.1467181467181465E-3</v>
+        <v>1.9726027397260273E-3</v>
       </c>
       <c r="L65" s="13">
-        <v>4408440000</v>
+        <v>1200000000</v>
       </c>
       <c r="M65" s="13">
-        <v>10683505000</v>
+        <v>5855000000</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O65" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P65" s="12">
-        <v>1.3914062753089427E-2</v>
+        <v>6.1778495784552405E-2</v>
       </c>
       <c r="Q65" s="12">
-        <v>0.41263985929711272</v>
+        <v>0.20495303159692571</v>
       </c>
       <c r="R65" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
@@ -5318,13 +5324,13 @@
         <v>321</v>
       </c>
       <c r="E66">
-        <v>7.53</v>
+        <v>8.52</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>13609948160</v>
+        <v>15399304192</v>
       </c>
       <c r="H66" s="6">
         <v>8.8000000000000007</v>
@@ -5333,11 +5339,11 @@
         <v>5.49</v>
       </c>
       <c r="J66" s="12">
-        <f>E66/I66-1</f>
-        <v>0.37158469945355188</v>
+        <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
+        <v>0.55191256830601088</v>
       </c>
       <c r="K66" s="11">
-        <v>3.3200531208499334E-2</v>
+        <v>2.9342723004694836E-2</v>
       </c>
       <c r="L66" s="13">
         <v>2897428000</v>
@@ -5352,160 +5358,160 @@
         <v>1</v>
       </c>
       <c r="P66" s="12">
-        <v>0.15641179744992564</v>
+        <v>0.1426340902135545</v>
       </c>
       <c r="Q66" s="12">
         <v>0.11156568921912897</v>
       </c>
       <c r="R66" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B67" s="1" t="s">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
+        <v>375</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E67">
-        <v>370.6</v>
+        <v>12.24</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>137391063040</v>
+        <v>3217688064</v>
       </c>
       <c r="H67" s="6">
-        <v>421.4</v>
+        <v>15.58</v>
       </c>
       <c r="I67" s="6">
-        <v>225.2</v>
+        <v>7.51</v>
       </c>
       <c r="J67" s="12">
-        <f>E67/I67-1</f>
-        <v>0.64564831261101263</v>
+        <f t="shared" si="2"/>
+        <v>0.62982689747004006</v>
       </c>
       <c r="K67" s="11">
-        <v>1.9427954668105772E-3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="13">
-        <v>1200000000</v>
+        <v>-481083000</v>
       </c>
       <c r="M67" s="13">
-        <v>5855000000</v>
+        <v>4136123000</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O67" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P67" s="12">
-        <v>6.1391002883252832E-2</v>
+        <v>0.49684646154958739</v>
       </c>
       <c r="Q67" s="12">
-        <v>0.20495303159692571</v>
+        <v>-0.11631254679805218</v>
       </c>
       <c r="R67" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B68" s="1" t="s">
-        <v>264</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>317</v>
+        <v>182</v>
       </c>
       <c r="D68" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E68">
-        <v>20.85</v>
+        <v>33.15</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>19199598592</v>
+        <v>22929192960</v>
       </c>
       <c r="H68" s="6">
-        <v>23.35</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="I68" s="6">
-        <v>9.9</v>
+        <v>13.48</v>
       </c>
       <c r="J68" s="12">
-        <f>E68/I68-1</f>
-        <v>1.106060606060606</v>
+        <f t="shared" si="2"/>
+        <v>1.4591988130563798</v>
       </c>
       <c r="K68" s="11">
-        <v>3.7410071942446041E-3</v>
+        <v>1.3876319758672701E-2</v>
       </c>
       <c r="L68" s="13">
-        <v>334940000</v>
+        <v>1323087000</v>
       </c>
       <c r="M68" s="13">
-        <v>3025375000</v>
+        <v>5952918000</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O68" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P68" s="12">
-        <v>0.15733334185040926</v>
+        <v>5.2106356537171293E-2</v>
       </c>
       <c r="Q68" s="12">
-        <v>0.11071024253191752</v>
+        <v>0.222258562943417</v>
       </c>
       <c r="R68" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B69" s="1" t="s">
-        <v>37</v>
+        <v>270</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>325</v>
       </c>
       <c r="D69" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="E69">
-        <v>6.03</v>
+        <v>3.22</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>4698588160</v>
+        <v>6077073920</v>
       </c>
       <c r="H69" s="6">
-        <v>8.09</v>
+        <v>4.18</v>
       </c>
       <c r="I69" s="6">
-        <v>4.0199999999999996</v>
+        <v>1.74</v>
       </c>
       <c r="J69" s="12">
-        <f>E69/I69-1</f>
-        <v>0.50000000000000022</v>
+        <f t="shared" si="2"/>
+        <v>0.85057471264367823</v>
       </c>
       <c r="K69" s="11">
-        <v>2.8192371475953566E-2</v>
+        <v>4.9689440993788817E-2</v>
       </c>
       <c r="L69" s="13">
-        <v>437453000</v>
+        <v>896597000</v>
       </c>
       <c r="M69" s="13">
-        <v>4911072000</v>
+        <v>6906279000</v>
       </c>
       <c r="N69" s="9" t="s">
         <v>68</v>
@@ -5514,214 +5520,214 @@
         <v>1</v>
       </c>
       <c r="P69" s="12">
-        <v>0.18158062733080144</v>
+        <v>0.11687460787694841</v>
       </c>
       <c r="Q69" s="12">
-        <v>8.9074849645861431E-2</v>
+        <v>0.12982345485897689</v>
       </c>
       <c r="R69" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B70" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E70">
-        <v>31.45</v>
+        <v>23.15</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>21753335808</v>
+        <v>26393081856</v>
       </c>
       <c r="H70" s="6">
-        <v>39.200000000000003</v>
+        <v>28.75</v>
       </c>
       <c r="I70" s="6">
-        <v>13.48</v>
+        <v>19.52</v>
       </c>
       <c r="J70" s="12">
-        <f>E70/I70-1</f>
-        <v>1.3330860534124627</v>
+        <f t="shared" si="2"/>
+        <v>0.18596311475409832</v>
       </c>
       <c r="K70" s="11">
-        <v>1.4626391096979333E-2</v>
+        <v>6.0475161987041039E-2</v>
       </c>
       <c r="L70" s="13">
-        <v>1323087000</v>
+        <v>3446618000</v>
       </c>
       <c r="M70" s="13">
-        <v>5952918000</v>
+        <v>34010798000</v>
       </c>
       <c r="N70" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O70" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P70" s="12">
-        <v>5.4636466972164843E-2</v>
+        <v>0.14632134692749155</v>
       </c>
       <c r="Q70" s="12">
-        <v>0.222258562943417</v>
+        <v>0.10133893359397213</v>
       </c>
       <c r="R70" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B71" s="1" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
-        <v>375</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="E71">
-        <v>11.56</v>
+        <v>6.36</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>3041702144</v>
+        <v>4955724800</v>
       </c>
       <c r="H71" s="6">
-        <v>15.58</v>
+        <v>8.09</v>
       </c>
       <c r="I71" s="6">
-        <v>7.51</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J71" s="12">
-        <f>E71/I71-1</f>
-        <v>0.53928095872170445</v>
+        <f t="shared" si="2"/>
+        <v>0.58208955223880632</v>
       </c>
       <c r="K71" s="11">
-        <v>0</v>
+        <v>2.6729559748427674E-2</v>
       </c>
       <c r="L71" s="13">
-        <v>-481083000</v>
+        <v>437453000</v>
       </c>
       <c r="M71" s="13">
-        <v>4136123000</v>
+        <v>4911072000</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O71" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P71" s="12">
-        <v>0.4246114618258639</v>
+        <v>0.16406892340244772</v>
       </c>
       <c r="Q71" s="12">
-        <v>-0.11631254679805218</v>
+        <v>8.9074849645861431E-2</v>
       </c>
       <c r="R71" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B72" s="1" t="s">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>325</v>
+        <v>154</v>
       </c>
       <c r="D72" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="E72">
-        <v>2.98</v>
+        <v>59.75</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>5624124416</v>
+        <v>165795495936</v>
       </c>
       <c r="H72" s="6">
-        <v>4.18</v>
+        <v>60</v>
       </c>
       <c r="I72" s="6">
-        <v>1.74</v>
+        <v>38.4</v>
       </c>
       <c r="J72" s="12">
-        <f>E72/I72-1</f>
-        <v>0.71264367816091956</v>
+        <f t="shared" si="2"/>
+        <v>0.55598958333333348</v>
       </c>
       <c r="K72" s="11">
-        <v>5.3691275167785234E-2</v>
+        <v>3.0125523012552301E-2</v>
       </c>
       <c r="L72" s="13">
-        <v>896597000</v>
+        <v>8955723006</v>
       </c>
       <c r="M72" s="13">
-        <v>6906279000</v>
+        <v>47495870210</v>
       </c>
       <c r="N72" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O72" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P72" s="12">
-        <v>0.12420831108668132</v>
+        <v>5.9154556950578426E-2</v>
       </c>
       <c r="Q72" s="12">
-        <v>0.12982345485897689</v>
+        <v>0.18855793075067021</v>
       </c>
       <c r="R72" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B73" s="1" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="E73">
-        <v>57.5</v>
+        <v>515</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>163077472256</v>
+        <v>4671564939264</v>
       </c>
       <c r="H73" s="6">
-        <v>60</v>
+        <v>547</v>
       </c>
       <c r="I73" s="6">
-        <v>38.4</v>
+        <v>349</v>
       </c>
       <c r="J73" s="12">
-        <f>E73/I73-1</f>
-        <v>0.49739583333333348</v>
+        <f t="shared" si="2"/>
+        <v>0.47564469914040108</v>
       </c>
       <c r="K73" s="11">
-        <v>3.1304347826086959E-2</v>
+        <v>8.211650485436893E-3</v>
       </c>
       <c r="L73" s="13">
-        <v>8955723006</v>
+        <v>253932000000</v>
       </c>
       <c r="M73" s="13">
-        <v>47495870210</v>
+        <v>1312163000000</v>
       </c>
       <c r="N73" s="9" t="s">
         <v>51</v>
@@ -5730,67 +5736,67 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>6.0165588734623306E-2</v>
+        <v>5.5224484997181182E-2</v>
       </c>
       <c r="Q73" s="12">
-        <v>0.18855793075067021</v>
+        <v>0.19352168899747973</v>
       </c>
       <c r="R73" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B74" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="E74">
-        <v>502</v>
+        <v>6.38</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>4556146606080</v>
+        <v>10378409984</v>
       </c>
       <c r="H74" s="6">
-        <v>547</v>
+        <v>7.05</v>
       </c>
       <c r="I74" s="6">
-        <v>349</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J74" s="12">
-        <f>E74/I74-1</f>
-        <v>0.43839541547277938</v>
+        <f t="shared" si="2"/>
+        <v>0.49414519906323195</v>
       </c>
       <c r="K74" s="11">
-        <v>8.4243027888446214E-3</v>
+        <v>4.3887147335423204E-2</v>
       </c>
       <c r="L74" s="13">
-        <v>253932000000</v>
+        <v>4094312000</v>
       </c>
       <c r="M74" s="13">
-        <v>1312163000000</v>
+        <v>37637054000</v>
       </c>
       <c r="N74" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O74" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P74" s="12">
-        <v>5.6553169400770709E-2</v>
+        <v>0.13295465906847695</v>
       </c>
       <c r="Q74" s="12">
-        <v>0.19352168899747973</v>
+        <v>0.10878407220713927</v>
       </c>
       <c r="R74" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
@@ -5804,26 +5810,26 @@
         <v>109</v>
       </c>
       <c r="E75">
-        <v>13.56</v>
+        <v>13.82</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>133768585216</v>
+        <v>136724807680</v>
       </c>
       <c r="H75" s="6">
-        <v>13.86</v>
+        <v>14.32</v>
       </c>
       <c r="I75" s="6">
         <v>5.83</v>
       </c>
       <c r="J75" s="12">
-        <f>E75/I75-1</f>
-        <v>1.32590051457976</v>
+        <f t="shared" si="2"/>
+        <v>1.3704974271012009</v>
       </c>
       <c r="K75" s="11">
-        <v>3.8348082595870206E-2</v>
+        <v>3.7626628075253257E-2</v>
       </c>
       <c r="L75" s="13">
         <v>8510100000</v>
@@ -5838,52 +5844,52 @@
         <v>1</v>
       </c>
       <c r="P75" s="12">
-        <v>5.7901571597518998E-2</v>
+        <v>5.6759917456197226E-2</v>
       </c>
       <c r="Q75" s="12">
         <v>0.18453201842262756</v>
       </c>
       <c r="R75" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B76" s="1" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>319</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="E76">
-        <v>23.05</v>
+        <v>7.26</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>26222139392</v>
+        <v>4957853696</v>
       </c>
       <c r="H76" s="6">
-        <v>28.75</v>
+        <v>10.06</v>
       </c>
       <c r="I76" s="6">
-        <v>19.52</v>
+        <v>6.56</v>
       </c>
       <c r="J76" s="12">
-        <f>E76/I76-1</f>
-        <v>0.18084016393442637</v>
+        <f t="shared" si="2"/>
+        <v>0.10670731707317072</v>
       </c>
       <c r="K76" s="11">
-        <v>6.0737527114967459E-2</v>
+        <v>4.9173553719008264E-2</v>
       </c>
       <c r="L76" s="13">
-        <v>3446618000</v>
+        <v>618033000</v>
       </c>
       <c r="M76" s="13">
-        <v>34010798000</v>
+        <v>5033024000</v>
       </c>
       <c r="N76" s="9" t="s">
         <v>51</v>
@@ -5892,376 +5898,376 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>0.14732205665172873</v>
+        <v>0.1104942267042521</v>
       </c>
       <c r="Q76" s="12">
-        <v>0.10133893359397213</v>
+        <v>0.12279555988606453</v>
       </c>
       <c r="R76" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B77" s="1" t="s">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>160</v>
+        <v>317</v>
       </c>
       <c r="D77" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="E77">
-        <v>5.94</v>
+        <v>24.9</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>9662657536</v>
+        <v>22929016832</v>
       </c>
       <c r="H77" s="6">
-        <v>7.05</v>
+        <v>25.1</v>
       </c>
       <c r="I77" s="6">
-        <v>4.2699999999999996</v>
+        <v>9.9</v>
       </c>
       <c r="J77" s="12">
-        <f>E77/I77-1</f>
-        <v>0.39110070257611262</v>
+        <f t="shared" si="2"/>
+        <v>1.5151515151515151</v>
       </c>
       <c r="K77" s="11">
-        <v>4.7138047138047139E-2</v>
+        <v>3.1325301204819279E-3</v>
       </c>
       <c r="L77" s="13">
-        <v>4094312000</v>
+        <v>334940000</v>
       </c>
       <c r="M77" s="13">
-        <v>37637054000</v>
+        <v>3025375000</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O77" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P77" s="12">
-        <v>0.13611841037247432</v>
+        <v>0.12814880776817372</v>
       </c>
       <c r="Q77" s="12">
-        <v>0.10878407220713927</v>
+        <v>0.11071024253191752</v>
       </c>
       <c r="R77" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B78" s="1" t="s">
-        <v>391</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>392</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="E78">
-        <v>7.25</v>
+        <v>3.1</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>4159354112</v>
+        <v>19223781376</v>
       </c>
       <c r="H78" s="6">
-        <v>9.24</v>
+        <v>4.13</v>
       </c>
       <c r="I78" s="6">
-        <v>6.78</v>
+        <v>2.11</v>
       </c>
       <c r="J78" s="12">
-        <f>E78/I78-1</f>
-        <v>6.9321533923303758E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.4691943127962086</v>
       </c>
       <c r="K78" s="11">
-        <v>5.5172413793103454E-2</v>
+        <v>5.1612903225806452E-2</v>
       </c>
       <c r="L78" s="13">
-        <v>498120000</v>
+        <v>1677300000</v>
       </c>
       <c r="M78" s="13">
-        <v>3284848000</v>
+        <v>11188800000</v>
       </c>
       <c r="N78" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O78" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P78" s="12">
-        <v>9.3166915749945886E-2</v>
+        <v>8.6143675219317165E-2</v>
       </c>
       <c r="Q78" s="12">
-        <v>0.15164171979951585</v>
+        <v>0.1499088374088374</v>
       </c>
       <c r="R78" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B79" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C79" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D79" t="s">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="E79">
-        <v>7.6</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>5147206144</v>
+        <v>112839213056</v>
       </c>
       <c r="H79" s="6">
-        <v>10.06</v>
+        <v>11</v>
       </c>
       <c r="I79" s="6">
-        <v>6.56</v>
+        <v>6.84</v>
       </c>
       <c r="J79" s="12">
-        <f>E79/I79-1</f>
-        <v>0.15853658536585358</v>
+        <f t="shared" si="2"/>
+        <v>0.22514619883040954</v>
       </c>
       <c r="K79" s="11">
-        <v>4.6973684210526313E-2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="13">
-        <v>618033000</v>
+        <v>1187000000</v>
       </c>
       <c r="M79" s="13">
-        <v>5033024000</v>
+        <v>10278000000</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O79" s="6">
-        <v>1.0683760683760684</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P79" s="12">
-        <v>0.10710058083730889</v>
+        <v>9.8866428537302056E-2</v>
       </c>
       <c r="Q79" s="12">
-        <v>0.12279555988606453</v>
+        <v>0.1154893948238957</v>
       </c>
       <c r="R79" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B80" s="1" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E80">
-        <v>3.08</v>
+        <v>14.86</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>19099756544</v>
+        <v>62717816832</v>
       </c>
       <c r="H80" s="6">
-        <v>4.13</v>
+        <v>15.5</v>
       </c>
       <c r="I80" s="6">
-        <v>2.11</v>
+        <v>10.98</v>
       </c>
       <c r="J80" s="12">
-        <f>E80/I80-1</f>
-        <v>0.45971563981042673</v>
+        <f t="shared" si="2"/>
+        <v>0.35336976320582858</v>
       </c>
       <c r="K80" s="11">
-        <v>5.1948051948051945E-2</v>
+        <v>5.9623149394347243E-2</v>
       </c>
       <c r="L80" s="13">
-        <v>1677300000</v>
+        <v>11996000000</v>
       </c>
       <c r="M80" s="13">
-        <v>11188800000</v>
+        <v>138296000000</v>
       </c>
       <c r="N80" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O80" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P80" s="12">
-        <v>8.6660350383692061E-2</v>
+        <v>0.1397226238435702</v>
       </c>
       <c r="Q80" s="12">
-        <v>0.1499088374088374</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R80" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B81" s="1" t="s">
-        <v>265</v>
+        <v>135</v>
       </c>
       <c r="C81" t="s">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="D81" t="s">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="E81">
-        <v>8.0399999999999991</v>
+        <v>14.86</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>106072522752</v>
+        <v>62717816832</v>
       </c>
       <c r="H81" s="6">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="I81" s="6">
-        <v>6.84</v>
+        <v>10.98</v>
       </c>
       <c r="J81" s="12">
-        <f>E81/I81-1</f>
-        <v>0.17543859649122795</v>
+        <f t="shared" si="2"/>
+        <v>0.35336976320582858</v>
       </c>
       <c r="K81" s="11">
-        <v>0</v>
+        <v>5.9623149394347243E-2</v>
       </c>
       <c r="L81" s="13">
-        <v>1187000000</v>
+        <v>11996000000</v>
       </c>
       <c r="M81" s="13">
-        <v>10278000000</v>
+        <v>138296000000</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O81" s="6">
-        <v>7.6923076923076916</v>
+        <v>1</v>
       </c>
       <c r="P81" s="12">
-        <v>0.10668293584484501</v>
+        <v>0.1397226238435702</v>
       </c>
       <c r="Q81" s="12">
-        <v>0.1154893948238957</v>
+        <v>8.6741482038526066E-2</v>
       </c>
       <c r="R81" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B82" s="1" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E82">
-        <v>14.84</v>
+        <v>13.48</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>62298472448</v>
+        <v>61809164288</v>
       </c>
       <c r="H82" s="6">
-        <v>15.38</v>
+        <v>14.7</v>
       </c>
       <c r="I82" s="6">
-        <v>10.98</v>
+        <v>7.51</v>
       </c>
       <c r="J82" s="12">
-        <f>E82/I82-1</f>
-        <v>0.35154826958105634</v>
+        <f t="shared" si="2"/>
+        <v>0.79494007989347537</v>
       </c>
       <c r="K82" s="11">
-        <v>5.9703504043126687E-2</v>
+        <v>3.2492581602373886E-2</v>
       </c>
       <c r="L82" s="13">
-        <v>11996000000</v>
+        <v>3967214824.1399999</v>
       </c>
       <c r="M82" s="13">
-        <v>138296000000</v>
+        <v>41038539262.660004</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O82" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P82" s="12">
-        <v>0.14040841874998103</v>
+        <v>0.11672724972844652</v>
       </c>
       <c r="Q82" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>9.6670468672106824E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B83" s="1" t="s">
-        <v>135</v>
+        <v>391</v>
       </c>
       <c r="C83" t="s">
-        <v>179</v>
+        <v>392</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="E83">
-        <v>14.84</v>
+        <v>7.59</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>62298472448</v>
+        <v>4354717184</v>
       </c>
       <c r="H83" s="6">
-        <v>15.38</v>
+        <v>9.24</v>
       </c>
       <c r="I83" s="6">
-        <v>10.98</v>
+        <v>6.78</v>
       </c>
       <c r="J83" s="12">
-        <f>E83/I83-1</f>
-        <v>0.35154826958105634</v>
+        <f t="shared" si="2"/>
+        <v>0.11946902654867242</v>
       </c>
       <c r="K83" s="11">
-        <v>5.9703504043126687E-2</v>
+        <v>5.2700922266139663E-2</v>
       </c>
       <c r="L83" s="13">
-        <v>11996000000</v>
+        <v>371538000</v>
       </c>
       <c r="M83" s="13">
-        <v>138296000000</v>
+        <v>3037286000</v>
       </c>
       <c r="N83" s="9" t="s">
         <v>68</v>
@@ -6270,67 +6276,67 @@
         <v>1</v>
       </c>
       <c r="P83" s="12">
-        <v>0.14040841874998103</v>
+        <v>6.8355299987935519E-2</v>
       </c>
       <c r="Q83" s="12">
-        <v>8.6741482038526066E-2</v>
+        <v>0.12232565520665489</v>
       </c>
       <c r="R83" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B84" s="1" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="D84" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="E84">
-        <v>13.86</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>62332297216</v>
+        <v>1884819200</v>
       </c>
       <c r="H84" s="6">
-        <v>14.7</v>
+        <v>2.54</v>
       </c>
       <c r="I84" s="6">
-        <v>7.51</v>
+        <v>1.72</v>
       </c>
       <c r="J84" s="12">
-        <f>E84/I84-1</f>
-        <v>0.84553928095872166</v>
+        <f t="shared" si="2"/>
+        <v>0.16860465116279055</v>
       </c>
       <c r="K84" s="11">
-        <v>3.1601731601731603E-2</v>
+        <v>5.4726368159203988E-2</v>
       </c>
       <c r="L84" s="13">
-        <v>3967214824.1399999</v>
+        <v>238321000</v>
       </c>
       <c r="M84" s="13">
-        <v>41038539262.660004</v>
+        <v>6087917000</v>
       </c>
       <c r="N84" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O84" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P84" s="12">
-        <v>0.11506944091670368</v>
+        <v>0.15574050207149945</v>
       </c>
       <c r="Q84" s="12">
-        <v>9.6670468672106824E-2</v>
+        <v>3.9146558666946343E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
@@ -6344,13 +6350,13 @@
         <v>104</v>
       </c>
       <c r="E85">
-        <v>31.65</v>
+        <v>33.1</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>71313776640</v>
+        <v>75590467584</v>
       </c>
       <c r="H85" s="6">
         <v>61.55</v>
@@ -6359,11 +6365,11 @@
         <v>24.85</v>
       </c>
       <c r="J85" s="12">
-        <f>E85/I85-1</f>
-        <v>0.27364185110663963</v>
+        <f t="shared" si="2"/>
+        <v>0.33199195171026163</v>
       </c>
       <c r="K85" s="11">
-        <v>1.7946287519747233E-2</v>
+        <v>1.7160120845921448E-2</v>
       </c>
       <c r="L85" s="13">
         <v>5261270000</v>
@@ -6378,106 +6384,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>7.2914023197588759E-2</v>
+        <v>6.9081657557763493E-2</v>
       </c>
       <c r="Q85" s="12">
         <v>0.12176329850933591</v>
       </c>
       <c r="R85" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B86" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D86" t="s">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="E86">
-        <v>1.94</v>
+        <v>51.95</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>1801431680</v>
+        <v>1066865983488</v>
       </c>
       <c r="H86" s="6">
-        <v>2.54</v>
+        <v>59.8</v>
       </c>
       <c r="I86" s="6">
-        <v>1.72</v>
+        <v>32.65</v>
       </c>
       <c r="J86" s="12">
-        <f>E86/I86-1</f>
-        <v>0.12790697674418605</v>
+        <f t="shared" si="2"/>
+        <v>0.59111791730474739</v>
       </c>
       <c r="K86" s="11">
-        <v>5.6701030927835051E-2</v>
+        <v>4.9085659287776702E-2</v>
       </c>
       <c r="L86" s="13">
-        <v>238321000</v>
+        <v>189900000000</v>
       </c>
       <c r="M86" s="13">
-        <v>6087917000</v>
+        <v>2315380000000</v>
       </c>
       <c r="N86" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O86" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>0.16471638365729493</v>
+        <v>0.13152822578296461</v>
       </c>
       <c r="Q86" s="12">
-        <v>3.9146558666946343E-2</v>
+        <v>8.2016774784268678E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B87" s="1" t="s">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>316</v>
+        <v>67</v>
       </c>
       <c r="D87" t="s">
-        <v>308</v>
+        <v>66</v>
       </c>
       <c r="E87">
-        <v>49.7</v>
+        <v>53.2</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>1032298889216</v>
+        <v>137838542848</v>
       </c>
       <c r="H87" s="6">
-        <v>59.8</v>
+        <v>82.25</v>
       </c>
       <c r="I87" s="6">
-        <v>32.65</v>
+        <v>37.85</v>
       </c>
       <c r="J87" s="12">
-        <f>E87/I87-1</f>
-        <v>0.52220520673813176</v>
+        <f t="shared" si="2"/>
+        <v>0.40554821664465002</v>
       </c>
       <c r="K87" s="11">
-        <v>5.1307847082494966E-2</v>
+        <v>1.9736842105263157E-2</v>
       </c>
       <c r="L87" s="13">
-        <v>189900000000</v>
+        <v>6350637223.7200003</v>
       </c>
       <c r="M87" s="13">
-        <v>2315380000000</v>
+        <v>57896384836.860001</v>
       </c>
       <c r="N87" s="9" t="s">
         <v>51</v>
@@ -6486,52 +6492,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>0.13454327719395667</v>
+        <v>6.3915976641537461E-2</v>
       </c>
       <c r="Q87" s="12">
-        <v>8.2016774784268678E-2</v>
+        <v>0.10968970241604512</v>
       </c>
       <c r="R87" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B88" s="1" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
+        <v>164</v>
       </c>
       <c r="E88">
-        <v>53.55</v>
+        <v>6.46</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>135770128384</v>
+        <v>46276145152</v>
       </c>
       <c r="H88" s="6">
-        <v>82.25</v>
+        <v>10.72</v>
       </c>
       <c r="I88" s="6">
-        <v>37.85</v>
+        <v>5</v>
       </c>
       <c r="J88" s="12">
-        <f>E88/I88-1</f>
-        <v>0.41479524438573301</v>
+        <f t="shared" si="2"/>
+        <v>0.29200000000000004</v>
       </c>
       <c r="K88" s="11">
-        <v>1.9607843137254905E-2</v>
+        <v>6.6563467492260067E-2</v>
       </c>
       <c r="L88" s="13">
-        <v>6350637223.7200003</v>
+        <v>6749146000</v>
       </c>
       <c r="M88" s="13">
-        <v>57896384836.860001</v>
+        <v>70848374000</v>
       </c>
       <c r="N88" s="9" t="s">
         <v>51</v>
@@ -6540,52 +6546,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>6.5186143652232173E-2</v>
+        <v>9.1429094736514824E-2</v>
       </c>
       <c r="Q88" s="12">
-        <v>0.10968970241604512</v>
+        <v>9.5261833390841127E-2</v>
       </c>
       <c r="R88" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B89" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="E89">
-        <v>21.45</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>126326136832</v>
+        <v>22669867008</v>
       </c>
       <c r="H89" s="6">
-        <v>26.6</v>
+        <v>11.68</v>
       </c>
       <c r="I89" s="6">
-        <v>16.02</v>
+        <v>5.19</v>
       </c>
       <c r="J89" s="12">
-        <f>E89/I89-1</f>
-        <v>0.33895131086142327</v>
+        <f t="shared" si="2"/>
+        <v>0.8362235067437378</v>
       </c>
       <c r="K89" s="11">
-        <v>3.3100233100233099E-2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="13">
-        <v>10795274825</v>
+        <v>13493113000</v>
       </c>
       <c r="M89" s="13">
-        <v>215275428010</v>
+        <v>208027754000</v>
       </c>
       <c r="N89" s="9" t="s">
         <v>51</v>
@@ -6594,52 +6600,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P89" s="12">
-        <v>0.13918556900974152</v>
+        <v>0.11832657836434349</v>
       </c>
       <c r="Q89" s="12">
-        <v>5.0146340085309396E-2</v>
+        <v>6.4862080854845933E-2</v>
       </c>
       <c r="R89" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B90" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C90" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D90" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="E90">
-        <v>6.66</v>
+        <v>22.15</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>48207273984</v>
+        <v>127867518976</v>
       </c>
       <c r="H90" s="6">
-        <v>10.72</v>
+        <v>26.6</v>
       </c>
       <c r="I90" s="6">
-        <v>5</v>
+        <v>16.02</v>
       </c>
       <c r="J90" s="12">
-        <f>E90/I90-1</f>
-        <v>0.33200000000000007</v>
+        <f t="shared" si="2"/>
+        <v>0.38264669163545562</v>
       </c>
       <c r="K90" s="11">
-        <v>6.4564564564564567E-2</v>
+        <v>3.2054176072234764E-2</v>
       </c>
       <c r="L90" s="13">
-        <v>6749146000</v>
+        <v>10795274825</v>
       </c>
       <c r="M90" s="13">
-        <v>70848374000</v>
+        <v>215275428010</v>
       </c>
       <c r="N90" s="9" t="s">
         <v>51</v>
@@ -6648,52 +6654,52 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>8.9243845539888608E-2</v>
+        <v>0.13664379695871273</v>
       </c>
       <c r="Q90" s="12">
-        <v>9.5261833390841127E-2</v>
+        <v>5.0146340085309396E-2</v>
       </c>
       <c r="R90" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B91" s="1" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="C91" t="s">
-        <v>180</v>
+        <v>314</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="E91">
-        <v>8.9</v>
+        <v>1.73</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>20970444800</v>
+        <v>63864332288</v>
       </c>
       <c r="H91" s="6">
-        <v>11.68</v>
+        <v>2.08</v>
       </c>
       <c r="I91" s="6">
-        <v>5.19</v>
+        <v>1.18</v>
       </c>
       <c r="J91" s="12">
-        <f>E91/I91-1</f>
-        <v>0.71483622350674358</v>
+        <f t="shared" si="2"/>
+        <v>0.46610169491525433</v>
       </c>
       <c r="K91" s="11">
-        <v>0</v>
+        <v>3.236994219653179E-2</v>
       </c>
       <c r="L91" s="13">
-        <v>13493113000</v>
+        <v>12616717000</v>
       </c>
       <c r="M91" s="13">
-        <v>208027754000</v>
+        <v>231208465000</v>
       </c>
       <c r="N91" s="9" t="s">
         <v>51</v>
@@ -6702,13 +6708,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P91" s="12">
-        <v>0.12000048131470691</v>
+        <v>0.1249556499731697</v>
       </c>
       <c r="Q91" s="12">
-        <v>6.4862080854845933E-2</v>
+        <v>5.4568577322633927E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
@@ -6722,13 +6728,13 @@
         <v>109</v>
       </c>
       <c r="E92">
-        <v>8.5399999999999991</v>
+        <v>8.33</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>5736420352</v>
+        <v>5595360768</v>
       </c>
       <c r="H92" s="6">
         <v>9.15</v>
@@ -6737,11 +6743,11 @@
         <v>5.6</v>
       </c>
       <c r="J92" s="12">
-        <f>E92/I92-1</f>
-        <v>0.52499999999999991</v>
+        <f t="shared" si="2"/>
+        <v>0.48750000000000004</v>
       </c>
       <c r="K92" s="11">
-        <v>5.9718969555035133E-2</v>
+        <v>6.1224489795918366E-2</v>
       </c>
       <c r="L92" s="13">
         <v>1136392000</v>
@@ -6756,268 +6762,268 @@
         <v>1</v>
       </c>
       <c r="P92" s="12">
-        <v>0.10973642034761508</v>
+        <v>0.11125183825866611</v>
       </c>
       <c r="Q92" s="12">
         <v>6.5089877530620205E-2</v>
       </c>
       <c r="R92" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B93" s="1" t="s">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="D93" t="s">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="E93">
-        <v>1.63</v>
+        <v>12.68</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>62819385344</v>
+        <v>96055566336</v>
       </c>
       <c r="H93" s="6">
-        <v>2.08</v>
+        <v>12.76</v>
       </c>
       <c r="I93" s="6">
-        <v>1.18</v>
+        <v>9.02</v>
       </c>
       <c r="J93" s="12">
-        <f>E93/I93-1</f>
-        <v>0.3813559322033897</v>
+        <f t="shared" si="2"/>
+        <v>0.40576496674057649</v>
       </c>
       <c r="K93" s="11">
-        <v>3.4355828220858899E-2</v>
+        <v>6.2145110410094642E-2</v>
       </c>
       <c r="L93" s="13">
-        <v>12616717000</v>
+        <v>8154000000</v>
       </c>
       <c r="M93" s="13">
-        <v>231208465000</v>
+        <v>79588000000</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O93" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P93" s="12">
-        <v>0.12617790814124877</v>
+        <v>5.9360286407885883E-2</v>
       </c>
       <c r="Q93" s="12">
-        <v>5.4568577322633927E-2</v>
+        <v>0.10245263104990703</v>
       </c>
       <c r="R93" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B94" s="1" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D94" t="s">
         <v>98</v>
       </c>
       <c r="E94">
-        <v>12.16</v>
+        <v>5.68</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>92116377600</v>
+        <v>725591588864</v>
       </c>
       <c r="H94" s="6">
-        <v>12.16</v>
+        <v>6.98</v>
       </c>
       <c r="I94" s="6">
-        <v>8.8800000000000008</v>
+        <v>4.08</v>
       </c>
       <c r="J94" s="12">
-        <f>E94/I94-1</f>
-        <v>0.36936936936936937</v>
+        <f t="shared" si="2"/>
+        <v>0.39215686274509798</v>
       </c>
       <c r="K94" s="11">
-        <v>6.4802631578947376E-2</v>
+        <v>4.5774647887323945E-2</v>
       </c>
       <c r="L94" s="13">
-        <v>8154000000</v>
+        <v>44563000000</v>
       </c>
       <c r="M94" s="13">
-        <v>79588000000</v>
+        <v>463922000000</v>
       </c>
       <c r="N94" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O94" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>6.1112811870355915E-2</v>
+        <v>6.7756874037394055E-2</v>
       </c>
       <c r="Q94" s="12">
-        <v>0.10245263104990703</v>
+        <v>9.605709580489824E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B95" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E95">
-        <v>5.53</v>
+        <v>10.84</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>729047564288</v>
+        <v>34629029888</v>
       </c>
       <c r="H95" s="6">
-        <v>6.98</v>
+        <v>11.34</v>
       </c>
       <c r="I95" s="6">
-        <v>4.08</v>
+        <v>5.6</v>
       </c>
       <c r="J95" s="12">
-        <f>E95/I95-1</f>
-        <v>0.35539215686274517</v>
+        <f t="shared" si="2"/>
+        <v>0.93571428571428572</v>
       </c>
       <c r="K95" s="11">
-        <v>4.701627486437613E-2</v>
+        <v>2.9520295202952032E-2</v>
       </c>
       <c r="L95" s="13">
-        <v>44563000000</v>
+        <v>1990539000</v>
       </c>
       <c r="M95" s="13">
-        <v>463922000000</v>
+        <v>18620709000</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O95" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P95" s="12">
-        <v>6.7425248481168668E-2</v>
+        <v>5.3248047334694702E-2</v>
       </c>
       <c r="Q95" s="12">
-        <v>9.605709580489824E-2</v>
+        <v>0.10689920561026972</v>
       </c>
       <c r="R95" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B96" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D96" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E96">
-        <v>10.64</v>
+        <v>9.26</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>33196802048</v>
+        <v>283337490432</v>
       </c>
       <c r="H96" s="6">
-        <v>10.8</v>
+        <v>11.56</v>
       </c>
       <c r="I96" s="6">
-        <v>5.6</v>
+        <v>5.88</v>
       </c>
       <c r="J96" s="12">
-        <f>E96/I96-1</f>
-        <v>0.90000000000000013</v>
+        <f t="shared" si="2"/>
+        <v>0.5748299319727892</v>
       </c>
       <c r="K96" s="11">
-        <v>3.007518796992481E-2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="13">
-        <v>1990539000</v>
+        <v>26994000000</v>
       </c>
       <c r="M96" s="13">
-        <v>18620709000</v>
+        <v>363169000000</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O96" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P96" s="12">
-        <v>5.5369410412929997E-2</v>
+        <v>9.7631408980080311E-2</v>
       </c>
       <c r="Q96" s="12">
-        <v>0.10689920561026972</v>
+        <v>7.4329031387590908E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B97" s="1" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>161</v>
+        <v>312</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E97">
-        <v>9.24</v>
+        <v>9.86</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>282725515264</v>
+        <v>25392556032</v>
       </c>
       <c r="H97" s="6">
-        <v>11.56</v>
+        <v>13.78</v>
       </c>
       <c r="I97" s="6">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="J97" s="12">
-        <f>E97/I97-1</f>
-        <v>0.5714285714285714</v>
+        <f t="shared" si="2"/>
+        <v>0.81249999999999978</v>
       </c>
       <c r="K97" s="11">
-        <v>0</v>
+        <v>3.0425963488843813E-2</v>
       </c>
       <c r="L97" s="13">
-        <v>26994000000</v>
+        <v>9652467000</v>
       </c>
       <c r="M97" s="13">
-        <v>363169000000</v>
+        <v>173514401000</v>
       </c>
       <c r="N97" s="9" t="s">
         <v>51</v>
@@ -7026,106 +7032,106 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>9.7834094251568249E-2</v>
+        <v>0.10423682715764739</v>
       </c>
       <c r="Q97" s="12">
-        <v>7.4329031387590908E-2</v>
+        <v>5.5629198178196171E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B98" s="1" t="s">
-        <v>258</v>
+        <v>117</v>
       </c>
       <c r="C98" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E98">
-        <v>48</v>
+        <v>1.91</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>183841914880</v>
+        <v>6798396416</v>
       </c>
       <c r="H98" s="6">
-        <v>52.95</v>
+        <v>2.95</v>
       </c>
       <c r="I98" s="6">
-        <v>36.9</v>
+        <v>1.37</v>
       </c>
       <c r="J98" s="12">
-        <f>E98/I98-1</f>
-        <v>0.30081300813008127</v>
+        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
+        <v>0.39416058394160558</v>
       </c>
       <c r="K98" s="11">
-        <v>4.5874999999999999E-2</v>
+        <v>4.9214659685863874E-2</v>
       </c>
       <c r="L98" s="13">
-        <v>41737000000</v>
+        <v>2220197000</v>
       </c>
       <c r="M98" s="13">
-        <v>794927000000</v>
+        <v>71097505000</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O98" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P98" s="12">
-        <v>0.10777237889220671</v>
+        <v>0.11810265841672082</v>
       </c>
       <c r="Q98" s="12">
-        <v>5.2504192208844336E-2</v>
+        <v>3.1227495254580313E-2</v>
       </c>
       <c r="R98" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B99" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C99" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D99" t="s">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="E99">
-        <v>9.77</v>
+        <v>5.45</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>24759818240</v>
+        <v>115553075200</v>
       </c>
       <c r="H99" s="6">
-        <v>13.78</v>
+        <v>7.03</v>
       </c>
       <c r="I99" s="6">
-        <v>5.44</v>
+        <v>4.22</v>
       </c>
       <c r="J99" s="12">
-        <f>E99/I99-1</f>
-        <v>0.7959558823529409</v>
+        <f t="shared" si="3"/>
+        <v>0.29146919431279628</v>
       </c>
       <c r="K99" s="11">
-        <v>3.0706243602865915E-2</v>
+        <v>5.5045871559633024E-2</v>
       </c>
       <c r="L99" s="13">
-        <v>9652467000</v>
+        <v>42109966000</v>
       </c>
       <c r="M99" s="13">
-        <v>173514401000</v>
+        <v>746176876000</v>
       </c>
       <c r="N99" s="9" t="s">
         <v>51</v>
@@ -7134,10 +7140,10 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>0.1049077771719794</v>
+        <v>0.10000360084802316</v>
       </c>
       <c r="Q99" s="12">
-        <v>5.5629198178196171E-2</v>
+        <v>5.643429507724386E-2</v>
       </c>
       <c r="R99" s="14">
         <v>70</v>
@@ -7145,149 +7151,149 @@
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B100" s="1" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
+        <v>311</v>
       </c>
       <c r="D100" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E100">
-        <v>1.82</v>
+        <v>48.7</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>6478053376</v>
+        <v>186522959872</v>
       </c>
       <c r="H100" s="6">
-        <v>2.95</v>
+        <v>52.95</v>
       </c>
       <c r="I100" s="6">
-        <v>1.37</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="J100" s="12">
-        <f>E100/I100-1</f>
-        <v>0.32846715328467146</v>
+        <f t="shared" si="3"/>
+        <v>0.30040053404539391</v>
       </c>
       <c r="K100" s="11">
-        <v>5.1648351648351645E-2</v>
+        <v>4.5215605749486652E-2</v>
       </c>
       <c r="L100" s="13">
-        <v>2220197000</v>
+        <v>41737000000</v>
       </c>
       <c r="M100" s="13">
-        <v>71097505000</v>
+        <v>794927000000</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O100" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P100" s="12">
-        <v>0.12001692222552164</v>
+        <v>0.10703140726644196</v>
       </c>
       <c r="Q100" s="12">
-        <v>3.1227495254580313E-2</v>
+        <v>5.2504192208844336E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B101" s="1" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="D101" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="E101">
-        <v>5.51</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>113926422528</v>
+        <v>123901050880</v>
       </c>
       <c r="H101" s="6">
-        <v>7.03</v>
+        <v>37.25</v>
       </c>
       <c r="I101" s="6">
-        <v>4.22</v>
+        <v>28.1</v>
       </c>
       <c r="J101" s="12">
-        <f>E101/I101-1</f>
-        <v>0.3056872037914693</v>
+        <f t="shared" si="3"/>
+        <v>0.24733096085409234</v>
       </c>
       <c r="K101" s="11">
-        <v>5.4446460980036297E-2</v>
+        <v>4.9643366619115552E-2</v>
       </c>
       <c r="L101" s="13">
-        <v>42109966000</v>
+        <v>16863000000</v>
       </c>
       <c r="M101" s="13">
-        <v>746176876000</v>
+        <v>448320000000</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O101" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P101" s="12">
-        <v>0.10036650356687733</v>
+        <v>0.1159255492885391</v>
       </c>
       <c r="Q101" s="12">
-        <v>5.643429507724386E-2</v>
+        <v>3.7613758029978586E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E102">
-        <v>34.700000000000003</v>
+        <v>5.76</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>121442369536</v>
+        <v>44588507136</v>
       </c>
       <c r="H102" s="6">
-        <v>37.25</v>
+        <v>5.81</v>
       </c>
       <c r="I102" s="6">
-        <v>28.1</v>
+        <v>3.9</v>
       </c>
       <c r="J102" s="12">
-        <f>E102/I102-1</f>
-        <v>0.23487544483985778</v>
+        <f t="shared" si="3"/>
+        <v>0.47692307692307701</v>
       </c>
       <c r="K102" s="11">
-        <v>5.0144092219020171E-2</v>
+        <v>6.6493055555555555E-2</v>
       </c>
       <c r="L102" s="13">
-        <v>16863000000</v>
+        <v>5474000000</v>
       </c>
       <c r="M102" s="13">
-        <v>448320000000</v>
+        <v>59407000000</v>
       </c>
       <c r="N102" s="9" t="s">
         <v>68</v>
@@ -7296,268 +7302,268 @@
         <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>0.1179186491718056</v>
+        <v>5.6877746025575292E-2</v>
       </c>
       <c r="Q102" s="12">
-        <v>3.7613758029978586E-2</v>
+        <v>9.2144023431582137E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B103" s="1" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="D103" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E103">
-        <v>5.55</v>
+        <v>1.7</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>42962886656</v>
+        <v>9286301696</v>
       </c>
       <c r="H103" s="6">
-        <v>5.59</v>
+        <v>1.82</v>
       </c>
       <c r="I103" s="6">
-        <v>3.87</v>
+        <v>0.81</v>
       </c>
       <c r="J103" s="12">
-        <f>E103/I103-1</f>
-        <v>0.43410852713178283</v>
+        <f t="shared" si="3"/>
+        <v>1.0987654320987654</v>
       </c>
       <c r="K103" s="11">
-        <v>6.9009009009009012E-2</v>
+        <v>0.02</v>
       </c>
       <c r="L103" s="13">
-        <v>5474000000</v>
+        <v>1384865000</v>
       </c>
       <c r="M103" s="13">
-        <v>59407000000</v>
+        <v>23827484000</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O103" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P103" s="12">
-        <v>5.7854977567373143E-2</v>
+        <v>7.2528237414429889E-2</v>
       </c>
       <c r="Q103" s="12">
-        <v>9.2144023431582137E-2</v>
+        <v>5.8120488088461209E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B104" s="1" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="D104" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="E104">
-        <v>1.63</v>
+        <v>25</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>8903923712</v>
+        <v>28203501568</v>
       </c>
       <c r="H104" s="6">
-        <v>1.82</v>
+        <v>26.65</v>
       </c>
       <c r="I104" s="6">
-        <v>0.81</v>
+        <v>14.52</v>
       </c>
       <c r="J104" s="12">
-        <f>E104/I104-1</f>
-        <v>1.0123456790123453</v>
+        <f t="shared" si="3"/>
+        <v>0.721763085399449</v>
       </c>
       <c r="K104" s="11">
-        <v>2.0858895705521477E-2</v>
+        <v>3.7599999999999995E-2</v>
       </c>
       <c r="L104" s="13">
-        <v>1384865000</v>
+        <v>3838344000</v>
       </c>
       <c r="M104" s="13">
-        <v>23827484000</v>
+        <v>81520873000</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O104" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P104" s="12">
-        <v>7.3913695294373277E-2</v>
+        <v>8.3403357612738135E-2</v>
       </c>
       <c r="Q104" s="12">
-        <v>5.8120488088461209E-2</v>
+        <v>4.7084186647510511E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B105" s="1" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="D105" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="E105">
-        <v>25.4</v>
+        <v>11.76</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>28151074816</v>
+        <v>205222576128</v>
       </c>
       <c r="H105" s="6">
-        <v>26.65</v>
+        <v>12.46</v>
       </c>
       <c r="I105" s="6">
-        <v>14.52</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J105" s="12">
-        <f>E105/I105-1</f>
-        <v>0.74931129476584024</v>
+        <f t="shared" si="3"/>
+        <v>0.27826086956521756</v>
       </c>
       <c r="K105" s="11">
-        <v>3.7007874015748031E-2</v>
+        <v>3.545918367346939E-2</v>
       </c>
       <c r="L105" s="13">
-        <v>3838344000</v>
+        <v>16758000000</v>
       </c>
       <c r="M105" s="13">
-        <v>81520873000</v>
+        <v>269590000000</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O105" s="6">
-        <v>1</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P105" s="12">
-        <v>8.3498477461101964E-2</v>
+        <v>5.9418087533155119E-2</v>
       </c>
       <c r="Q105" s="12">
-        <v>4.7084186647510511E-2</v>
+        <v>6.2161059386475759E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B106" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D106" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E106">
-        <v>11.28</v>
+        <v>6.72</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>198537035776</v>
+        <v>7012588544</v>
       </c>
       <c r="H106" s="6">
-        <v>12.46</v>
+        <v>7</v>
       </c>
       <c r="I106" s="6">
-        <v>9.1999999999999993</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J106" s="12">
-        <f>E106/I106-1</f>
-        <v>0.22608695652173916</v>
+        <f t="shared" si="3"/>
+        <v>0.67164179104477628</v>
       </c>
       <c r="K106" s="11">
-        <v>3.6968085106382977E-2</v>
+        <v>0</v>
       </c>
       <c r="L106" s="13">
-        <v>16758000000</v>
+        <v>303335000</v>
       </c>
       <c r="M106" s="13">
-        <v>269590000000</v>
+        <v>3620162000</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O106" s="6">
-        <v>1.0683760683760684</v>
+        <v>1</v>
       </c>
       <c r="P106" s="12">
-        <v>6.0766342228791952E-2</v>
+        <v>5.1250867323799743E-2</v>
       </c>
       <c r="Q106" s="12">
-        <v>6.2161059386475759E-2</v>
+        <v>8.3790449156695201E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B107" s="1" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="D107" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="E107">
-        <v>6.85</v>
+        <v>2.37</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>7148248576</v>
+        <v>10179149824</v>
       </c>
       <c r="H107" s="6">
-        <v>7</v>
+        <v>3.04</v>
       </c>
       <c r="I107" s="6">
-        <v>4.0199999999999996</v>
+        <v>1.93</v>
       </c>
       <c r="J107" s="12">
-        <f>E107/I107-1</f>
-        <v>0.70398009950248763</v>
+        <f t="shared" si="3"/>
+        <v>0.22797927461139911</v>
       </c>
       <c r="K107" s="11">
-        <v>0</v>
+        <v>4.514767932489451E-2</v>
       </c>
       <c r="L107" s="13">
-        <v>303335000</v>
+        <v>1938532000</v>
       </c>
       <c r="M107" s="13">
-        <v>3620162000</v>
+        <v>49986396000</v>
       </c>
       <c r="N107" s="9" t="s">
         <v>68</v>
@@ -7566,52 +7572,52 @@
         <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>5.0102476266993719E-2</v>
+        <v>6.3128576869622949E-2</v>
       </c>
       <c r="Q107" s="12">
-        <v>8.3790449156695201E-2</v>
+        <v>3.8781191586606881E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B108" s="1" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>322</v>
       </c>
       <c r="D108" t="s">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="E108">
-        <v>2.3199999999999998</v>
+        <v>9.44</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>9964399616</v>
+        <v>9996959744</v>
       </c>
       <c r="H108" s="6">
-        <v>3.04</v>
+        <v>12.88</v>
       </c>
       <c r="I108" s="6">
-        <v>1.93</v>
+        <v>4.47</v>
       </c>
       <c r="J108" s="12">
-        <f>E108/I108-1</f>
-        <v>0.20207253886010368</v>
+        <f t="shared" si="3"/>
+        <v>1.1118568232662192</v>
       </c>
       <c r="K108" s="11">
-        <v>4.6120689655172416E-2</v>
+        <v>1.5042372881355931E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>1938532000</v>
+        <v>161696000</v>
       </c>
       <c r="M108" s="13">
-        <v>49986396000</v>
+        <v>3260547000</v>
       </c>
       <c r="N108" s="9" t="s">
         <v>68</v>
@@ -7620,52 +7626,52 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>6.3573167667339003E-2</v>
+        <v>1.6564905324730955E-2</v>
       </c>
       <c r="Q108" s="12">
-        <v>3.8781191586606881E-2</v>
+        <v>4.95916789422143E-2</v>
       </c>
       <c r="R108" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B109" s="1" t="s">
-        <v>268</v>
+        <v>389</v>
       </c>
       <c r="C109" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="D109" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E109">
-        <v>9.7200000000000006</v>
+        <v>2.1</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>10331874304</v>
+        <v>11957545984</v>
       </c>
       <c r="H109" s="6">
-        <v>12.88</v>
+        <v>2.99</v>
       </c>
       <c r="I109" s="6">
-        <v>4.47</v>
+        <v>0.91</v>
       </c>
       <c r="J109" s="12">
-        <f>E109/I109-1</f>
-        <v>1.1744966442953024</v>
+        <f t="shared" si="3"/>
+        <v>1.3076923076923079</v>
       </c>
       <c r="K109" s="11">
-        <v>1.4609053497942384E-2</v>
+        <v>7.1428571428571426E-3</v>
       </c>
       <c r="L109" s="13">
-        <v>161696000</v>
+        <v>429393000</v>
       </c>
       <c r="M109" s="13">
-        <v>3260547000</v>
+        <v>18333659000</v>
       </c>
       <c r="N109" s="9" t="s">
         <v>68</v>
@@ -7674,67 +7680,67 @@
         <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>1.6015412728627863E-2</v>
+        <v>3.5561230253856144E-2</v>
       </c>
       <c r="Q109" s="12">
-        <v>4.95916789422143E-2</v>
+        <v>2.3421020321148112E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B110" s="1" t="s">
-        <v>389</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
-        <v>390</v>
+        <v>195</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E110">
-        <v>1.51</v>
+        <v>45.9</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>8360310784</v>
+        <v>466949898240</v>
       </c>
       <c r="H110" s="6">
-        <v>2.99</v>
+        <v>59.7</v>
       </c>
       <c r="I110" s="6">
-        <v>0.91</v>
+        <v>15.24</v>
       </c>
       <c r="J110" s="12">
-        <f>E110/I110-1</f>
-        <v>0.65934065934065922</v>
+        <f t="shared" si="3"/>
+        <v>2.0118110236220472</v>
       </c>
       <c r="K110" s="11">
-        <v>9.9337748344370865E-3</v>
+        <v>0</v>
       </c>
       <c r="L110" s="13">
-        <v>429393000</v>
+        <v>984027000</v>
       </c>
       <c r="M110" s="13">
-        <v>18333659000</v>
+        <v>32183526000</v>
       </c>
       <c r="N110" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O110" s="6">
-        <v>1</v>
+        <v>7.6923076923076916</v>
       </c>
       <c r="P110" s="12">
-        <v>5.0650805134496227E-2</v>
+        <v>1.4924131353543519E-2</v>
       </c>
       <c r="Q110" s="12">
-        <v>2.3421020321148112E-2</v>
+        <v>3.0575487595734537E-2</v>
       </c>
       <c r="R110" s="14">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
@@ -7748,26 +7754,26 @@
         <v>153</v>
       </c>
       <c r="E111">
-        <v>15.08</v>
+        <v>14.98</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>15487310848</v>
+        <v>15507594240</v>
       </c>
       <c r="H111" s="6">
-        <v>15.14</v>
+        <v>15.22</v>
       </c>
       <c r="I111" s="6">
         <v>10.36</v>
       </c>
       <c r="J111" s="12">
-        <f>E111/I111-1</f>
-        <v>0.45559845559845558</v>
+        <f t="shared" si="3"/>
+        <v>0.44594594594594605</v>
       </c>
       <c r="K111" s="11">
-        <v>7.161803713527852E-2</v>
+        <v>7.209612817089453E-2</v>
       </c>
       <c r="L111" s="13">
         <v>984000000</v>
@@ -7782,106 +7788,106 @@
         <v>1</v>
       </c>
       <c r="P111" s="12">
-        <v>2.4333962357159761E-2</v>
+        <v>2.4321762538888916E-2</v>
       </c>
       <c r="Q111" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R111" s="14">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B112" s="1" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="C112" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D112" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="E112">
-        <v>44.3</v>
+        <v>31.8</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>454030688256</v>
+        <v>32470661120</v>
       </c>
       <c r="H112" s="6">
-        <v>59.7</v>
+        <v>36</v>
       </c>
       <c r="I112" s="6">
-        <v>15.24</v>
+        <v>22.4</v>
       </c>
       <c r="J112" s="12">
-        <f>E112/I112-1</f>
-        <v>1.9068241469816272</v>
+        <f t="shared" si="3"/>
+        <v>0.41964285714285721</v>
       </c>
       <c r="K112" s="11">
         <v>0</v>
       </c>
       <c r="L112" s="13">
-        <v>984027000</v>
+        <v>-90314000</v>
       </c>
       <c r="M112" s="13">
-        <v>32183526000</v>
+        <v>18374441000</v>
       </c>
       <c r="N112" s="9" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O112" s="6">
-        <v>7.6923076923076916</v>
+        <v>1.0683760683760684</v>
       </c>
       <c r="P112" s="12">
-        <v>1.5314213482591913E-2</v>
+        <v>-3.3088640153491021E-3</v>
       </c>
       <c r="Q112" s="12">
-        <v>3.0575487595734537E-2</v>
+        <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R112" s="14">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B113" s="1" t="s">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="C113" t="s">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="D113" t="s">
-        <v>174</v>
+        <v>377</v>
       </c>
       <c r="E113">
-        <v>29.1</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>29713719296</v>
+        <v>5170202112</v>
       </c>
       <c r="H113" s="6">
-        <v>36</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I113" s="6">
-        <v>22.4</v>
+        <v>0.99</v>
       </c>
       <c r="J113" s="12">
-        <f>E113/I113-1</f>
-        <v>0.29910714285714302</v>
+        <f t="shared" si="3"/>
+        <v>1.2828282828282824</v>
       </c>
       <c r="K113" s="11">
         <v>0</v>
       </c>
       <c r="L113" s="13">
-        <v>-90314000</v>
+        <v>-732033000</v>
       </c>
       <c r="M113" s="13">
-        <v>18374441000</v>
+        <v>7864121000</v>
       </c>
       <c r="N113" s="9" t="s">
         <v>51</v>
@@ -7890,13 +7896,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P113" s="12">
-        <v>-3.6543561486810142E-3</v>
+        <v>-12.890588161786203</v>
       </c>
       <c r="Q113" s="12">
-        <v>-4.9151971480384084E-3</v>
+        <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R113" s="14">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.5">
@@ -7910,26 +7916,26 @@
         <v>229</v>
       </c>
       <c r="E114">
-        <v>34.6</v>
+        <v>36.85</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>365818871808</v>
+        <v>391192215552</v>
       </c>
       <c r="H114" s="6">
-        <v>37</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="I114" s="6">
         <v>21.5</v>
       </c>
       <c r="J114" s="12">
-        <f>E114/I114-1</f>
-        <v>0.60930232558139541</v>
+        <f t="shared" si="3"/>
+        <v>0.71395348837209305</v>
       </c>
       <c r="K114" s="11">
-        <v>5.7485549132947976E-2</v>
+        <v>5.397557666214383E-2</v>
       </c>
       <c r="M114" s="13">
         <v>415994000000</v>
@@ -7943,38 +7949,38 @@
     </row>
     <row r="115" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B115" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C115" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D115" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E115">
-        <v>7.34</v>
+        <v>5.89</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>736642465792</v>
+        <v>742181240832</v>
       </c>
       <c r="H115" s="6">
-        <v>7.62</v>
+        <v>5.95</v>
       </c>
       <c r="I115" s="6">
-        <v>5.08</v>
+        <v>3.89</v>
       </c>
       <c r="J115" s="12">
-        <f>E115/I115-1</f>
-        <v>0.4448818897637794</v>
+        <f t="shared" si="3"/>
+        <v>0.51413881748071977</v>
       </c>
       <c r="K115" s="11">
-        <v>5.1634877384196184E-2</v>
+        <v>0</v>
       </c>
       <c r="M115" s="13">
-        <v>2314289000000</v>
+        <v>1271649000000</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>51</v>
@@ -7985,38 +7991,38 @@
     </row>
     <row r="116" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B116" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C116" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D116" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E116">
-        <v>6.13</v>
+        <v>7.59</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>2820498784256</v>
+        <v>499557105664</v>
       </c>
       <c r="H116" s="6">
-        <v>6.48</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="I116" s="6">
-        <v>4.0599999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="J116" s="12">
-        <f>E116/I116-1</f>
-        <v>0.50985221674876868</v>
+        <f t="shared" si="3"/>
+        <v>0.78169014084507049</v>
       </c>
       <c r="K116" s="11">
-        <v>5.0244698205546494E-2</v>
+        <v>4.6772068511198944E-2</v>
       </c>
       <c r="M116" s="13">
-        <v>6434377000000</v>
+        <v>2066897000000</v>
       </c>
       <c r="N116" s="9" t="s">
         <v>51</v>
@@ -8027,38 +8033,38 @@
     </row>
     <row r="117" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B117" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C117" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D117" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E117">
-        <v>5.69</v>
+        <v>7.43</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G117" s="7">
-        <v>745543630848</v>
+        <v>731638792192</v>
       </c>
       <c r="H117" s="6">
-        <v>5.69</v>
+        <v>7.62</v>
       </c>
       <c r="I117" s="6">
-        <v>3.89</v>
+        <v>5.08</v>
       </c>
       <c r="J117" s="12">
-        <f>E117/I117-1</f>
-        <v>0.46272493573264795</v>
+        <f t="shared" si="3"/>
+        <v>0.46259842519685024</v>
       </c>
       <c r="K117" s="11">
-        <v>0</v>
+        <v>5.1009421265141325E-2</v>
       </c>
       <c r="M117" s="13">
-        <v>1271649000000</v>
+        <v>2314289000000</v>
       </c>
       <c r="N117" s="9" t="s">
         <v>51</v>
@@ -8069,38 +8075,38 @@
     </row>
     <row r="118" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B118" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D118" t="s">
         <v>231</v>
       </c>
       <c r="E118">
-        <v>8.1999999999999993</v>
+        <v>6.22</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="7">
-        <v>2198501982208</v>
+        <v>2837022769152</v>
       </c>
       <c r="H118" s="6">
-        <v>8.2200000000000006</v>
+        <v>6.48</v>
       </c>
       <c r="I118" s="6">
-        <v>5.23</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J118" s="12">
-        <f>E118/I118-1</f>
-        <v>0.56787762906309736</v>
+        <f t="shared" si="3"/>
+        <v>0.53201970443349755</v>
       </c>
       <c r="K118" s="11">
-        <v>4.9146341463414643E-2</v>
+        <v>4.9517684887459806E-2</v>
       </c>
       <c r="M118" s="13">
-        <v>6128626000000</v>
+        <v>6434377000000</v>
       </c>
       <c r="N118" s="9" t="s">
         <v>51</v>
@@ -8111,38 +8117,38 @@
     </row>
     <row r="119" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B119" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C119" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D119" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E119">
-        <v>7.84</v>
+        <v>8.36</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G119" s="7">
-        <v>517655592960</v>
+        <v>2241315733504</v>
       </c>
       <c r="H119" s="6">
-        <v>7.97</v>
+        <v>8.56</v>
       </c>
       <c r="I119" s="6">
-        <v>4.26</v>
+        <v>5.23</v>
       </c>
       <c r="J119" s="12">
-        <f>E119/I119-1</f>
-        <v>0.84037558685446023</v>
+        <f t="shared" si="3"/>
+        <v>0.59847036328871872</v>
       </c>
       <c r="K119" s="11">
-        <v>4.5280612244897961E-2</v>
+        <v>4.8205741626794266E-2</v>
       </c>
       <c r="M119" s="13">
-        <v>2066897000000</v>
+        <v>6128626000000</v>
       </c>
       <c r="N119" s="9" t="s">
         <v>51</v>
@@ -8151,9 +8157,19 @@
         <v>1.0683760683760684</v>
       </c>
     </row>
+    <row r="120" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B120" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="121" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B121" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:R20" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R119">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:R121">
       <sortCondition ref="R1:R20"/>
     </sortState>
   </autoFilter>
@@ -8260,26 +8276,26 @@
         <v>379</v>
       </c>
       <c r="E2">
-        <v>14.67</v>
+        <v>15.24</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="7">
-        <v>8456624640</v>
+        <v>8785205248</v>
       </c>
       <c r="H2" s="6">
         <v>22.97</v>
       </c>
       <c r="I2" s="6">
-        <v>14.63</v>
+        <v>14.43</v>
       </c>
       <c r="J2" s="12">
         <f t="shared" ref="J2:J21" si="0">E2/I2-1</f>
-        <v>2.7341079972658111E-3</v>
+        <v>5.6133056133056192E-2</v>
       </c>
       <c r="K2" s="11">
-        <v>7.2256305385139746E-2</v>
+        <v>6.9553805774278221E-2</v>
       </c>
       <c r="L2" s="13">
         <v>1115194928.8599999</v>
@@ -8294,7 +8310,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="12">
-        <v>0.15876583501828892</v>
+        <v>0.15167086821618922</v>
       </c>
       <c r="Q2" s="12">
         <v>0.23555964555041065</v>
@@ -8314,13 +8330,13 @@
         <v>59</v>
       </c>
       <c r="E3">
-        <v>119.56</v>
+        <v>125.26</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="7">
-        <v>464085286912</v>
+        <v>486210469888</v>
       </c>
       <c r="H3" s="6">
         <v>178.76</v>
@@ -8330,10 +8346,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.12442396313364057</v>
+        <v>0.17803065926831563</v>
       </c>
       <c r="K3" s="11">
-        <v>4.8051187688190028E-2</v>
+        <v>4.5864601628612486E-2</v>
       </c>
       <c r="L3" s="13">
         <v>44203762134.690002</v>
@@ -8348,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="12">
-        <v>0.13097839090027466</v>
+        <v>0.12291997371370084</v>
       </c>
       <c r="Q3" s="12">
         <v>0.33164773684009302</v>
@@ -8368,13 +8384,13 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>8.7799999999999994</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G4" s="7">
-        <v>15132065792</v>
+        <v>15287178240</v>
       </c>
       <c r="H4" s="6">
         <v>9.76</v>
@@ -8384,10 +8400,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.24362606232294626</v>
+        <v>0.25637393767705374</v>
       </c>
       <c r="K4" s="11">
-        <v>5.1252847380410027E-2</v>
+        <v>5.073280721533259E-2</v>
       </c>
       <c r="L4" s="13">
         <v>1541495041.8099999</v>
@@ -8402,13 +8418,13 @@
         <v>1</v>
       </c>
       <c r="P4" s="12">
-        <v>0.18801291100167322</v>
+        <v>0.18452198761651467</v>
       </c>
       <c r="Q4" s="12">
         <v>0.1287769864044232</v>
       </c>
       <c r="R4" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
@@ -8422,13 +8438,13 @@
         <v>243</v>
       </c>
       <c r="E5">
-        <v>54.82</v>
+        <v>55.23</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G5" s="7">
-        <v>26531291136</v>
+        <v>26729717760</v>
       </c>
       <c r="H5" s="6">
         <v>77</v>
@@ -8438,10 +8454,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>7.807276302851518E-2</v>
+        <v>8.6135693215339204E-2</v>
       </c>
       <c r="K5" s="11">
-        <v>4.3779642466253189E-2</v>
+        <v>4.3454644215100487E-2</v>
       </c>
       <c r="L5" s="13">
         <v>2927600473.4699998</v>
@@ -8456,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="12">
-        <v>0.11426165027253582</v>
+        <v>0.1133835609035308</v>
       </c>
       <c r="Q5" s="12">
         <v>2.4700897903693781</v>
@@ -8476,26 +8492,26 @@
         <v>61</v>
       </c>
       <c r="E6">
-        <v>12.78</v>
+        <v>12.94</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G6" s="7">
-        <v>13076495360</v>
+        <v>13240207360</v>
       </c>
       <c r="H6" s="6">
-        <v>13.65</v>
+        <v>14.08</v>
       </c>
       <c r="I6" s="6">
         <v>9.18</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.39215686274509798</v>
+        <v>0.40958605664488013</v>
       </c>
       <c r="K6" s="11">
-        <v>4.6948356807511735E-2</v>
+        <v>4.6367851622874809E-2</v>
       </c>
       <c r="L6" s="13">
         <v>1324661161.8800001</v>
@@ -8510,13 +8526,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>0.16694372699931267</v>
+        <v>0.16356893781078333</v>
       </c>
       <c r="Q6" s="12">
         <v>0.11527544475940803</v>
       </c>
       <c r="R6" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
@@ -8530,13 +8546,13 @@
         <v>59</v>
       </c>
       <c r="E7">
-        <v>65.930000000000007</v>
+        <v>67.16</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G7" s="7">
-        <v>99320250368</v>
+        <v>101173190656</v>
       </c>
       <c r="H7" s="6">
         <v>109</v>
@@ -8546,10 +8562,10 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>4.3691625771727249E-2</v>
+        <v>6.3162893778692331E-2</v>
       </c>
       <c r="K7" s="11">
-        <v>7.0483846503867728E-2</v>
+        <v>6.9192972007147122E-2</v>
       </c>
       <c r="L7" s="13">
         <v>9146031692.1700001</v>
@@ -8564,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="12">
-        <v>0.1178070730450875</v>
+        <v>0.11506090027873969</v>
       </c>
       <c r="Q7" s="12">
         <v>0.1772890708714728</v>
@@ -8584,26 +8600,26 @@
         <v>87</v>
       </c>
       <c r="E8">
-        <v>21.5</v>
+        <v>21.56</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G8" s="7">
-        <v>10875882496</v>
+        <v>10906233856</v>
       </c>
       <c r="H8" s="6">
         <v>36.86</v>
       </c>
       <c r="I8" s="6">
-        <v>21.48</v>
+        <v>21.21</v>
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>9.3109869646190724E-4</v>
+        <v>1.6501650165016368E-2</v>
       </c>
       <c r="K8" s="11">
-        <v>6.0465116279069767E-2</v>
+        <v>6.0296846011131729E-2</v>
       </c>
       <c r="L8" s="13">
         <v>1139111857.1300001</v>
@@ -8618,13 +8634,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.13239740807001091</v>
+        <v>0.13193199198759362</v>
       </c>
       <c r="Q8" s="12">
         <v>0.14359699139283291</v>
       </c>
       <c r="R8" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
@@ -8638,13 +8654,13 @@
         <v>61</v>
       </c>
       <c r="E9">
-        <v>13.53</v>
+        <v>13.25</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="7">
-        <v>24299880448</v>
+        <v>23797000192</v>
       </c>
       <c r="H9" s="6">
         <v>15.58</v>
@@ -8654,10 +8670,10 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.17959895379250201</v>
+        <v>0.15518744551002617</v>
       </c>
       <c r="K9" s="11">
-        <v>4.0650406504065047E-2</v>
+        <v>4.1509433962264156E-2</v>
       </c>
       <c r="L9" s="13">
         <v>1789808265.4000001</v>
@@ -8672,13 +8688,13 @@
         <v>1</v>
       </c>
       <c r="P9" s="12">
-        <v>0.15046031016706551</v>
+        <v>0.15710173097313881</v>
       </c>
       <c r="Q9" s="12">
         <v>0.11487361117809598</v>
       </c>
       <c r="R9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -8692,13 +8708,13 @@
         <v>83</v>
       </c>
       <c r="E10">
-        <v>42.71</v>
+        <v>48.03</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="7">
-        <v>21626122240</v>
+        <v>24319893504</v>
       </c>
       <c r="H10" s="6">
         <v>71.2</v>
@@ -8708,10 +8724,10 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>9.4286446323341044E-2</v>
+        <v>0.23059185242121449</v>
       </c>
       <c r="K10" s="11">
-        <v>2.3413720440177945E-2</v>
+        <v>2.0820320632937747E-2</v>
       </c>
       <c r="L10" s="13">
         <v>1949016683.5799999</v>
@@ -8726,13 +8742,13 @@
         <v>1</v>
       </c>
       <c r="P10" s="12">
-        <v>0.11045980042056196</v>
+        <v>9.5829634690265855E-2</v>
       </c>
       <c r="Q10" s="12">
         <v>0.18520750257426369</v>
       </c>
       <c r="R10" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -8746,26 +8762,26 @@
         <v>61</v>
       </c>
       <c r="E11">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="7">
-        <v>14061801472</v>
+        <v>13661424640</v>
       </c>
       <c r="H11" s="6">
         <v>17.100000000000001</v>
       </c>
       <c r="I11" s="6">
-        <v>10.08</v>
+        <v>9.91</v>
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.0726538849646978E-3</v>
       </c>
       <c r="K11" s="11">
-        <v>3.9682539682539687E-2</v>
+        <v>4.004004004004004E-2</v>
       </c>
       <c r="L11" s="13">
         <v>1310024443.6900001</v>
@@ -8780,13 +8796,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.20965076363001239</v>
+        <v>0.22400371485328285</v>
       </c>
       <c r="Q11" s="12">
         <v>6.7272978770076819E-2</v>
       </c>
       <c r="R11" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
@@ -8800,26 +8816,26 @@
         <v>56</v>
       </c>
       <c r="E12">
-        <v>107.68</v>
+        <v>123.59</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G12" s="7">
-        <v>57236008960</v>
+        <v>66331942912</v>
       </c>
       <c r="H12" s="6">
-        <v>121.53</v>
+        <v>125.98</v>
       </c>
       <c r="I12" s="6">
         <v>50.21</v>
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>1.1445927106154152</v>
+        <v>1.4614618601872138</v>
       </c>
       <c r="K12" s="11">
-        <v>1.950222882615156E-2</v>
+        <v>1.6991665992394208E-2</v>
       </c>
       <c r="L12" s="13">
         <v>2351242906.4000001</v>
@@ -8834,13 +8850,13 @@
         <v>1</v>
       </c>
       <c r="P12" s="12">
-        <v>4.1732937392270866E-2</v>
+        <v>3.5931862379403122E-2</v>
       </c>
       <c r="Q12" s="12">
         <v>0.22747360748931247</v>
       </c>
       <c r="R12" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -8854,13 +8870,13 @@
         <v>330</v>
       </c>
       <c r="E13">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G13" s="7">
-        <v>24229054464</v>
+        <v>24096411648</v>
       </c>
       <c r="H13" s="6">
         <v>6.4</v>
@@ -8870,10 +8886,10 @@
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.15368421052631587</v>
+        <v>0.14736842105263159</v>
       </c>
       <c r="K13" s="11">
-        <v>3.6678832116788324E-2</v>
+        <v>3.6880733944954128E-2</v>
       </c>
       <c r="L13" s="13">
         <v>2697498300</v>
@@ -8888,13 +8904,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="12">
-        <v>0.13909048640312721</v>
+        <v>0.14004833735872468</v>
       </c>
       <c r="Q13" s="12">
         <v>0.10219141995145171</v>
       </c>
       <c r="R13" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -8908,26 +8924,26 @@
         <v>153</v>
       </c>
       <c r="E14">
-        <v>21.78</v>
+        <v>20.81</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G14" s="7">
-        <v>21938558976</v>
+        <v>20961497088</v>
       </c>
       <c r="H14" s="6">
         <v>30.34</v>
       </c>
       <c r="I14" s="6">
-        <v>20.53</v>
+        <v>20.28</v>
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>6.0886507549926971E-2</v>
+        <v>2.6134122287968298E-2</v>
       </c>
       <c r="K14" s="11">
-        <v>5.0505050505050504E-2</v>
+        <v>5.2859202306583378E-2</v>
       </c>
       <c r="L14" s="13">
         <v>1686709166</v>
@@ -8942,13 +8958,13 @@
         <v>1</v>
       </c>
       <c r="P14" s="12">
-        <v>8.8418515522175958E-2</v>
+        <v>9.319163167713776E-2</v>
       </c>
       <c r="Q14" s="12">
         <v>0.15707734987937541</v>
       </c>
       <c r="R14" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
@@ -8962,26 +8978,26 @@
         <v>50</v>
       </c>
       <c r="E15">
-        <v>208.54</v>
+        <v>167.45</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G15" s="7">
-        <v>38549241856</v>
+        <v>43383951360</v>
       </c>
       <c r="H15" s="6">
-        <v>333.5</v>
+        <v>238.21428</v>
       </c>
       <c r="I15" s="6">
-        <v>173</v>
+        <v>123.57143000000001</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.20543352601156073</v>
+        <v>0.35508668953656986</v>
       </c>
       <c r="K15" s="11">
-        <v>5.130910137143954E-3</v>
+        <v>4.5625559868617506E-3</v>
       </c>
       <c r="L15" s="13">
         <v>2107869808</v>
@@ -8996,13 +9012,13 @@
         <v>1</v>
       </c>
       <c r="P15" s="12">
-        <v>5.6537424157839612E-2</v>
+        <v>5.0047428753545634E-2</v>
       </c>
       <c r="Q15" s="12">
         <v>0.16379150253744434</v>
       </c>
       <c r="R15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -9016,13 +9032,13 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>12.18</v>
+        <v>12.98</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G16" s="7">
-        <v>4305910272</v>
+        <v>4588728320</v>
       </c>
       <c r="H16" s="6">
         <v>14.68</v>
@@ -9032,10 +9048,10 @@
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>0.25179856115107913</v>
+        <v>0.33401849948612528</v>
       </c>
       <c r="K16" s="11">
-        <v>3.9408866995073892E-2</v>
+        <v>3.697996918335901E-2</v>
       </c>
       <c r="L16" s="13">
         <v>339663210.94999999</v>
@@ -9050,13 +9066,13 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.10039516018508211</v>
+        <v>9.2650223727235179E-2</v>
       </c>
       <c r="Q16" s="12">
         <v>0.12344330708657501</v>
       </c>
       <c r="R16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
@@ -9070,26 +9086,26 @@
         <v>61</v>
       </c>
       <c r="E17">
-        <v>9.1999999999999993</v>
+        <v>9.69</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G17" s="7">
-        <v>11165580288</v>
+        <v>11760268288</v>
       </c>
       <c r="H17" s="6">
         <v>10.27</v>
       </c>
       <c r="I17" s="6">
-        <v>7.54</v>
+        <v>7.55</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.22015915119363383</v>
+        <v>0.28344370860927159</v>
       </c>
       <c r="K17" s="11">
-        <v>4.3478260869565223E-2</v>
+        <v>4.1279669762641906E-2</v>
       </c>
       <c r="L17" s="13">
         <v>1074859531.29</v>
@@ -9104,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="12">
-        <v>0.11308388846473458</v>
+        <v>0.10642528693022021</v>
       </c>
       <c r="Q17" s="12">
         <v>0.1128187617835559</v>
@@ -9124,13 +9140,13 @@
         <v>61</v>
       </c>
       <c r="E18">
-        <v>7.76</v>
+        <v>8.09</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="7">
-        <v>17244428288</v>
+        <v>17977759744</v>
       </c>
       <c r="H18" s="6">
         <v>10.53</v>
@@ -9140,10 +9156,10 @@
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>8.5314685314685335E-2</v>
+        <v>0.13146853146853132</v>
       </c>
       <c r="K18" s="11">
-        <v>3.8659793814432991E-2</v>
+        <v>3.7082818294190356E-2</v>
       </c>
       <c r="L18" s="13">
         <v>1357643494.6700001</v>
@@ -9158,13 +9174,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="12">
-        <v>0.12062979961304117</v>
+        <v>0.1132505931281193</v>
       </c>
       <c r="Q18" s="12">
         <v>9.9124832291360196E-2</v>
       </c>
       <c r="R18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
@@ -9178,26 +9194,26 @@
         <v>54</v>
       </c>
       <c r="E19">
-        <v>53.88</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G19" s="7">
-        <v>30996948992</v>
+        <v>40581304320</v>
       </c>
       <c r="H19" s="6">
-        <v>68.39</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="I19" s="6">
         <v>36.25</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>0.48634482758620701</v>
+        <v>0.94758620689655149</v>
       </c>
       <c r="K19" s="11">
-        <v>8.3518930957683733E-3</v>
+        <v>6.373937677053825E-3</v>
       </c>
       <c r="L19" s="13">
         <v>939613185.05999994</v>
@@ -9212,13 +9228,13 @@
         <v>1</v>
       </c>
       <c r="P19" s="12">
-        <v>3.3693862499442798E-2</v>
+        <v>2.5075655844200882E-2</v>
       </c>
       <c r="Q19" s="12">
         <v>0.10362091390188061</v>
       </c>
       <c r="R19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
@@ -9232,13 +9248,13 @@
         <v>251</v>
       </c>
       <c r="E20">
-        <v>13.87</v>
+        <v>14.56</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="7">
-        <v>4048028928</v>
+        <v>4252364288</v>
       </c>
       <c r="H20" s="6">
         <v>18.78</v>
@@ -9248,10 +9264,10 @@
       </c>
       <c r="J20" s="12">
         <f t="shared" si="0"/>
-        <v>0.18547008547008548</v>
+        <v>0.24444444444444446</v>
       </c>
       <c r="K20" s="11">
-        <v>2.8839221341023794E-2</v>
+        <v>2.7472527472527472E-2</v>
       </c>
       <c r="L20" s="13">
         <v>225008130.19999999</v>
@@ -9266,13 +9282,13 @@
         <v>1</v>
       </c>
       <c r="P20" s="12">
-        <v>6.9519589342282306E-2</v>
+        <v>6.5391278920123294E-2</v>
       </c>
       <c r="Q20" s="12">
         <v>8.957258997528339E-2</v>
       </c>
       <c r="R20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
@@ -9286,26 +9302,26 @@
         <v>229</v>
       </c>
       <c r="E21">
-        <v>23.16</v>
+        <v>24.47</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G21" s="7">
-        <v>490130440192</v>
+        <v>517853675520</v>
       </c>
       <c r="H21" s="6">
-        <v>24.33</v>
+        <v>25.45</v>
       </c>
       <c r="I21" s="6">
         <v>15.68</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.47704081632653073</v>
+        <v>0.56058673469387754</v>
       </c>
       <c r="K21" s="11">
-        <v>4.5768566493955096E-2</v>
+        <v>4.3318348998774014E-2</v>
       </c>
       <c r="M21" s="13">
         <v>2415915000000</v>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D0FF65-BF30-4DD8-BC93-F53436035885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08424A03-6E48-4746-A496-E3AA96CF4521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="396">
   <si>
     <t>Ticker</t>
   </si>
@@ -1284,6 +1284,9 @@
   </si>
   <si>
     <t>2331.HK</t>
+  </si>
+  <si>
+    <t>0823.HK</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V121"/>
+  <dimension ref="B1:V122"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -7067,7 +7070,7 @@
         <v>1.37</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
+        <f t="shared" ref="J98:J119" si="3">E98/I98-1</f>
         <v>0.39416058394160558</v>
       </c>
       <c r="K98" s="11">
@@ -8165,6 +8168,11 @@
     <row r="121" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B121" s="1" t="s">
         <v>394</v>
+      </c>
+    </row>
+    <row r="122" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B122" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08424A03-6E48-4746-A496-E3AA96CF4521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C08A4F-CE92-4F5C-950F-5E2DB0084197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="400">
   <si>
     <t>Ticker</t>
   </si>
@@ -1287,6 +1287,18 @@
   </si>
   <si>
     <t>0823.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>LI NING</t>
+  </si>
+  <si>
+    <t>LINK REIT</t>
+  </si>
+  <si>
+    <t>REIT - Retail</t>
   </si>
 </sst>
 </file>
@@ -1871,26 +1883,26 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>13.82</v>
+        <v>15.42</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>247295082496</v>
+        <v>271720431616</v>
       </c>
       <c r="H2" s="6">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="I2" s="6">
         <v>9.52</v>
       </c>
       <c r="J2" s="12">
         <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.45168067226890773</v>
+        <v>0.61974789915966388</v>
       </c>
       <c r="K2" s="11">
-        <v>0.11215629522431259</v>
+        <v>0.10051880674448768</v>
       </c>
       <c r="L2" s="13">
         <v>70144988000</v>
@@ -1905,13 +1917,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.56796921781344512</v>
+        <v>0.47925186167505085</v>
       </c>
       <c r="Q2" s="12">
         <v>0.26042924055386191</v>
       </c>
       <c r="R2" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.5">
@@ -1925,13 +1937,13 @@
         <v>153</v>
       </c>
       <c r="E3">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>2748734464</v>
+        <v>2965739776</v>
       </c>
       <c r="H3" s="6">
         <v>3.55</v>
@@ -1941,10 +1953,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.31034482758620707</v>
+        <v>0.4137931034482758</v>
       </c>
       <c r="K3" s="11">
-        <v>5.5592105263157901E-2</v>
+        <v>5.1524390243902443E-2</v>
       </c>
       <c r="L3" s="13">
         <v>504294000</v>
@@ -1959,7 +1971,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.36124847109610175</v>
+        <v>0.31536263347456289</v>
       </c>
       <c r="Q3" s="12">
         <v>0.29581628786323422</v>
@@ -1979,13 +1991,13 @@
         <v>148</v>
       </c>
       <c r="E4">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>8923508736</v>
+        <v>9202853888</v>
       </c>
       <c r="H4" s="6">
         <v>3.35</v>
@@ -1995,10 +2007,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.3347457627118644</v>
+        <v>0.39406779661016955</v>
       </c>
       <c r="K4" s="11">
-        <v>4.8571428571428571E-2</v>
+        <v>4.6504559270516714E-2</v>
       </c>
       <c r="L4" s="13">
         <v>1871151000</v>
@@ -2013,13 +2025,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.42299422870228842</v>
+        <v>0.39938743571668051</v>
       </c>
       <c r="Q4" s="12">
         <v>0.28956319566547578</v>
       </c>
       <c r="R4" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
@@ -2033,26 +2045,26 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>7.58</v>
+        <v>7.92</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>29577463808</v>
+        <v>30904158208</v>
       </c>
       <c r="H5" s="6">
-        <v>7.8</v>
+        <v>8.35</v>
       </c>
       <c r="I5" s="6">
         <v>4.22</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.79620853080568743</v>
+        <v>0.87677725118483418</v>
       </c>
       <c r="K5" s="11">
-        <v>5.6728232189973606E-3</v>
+        <v>5.4292929292929287E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2067,7 +2079,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.27373429830530244</v>
+        <v>0.25823826016454682</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
@@ -2087,13 +2099,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>133.69999999999999</v>
+        <v>146.6</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>88291868672</v>
+        <v>96810688512</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2103,10 +2115,10 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.46923076923076912</v>
+        <v>0.61098901098901082</v>
       </c>
       <c r="K6" s="11">
-        <v>1.4584891548242334E-2</v>
+        <v>1.330150068212824E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2121,7 +2133,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.53259166215192788</v>
+        <v>0.43518402790640787</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
@@ -2141,26 +2153,26 @@
         <v>306</v>
       </c>
       <c r="E7">
-        <v>5.64</v>
+        <v>6.13</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>377978683392</v>
+        <v>383386124288</v>
       </c>
       <c r="H7" s="6">
         <v>6.24</v>
       </c>
       <c r="I7" s="6">
-        <v>2.5099999999999998</v>
+        <v>2.52</v>
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>1.2470119521912353</v>
+        <v>1.4325396825396823</v>
       </c>
       <c r="K7" s="11">
-        <v>3.1914893617021274E-2</v>
+        <v>2.936378466557912E-2</v>
       </c>
       <c r="L7" s="13">
         <v>72477000000</v>
@@ -2175,7 +2187,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.18998498234880884</v>
+        <v>0.18749737468869018</v>
       </c>
       <c r="Q7" s="12">
         <v>0.22694806719794586</v>
@@ -2195,26 +2207,26 @@
         <v>146</v>
       </c>
       <c r="E8">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>13338602496</v>
+        <v>14815013888</v>
       </c>
       <c r="H8" s="6">
-        <v>3.1128110000000002</v>
+        <v>3.12</v>
       </c>
       <c r="I8" s="6">
         <v>2.23</v>
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.17488789237668168</v>
+        <v>0.30493273542600896</v>
       </c>
       <c r="K8" s="11">
-        <v>0.11450381679389313</v>
+        <v>0.10309278350515463</v>
       </c>
       <c r="L8" s="13">
         <v>2527643000</v>
@@ -2229,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.44294875583510041</v>
+        <v>0.35190160057272546</v>
       </c>
       <c r="Q8" s="12">
         <v>0.15337570692947131</v>
@@ -2249,26 +2261,26 @@
         <v>225</v>
       </c>
       <c r="E9">
-        <v>16.559999999999999</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>147142721536</v>
+        <v>149609152512</v>
       </c>
       <c r="H9" s="6">
-        <v>17.88</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I9" s="6">
         <v>10.6</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.5622641509433961</v>
+        <v>0.62830188679245302</v>
       </c>
       <c r="K9" s="11">
-        <v>4.3417874396135266E-2</v>
+        <v>4.1657010428736957E-2</v>
       </c>
       <c r="L9" s="13">
         <v>21175963859.630001</v>
@@ -2283,7 +2295,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.19446075104810709</v>
+        <v>0.19042378788707598</v>
       </c>
       <c r="Q9" s="12">
         <v>0.20347556909712136</v>
@@ -2303,26 +2315,26 @@
         <v>304</v>
       </c>
       <c r="E10">
-        <v>7.88</v>
+        <v>9.31</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>185906544640</v>
+        <v>215139205120</v>
       </c>
       <c r="H10" s="6">
-        <v>8.5399999999999991</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="I10" s="6">
         <v>4.58</v>
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>0.72052401746724892</v>
+        <v>1.0327510917030569</v>
       </c>
       <c r="K10" s="11">
-        <v>3.2360406091370558E-2</v>
+        <v>2.7389903329752954E-2</v>
       </c>
       <c r="L10" s="13">
         <v>29168443138.220001</v>
@@ -2337,13 +2349,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.16779916976867329</v>
+        <v>0.14497868317798404</v>
       </c>
       <c r="Q10" s="12">
         <v>0.2888078161719172</v>
       </c>
       <c r="R10" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -2357,26 +2369,26 @@
         <v>223</v>
       </c>
       <c r="E11">
-        <v>1.97</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>1970000000</v>
+        <v>2260000000</v>
       </c>
       <c r="H11" s="6">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="I11" s="6">
         <v>1.35</v>
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.45925925925925903</v>
+        <v>0.67407407407407383</v>
       </c>
       <c r="K11" s="11">
-        <v>0.1065989847715736</v>
+        <v>9.2920353982300891E-2</v>
       </c>
       <c r="L11" s="13">
         <v>315190000</v>
@@ -2391,13 +2403,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.14737850122718005</v>
+        <v>0.12978029294548438</v>
       </c>
       <c r="Q11" s="12">
         <v>0.51857007005524791</v>
       </c>
       <c r="R11" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
@@ -2411,13 +2423,13 @@
         <v>301</v>
       </c>
       <c r="E12">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>3303369984</v>
+        <v>3222800128</v>
       </c>
       <c r="H12" s="6">
         <v>1.66</v>
@@ -2427,10 +2439,10 @@
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.45132743362831862</v>
+        <v>0.41592920353982321</v>
       </c>
       <c r="K12" s="11">
-        <v>7.2560975609756093E-2</v>
+        <v>7.4374999999999997E-2</v>
       </c>
       <c r="L12" s="13">
         <v>929863000</v>
@@ -2445,13 +2457,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.32106674168545463</v>
+        <v>0.32965052125613736</v>
       </c>
       <c r="Q12" s="12">
         <v>0.15429118804462028</v>
       </c>
       <c r="R12" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -2465,13 +2477,13 @@
         <v>87</v>
       </c>
       <c r="E13">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>41159970816</v>
+        <v>42787975168</v>
       </c>
       <c r="H13" s="6">
         <v>7.38</v>
@@ -2481,10 +2493,10 @@
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.32743362831858391</v>
+        <v>0.39233038348082583</v>
       </c>
       <c r="K13" s="11">
-        <v>6.8222222222222226E-2</v>
+        <v>6.5042372881355934E-2</v>
       </c>
       <c r="L13" s="13">
         <v>5594372000</v>
@@ -2499,13 +2511,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.18472040109109944</v>
+        <v>0.1758714794662688</v>
       </c>
       <c r="Q13" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -2519,13 +2531,13 @@
         <v>301</v>
       </c>
       <c r="E14">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>2069900032</v>
+        <v>2022588032</v>
       </c>
       <c r="H14" s="6">
         <v>2.77</v>
@@ -2535,10 +2547,10 @@
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.28676470588235281</v>
+        <v>0.25735294117647056</v>
       </c>
       <c r="K14" s="11">
-        <v>3.4857142857142857E-2</v>
+        <v>3.5672514619883043E-2</v>
       </c>
       <c r="L14" s="13">
         <v>841215000</v>
@@ -2553,13 +2565,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.53165327323452871</v>
+        <v>0.54696151852339225</v>
       </c>
       <c r="Q14" s="12">
         <v>0.14567921288909008</v>
       </c>
       <c r="R14" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
@@ -2573,26 +2585,26 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>5.07</v>
+        <v>5.46</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>10483137536</v>
+        <v>11289532416</v>
       </c>
       <c r="H15" s="6">
-        <v>5.19</v>
+        <v>5.54</v>
       </c>
       <c r="I15" s="6">
         <v>3.15</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.60952380952380958</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="K15" s="11">
-        <v>4.9309664694280074E-2</v>
+        <v>4.5787545787545784E-2</v>
       </c>
       <c r="L15" s="13">
         <v>1576240000</v>
@@ -2607,13 +2619,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.27071585229147094</v>
+        <v>0.2396494228748017</v>
       </c>
       <c r="Q15" s="12">
         <v>0.16357040581906512</v>
       </c>
       <c r="R15" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2627,26 +2639,26 @@
         <v>308</v>
       </c>
       <c r="E16">
-        <v>15.3</v>
+        <v>17.02</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>54988509184</v>
+        <v>61170225152</v>
       </c>
       <c r="H16" s="6">
-        <v>16.600000000000001</v>
+        <v>17.28</v>
       </c>
       <c r="I16" s="6">
-        <v>7.55</v>
+        <v>7.62</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>1.0264900662251657</v>
+        <v>1.2335958005249341</v>
       </c>
       <c r="K16" s="11">
-        <v>2.2875816993464051E-2</v>
+        <v>2.0564042303172738E-2</v>
       </c>
       <c r="L16" s="13">
         <v>25585077000</v>
@@ -2661,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.27592878551536126</v>
+        <v>0.25868284229842736</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15251313559762292</v>
@@ -2681,13 +2693,13 @@
         <v>83</v>
       </c>
       <c r="E17">
-        <v>15.52</v>
+        <v>16.16</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>32660598784</v>
+        <v>32171489280</v>
       </c>
       <c r="H17" s="6">
         <v>17.059999999999999</v>
@@ -2697,10 +2709,10 @@
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.94974874371859297</v>
+        <v>1.0301507537688441</v>
       </c>
       <c r="K17" s="11">
-        <v>7.2164948453608255E-2</v>
+        <v>6.9306930693069313E-2</v>
       </c>
       <c r="L17" s="13">
         <v>5451928473.2399998</v>
@@ -2715,13 +2727,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.16123204623099219</v>
+        <v>0.16344490942638637</v>
       </c>
       <c r="Q17" s="12">
         <v>0.20973136925592797</v>
       </c>
       <c r="R17" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.5">
@@ -2735,13 +2747,13 @@
         <v>77</v>
       </c>
       <c r="E18">
-        <v>23.7</v>
+        <v>25.75</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>62879420416</v>
+        <v>68318355456</v>
       </c>
       <c r="H18" s="6">
         <v>26.15</v>
@@ -2751,10 +2763,10 @@
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.50955414012738864</v>
+        <v>0.64012738853503182</v>
       </c>
       <c r="K18" s="11">
-        <v>1.1476793248945148E-2</v>
+        <v>1.0563106796116505E-2</v>
       </c>
       <c r="L18" s="13">
         <v>1069250000</v>
@@ -2769,13 +2781,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P18" s="12">
-        <v>0.13675631647331854</v>
+        <v>0.12541472763078063</v>
       </c>
       <c r="Q18" s="12">
         <v>0.41587371596437778</v>
       </c>
       <c r="R18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
@@ -2789,26 +2801,26 @@
         <v>87</v>
       </c>
       <c r="E19">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>99177447424</v>
+        <v>101615181824</v>
       </c>
       <c r="H19" s="6">
-        <v>7.88</v>
+        <v>8.16</v>
       </c>
       <c r="I19" s="6">
         <v>4.84</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>0.5971074380165291</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="K19" s="11">
-        <v>8.2794307891332474E-3</v>
+        <v>8.0808080808080808E-3</v>
       </c>
       <c r="L19" s="13">
         <v>2553000000</v>
@@ -2823,13 +2835,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P19" s="12">
-        <v>0.17531850359793735</v>
+        <v>0.17158441585182907</v>
       </c>
       <c r="Q19" s="12">
         <v>0.18273566673824351</v>
       </c>
       <c r="R19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
@@ -2843,13 +2855,13 @@
         <v>87</v>
       </c>
       <c r="E20">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="7">
-        <v>1663267584</v>
+        <v>1728922880</v>
       </c>
       <c r="H20" s="6">
         <v>0.82</v>
@@ -2859,10 +2871,10 @@
       </c>
       <c r="J20" s="12">
         <f t="shared" si="0"/>
-        <v>0.80952380952380953</v>
+        <v>0.88095238095238115</v>
       </c>
       <c r="K20" s="11">
-        <v>4.8684210526315788E-2</v>
+        <v>4.6835443037974676E-2</v>
       </c>
       <c r="L20" s="13">
         <v>219938000</v>
@@ -2877,13 +2889,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P20" s="12">
-        <v>0.29986224591557764</v>
+        <v>0.27668052261777509</v>
       </c>
       <c r="Q20" s="12">
         <v>0.14466826109721026</v>
       </c>
       <c r="R20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
@@ -2897,26 +2909,26 @@
         <v>96</v>
       </c>
       <c r="E21">
-        <v>14.34</v>
+        <v>15.88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>12000945152</v>
+        <v>13216733184</v>
       </c>
       <c r="H21" s="6">
         <v>19.440000000000001</v>
       </c>
       <c r="I21" s="6">
-        <v>12.12</v>
+        <v>12.14</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.18316831683168333</v>
+        <v>0.30807248764415163</v>
       </c>
       <c r="K21" s="11">
-        <v>1.0320781032078103E-2</v>
+        <v>9.319899244332493E-3</v>
       </c>
       <c r="L21" s="13">
         <v>199557000</v>
@@ -2931,7 +2943,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P21" s="12">
-        <v>0.1737432874401873</v>
+        <v>0.15272691042116737</v>
       </c>
       <c r="Q21" s="12">
         <v>0.18009145491283626</v>
@@ -2951,13 +2963,13 @@
         <v>74</v>
       </c>
       <c r="E22">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>2797089024</v>
+        <v>2973856512</v>
       </c>
       <c r="H22" s="6">
         <v>3.34</v>
@@ -2967,10 +2979,10 @@
       </c>
       <c r="J22" s="12">
         <f t="shared" si="0"/>
-        <v>0.40104166666666674</v>
+        <v>0.48958333333333326</v>
       </c>
       <c r="K22" s="11">
-        <v>0.10855018587360594</v>
+        <v>0.10209790209790209</v>
       </c>
       <c r="L22" s="13">
         <v>762183000</v>
@@ -2985,13 +2997,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="12">
-        <v>0.21517658165819023</v>
+        <v>0.20494875361262907</v>
       </c>
       <c r="Q22" s="12">
         <v>0.15218339726363278</v>
       </c>
       <c r="R22" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
@@ -3005,13 +3017,13 @@
         <v>81</v>
       </c>
       <c r="E23">
-        <v>7.74</v>
+        <v>7.82</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>67453009920</v>
+        <v>67713384448</v>
       </c>
       <c r="H23" s="6">
         <v>8.6199999999999992</v>
@@ -3021,10 +3033,10 @@
       </c>
       <c r="J23" s="12">
         <f t="shared" si="0"/>
-        <v>9.3220338983050821E-2</v>
+        <v>0.10451977401129953</v>
       </c>
       <c r="K23" s="11">
-        <v>4.0826873385012917E-2</v>
+        <v>4.0409207161125317E-2</v>
       </c>
       <c r="L23" s="13">
         <v>13438000000</v>
@@ -3039,13 +3051,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.22551513898677181</v>
+        <v>0.22459655578037108</v>
       </c>
       <c r="Q23" s="12">
         <v>0.15165160081705431</v>
       </c>
       <c r="R23" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
@@ -3059,13 +3071,13 @@
         <v>79</v>
       </c>
       <c r="E24">
-        <v>9.23</v>
+        <v>10.32</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>150141632512</v>
+        <v>164788715520</v>
       </c>
       <c r="H24" s="6">
         <v>10.76</v>
@@ -3075,10 +3087,10 @@
       </c>
       <c r="J24" s="12">
         <f t="shared" si="0"/>
-        <v>0.28910614525139677</v>
+        <v>0.44134078212290495</v>
       </c>
       <c r="K24" s="11">
-        <v>5.1895991332611045E-2</v>
+        <v>4.6414728682170538E-2</v>
       </c>
       <c r="L24" s="13">
         <v>32866046000</v>
@@ -3093,13 +3105,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>0.18769668293971206</v>
+        <v>0.17406796560984755</v>
       </c>
       <c r="Q24" s="12">
         <v>0.15266623500015464</v>
       </c>
       <c r="R24" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
@@ -3113,13 +3125,13 @@
         <v>71</v>
       </c>
       <c r="E25">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="7">
-        <v>2090304768</v>
+        <v>2296719872</v>
       </c>
       <c r="H25" s="6">
         <v>4.84</v>
@@ -3129,16 +3141,16 @@
       </c>
       <c r="J25" s="12">
         <f t="shared" si="0"/>
-        <v>0.27857142857142869</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K25" s="11">
-        <v>7.2625698324022353E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="L25" s="13">
-        <v>424258000</v>
+        <v>392836000</v>
       </c>
       <c r="M25" s="13">
-        <v>2485347000</v>
+        <v>3201831000</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>68</v>
@@ -3147,13 +3159,13 @@
         <v>1</v>
       </c>
       <c r="P25" s="12">
-        <v>0.16879885889810164</v>
+        <v>0.1164082386542019</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.17070372869462494</v>
+        <v>0.12269104771613493</v>
       </c>
       <c r="R25" s="14">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
@@ -3167,13 +3179,13 @@
         <v>96</v>
       </c>
       <c r="E26">
-        <v>12.1</v>
+        <v>12.74</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>19798263808</v>
+        <v>20441966592</v>
       </c>
       <c r="H26" s="6">
         <v>18.399999999999999</v>
@@ -3183,7 +3195,7 @@
       </c>
       <c r="J26" s="12">
         <f t="shared" si="0"/>
-        <v>0.25649013499480766</v>
+        <v>0.32294911734164056</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3201,13 +3213,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P26" s="12">
-        <v>0.22775729862435659</v>
+        <v>0.22111842309123225</v>
       </c>
       <c r="Q26" s="12">
         <v>0.12218132992627646</v>
       </c>
       <c r="R26" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
@@ -3221,13 +3233,13 @@
         <v>75</v>
       </c>
       <c r="E27">
-        <v>5.36</v>
+        <v>5.72</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>14344111104</v>
+        <v>15307520000</v>
       </c>
       <c r="H27" s="6">
         <v>7.13</v>
@@ -3237,10 +3249,10 @@
       </c>
       <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>0.29156626506024086</v>
+        <v>0.3783132530120481</v>
       </c>
       <c r="K27" s="11">
-        <v>4.2910447761194029E-2</v>
+        <v>4.0209790209790215E-2</v>
       </c>
       <c r="L27" s="13">
         <v>2030839000</v>
@@ -3255,7 +3267,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.15072049521902778</v>
+        <v>0.14126635461935361</v>
       </c>
       <c r="Q27" s="12">
         <v>0.17526328902672489</v>
@@ -3275,13 +3287,13 @@
         <v>61</v>
       </c>
       <c r="E28">
-        <v>11.44</v>
+        <v>11.58</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>17492789248</v>
+        <v>18211749888</v>
       </c>
       <c r="H28" s="6">
         <v>11.9</v>
@@ -3291,10 +3303,10 @@
       </c>
       <c r="J28" s="12">
         <f t="shared" si="0"/>
-        <v>0.31949250288350628</v>
+        <v>0.33564013840830453</v>
       </c>
       <c r="K28" s="11">
-        <v>5.2447552447552448E-2</v>
+        <v>5.181347150259067E-2</v>
       </c>
       <c r="L28" s="13">
         <v>1721368005.75</v>
@@ -3309,13 +3321,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>0.23173426462119645</v>
+        <v>0.21248452750721705</v>
       </c>
       <c r="Q28" s="12">
         <v>0.11773304155211949</v>
       </c>
       <c r="R28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
@@ -3329,13 +3341,13 @@
         <v>54</v>
       </c>
       <c r="E29">
-        <v>4.46</v>
+        <v>4.59</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>17296236544</v>
+        <v>17800388608</v>
       </c>
       <c r="H29" s="6">
         <v>6.97</v>
@@ -3345,10 +3357,10 @@
       </c>
       <c r="J29" s="12">
         <f t="shared" si="0"/>
-        <v>0.33933933933933935</v>
+        <v>0.37837837837837829</v>
       </c>
       <c r="K29" s="11">
-        <v>6.0538116591928252E-2</v>
+        <v>5.8823529411764712E-2</v>
       </c>
       <c r="L29" s="13">
         <v>2823432000</v>
@@ -3363,13 +3375,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>0.15412077727863235</v>
+        <v>0.14999299867774846</v>
       </c>
       <c r="Q29" s="12">
         <v>0.16681818624944278</v>
       </c>
       <c r="R29" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
@@ -3383,13 +3395,13 @@
         <v>241</v>
       </c>
       <c r="E30">
-        <v>9.49</v>
+        <v>9.36</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>9371697152</v>
+        <v>9243318272</v>
       </c>
       <c r="H30" s="6">
         <v>9.65</v>
@@ -3399,10 +3411,10 @@
       </c>
       <c r="J30" s="12">
         <f t="shared" si="0"/>
-        <v>0.89800000000000013</v>
+        <v>0.87199999999999989</v>
       </c>
       <c r="K30" s="11">
-        <v>3.7302423603793461E-2</v>
+        <v>3.7820512820512818E-2</v>
       </c>
       <c r="L30" s="13">
         <v>1333116000</v>
@@ -3417,13 +3429,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.15494069265362856</v>
+        <v>0.15713521756279702</v>
       </c>
       <c r="Q30" s="12">
         <v>0.16622802330680692</v>
       </c>
       <c r="R30" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
@@ -3437,13 +3449,13 @@
         <v>227</v>
       </c>
       <c r="E31">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="7">
-        <v>1643724928</v>
+        <v>1667547008</v>
       </c>
       <c r="H31" s="6">
         <v>0.84</v>
@@ -3453,10 +3465,10 @@
       </c>
       <c r="J31" s="12">
         <f t="shared" si="0"/>
-        <v>0.25454545454545441</v>
+        <v>0.27272727272727249</v>
       </c>
       <c r="K31" s="11">
-        <v>1.4492753623188408E-2</v>
+        <v>1.4285714285714287E-2</v>
       </c>
       <c r="L31" s="13">
         <v>54195000</v>
@@ -3471,7 +3483,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P31" s="12">
-        <v>1.2095413323209785</v>
+        <v>1.131346144820242</v>
       </c>
       <c r="Q31" s="12">
         <v>9.2370860611101543E-2</v>
@@ -3491,13 +3503,13 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>6.09</v>
+        <v>6.3</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>6550951936</v>
+        <v>6676992000</v>
       </c>
       <c r="H32" s="6">
         <v>6.88</v>
@@ -3507,10 +3519,10 @@
       </c>
       <c r="J32" s="12">
         <f t="shared" si="0"/>
-        <v>0.53400503778337516</v>
+        <v>0.58690176322418131</v>
       </c>
       <c r="K32" s="11">
-        <v>8.0459770114942528E-2</v>
+        <v>7.7777777777777779E-2</v>
       </c>
       <c r="L32" s="13">
         <v>866801000</v>
@@ -3525,13 +3537,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.24381360702346375</v>
+        <v>0.23546575196966005</v>
       </c>
       <c r="Q32" s="12">
         <v>0.11511220438953086</v>
       </c>
       <c r="R32" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
@@ -3545,13 +3557,13 @@
         <v>50</v>
       </c>
       <c r="E33">
-        <v>7.23</v>
+        <v>7.9</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>9267341312</v>
+        <v>9838818304</v>
       </c>
       <c r="H33" s="6">
         <v>8.6</v>
@@ -3561,10 +3573,10 @@
       </c>
       <c r="J33" s="12">
         <f t="shared" si="0"/>
-        <v>1.0895953757225434</v>
+        <v>1.2832369942196533</v>
       </c>
       <c r="K33" s="11">
-        <v>1.9502074688796677E-2</v>
+        <v>1.7848101265822782E-2</v>
       </c>
       <c r="L33" s="13">
         <v>921702000</v>
@@ -3579,13 +3591,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P33" s="12">
-        <v>0.14459028925795669</v>
+        <v>0.13339672580257989</v>
       </c>
       <c r="Q33" s="12">
         <v>0.17514380877385538</v>
       </c>
       <c r="R33" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
@@ -3599,13 +3611,13 @@
         <v>71</v>
       </c>
       <c r="E34">
-        <v>4.3099999999999996</v>
+        <v>4.49</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>49839546368</v>
+        <v>51921010688</v>
       </c>
       <c r="H34" s="6">
         <v>5.14</v>
@@ -3615,10 +3627,10 @@
       </c>
       <c r="J34" s="12">
         <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>0.24566473988439297</v>
+        <v>0.29768786127167646</v>
       </c>
       <c r="K34" s="11">
-        <v>6.0556844547563812E-2</v>
+        <v>5.8129175946547887E-2</v>
       </c>
       <c r="L34" s="13">
         <v>4734613000</v>
@@ -3633,13 +3645,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>0.10848939091083475</v>
+        <v>0.10385313688843621</v>
       </c>
       <c r="Q34" s="12">
         <v>0.29201860560357656</v>
       </c>
       <c r="R34" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
@@ -3653,26 +3665,26 @@
         <v>50</v>
       </c>
       <c r="E35">
-        <v>5.81</v>
+        <v>7.6</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>12992787456</v>
+        <v>16995728384</v>
       </c>
       <c r="H35" s="6">
-        <v>6.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="I35" s="6">
         <v>2.16</v>
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
-        <v>1.6898148148148144</v>
+        <v>2.5185185185185182</v>
       </c>
       <c r="K35" s="11">
-        <v>3.9759036144578319E-2</v>
+        <v>3.0394736842105266E-2</v>
       </c>
       <c r="L35" s="13">
         <v>2184074765.02</v>
@@ -3687,13 +3699,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>0.52794055264095585</v>
+        <v>0.27703593390796261</v>
       </c>
       <c r="Q35" s="12">
         <v>9.29654274042198E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
@@ -3707,13 +3719,13 @@
         <v>181</v>
       </c>
       <c r="E36">
-        <v>10.14</v>
+        <v>10.44</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>125783662592</v>
+        <v>129505067008</v>
       </c>
       <c r="H36" s="6">
         <v>13.6</v>
@@ -3723,10 +3735,10 @@
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
-        <v>0.54337899543378998</v>
+        <v>0.58904109589041087</v>
       </c>
       <c r="K36" s="11">
-        <v>4.9309664694280079E-3</v>
+        <v>4.7892720306513415E-3</v>
       </c>
       <c r="L36" s="13">
         <v>2250990000</v>
@@ -3741,13 +3753,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P36" s="12">
-        <v>0.12968989988527038</v>
+        <v>0.12617308481660089</v>
       </c>
       <c r="Q36" s="12">
         <v>0.19681397761416858</v>
       </c>
       <c r="R36" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
@@ -3761,26 +3773,26 @@
         <v>98</v>
       </c>
       <c r="E37">
-        <v>4.6500000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>5119417856</v>
+        <v>5064370176</v>
       </c>
       <c r="H37" s="6">
-        <v>4.6500000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="I37" s="6">
         <v>3.69</v>
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
-        <v>0.26016260162601634</v>
+        <v>0.24661246612466114</v>
       </c>
       <c r="K37" s="11">
-        <v>6.8817204301075269E-2</v>
+        <v>6.9565217391304349E-2</v>
       </c>
       <c r="L37" s="13">
         <v>765224000</v>
@@ -3795,13 +3807,13 @@
         <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.16983545087350985</v>
+        <v>0.17193606249074636</v>
       </c>
       <c r="Q37" s="12">
         <v>0.14577225152582682</v>
       </c>
       <c r="R37" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
@@ -3815,13 +3827,13 @@
         <v>77</v>
       </c>
       <c r="E38">
-        <v>5.76</v>
+        <v>5.96</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>8443987968</v>
+        <v>8737181696</v>
       </c>
       <c r="H38" s="6">
         <v>6.07</v>
@@ -3831,10 +3843,10 @@
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
-        <v>0.66956521739130426</v>
+        <v>0.72753623188405792</v>
       </c>
       <c r="K38" s="11">
-        <v>8.3333333333333329E-2</v>
+        <v>8.0536912751677847E-2</v>
       </c>
       <c r="L38" s="13">
         <v>784607000</v>
@@ -3849,13 +3861,13 @@
         <v>1</v>
       </c>
       <c r="P38" s="12">
-        <v>0.28808923901898364</v>
+        <v>0.26008959487490779</v>
       </c>
       <c r="Q38" s="12">
         <v>9.9663185641922489E-2</v>
       </c>
       <c r="R38" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
@@ -3869,13 +3881,13 @@
         <v>71</v>
       </c>
       <c r="E39">
-        <v>5.39</v>
+        <v>5.73</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>15806228480</v>
+        <v>16346658816</v>
       </c>
       <c r="H39" s="6">
         <v>6.21</v>
@@ -3885,10 +3897,10 @@
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
-        <v>0.67391304347826075</v>
+        <v>0.77950310559006208</v>
       </c>
       <c r="K39" s="11">
-        <v>7.7922077922077931E-3</v>
+        <v>7.3298429319371729E-3</v>
       </c>
       <c r="L39" s="13">
         <v>259348000</v>
@@ -3903,13 +3915,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P39" s="12">
-        <v>0.14385894495567547</v>
+        <v>0.13846296094861918</v>
       </c>
       <c r="Q39" s="12">
         <v>0.15459217096529801</v>
       </c>
       <c r="R39" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
@@ -3923,13 +3935,13 @@
         <v>98</v>
       </c>
       <c r="E40">
-        <v>4.47</v>
+        <v>4.59</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>31096895488</v>
+        <v>31790434304</v>
       </c>
       <c r="H40" s="6">
         <v>6.15</v>
@@ -3939,10 +3951,10 @@
       </c>
       <c r="J40" s="12">
         <f t="shared" si="1"/>
-        <v>0.20485175202156336</v>
+        <v>0.23719676549865221</v>
       </c>
       <c r="K40" s="11">
-        <v>4.8993288590604027E-2</v>
+        <v>4.7712418300653599E-2</v>
       </c>
       <c r="L40" s="13">
         <v>4216348000</v>
@@ -3957,13 +3969,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.36669762250478299</v>
+        <v>0.34710130302767522</v>
       </c>
       <c r="Q40" s="12">
         <v>9.1377422623841298E-2</v>
       </c>
       <c r="R40" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
@@ -3977,13 +3989,13 @@
         <v>306</v>
       </c>
       <c r="E41">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>40025223168</v>
+        <v>44280774656</v>
       </c>
       <c r="H41" s="6">
         <v>4.1100000000000003</v>
@@ -3993,10 +4005,10 @@
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
-        <v>0.48085106382978715</v>
+        <v>0.63829787234042556</v>
       </c>
       <c r="K41" s="11">
-        <v>5.459770114942529E-2</v>
+        <v>4.9350649350649353E-2</v>
       </c>
       <c r="L41" s="13">
         <v>9414000000</v>
@@ -4011,13 +4023,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>0.1851014057667357</v>
+        <v>0.17165736953056121</v>
       </c>
       <c r="Q41" s="12">
         <v>0.11538320116682396</v>
       </c>
       <c r="R41" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
@@ -4031,13 +4043,13 @@
         <v>151</v>
       </c>
       <c r="E42">
-        <v>28.6</v>
+        <v>29.95</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>208246046720</v>
+        <v>213571649536</v>
       </c>
       <c r="H42" s="6">
         <v>32.299999999999997</v>
@@ -4047,10 +4059,10 @@
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
-        <v>0.54094827586206917</v>
+        <v>0.6136853448275863</v>
       </c>
       <c r="K42" s="11">
-        <v>4.6118881118881114E-2</v>
+        <v>4.4040066777963273E-2</v>
       </c>
       <c r="L42" s="13">
         <v>61181051000</v>
@@ -4065,13 +4077,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.1854429602744915</v>
+        <v>0.18268279124126716</v>
       </c>
       <c r="Q42" s="12">
         <v>0.11493949471384535</v>
       </c>
       <c r="R42" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
@@ -4085,13 +4097,13 @@
         <v>87</v>
       </c>
       <c r="E43">
-        <v>11.26</v>
+        <v>11.88</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>63443795968</v>
+        <v>66937151488</v>
       </c>
       <c r="H43" s="6">
         <v>14.24</v>
@@ -4101,10 +4113,10 @@
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
-        <v>0.27809307604994316</v>
+        <v>0.3484676503972759</v>
       </c>
       <c r="K43" s="11">
-        <v>2.9396092362344584E-2</v>
+        <v>2.7861952861952862E-2</v>
       </c>
       <c r="L43" s="13">
         <v>6482967000</v>
@@ -4119,13 +4131,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>9.9154088768325502E-2</v>
+        <v>9.4431580673540572E-2</v>
       </c>
       <c r="Q43" s="12">
         <v>0.23588267049650188</v>
       </c>
       <c r="R43" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
@@ -4139,13 +4151,13 @@
         <v>87</v>
       </c>
       <c r="E44">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>65625235456</v>
+        <v>67277668352</v>
       </c>
       <c r="H44" s="6">
         <v>5.77</v>
@@ -4155,16 +4167,16 @@
       </c>
       <c r="J44" s="12">
         <f t="shared" si="1"/>
-        <v>0.28110599078341014</v>
+        <v>0.31336405529953915</v>
       </c>
       <c r="K44" s="11">
-        <v>2.6618705035971222E-2</v>
+        <v>2.5964912280701753E-2</v>
       </c>
       <c r="L44" s="13">
-        <v>5687261000</v>
+        <v>5915895000</v>
       </c>
       <c r="M44" s="13">
-        <v>21716551000</v>
+        <v>21902003000</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>51</v>
@@ -4173,13 +4185,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>9.7150769939110218E-2</v>
+        <v>0.10024247115622946</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.26188601495697911</v>
+        <v>0.27010748742934609</v>
       </c>
       <c r="R44" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
@@ -4193,13 +4205,13 @@
         <v>85</v>
       </c>
       <c r="E45">
-        <v>92.6</v>
+        <v>90.8</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>258169716736</v>
+        <v>253151313920</v>
       </c>
       <c r="H45" s="6">
         <v>107.5</v>
@@ -4209,10 +4221,10 @@
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
-        <v>0.41266209000762766</v>
+        <v>0.38520213577421814</v>
       </c>
       <c r="K45" s="11">
-        <v>2.3952483801295898E-2</v>
+        <v>2.4427312775330397E-2</v>
       </c>
       <c r="L45" s="13">
         <v>22510000000</v>
@@ -4227,13 +4239,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>8.7120806589933791E-2</v>
+        <v>8.8733967386986717E-2</v>
       </c>
       <c r="Q45" s="12">
         <v>0.27269973953601068</v>
       </c>
       <c r="R45" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
@@ -4247,13 +4259,13 @@
         <v>56</v>
       </c>
       <c r="E46">
-        <v>10.58</v>
+        <v>9.41</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>26670485504</v>
+        <v>23721103360</v>
       </c>
       <c r="H46" s="6">
         <v>11.22</v>
@@ -4263,10 +4275,10 @@
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
-        <v>1.4321839080459773</v>
+        <v>1.1632183908045981</v>
       </c>
       <c r="K46" s="11">
-        <v>3.0056710775047259E-2</v>
+        <v>3.3793836344314557E-2</v>
       </c>
       <c r="L46" s="13">
         <v>3301437000</v>
@@ -4281,13 +4293,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>0.14438024431328672</v>
+        <v>0.16576072371997866</v>
       </c>
       <c r="Q46" s="12">
         <v>0.15134190781174311</v>
       </c>
       <c r="R46" s="14">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
@@ -4301,13 +4313,13 @@
         <v>54</v>
       </c>
       <c r="E47">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>250182746112</v>
+        <v>250693746688</v>
       </c>
       <c r="H47" s="6">
         <v>36.450000000000003</v>
@@ -4317,10 +4329,10 @@
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
-        <v>0.29417879417879411</v>
+        <v>0.33575883575883592</v>
       </c>
       <c r="K47" s="11">
-        <v>3.8755020080321285E-2</v>
+        <v>3.7548638132295718E-2</v>
       </c>
       <c r="L47" s="13">
         <v>25459748125.549999</v>
@@ -4335,13 +4347,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>0.11414554241220609</v>
+        <v>0.11390129456087218</v>
       </c>
       <c r="Q47" s="12">
         <v>0.18884873513587705</v>
       </c>
       <c r="R47" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
@@ -4355,26 +4367,26 @@
         <v>337</v>
       </c>
       <c r="E48">
-        <v>5.69</v>
+        <v>6.18</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>7295945728</v>
+        <v>7924242944</v>
       </c>
       <c r="H48" s="6">
-        <v>5.92</v>
+        <v>6.27</v>
       </c>
       <c r="I48" s="6">
         <v>3.36</v>
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
-        <v>0.69345238095238115</v>
+        <v>0.83928571428571419</v>
       </c>
       <c r="K48" s="11">
-        <v>4.5694200351493845E-2</v>
+        <v>4.2071197411003243E-2</v>
       </c>
       <c r="L48" s="13">
         <v>2871477000</v>
@@ -4389,13 +4401,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>0.15104351679776906</v>
+        <v>0.14651131845593979</v>
       </c>
       <c r="Q48" s="12">
         <v>0.1318118502166547</v>
       </c>
       <c r="R48" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
@@ -4409,13 +4421,13 @@
         <v>87</v>
       </c>
       <c r="E49">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>2511525376</v>
+        <v>2581942016</v>
       </c>
       <c r="H49" s="6">
         <v>17</v>
@@ -4425,10 +4437,10 @@
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
-        <v>0.4538043478260867</v>
+        <v>0.49456521739130421</v>
       </c>
       <c r="K49" s="11">
-        <v>3.925233644859813E-2</v>
+        <v>3.8181818181818178E-2</v>
       </c>
       <c r="L49" s="13">
         <v>244811000</v>
@@ -4443,13 +4455,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="12">
-        <v>0.30259840651323888</v>
+        <v>0.27836955941136471</v>
       </c>
       <c r="Q49" s="12">
         <v>8.4294835486117978E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
@@ -4463,13 +4475,13 @@
         <v>109</v>
       </c>
       <c r="E50">
-        <v>49.25</v>
+        <v>48.05</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>127422554112</v>
+        <v>122951303168</v>
       </c>
       <c r="H50" s="6">
         <v>71.7</v>
@@ -4479,10 +4491,10 @@
       </c>
       <c r="J50" s="12">
         <f t="shared" si="1"/>
-        <v>0.13088404133180265</v>
+        <v>0.10332950631458093</v>
       </c>
       <c r="K50" s="11">
-        <v>3.3299492385786803E-3</v>
+        <v>3.4131113423517172E-3</v>
       </c>
       <c r="L50" s="13">
         <v>1279098000</v>
@@ -4497,13 +4509,13 @@
         <v>8.7546153846153842</v>
       </c>
       <c r="P50" s="12">
-        <v>7.8324331600632152E-2</v>
+        <v>8.0852934540369251E-2</v>
       </c>
       <c r="Q50" s="12">
         <v>0.26583067696212276</v>
       </c>
       <c r="R50" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -4517,13 +4529,13 @@
         <v>174</v>
       </c>
       <c r="E51">
-        <v>79.5</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>19463587840</v>
+        <v>19806343168</v>
       </c>
       <c r="H51" s="6">
         <v>95.5</v>
@@ -4533,10 +4545,10 @@
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
-        <v>0.44414168937329701</v>
+        <v>0.46957311534968227</v>
       </c>
       <c r="K51" s="11">
-        <v>1.0314465408805032E-2</v>
+        <v>1.0135970333745364E-2</v>
       </c>
       <c r="L51" s="13">
         <v>526052000</v>
@@ -4551,13 +4563,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P51" s="12">
-        <v>0.2066878179992655</v>
+        <v>0.20313157678503616</v>
       </c>
       <c r="Q51" s="12">
         <v>9.8446219337080781E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
@@ -4571,13 +4583,13 @@
         <v>50</v>
       </c>
       <c r="E52">
-        <v>20.95</v>
+        <v>22.4</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>33596887040</v>
+        <v>35750400000</v>
       </c>
       <c r="H52" s="6">
         <v>27.5</v>
@@ -4587,10 +4599,10 @@
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
-        <v>0.29480840543881337</v>
+        <v>0.38442521631643989</v>
       </c>
       <c r="K52" s="11">
-        <v>3.274463007159905E-2</v>
+        <v>3.0625000000000003E-2</v>
       </c>
       <c r="L52" s="13">
         <v>3811007000</v>
@@ -4605,13 +4617,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.12378449891056212</v>
+        <v>0.11617818175071594</v>
       </c>
       <c r="Q52" s="12">
         <v>0.1667375806872122</v>
       </c>
       <c r="R52" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
@@ -4625,13 +4637,13 @@
         <v>330</v>
       </c>
       <c r="E53">
-        <v>6.48</v>
+        <v>6.75</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>13244472320</v>
+        <v>13690890240</v>
       </c>
       <c r="H53" s="6">
         <v>7.86</v>
@@ -4641,10 +4653,10 @@
       </c>
       <c r="J53" s="12">
         <f t="shared" si="1"/>
-        <v>0.22033898305084754</v>
+        <v>0.27118644067796627</v>
       </c>
       <c r="K53" s="11">
-        <v>4.1666666666666664E-2</v>
+        <v>0.04</v>
       </c>
       <c r="L53" s="13">
         <v>1537565000</v>
@@ -4659,13 +4671,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>0.1854337353602912</v>
+        <v>0.1765374329408417</v>
       </c>
       <c r="Q53" s="12">
         <v>0.10614925092863724</v>
       </c>
       <c r="R53" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
@@ -4679,13 +4691,13 @@
         <v>96</v>
       </c>
       <c r="E54">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G54" s="7">
-        <v>2695529216</v>
+        <v>2799203584</v>
       </c>
       <c r="H54" s="6">
         <v>0.68</v>
@@ -4695,7 +4707,7 @@
       </c>
       <c r="J54" s="12">
         <f t="shared" si="1"/>
-        <v>0.13043478260869557</v>
+        <v>0.17391304347826098</v>
       </c>
       <c r="K54" s="11">
         <v>0</v>
@@ -4713,13 +4725,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P54" s="12">
-        <v>0.28949073626199495</v>
+        <v>0.27911909766491833</v>
       </c>
       <c r="Q54" s="12">
         <v>8.5775443346640556E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
@@ -4733,26 +4745,26 @@
         <v>339</v>
       </c>
       <c r="E55">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>8357280256</v>
+        <v>8448343040</v>
       </c>
       <c r="H55" s="6">
-        <v>4.9800000000000004</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="I55" s="6">
         <v>3.34</v>
       </c>
       <c r="J55" s="12">
         <f t="shared" si="1"/>
-        <v>9.5808383233533023E-2</v>
+        <v>0.11377245508982048</v>
       </c>
       <c r="K55" s="11">
-        <v>4.0983606557377046E-2</v>
+        <v>4.0322580645161289E-2</v>
       </c>
       <c r="L55" s="13">
         <v>826931000</v>
@@ -4767,13 +4779,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>0.13950636526246654</v>
+        <v>0.13752878046521555</v>
       </c>
       <c r="Q55" s="12">
         <v>0.14788755315990715</v>
       </c>
       <c r="R55" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
@@ -4787,13 +4799,13 @@
         <v>181</v>
       </c>
       <c r="E56">
-        <v>8.11</v>
+        <v>7.81</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>3145739008</v>
+        <v>3029373952</v>
       </c>
       <c r="H56" s="6">
         <v>14.18</v>
@@ -4803,10 +4815,10 @@
       </c>
       <c r="J56" s="12">
         <f t="shared" si="1"/>
-        <v>1.2280219780219777</v>
+        <v>1.1456043956043955</v>
       </c>
       <c r="K56" s="11">
-        <v>4.3156596794081382E-2</v>
+        <v>4.4814340588988477E-2</v>
       </c>
       <c r="L56" s="13">
         <v>348303000</v>
@@ -4821,13 +4833,13 @@
         <v>1</v>
       </c>
       <c r="P56" s="12">
-        <v>0.19987948707851019</v>
+        <v>0.21418214873984942</v>
       </c>
       <c r="Q56" s="12">
         <v>9.4606035666412708E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
@@ -4841,13 +4853,13 @@
         <v>310</v>
       </c>
       <c r="E57">
-        <v>6.06</v>
+        <v>6.23</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>26235072512</v>
+        <v>27375618048</v>
       </c>
       <c r="H57" s="6">
         <v>6.87</v>
@@ -4857,10 +4869,10 @@
       </c>
       <c r="J57" s="12">
         <f t="shared" si="1"/>
-        <v>0.27044025157232698</v>
+        <v>0.30607966457023084</v>
       </c>
       <c r="K57" s="11">
-        <v>5.9075907590759077E-2</v>
+        <v>5.7463884430176561E-2</v>
       </c>
       <c r="L57" s="13">
         <v>2919921000</v>
@@ -4875,13 +4887,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>0.21331297654954046</v>
+        <v>0.19788043323293975</v>
       </c>
       <c r="Q57" s="12">
         <v>9.2221214358852555E-2</v>
       </c>
       <c r="R57" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
@@ -4895,26 +4907,26 @@
         <v>324</v>
       </c>
       <c r="E58">
-        <v>6.9</v>
+        <v>8.64</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>17295886336</v>
+        <v>21657458688</v>
       </c>
       <c r="H58" s="6">
-        <v>7.26</v>
+        <v>8.65</v>
       </c>
       <c r="I58" s="6">
         <v>3.99</v>
       </c>
       <c r="J58" s="12">
         <f t="shared" si="1"/>
-        <v>0.72932330827067671</v>
+        <v>1.1654135338345863</v>
       </c>
       <c r="K58" s="11">
-        <v>4.652173913043478E-2</v>
+        <v>3.7152777777777778E-2</v>
       </c>
       <c r="L58" s="13">
         <v>3040816000</v>
@@ -4929,7 +4941,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.17225133693150912</v>
+        <v>0.13989897925799713</v>
       </c>
       <c r="Q58" s="12">
         <v>0.102358453189061</v>
@@ -4949,13 +4961,13 @@
         <v>151</v>
       </c>
       <c r="E59">
-        <v>4.4000000000000004</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>6661116416</v>
+        <v>6660302336</v>
       </c>
       <c r="H59" s="6">
         <v>7.92</v>
@@ -4965,10 +4977,10 @@
       </c>
       <c r="J59" s="12">
         <f t="shared" si="1"/>
-        <v>0.86440677966101709</v>
+        <v>0.96610169491525411</v>
       </c>
       <c r="K59" s="11">
-        <v>5.7727272727272724E-2</v>
+        <v>5.4741379310344833E-2</v>
       </c>
       <c r="L59" s="13">
         <v>811880000</v>
@@ -4983,13 +4995,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P59" s="12">
-        <v>0.13453919557835634</v>
+        <v>0.13455618597767807</v>
       </c>
       <c r="Q59" s="12">
         <v>0.14675695119790894</v>
       </c>
       <c r="R59" s="14">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
@@ -5003,13 +5015,13 @@
         <v>308</v>
       </c>
       <c r="E60">
-        <v>5.54</v>
+        <v>4.91</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G60" s="7">
-        <v>5119746560</v>
+        <v>4537537024</v>
       </c>
       <c r="H60" s="6">
         <v>5.59</v>
@@ -5019,10 +5031,10 @@
       </c>
       <c r="J60" s="12">
         <f t="shared" si="1"/>
-        <v>0.62941176470588234</v>
+        <v>0.44411764705882351</v>
       </c>
       <c r="K60" s="11">
-        <v>2.6173285198555954E-2</v>
+        <v>2.9531568228105903E-2</v>
       </c>
       <c r="L60" s="13">
         <v>754477000</v>
@@ -5037,13 +5049,13 @@
         <v>1</v>
       </c>
       <c r="P60" s="12">
-        <v>0.2901681094134112</v>
+        <v>0.37388697269016175</v>
       </c>
       <c r="Q60" s="12">
         <v>6.460670188445812E-2</v>
       </c>
       <c r="R60" s="14">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
@@ -5057,26 +5069,26 @@
         <v>101</v>
       </c>
       <c r="E61">
-        <v>426.2</v>
+        <v>435.8</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>542454611968</v>
+        <v>550781452288</v>
       </c>
       <c r="H61" s="6">
-        <v>432.2</v>
+        <v>452</v>
       </c>
       <c r="I61" s="6">
         <v>218.4</v>
       </c>
       <c r="J61" s="12">
         <f t="shared" si="1"/>
-        <v>0.95146520146520142</v>
+        <v>0.99542124542124544</v>
       </c>
       <c r="K61" s="11">
-        <v>2.1726888784608166E-2</v>
+        <v>2.1248279027076638E-2</v>
       </c>
       <c r="L61" s="13">
         <v>20744000000</v>
@@ -5091,13 +5103,13 @@
         <v>1</v>
       </c>
       <c r="P61" s="12">
-        <v>5.0671300446734742E-2</v>
+        <v>4.9661194462276889E-2</v>
       </c>
       <c r="Q61" s="12">
         <v>0.38520389214885242</v>
       </c>
       <c r="R61" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
@@ -5111,26 +5123,26 @@
         <v>177</v>
       </c>
       <c r="E62">
-        <v>20.45</v>
+        <v>22.45</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>550624428032</v>
+        <v>582864863232</v>
       </c>
       <c r="H62" s="6">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="I62" s="6">
         <v>13.52</v>
       </c>
       <c r="J62" s="12">
         <f t="shared" si="1"/>
-        <v>0.51257396449704151</v>
+        <v>0.66050295857988162</v>
       </c>
       <c r="K62" s="11">
-        <v>1.8581907090464547E-2</v>
+        <v>1.6926503340757237E-2</v>
       </c>
       <c r="L62" s="13">
         <v>52374992116</v>
@@ -5145,13 +5157,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>8.2909089818828094E-2</v>
+        <v>7.9129095703627056E-2</v>
       </c>
       <c r="Q62" s="12">
         <v>0.19428864891763736</v>
       </c>
       <c r="R62" s="14">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
@@ -5165,26 +5177,26 @@
         <v>83</v>
       </c>
       <c r="E63">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>10229439488</v>
+        <v>11470668800</v>
       </c>
       <c r="H63" s="6">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="I63" s="6">
         <v>1.34</v>
       </c>
       <c r="J63" s="12">
         <f t="shared" si="1"/>
-        <v>0.78358208955223874</v>
+        <v>1</v>
       </c>
       <c r="K63" s="11">
-        <v>5.1046025104602509E-2</v>
+        <v>4.5522388059701491E-2</v>
       </c>
       <c r="L63" s="13">
         <v>1230913000</v>
@@ -5199,13 +5211,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>0.14719410929571736</v>
+        <v>0.12923912780769176</v>
       </c>
       <c r="Q63" s="12">
         <v>0.11502419323187564</v>
       </c>
       <c r="R63" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
@@ -5219,13 +5231,13 @@
         <v>85</v>
       </c>
       <c r="E64">
-        <v>247.8</v>
+        <v>245.2</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>329118056448</v>
+        <v>325664833536</v>
       </c>
       <c r="H64" s="6">
         <v>283.39999999999998</v>
@@ -5235,10 +5247,10 @@
       </c>
       <c r="J64" s="12">
         <f t="shared" si="1"/>
-        <v>5.7890410958904113</v>
+        <v>5.7178082191780817</v>
       </c>
       <c r="K64" s="11">
-        <v>3.2889426957223565E-3</v>
+        <v>3.323817292006525E-3</v>
       </c>
       <c r="L64" s="13">
         <v>4408440000</v>
@@ -5253,13 +5265,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P64" s="12">
-        <v>1.4553627636866826E-2</v>
+        <v>1.4710597799745991E-2</v>
       </c>
       <c r="Q64" s="12">
         <v>0.41263985929711272</v>
       </c>
       <c r="R64" s="14">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
@@ -5273,26 +5285,26 @@
         <v>185</v>
       </c>
       <c r="E65">
-        <v>365</v>
+        <v>375.8</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>136447959040</v>
+        <v>141275611136</v>
       </c>
       <c r="H65" s="6">
         <v>421.4</v>
       </c>
       <c r="I65" s="6">
-        <v>225.2</v>
+        <v>225.6</v>
       </c>
       <c r="J65" s="12">
         <f t="shared" si="1"/>
-        <v>0.62078152753108351</v>
+        <v>0.66578014184397172</v>
       </c>
       <c r="K65" s="11">
-        <v>1.9726027397260273E-3</v>
+        <v>1.9159127195316657E-3</v>
       </c>
       <c r="L65" s="13">
         <v>1200000000</v>
@@ -5307,13 +5319,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P65" s="12">
-        <v>6.1778495784552405E-2</v>
+        <v>5.9844913559188487E-2</v>
       </c>
       <c r="Q65" s="12">
         <v>0.20495303159692571</v>
       </c>
       <c r="R65" s="14">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
@@ -5327,26 +5339,26 @@
         <v>321</v>
       </c>
       <c r="E66">
-        <v>8.52</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>15399304192</v>
+        <v>16212647936</v>
       </c>
       <c r="H66" s="6">
-        <v>8.8000000000000007</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="I66" s="6">
         <v>5.49</v>
       </c>
       <c r="J66" s="12">
         <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
-        <v>0.55191256830601088</v>
+        <v>0.63387978142076506</v>
       </c>
       <c r="K66" s="11">
-        <v>2.9342723004694836E-2</v>
+        <v>2.7870680044593085E-2</v>
       </c>
       <c r="L66" s="13">
         <v>2897428000</v>
@@ -5361,13 +5373,13 @@
         <v>1</v>
       </c>
       <c r="P66" s="12">
-        <v>0.1426340902135545</v>
+        <v>0.13714300144961752</v>
       </c>
       <c r="Q66" s="12">
         <v>0.11156568921912897</v>
       </c>
       <c r="R66" s="14">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
@@ -5381,13 +5393,13 @@
         <v>174</v>
       </c>
       <c r="E67">
-        <v>12.24</v>
+        <v>12.6</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>3217688064</v>
+        <v>3317731328</v>
       </c>
       <c r="H67" s="6">
         <v>15.58</v>
@@ -5397,7 +5409,7 @@
       </c>
       <c r="J67" s="12">
         <f t="shared" si="2"/>
-        <v>0.62982689747004006</v>
+        <v>0.67776298268974711</v>
       </c>
       <c r="K67" s="11">
         <v>0</v>
@@ -5415,13 +5427,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P67" s="12">
-        <v>0.49684646154958739</v>
+        <v>0.55004017419353191</v>
       </c>
       <c r="Q67" s="12">
         <v>-0.11631254679805218</v>
       </c>
       <c r="R67" s="14">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
@@ -5435,13 +5447,13 @@
         <v>183</v>
       </c>
       <c r="E68">
-        <v>33.15</v>
+        <v>32.65</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>22929192960</v>
+        <v>22583353344</v>
       </c>
       <c r="H68" s="6">
         <v>39.200000000000003</v>
@@ -5451,10 +5463,10 @@
       </c>
       <c r="J68" s="12">
         <f t="shared" si="2"/>
-        <v>1.4591988130563798</v>
+        <v>1.422106824925816</v>
       </c>
       <c r="K68" s="11">
-        <v>1.3876319758672701E-2</v>
+        <v>1.4088820826952527E-2</v>
       </c>
       <c r="L68" s="13">
         <v>1323087000</v>
@@ -5469,13 +5481,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="12">
-        <v>5.2106356537171293E-2</v>
+        <v>5.2825844434398944E-2</v>
       </c>
       <c r="Q68" s="12">
         <v>0.222258562943417</v>
       </c>
       <c r="R68" s="14">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
@@ -5489,13 +5501,13 @@
         <v>50</v>
       </c>
       <c r="E69">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>6077073920</v>
+        <v>5869471744</v>
       </c>
       <c r="H69" s="6">
         <v>4.18</v>
@@ -5505,10 +5517,10 @@
       </c>
       <c r="J69" s="12">
         <f t="shared" si="2"/>
-        <v>0.85057471264367823</v>
+        <v>0.78735632183908044</v>
       </c>
       <c r="K69" s="11">
-        <v>4.9689440993788817E-2</v>
+        <v>5.1446945337620585E-2</v>
       </c>
       <c r="L69" s="13">
         <v>896597000</v>
@@ -5523,13 +5535,13 @@
         <v>1</v>
       </c>
       <c r="P69" s="12">
-        <v>0.11687460787694841</v>
+        <v>0.12012540334483277</v>
       </c>
       <c r="Q69" s="12">
         <v>0.12982345485897689</v>
       </c>
       <c r="R69" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
@@ -5543,13 +5555,13 @@
         <v>167</v>
       </c>
       <c r="E70">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>26393081856</v>
+        <v>27075354624</v>
       </c>
       <c r="H70" s="6">
         <v>28.75</v>
@@ -5559,10 +5571,10 @@
       </c>
       <c r="J70" s="12">
         <f t="shared" si="2"/>
-        <v>0.18596311475409832</v>
+        <v>0.21926229508196737</v>
       </c>
       <c r="K70" s="11">
-        <v>6.0475161987041039E-2</v>
+        <v>5.8823529411764698E-2</v>
       </c>
       <c r="L70" s="13">
         <v>3446618000</v>
@@ -5577,13 +5589,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P70" s="12">
-        <v>0.14632134692749155</v>
+        <v>0.14245911225562893</v>
       </c>
       <c r="Q70" s="12">
         <v>0.10133893359397213</v>
       </c>
       <c r="R70" s="14">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
@@ -5597,13 +5609,13 @@
         <v>104</v>
       </c>
       <c r="E71">
-        <v>6.36</v>
+        <v>6.47</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>4955724800</v>
+        <v>5041436672</v>
       </c>
       <c r="H71" s="6">
         <v>8.09</v>
@@ -5613,10 +5625,10 @@
       </c>
       <c r="J71" s="12">
         <f t="shared" si="2"/>
-        <v>0.58208955223880632</v>
+        <v>0.60945273631840813</v>
       </c>
       <c r="K71" s="11">
-        <v>2.6729559748427674E-2</v>
+        <v>2.6275115919629059E-2</v>
       </c>
       <c r="L71" s="13">
         <v>437453000</v>
@@ -5631,13 +5643,13 @@
         <v>1</v>
       </c>
       <c r="P71" s="12">
-        <v>0.16406892340244772</v>
+        <v>0.15895892428983235</v>
       </c>
       <c r="Q71" s="12">
         <v>8.9074849645861431E-2</v>
       </c>
       <c r="R71" s="14">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
@@ -5651,26 +5663,26 @@
         <v>155</v>
       </c>
       <c r="E72">
-        <v>59.75</v>
+        <v>57.95</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>165795495936</v>
+        <v>159968657408</v>
       </c>
       <c r="H72" s="6">
-        <v>60</v>
+        <v>61.15</v>
       </c>
       <c r="I72" s="6">
         <v>38.4</v>
       </c>
       <c r="J72" s="12">
         <f t="shared" si="2"/>
-        <v>0.55598958333333348</v>
+        <v>0.50911458333333348</v>
       </c>
       <c r="K72" s="11">
-        <v>3.0125523012552301E-2</v>
+        <v>3.1061259706643658E-2</v>
       </c>
       <c r="L72" s="13">
         <v>8955723006</v>
@@ -5685,13 +5697,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P72" s="12">
-        <v>5.9154556950578426E-2</v>
+        <v>6.1365199557002544E-2</v>
       </c>
       <c r="Q72" s="12">
         <v>0.18855793075067021</v>
       </c>
       <c r="R72" s="14">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
@@ -5705,26 +5717,26 @@
         <v>174</v>
       </c>
       <c r="E73">
-        <v>515</v>
+        <v>550.5</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>4671564939264</v>
+        <v>4993585250304</v>
       </c>
       <c r="H73" s="6">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="I73" s="6">
         <v>349</v>
       </c>
       <c r="J73" s="12">
         <f t="shared" si="2"/>
-        <v>0.47564469914040108</v>
+        <v>0.5773638968481376</v>
       </c>
       <c r="K73" s="11">
-        <v>8.211650485436893E-3</v>
+        <v>7.682107175295186E-3</v>
       </c>
       <c r="L73" s="13">
         <v>253932000000</v>
@@ -5739,13 +5751,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>5.5224484997181182E-2</v>
+        <v>5.1827206457859501E-2</v>
       </c>
       <c r="Q73" s="12">
         <v>0.19352168899747973</v>
       </c>
       <c r="R73" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
@@ -5759,13 +5771,13 @@
         <v>69</v>
       </c>
       <c r="E74">
-        <v>6.38</v>
+        <v>6.61</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>10378409984</v>
+        <v>10752552960</v>
       </c>
       <c r="H74" s="6">
         <v>7.05</v>
@@ -5775,10 +5787,10 @@
       </c>
       <c r="J74" s="12">
         <f t="shared" si="2"/>
-        <v>0.49414519906323195</v>
+        <v>0.54800936768149899</v>
       </c>
       <c r="K74" s="11">
-        <v>4.3887147335423204E-2</v>
+        <v>4.2360060514372168E-2</v>
       </c>
       <c r="L74" s="13">
         <v>4094312000</v>
@@ -5793,13 +5805,13 @@
         <v>1</v>
       </c>
       <c r="P74" s="12">
-        <v>0.13295465906847695</v>
+        <v>0.13135870974556493</v>
       </c>
       <c r="Q74" s="12">
         <v>0.10878407220713927</v>
       </c>
       <c r="R74" s="14">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
@@ -5813,13 +5825,13 @@
         <v>109</v>
       </c>
       <c r="E75">
-        <v>13.82</v>
+        <v>13.72</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>136724807680</v>
+        <v>135346970624</v>
       </c>
       <c r="H75" s="6">
         <v>14.32</v>
@@ -5829,10 +5841,10 @@
       </c>
       <c r="J75" s="12">
         <f t="shared" si="2"/>
-        <v>1.3704974271012009</v>
+        <v>1.3533447684391082</v>
       </c>
       <c r="K75" s="11">
-        <v>3.7626628075253257E-2</v>
+        <v>3.7900874635568516E-2</v>
       </c>
       <c r="L75" s="13">
         <v>8510100000</v>
@@ -5847,13 +5859,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="12">
-        <v>5.6759917456197226E-2</v>
+        <v>5.7286366363438257E-2</v>
       </c>
       <c r="Q75" s="12">
         <v>0.18453201842262756</v>
       </c>
       <c r="R75" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
@@ -5867,13 +5879,13 @@
         <v>75</v>
       </c>
       <c r="E76">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>4957853696</v>
+        <v>4862755328</v>
       </c>
       <c r="H76" s="6">
         <v>10.06</v>
@@ -5883,10 +5895,10 @@
       </c>
       <c r="J76" s="12">
         <f t="shared" si="2"/>
-        <v>0.10670731707317072</v>
+        <v>9.4512195121951192E-2</v>
       </c>
       <c r="K76" s="11">
-        <v>4.9173553719008264E-2</v>
+        <v>4.9721448467966577E-2</v>
       </c>
       <c r="L76" s="13">
         <v>618033000</v>
@@ -5901,13 +5913,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>0.1104942267042521</v>
+        <v>0.1122810570821956</v>
       </c>
       <c r="Q76" s="12">
         <v>0.12279555988606453</v>
       </c>
       <c r="R76" s="14">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
@@ -5921,26 +5933,26 @@
         <v>155</v>
       </c>
       <c r="E77">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>22929016832</v>
+        <v>23159226368</v>
       </c>
       <c r="H77" s="6">
-        <v>25.1</v>
+        <v>26.45</v>
       </c>
       <c r="I77" s="6">
         <v>9.9</v>
       </c>
       <c r="J77" s="12">
         <f t="shared" si="2"/>
-        <v>1.5151515151515151</v>
+        <v>1.5404040404040402</v>
       </c>
       <c r="K77" s="11">
-        <v>3.1325301204819279E-3</v>
+        <v>3.1013916500994038E-3</v>
       </c>
       <c r="L77" s="13">
         <v>334940000</v>
@@ -5955,13 +5967,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P77" s="12">
-        <v>0.12814880776817372</v>
+        <v>0.1266980855299184</v>
       </c>
       <c r="Q77" s="12">
         <v>0.11071024253191752</v>
       </c>
       <c r="R77" s="14">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
@@ -5975,13 +5987,13 @@
         <v>75</v>
       </c>
       <c r="E78">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G78" s="7">
-        <v>19223781376</v>
+        <v>20153964544</v>
       </c>
       <c r="H78" s="6">
         <v>4.13</v>
@@ -5991,10 +6003,10 @@
       </c>
       <c r="J78" s="12">
         <f t="shared" si="2"/>
-        <v>0.4691943127962086</v>
+        <v>0.54028436018957349</v>
       </c>
       <c r="K78" s="11">
-        <v>5.1612903225806452E-2</v>
+        <v>4.9230769230769231E-2</v>
       </c>
       <c r="L78" s="13">
         <v>1677300000</v>
@@ -6009,13 +6021,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P78" s="12">
-        <v>8.6143675219317165E-2</v>
+        <v>8.2456596746649582E-2</v>
       </c>
       <c r="Q78" s="12">
         <v>0.1499088374088374</v>
       </c>
       <c r="R78" s="14">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
@@ -6029,13 +6041,13 @@
         <v>243</v>
       </c>
       <c r="E79">
-        <v>8.3800000000000008</v>
+        <v>8.77</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>112839213056</v>
+        <v>115703496704</v>
       </c>
       <c r="H79" s="6">
         <v>11</v>
@@ -6045,7 +6057,7 @@
       </c>
       <c r="J79" s="12">
         <f t="shared" si="2"/>
-        <v>0.22514619883040954</v>
+        <v>0.28216374269005851</v>
       </c>
       <c r="K79" s="11">
         <v>0</v>
@@ -6063,13 +6075,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P79" s="12">
-        <v>9.8866428537302056E-2</v>
+        <v>9.5892422849861741E-2</v>
       </c>
       <c r="Q79" s="12">
         <v>0.1154893948238957</v>
       </c>
       <c r="R79" s="14">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
@@ -6083,26 +6095,26 @@
         <v>77</v>
       </c>
       <c r="E80">
-        <v>14.86</v>
+        <v>15.62</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>62717816832</v>
+        <v>65572917248</v>
       </c>
       <c r="H80" s="6">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="I80" s="6">
         <v>10.98</v>
       </c>
       <c r="J80" s="12">
         <f t="shared" si="2"/>
-        <v>0.35336976320582858</v>
+        <v>0.42258652094717664</v>
       </c>
       <c r="K80" s="11">
-        <v>5.9623149394347243E-2</v>
+        <v>5.6722151088348272E-2</v>
       </c>
       <c r="L80" s="13">
         <v>11996000000</v>
@@ -6117,13 +6129,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="12">
-        <v>0.1397226238435702</v>
+        <v>0.13522574641477345</v>
       </c>
       <c r="Q80" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R80" s="14">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
@@ -6137,26 +6149,26 @@
         <v>77</v>
       </c>
       <c r="E81">
-        <v>14.86</v>
+        <v>15.62</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>62717816832</v>
+        <v>65572917248</v>
       </c>
       <c r="H81" s="6">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="I81" s="6">
         <v>10.98</v>
       </c>
       <c r="J81" s="12">
         <f t="shared" si="2"/>
-        <v>0.35336976320582858</v>
+        <v>0.42258652094717664</v>
       </c>
       <c r="K81" s="11">
-        <v>5.9623149394347243E-2</v>
+        <v>5.6722151088348272E-2</v>
       </c>
       <c r="L81" s="13">
         <v>11996000000</v>
@@ -6171,13 +6183,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="12">
-        <v>0.1397226238435702</v>
+        <v>0.13522574641477345</v>
       </c>
       <c r="Q81" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R81" s="14">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
@@ -6191,26 +6203,26 @@
         <v>50</v>
       </c>
       <c r="E82">
-        <v>13.48</v>
+        <v>19.52</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>61809164288</v>
+        <v>76687253504</v>
       </c>
       <c r="H82" s="6">
-        <v>14.7</v>
+        <v>119.9</v>
       </c>
       <c r="I82" s="6">
         <v>7.51</v>
       </c>
       <c r="J82" s="12">
         <f t="shared" si="2"/>
-        <v>0.79494007989347537</v>
+        <v>1.5992010652463384</v>
       </c>
       <c r="K82" s="11">
-        <v>3.2492581602373886E-2</v>
+        <v>2.2438524590163936E-2</v>
       </c>
       <c r="L82" s="13">
         <v>3967214824.1399999</v>
@@ -6225,13 +6237,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P82" s="12">
-        <v>0.11672724972844652</v>
+        <v>8.2800486340514443E-2</v>
       </c>
       <c r="Q82" s="12">
         <v>9.6670468672106824E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
@@ -6245,13 +6257,13 @@
         <v>185</v>
       </c>
       <c r="E83">
-        <v>7.59</v>
+        <v>7.54</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>4354717184</v>
+        <v>4326029824</v>
       </c>
       <c r="H83" s="6">
         <v>9.24</v>
@@ -6261,10 +6273,10 @@
       </c>
       <c r="J83" s="12">
         <f t="shared" si="2"/>
-        <v>0.11946902654867242</v>
+        <v>0.11209439528023601</v>
       </c>
       <c r="K83" s="11">
-        <v>5.2700922266139663E-2</v>
+        <v>5.3050397877984087E-2</v>
       </c>
       <c r="L83" s="13">
         <v>371538000</v>
@@ -6279,13 +6291,13 @@
         <v>1</v>
       </c>
       <c r="P83" s="12">
-        <v>6.8355299987935519E-2</v>
+        <v>6.8717985290189645E-2</v>
       </c>
       <c r="Q83" s="12">
         <v>0.12232565520665489</v>
       </c>
       <c r="R83" s="14">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
@@ -6299,13 +6311,13 @@
         <v>98</v>
       </c>
       <c r="E84">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="7">
-        <v>1884819200</v>
+        <v>1885003136</v>
       </c>
       <c r="H84" s="6">
         <v>2.54</v>
@@ -6315,10 +6327,10 @@
       </c>
       <c r="J84" s="12">
         <f t="shared" si="2"/>
-        <v>0.16860465116279055</v>
+        <v>0.18023255813953476</v>
       </c>
       <c r="K84" s="11">
-        <v>5.4726368159203988E-2</v>
+        <v>5.4187192118226604E-2</v>
       </c>
       <c r="L84" s="13">
         <v>238321000</v>
@@ -6333,13 +6345,13 @@
         <v>1</v>
       </c>
       <c r="P84" s="12">
-        <v>0.15574050207149945</v>
+        <v>0.15572178424717617</v>
       </c>
       <c r="Q84" s="12">
         <v>3.9146558666946343E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
@@ -6353,13 +6365,13 @@
         <v>104</v>
       </c>
       <c r="E85">
-        <v>33.1</v>
+        <v>34.4</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>75590467584</v>
+        <v>77510082560</v>
       </c>
       <c r="H85" s="6">
         <v>61.55</v>
@@ -6369,10 +6381,10 @@
       </c>
       <c r="J85" s="12">
         <f t="shared" si="2"/>
-        <v>0.33199195171026163</v>
+        <v>0.38430583501006033</v>
       </c>
       <c r="K85" s="11">
-        <v>1.7160120845921448E-2</v>
+        <v>1.6511627906976745E-2</v>
       </c>
       <c r="L85" s="13">
         <v>5261270000</v>
@@ -6387,13 +6399,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>6.9081657557763493E-2</v>
+        <v>6.7489455924387765E-2</v>
       </c>
       <c r="Q85" s="12">
         <v>0.12176329850933591</v>
       </c>
       <c r="R85" s="14">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
@@ -6407,13 +6419,13 @@
         <v>308</v>
       </c>
       <c r="E86">
-        <v>51.95</v>
+        <v>54.5</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>1066865983488</v>
+        <v>1091754917888</v>
       </c>
       <c r="H86" s="6">
         <v>59.8</v>
@@ -6423,10 +6435,10 @@
       </c>
       <c r="J86" s="12">
         <f t="shared" si="2"/>
-        <v>0.59111791730474739</v>
+        <v>0.66921898928024515</v>
       </c>
       <c r="K86" s="11">
-        <v>4.9085659287776702E-2</v>
+        <v>4.6788990825688069E-2</v>
       </c>
       <c r="L86" s="13">
         <v>189900000000</v>
@@ -6441,13 +6453,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>0.13152822578296461</v>
+        <v>0.1294396819895004</v>
       </c>
       <c r="Q86" s="12">
         <v>8.2016774784268678E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
@@ -6461,13 +6473,13 @@
         <v>66</v>
       </c>
       <c r="E87">
-        <v>53.2</v>
+        <v>61.3</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>137838542848</v>
+        <v>152916525056</v>
       </c>
       <c r="H87" s="6">
         <v>82.25</v>
@@ -6477,10 +6489,10 @@
       </c>
       <c r="J87" s="12">
         <f t="shared" si="2"/>
-        <v>0.40554821664465002</v>
+        <v>0.61955085865257575</v>
       </c>
       <c r="K87" s="11">
-        <v>1.9736842105263157E-2</v>
+        <v>1.7128874388254486E-2</v>
       </c>
       <c r="L87" s="13">
         <v>6350637223.7200003</v>
@@ -6495,13 +6507,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>6.3915976641537461E-2</v>
+        <v>5.5966487009343341E-2</v>
       </c>
       <c r="Q87" s="12">
         <v>0.10968970241604512</v>
       </c>
       <c r="R87" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
@@ -6515,13 +6527,13 @@
         <v>164</v>
       </c>
       <c r="E88">
-        <v>6.46</v>
+        <v>6.7</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>46276145152</v>
+        <v>48257622016</v>
       </c>
       <c r="H88" s="6">
         <v>10.72</v>
@@ -6531,10 +6543,10 @@
       </c>
       <c r="J88" s="12">
         <f t="shared" si="2"/>
-        <v>0.29200000000000004</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="K88" s="11">
-        <v>6.6563467492260067E-2</v>
+        <v>6.4179104477611937E-2</v>
       </c>
       <c r="L88" s="13">
         <v>6749146000</v>
@@ -6549,13 +6561,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>9.1429094736514824E-2</v>
+        <v>8.9188268484422781E-2</v>
       </c>
       <c r="Q88" s="12">
         <v>9.5261833390841127E-2</v>
       </c>
       <c r="R88" s="14">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
@@ -6569,13 +6581,13 @@
         <v>181</v>
       </c>
       <c r="E89">
-        <v>9.5299999999999994</v>
+        <v>10.58</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>22669867008</v>
+        <v>24928911360</v>
       </c>
       <c r="H89" s="6">
         <v>11.68</v>
@@ -6585,7 +6597,7 @@
       </c>
       <c r="J89" s="12">
         <f t="shared" si="2"/>
-        <v>0.8362235067437378</v>
+        <v>1.0385356454720616</v>
       </c>
       <c r="K89" s="11">
         <v>0</v>
@@ -6603,13 +6615,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P89" s="12">
-        <v>0.11832657836434349</v>
+        <v>0.11617243868152641</v>
       </c>
       <c r="Q89" s="12">
         <v>6.4862080854845933E-2</v>
       </c>
       <c r="R89" s="14">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
@@ -6623,13 +6635,13 @@
         <v>93</v>
       </c>
       <c r="E90">
-        <v>22.15</v>
+        <v>23.6</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>127867518976</v>
+        <v>137706471424</v>
       </c>
       <c r="H90" s="6">
         <v>26.6</v>
@@ -6639,10 +6651,10 @@
       </c>
       <c r="J90" s="12">
         <f t="shared" si="2"/>
-        <v>0.38264669163545562</v>
+        <v>0.47315855181023725</v>
       </c>
       <c r="K90" s="11">
-        <v>3.2054176072234764E-2</v>
+        <v>3.0084745762711862E-2</v>
       </c>
       <c r="L90" s="13">
         <v>10795274825</v>
@@ -6657,13 +6669,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>0.13664379695871273</v>
+        <v>0.12237834591778861</v>
       </c>
       <c r="Q90" s="12">
         <v>5.0146340085309396E-2</v>
       </c>
       <c r="R90" s="14">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
@@ -6677,13 +6689,13 @@
         <v>310</v>
       </c>
       <c r="E91">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>63864332288</v>
+        <v>66086821888</v>
       </c>
       <c r="H91" s="6">
         <v>2.08</v>
@@ -6693,10 +6705,10 @@
       </c>
       <c r="J91" s="12">
         <f t="shared" si="2"/>
-        <v>0.46610169491525433</v>
+        <v>0.52542372881355948</v>
       </c>
       <c r="K91" s="11">
-        <v>3.236994219653179E-2</v>
+        <v>3.111111111111111E-2</v>
       </c>
       <c r="L91" s="13">
         <v>12616717000</v>
@@ -6711,13 +6723,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P91" s="12">
-        <v>0.1249556499731697</v>
+        <v>0.12243318997716839</v>
       </c>
       <c r="Q91" s="12">
         <v>5.4568577322633927E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
@@ -6731,13 +6743,13 @@
         <v>109</v>
       </c>
       <c r="E92">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G92" s="7">
-        <v>5595360768</v>
+        <v>5709552128</v>
       </c>
       <c r="H92" s="6">
         <v>9.15</v>
@@ -6747,10 +6759,10 @@
       </c>
       <c r="J92" s="12">
         <f t="shared" si="2"/>
-        <v>0.48750000000000004</v>
+        <v>0.51785714285714302</v>
       </c>
       <c r="K92" s="11">
-        <v>6.1224489795918366E-2</v>
+        <v>0.06</v>
       </c>
       <c r="L92" s="13">
         <v>1136392000</v>
@@ -6765,13 +6777,13 @@
         <v>1</v>
       </c>
       <c r="P92" s="12">
-        <v>0.11125183825866611</v>
+        <v>0.11002187730530083</v>
       </c>
       <c r="Q92" s="12">
         <v>6.5089877530620205E-2</v>
       </c>
       <c r="R92" s="14">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
@@ -6785,26 +6797,26 @@
         <v>98</v>
       </c>
       <c r="E93">
-        <v>12.68</v>
+        <v>12.3</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>96055566336</v>
+        <v>93176930304</v>
       </c>
       <c r="H93" s="6">
         <v>12.76</v>
       </c>
       <c r="I93" s="6">
-        <v>9.02</v>
+        <v>9.35</v>
       </c>
       <c r="J93" s="12">
         <f t="shared" si="2"/>
-        <v>0.40576496674057649</v>
+        <v>0.31550802139037448</v>
       </c>
       <c r="K93" s="11">
-        <v>6.2145110410094642E-2</v>
+        <v>6.4065040650406496E-2</v>
       </c>
       <c r="L93" s="13">
         <v>8154000000</v>
@@ -6819,13 +6831,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="12">
-        <v>5.9360286407885883E-2</v>
+        <v>6.0630877754782327E-2</v>
       </c>
       <c r="Q93" s="12">
         <v>0.10245263104990703</v>
       </c>
       <c r="R93" s="14">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
@@ -6839,13 +6851,13 @@
         <v>98</v>
       </c>
       <c r="E94">
-        <v>5.68</v>
+        <v>5.72</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>725591588864</v>
+        <v>707981541376</v>
       </c>
       <c r="H94" s="6">
         <v>6.98</v>
@@ -6855,10 +6867,10 @@
       </c>
       <c r="J94" s="12">
         <f t="shared" si="2"/>
-        <v>0.39215686274509798</v>
+        <v>0.40196078431372539</v>
       </c>
       <c r="K94" s="11">
-        <v>4.5774647887323945E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="L94" s="13">
         <v>44563000000</v>
@@ -6873,13 +6885,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>6.7756874037394055E-2</v>
+        <v>6.9498647503900349E-2</v>
       </c>
       <c r="Q94" s="12">
         <v>9.605709580489824E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
@@ -6893,13 +6905,13 @@
         <v>104</v>
       </c>
       <c r="E95">
-        <v>10.84</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>34629029888</v>
+        <v>31823998976</v>
       </c>
       <c r="H95" s="6">
         <v>11.34</v>
@@ -6909,10 +6921,10 @@
       </c>
       <c r="J95" s="12">
         <f t="shared" si="2"/>
-        <v>0.93571428571428572</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="K95" s="11">
-        <v>2.9520295202952032E-2</v>
+        <v>3.1372549019607843E-2</v>
       </c>
       <c r="L95" s="13">
         <v>1990539000</v>
@@ -6927,13 +6939,13 @@
         <v>1</v>
       </c>
       <c r="P95" s="12">
-        <v>5.3248047334694702E-2</v>
+        <v>5.75677075053697E-2</v>
       </c>
       <c r="Q95" s="12">
         <v>0.10689920561026972</v>
       </c>
       <c r="R95" s="14">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
@@ -6947,13 +6959,13 @@
         <v>98</v>
       </c>
       <c r="E96">
-        <v>9.26</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>283337490432</v>
+        <v>289151090688</v>
       </c>
       <c r="H96" s="6">
         <v>11.56</v>
@@ -6963,7 +6975,7 @@
       </c>
       <c r="J96" s="12">
         <f t="shared" si="2"/>
-        <v>0.5748299319727892</v>
+        <v>0.60714285714285698</v>
       </c>
       <c r="K96" s="11">
         <v>0</v>
@@ -6981,13 +6993,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P96" s="12">
-        <v>9.7631408980080311E-2</v>
+        <v>9.5747028346081578E-2</v>
       </c>
       <c r="Q96" s="12">
         <v>7.4329031387590908E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
@@ -7001,13 +7013,13 @@
         <v>151</v>
       </c>
       <c r="E97">
-        <v>9.86</v>
+        <v>10.78</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>25392556032</v>
+        <v>27319429120</v>
       </c>
       <c r="H97" s="6">
         <v>13.78</v>
@@ -7017,10 +7029,10 @@
       </c>
       <c r="J97" s="12">
         <f t="shared" si="2"/>
-        <v>0.81249999999999978</v>
+        <v>0.98161764705882337</v>
       </c>
       <c r="K97" s="11">
-        <v>3.0425963488843813E-2</v>
+        <v>2.7829313543599257E-2</v>
       </c>
       <c r="L97" s="13">
         <v>9652467000</v>
@@ -7035,13 +7047,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>0.10423682715764739</v>
+        <v>0.10224543971218297</v>
       </c>
       <c r="Q97" s="12">
         <v>5.5629198178196171E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
@@ -7055,13 +7067,13 @@
         <v>151</v>
       </c>
       <c r="E98">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G98" s="7">
-        <v>6798396416</v>
+        <v>7332301824</v>
       </c>
       <c r="H98" s="6">
         <v>2.95</v>
@@ -7070,11 +7082,11 @@
         <v>1.37</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J119" si="3">E98/I98-1</f>
-        <v>0.39416058394160558</v>
+        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
+        <v>0.50364963503649629</v>
       </c>
       <c r="K98" s="11">
-        <v>4.9214659685863874E-2</v>
+        <v>4.5631067961165048E-2</v>
       </c>
       <c r="L98" s="13">
         <v>2220197000</v>
@@ -7089,13 +7101,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P98" s="12">
-        <v>0.11810265841672082</v>
+        <v>0.11504440250808318</v>
       </c>
       <c r="Q98" s="12">
         <v>3.1227495254580313E-2</v>
       </c>
       <c r="R98" s="14">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
@@ -7109,13 +7121,13 @@
         <v>310</v>
       </c>
       <c r="E99">
-        <v>5.45</v>
+        <v>5.78</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>115553075200</v>
+        <v>116254294016</v>
       </c>
       <c r="H99" s="6">
         <v>7.03</v>
@@ -7125,10 +7137,10 @@
       </c>
       <c r="J99" s="12">
         <f t="shared" si="3"/>
-        <v>0.29146919431279628</v>
+        <v>0.36966824644549767</v>
       </c>
       <c r="K99" s="11">
-        <v>5.5045871559633024E-2</v>
+        <v>5.1903114186851208E-2</v>
       </c>
       <c r="L99" s="13">
         <v>42109966000</v>
@@ -7143,13 +7155,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>0.10000360084802316</v>
+        <v>9.9847968671539111E-2</v>
       </c>
       <c r="Q99" s="12">
         <v>5.643429507724386E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
@@ -7163,26 +7175,26 @@
         <v>171</v>
       </c>
       <c r="E100">
-        <v>48.7</v>
+        <v>53.45</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>186522959872</v>
+        <v>204715638784</v>
       </c>
       <c r="H100" s="6">
-        <v>52.95</v>
+        <v>53.8</v>
       </c>
       <c r="I100" s="6">
         <v>37.450000000000003</v>
       </c>
       <c r="J100" s="12">
         <f t="shared" si="3"/>
-        <v>0.30040053404539391</v>
+        <v>0.42723631508678239</v>
       </c>
       <c r="K100" s="11">
-        <v>4.5215605749486652E-2</v>
+        <v>4.1197380729653878E-2</v>
       </c>
       <c r="L100" s="13">
         <v>41737000000</v>
@@ -7197,13 +7209,13 @@
         <v>1</v>
       </c>
       <c r="P100" s="12">
-        <v>0.10703140726644196</v>
+        <v>0.10226056719724666</v>
       </c>
       <c r="Q100" s="12">
         <v>5.2504192208844336E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
@@ -7217,13 +7229,13 @@
         <v>151</v>
       </c>
       <c r="E101">
-        <v>35.049999999999997</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>123901050880</v>
+        <v>127916957696</v>
       </c>
       <c r="H101" s="6">
         <v>37.25</v>
@@ -7233,10 +7245,10 @@
       </c>
       <c r="J101" s="12">
         <f t="shared" si="3"/>
-        <v>0.24733096085409234</v>
+        <v>0.30071174377224175</v>
       </c>
       <c r="K101" s="11">
-        <v>4.9643366619115552E-2</v>
+        <v>4.7606019151846792E-2</v>
       </c>
       <c r="L101" s="13">
         <v>16863000000</v>
@@ -7251,13 +7263,13 @@
         <v>1</v>
       </c>
       <c r="P101" s="12">
-        <v>0.1159255492885391</v>
+        <v>0.11281111033155748</v>
       </c>
       <c r="Q101" s="12">
         <v>3.7613758029978586E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
@@ -7271,26 +7283,26 @@
         <v>98</v>
       </c>
       <c r="E102">
-        <v>5.76</v>
+        <v>5.64</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>44588507136</v>
+        <v>43659579392</v>
       </c>
       <c r="H102" s="6">
-        <v>5.81</v>
+        <v>5.83</v>
       </c>
       <c r="I102" s="6">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="J102" s="12">
         <f t="shared" si="3"/>
-        <v>0.47692307692307701</v>
+        <v>0.42424242424242409</v>
       </c>
       <c r="K102" s="11">
-        <v>6.6493055555555555E-2</v>
+        <v>6.7907801418439717E-2</v>
       </c>
       <c r="L102" s="13">
         <v>5474000000</v>
@@ -7305,13 +7317,13 @@
         <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>5.6877746025575292E-2</v>
+        <v>5.743208330861159E-2</v>
       </c>
       <c r="Q102" s="12">
         <v>9.2144023431582137E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
@@ -7325,26 +7337,26 @@
         <v>93</v>
       </c>
       <c r="E103">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>9286301696</v>
+        <v>11362062336</v>
       </c>
       <c r="H103" s="6">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="I103" s="6">
         <v>0.81</v>
       </c>
       <c r="J103" s="12">
         <f t="shared" si="3"/>
-        <v>1.0987654320987654</v>
+        <v>1.5679012345679011</v>
       </c>
       <c r="K103" s="11">
-        <v>0.02</v>
+        <v>1.6346153846153847E-2</v>
       </c>
       <c r="L103" s="13">
         <v>1384865000</v>
@@ -7359,13 +7371,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P103" s="12">
-        <v>7.2528237414429889E-2</v>
+        <v>6.5829774282170239E-2</v>
       </c>
       <c r="Q103" s="12">
         <v>5.8120488088461209E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
@@ -7379,26 +7391,26 @@
         <v>171</v>
       </c>
       <c r="E104">
-        <v>25</v>
+        <v>28.1</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>28203501568</v>
+        <v>31143512064</v>
       </c>
       <c r="H104" s="6">
-        <v>26.65</v>
+        <v>29.2</v>
       </c>
       <c r="I104" s="6">
         <v>14.52</v>
       </c>
       <c r="J104" s="12">
         <f t="shared" si="3"/>
-        <v>0.721763085399449</v>
+        <v>0.93526170798898089</v>
       </c>
       <c r="K104" s="11">
-        <v>3.7599999999999995E-2</v>
+        <v>3.345195729537366E-2</v>
       </c>
       <c r="L104" s="13">
         <v>3838344000</v>
@@ -7413,13 +7425,13 @@
         <v>1</v>
       </c>
       <c r="P104" s="12">
-        <v>8.3403357612738135E-2</v>
+        <v>7.8395199943308624E-2</v>
       </c>
       <c r="Q104" s="12">
         <v>4.7084186647510511E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
@@ -7433,13 +7445,13 @@
         <v>98</v>
       </c>
       <c r="E105">
-        <v>11.76</v>
+        <v>11.74</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>205222576128</v>
+        <v>206633402368</v>
       </c>
       <c r="H105" s="6">
         <v>12.46</v>
@@ -7449,10 +7461,10 @@
       </c>
       <c r="J105" s="12">
         <f t="shared" si="3"/>
-        <v>0.27826086956521756</v>
+        <v>0.2760869565217392</v>
       </c>
       <c r="K105" s="11">
-        <v>3.545918367346939E-2</v>
+        <v>3.5519591141396932E-2</v>
       </c>
       <c r="L105" s="13">
         <v>16758000000</v>
@@ -7467,13 +7479,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P105" s="12">
-        <v>5.9418087533155119E-2</v>
+        <v>5.9141179317688433E-2</v>
       </c>
       <c r="Q105" s="12">
         <v>6.2161059386475759E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
@@ -7487,13 +7499,13 @@
         <v>87</v>
       </c>
       <c r="E106">
-        <v>6.72</v>
+        <v>6.77</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>7012588544</v>
+        <v>7064765440</v>
       </c>
       <c r="H106" s="6">
         <v>7</v>
@@ -7503,7 +7515,7 @@
       </c>
       <c r="J106" s="12">
         <f t="shared" si="3"/>
-        <v>0.67164179104477628</v>
+        <v>0.68407960199004991</v>
       </c>
       <c r="K106" s="11">
         <v>0</v>
@@ -7521,13 +7533,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="12">
-        <v>5.1250867323799743E-2</v>
+        <v>5.0803003152450829E-2</v>
       </c>
       <c r="Q106" s="12">
         <v>8.3790449156695201E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
@@ -7541,13 +7553,13 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>10179149824</v>
+        <v>12111899648</v>
       </c>
       <c r="H107" s="6">
         <v>3.04</v>
@@ -7557,10 +7569,10 @@
       </c>
       <c r="J107" s="12">
         <f t="shared" si="3"/>
-        <v>0.22797927461139911</v>
+        <v>0.46113989637305686</v>
       </c>
       <c r="K107" s="11">
-        <v>4.514767932489451E-2</v>
+        <v>3.7943262411347517E-2</v>
       </c>
       <c r="L107" s="13">
         <v>1938532000</v>
@@ -7575,13 +7587,13 @@
         <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>6.3128576869622949E-2</v>
+        <v>5.9390520887332217E-2</v>
       </c>
       <c r="Q107" s="12">
         <v>3.8781191586606881E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
@@ -7595,13 +7607,13 @@
         <v>87</v>
       </c>
       <c r="E108">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>9996959744</v>
+        <v>10015335424</v>
       </c>
       <c r="H108" s="6">
         <v>12.88</v>
@@ -7611,16 +7623,16 @@
       </c>
       <c r="J108" s="12">
         <f t="shared" si="3"/>
-        <v>1.1118568232662192</v>
+        <v>1.1208053691275168</v>
       </c>
       <c r="K108" s="11">
-        <v>1.5042372881355931E-2</v>
+        <v>1.4978902953586495E-2</v>
       </c>
       <c r="L108" s="13">
-        <v>161696000</v>
+        <v>350106000</v>
       </c>
       <c r="M108" s="13">
-        <v>3260547000</v>
+        <v>3348556000</v>
       </c>
       <c r="N108" s="9" t="s">
         <v>68</v>
@@ -7629,13 +7641,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>1.6564905324730955E-2</v>
+        <v>3.7603317032345991E-2</v>
       </c>
       <c r="Q108" s="12">
-        <v>4.95916789422143E-2</v>
+        <v>0.10455432132537129</v>
       </c>
       <c r="R108" s="14">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
@@ -7649,13 +7661,13 @@
         <v>85</v>
       </c>
       <c r="E109">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>11957545984</v>
+        <v>10519596032</v>
       </c>
       <c r="H109" s="6">
         <v>2.99</v>
@@ -7665,10 +7677,10 @@
       </c>
       <c r="J109" s="12">
         <f t="shared" si="3"/>
-        <v>1.3076923076923079</v>
+        <v>1.0879120879120876</v>
       </c>
       <c r="K109" s="11">
-        <v>7.1428571428571426E-3</v>
+        <v>7.8947368421052634E-3</v>
       </c>
       <c r="L109" s="13">
         <v>429393000</v>
@@ -7683,13 +7695,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>3.5561230253856144E-2</v>
+        <v>4.036862198589633E-2</v>
       </c>
       <c r="Q109" s="12">
         <v>2.3421020321148112E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
@@ -7703,13 +7715,13 @@
         <v>196</v>
       </c>
       <c r="E110">
-        <v>45.9</v>
+        <v>52.75</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>466949898240</v>
+        <v>520297512960</v>
       </c>
       <c r="H110" s="6">
         <v>59.7</v>
@@ -7719,7 +7731,7 @@
       </c>
       <c r="J110" s="12">
         <f t="shared" si="3"/>
-        <v>2.0118110236220472</v>
+        <v>2.4612860892388451</v>
       </c>
       <c r="K110" s="11">
         <v>0</v>
@@ -7737,13 +7749,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P110" s="12">
-        <v>1.4924131353543519E-2</v>
+        <v>1.3503780086771638E-2</v>
       </c>
       <c r="Q110" s="12">
         <v>3.0575487595734537E-2</v>
       </c>
       <c r="R110" s="14">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
@@ -7757,26 +7769,26 @@
         <v>153</v>
       </c>
       <c r="E111">
-        <v>14.98</v>
+        <v>15.34</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>15507594240</v>
+        <v>15754333184</v>
       </c>
       <c r="H111" s="6">
-        <v>15.22</v>
+        <v>15.48</v>
       </c>
       <c r="I111" s="6">
         <v>10.36</v>
       </c>
       <c r="J111" s="12">
         <f t="shared" si="3"/>
-        <v>0.44594594594594605</v>
+        <v>0.48069498069498073</v>
       </c>
       <c r="K111" s="11">
-        <v>7.209612817089453E-2</v>
+        <v>7.0404172099087364E-2</v>
       </c>
       <c r="L111" s="13">
         <v>984000000</v>
@@ -7791,13 +7803,13 @@
         <v>1</v>
       </c>
       <c r="P111" s="12">
-        <v>2.4321762538888916E-2</v>
+        <v>2.4174330422068905E-2</v>
       </c>
       <c r="Q111" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R111" s="14">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
@@ -7811,13 +7823,13 @@
         <v>174</v>
       </c>
       <c r="E112">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="7">
-        <v>32470661120</v>
+        <v>31755898880</v>
       </c>
       <c r="H112" s="6">
         <v>36</v>
@@ -7827,7 +7839,7 @@
       </c>
       <c r="J112" s="12">
         <f t="shared" si="3"/>
-        <v>0.41964285714285721</v>
+        <v>0.38839285714285721</v>
       </c>
       <c r="K112" s="11">
         <v>0</v>
@@ -7845,13 +7857,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P112" s="12">
-        <v>-3.3088640153491021E-3</v>
+        <v>-3.3920055125667469E-3</v>
       </c>
       <c r="Q112" s="12">
         <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R112" s="14">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.5">
@@ -7865,23 +7877,23 @@
         <v>377</v>
       </c>
       <c r="E113">
-        <v>2.2599999999999998</v>
+        <v>2.36</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>5170202112</v>
+        <v>5042210816</v>
       </c>
       <c r="H113" s="6">
-        <v>2.5499999999999998</v>
+        <v>2.62</v>
       </c>
       <c r="I113" s="6">
         <v>0.99</v>
       </c>
       <c r="J113" s="12">
         <f t="shared" si="3"/>
-        <v>1.2828282828282824</v>
+        <v>1.3838383838383836</v>
       </c>
       <c r="K113" s="11">
         <v>0</v>
@@ -7899,13 +7911,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P113" s="12">
-        <v>-12.890588161786203</v>
+        <v>11.617418292408182</v>
       </c>
       <c r="Q113" s="12">
         <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R113" s="14">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.5">
@@ -7919,13 +7931,13 @@
         <v>229</v>
       </c>
       <c r="E114">
-        <v>36.85</v>
+        <v>35.9</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>391192215552</v>
+        <v>379563540480</v>
       </c>
       <c r="H114" s="6">
         <v>37.950000000000003</v>
@@ -7935,10 +7947,10 @@
       </c>
       <c r="J114" s="12">
         <f t="shared" si="3"/>
-        <v>0.71395348837209305</v>
+        <v>0.66976744186046511</v>
       </c>
       <c r="K114" s="11">
-        <v>5.397557666214383E-2</v>
+        <v>5.540389972144847E-2</v>
       </c>
       <c r="M114" s="13">
         <v>415994000000</v>
@@ -7961,13 +7973,13 @@
         <v>229</v>
       </c>
       <c r="E115">
-        <v>5.89</v>
+        <v>5.67</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>742181240832</v>
+        <v>728492933120</v>
       </c>
       <c r="H115" s="6">
         <v>5.95</v>
@@ -7977,7 +7989,7 @@
       </c>
       <c r="J115" s="12">
         <f t="shared" si="3"/>
-        <v>0.51413881748071977</v>
+        <v>0.45758354755784048</v>
       </c>
       <c r="K115" s="11">
         <v>0</v>
@@ -8003,13 +8015,13 @@
         <v>229</v>
       </c>
       <c r="E116">
-        <v>7.59</v>
+        <v>7.5</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>499557105664</v>
+        <v>475682996224</v>
       </c>
       <c r="H116" s="6">
         <v>8.1199999999999992</v>
@@ -8019,10 +8031,10 @@
       </c>
       <c r="J116" s="12">
         <f t="shared" si="3"/>
-        <v>0.78169014084507049</v>
+        <v>0.76056338028169024</v>
       </c>
       <c r="K116" s="11">
-        <v>4.6772068511198944E-2</v>
+        <v>4.7333333333333331E-2</v>
       </c>
       <c r="M116" s="13">
         <v>2066897000000</v>
@@ -8045,13 +8057,13 @@
         <v>231</v>
       </c>
       <c r="E117">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G117" s="7">
-        <v>731638792192</v>
+        <v>707272835072</v>
       </c>
       <c r="H117" s="6">
         <v>7.62</v>
@@ -8061,10 +8073,10 @@
       </c>
       <c r="J117" s="12">
         <f t="shared" si="3"/>
-        <v>0.46259842519685024</v>
+        <v>0.42913385826771644</v>
       </c>
       <c r="K117" s="11">
-        <v>5.1009421265141325E-2</v>
+        <v>5.2203856749311293E-2</v>
       </c>
       <c r="M117" s="13">
         <v>2314289000000</v>
@@ -8087,13 +8099,13 @@
         <v>231</v>
       </c>
       <c r="E118">
-        <v>6.22</v>
+        <v>6.09</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="7">
-        <v>2837022769152</v>
+        <v>2744281989120</v>
       </c>
       <c r="H118" s="6">
         <v>6.48</v>
@@ -8103,10 +8115,10 @@
       </c>
       <c r="J118" s="12">
         <f t="shared" si="3"/>
-        <v>0.53201970443349755</v>
+        <v>0.5</v>
       </c>
       <c r="K118" s="11">
-        <v>4.9517684887459806E-2</v>
+        <v>5.057471264367816E-2</v>
       </c>
       <c r="M118" s="13">
         <v>6434377000000</v>
@@ -8129,13 +8141,13 @@
         <v>231</v>
       </c>
       <c r="E119">
-        <v>8.36</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G119" s="7">
-        <v>2241315733504</v>
+        <v>2212780048384</v>
       </c>
       <c r="H119" s="6">
         <v>8.56</v>
@@ -8145,10 +8157,10 @@
       </c>
       <c r="J119" s="12">
         <f t="shared" si="3"/>
-        <v>0.59847036328871872</v>
+        <v>0.58699808795411101</v>
       </c>
       <c r="K119" s="11">
-        <v>4.8205741626794266E-2</v>
+        <v>4.8554216867469878E-2</v>
       </c>
       <c r="M119" s="13">
         <v>6128626000000</v>
@@ -8164,15 +8176,162 @@
       <c r="B120" s="1" t="s">
         <v>393</v>
       </c>
+      <c r="C120" t="s">
+        <v>396</v>
+      </c>
+      <c r="D120" t="s">
+        <v>151</v>
+      </c>
+      <c r="E120">
+        <v>8.94</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G120" s="7">
+        <v>81801895936</v>
+      </c>
+      <c r="H120" s="6">
+        <v>9.08</v>
+      </c>
+      <c r="I120" s="6">
+        <v>7.31</v>
+      </c>
+      <c r="J120" s="12">
+        <f t="shared" si="3"/>
+        <v>0.22298221614227076</v>
+      </c>
+      <c r="K120" s="11">
+        <v>6.4876957494407153E-2</v>
+      </c>
+      <c r="L120" s="13">
+        <v>4813000000</v>
+      </c>
+      <c r="M120" s="13">
+        <v>168240000000</v>
+      </c>
+      <c r="N120" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O120" s="6">
+        <v>1</v>
+      </c>
+      <c r="P120" s="12">
+        <v>5.8362812682257618E-2</v>
+      </c>
+      <c r="Q120" s="12">
+        <v>2.8607941036614362E-2</v>
+      </c>
+      <c r="R120" s="14">
+        <v>72</v>
+      </c>
     </row>
     <row r="121" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B121" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="C121" t="s">
+        <v>397</v>
+      </c>
+      <c r="D121" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121">
+        <v>17.04</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" s="7">
+        <v>43881922560</v>
+      </c>
+      <c r="H121" s="6">
+        <v>21</v>
+      </c>
+      <c r="I121" s="6">
+        <v>12.56</v>
+      </c>
+      <c r="J121" s="12">
+        <f t="shared" si="3"/>
+        <v>0.3566878980891719</v>
+      </c>
+      <c r="K121" s="11">
+        <v>3.4330985915492961E-2</v>
+      </c>
+      <c r="L121" s="13">
+        <v>4264779000</v>
+      </c>
+      <c r="M121" s="13">
+        <v>26103689000</v>
+      </c>
+      <c r="N121" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O121" s="6">
+        <v>1.0683760683760684</v>
+      </c>
+      <c r="P121" s="12">
+        <v>0.12009733705228849</v>
+      </c>
+      <c r="Q121" s="12">
+        <v>0.16337840218675606</v>
+      </c>
+      <c r="R121" s="14">
+        <v>35</v>
+      </c>
     </row>
     <row r="122" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B122" s="1" t="s">
         <v>395</v>
+      </c>
+      <c r="C122" t="s">
+        <v>398</v>
+      </c>
+      <c r="D122" t="s">
+        <v>399</v>
+      </c>
+      <c r="E122">
+        <v>43.65</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G122" s="7">
+        <v>112721764352</v>
+      </c>
+      <c r="H122" s="6">
+        <v>44.1</v>
+      </c>
+      <c r="I122" s="6">
+        <v>31.1</v>
+      </c>
+      <c r="J122" s="12">
+        <f t="shared" si="3"/>
+        <v>0.40353697749196127</v>
+      </c>
+      <c r="K122" s="11">
+        <v>6.2382588774341351E-2</v>
+      </c>
+      <c r="L122" s="13">
+        <v>-6742000000</v>
+      </c>
+      <c r="M122" s="13">
+        <v>216378000000</v>
+      </c>
+      <c r="N122" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O122" s="6">
+        <v>1</v>
+      </c>
+      <c r="P122" s="12">
+        <v>-4.148239846452733E-2</v>
+      </c>
+      <c r="Q122" s="12">
+        <v>-3.1158435700487111E-2</v>
+      </c>
+      <c r="R122" s="14">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C08A4F-CE92-4F5C-950F-5E2DB0084197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A79D65-6EBB-4E3D-ABB4-873584A093D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -1883,13 +1883,13 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>15.42</v>
+        <v>14.86</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>271720431616</v>
+        <v>261962481664</v>
       </c>
       <c r="H2" s="6">
         <v>15.6</v>
@@ -1899,10 +1899,10 @@
       </c>
       <c r="J2" s="12">
         <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.61974789915966388</v>
+        <v>0.56092436974789917</v>
       </c>
       <c r="K2" s="11">
-        <v>0.10051880674448768</v>
+        <v>0.10430686406460297</v>
       </c>
       <c r="L2" s="13">
         <v>70144988000</v>
@@ -1917,7 +1917,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.47925186167505085</v>
+        <v>0.51114879571340921</v>
       </c>
       <c r="Q2" s="12">
         <v>0.26042924055386191</v>
@@ -1937,13 +1937,13 @@
         <v>153</v>
       </c>
       <c r="E3">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>2965739776</v>
+        <v>2947656192</v>
       </c>
       <c r="H3" s="6">
         <v>3.55</v>
@@ -1953,10 +1953,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.4137931034482758</v>
+        <v>0.40517241379310343</v>
       </c>
       <c r="K3" s="11">
-        <v>5.1524390243902443E-2</v>
+        <v>5.1840490797546018E-2</v>
       </c>
       <c r="L3" s="13">
         <v>504294000</v>
@@ -1971,13 +1971,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.31536263347456289</v>
+        <v>0.31873642691061266</v>
       </c>
       <c r="Q3" s="12">
         <v>0.29581628786323422</v>
       </c>
       <c r="R3" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.5">
@@ -1991,26 +1991,26 @@
         <v>148</v>
       </c>
       <c r="E4">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>9202853888</v>
+        <v>9286770688</v>
       </c>
       <c r="H4" s="6">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="I4" s="6">
         <v>2.36</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.39406779661016955</v>
+        <v>0.40677966101694918</v>
       </c>
       <c r="K4" s="11">
-        <v>4.6504559270516714E-2</v>
+        <v>4.608433734939759E-2</v>
       </c>
       <c r="L4" s="13">
         <v>1871151000</v>
@@ -2025,7 +2025,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.39938743571668051</v>
+        <v>0.39280200743904892</v>
       </c>
       <c r="Q4" s="12">
         <v>0.28956319566547578</v>
@@ -2045,13 +2045,13 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>7.92</v>
+        <v>7.94</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>30904158208</v>
+        <v>30982199296</v>
       </c>
       <c r="H5" s="6">
         <v>8.35</v>
@@ -2061,10 +2061,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.87677725118483418</v>
+        <v>0.88151658767772534</v>
       </c>
       <c r="K5" s="11">
-        <v>5.4292929292929287E-3</v>
+        <v>5.4156171284634753E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2079,13 +2079,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.25823826016454682</v>
+        <v>0.25738118152940009</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
       </c>
       <c r="R5" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.5">
@@ -2099,13 +2099,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>146.6</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>96810688512</v>
+        <v>94631452672</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2115,10 +2115,10 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.61098901098901082</v>
+        <v>0.5747252747252749</v>
       </c>
       <c r="K6" s="11">
-        <v>1.330150068212824E-2</v>
+        <v>1.3607815771109559E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2133,13 +2133,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.43518402790640787</v>
+        <v>0.45654427812122245</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
       </c>
       <c r="R6" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.5">
@@ -2153,26 +2153,26 @@
         <v>306</v>
       </c>
       <c r="E7">
-        <v>6.13</v>
+        <v>6.31</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>383386124288</v>
+        <v>397220184064</v>
       </c>
       <c r="H7" s="6">
-        <v>6.24</v>
+        <v>6.42</v>
       </c>
       <c r="I7" s="6">
         <v>2.52</v>
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>1.4325396825396823</v>
+        <v>1.503968253968254</v>
       </c>
       <c r="K7" s="11">
-        <v>2.936378466557912E-2</v>
+        <v>2.8526148969889066E-2</v>
       </c>
       <c r="L7" s="13">
         <v>72477000000</v>
@@ -2187,13 +2187,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.18749737468869018</v>
+        <v>0.1814201404208311</v>
       </c>
       <c r="Q7" s="12">
         <v>0.22694806719794586</v>
       </c>
       <c r="R7" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.5">
@@ -2207,13 +2207,13 @@
         <v>146</v>
       </c>
       <c r="E8">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>14815013888</v>
+        <v>14967745536</v>
       </c>
       <c r="H8" s="6">
         <v>3.12</v>
@@ -2223,10 +2223,10 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.30493273542600896</v>
+        <v>0.31838565022421528</v>
       </c>
       <c r="K8" s="11">
-        <v>0.10309278350515463</v>
+        <v>0.10204081632653061</v>
       </c>
       <c r="L8" s="13">
         <v>2527643000</v>
@@ -2241,13 +2241,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.35190160057272546</v>
+        <v>0.34457473908992692</v>
       </c>
       <c r="Q8" s="12">
         <v>0.15337570692947131</v>
       </c>
       <c r="R8" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.5">
@@ -2261,13 +2261,13 @@
         <v>225</v>
       </c>
       <c r="E9">
-        <v>17.260000000000002</v>
+        <v>17.04</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>149609152512</v>
+        <v>149461073920</v>
       </c>
       <c r="H9" s="6">
         <v>18.100000000000001</v>
@@ -2277,10 +2277,10 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.62830188679245302</v>
+        <v>0.60754716981132062</v>
       </c>
       <c r="K9" s="11">
-        <v>4.1657010428736957E-2</v>
+        <v>4.2194835680751178E-2</v>
       </c>
       <c r="L9" s="13">
         <v>21175963859.630001</v>
@@ -2295,13 +2295,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.19042378788707598</v>
+        <v>0.19066142209904643</v>
       </c>
       <c r="Q9" s="12">
         <v>0.20347556909712136</v>
       </c>
       <c r="R9" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -2315,13 +2315,13 @@
         <v>304</v>
       </c>
       <c r="E10">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>215139205120</v>
+        <v>217569705984</v>
       </c>
       <c r="H10" s="6">
         <v>9.5399999999999991</v>
@@ -2331,10 +2331,10 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>1.0327510917030569</v>
+        <v>1.0393013100436681</v>
       </c>
       <c r="K10" s="11">
-        <v>2.7389903329752954E-2</v>
+        <v>2.7301927194860815E-2</v>
       </c>
       <c r="L10" s="13">
         <v>29168443138.220001</v>
@@ -2349,13 +2349,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.14497868317798404</v>
+        <v>0.14335768137381114</v>
       </c>
       <c r="Q10" s="12">
         <v>0.2888078161719172</v>
       </c>
       <c r="R10" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -2369,13 +2369,13 @@
         <v>223</v>
       </c>
       <c r="E11">
-        <v>2.2599999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>2260000000</v>
+        <v>2230000128</v>
       </c>
       <c r="H11" s="6">
         <v>2.42</v>
@@ -2385,10 +2385,10 @@
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.67407407407407383</v>
+        <v>0.65185185185185168</v>
       </c>
       <c r="K11" s="11">
-        <v>9.2920353982300891E-2</v>
+        <v>9.417040358744394E-2</v>
       </c>
       <c r="L11" s="13">
         <v>315190000</v>
@@ -2403,13 +2403,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.12978029294548438</v>
+        <v>0.13140345736333311</v>
       </c>
       <c r="Q11" s="12">
         <v>0.51857007005524791</v>
       </c>
       <c r="R11" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.5">
@@ -2423,13 +2423,13 @@
         <v>301</v>
       </c>
       <c r="E12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>3222800128</v>
+        <v>3242942464</v>
       </c>
       <c r="H12" s="6">
         <v>1.66</v>
@@ -2439,10 +2439,10 @@
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.41592920353982321</v>
+        <v>0.42477876106194712</v>
       </c>
       <c r="K12" s="11">
-        <v>7.4374999999999997E-2</v>
+        <v>7.3913043478260859E-2</v>
       </c>
       <c r="L12" s="13">
         <v>929863000</v>
@@ -2457,13 +2457,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.32965052125613736</v>
+        <v>0.32746184668900374</v>
       </c>
       <c r="Q12" s="12">
         <v>0.15429118804462028</v>
       </c>
       <c r="R12" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -2477,13 +2477,13 @@
         <v>87</v>
       </c>
       <c r="E13">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>42787975168</v>
+        <v>42697326592</v>
       </c>
       <c r="H13" s="6">
         <v>7.38</v>
@@ -2493,10 +2493,10 @@
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.39233038348082583</v>
+        <v>0.38938053097345127</v>
       </c>
       <c r="K13" s="11">
-        <v>6.5042372881355934E-2</v>
+        <v>6.5180467091295116E-2</v>
       </c>
       <c r="L13" s="13">
         <v>5594372000</v>
@@ -2511,13 +2511,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.1758714794662688</v>
+        <v>0.17634184586825569</v>
       </c>
       <c r="Q13" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -2531,13 +2531,13 @@
         <v>301</v>
       </c>
       <c r="E14">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>2022588032</v>
+        <v>1963447936</v>
       </c>
       <c r="H14" s="6">
         <v>2.77</v>
@@ -2547,10 +2547,10 @@
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.25735294117647056</v>
+        <v>0.22058823529411753</v>
       </c>
       <c r="K14" s="11">
-        <v>3.5672514619883043E-2</v>
+        <v>3.6746987951807232E-2</v>
       </c>
       <c r="L14" s="13">
         <v>841215000</v>
@@ -2565,13 +2565,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.54696151852339225</v>
+        <v>0.567382839661148</v>
       </c>
       <c r="Q14" s="12">
         <v>0.14567921288909008</v>
       </c>
       <c r="R14" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
@@ -2585,26 +2585,26 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>5.46</v>
+        <v>6</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>11289532416</v>
+        <v>12406079488</v>
       </c>
       <c r="H15" s="6">
-        <v>5.54</v>
+        <v>6</v>
       </c>
       <c r="I15" s="6">
         <v>3.15</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.73333333333333339</v>
+        <v>0.90476190476190488</v>
       </c>
       <c r="K15" s="11">
-        <v>4.5787545787545784E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="L15" s="13">
         <v>1576240000</v>
@@ -2619,13 +2619,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.2396494228748017</v>
+        <v>0.20679153222118959</v>
       </c>
       <c r="Q15" s="12">
         <v>0.16357040581906512</v>
       </c>
       <c r="R15" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2639,26 +2639,26 @@
         <v>308</v>
       </c>
       <c r="E16">
-        <v>17.02</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>61170225152</v>
+        <v>63757914112</v>
       </c>
       <c r="H16" s="6">
-        <v>17.28</v>
+        <v>18.079999999999998</v>
       </c>
       <c r="I16" s="6">
         <v>7.62</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>1.2335958005249341</v>
+        <v>1.3280839895013119</v>
       </c>
       <c r="K16" s="11">
-        <v>2.0564042303172738E-2</v>
+        <v>1.9729425028184894E-2</v>
       </c>
       <c r="L16" s="13">
         <v>25585077000</v>
@@ -2673,13 +2673,13 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.25868284229842736</v>
+        <v>0.25208739729739288</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
@@ -2693,13 +2693,13 @@
         <v>83</v>
       </c>
       <c r="E17">
-        <v>16.16</v>
+        <v>15.22</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>32171489280</v>
+        <v>31020034048</v>
       </c>
       <c r="H17" s="6">
         <v>17.059999999999999</v>
@@ -2709,10 +2709,10 @@
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>1.0301507537688441</v>
+        <v>0.9120603015075377</v>
       </c>
       <c r="K17" s="11">
-        <v>6.9306930693069313E-2</v>
+        <v>7.3587385019710905E-2</v>
       </c>
       <c r="L17" s="13">
         <v>5451928473.2399998</v>
@@ -2727,7 +2727,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.16344490942638637</v>
+        <v>0.16890223095168</v>
       </c>
       <c r="Q17" s="12">
         <v>0.20973136925592797</v>
@@ -2747,26 +2747,26 @@
         <v>77</v>
       </c>
       <c r="E18">
-        <v>25.75</v>
+        <v>25.85</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>68318355456</v>
+        <v>68583669760</v>
       </c>
       <c r="H18" s="6">
-        <v>26.15</v>
+        <v>26.3</v>
       </c>
       <c r="I18" s="6">
         <v>15.7</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.64012738853503182</v>
+        <v>0.64649681528662439</v>
       </c>
       <c r="K18" s="11">
-        <v>1.0563106796116505E-2</v>
+        <v>1.0522243713733075E-2</v>
       </c>
       <c r="L18" s="13">
         <v>1069250000</v>
@@ -2781,13 +2781,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P18" s="12">
-        <v>0.12541472763078063</v>
+        <v>0.12490940536069382</v>
       </c>
       <c r="Q18" s="12">
         <v>0.41587371596437778</v>
       </c>
       <c r="R18" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
@@ -2801,13 +2801,13 @@
         <v>87</v>
       </c>
       <c r="E19">
-        <v>7.92</v>
+        <v>8.1</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>101615181824</v>
+        <v>103924621312</v>
       </c>
       <c r="H19" s="6">
         <v>8.16</v>
@@ -2817,10 +2817,10 @@
       </c>
       <c r="J19" s="12">
         <f t="shared" si="0"/>
-        <v>0.63636363636363646</v>
+        <v>0.67355371900826433</v>
       </c>
       <c r="K19" s="11">
-        <v>8.0808080808080808E-3</v>
+        <v>7.9012345679012348E-3</v>
       </c>
       <c r="L19" s="13">
         <v>2553000000</v>
@@ -2835,13 +2835,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P19" s="12">
-        <v>0.17158441585182907</v>
+        <v>0.1681906734478098</v>
       </c>
       <c r="Q19" s="12">
         <v>0.18273566673824351</v>
       </c>
       <c r="R19" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.5">
@@ -2895,7 +2895,7 @@
         <v>0.14466826109721026</v>
       </c>
       <c r="R20" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.5">
@@ -2909,13 +2909,13 @@
         <v>96</v>
       </c>
       <c r="E21">
-        <v>15.88</v>
+        <v>16.32</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="7">
-        <v>13216733184</v>
+        <v>13582940160</v>
       </c>
       <c r="H21" s="6">
         <v>19.440000000000001</v>
@@ -2925,10 +2925,10 @@
       </c>
       <c r="J21" s="12">
         <f t="shared" si="0"/>
-        <v>0.30807248764415163</v>
+        <v>0.34431630971993399</v>
       </c>
       <c r="K21" s="11">
-        <v>9.319899244332493E-3</v>
+        <v>9.0686274509803912E-3</v>
       </c>
       <c r="L21" s="13">
         <v>199557000</v>
@@ -2943,13 +2943,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P21" s="12">
-        <v>0.15272691042116737</v>
+        <v>0.14735792693234448</v>
       </c>
       <c r="Q21" s="12">
         <v>0.18009145491283626</v>
       </c>
       <c r="R21" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.5">
@@ -2963,13 +2963,13 @@
         <v>74</v>
       </c>
       <c r="E22">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="7">
-        <v>2973856512</v>
+        <v>3109031936</v>
       </c>
       <c r="H22" s="6">
         <v>3.34</v>
@@ -2979,10 +2979,10 @@
       </c>
       <c r="J22" s="12">
         <f t="shared" si="0"/>
-        <v>0.48958333333333326</v>
+        <v>0.55729166666666674</v>
       </c>
       <c r="K22" s="11">
-        <v>0.10209790209790209</v>
+        <v>9.7658862876254166E-2</v>
       </c>
       <c r="L22" s="13">
         <v>762183000</v>
@@ -2997,13 +2997,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="12">
-        <v>0.20494875361262907</v>
+        <v>0.19776050120941521</v>
       </c>
       <c r="Q22" s="12">
         <v>0.15218339726363278</v>
       </c>
       <c r="R22" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.5">
@@ -3017,13 +3017,13 @@
         <v>81</v>
       </c>
       <c r="E23">
-        <v>7.82</v>
+        <v>7.76</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="7">
-        <v>67713384448</v>
+        <v>67193843712</v>
       </c>
       <c r="H23" s="6">
         <v>8.6199999999999992</v>
@@ -3033,10 +3033,10 @@
       </c>
       <c r="J23" s="12">
         <f t="shared" si="0"/>
-        <v>0.10451977401129953</v>
+        <v>9.6045197740112886E-2</v>
       </c>
       <c r="K23" s="11">
-        <v>4.0409207161125317E-2</v>
+        <v>4.0721649484536084E-2</v>
       </c>
       <c r="L23" s="13">
         <v>13438000000</v>
@@ -3051,13 +3051,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P23" s="12">
-        <v>0.22459655578037108</v>
+        <v>0.22643695147490772</v>
       </c>
       <c r="Q23" s="12">
         <v>0.15165160081705431</v>
       </c>
       <c r="R23" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.5">
@@ -3071,13 +3071,13 @@
         <v>79</v>
       </c>
       <c r="E24">
-        <v>10.32</v>
+        <v>9.98</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="7">
-        <v>164788715520</v>
+        <v>160022298624</v>
       </c>
       <c r="H24" s="6">
         <v>10.76</v>
@@ -3087,10 +3087,10 @@
       </c>
       <c r="J24" s="12">
         <f t="shared" si="0"/>
-        <v>0.44134078212290495</v>
+        <v>0.3938547486033519</v>
       </c>
       <c r="K24" s="11">
-        <v>4.6414728682170538E-2</v>
+        <v>4.799599198396793E-2</v>
       </c>
       <c r="L24" s="13">
         <v>32866046000</v>
@@ -3105,13 +3105,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P24" s="12">
-        <v>0.17406796560984755</v>
+        <v>0.17828049655268605</v>
       </c>
       <c r="Q24" s="12">
         <v>0.15266623500015464</v>
       </c>
       <c r="R24" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.5">
@@ -3165,7 +3165,7 @@
         <v>0.12269104771613493</v>
       </c>
       <c r="R25" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.5">
@@ -3179,13 +3179,13 @@
         <v>96</v>
       </c>
       <c r="E26">
-        <v>12.74</v>
+        <v>12.78</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="7">
-        <v>20441966592</v>
+        <v>20506148864</v>
       </c>
       <c r="H26" s="6">
         <v>18.399999999999999</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="J26" s="12">
         <f t="shared" si="0"/>
-        <v>0.32294911734164056</v>
+        <v>0.32710280373831768</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3213,13 +3213,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P26" s="12">
-        <v>0.22111842309123225</v>
+        <v>0.22047763200999473</v>
       </c>
       <c r="Q26" s="12">
         <v>0.12218132992627646</v>
       </c>
       <c r="R26" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.5">
@@ -3233,13 +3233,13 @@
         <v>75</v>
       </c>
       <c r="E27">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="7">
-        <v>15307520000</v>
+        <v>15334282240</v>
       </c>
       <c r="H27" s="6">
         <v>7.13</v>
@@ -3249,10 +3249,10 @@
       </c>
       <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>0.3783132530120481</v>
+        <v>0.38072289156626504</v>
       </c>
       <c r="K27" s="11">
-        <v>4.0209790209790215E-2</v>
+        <v>4.0139616055846421E-2</v>
       </c>
       <c r="L27" s="13">
         <v>2030839000</v>
@@ -3267,13 +3267,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P27" s="12">
-        <v>0.14126635461935361</v>
+        <v>0.14102063252318034</v>
       </c>
       <c r="Q27" s="12">
         <v>0.17526328902672489</v>
       </c>
       <c r="R27" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.5">
@@ -3287,26 +3287,26 @@
         <v>61</v>
       </c>
       <c r="E28">
-        <v>11.58</v>
+        <v>12.08</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="7">
-        <v>18211749888</v>
+        <v>18656593920</v>
       </c>
       <c r="H28" s="6">
-        <v>11.9</v>
+        <v>12.14</v>
       </c>
       <c r="I28" s="6">
         <v>8.67</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="0"/>
-        <v>0.33564013840830453</v>
+        <v>0.39331026528258373</v>
       </c>
       <c r="K28" s="11">
-        <v>5.181347150259067E-2</v>
+        <v>4.9668874172185427E-2</v>
       </c>
       <c r="L28" s="13">
         <v>1721368005.75</v>
@@ -3321,13 +3321,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P28" s="12">
-        <v>0.21248452750721705</v>
+        <v>0.20209734391412587</v>
       </c>
       <c r="Q28" s="12">
         <v>0.11773304155211949</v>
       </c>
       <c r="R28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.5">
@@ -3341,13 +3341,13 @@
         <v>54</v>
       </c>
       <c r="E29">
-        <v>4.59</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="7">
-        <v>17800388608</v>
+        <v>17877948416</v>
       </c>
       <c r="H29" s="6">
         <v>6.97</v>
@@ -3357,10 +3357,10 @@
       </c>
       <c r="J29" s="12">
         <f t="shared" si="0"/>
-        <v>0.37837837837837829</v>
+        <v>0.38438438438438438</v>
       </c>
       <c r="K29" s="11">
-        <v>5.8823529411764712E-2</v>
+        <v>5.8568329718004339E-2</v>
       </c>
       <c r="L29" s="13">
         <v>2823432000</v>
@@ -3375,13 +3375,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12">
-        <v>0.14999299867774846</v>
+        <v>0.14937751631177007</v>
       </c>
       <c r="Q29" s="12">
         <v>0.16681818624944278</v>
       </c>
       <c r="R29" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.5">
@@ -3395,13 +3395,13 @@
         <v>241</v>
       </c>
       <c r="E30">
-        <v>9.36</v>
+        <v>9.08</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="7">
-        <v>9243318272</v>
+        <v>8966808576</v>
       </c>
       <c r="H30" s="6">
         <v>9.65</v>
@@ -3411,10 +3411,10 @@
       </c>
       <c r="J30" s="12">
         <f t="shared" si="0"/>
-        <v>0.87199999999999989</v>
+        <v>0.81600000000000006</v>
       </c>
       <c r="K30" s="11">
-        <v>3.7820512820512818E-2</v>
+        <v>3.8986784140969163E-2</v>
       </c>
       <c r="L30" s="13">
         <v>1333116000</v>
@@ -3429,13 +3429,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P30" s="12">
-        <v>0.15713521756279702</v>
+        <v>0.16207969517781859</v>
       </c>
       <c r="Q30" s="12">
         <v>0.16622802330680692</v>
       </c>
       <c r="R30" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.5">
@@ -3489,7 +3489,7 @@
         <v>9.2370860611101543E-2</v>
       </c>
       <c r="R31" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.5">
@@ -3503,13 +3503,13 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>6.3</v>
+        <v>6.44</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <v>6676992000</v>
+        <v>6825369600</v>
       </c>
       <c r="H32" s="6">
         <v>6.88</v>
@@ -3519,10 +3519,10 @@
       </c>
       <c r="J32" s="12">
         <f t="shared" si="0"/>
-        <v>0.58690176322418131</v>
+        <v>0.62216624685138533</v>
       </c>
       <c r="K32" s="11">
-        <v>7.7777777777777779E-2</v>
+        <v>7.6086956521739121E-2</v>
       </c>
       <c r="L32" s="13">
         <v>866801000</v>
@@ -3537,13 +3537,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="12">
-        <v>0.23546575196966005</v>
+        <v>0.22634263880430644</v>
       </c>
       <c r="Q32" s="12">
         <v>0.11511220438953086</v>
       </c>
       <c r="R32" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.5">
@@ -3557,26 +3557,26 @@
         <v>50</v>
       </c>
       <c r="E33">
-        <v>7.9</v>
+        <v>8.89</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="7">
-        <v>9838818304</v>
+        <v>11071784960</v>
       </c>
       <c r="H33" s="6">
-        <v>8.6</v>
+        <v>9.06</v>
       </c>
       <c r="I33" s="6">
         <v>3.46</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="0"/>
-        <v>1.2832369942196533</v>
+        <v>1.5693641618497112</v>
       </c>
       <c r="K33" s="11">
-        <v>1.7848101265822782E-2</v>
+        <v>1.5860517435320583E-2</v>
       </c>
       <c r="L33" s="13">
         <v>921702000</v>
@@ -3591,13 +3591,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P33" s="12">
-        <v>0.13339672580257989</v>
+        <v>0.11430492992253397</v>
       </c>
       <c r="Q33" s="12">
         <v>0.17514380877385538</v>
       </c>
       <c r="R33" s="14">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
@@ -3611,13 +3611,13 @@
         <v>71</v>
       </c>
       <c r="E34">
-        <v>4.49</v>
+        <v>4.41</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="7">
-        <v>51921010688</v>
+        <v>50995916800</v>
       </c>
       <c r="H34" s="6">
         <v>5.14</v>
@@ -3627,10 +3627,10 @@
       </c>
       <c r="J34" s="12">
         <f t="shared" ref="J34:J65" si="1">E34/I34-1</f>
-        <v>0.29768786127167646</v>
+        <v>0.27456647398843925</v>
       </c>
       <c r="K34" s="11">
-        <v>5.8129175946547887E-2</v>
+        <v>5.9183673469387757E-2</v>
       </c>
       <c r="L34" s="13">
         <v>4734613000</v>
@@ -3645,13 +3645,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P34" s="12">
-        <v>0.10385313688843621</v>
+        <v>0.10586382341687654</v>
       </c>
       <c r="Q34" s="12">
         <v>0.29201860560357656</v>
       </c>
       <c r="R34" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
@@ -3665,13 +3665,13 @@
         <v>50</v>
       </c>
       <c r="E35">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="7">
-        <v>16995728384</v>
+        <v>17174630400</v>
       </c>
       <c r="H35" s="6">
         <v>8.6999999999999993</v>
@@ -3681,10 +3681,10 @@
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
-        <v>2.5185185185185182</v>
+        <v>2.5555555555555554</v>
       </c>
       <c r="K35" s="11">
-        <v>3.0394736842105266E-2</v>
+        <v>3.0078125000000004E-2</v>
       </c>
       <c r="L35" s="13">
         <v>2184074765.02</v>
@@ -3699,13 +3699,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P35" s="12">
-        <v>0.27703593390796261</v>
+        <v>0.27127400538541924</v>
       </c>
       <c r="Q35" s="12">
         <v>9.29654274042198E-2</v>
       </c>
       <c r="R35" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
@@ -3719,13 +3719,13 @@
         <v>181</v>
       </c>
       <c r="E36">
-        <v>10.44</v>
+        <v>10.52</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G36" s="7">
-        <v>129505067008</v>
+        <v>130497454080</v>
       </c>
       <c r="H36" s="6">
         <v>13.6</v>
@@ -3735,10 +3735,10 @@
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
-        <v>0.58904109589041087</v>
+        <v>0.60121765601217647</v>
       </c>
       <c r="K36" s="11">
-        <v>4.7892720306513415E-3</v>
+        <v>4.7528517110266167E-3</v>
       </c>
       <c r="L36" s="13">
         <v>2250990000</v>
@@ -3753,13 +3753,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P36" s="12">
-        <v>0.12617308481660089</v>
+        <v>0.12526723728485289</v>
       </c>
       <c r="Q36" s="12">
         <v>0.19681397761416858</v>
       </c>
       <c r="R36" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
@@ -3773,26 +3773,26 @@
         <v>98</v>
       </c>
       <c r="E37">
-        <v>4.5999999999999996</v>
+        <v>4.68</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="7">
-        <v>5064370176</v>
+        <v>5152445952</v>
       </c>
       <c r="H37" s="6">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="I37" s="6">
         <v>3.69</v>
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
-        <v>0.24661246612466114</v>
+        <v>0.26829268292682928</v>
       </c>
       <c r="K37" s="11">
-        <v>6.9565217391304349E-2</v>
+        <v>6.8376068376068383E-2</v>
       </c>
       <c r="L37" s="13">
         <v>765224000</v>
@@ -3807,13 +3807,13 @@
         <v>1</v>
       </c>
       <c r="P37" s="12">
-        <v>0.17193606249074636</v>
+        <v>0.16859956108485941</v>
       </c>
       <c r="Q37" s="12">
         <v>0.14577225152582682</v>
       </c>
       <c r="R37" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
@@ -3827,13 +3827,13 @@
         <v>77</v>
       </c>
       <c r="E38">
-        <v>5.96</v>
+        <v>5.89</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G38" s="7">
-        <v>8737181696</v>
+        <v>8634563584</v>
       </c>
       <c r="H38" s="6">
         <v>6.07</v>
@@ -3843,10 +3843,10 @@
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
-        <v>0.72753623188405792</v>
+        <v>0.70724637681159397</v>
       </c>
       <c r="K38" s="11">
-        <v>8.0536912751677847E-2</v>
+        <v>8.1494057724957561E-2</v>
       </c>
       <c r="L38" s="13">
         <v>784607000</v>
@@ -3861,13 +3861,13 @@
         <v>1</v>
       </c>
       <c r="P38" s="12">
-        <v>0.26008959487490779</v>
+        <v>0.26924859938032114</v>
       </c>
       <c r="Q38" s="12">
         <v>9.9663185641922489E-2</v>
       </c>
       <c r="R38" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.5">
@@ -3881,13 +3881,13 @@
         <v>71</v>
       </c>
       <c r="E39">
-        <v>5.73</v>
+        <v>5.78</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="7">
-        <v>16346658816</v>
+        <v>16489299968</v>
       </c>
       <c r="H39" s="6">
         <v>6.21</v>
@@ -3897,10 +3897,10 @@
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
-        <v>0.77950310559006208</v>
+        <v>0.79503105590062106</v>
       </c>
       <c r="K39" s="11">
-        <v>7.3298429319371729E-3</v>
+        <v>7.2664359861591699E-3</v>
       </c>
       <c r="L39" s="13">
         <v>259348000</v>
@@ -3915,13 +3915,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P39" s="12">
-        <v>0.13846296094861918</v>
+        <v>0.1371056038853809</v>
       </c>
       <c r="Q39" s="12">
         <v>0.15459217096529801</v>
       </c>
       <c r="R39" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.5">
@@ -3935,13 +3935,13 @@
         <v>98</v>
       </c>
       <c r="E40">
-        <v>4.59</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G40" s="7">
-        <v>31790434304</v>
+        <v>32205993984</v>
       </c>
       <c r="H40" s="6">
         <v>6.15</v>
@@ -3951,10 +3951,10 @@
       </c>
       <c r="J40" s="12">
         <f t="shared" si="1"/>
-        <v>0.23719676549865221</v>
+        <v>0.25336927223719696</v>
       </c>
       <c r="K40" s="11">
-        <v>4.7712418300653599E-2</v>
+        <v>4.7096774193548387E-2</v>
       </c>
       <c r="L40" s="13">
         <v>4216348000</v>
@@ -3969,13 +3969,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P40" s="12">
-        <v>0.34710130302767522</v>
+        <v>0.33633176837248197</v>
       </c>
       <c r="Q40" s="12">
         <v>9.1377422623841298E-2</v>
       </c>
       <c r="R40" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.5">
@@ -3989,26 +3989,26 @@
         <v>306</v>
       </c>
       <c r="E41">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="7">
-        <v>44280774656</v>
+        <v>46466060288</v>
       </c>
       <c r="H41" s="6">
-        <v>4.1100000000000003</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="I41" s="6">
         <v>2.35</v>
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
-        <v>0.63829787234042556</v>
+        <v>0.7191489361702128</v>
       </c>
       <c r="K41" s="11">
-        <v>4.9350649350649353E-2</v>
+        <v>4.702970297029703E-2</v>
       </c>
       <c r="L41" s="13">
         <v>9414000000</v>
@@ -4023,13 +4023,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P41" s="12">
-        <v>0.17165736953056121</v>
+        <v>0.16548528725941203</v>
       </c>
       <c r="Q41" s="12">
         <v>0.11538320116682396</v>
       </c>
       <c r="R41" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.5">
@@ -4043,13 +4043,13 @@
         <v>151</v>
       </c>
       <c r="E42">
-        <v>29.95</v>
+        <v>30.15</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="7">
-        <v>213571649536</v>
+        <v>214997827584</v>
       </c>
       <c r="H42" s="6">
         <v>32.299999999999997</v>
@@ -4059,10 +4059,10 @@
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
-        <v>0.6136853448275863</v>
+        <v>0.62446120689655182</v>
       </c>
       <c r="K42" s="11">
-        <v>4.4040066777963273E-2</v>
+        <v>4.3747927031509121E-2</v>
       </c>
       <c r="L42" s="13">
         <v>61181051000</v>
@@ -4077,13 +4077,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P42" s="12">
-        <v>0.18268279124126716</v>
+        <v>0.18195752024365092</v>
       </c>
       <c r="Q42" s="12">
         <v>0.11493949471384535</v>
       </c>
       <c r="R42" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.5">
@@ -4097,13 +4097,13 @@
         <v>87</v>
       </c>
       <c r="E43">
-        <v>11.88</v>
+        <v>11.6</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="7">
-        <v>66937151488</v>
+        <v>65359507456</v>
       </c>
       <c r="H43" s="6">
         <v>14.24</v>
@@ -4113,10 +4113,10 @@
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
-        <v>0.3484676503972759</v>
+        <v>0.31668558456299656</v>
       </c>
       <c r="K43" s="11">
-        <v>2.7861952861952862E-2</v>
+        <v>2.853448275862069E-2</v>
       </c>
       <c r="L43" s="13">
         <v>6482967000</v>
@@ -4131,13 +4131,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P43" s="12">
-        <v>9.4431580673540572E-2</v>
+        <v>9.6507396973764092E-2</v>
       </c>
       <c r="Q43" s="12">
         <v>0.23588267049650188</v>
       </c>
       <c r="R43" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.5">
@@ -4151,26 +4151,26 @@
         <v>87</v>
       </c>
       <c r="E44">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G44" s="7">
-        <v>67277668352</v>
+        <v>67513729024</v>
       </c>
       <c r="H44" s="6">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="I44" s="6">
         <v>4.34</v>
       </c>
       <c r="J44" s="12">
         <f t="shared" si="1"/>
-        <v>0.31336405529953915</v>
+        <v>0.31797235023041481</v>
       </c>
       <c r="K44" s="11">
-        <v>2.5964912280701753E-2</v>
+        <v>2.5874125874125874E-2</v>
       </c>
       <c r="L44" s="13">
         <v>5915895000</v>
@@ -4185,13 +4185,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P44" s="12">
-        <v>0.10024247115622946</v>
+        <v>9.9868567582826182E-2</v>
       </c>
       <c r="Q44" s="12">
         <v>0.27010748742934609</v>
       </c>
       <c r="R44" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.5">
@@ -4205,13 +4205,13 @@
         <v>85</v>
       </c>
       <c r="E45">
-        <v>90.8</v>
+        <v>92.15</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G45" s="7">
-        <v>253151313920</v>
+        <v>256915128320</v>
       </c>
       <c r="H45" s="6">
         <v>107.5</v>
@@ -4221,10 +4221,10 @@
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
-        <v>0.38520213577421814</v>
+        <v>0.40579710144927561</v>
       </c>
       <c r="K45" s="11">
-        <v>2.4427312775330397E-2</v>
+        <v>2.406945198046663E-2</v>
       </c>
       <c r="L45" s="13">
         <v>22510000000</v>
@@ -4239,13 +4239,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P45" s="12">
-        <v>8.8733967386986717E-2</v>
+        <v>8.7518568985433115E-2</v>
       </c>
       <c r="Q45" s="12">
         <v>0.27269973953601068</v>
       </c>
       <c r="R45" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.5">
@@ -4259,13 +4259,13 @@
         <v>56</v>
       </c>
       <c r="E46">
-        <v>9.41</v>
+        <v>10.34</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G46" s="7">
-        <v>23721103360</v>
+        <v>26065485824</v>
       </c>
       <c r="H46" s="6">
         <v>11.22</v>
@@ -4275,10 +4275,10 @@
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
-        <v>1.1632183908045981</v>
+        <v>1.3770114942528737</v>
       </c>
       <c r="K46" s="11">
-        <v>3.3793836344314557E-2</v>
+        <v>3.0754352030947778E-2</v>
       </c>
       <c r="L46" s="13">
         <v>3301437000</v>
@@ -4293,13 +4293,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12">
-        <v>0.16576072371997866</v>
+        <v>0.14830410031943025</v>
       </c>
       <c r="Q46" s="12">
         <v>0.15134190781174311</v>
       </c>
       <c r="R46" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.5">
@@ -4313,13 +4313,13 @@
         <v>54</v>
       </c>
       <c r="E47">
-        <v>25.7</v>
+        <v>25.65</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G47" s="7">
-        <v>250693746688</v>
+        <v>248283283456</v>
       </c>
       <c r="H47" s="6">
         <v>36.450000000000003</v>
@@ -4329,10 +4329,10 @@
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
-        <v>0.33575883575883592</v>
+        <v>0.33316008316008316</v>
       </c>
       <c r="K47" s="11">
-        <v>3.7548638132295718E-2</v>
+        <v>3.7621832358674466E-2</v>
       </c>
       <c r="L47" s="13">
         <v>25459748125.549999</v>
@@ -4347,13 +4347,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P47" s="12">
-        <v>0.11390129456087218</v>
+        <v>0.11506270438326018</v>
       </c>
       <c r="Q47" s="12">
         <v>0.18884873513587705</v>
       </c>
       <c r="R47" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.5">
@@ -4367,26 +4367,26 @@
         <v>337</v>
       </c>
       <c r="E48">
-        <v>6.18</v>
+        <v>6.5</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="7">
-        <v>7924242944</v>
+        <v>8334560256</v>
       </c>
       <c r="H48" s="6">
-        <v>6.27</v>
+        <v>6.52</v>
       </c>
       <c r="I48" s="6">
         <v>3.36</v>
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
-        <v>0.83928571428571419</v>
+        <v>0.93452380952380953</v>
       </c>
       <c r="K48" s="11">
-        <v>4.2071197411003243E-2</v>
+        <v>0.04</v>
       </c>
       <c r="L48" s="13">
         <v>2871477000</v>
@@ -4401,13 +4401,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P48" s="12">
-        <v>0.14651131845593979</v>
+        <v>0.14369549973892795</v>
       </c>
       <c r="Q48" s="12">
         <v>0.1318118502166547</v>
       </c>
       <c r="R48" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.5">
@@ -4421,26 +4421,26 @@
         <v>87</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>10.98</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="7">
-        <v>2581942016</v>
+        <v>2577247488</v>
       </c>
       <c r="H49" s="6">
         <v>17</v>
       </c>
       <c r="I49" s="6">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
-        <v>0.49456521739130421</v>
+        <v>0.4898236092265944</v>
       </c>
       <c r="K49" s="11">
-        <v>3.8181818181818178E-2</v>
+        <v>3.8251366120218573E-2</v>
       </c>
       <c r="L49" s="13">
         <v>244811000</v>
@@ -4455,13 +4455,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="12">
-        <v>0.27836955941136471</v>
+        <v>0.27986348506788705</v>
       </c>
       <c r="Q49" s="12">
         <v>8.4294835486117978E-2</v>
       </c>
       <c r="R49" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.5">
@@ -4475,13 +4475,13 @@
         <v>109</v>
       </c>
       <c r="E50">
-        <v>48.05</v>
+        <v>47.5</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G50" s="7">
-        <v>122951303168</v>
+        <v>121543958528</v>
       </c>
       <c r="H50" s="6">
         <v>71.7</v>
@@ -4491,10 +4491,10 @@
       </c>
       <c r="J50" s="12">
         <f t="shared" si="1"/>
-        <v>0.10332950631458093</v>
+        <v>9.070034443168784E-2</v>
       </c>
       <c r="K50" s="11">
-        <v>3.4131113423517172E-3</v>
+        <v>3.4526315789473686E-3</v>
       </c>
       <c r="L50" s="13">
         <v>1279098000</v>
@@ -4509,13 +4509,13 @@
         <v>8.7546153846153842</v>
       </c>
       <c r="P50" s="12">
-        <v>8.0852934540369251E-2</v>
+        <v>8.1682951143369348E-2</v>
       </c>
       <c r="Q50" s="12">
         <v>0.26583067696212276</v>
       </c>
       <c r="R50" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.5">
@@ -4529,13 +4529,13 @@
         <v>174</v>
       </c>
       <c r="E51">
-        <v>80.900000000000006</v>
+        <v>80.150000000000006</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G51" s="7">
-        <v>19806343168</v>
+        <v>19622723584</v>
       </c>
       <c r="H51" s="6">
         <v>95.5</v>
@@ -4545,10 +4545,10 @@
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
-        <v>0.46957311534968227</v>
+        <v>0.4559491371480473</v>
       </c>
       <c r="K51" s="11">
-        <v>1.0135970333745364E-2</v>
+        <v>1.023081721771678E-2</v>
       </c>
       <c r="L51" s="13">
         <v>526052000</v>
@@ -4563,13 +4563,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P51" s="12">
-        <v>0.20313157678503616</v>
+        <v>0.20502135226085508</v>
       </c>
       <c r="Q51" s="12">
         <v>9.8446219337080781E-2</v>
       </c>
       <c r="R51" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.5">
@@ -4583,13 +4583,13 @@
         <v>50</v>
       </c>
       <c r="E52">
-        <v>22.4</v>
+        <v>21.95</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G52" s="7">
-        <v>35750400000</v>
+        <v>35032203264</v>
       </c>
       <c r="H52" s="6">
         <v>27.5</v>
@@ -4599,10 +4599,10 @@
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
-        <v>0.38442521631643989</v>
+        <v>0.35661310259579726</v>
       </c>
       <c r="K52" s="11">
-        <v>3.0625000000000003E-2</v>
+        <v>3.1252847380410023E-2</v>
       </c>
       <c r="L52" s="13">
         <v>3811007000</v>
@@ -4617,13 +4617,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P52" s="12">
-        <v>0.11617818175071594</v>
+        <v>0.11860882435411028</v>
       </c>
       <c r="Q52" s="12">
         <v>0.1667375806872122</v>
       </c>
       <c r="R52" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.5">
@@ -4637,13 +4637,13 @@
         <v>330</v>
       </c>
       <c r="E53">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G53" s="7">
-        <v>13690890240</v>
+        <v>13954567168</v>
       </c>
       <c r="H53" s="6">
         <v>7.86</v>
@@ -4653,10 +4653,10 @@
       </c>
       <c r="J53" s="12">
         <f t="shared" si="1"/>
-        <v>0.27118644067796627</v>
+        <v>0.29566854990583802</v>
       </c>
       <c r="K53" s="11">
-        <v>0.04</v>
+        <v>3.9244186046511628E-2</v>
       </c>
       <c r="L53" s="13">
         <v>1537565000</v>
@@ -4671,13 +4671,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P53" s="12">
-        <v>0.1765374329408417</v>
+        <v>0.17167277041633916</v>
       </c>
       <c r="Q53" s="12">
         <v>0.10614925092863724</v>
       </c>
       <c r="R53" s="14">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.5">
@@ -4731,7 +4731,7 @@
         <v>8.5775443346640556E-2</v>
       </c>
       <c r="R54" s="14">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.5">
@@ -4745,13 +4745,13 @@
         <v>339</v>
       </c>
       <c r="E55">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G55" s="7">
-        <v>8448343040</v>
+        <v>8357500928</v>
       </c>
       <c r="H55" s="6">
         <v>4.9400000000000004</v>
@@ -4761,10 +4761,10 @@
       </c>
       <c r="J55" s="12">
         <f t="shared" si="1"/>
-        <v>0.11377245508982048</v>
+        <v>0.10179640718562877</v>
       </c>
       <c r="K55" s="11">
-        <v>4.0322580645161289E-2</v>
+        <v>4.0760869565217385E-2</v>
       </c>
       <c r="L55" s="13">
         <v>826931000</v>
@@ -4779,13 +4779,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P55" s="12">
-        <v>0.13752878046521555</v>
+        <v>0.13950150425015423</v>
       </c>
       <c r="Q55" s="12">
         <v>0.14788755315990715</v>
       </c>
       <c r="R55" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.5">
@@ -4799,13 +4799,13 @@
         <v>181</v>
       </c>
       <c r="E56">
-        <v>7.81</v>
+        <v>7.69</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G56" s="7">
-        <v>3029373952</v>
+        <v>2982828032</v>
       </c>
       <c r="H56" s="6">
         <v>14.18</v>
@@ -4815,10 +4815,10 @@
       </c>
       <c r="J56" s="12">
         <f t="shared" si="1"/>
-        <v>1.1456043956043955</v>
+        <v>1.1126373626373627</v>
       </c>
       <c r="K56" s="11">
-        <v>4.4814340588988477E-2</v>
+        <v>4.5513654096228866E-2</v>
       </c>
       <c r="L56" s="13">
         <v>348303000</v>
@@ -4833,13 +4833,13 @@
         <v>1</v>
       </c>
       <c r="P56" s="12">
-        <v>0.21418214873984942</v>
+        <v>0.22049321746674719</v>
       </c>
       <c r="Q56" s="12">
         <v>9.4606035666412708E-2</v>
       </c>
       <c r="R56" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.5">
@@ -4853,26 +4853,26 @@
         <v>310</v>
       </c>
       <c r="E57">
-        <v>6.23</v>
+        <v>6.27</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G57" s="7">
-        <v>27375618048</v>
+        <v>27551383552</v>
       </c>
       <c r="H57" s="6">
         <v>6.87</v>
       </c>
       <c r="I57" s="6">
-        <v>4.7699999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="J57" s="12">
         <f t="shared" si="1"/>
-        <v>0.30607966457023084</v>
+        <v>0.30624999999999991</v>
       </c>
       <c r="K57" s="11">
-        <v>5.7463884430176561E-2</v>
+        <v>5.7097288676236049E-2</v>
       </c>
       <c r="L57" s="13">
         <v>2919921000</v>
@@ -4887,13 +4887,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P57" s="12">
-        <v>0.19788043323293975</v>
+        <v>0.19569856318421008</v>
       </c>
       <c r="Q57" s="12">
         <v>9.2221214358852555E-2</v>
       </c>
       <c r="R57" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.5">
@@ -4907,26 +4907,26 @@
         <v>324</v>
       </c>
       <c r="E58">
-        <v>8.64</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G58" s="7">
-        <v>21657458688</v>
+        <v>22058520576</v>
       </c>
       <c r="H58" s="6">
-        <v>8.65</v>
+        <v>8.84</v>
       </c>
       <c r="I58" s="6">
         <v>3.99</v>
       </c>
       <c r="J58" s="12">
         <f t="shared" si="1"/>
-        <v>1.1654135338345863</v>
+        <v>1.2055137844611528</v>
       </c>
       <c r="K58" s="11">
-        <v>3.7152777777777778E-2</v>
+        <v>3.6477272727272726E-2</v>
       </c>
       <c r="L58" s="13">
         <v>3040816000</v>
@@ -4941,13 +4941,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P58" s="12">
-        <v>0.13989897925799713</v>
+        <v>0.137523836994524</v>
       </c>
       <c r="Q58" s="12">
         <v>0.102358453189061</v>
       </c>
       <c r="R58" s="14">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.5">
@@ -4961,13 +4961,13 @@
         <v>151</v>
       </c>
       <c r="E59">
-        <v>4.6399999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G59" s="7">
-        <v>6660302336</v>
+        <v>6459345408</v>
       </c>
       <c r="H59" s="6">
         <v>7.92</v>
@@ -4977,10 +4977,10 @@
       </c>
       <c r="J59" s="12">
         <f t="shared" si="1"/>
-        <v>0.96610169491525411</v>
+        <v>0.90677966101694918</v>
       </c>
       <c r="K59" s="11">
-        <v>5.4741379310344833E-2</v>
+        <v>5.6444444444444443E-2</v>
       </c>
       <c r="L59" s="13">
         <v>811880000</v>
@@ -4995,13 +4995,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P59" s="12">
-        <v>0.13455618597767807</v>
+        <v>0.13888579300836648</v>
       </c>
       <c r="Q59" s="12">
         <v>0.14675695119790894</v>
       </c>
       <c r="R59" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.5">
@@ -5055,7 +5055,7 @@
         <v>6.460670188445812E-2</v>
       </c>
       <c r="R60" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.5">
@@ -5069,13 +5069,13 @@
         <v>101</v>
       </c>
       <c r="E61">
-        <v>435.8</v>
+        <v>440.8</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G61" s="7">
-        <v>550781452288</v>
+        <v>557100630016</v>
       </c>
       <c r="H61" s="6">
         <v>452</v>
@@ -5085,10 +5085,10 @@
       </c>
       <c r="J61" s="12">
         <f t="shared" si="1"/>
-        <v>0.99542124542124544</v>
+        <v>1.0183150183150182</v>
       </c>
       <c r="K61" s="11">
-        <v>2.1248279027076638E-2</v>
+        <v>2.1007259528130671E-2</v>
       </c>
       <c r="L61" s="13">
         <v>20744000000</v>
@@ -5103,13 +5103,13 @@
         <v>1</v>
       </c>
       <c r="P61" s="12">
-        <v>4.9661194462276889E-2</v>
+        <v>4.8921109591368091E-2</v>
       </c>
       <c r="Q61" s="12">
         <v>0.38520389214885242</v>
       </c>
       <c r="R61" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.5">
@@ -5123,13 +5123,13 @@
         <v>177</v>
       </c>
       <c r="E62">
-        <v>22.45</v>
+        <v>22.4</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="7">
-        <v>582864863232</v>
+        <v>579425271808</v>
       </c>
       <c r="H62" s="6">
         <v>23</v>
@@ -5139,10 +5139,10 @@
       </c>
       <c r="J62" s="12">
         <f t="shared" si="1"/>
-        <v>0.66050295857988162</v>
+        <v>0.65680473372781067</v>
       </c>
       <c r="K62" s="11">
-        <v>1.6926503340757237E-2</v>
+        <v>1.6964285714285716E-2</v>
       </c>
       <c r="L62" s="13">
         <v>52374992116</v>
@@ -5157,13 +5157,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P62" s="12">
-        <v>7.9129095703627056E-2</v>
+        <v>7.9515862078542776E-2</v>
       </c>
       <c r="Q62" s="12">
         <v>0.19428864891763736</v>
       </c>
       <c r="R62" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.5">
@@ -5177,13 +5177,13 @@
         <v>83</v>
       </c>
       <c r="E63">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G63" s="7">
-        <v>11470668800</v>
+        <v>11556270080</v>
       </c>
       <c r="H63" s="6">
         <v>3.55</v>
@@ -5193,10 +5193,10 @@
       </c>
       <c r="J63" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.0149253731343282</v>
       </c>
       <c r="K63" s="11">
-        <v>4.5522388059701491E-2</v>
+        <v>4.5185185185185182E-2</v>
       </c>
       <c r="L63" s="13">
         <v>1230913000</v>
@@ -5211,13 +5211,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P63" s="12">
-        <v>0.12923912780769176</v>
+        <v>0.12816097930323397</v>
       </c>
       <c r="Q63" s="12">
         <v>0.11502419323187564</v>
       </c>
       <c r="R63" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.5">
@@ -5231,13 +5231,13 @@
         <v>85</v>
       </c>
       <c r="E64">
-        <v>245.2</v>
+        <v>261.8</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G64" s="7">
-        <v>325664833536</v>
+        <v>347712258048</v>
       </c>
       <c r="H64" s="6">
         <v>283.39999999999998</v>
@@ -5247,10 +5247,10 @@
       </c>
       <c r="J64" s="12">
         <f t="shared" si="1"/>
-        <v>5.7178082191780817</v>
+        <v>6.1726027397260275</v>
       </c>
       <c r="K64" s="11">
-        <v>3.323817292006525E-3</v>
+        <v>3.1130634071810537E-3</v>
       </c>
       <c r="L64" s="13">
         <v>4408440000</v>
@@ -5265,13 +5265,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P64" s="12">
-        <v>1.4710597799745991E-2</v>
+        <v>1.3762860836943074E-2</v>
       </c>
       <c r="Q64" s="12">
         <v>0.41263985929711272</v>
       </c>
       <c r="R64" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.5">
@@ -5285,13 +5285,13 @@
         <v>185</v>
       </c>
       <c r="E65">
-        <v>375.8</v>
+        <v>368.4</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G65" s="7">
-        <v>141275611136</v>
+        <v>137159008256</v>
       </c>
       <c r="H65" s="6">
         <v>421.4</v>
@@ -5301,10 +5301,10 @@
       </c>
       <c r="J65" s="12">
         <f t="shared" si="1"/>
-        <v>0.66578014184397172</v>
+        <v>0.63297872340425521</v>
       </c>
       <c r="K65" s="11">
-        <v>1.9159127195316657E-3</v>
+        <v>1.9543973941368079E-3</v>
       </c>
       <c r="L65" s="13">
         <v>1200000000</v>
@@ -5319,13 +5319,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P65" s="12">
-        <v>5.9844913559188487E-2</v>
+        <v>6.1485895596350086E-2</v>
       </c>
       <c r="Q65" s="12">
         <v>0.20495303159692571</v>
       </c>
       <c r="R65" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.5">
@@ -5339,13 +5339,13 @@
         <v>321</v>
       </c>
       <c r="E66">
-        <v>8.9700000000000006</v>
+        <v>8.75</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G66" s="7">
-        <v>16212647936</v>
+        <v>15815012352</v>
       </c>
       <c r="H66" s="6">
         <v>9.0399999999999991</v>
@@ -5355,10 +5355,10 @@
       </c>
       <c r="J66" s="12">
         <f t="shared" ref="J66:J97" si="2">E66/I66-1</f>
-        <v>0.63387978142076506</v>
+        <v>0.59380692167577398</v>
       </c>
       <c r="K66" s="11">
-        <v>2.7870680044593085E-2</v>
+        <v>2.8571428571428571E-2</v>
       </c>
       <c r="L66" s="13">
         <v>2897428000</v>
@@ -5373,13 +5373,13 @@
         <v>1</v>
       </c>
       <c r="P66" s="12">
-        <v>0.13714300144961752</v>
+        <v>0.13977370380000756</v>
       </c>
       <c r="Q66" s="12">
         <v>0.11156568921912897</v>
       </c>
       <c r="R66" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.5">
@@ -5393,13 +5393,13 @@
         <v>174</v>
       </c>
       <c r="E67">
-        <v>12.6</v>
+        <v>12.08</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G67" s="7">
-        <v>3317731328</v>
+        <v>3180808960</v>
       </c>
       <c r="H67" s="6">
         <v>15.58</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="J67" s="12">
         <f t="shared" si="2"/>
-        <v>0.67776298268974711</v>
+        <v>0.60852197070572567</v>
       </c>
       <c r="K67" s="11">
         <v>0</v>
@@ -5427,13 +5427,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P67" s="12">
-        <v>0.55004017419353191</v>
+        <v>0.4797436452434547</v>
       </c>
       <c r="Q67" s="12">
         <v>-0.11631254679805218</v>
       </c>
       <c r="R67" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.5">
@@ -5447,13 +5447,13 @@
         <v>183</v>
       </c>
       <c r="E68">
-        <v>32.65</v>
+        <v>34.4</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G68" s="7">
-        <v>22583353344</v>
+        <v>23793793024</v>
       </c>
       <c r="H68" s="6">
         <v>39.200000000000003</v>
@@ -5463,10 +5463,10 @@
       </c>
       <c r="J68" s="12">
         <f t="shared" si="2"/>
-        <v>1.422106824925816</v>
+        <v>1.5519287833827891</v>
       </c>
       <c r="K68" s="11">
-        <v>1.4088820826952527E-2</v>
+        <v>1.3372093023255816E-2</v>
       </c>
       <c r="L68" s="13">
         <v>1323087000</v>
@@ -5481,13 +5481,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="12">
-        <v>5.2825844434398944E-2</v>
+        <v>5.0390556310605197E-2</v>
       </c>
       <c r="Q68" s="12">
         <v>0.222258562943417</v>
       </c>
       <c r="R68" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.5">
@@ -5501,13 +5501,13 @@
         <v>50</v>
       </c>
       <c r="E69">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7">
-        <v>5869471744</v>
+        <v>5926090752</v>
       </c>
       <c r="H69" s="6">
         <v>4.18</v>
@@ -5517,10 +5517,10 @@
       </c>
       <c r="J69" s="12">
         <f t="shared" si="2"/>
-        <v>0.78735632183908044</v>
+        <v>0.80459770114942541</v>
       </c>
       <c r="K69" s="11">
-        <v>5.1446945337620585E-2</v>
+        <v>5.0955414012738849E-2</v>
       </c>
       <c r="L69" s="13">
         <v>896597000</v>
@@ -5535,13 +5535,13 @@
         <v>1</v>
       </c>
       <c r="P69" s="12">
-        <v>0.12012540334483277</v>
+        <v>0.11922101977083757</v>
       </c>
       <c r="Q69" s="12">
         <v>0.12982345485897689</v>
       </c>
       <c r="R69" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.5">
@@ -5555,13 +5555,13 @@
         <v>167</v>
       </c>
       <c r="E70">
-        <v>23.8</v>
+        <v>24.05</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G70" s="7">
-        <v>27075354624</v>
+        <v>27359760384</v>
       </c>
       <c r="H70" s="6">
         <v>28.75</v>
@@ -5571,10 +5571,10 @@
       </c>
       <c r="J70" s="12">
         <f t="shared" si="2"/>
-        <v>0.21926229508196737</v>
+        <v>0.23206967213114771</v>
       </c>
       <c r="K70" s="11">
-        <v>5.8823529411764698E-2</v>
+        <v>5.8212058212058208E-2</v>
       </c>
       <c r="L70" s="13">
         <v>3446618000</v>
@@ -5589,13 +5589,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P70" s="12">
-        <v>0.14245911225562893</v>
+        <v>0.14090869317113167</v>
       </c>
       <c r="Q70" s="12">
         <v>0.10133893359397213</v>
       </c>
       <c r="R70" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.5">
@@ -5609,13 +5609,13 @@
         <v>104</v>
       </c>
       <c r="E71">
-        <v>6.47</v>
+        <v>6.17</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G71" s="7">
-        <v>5041436672</v>
+        <v>4807676416</v>
       </c>
       <c r="H71" s="6">
         <v>8.09</v>
@@ -5625,10 +5625,10 @@
       </c>
       <c r="J71" s="12">
         <f t="shared" si="2"/>
-        <v>0.60945273631840813</v>
+        <v>0.53482587064676634</v>
       </c>
       <c r="K71" s="11">
-        <v>2.6275115919629059E-2</v>
+        <v>2.755267423014587E-2</v>
       </c>
       <c r="L71" s="13">
         <v>437453000</v>
@@ -5643,13 +5643,13 @@
         <v>1</v>
       </c>
       <c r="P71" s="12">
-        <v>0.15895892428983235</v>
+        <v>0.17371465230684313</v>
       </c>
       <c r="Q71" s="12">
         <v>8.9074849645861431E-2</v>
       </c>
       <c r="R71" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.5">
@@ -5663,13 +5663,13 @@
         <v>155</v>
       </c>
       <c r="E72">
-        <v>57.95</v>
+        <v>56.9</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G72" s="7">
-        <v>159968657408</v>
+        <v>156110274560</v>
       </c>
       <c r="H72" s="6">
         <v>61.15</v>
@@ -5679,10 +5679,10 @@
       </c>
       <c r="J72" s="12">
         <f t="shared" si="2"/>
-        <v>0.50911458333333348</v>
+        <v>0.48177083333333326</v>
       </c>
       <c r="K72" s="11">
-        <v>3.1061259706643658E-2</v>
+        <v>3.163444639718805E-2</v>
       </c>
       <c r="L72" s="13">
         <v>8955723006</v>
@@ -5697,13 +5697,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P72" s="12">
-        <v>6.1365199557002544E-2</v>
+        <v>6.2922265538328678E-2</v>
       </c>
       <c r="Q72" s="12">
         <v>0.18855793075067021</v>
       </c>
       <c r="R72" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.5">
@@ -5717,13 +5717,13 @@
         <v>174</v>
       </c>
       <c r="E73">
-        <v>550.5</v>
+        <v>555</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="7">
-        <v>4993585250304</v>
+        <v>5034404741120</v>
       </c>
       <c r="H73" s="6">
         <v>560</v>
@@ -5733,10 +5733,10 @@
       </c>
       <c r="J73" s="12">
         <f t="shared" si="2"/>
-        <v>0.5773638968481376</v>
+        <v>0.59025787965616039</v>
       </c>
       <c r="K73" s="11">
-        <v>7.682107175295186E-3</v>
+        <v>7.6198198198198196E-3</v>
       </c>
       <c r="L73" s="13">
         <v>253932000000</v>
@@ -5751,13 +5751,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P73" s="12">
-        <v>5.1827206457859501E-2</v>
+        <v>5.1426184546115389E-2</v>
       </c>
       <c r="Q73" s="12">
         <v>0.19352168899747973</v>
       </c>
       <c r="R73" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.5">
@@ -5771,13 +5771,13 @@
         <v>69</v>
       </c>
       <c r="E74">
-        <v>6.61</v>
+        <v>6.42</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G74" s="7">
-        <v>10752552960</v>
+        <v>10443478016</v>
       </c>
       <c r="H74" s="6">
         <v>7.05</v>
@@ -5787,10 +5787,10 @@
       </c>
       <c r="J74" s="12">
         <f t="shared" si="2"/>
-        <v>0.54800936768149899</v>
+        <v>0.503512880562061</v>
       </c>
       <c r="K74" s="11">
-        <v>4.2360060514372168E-2</v>
+        <v>4.3613707165109039E-2</v>
       </c>
       <c r="L74" s="13">
         <v>4094312000</v>
@@ -5805,13 +5805,13 @@
         <v>1</v>
       </c>
       <c r="P74" s="12">
-        <v>0.13135870974556493</v>
+        <v>0.132674324159505</v>
       </c>
       <c r="Q74" s="12">
         <v>0.10878407220713927</v>
       </c>
       <c r="R74" s="14">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.5">
@@ -5825,13 +5825,13 @@
         <v>109</v>
       </c>
       <c r="E75">
-        <v>13.72</v>
+        <v>13.78</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="7">
-        <v>135346970624</v>
+        <v>135938867200</v>
       </c>
       <c r="H75" s="6">
         <v>14.32</v>
@@ -5841,10 +5841,10 @@
       </c>
       <c r="J75" s="12">
         <f t="shared" si="2"/>
-        <v>1.3533447684391082</v>
+        <v>1.3636363636363633</v>
       </c>
       <c r="K75" s="11">
-        <v>3.7900874635568516E-2</v>
+        <v>3.7735849056603779E-2</v>
       </c>
       <c r="L75" s="13">
         <v>8510100000</v>
@@ -5859,13 +5859,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="12">
-        <v>5.7286366363438257E-2</v>
+        <v>5.7059020658577105E-2</v>
       </c>
       <c r="Q75" s="12">
         <v>0.18453201842262756</v>
       </c>
       <c r="R75" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.5">
@@ -5879,13 +5879,13 @@
         <v>75</v>
       </c>
       <c r="E76">
-        <v>7.18</v>
+        <v>7.06</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G76" s="7">
-        <v>4862755328</v>
+        <v>4781484032</v>
       </c>
       <c r="H76" s="6">
         <v>10.06</v>
@@ -5895,10 +5895,10 @@
       </c>
       <c r="J76" s="12">
         <f t="shared" si="2"/>
-        <v>9.4512195121951192E-2</v>
+        <v>7.6219512195121908E-2</v>
       </c>
       <c r="K76" s="11">
-        <v>4.9721448467966577E-2</v>
+        <v>5.0566572237960343E-2</v>
       </c>
       <c r="L76" s="13">
         <v>618033000</v>
@@ -5913,13 +5913,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P76" s="12">
-        <v>0.1122810570821956</v>
+        <v>0.11385452597454558</v>
       </c>
       <c r="Q76" s="12">
         <v>0.12279555988606453</v>
       </c>
       <c r="R76" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.5">
@@ -5933,13 +5933,13 @@
         <v>155</v>
       </c>
       <c r="E77">
-        <v>25.15</v>
+        <v>24.95</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G77" s="7">
-        <v>23159226368</v>
+        <v>22975059968</v>
       </c>
       <c r="H77" s="6">
         <v>26.45</v>
@@ -5949,10 +5949,10 @@
       </c>
       <c r="J77" s="12">
         <f t="shared" si="2"/>
-        <v>1.5404040404040402</v>
+        <v>1.5202020202020199</v>
       </c>
       <c r="K77" s="11">
-        <v>3.1013916500994038E-3</v>
+        <v>3.1262525050100203E-3</v>
       </c>
       <c r="L77" s="13">
         <v>334940000</v>
@@ -5967,13 +5967,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P77" s="12">
-        <v>0.1266980855299184</v>
+        <v>0.1278560038199838</v>
       </c>
       <c r="Q77" s="12">
         <v>0.11071024253191752</v>
       </c>
       <c r="R77" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.5">
@@ -6027,7 +6027,7 @@
         <v>0.1499088374088374</v>
       </c>
       <c r="R78" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.5">
@@ -6041,13 +6041,13 @@
         <v>243</v>
       </c>
       <c r="E79">
-        <v>8.77</v>
+        <v>8.85</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G79" s="7">
-        <v>115703496704</v>
+        <v>116758945792</v>
       </c>
       <c r="H79" s="6">
         <v>11</v>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="J79" s="12">
         <f t="shared" si="2"/>
-        <v>0.28216374269005851</v>
+        <v>0.29385964912280693</v>
       </c>
       <c r="K79" s="11">
         <v>0</v>
@@ -6075,13 +6075,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P79" s="12">
-        <v>9.5892422849861741E-2</v>
+        <v>9.4841160589041754E-2</v>
       </c>
       <c r="Q79" s="12">
         <v>0.1154893948238957</v>
       </c>
       <c r="R79" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.5">
@@ -6095,26 +6095,26 @@
         <v>77</v>
       </c>
       <c r="E80">
-        <v>15.62</v>
+        <v>15.58</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7">
-        <v>65572917248</v>
+        <v>65404997632</v>
       </c>
       <c r="H80" s="6">
-        <v>15.62</v>
+        <v>15.7</v>
       </c>
       <c r="I80" s="6">
         <v>10.98</v>
       </c>
       <c r="J80" s="12">
         <f t="shared" si="2"/>
-        <v>0.42258652094717664</v>
+        <v>0.41894353369763193</v>
       </c>
       <c r="K80" s="11">
-        <v>5.6722151088348272E-2</v>
+        <v>5.6867779204107828E-2</v>
       </c>
       <c r="L80" s="13">
         <v>11996000000</v>
@@ -6129,13 +6129,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="12">
-        <v>0.13522574641477345</v>
+        <v>0.13548219871499551</v>
       </c>
       <c r="Q80" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R80" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.5">
@@ -6149,26 +6149,26 @@
         <v>77</v>
       </c>
       <c r="E81">
-        <v>15.62</v>
+        <v>15.58</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G81" s="7">
-        <v>65572917248</v>
+        <v>65404997632</v>
       </c>
       <c r="H81" s="6">
-        <v>15.62</v>
+        <v>15.7</v>
       </c>
       <c r="I81" s="6">
         <v>10.98</v>
       </c>
       <c r="J81" s="12">
         <f t="shared" si="2"/>
-        <v>0.42258652094717664</v>
+        <v>0.41894353369763193</v>
       </c>
       <c r="K81" s="11">
-        <v>5.6722151088348272E-2</v>
+        <v>5.6867779204107828E-2</v>
       </c>
       <c r="L81" s="13">
         <v>11996000000</v>
@@ -6183,13 +6183,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="12">
-        <v>0.13522574641477345</v>
+        <v>0.13548219871499551</v>
       </c>
       <c r="Q81" s="12">
         <v>8.6741482038526066E-2</v>
       </c>
       <c r="R81" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.5">
@@ -6203,13 +6203,13 @@
         <v>50</v>
       </c>
       <c r="E82">
-        <v>19.52</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G82" s="7">
-        <v>76687253504</v>
+        <v>75381800960</v>
       </c>
       <c r="H82" s="6">
         <v>119.9</v>
@@ -6219,10 +6219,10 @@
       </c>
       <c r="J82" s="12">
         <f t="shared" si="2"/>
-        <v>1.5992010652463384</v>
+        <v>1.6098535286284954</v>
       </c>
       <c r="K82" s="11">
-        <v>2.2438524590163936E-2</v>
+        <v>2.2346938775510201E-2</v>
       </c>
       <c r="L82" s="13">
         <v>3967214824.1399999</v>
@@ -6237,13 +6237,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P82" s="12">
-        <v>8.2800486340514443E-2</v>
+        <v>8.4967373524531167E-2</v>
       </c>
       <c r="Q82" s="12">
         <v>9.6670468672106824E-2</v>
       </c>
       <c r="R82" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.5">
@@ -6257,13 +6257,13 @@
         <v>185</v>
       </c>
       <c r="E83">
-        <v>7.54</v>
+        <v>7.43</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="7">
-        <v>4326029824</v>
+        <v>4262917888</v>
       </c>
       <c r="H83" s="6">
         <v>9.24</v>
@@ -6273,10 +6273,10 @@
       </c>
       <c r="J83" s="12">
         <f t="shared" si="2"/>
-        <v>0.11209439528023601</v>
+        <v>9.587020648967548E-2</v>
       </c>
       <c r="K83" s="11">
-        <v>5.3050397877984087E-2</v>
+        <v>5.383580080753702E-2</v>
       </c>
       <c r="L83" s="13">
         <v>371538000</v>
@@ -6291,13 +6291,13 @@
         <v>1</v>
       </c>
       <c r="P83" s="12">
-        <v>6.8717985290189645E-2</v>
+        <v>6.952959716956747E-2</v>
       </c>
       <c r="Q83" s="12">
         <v>0.12232565520665489</v>
       </c>
       <c r="R83" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.5">
@@ -6351,7 +6351,7 @@
         <v>3.9146558666946343E-2</v>
       </c>
       <c r="R84" s="14">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.5">
@@ -6365,13 +6365,13 @@
         <v>104</v>
       </c>
       <c r="E85">
-        <v>34.4</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7">
-        <v>77510082560</v>
+        <v>78411350016</v>
       </c>
       <c r="H85" s="6">
         <v>61.55</v>
@@ -6381,10 +6381,10 @@
       </c>
       <c r="J85" s="12">
         <f t="shared" si="2"/>
-        <v>0.38430583501006033</v>
+        <v>0.40040241448692138</v>
       </c>
       <c r="K85" s="11">
-        <v>1.6511627906976745E-2</v>
+        <v>1.6321839080459769E-2</v>
       </c>
       <c r="L85" s="13">
         <v>5261270000</v>
@@ -6399,13 +6399,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P85" s="12">
-        <v>6.7489455924387765E-2</v>
+        <v>6.6766958228337253E-2</v>
       </c>
       <c r="Q85" s="12">
         <v>0.12176329850933591</v>
       </c>
       <c r="R85" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.5">
@@ -6419,13 +6419,13 @@
         <v>308</v>
       </c>
       <c r="E86">
-        <v>54.5</v>
+        <v>56.4</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="7">
-        <v>1091754917888</v>
+        <v>1129607462912</v>
       </c>
       <c r="H86" s="6">
         <v>59.8</v>
@@ -6435,10 +6435,10 @@
       </c>
       <c r="J86" s="12">
         <f t="shared" si="2"/>
-        <v>0.66921898928024515</v>
+        <v>0.72741194486983152</v>
       </c>
       <c r="K86" s="11">
-        <v>4.6788990825688069E-2</v>
+        <v>4.5212765957446804E-2</v>
       </c>
       <c r="L86" s="13">
         <v>189900000000</v>
@@ -6453,13 +6453,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P86" s="12">
-        <v>0.1294396819895004</v>
+        <v>0.12638745125012527</v>
       </c>
       <c r="Q86" s="12">
         <v>8.2016774784268678E-2</v>
       </c>
       <c r="R86" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.5">
@@ -6473,13 +6473,13 @@
         <v>66</v>
       </c>
       <c r="E87">
-        <v>61.3</v>
+        <v>58.05</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G87" s="7">
-        <v>152916525056</v>
+        <v>149299953664</v>
       </c>
       <c r="H87" s="6">
         <v>82.25</v>
@@ -6489,10 +6489,10 @@
       </c>
       <c r="J87" s="12">
         <f t="shared" si="2"/>
-        <v>0.61955085865257575</v>
+        <v>0.53368560105680296</v>
       </c>
       <c r="K87" s="11">
-        <v>1.7128874388254486E-2</v>
+        <v>1.8087855297157625E-2</v>
       </c>
       <c r="L87" s="13">
         <v>6350637223.7200003</v>
@@ -6507,13 +6507,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P87" s="12">
-        <v>5.5966487009343341E-2</v>
+        <v>5.7687423226320769E-2</v>
       </c>
       <c r="Q87" s="12">
         <v>0.10968970241604512</v>
       </c>
       <c r="R87" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.5">
@@ -6527,13 +6527,13 @@
         <v>164</v>
       </c>
       <c r="E88">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G88" s="7">
-        <v>48257622016</v>
+        <v>47769288704</v>
       </c>
       <c r="H88" s="6">
         <v>10.72</v>
@@ -6543,10 +6543,10 @@
       </c>
       <c r="J88" s="12">
         <f t="shared" si="2"/>
-        <v>0.34000000000000008</v>
+        <v>0.32799999999999985</v>
       </c>
       <c r="K88" s="11">
-        <v>6.4179104477611937E-2</v>
+        <v>6.4759036144578314E-2</v>
       </c>
       <c r="L88" s="13">
         <v>6749146000</v>
@@ -6561,13 +6561,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P88" s="12">
-        <v>8.9188268484422781E-2</v>
+        <v>8.9730256920477605E-2</v>
       </c>
       <c r="Q88" s="12">
         <v>9.5261833390841127E-2</v>
       </c>
       <c r="R88" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.5">
@@ -6581,13 +6581,13 @@
         <v>181</v>
       </c>
       <c r="E89">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G89" s="7">
-        <v>24928911360</v>
+        <v>24457666560</v>
       </c>
       <c r="H89" s="6">
         <v>11.68</v>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J89" s="12">
         <f t="shared" si="2"/>
-        <v>1.0385356454720616</v>
+        <v>1</v>
       </c>
       <c r="K89" s="11">
         <v>0</v>
@@ -6615,13 +6615,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P89" s="12">
-        <v>0.11617243868152641</v>
+        <v>0.11661530118082501</v>
       </c>
       <c r="Q89" s="12">
         <v>6.4862080854845933E-2</v>
       </c>
       <c r="R89" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.5">
@@ -6635,13 +6635,13 @@
         <v>93</v>
       </c>
       <c r="E90">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="7">
-        <v>137706471424</v>
+        <v>137473523712</v>
       </c>
       <c r="H90" s="6">
         <v>26.6</v>
@@ -6651,10 +6651,10 @@
       </c>
       <c r="J90" s="12">
         <f t="shared" si="2"/>
-        <v>0.47315855181023725</v>
+        <v>0.4918851435705367</v>
       </c>
       <c r="K90" s="11">
-        <v>3.0084745762711862E-2</v>
+        <v>2.9707112970711297E-2</v>
       </c>
       <c r="L90" s="13">
         <v>10795274825</v>
@@ -6669,13 +6669,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P90" s="12">
-        <v>0.12237834591778861</v>
+        <v>0.12268158456500781</v>
       </c>
       <c r="Q90" s="12">
         <v>5.0146340085309396E-2</v>
       </c>
       <c r="R90" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.5">
@@ -6689,13 +6689,13 @@
         <v>310</v>
       </c>
       <c r="E91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G91" s="7">
-        <v>66086821888</v>
+        <v>65634476032</v>
       </c>
       <c r="H91" s="6">
         <v>2.08</v>
@@ -6705,10 +6705,10 @@
       </c>
       <c r="J91" s="12">
         <f t="shared" si="2"/>
-        <v>0.52542372881355948</v>
+        <v>0.50847457627118664</v>
       </c>
       <c r="K91" s="11">
-        <v>3.111111111111111E-2</v>
+        <v>3.1460674157303373E-2</v>
       </c>
       <c r="L91" s="13">
         <v>12616717000</v>
@@ -6723,13 +6723,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P91" s="12">
-        <v>0.12243318997716839</v>
+        <v>0.12293830056678023</v>
       </c>
       <c r="Q91" s="12">
         <v>5.4568577322633927E-2</v>
       </c>
       <c r="R91" s="14">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.5">
@@ -6783,7 +6783,7 @@
         <v>6.5089877530620205E-2</v>
       </c>
       <c r="R92" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.5">
@@ -6797,13 +6797,13 @@
         <v>98</v>
       </c>
       <c r="E93">
-        <v>12.3</v>
+        <v>12.38</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7">
-        <v>93176930304</v>
+        <v>93782958080</v>
       </c>
       <c r="H93" s="6">
         <v>12.76</v>
@@ -6813,10 +6813,10 @@
       </c>
       <c r="J93" s="12">
         <f t="shared" si="2"/>
-        <v>0.31550802139037448</v>
+        <v>0.32406417112299479</v>
       </c>
       <c r="K93" s="11">
-        <v>6.4065040650406496E-2</v>
+        <v>6.3651050080775443E-2</v>
       </c>
       <c r="L93" s="13">
         <v>8154000000</v>
@@ -6831,13 +6831,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="12">
-        <v>6.0630877754782327E-2</v>
+        <v>6.0358885279990455E-2</v>
       </c>
       <c r="Q93" s="12">
         <v>0.10245263104990703</v>
       </c>
       <c r="R93" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.5">
@@ -6851,13 +6851,13 @@
         <v>98</v>
       </c>
       <c r="E94">
-        <v>5.72</v>
+        <v>6</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G94" s="7">
-        <v>707981541376</v>
+        <v>720960028672</v>
       </c>
       <c r="H94" s="6">
         <v>6.98</v>
@@ -6867,10 +6867,10 @@
       </c>
       <c r="J94" s="12">
         <f t="shared" si="2"/>
-        <v>0.40196078431372539</v>
+        <v>0.47058823529411753</v>
       </c>
       <c r="K94" s="11">
-        <v>4.5454545454545456E-2</v>
+        <v>4.3333333333333335E-2</v>
       </c>
       <c r="L94" s="13">
         <v>44563000000</v>
@@ -6885,13 +6885,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P94" s="12">
-        <v>6.9498647503900349E-2</v>
+        <v>6.8206454653877244E-2</v>
       </c>
       <c r="Q94" s="12">
         <v>9.605709580489824E-2</v>
       </c>
       <c r="R94" s="14">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.5">
@@ -6905,13 +6905,13 @@
         <v>104</v>
       </c>
       <c r="E95">
-        <v>10.199999999999999</v>
+        <v>10.64</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="7">
-        <v>31823998976</v>
+        <v>33196802048</v>
       </c>
       <c r="H95" s="6">
         <v>11.34</v>
@@ -6921,10 +6921,10 @@
       </c>
       <c r="J95" s="12">
         <f t="shared" si="2"/>
-        <v>0.8214285714285714</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="K95" s="11">
-        <v>3.1372549019607843E-2</v>
+        <v>3.007518796992481E-2</v>
       </c>
       <c r="L95" s="13">
         <v>1990539000</v>
@@ -6939,13 +6939,13 @@
         <v>1</v>
       </c>
       <c r="P95" s="12">
-        <v>5.75677075053697E-2</v>
+        <v>5.5369410412929997E-2</v>
       </c>
       <c r="Q95" s="12">
         <v>0.10689920561026972</v>
       </c>
       <c r="R95" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.5">
@@ -6959,13 +6959,13 @@
         <v>98</v>
       </c>
       <c r="E96">
-        <v>9.4499999999999993</v>
+        <v>9.61</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7">
-        <v>289151090688</v>
+        <v>294046760960</v>
       </c>
       <c r="H96" s="6">
         <v>11.56</v>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="J96" s="12">
         <f t="shared" si="2"/>
-        <v>0.60714285714285698</v>
+        <v>0.63435374149659851</v>
       </c>
       <c r="K96" s="11">
         <v>0</v>
@@ -6993,13 +6993,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P96" s="12">
-        <v>9.5747028346081578E-2</v>
+        <v>9.421569643849026E-2</v>
       </c>
       <c r="Q96" s="12">
         <v>7.4329031387590908E-2</v>
       </c>
       <c r="R96" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.5">
@@ -7013,13 +7013,13 @@
         <v>151</v>
       </c>
       <c r="E97">
-        <v>10.78</v>
+        <v>10.68</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7">
-        <v>27319429120</v>
+        <v>27066003456</v>
       </c>
       <c r="H97" s="6">
         <v>13.78</v>
@@ -7029,10 +7029,10 @@
       </c>
       <c r="J97" s="12">
         <f t="shared" si="2"/>
-        <v>0.98161764705882337</v>
+        <v>0.96323529411764697</v>
       </c>
       <c r="K97" s="11">
-        <v>2.7829313543599257E-2</v>
+        <v>2.8089887640449437E-2</v>
       </c>
       <c r="L97" s="13">
         <v>9652467000</v>
@@ -7047,13 +7047,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P97" s="12">
-        <v>0.10224543971218297</v>
+        <v>0.10250299389868719</v>
       </c>
       <c r="Q97" s="12">
         <v>5.5629198178196171E-2</v>
       </c>
       <c r="R97" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.5">
@@ -7107,7 +7107,7 @@
         <v>3.1227495254580313E-2</v>
       </c>
       <c r="R98" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.5">
@@ -7121,13 +7121,13 @@
         <v>310</v>
       </c>
       <c r="E99">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="7">
-        <v>116254294016</v>
+        <v>115035119616</v>
       </c>
       <c r="H99" s="6">
         <v>7.03</v>
@@ -7137,10 +7137,10 @@
       </c>
       <c r="J99" s="12">
         <f t="shared" si="3"/>
-        <v>0.36966824644549767</v>
+        <v>0.35071090047393372</v>
       </c>
       <c r="K99" s="11">
-        <v>5.1903114186851208E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="L99" s="13">
         <v>42109966000</v>
@@ -7155,13 +7155,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P99" s="12">
-        <v>9.9847968671539111E-2</v>
+        <v>0.10011887051991936</v>
       </c>
       <c r="Q99" s="12">
         <v>5.643429507724386E-2</v>
       </c>
       <c r="R99" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.5">
@@ -7175,26 +7175,26 @@
         <v>171</v>
       </c>
       <c r="E100">
-        <v>53.45</v>
+        <v>53.3</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="7">
-        <v>204715638784</v>
+        <v>204141133824</v>
       </c>
       <c r="H100" s="6">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="I100" s="6">
         <v>37.450000000000003</v>
       </c>
       <c r="J100" s="12">
         <f t="shared" si="3"/>
-        <v>0.42723631508678239</v>
+        <v>0.42323097463284354</v>
       </c>
       <c r="K100" s="11">
-        <v>4.1197380729653878E-2</v>
+        <v>4.1313320825515948E-2</v>
       </c>
       <c r="L100" s="13">
         <v>41737000000</v>
@@ -7209,13 +7209,13 @@
         <v>1</v>
       </c>
       <c r="P100" s="12">
-        <v>0.10226056719724666</v>
+        <v>0.10240471256595017</v>
       </c>
       <c r="Q100" s="12">
         <v>5.2504192208844336E-2</v>
       </c>
       <c r="R100" s="14">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.5">
@@ -7229,13 +7229,13 @@
         <v>151</v>
       </c>
       <c r="E101">
-        <v>36.549999999999997</v>
+        <v>36.9</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G101" s="7">
-        <v>127916957696</v>
+        <v>129141891072</v>
       </c>
       <c r="H101" s="6">
         <v>37.25</v>
@@ -7245,10 +7245,10 @@
       </c>
       <c r="J101" s="12">
         <f t="shared" si="3"/>
-        <v>0.30071174377224175</v>
+        <v>0.31316725978647675</v>
       </c>
       <c r="K101" s="11">
-        <v>4.7606019151846792E-2</v>
+        <v>4.715447154471545E-2</v>
       </c>
       <c r="L101" s="13">
         <v>16863000000</v>
@@ -7263,13 +7263,13 @@
         <v>1</v>
       </c>
       <c r="P101" s="12">
-        <v>0.11281111033155748</v>
+        <v>0.11189417861656274</v>
       </c>
       <c r="Q101" s="12">
         <v>3.7613758029978586E-2</v>
       </c>
       <c r="R101" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.5">
@@ -7283,13 +7283,13 @@
         <v>98</v>
       </c>
       <c r="E102">
-        <v>5.64</v>
+        <v>5.61</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="7">
-        <v>43659579392</v>
+        <v>43427348480</v>
       </c>
       <c r="H102" s="6">
         <v>5.83</v>
@@ -7299,10 +7299,10 @@
       </c>
       <c r="J102" s="12">
         <f t="shared" si="3"/>
-        <v>0.42424242424242409</v>
+        <v>0.41666666666666674</v>
       </c>
       <c r="K102" s="11">
-        <v>6.7907801418439717E-2</v>
+        <v>6.8270944741532974E-2</v>
       </c>
       <c r="L102" s="13">
         <v>5474000000</v>
@@ -7317,13 +7317,13 @@
         <v>1</v>
       </c>
       <c r="P102" s="12">
-        <v>5.743208330861159E-2</v>
+        <v>5.7572359457132689E-2</v>
       </c>
       <c r="Q102" s="12">
         <v>9.2144023431582137E-2</v>
       </c>
       <c r="R102" s="14">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.5">
@@ -7337,13 +7337,13 @@
         <v>93</v>
       </c>
       <c r="E103">
-        <v>2.08</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="7">
-        <v>11362062336</v>
+        <v>11088935936</v>
       </c>
       <c r="H103" s="6">
         <v>2.25</v>
@@ -7353,10 +7353,10 @@
       </c>
       <c r="J103" s="12">
         <f t="shared" si="3"/>
-        <v>1.5679012345679011</v>
+        <v>1.5061728395061724</v>
       </c>
       <c r="K103" s="11">
-        <v>1.6346153846153847E-2</v>
+        <v>1.6748768472906406E-2</v>
       </c>
       <c r="L103" s="13">
         <v>1384865000</v>
@@ -7371,13 +7371,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P103" s="12">
-        <v>6.5829774282170239E-2</v>
+        <v>6.6639591076670057E-2</v>
       </c>
       <c r="Q103" s="12">
         <v>5.8120488088461209E-2</v>
       </c>
       <c r="R103" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.5">
@@ -7391,26 +7391,26 @@
         <v>171</v>
       </c>
       <c r="E104">
-        <v>28.1</v>
+        <v>29</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="7">
-        <v>31143512064</v>
+        <v>32140990464</v>
       </c>
       <c r="H104" s="6">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="I104" s="6">
         <v>14.52</v>
       </c>
       <c r="J104" s="12">
         <f t="shared" si="3"/>
-        <v>0.93526170798898089</v>
+        <v>0.99724517906336096</v>
       </c>
       <c r="K104" s="11">
-        <v>3.345195729537366E-2</v>
+        <v>3.2413793103448274E-2</v>
       </c>
       <c r="L104" s="13">
         <v>3838344000</v>
@@ -7425,13 +7425,13 @@
         <v>1</v>
       </c>
       <c r="P104" s="12">
-        <v>7.8395199943308624E-2</v>
+        <v>7.6829964370762768E-2</v>
       </c>
       <c r="Q104" s="12">
         <v>4.7084186647510511E-2</v>
       </c>
       <c r="R104" s="14">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.5">
@@ -7445,13 +7445,13 @@
         <v>98</v>
       </c>
       <c r="E105">
-        <v>11.74</v>
+        <v>11.38</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="7">
-        <v>206633402368</v>
+        <v>200297119744</v>
       </c>
       <c r="H105" s="6">
         <v>12.46</v>
@@ -7461,10 +7461,10 @@
       </c>
       <c r="J105" s="12">
         <f t="shared" si="3"/>
-        <v>0.2760869565217392</v>
+        <v>0.23695652173913051</v>
       </c>
       <c r="K105" s="11">
-        <v>3.5519591141396932E-2</v>
+        <v>3.6643233743409484E-2</v>
       </c>
       <c r="L105" s="13">
         <v>16758000000</v>
@@ -7479,13 +7479,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P105" s="12">
-        <v>5.9141179317688433E-2</v>
+        <v>6.0405492341977687E-2</v>
       </c>
       <c r="Q105" s="12">
         <v>6.2161059386475759E-2</v>
       </c>
       <c r="R105" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.5">
@@ -7499,13 +7499,13 @@
         <v>87</v>
       </c>
       <c r="E106">
-        <v>6.77</v>
+        <v>6.83</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G106" s="7">
-        <v>7064765440</v>
+        <v>7127377920</v>
       </c>
       <c r="H106" s="6">
         <v>7</v>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="J106" s="12">
         <f t="shared" si="3"/>
-        <v>0.68407960199004991</v>
+        <v>0.69900497512437831</v>
       </c>
       <c r="K106" s="11">
         <v>0</v>
@@ -7533,13 +7533,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="12">
-        <v>5.0803003152450829E-2</v>
+        <v>5.02757894769921E-2</v>
       </c>
       <c r="Q106" s="12">
         <v>8.3790449156695201E-2</v>
       </c>
       <c r="R106" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.5">
@@ -7553,13 +7553,13 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="7">
-        <v>12111899648</v>
+        <v>11639450624</v>
       </c>
       <c r="H107" s="6">
         <v>3.04</v>
@@ -7569,10 +7569,10 @@
       </c>
       <c r="J107" s="12">
         <f t="shared" si="3"/>
-        <v>0.46113989637305686</v>
+        <v>0.40414507772020736</v>
       </c>
       <c r="K107" s="11">
-        <v>3.7943262411347517E-2</v>
+        <v>3.9483394833948339E-2</v>
       </c>
       <c r="L107" s="13">
         <v>1938532000</v>
@@ -7587,13 +7587,13 @@
         <v>1</v>
       </c>
       <c r="P107" s="12">
-        <v>5.9390520887332217E-2</v>
+        <v>6.0262785630978165E-2</v>
       </c>
       <c r="Q107" s="12">
         <v>3.8781191586606881E-2</v>
       </c>
       <c r="R107" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.5">
@@ -7607,13 +7607,13 @@
         <v>87</v>
       </c>
       <c r="E108">
-        <v>9.48</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G108" s="7">
-        <v>10015335424</v>
+        <v>9814606848</v>
       </c>
       <c r="H108" s="6">
         <v>12.88</v>
@@ -7623,10 +7623,10 @@
       </c>
       <c r="J108" s="12">
         <f t="shared" si="3"/>
-        <v>1.1208053691275168</v>
+        <v>1.0782997762863533</v>
       </c>
       <c r="K108" s="11">
-        <v>1.4978902953586495E-2</v>
+        <v>1.5285252960172229E-2</v>
       </c>
       <c r="L108" s="13">
         <v>350106000</v>
@@ -7641,13 +7641,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="12">
-        <v>3.7603317032345991E-2</v>
+        <v>3.8431883738317095E-2</v>
       </c>
       <c r="Q108" s="12">
         <v>0.10455432132537129</v>
       </c>
       <c r="R108" s="14">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.5">
@@ -7661,13 +7661,13 @@
         <v>85</v>
       </c>
       <c r="E109">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="7">
-        <v>10519596032</v>
+        <v>10076666880</v>
       </c>
       <c r="H109" s="6">
         <v>2.99</v>
@@ -7677,10 +7677,10 @@
       </c>
       <c r="J109" s="12">
         <f t="shared" si="3"/>
-        <v>1.0879120879120876</v>
+        <v>1</v>
       </c>
       <c r="K109" s="11">
-        <v>7.8947368421052634E-3</v>
+        <v>8.241758241758242E-3</v>
       </c>
       <c r="L109" s="13">
         <v>429393000</v>
@@ -7695,13 +7695,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="12">
-        <v>4.036862198589633E-2</v>
+        <v>4.2122660070159718E-2</v>
       </c>
       <c r="Q109" s="12">
         <v>2.3421020321148112E-2</v>
       </c>
       <c r="R109" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.5">
@@ -7715,13 +7715,13 @@
         <v>196</v>
       </c>
       <c r="E110">
-        <v>52.75</v>
+        <v>53.35</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G110" s="7">
-        <v>520297512960</v>
+        <v>522018521088</v>
       </c>
       <c r="H110" s="6">
         <v>59.7</v>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="J110" s="12">
         <f t="shared" si="3"/>
-        <v>2.4612860892388451</v>
+        <v>2.5006561679790025</v>
       </c>
       <c r="K110" s="11">
         <v>0</v>
@@ -7749,13 +7749,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P110" s="12">
-        <v>1.3503780086771638E-2</v>
+        <v>1.3462446925771121E-2</v>
       </c>
       <c r="Q110" s="12">
         <v>3.0575487595734537E-2</v>
       </c>
       <c r="R110" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.5">
@@ -7769,26 +7769,26 @@
         <v>153</v>
       </c>
       <c r="E111">
-        <v>15.34</v>
+        <v>15.9</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="7">
-        <v>15754333184</v>
+        <v>16329458688</v>
       </c>
       <c r="H111" s="6">
-        <v>15.48</v>
+        <v>15.98</v>
       </c>
       <c r="I111" s="6">
         <v>10.36</v>
       </c>
       <c r="J111" s="12">
         <f t="shared" si="3"/>
-        <v>0.48069498069498073</v>
+        <v>0.5347490347490349</v>
       </c>
       <c r="K111" s="11">
-        <v>7.0404172099087364E-2</v>
+        <v>6.7924528301886791E-2</v>
       </c>
       <c r="L111" s="13">
         <v>984000000</v>
@@ -7803,13 +7803,13 @@
         <v>1</v>
       </c>
       <c r="P111" s="12">
-        <v>2.4174330422068905E-2</v>
+        <v>2.3837521888000198E-2</v>
       </c>
       <c r="Q111" s="12">
         <v>9.6523581574197593E-3</v>
       </c>
       <c r="R111" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.5">
@@ -7863,7 +7863,7 @@
         <v>-4.9151971480384084E-3</v>
       </c>
       <c r="R112" s="14">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.5">
@@ -7877,13 +7877,13 @@
         <v>377</v>
       </c>
       <c r="E113">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G113" s="7">
-        <v>5042210816</v>
+        <v>5020845568</v>
       </c>
       <c r="H113" s="6">
         <v>2.62</v>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="J113" s="12">
         <f t="shared" si="3"/>
-        <v>1.3838383838383836</v>
+        <v>1.3737373737373737</v>
       </c>
       <c r="K113" s="11">
         <v>0</v>
@@ -7911,13 +7911,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P113" s="12">
-        <v>11.617418292408182</v>
+        <v>8.818660196726178</v>
       </c>
       <c r="Q113" s="12">
         <v>-9.3085164890011229E-2</v>
       </c>
       <c r="R113" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.5">
@@ -7931,13 +7931,13 @@
         <v>229</v>
       </c>
       <c r="E114">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G114" s="7">
-        <v>379563540480</v>
+        <v>384849936384</v>
       </c>
       <c r="H114" s="6">
         <v>37.950000000000003</v>
@@ -7947,10 +7947,10 @@
       </c>
       <c r="J114" s="12">
         <f t="shared" si="3"/>
-        <v>0.66976744186046511</v>
+        <v>0.69302325581395352</v>
       </c>
       <c r="K114" s="11">
-        <v>5.540389972144847E-2</v>
+        <v>5.4642857142857146E-2</v>
       </c>
       <c r="M114" s="13">
         <v>415994000000</v>
@@ -7973,13 +7973,13 @@
         <v>229</v>
       </c>
       <c r="E115">
-        <v>5.67</v>
+        <v>5.66</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G115" s="7">
-        <v>728492933120</v>
+        <v>727213735936</v>
       </c>
       <c r="H115" s="6">
         <v>5.95</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="J115" s="12">
         <f t="shared" si="3"/>
-        <v>0.45758354755784048</v>
+        <v>0.45501285347043696</v>
       </c>
       <c r="K115" s="11">
         <v>0</v>
@@ -8015,13 +8015,13 @@
         <v>229</v>
       </c>
       <c r="E116">
-        <v>7.5</v>
+        <v>7.35</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G116" s="7">
-        <v>475682996224</v>
+        <v>467426902016</v>
       </c>
       <c r="H116" s="6">
         <v>8.1199999999999992</v>
@@ -8031,10 +8031,10 @@
       </c>
       <c r="J116" s="12">
         <f t="shared" si="3"/>
-        <v>0.76056338028169024</v>
+        <v>0.72535211267605626</v>
       </c>
       <c r="K116" s="11">
-        <v>4.7333333333333331E-2</v>
+        <v>4.8299319727891157E-2</v>
       </c>
       <c r="M116" s="13">
         <v>2066897000000</v>
@@ -8057,13 +8057,13 @@
         <v>231</v>
       </c>
       <c r="E117">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G117" s="7">
-        <v>707272835072</v>
+        <v>699403862016</v>
       </c>
       <c r="H117" s="6">
         <v>7.62</v>
@@ -8073,10 +8073,10 @@
       </c>
       <c r="J117" s="12">
         <f t="shared" si="3"/>
-        <v>0.42913385826771644</v>
+        <v>0.41929133858267709</v>
       </c>
       <c r="K117" s="11">
-        <v>5.2203856749311293E-2</v>
+        <v>5.256588072122053E-2</v>
       </c>
       <c r="M117" s="13">
         <v>2314289000000</v>
@@ -8099,13 +8099,13 @@
         <v>231</v>
       </c>
       <c r="E118">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="7">
-        <v>2744281989120</v>
+        <v>2724331520000</v>
       </c>
       <c r="H118" s="6">
         <v>6.48</v>
@@ -8115,10 +8115,10 @@
       </c>
       <c r="J118" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.49507389162561588</v>
       </c>
       <c r="K118" s="11">
-        <v>5.057471264367816E-2</v>
+        <v>5.074135090609555E-2</v>
       </c>
       <c r="M118" s="13">
         <v>6434377000000</v>
@@ -8141,13 +8141,13 @@
         <v>231</v>
       </c>
       <c r="E119">
-        <v>8.3000000000000007</v>
+        <v>8.19</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G119" s="7">
-        <v>2212780048384</v>
+        <v>2182872432640</v>
       </c>
       <c r="H119" s="6">
         <v>8.56</v>
@@ -8157,10 +8157,10 @@
       </c>
       <c r="J119" s="12">
         <f t="shared" si="3"/>
-        <v>0.58699808795411101</v>
+        <v>0.56596558317399603</v>
       </c>
       <c r="K119" s="11">
-        <v>4.8554216867469878E-2</v>
+        <v>4.9206349206349212E-2</v>
       </c>
       <c r="M119" s="13">
         <v>6128626000000</v>
@@ -8183,26 +8183,26 @@
         <v>151</v>
       </c>
       <c r="E120">
-        <v>8.94</v>
+        <v>9.25</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G120" s="7">
-        <v>81801895936</v>
+        <v>84638433280</v>
       </c>
       <c r="H120" s="6">
-        <v>9.08</v>
+        <v>9.26</v>
       </c>
       <c r="I120" s="6">
         <v>7.31</v>
       </c>
       <c r="J120" s="12">
         <f t="shared" si="3"/>
-        <v>0.22298221614227076</v>
+        <v>0.26538987688098503</v>
       </c>
       <c r="K120" s="11">
-        <v>6.4876957494407153E-2</v>
+        <v>6.2702702702702701E-2</v>
       </c>
       <c r="L120" s="13">
         <v>4813000000</v>
@@ -8217,13 +8217,13 @@
         <v>1</v>
       </c>
       <c r="P120" s="12">
-        <v>5.8362812682257618E-2</v>
+        <v>5.6422113564899644E-2</v>
       </c>
       <c r="Q120" s="12">
         <v>2.8607941036614362E-2</v>
       </c>
       <c r="R120" s="14">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="2:18" x14ac:dyDescent="0.5">
@@ -8237,13 +8237,13 @@
         <v>85</v>
       </c>
       <c r="E121">
-        <v>17.04</v>
+        <v>17</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G121" s="7">
-        <v>43881922560</v>
+        <v>43778908160</v>
       </c>
       <c r="H121" s="6">
         <v>21</v>
@@ -8253,10 +8253,10 @@
       </c>
       <c r="J121" s="12">
         <f t="shared" si="3"/>
-        <v>0.3566878980891719</v>
+        <v>0.35350318471337583</v>
       </c>
       <c r="K121" s="11">
-        <v>3.4330985915492961E-2</v>
+        <v>3.441176470588235E-2</v>
       </c>
       <c r="L121" s="13">
         <v>4264779000</v>
@@ -8271,13 +8271,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P121" s="12">
-        <v>0.12009733705228849</v>
+        <v>0.12042431979683793</v>
       </c>
       <c r="Q121" s="12">
         <v>0.16337840218675606</v>
       </c>
       <c r="R121" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122" spans="2:18" x14ac:dyDescent="0.5">
@@ -8291,26 +8291,26 @@
         <v>399</v>
       </c>
       <c r="E122">
-        <v>43.65</v>
+        <v>44.5</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G122" s="7">
-        <v>112721764352</v>
+        <v>114916802560</v>
       </c>
       <c r="H122" s="6">
-        <v>44.1</v>
+        <v>44.8</v>
       </c>
       <c r="I122" s="6">
         <v>31.1</v>
       </c>
       <c r="J122" s="12">
         <f t="shared" si="3"/>
-        <v>0.40353697749196127</v>
+        <v>0.43086816720257226</v>
       </c>
       <c r="K122" s="11">
-        <v>6.2382588774341351E-2</v>
+        <v>6.1191011235955051E-2</v>
       </c>
       <c r="L122" s="13">
         <v>-6742000000</v>
@@ -8325,13 +8325,13 @@
         <v>1</v>
       </c>
       <c r="P122" s="12">
-        <v>-4.148239846452733E-2</v>
+        <v>-4.0929615237449958E-2</v>
       </c>
       <c r="Q122" s="12">
         <v>-3.1158435700487111E-2</v>
       </c>
       <c r="R122" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A79D65-6EBB-4E3D-ABB4-873584A093D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E8947E-6BEC-4455-81EE-842B869B9136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="401">
   <si>
     <t>Ticker</t>
   </si>
@@ -1299,6 +1299,9 @@
   </si>
   <si>
     <t>REIT - Retail</t>
+  </si>
+  <si>
+    <t>1810.HK</t>
   </si>
 </sst>
 </file>
@@ -1796,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9EDF16-08C4-B24B-A5E4-CFD78B458569}">
-  <dimension ref="B1:V122"/>
+  <dimension ref="B1:V123"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.8125" customWidth="1"/>
@@ -7082,7 +7085,7 @@
         <v>1.37</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" ref="J98:J129" si="3">E98/I98-1</f>
+        <f t="shared" ref="J98:J122" si="3">E98/I98-1</f>
         <v>0.50364963503649629</v>
       </c>
       <c r="K98" s="11">
@@ -8332,6 +8335,11 @@
       </c>
       <c r="R122" s="14">
         <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="B123" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/level2_screener.xlsx
+++ b/financial_models/level2_screener.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E8947E-6BEC-4455-81EE-842B869B9136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5920B884-133D-4BE3-A3C9-AFB142CF8099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F6774656-057E-A240-BF5A-628B92823BF8}"/>
   </bookViews>
   <sheets>
     <sheet name="hk_screener" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="427">
   <si>
     <t>Ticker</t>
   </si>
@@ -1302,6 +1302,84 @@
   </si>
   <si>
     <t>1810.HK</t>
+  </si>
+  <si>
+    <t>XIAOMI-W</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>DEO</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>Fair Isaac Corporation</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>lululemon athletica inc.</t>
+  </si>
+  <si>
+    <t>Salesforce, Inc.</t>
+  </si>
+  <si>
+    <t>Adobe Inc.</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>Autodesk, Inc.</t>
+  </si>
+  <si>
+    <t>United Parcel Service, Inc.</t>
+  </si>
+  <si>
+    <t>Diageo plc</t>
+  </si>
+  <si>
+    <t>Colgate-Palmolive Company</t>
+  </si>
+  <si>
+    <t>General Mills, Inc.</t>
+  </si>
+  <si>
+    <t>Procter &amp; Gamble Company (The)</t>
+  </si>
+  <si>
+    <t>Pepsico, Inc.</t>
   </si>
 </sst>
 </file>
@@ -1886,13 +1964,13 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>14.86</v>
+        <v>14.3</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7">
-        <v>261962481664</v>
+        <v>254252580864</v>
       </c>
       <c r="H2" s="6">
         <v>15.6</v>
@@ -1902,10 +1980,10 @@
       </c>
       <c r="J2" s="12">
         <f t="shared" ref="J2:J33" si="0">E2/I2-1</f>
-        <v>0.56092436974789917</v>
+        <v>0.50210084033613467</v>
       </c>
       <c r="K2" s="11">
-        <v>0.10430686406460297</v>
+        <v>0.10839160839160839</v>
       </c>
       <c r="L2" s="13">
         <v>70144988000</v>
@@ -1920,7 +1998,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P2" s="12">
-        <v>0.51114879571340921</v>
+        <v>0.53952035258055575</v>
       </c>
       <c r="Q2" s="12">
         <v>0.26042924055386191</v>
@@ -1940,13 +2018,13 @@
         <v>153</v>
       </c>
       <c r="E3">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7">
-        <v>2947656192</v>
+        <v>2866279168</v>
       </c>
       <c r="H3" s="6">
         <v>3.55</v>
@@ -1956,10 +2034,10 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" si="0"/>
-        <v>0.40517241379310343</v>
+        <v>0.36637931034482762</v>
       </c>
       <c r="K3" s="11">
-        <v>5.1840490797546018E-2</v>
+        <v>5.3312302839116726E-2</v>
       </c>
       <c r="L3" s="13">
         <v>504294000</v>
@@ -1974,7 +2052,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P3" s="12">
-        <v>0.31873642691061266</v>
+        <v>0.33485717376923463</v>
       </c>
       <c r="Q3" s="12">
         <v>0.29581628786323422</v>
@@ -1994,13 +2072,13 @@
         <v>148</v>
       </c>
       <c r="E4">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="7">
-        <v>9286770688</v>
+        <v>9174880256</v>
       </c>
       <c r="H4" s="6">
         <v>3.37</v>
@@ -2010,10 +2088,10 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>0.40677966101694918</v>
+        <v>0.37711864406779672</v>
       </c>
       <c r="K4" s="11">
-        <v>4.608433734939759E-2</v>
+        <v>4.7076923076923079E-2</v>
       </c>
       <c r="L4" s="13">
         <v>1871151000</v>
@@ -2028,7 +2106,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P4" s="12">
-        <v>0.39280200743904892</v>
+        <v>0.40163203393029273</v>
       </c>
       <c r="Q4" s="12">
         <v>0.28956319566547578</v>
@@ -2048,13 +2126,13 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <v>7.94</v>
+        <v>7.3</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="7">
-        <v>30982199296</v>
+        <v>28484892672</v>
       </c>
       <c r="H5" s="6">
         <v>8.35</v>
@@ -2064,10 +2142,10 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>0.88151658767772534</v>
+        <v>0.72985781990521326</v>
       </c>
       <c r="K5" s="11">
-        <v>5.4156171284634753E-3</v>
+        <v>5.8904109589041093E-3</v>
       </c>
       <c r="L5" s="13">
         <v>786762000</v>
@@ -2082,7 +2160,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P5" s="12">
-        <v>0.25738118152940009</v>
+        <v>0.28796473482648993</v>
       </c>
       <c r="Q5" s="12">
         <v>0.34518550887925997</v>
@@ -2102,13 +2180,13 @@
         <v>77</v>
       </c>
       <c r="E6">
-        <v>143.30000000000001</v>
+        <v>140.19999999999999</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7">
-        <v>94631452672</v>
+        <v>92584288256</v>
       </c>
       <c r="H6" s="6">
         <v>149.5</v>
@@ -2118,10 +2196,10 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>0.5747252747252749</v>
+        <v>0.54065934065934051</v>
       </c>
       <c r="K6" s="11">
-        <v>1.3607815771109559E-2</v>
+        <v>1.3908701854493581E-2</v>
       </c>
       <c r="L6" s="13">
         <v>2635100000</v>
@@ -2136,7 +2214,7 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P6" s="12">
-        <v>0.45654427812122245</v>
+        <v>0.47861242406875482</v>
       </c>
       <c r="Q6" s="12">
         <v>0.19894228627727803</v>
@@ -2156,13 +2234,13 @@
         <v>306</v>
       </c>
       <c r="E7">
-        <v>6.31</v>
+        <v>5.99</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7">
-        <v>397220184064</v>
+        <v>368051355648</v>
       </c>
       <c r="H7" s="6">
         <v>6.42</v>
@@ -2172,10 +2250,10 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>1.503968253968254</v>
+        <v>1.376984126984127</v>
       </c>
       <c r="K7" s="11">
-        <v>2.8526148969889066E-2</v>
+        <v>3.0050083472454088E-2</v>
       </c>
       <c r="L7" s="13">
         <v>72477000000</v>
@@ -2190,7 +2268,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P7" s="12">
-        <v>0.1814201404208311</v>
+        <v>0.19472801047260974</v>
       </c>
       <c r="Q7" s="12">
         <v>0.22694806719794586</v>
@@ -2210,13 +2288,13 @@
         <v>146</v>
       </c>
       <c r="E8">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="7">
-        <v>14967745536</v>
+        <v>14458638336</v>
       </c>
       <c r="H8" s="6">
         <v>3.12</v>
@@ -2226,10 +2304,10 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>0.31838565022421528</v>
+        <v>0.27354260089686089</v>
       </c>
       <c r="K8" s="11">
-        <v>0.10204081632653061</v>
+        <v>0.10563380281690141</v>
       </c>
       <c r="L8" s="13">
         <v>2527643000</v>
@@ -2244,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>0.34457473908992692</v>
+        <v>0.37027269802110113</v>
       </c>
       <c r="Q8" s="12">
         <v>0.15337570692947131</v>
@@ -2264,13 +2342,13 @@
         <v>225</v>
       </c>
       <c r="E9">
-        <v>17.04</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="7">
-        <v>149461073920</v>
+        <v>143688302592</v>
       </c>
       <c r="H9" s="6">
         <v>18.100000000000001</v>
@@ -2280,10 +2358,10 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>0.60754716981132062</v>
+        <v>0.54905660377358512</v>
       </c>
       <c r="K9" s="11">
-        <v>4.2194835680751178E-2</v>
+        <v>4.3788063337393414E-2</v>
       </c>
       <c r="L9" s="13">
         <v>21175963859.630001</v>
@@ -2298,13 +2376,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P9" s="12">
-        <v>0.19066142209904643</v>
+        <v>0.20041136778051782</v>
       </c>
       <c r="Q9" s="12">
         <v>0.20347556909712136</v>
       </c>
       <c r="R9" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.5">
@@ -2318,26 +2396,26 @@
         <v>304</v>
       </c>
       <c r="E10">
-        <v>9.34</v>
+        <v>8.9</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="7">
-        <v>217569705984</v>
+        <v>206957920256</v>
       </c>
       <c r="H10" s="6">
-        <v>9.5399999999999991</v>
+        <v>9.77</v>
       </c>
       <c r="I10" s="6">
         <v>4.58</v>
       </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>1.0393013100436681</v>
+        <v>0.94323144104803491</v>
       </c>
       <c r="K10" s="11">
-        <v>2.7301927194860815E-2</v>
+        <v>2.8651685393258425E-2</v>
       </c>
       <c r="L10" s="13">
         <v>29168443138.220001</v>
@@ -2352,13 +2430,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P10" s="12">
-        <v>0.14335768137381114</v>
+        <v>0.15071515945863481</v>
       </c>
       <c r="Q10" s="12">
         <v>0.2888078161719172</v>
       </c>
       <c r="R10" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.5">
@@ -2372,13 +2450,13 @@
         <v>223</v>
       </c>
       <c r="E11">
-        <v>2.23</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="7">
-        <v>2230000128</v>
+        <v>2280000000</v>
       </c>
       <c r="H11" s="6">
         <v>2.42</v>
@@ -2388,10 +2466,10 @@
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>0.65185185185185168</v>
+        <v>0.68888888888888866</v>
       </c>
       <c r="K11" s="11">
-        <v>9.417040358744394E-2</v>
+        <v>9.2105263157894746E-2</v>
       </c>
       <c r="L11" s="13">
         <v>315190000</v>
@@ -2406,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="12">
-        <v>0.13140345736333311</v>
+        <v>0.12872027486244422</v>
       </c>
       <c r="Q11" s="12">
         <v>0.51857007005524791</v>
@@ -2426,13 +2504,13 @@
         <v>301</v>
       </c>
       <c r="E12">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="7">
-        <v>3242942464</v>
+        <v>3001232384</v>
       </c>
       <c r="H12" s="6">
         <v>1.66</v>
@@ -2442,10 +2520,10 @@
       </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>0.42477876106194712</v>
+        <v>0.31858407079646023</v>
       </c>
       <c r="K12" s="11">
-        <v>7.3913043478260859E-2</v>
+        <v>7.986577181208053E-2</v>
       </c>
       <c r="L12" s="13">
         <v>929863000</v>
@@ -2460,13 +2538,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P12" s="12">
-        <v>0.32746184668900374</v>
+        <v>0.35581040620793974</v>
       </c>
       <c r="Q12" s="12">
         <v>0.15429118804462028</v>
       </c>
       <c r="R12" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.5">
@@ -2480,26 +2558,26 @@
         <v>87</v>
       </c>
       <c r="E13">
-        <v>4.71</v>
+        <v>4.58</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="7">
-        <v>42697326592</v>
+        <v>41518841856</v>
       </c>
       <c r="H13" s="6">
         <v>7.38</v>
       </c>
       <c r="I13" s="6">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>0.38938053097345127</v>
+        <v>0.327536231884058</v>
       </c>
       <c r="K13" s="11">
-        <v>6.5180467091295116E-2</v>
+        <v>6.7030567685589515E-2</v>
       </c>
       <c r="L13" s="13">
         <v>5594372000</v>
@@ -2514,13 +2592,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P13" s="12">
-        <v>0.17634184586825569</v>
+        <v>0.18269410771856107</v>
       </c>
       <c r="Q13" s="12">
         <v>0.20771406306691512</v>
       </c>
       <c r="R13" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.5">
@@ -2534,13 +2612,13 @@
         <v>301</v>
       </c>
       <c r="E14">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="7">
-        <v>1963447936</v>
+        <v>1951619968</v>
       </c>
       <c r="H14" s="6">
         <v>2.77</v>
@@ -2550,10 +2628,10 @@
       </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>0.22058823529411753</v>
+        <v>0.21323529411764697</v>
       </c>
       <c r="K14" s="11">
-        <v>3.6746987951807232E-2</v>
+        <v>3.6969696969696972E-2</v>
       </c>
       <c r="L14" s="13">
         <v>841215000</v>
@@ -2568,13 +2646,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P14" s="12">
-        <v>0.567382839661148</v>
+        <v>0.57165144975756232</v>
       </c>
       <c r="Q14" s="12">
         <v>0.14567921288909008</v>
       </c>
       <c r="R14" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.5">
@@ -2588,26 +2666,26 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>6.26</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="7">
-        <v>12406079488</v>
+        <v>12943677440</v>
       </c>
       <c r="H15" s="6">
-        <v>6</v>
+        <v>6.48</v>
       </c>
       <c r="I15" s="6">
         <v>3.15</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>0.90476190476190488</v>
+        <v>0.98730158730158735</v>
       </c>
       <c r="K15" s="11">
-        <v>4.1666666666666664E-2</v>
+        <v>3.9936102236421724E-2</v>
       </c>
       <c r="L15" s="13">
         <v>1576240000</v>
@@ -2622,13 +2700,13 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P15" s="12">
-        <v>0.20679153222118959</v>
+        <v>0.19398554039961488</v>
       </c>
       <c r="Q15" s="12">
         <v>0.16357040581906512</v>
       </c>
       <c r="R15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.5">
@@ -2642,26 +2720,26 @@
         <v>308</v>
       </c>
       <c r="E16">
-        <v>17.739999999999998</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="7">
-        <v>63757914112</v>
+        <v>61457743872</v>
       </c>
       <c r="H16" s="6">
-        <v>18.079999999999998</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="I16" s="6">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>1.3280839895013119</v>
+        <v>1.2265625000000004</v>
       </c>
       <c r="K16" s="11">
-        <v>1.9729425028184894E-2</v>
+        <v>2.0467836257309937E-2</v>
       </c>
       <c r="L16" s="13">
         <v>25585077000</v>
@@ -2676,13 +2754,13 @@
         <v>1</v>
       </c>
       <c r="P16" s="12">
-        <v>0.25208739729739288</v>
+        <v>0.25793302755094921</v>
       </c>
       <c r="Q16" s="12">
         <v>0.15251313559762292</v>
       </c>
       <c r="R16" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.5">
@@ -2696,13 +2774,13 @@
         <v>83</v>
       </c>
       <c r="E17">
-        <v>15.22</v>
+        <v>15.28</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7">
-        <v>31020034048</v>
+        <v>31877136384</v>
       </c>
       <c r="H17" s="6">
         <v>17.059999999999999</v>
@@ -2712,10 +2790,10 @@
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>0.9120603015075377</v>
+        <v>0.91959798994974862</v>
       </c>
       <c r="K17" s="11">
-        <v>7.3587385019710905E-2</v>
+        <v>7.3298429319371736E-2</v>
       </c>
       <c r="L17" s="13">
         <v>5451928473.2399998</v>
@@ -2730,7 +2808,7 @@
         <v>1.0683760683760684</v>
       </c>
       <c r="P17" s="12">
-        <v>0.16890223095168</v>
+        <v>0.16480616245160498</v>
       </c>
       <c r="Q17" s="12">
         <v>0.20973136925592797</v>
@@ -2750,13 +2828,13 @@
         <v>77</v>
       </c>
       <c r="E18">
-        <v>25.85</v>
+        <v>25.75</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7">
-        <v>68583669760</v>
+        <v>68318355456</v>
       </c>
       <c r="H18" s="6">
         <v>26.3</v>
@@ -2766,10 +2844,10 @@
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>0.64649681528662439</v>
+        <v>0.64012738853503182</v>
       </c>
       <c r="K18" s="11">
-        <v>1.0522243713733075E-2</v>
+        <v>1.0563106796116505E-2</v>
       </c>
       <c r="L18" s="13">
         <v>1069250000</v>
@@ -2784,13 +2862,13 @@
         <v>7.6923076923076916</v>
       </c>
       <c r="P18" s="12">
-        <v>0.12490940536069382</v>
+        <v>0.12541472763078063</v>
       </c>
       <c r="Q18" s="12">
         <v>0.41587371596437778</v>
       </c>
       <c r="R18" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.5">
@@ -2804,26 +2882,26 @@
         <v>87</v>
       </c>
       <c r="E19">
-        <v>8.1</v>
+        <v>7.97</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="7">
-        <v>103924621312</v>
+        <v>102256689152</v>
       </c>
       <c r="H19" s="6">
         <v>8